--- a/project_2/project2_project status(C2).xlsx
+++ b/project_2/project2_project status(C2).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pyostry\workspace\aiffel\ai-data-bootcamp\Project_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42D23758-A6CB-413A-823C-DAB0C3030AE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFCE2D5D-21CF-4640-AC74-F3A2D633218A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{5FF54064-7DDC-427B-93D7-EF78D75E5195}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="4" xr2:uid="{5FF54064-7DDC-427B-93D7-EF78D75E5195}"/>
   </bookViews>
   <sheets>
     <sheet name="제작 가이드라인" sheetId="12" r:id="rId1"/>
@@ -991,10 +991,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>오퍼 1건당 매출</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>순증 전환율</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1020,10 +1016,6 @@
   </si>
   <si>
     <t>Difficulty (평균 7.7)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>퍼널 3단계 전체에 적용 → 어떤 오퍼 속성이 어느 단계에서 이탈을 만드는지 분리해서 봄</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1050,11 +1042,6 @@
   <si>
     <t>01 북극성 지표: Tier A로 시작할지, 처음부터 Tier B(순증)로 갈지
 Tier A는 3~4단계로 바로 진입 가능하지만 함정을 안고 감. Tier B는 정확하지만 대조군/시점비교 설계가 먼저 필요.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>02 informational 오퍼의 "전환" 정의
-completed 이벤트가 없는 오퍼 타입을 노출 후 N일 내 transaction 발생으로 볼지, 아니면 퍼널을 노출 단계에서 끊고 별도로 다룰지.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1166,24 +1153,9 @@
     <t>측정 가능 여부</t>
   </si>
   <si>
-    <t>열람 후 완료 → 오퍼가 실제로 구매를 유도한 것이다</t>
-  </si>
-  <si>
-    <t>오퍼 열람율, 열람→완료 전환율</t>
-  </si>
-  <si>
-    <t>무열람 완료 → 오퍼 없이도 샀을 고객(Sure-thing)일 것이다</t>
-  </si>
-  <si>
     <t>Sure-thing 비율</t>
   </si>
   <si>
-    <t>오퍼를 받으면 재구매 텀이 짧아질 것이다</t>
-  </si>
-  <si>
-    <t>오퍼타입별 구매텀 단축률</t>
-  </si>
-  <si>
     <t>가능 (신규)</t>
   </si>
   <si>
@@ -1202,18 +1174,6 @@
     <t>할인형이 BOGO보다 완료율이 높을 것이다</t>
   </si>
   <si>
-    <t>오퍼유형별 완료율, 리워드 대비 ROI</t>
-  </si>
-  <si>
-    <t>오퍼타입별로 객단가가 다를 것이다</t>
-  </si>
-  <si>
-    <t>오퍼타입별 평균 거래액</t>
-  </si>
-  <si>
-    <t>리워드 허들이 낮으면 완료율이 높을 것이다</t>
-  </si>
-  <si>
     <t>난이도 구간별 완료율(회귀계수)</t>
   </si>
   <si>
@@ -1274,6 +1234,164 @@
   </si>
   <si>
     <t>프로모션 설계는 10개뿐이므로 보상·기간·난이도·채널 각각의 독립적인 효과를 강하게 단정하지 않는다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>05. AARRR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>04. 다음 결정이 필요한 지점</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>01. 북극성 지표 후보</t>
+  </si>
+  <si>
+    <t>03. 세그먼트 축 — 퍼널의 모든 단계를 가르는 절단면</t>
+  </si>
+  <si>
+    <t>6. 현재 측정하기 어려운 지표</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지표</t>
+  </si>
+  <si>
+    <t>측정이 어려운 이유</t>
+  </si>
+  <si>
+    <t>추가로 필요한 데이터</t>
+  </si>
+  <si>
+    <t>개별 채널의 직접 효과</t>
+  </si>
+  <si>
+    <t>실제로 어떤 채널에서 열람했는지 알 수 없음</t>
+  </si>
+  <si>
+    <t>채널별 노출·클릭 로그</t>
+  </si>
+  <si>
+    <t>프로모션의 정확한 구매 유발 효과</t>
+  </si>
+  <si>
+    <t>결제 기록에 프로모션 ID가 없음</t>
+  </si>
+  <si>
+    <t>결제별 프로모션 연결 정보 또는 대조군</t>
+  </si>
+  <si>
+    <t>정확한 ROI</t>
+  </si>
+  <si>
+    <t>프로모션 운영비와 상품 원가 정보가 없음</t>
+  </si>
+  <si>
+    <t>캠페인 비용·상품 원가·마진 데이터</t>
+  </si>
+  <si>
+    <t>장기 재구매 효과</t>
+  </si>
+  <si>
+    <t>관찰기간이 약 30일로 짧음</t>
+  </si>
+  <si>
+    <t>장기간 고객 행동 기록</t>
+  </si>
+  <si>
+    <t>7. 참고</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수신 후 완료율</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Tier B — 사용 불가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유효기간 내 완료된 offer(bogo, discount) 수
+÷ 발송된 offer(bogo, discount) 수 × 100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수신율</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>수신된 offer(bogo, discount) 수
+÷ 발송된 offer(bogo, discount) 수 × 100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>결제금액</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>transaction의 amount 합계</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Comment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시철, 서영</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>링크</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가설 트리의 각 가지를 AARRR 어느 단계 지표로 측정할지 매핑한다. HEART, GAME 등 다른 지표 설계 프레임워크를 적용할 수 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>offer 1건당 매출</t>
+  </si>
+  <si>
+    <t>02. offer 반응 퍼널</t>
+  </si>
+  <si>
+    <t>퍼널 3단계 전체에 적용 → 어떤 offer 속성이 어느 단계에서 이탈을 만드는지 분리해서 봄</t>
+  </si>
+  <si>
+    <t>02 informational offer의 "전환" 정의
+completed 이벤트가 없는 offer 타입을 노출 후 N일 내 transaction 발생으로 볼지, 아니면 퍼널을 노출 단계에서 끊고 별도로 다룰지.</t>
+  </si>
+  <si>
+    <t>수신 후 완료 → offer가 실제로 구매를 유도한 것이다</t>
+  </si>
+  <si>
+    <t>offer 열람율, 열람→완료 전환율</t>
+  </si>
+  <si>
+    <t>수신 미 완료 → offer 없이도 샀을 고객(Sure-thing)일 것이다</t>
+  </si>
+  <si>
+    <t>offer를 받으면 재구매 텀이 짧아질 것이다</t>
+  </si>
+  <si>
+    <t>offer 타입별로 객단가가 다를 것이다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Reward 허들이 낮으면 완료율이 높을 것이다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>offer 타입별 평균 거래액</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>offer 타입별 완료율, 리워드 대비 ROI</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>offer 타입별 구매텀 단축률</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1305,7 +1423,7 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
-      <t>전환매출</t>
+      <t>전환매출(</t>
     </r>
     <r>
       <rPr>
@@ -1314,7 +1432,7 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> ÷ </t>
+      <t xml:space="preserve">transaction) ÷ </t>
     </r>
     <r>
       <rPr>
@@ -1329,122 +1447,6 @@
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
-  <si>
-    <t>05. AARRR</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>04. 다음 결정이 필요한 지점</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>01. 북극성 지표 후보</t>
-  </si>
-  <si>
-    <t>02. 오퍼 반응 퍼널</t>
-  </si>
-  <si>
-    <t>03. 세그먼트 축 — 퍼널의 모든 단계를 가르는 절단면</t>
-  </si>
-  <si>
-    <t>6. 현재 측정하기 어려운 지표</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>지표</t>
-  </si>
-  <si>
-    <t>측정이 어려운 이유</t>
-  </si>
-  <si>
-    <t>추가로 필요한 데이터</t>
-  </si>
-  <si>
-    <t>개별 채널의 직접 효과</t>
-  </si>
-  <si>
-    <t>실제로 어떤 채널에서 열람했는지 알 수 없음</t>
-  </si>
-  <si>
-    <t>채널별 노출·클릭 로그</t>
-  </si>
-  <si>
-    <t>프로모션의 정확한 구매 유발 효과</t>
-  </si>
-  <si>
-    <t>결제 기록에 프로모션 ID가 없음</t>
-  </si>
-  <si>
-    <t>결제별 프로모션 연결 정보 또는 대조군</t>
-  </si>
-  <si>
-    <t>정확한 ROI</t>
-  </si>
-  <si>
-    <t>프로모션 운영비와 상품 원가 정보가 없음</t>
-  </si>
-  <si>
-    <t>캠페인 비용·상품 원가·마진 데이터</t>
-  </si>
-  <si>
-    <t>장기 재구매 효과</t>
-  </si>
-  <si>
-    <t>관찰기간이 약 30일로 짧음</t>
-  </si>
-  <si>
-    <t>장기간 고객 행동 기록</t>
-  </si>
-  <si>
-    <t>7. 참고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>수신 후 완료율</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Tier B — 사용 불가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>유효기간 내 완료된 offer(bogo, discount) 수
-÷ 발송된 offer(bogo, discount) 수 × 100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>수신율</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>수신된 offer(bogo, discount) 수
-÷ 발송된 offer(bogo, discount) 수 × 100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>결제금액</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>transaction의 amount 합계</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Comment</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>시철, 서영</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>링크</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>가설 트리의 각 가지를 AARRR 어느 단계 지표로 측정할지 매핑한다. HEART, GAME 등 다른 지표 설계 프레임워크를 적용할 수 있다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
 </sst>
 </file>
 
@@ -1454,7 +1456,7 @@
     <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="177" formatCode="[$-412]yyyy&quot;년&quot;\ m&quot;월&quot;\ d&quot;일&quot;\ dddd\ h&quot;시&quot;\ mm&quot;분&quot;"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1636,6 +1638,14 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="161"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -1939,7 +1949,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2138,6 +2148,21 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2157,9 +2182,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2183,17 +2205,8 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -11047,7 +11060,7 @@
     </row>
     <row r="35" spans="1:1" hidden="1" outlineLevel="2" x14ac:dyDescent="0.45">
       <c r="A35" s="20" t="s">
-        <v>318</v>
+        <v>304</v>
       </c>
     </row>
     <row r="36" spans="1:1" hidden="1" outlineLevel="2" x14ac:dyDescent="0.45">
@@ -11072,39 +11085,39 @@
         <v>193</v>
       </c>
     </row>
-    <row r="42" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A42" s="20" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="43" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A43" s="20" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="44" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A44" s="20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="45" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="46" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="46" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A46" s="22" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="47" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="48" spans="1:1" ht="21" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="48" spans="1:1" ht="21" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A48" s="23" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="21" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:3" ht="21" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A49" s="23" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="50" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A50" s="26"/>
       <c r="B50" s="17" t="s">
         <v>77</v>
@@ -11113,7 +11126,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="51" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A51" s="27" t="s">
         <v>79</v>
       </c>
@@ -11124,7 +11137,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="52" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A52" s="27" t="s">
         <v>82</v>
       </c>
@@ -11135,7 +11148,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="53" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A53" s="27" t="s">
         <v>85</v>
       </c>
@@ -11146,7 +11159,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="54" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A54" s="27" t="s">
         <v>88</v>
       </c>
@@ -11157,7 +11170,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="55" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A55" s="27" t="s">
         <v>91</v>
       </c>
@@ -11168,137 +11181,137 @@
         <v>93</v>
       </c>
     </row>
-    <row r="56" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="57" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="57" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A57" s="22" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="58" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A58" s="24" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="59" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="60" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="60" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A60" s="25" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="61" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A61" s="25" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="62" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A62" s="25" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="63" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A63" s="25" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="64" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A64" s="25" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="65" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A65" s="25" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="66" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A66" s="25" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="67" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A67" s="25" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="68" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A68" s="25" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="69" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A69" s="25" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="70" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A70" s="25" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="71" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A71" s="25" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="72" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A72" s="25" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="73" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A73" s="25" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="74" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="75" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="75" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A75" s="22" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A76" s="20" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="77" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A77" s="20" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="78" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A78" s="20" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="79" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="80" spans="1:1" ht="21" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="80" spans="1:1" ht="21" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A80" s="23" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="81" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A81" s="22" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="82" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A82" s="22" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="83" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A83" s="22" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="84" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A84" s="20" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="85" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="86" spans="1:1" ht="26" collapsed="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="86" spans="1:1" ht="26" x14ac:dyDescent="0.45">
       <c r="A86" s="21" t="s">
         <v>194</v>
       </c>
@@ -11589,7 +11602,7 @@
         <v>46274</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="34" x14ac:dyDescent="0.45">
@@ -11597,7 +11610,7 @@
         <v>174</v>
       </c>
       <c r="B3" s="56" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="C3" s="35">
         <v>46274</v>
@@ -11609,7 +11622,7 @@
         <v>172</v>
       </c>
       <c r="B4" s="56" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="C4" s="35">
         <v>46274</v>
@@ -11824,7 +11837,7 @@
         <v>14</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F7" s="14"/>
       <c r="G7" s="15"/>
@@ -11847,7 +11860,7 @@
         <v>36</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
@@ -11864,7 +11877,7 @@
       <c r="E9" s="5"/>
       <c r="F9" s="3"/>
       <c r="G9" s="10" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
@@ -11879,7 +11892,7 @@
         <v>14</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="11"/>
@@ -11913,7 +11926,7 @@
       <c r="E12" s="13"/>
       <c r="F12" s="14"/>
       <c r="G12" s="10" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
@@ -11930,11 +11943,11 @@
         <v>14</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F13" s="9"/>
       <c r="G13" s="10" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="64.5" thickBot="1" x14ac:dyDescent="0.5">
@@ -11957,7 +11970,7 @@
     <row r="15" spans="1:7" ht="64" x14ac:dyDescent="0.45">
       <c r="A15" s="64"/>
       <c r="B15" s="4" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>45</v>
@@ -11966,13 +11979,13 @@
         <v>13</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>41</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
@@ -11989,7 +12002,7 @@
       <c r="E16" s="13"/>
       <c r="F16" s="14"/>
       <c r="G16" s="42" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
     </row>
   </sheetData>
@@ -12091,7 +12104,7 @@
         <v>197</v>
       </c>
       <c r="D1" s="40" t="s">
-        <v>315</v>
+        <v>301</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
@@ -12102,10 +12115,10 @@
         <v>198</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D2" s="50" t="s">
-        <v>316</v>
+        <v>302</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="64" x14ac:dyDescent="0.45">
@@ -12113,7 +12126,7 @@
         <v>190</v>
       </c>
       <c r="B3" s="46" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C3" s="37" t="s">
         <v>199</v>
@@ -12123,86 +12136,86 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A5" s="73" t="s">
-        <v>288</v>
-      </c>
-      <c r="B5" s="73"/>
-      <c r="C5" s="73"/>
+      <c r="A5" s="67" t="s">
+        <v>275</v>
+      </c>
+      <c r="B5" s="67"/>
+      <c r="C5" s="67"/>
     </row>
     <row r="6" spans="1:4" ht="32" x14ac:dyDescent="0.45">
-      <c r="A6" s="75" t="s">
+      <c r="A6" s="79" t="s">
         <v>205</v>
       </c>
       <c r="B6" s="47" t="s">
         <v>206</v>
       </c>
       <c r="C6" s="48" t="s">
-        <v>310</v>
+        <v>296</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="32" x14ac:dyDescent="0.45">
-      <c r="A7" s="76"/>
+      <c r="A7" s="80"/>
       <c r="B7" s="47" t="s">
-        <v>308</v>
+        <v>294</v>
       </c>
       <c r="C7" s="48" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="32" x14ac:dyDescent="0.45">
-      <c r="A8" s="76"/>
+      <c r="A8" s="80"/>
       <c r="B8" s="47" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="C8" s="48" t="s">
-        <v>312</v>
+        <v>298</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A9" s="76"/>
+      <c r="A9" s="80"/>
       <c r="B9" s="47" t="s">
-        <v>207</v>
-      </c>
-      <c r="C9" s="48" t="s">
-        <v>285</v>
+        <v>305</v>
+      </c>
+      <c r="C9" s="85" t="s">
+        <v>318</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A10" s="77"/>
+      <c r="A10" s="81"/>
       <c r="B10" s="47" t="s">
-        <v>313</v>
+        <v>299</v>
       </c>
       <c r="C10" s="48" t="s">
-        <v>314</v>
+        <v>300</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" s="54" t="s">
-        <v>309</v>
+        <v>295</v>
       </c>
       <c r="B11" s="47" t="s">
+        <v>207</v>
+      </c>
+      <c r="C11" s="48" t="s">
         <v>208</v>
-      </c>
-      <c r="C11" s="48" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.45">
       <c r="C12" s="49"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A13" s="67" t="s">
-        <v>289</v>
-      </c>
-      <c r="B13" s="68"/>
-      <c r="C13" s="69"/>
+      <c r="A13" s="72" t="s">
+        <v>306</v>
+      </c>
+      <c r="B13" s="73"/>
+      <c r="C13" s="74"/>
     </row>
     <row r="14" spans="1:4" ht="52" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="78" t="s">
-        <v>235</v>
-      </c>
-      <c r="B14" s="79"/>
-      <c r="C14" s="80"/>
+      <c r="A14" s="82" t="s">
+        <v>232</v>
+      </c>
+      <c r="B14" s="83"/>
+      <c r="C14" s="84"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="49"/>
@@ -12210,452 +12223,440 @@
       <c r="D19" s="49"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A31" s="73" t="s">
-        <v>290</v>
-      </c>
-      <c r="B31" s="73"/>
-      <c r="C31" s="73"/>
+      <c r="A31" s="67" t="s">
+        <v>276</v>
+      </c>
+      <c r="B31" s="67"/>
+      <c r="C31" s="67"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A32" s="70" t="s">
+      <c r="A32" s="75" t="s">
+        <v>209</v>
+      </c>
+      <c r="B32" s="76"/>
+      <c r="C32" s="77"/>
+    </row>
+    <row r="33" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="71" t="s">
+        <v>233</v>
+      </c>
+      <c r="B33" s="50" t="s">
         <v>210</v>
       </c>
-      <c r="B32" s="71"/>
-      <c r="C32" s="72"/>
-    </row>
-    <row r="33" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="66" t="s">
-        <v>236</v>
-      </c>
-      <c r="B33" s="50" t="s">
+      <c r="C33" s="78" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A34" s="71"/>
+      <c r="B34" s="50" t="s">
         <v>211</v>
       </c>
-      <c r="C33" s="74" t="s">
+      <c r="C34" s="78"/>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A35" s="71"/>
+      <c r="B35" s="50" t="s">
+        <v>212</v>
+      </c>
+      <c r="C35" s="78"/>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A36" s="71"/>
+      <c r="B36" s="50" t="s">
+        <v>213</v>
+      </c>
+      <c r="C36" s="78"/>
+    </row>
+    <row r="37" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+      <c r="A37" s="71"/>
+      <c r="B37" s="48" t="s">
+        <v>214</v>
+      </c>
+      <c r="C37" s="78"/>
+    </row>
+    <row r="38" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="71" t="s">
+        <v>234</v>
+      </c>
+      <c r="B38" s="50" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A34" s="66"/>
-      <c r="B34" s="50" t="s">
-        <v>212</v>
-      </c>
-      <c r="C34" s="74"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A35" s="66"/>
-      <c r="B35" s="50" t="s">
-        <v>213</v>
-      </c>
-      <c r="C35" s="74"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A36" s="66"/>
-      <c r="B36" s="50" t="s">
-        <v>214</v>
-      </c>
-      <c r="C36" s="74"/>
-    </row>
-    <row r="37" spans="1:5" ht="32" x14ac:dyDescent="0.45">
-      <c r="A37" s="66"/>
-      <c r="B37" s="48" t="s">
+      <c r="C38" s="78" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A39" s="71"/>
+      <c r="B39" s="50" t="s">
         <v>216</v>
       </c>
-      <c r="C37" s="74"/>
-    </row>
-    <row r="38" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="66" t="s">
-        <v>237</v>
-      </c>
-      <c r="B38" s="50" t="s">
+      <c r="C39" s="78"/>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A40" s="71"/>
+      <c r="B40" s="50" t="s">
         <v>217</v>
       </c>
-      <c r="C38" s="74" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A39" s="66"/>
-      <c r="B39" s="50" t="s">
-        <v>218</v>
-      </c>
-      <c r="C39" s="74"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A40" s="66"/>
-      <c r="B40" s="50" t="s">
+      <c r="C40" s="78"/>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A42" s="72" t="s">
+        <v>274</v>
+      </c>
+      <c r="B42" s="73"/>
+      <c r="C42" s="74"/>
+    </row>
+    <row r="43" spans="1:5" ht="53" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A43" s="71" t="s">
         <v>219</v>
       </c>
-      <c r="C40" s="74"/>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A42" s="67" t="s">
-        <v>287</v>
-      </c>
-      <c r="B42" s="68"/>
-      <c r="C42" s="69"/>
-    </row>
-    <row r="43" spans="1:5" ht="53" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A43" s="66" t="s">
-        <v>221</v>
-      </c>
-      <c r="B43" s="66"/>
-      <c r="C43" s="66"/>
+      <c r="B43" s="71"/>
+      <c r="C43" s="71"/>
     </row>
     <row r="44" spans="1:5" ht="50.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A44" s="66" t="s">
-        <v>222</v>
-      </c>
-      <c r="B44" s="66"/>
-      <c r="C44" s="66"/>
+      <c r="A44" s="71" t="s">
+        <v>308</v>
+      </c>
+      <c r="B44" s="71"/>
+      <c r="C44" s="71"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A46" s="73" t="s">
-        <v>286</v>
-      </c>
-      <c r="B46" s="73"/>
-      <c r="C46" s="73"/>
-      <c r="D46" s="73"/>
-      <c r="E46" s="73"/>
+      <c r="A46" s="67" t="s">
+        <v>273</v>
+      </c>
+      <c r="B46" s="67"/>
+      <c r="C46" s="67"/>
+      <c r="D46" s="67"/>
+      <c r="E46" s="67"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" s="44" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B47" s="44" t="s">
+        <v>244</v>
+      </c>
+      <c r="C47" s="44" t="s">
+        <v>245</v>
+      </c>
+      <c r="D47" s="44" t="s">
+        <v>246</v>
+      </c>
+      <c r="E47" s="44" t="s">
         <v>247</v>
-      </c>
-      <c r="C47" s="44" t="s">
-        <v>248</v>
-      </c>
-      <c r="D47" s="44" t="s">
-        <v>249</v>
-      </c>
-      <c r="E47" s="44" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="32" x14ac:dyDescent="0.45">
       <c r="A48" s="43" t="s">
-        <v>251</v>
+        <v>309</v>
       </c>
       <c r="B48" s="43" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C48" s="43" t="s">
-        <v>252</v>
+        <v>310</v>
       </c>
       <c r="D48" s="43" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="E48" s="43" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="32" x14ac:dyDescent="0.45">
       <c r="A49" s="43" t="s">
-        <v>253</v>
+        <v>311</v>
       </c>
       <c r="B49" s="43" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C49" s="43" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="D49" s="43" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="E49" s="43" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="48" x14ac:dyDescent="0.45">
       <c r="A50" s="43" t="s">
-        <v>255</v>
+        <v>312</v>
       </c>
       <c r="B50" s="43" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C50" s="43" t="s">
-        <v>256</v>
+        <v>317</v>
       </c>
       <c r="D50" s="43" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="E50" s="43" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="32" x14ac:dyDescent="0.45">
       <c r="A51" s="43" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="B51" s="43" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C51" s="43" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="D51" s="43" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E51" s="43" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="32" x14ac:dyDescent="0.45">
       <c r="A52" s="43" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="B52" s="43" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C52" s="43" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="D52" s="43" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="E52" s="43" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="32" x14ac:dyDescent="0.45">
       <c r="A53" s="43" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="B53" s="43" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C53" s="43" t="s">
-        <v>263</v>
+        <v>316</v>
       </c>
       <c r="D53" s="43" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E53" s="43" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" s="43" t="s">
-        <v>264</v>
+        <v>313</v>
       </c>
       <c r="B54" s="43" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C54" s="43" t="s">
-        <v>265</v>
+        <v>315</v>
       </c>
       <c r="D54" s="43" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="E54" s="43" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="32" x14ac:dyDescent="0.45">
       <c r="A55" s="43" t="s">
-        <v>266</v>
+        <v>314</v>
       </c>
       <c r="B55" s="43" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C55" s="43" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
       <c r="D55" s="43" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="E55" s="43" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="48" x14ac:dyDescent="0.45">
       <c r="A56" s="43"/>
       <c r="B56" s="43" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="C56" s="43" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="D56" s="43" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
       <c r="E56" s="51" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="48" x14ac:dyDescent="0.45">
       <c r="A57" s="43"/>
       <c r="B57" s="43" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="C57" s="43" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="D57" s="43" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="E57" s="51" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A59" s="82" t="s">
-        <v>291</v>
-      </c>
-      <c r="B59" s="83"/>
-      <c r="C59" s="84"/>
+      <c r="A59" s="68" t="s">
+        <v>277</v>
+      </c>
+      <c r="B59" s="69"/>
+      <c r="C59" s="70"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" s="53" t="s">
-        <v>292</v>
+        <v>278</v>
       </c>
       <c r="B60" s="53" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="C60" s="53" t="s">
-        <v>294</v>
+        <v>280</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="32" x14ac:dyDescent="0.45">
       <c r="A61" s="52" t="s">
-        <v>295</v>
+        <v>281</v>
       </c>
       <c r="B61" s="52" t="s">
-        <v>296</v>
+        <v>282</v>
       </c>
       <c r="C61" s="52" t="s">
-        <v>297</v>
+        <v>283</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="32" x14ac:dyDescent="0.45">
       <c r="A62" s="52" t="s">
-        <v>298</v>
+        <v>284</v>
       </c>
       <c r="B62" s="52" t="s">
-        <v>299</v>
+        <v>285</v>
       </c>
       <c r="C62" s="52" t="s">
-        <v>300</v>
+        <v>286</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="32" x14ac:dyDescent="0.45">
       <c r="A63" s="52" t="s">
-        <v>301</v>
+        <v>287</v>
       </c>
       <c r="B63" s="52" t="s">
-        <v>302</v>
+        <v>288</v>
       </c>
       <c r="C63" s="52" t="s">
-        <v>303</v>
+        <v>289</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A64" s="52" t="s">
-        <v>304</v>
+        <v>290</v>
       </c>
       <c r="B64" s="52" t="s">
-        <v>305</v>
+        <v>291</v>
       </c>
       <c r="C64" s="52" t="s">
-        <v>306</v>
+        <v>292</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A66" s="73" t="s">
-        <v>307</v>
-      </c>
-      <c r="B66" s="73"/>
-      <c r="C66" s="73"/>
-      <c r="D66" s="73"/>
+      <c r="A66" s="67" t="s">
+        <v>293</v>
+      </c>
+      <c r="B66" s="67"/>
+      <c r="C66" s="67"/>
+      <c r="D66" s="67"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A67" s="81" t="s">
-        <v>276</v>
-      </c>
-      <c r="B67" s="81"/>
-      <c r="C67" s="81"/>
-      <c r="D67" s="81"/>
+      <c r="A67" s="66" t="s">
+        <v>264</v>
+      </c>
+      <c r="B67" s="66"/>
+      <c r="C67" s="66"/>
+      <c r="D67" s="66"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A68" s="81" t="s">
-        <v>277</v>
-      </c>
-      <c r="B68" s="81"/>
-      <c r="C68" s="81"/>
-      <c r="D68" s="81"/>
+      <c r="A68" s="66" t="s">
+        <v>265</v>
+      </c>
+      <c r="B68" s="66"/>
+      <c r="C68" s="66"/>
+      <c r="D68" s="66"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A69" s="81" t="s">
-        <v>278</v>
-      </c>
-      <c r="B69" s="81"/>
-      <c r="C69" s="81"/>
-      <c r="D69" s="81"/>
+      <c r="A69" s="66" t="s">
+        <v>266</v>
+      </c>
+      <c r="B69" s="66"/>
+      <c r="C69" s="66"/>
+      <c r="D69" s="66"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A70" s="81" t="s">
-        <v>279</v>
-      </c>
-      <c r="B70" s="81"/>
-      <c r="C70" s="81"/>
-      <c r="D70" s="81"/>
+      <c r="A70" s="66" t="s">
+        <v>267</v>
+      </c>
+      <c r="B70" s="66"/>
+      <c r="C70" s="66"/>
+      <c r="D70" s="66"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A71" s="81" t="s">
-        <v>280</v>
-      </c>
-      <c r="B71" s="81"/>
-      <c r="C71" s="81"/>
-      <c r="D71" s="81"/>
+      <c r="A71" s="66" t="s">
+        <v>268</v>
+      </c>
+      <c r="B71" s="66"/>
+      <c r="C71" s="66"/>
+      <c r="D71" s="66"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A72" s="81" t="s">
-        <v>281</v>
-      </c>
-      <c r="B72" s="81"/>
-      <c r="C72" s="81"/>
-      <c r="D72" s="81"/>
+      <c r="A72" s="66" t="s">
+        <v>269</v>
+      </c>
+      <c r="B72" s="66"/>
+      <c r="C72" s="66"/>
+      <c r="D72" s="66"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A73" s="81" t="s">
-        <v>282</v>
-      </c>
-      <c r="B73" s="81"/>
-      <c r="C73" s="81"/>
-      <c r="D73" s="81"/>
+      <c r="A73" s="66" t="s">
+        <v>270</v>
+      </c>
+      <c r="B73" s="66"/>
+      <c r="C73" s="66"/>
+      <c r="D73" s="66"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A74" s="81" t="s">
-        <v>283</v>
-      </c>
-      <c r="B74" s="81"/>
-      <c r="C74" s="81"/>
-      <c r="D74" s="81"/>
+      <c r="A74" s="66" t="s">
+        <v>271</v>
+      </c>
+      <c r="B74" s="66"/>
+      <c r="C74" s="66"/>
+      <c r="D74" s="66"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A75" s="81" t="s">
-        <v>284</v>
-      </c>
-      <c r="B75" s="81"/>
-      <c r="C75" s="81"/>
-      <c r="D75" s="81"/>
+      <c r="A75" s="66" t="s">
+        <v>272</v>
+      </c>
+      <c r="B75" s="66"/>
+      <c r="C75" s="66"/>
+      <c r="D75" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A73:D73"/>
-    <mergeCell ref="A74:D74"/>
-    <mergeCell ref="A75:D75"/>
-    <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A66:D66"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A67:D67"/>
-    <mergeCell ref="A68:D68"/>
-    <mergeCell ref="A69:D69"/>
-    <mergeCell ref="A70:D70"/>
-    <mergeCell ref="A71:D71"/>
-    <mergeCell ref="A72:D72"/>
     <mergeCell ref="A44:C44"/>
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="A32:C32"/>
@@ -12669,6 +12670,18 @@
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="A74:D74"/>
+    <mergeCell ref="A75:D75"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A67:D67"/>
+    <mergeCell ref="A68:D68"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="A70:D70"/>
+    <mergeCell ref="A71:D71"/>
+    <mergeCell ref="A72:D72"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/project_2/project2_project status(C2).xlsx
+++ b/project_2/project2_project status(C2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pyostry\workspace\aiffel\ai-data-bootcamp\Project_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFCE2D5D-21CF-4640-AC74-F3A2D633218A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B936071-473E-44CD-B83E-F8E4B0D93394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="4" xr2:uid="{5FF54064-7DDC-427B-93D7-EF78D75E5195}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="321">
   <si>
     <t>reward</t>
   </si>
@@ -999,10 +999,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1단계 가설 트리의 두 갈래를 그대로 퍼널 절단 기준으로 씁니다. 노출율·조건부전환율·전체완료율 세 지표 모두 이 두 축으로 나눠 봅니다.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Offer type</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1357,10 +1353,6 @@
   </si>
   <si>
     <t>퍼널 3단계 전체에 적용 → 어떤 offer 속성이 어느 단계에서 이탈을 만드는지 분리해서 봄</t>
-  </si>
-  <si>
-    <t>02 informational offer의 "전환" 정의
-completed 이벤트가 없는 offer 타입을 노출 후 N일 내 transaction 발생으로 볼지, 아니면 퍼널을 노출 단계에서 끊고 별도로 다룰지.</t>
   </si>
   <si>
     <t>수신 후 완료 → offer가 실제로 구매를 유도한 것이다</t>
@@ -1445,6 +1437,23 @@
       </rPr>
       <t>발송건수</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시철, 서영, 서현</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>시철, 서영</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>02 informational offer의 "완료" 정의
+completed 이벤트가 없는 offer 타입을 수신 후 N일 내 transaction 발생으로 볼지, 아니면 퍼널을 수신 단계에서 끊고 별도로 다룰지.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1단계 가설 트리의 두 갈래를 그대로 퍼널 절단 기준으로 씁니다. 수신율·조건부 완료율·전체완료율 세 지표 모두 이 두 축으로 나눠 봅니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2121,6 +2130,9 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2148,21 +2160,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2182,6 +2179,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2205,8 +2205,17 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2973,7 +2982,3141 @@
 </dgm:colorsDef>
 </file>
 
+<file path=xl/diagrams/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<dgm:colorsDef xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uniqueId="urn:microsoft.com/office/officeart/2005/8/colors/accent6_2">
+  <dgm:title val=""/>
+  <dgm:desc val=""/>
+  <dgm:catLst>
+    <dgm:cat type="accent6" pri="11200"/>
+  </dgm:catLst>
+  <dgm:styleLbl name="node0">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="node1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="alignNode1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="lnNode1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="vennNode1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:alpha val="50000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="node2">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="node3">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="node4">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgImgPlace1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:tint val="50000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="alignImgPlace1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:tint val="50000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="bgImgPlace1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:tint val="50000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="sibTrans2D1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:tint val="60000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:tint val="60000"/>
+      </a:schemeClr>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgSibTrans2D1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:tint val="60000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:tint val="60000"/>
+      </a:schemeClr>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="bgSibTrans2D1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:tint val="60000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:tint val="60000"/>
+      </a:schemeClr>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="sibTrans1D1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="tx1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="callout">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:tint val="50000"/>
+      </a:schemeClr>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="tx1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="asst0">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="asst1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="asst2">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="asst3">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="asst4">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst/>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans2D1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:tint val="60000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:tint val="60000"/>
+      </a:schemeClr>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans2D2">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans2D3">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans2D4">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans1D1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:shade val="60000"/>
+      </a:schemeClr>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="tx1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans1D2">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:shade val="60000"/>
+      </a:schemeClr>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="tx1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans1D3">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:shade val="80000"/>
+      </a:schemeClr>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="tx1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans1D4">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:shade val="80000"/>
+      </a:schemeClr>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="tx1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgAcc1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="lt1">
+        <a:alpha val="90000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="conFgAcc1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="lt1">
+        <a:alpha val="90000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="alignAcc1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="lt1">
+        <a:alpha val="90000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="trAlignAcc1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="lt1">
+        <a:alpha val="40000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="bgAcc1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="lt1">
+        <a:alpha val="90000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="solidFgAcc1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="solidAlignAcc1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="solidBgAcc1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgAccFollowNode1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:alpha val="90000"/>
+        <a:tint val="40000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:alpha val="90000"/>
+        <a:tint val="40000"/>
+      </a:schemeClr>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="alignAccFollowNode1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:alpha val="90000"/>
+        <a:tint val="40000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:alpha val="90000"/>
+        <a:tint val="40000"/>
+      </a:schemeClr>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="bgAccFollowNode1">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:alpha val="90000"/>
+        <a:tint val="40000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:alpha val="90000"/>
+        <a:tint val="40000"/>
+      </a:schemeClr>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgAcc0">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="lt1">
+        <a:alpha val="90000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgAcc2">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="lt1">
+        <a:alpha val="90000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgAcc3">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="lt1">
+        <a:alpha val="90000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgAcc4">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="lt1">
+        <a:alpha val="90000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="bgShp">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:tint val="40000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="dkBgShp">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:shade val="80000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="trBgShp">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:tint val="50000"/>
+        <a:alpha val="40000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="accent6"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgShp">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="accent6">
+        <a:tint val="60000"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="lt1"/>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="dk1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="revTx">
+    <dgm:fillClrLst meth="repeat">
+      <a:schemeClr val="lt1">
+        <a:alpha val="0"/>
+      </a:schemeClr>
+    </dgm:fillClrLst>
+    <dgm:linClrLst meth="repeat">
+      <a:schemeClr val="dk1">
+        <a:alpha val="0"/>
+      </a:schemeClr>
+    </dgm:linClrLst>
+    <dgm:effectClrLst/>
+    <dgm:txLinClrLst/>
+    <dgm:txFillClrLst meth="repeat">
+      <a:schemeClr val="tx1"/>
+    </dgm:txFillClrLst>
+    <dgm:txEffectClrLst/>
+  </dgm:styleLbl>
+</dgm:colorsDef>
+</file>
+
 <file path=xl/diagrams/data1.xml><?xml version="1.0" encoding="utf-8"?>
+<dgm:dataModel xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <dgm:ptLst>
+    <dgm:pt modelId="{88FEBD44-95B4-432B-B0FC-B98161E3F20C}" type="doc">
+      <dgm:prSet loTypeId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2" loCatId="hierarchy" qsTypeId="urn:microsoft.com/office/officeart/2005/8/quickstyle/simple1" qsCatId="simple" csTypeId="urn:microsoft.com/office/officeart/2005/8/colors/accent6_2" csCatId="accent6" phldr="1"/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{D28EA82C-9573-422A-B949-9F47D5EA00C0}">
+      <dgm:prSet phldrT="[텍스트]" custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1">
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Offer(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>행사</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" i="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>설계에 따라 주문 완료율의 차이가 있는가</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{8FA42352-D834-44A6-A154-3CB76BE81B68}" type="parTrans" cxnId="{3F4922AB-4BCF-4C3F-BDDB-346BCDC296AB}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="4000" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{71F878CA-1A36-404F-978F-D8724DEDCCAF}" type="sibTrans" cxnId="{3F4922AB-4BCF-4C3F-BDDB-346BCDC296AB}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="4000" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{BAD7D27F-CDF5-4751-8931-8050F17DA501}">
+      <dgm:prSet phldrT="[텍스트]" custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Offer type</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{A0B55608-A4DF-4F07-AF6C-C6F0A73452F0}" type="parTrans" cxnId="{66D4E714-31E6-4954-A82A-B5A60F0C6BA7}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{33CA151E-3B69-4314-B123-3297DFC7D670}" type="sibTrans" cxnId="{66D4E714-31E6-4954-A82A-B5A60F0C6BA7}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="4000" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{111C26C2-0F68-4BE1-8C76-558F1B44A0DF}">
+      <dgm:prSet phldrT="[텍스트]" custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Reward</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{0A6C6A19-7DE5-478D-8FB1-EB8E7418F39D}" type="parTrans" cxnId="{1656E178-28D2-4281-83AE-77EE7CA41B4C}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{E023194C-F95D-4763-92F5-F1ECD4BC9C73}" type="sibTrans" cxnId="{1656E178-28D2-4281-83AE-77EE7CA41B4C}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="4000" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{8FB65972-A8FD-4108-86AC-8A3B3296241B}">
+      <dgm:prSet phldrT="[텍스트]" custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Reward</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>가 평균</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(4.2)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> 보다 높은 경우</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>,</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> 낮은 경우보다 완료율이 높을 것이다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{A053B034-DC2F-4DD0-B5B2-98F1296693EF}" type="parTrans" cxnId="{C31D5CA3-AC5A-423C-99A3-985CE8E3D2CE}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{B9BFC1E1-36FA-4DFA-A7FB-937425619DD8}" type="sibTrans" cxnId="{C31D5CA3-AC5A-423C-99A3-985CE8E3D2CE}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="4000" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{590C90E1-6DC6-4F7C-B608-A2B2336F2B00}">
+      <dgm:prSet phldrT="[텍스트]" custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>완료율은 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>discount &gt; bogo &gt; information </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>순으로 높을 것이다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{B0E34315-446D-43CA-9C1A-43AC03C7FA4E}" type="sibTrans" cxnId="{2FD81CA3-1E57-4F8C-AF6C-72CC43E05195}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="4000" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{4FE8AF39-819D-45D6-81C9-F2B354274064}" type="parTrans" cxnId="{2FD81CA3-1E57-4F8C-AF6C-72CC43E05195}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{CB5507C6-5818-40A7-BD49-1000BD011A9B}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Duration(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>기간</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{BD9F1B93-0ABC-4B77-95B3-1DB7C4CB2918}" type="parTrans" cxnId="{C5516619-C5B2-4288-84CD-67C055A97476}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{05412BF9-284B-4F1C-86AC-AF524BDD7D14}" type="sibTrans" cxnId="{C5516619-C5B2-4288-84CD-67C055A97476}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="4000" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{5E0D9290-77BE-490F-8462-B30D1FA58D8B}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Duration</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>이 평균</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(6.7)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>보다 높은 경우</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>낮은 경우보다 완료율이 높을 것이다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{3469793B-2EFB-4C9D-A053-78B2C324DBC1}" type="parTrans" cxnId="{F7115254-B2DB-4711-9B96-1797D64046C8}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{827A2A25-BF22-45D1-8C10-6D340F70C6A1}" type="sibTrans" cxnId="{F7115254-B2DB-4711-9B96-1797D64046C8}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="4000" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{3E881757-362F-489E-B630-0D8A32984B2B}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Channels</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{3DB36DA8-7484-4811-81A8-5926BB1B2E09}" type="parTrans" cxnId="{8CEC1554-B055-464F-AC47-FCFB34B80966}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{278E719C-4D84-4910-9C25-3DCD78815614}" type="sibTrans" cxnId="{8CEC1554-B055-464F-AC47-FCFB34B80966}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="4000" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{6AAA0E55-4800-4C4F-82AE-D951A95A6406}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Web</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>이 포함되어 있는 경우 완료율은 높아지지 않을 것이다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{C6CBFA23-E16E-4404-82E5-1AD7E38B3BD0}" type="parTrans" cxnId="{7BB5B180-6C85-4AD5-A51A-F3D1DBE6B7D9}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{213EC674-33B2-46B5-97B4-B78DD7CC6633}" type="sibTrans" cxnId="{7BB5B180-6C85-4AD5-A51A-F3D1DBE6B7D9}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="4000" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{26FF4984-A8FB-481E-B952-91DAFB5870E3}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Mobile</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>이 포함되어 있는 경우 포함되지 않은 경우보다 완료율이 높을 것이다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{3D2CC029-AC34-412D-A670-9D22EF25DA78}" type="parTrans" cxnId="{57FC0E72-DB14-4028-8299-0FF8C7177C5C}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{DE75E50D-DFA6-418B-9C06-95A5C3944847}" type="sibTrans" cxnId="{57FC0E72-DB14-4028-8299-0FF8C7177C5C}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="4000" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{C2DA3B5A-4288-4EA2-AC91-4F8B0C844A32}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Social</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>이 포함되어 있는 경우 포함되지 않은 경우보다 완료율이 높을 것이다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{224B5B07-5A27-4D67-B5C9-B95010D5C5A9}" type="parTrans" cxnId="{4E3A3AD6-8FD2-4BA3-AC8C-7F9CF3D587F7}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{81FA6521-2044-4D8B-A3F2-96C820EAF9F1}" type="sibTrans" cxnId="{4E3A3AD6-8FD2-4BA3-AC8C-7F9CF3D587F7}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="4000" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{C9187AAC-B0F0-4EDA-B360-D95444C1095C}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>email</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>이 포함되어 있는 경우 완료율은 높아지지 않을 것이다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{336D58B7-98DD-484F-996F-4A6B86B1D8F7}" type="parTrans" cxnId="{8C4A7307-2CD9-4D4B-B2EB-D69B2D3FE10B}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{D56ED9E6-07E6-476D-B72A-1DAC45654595}" type="sibTrans" cxnId="{8C4A7307-2CD9-4D4B-B2EB-D69B2D3FE10B}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="4000" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{17CAE9F0-2C16-460C-A0EF-CF983A8E5B95}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Difficulty</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{349EE8AE-E5A3-4960-8F4D-2C9AC7DAFBEF}" type="parTrans" cxnId="{4E1C2DAE-C050-4639-9A7A-2B8E19863364}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{B5F3BFB9-0C8D-4ED3-BB39-6E65AD6E6202}" type="sibTrans" cxnId="{4E1C2DAE-C050-4639-9A7A-2B8E19863364}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="4000"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{F145AA98-6443-4870-A7B4-EC590B09FF29}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Difficulty</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>가 평균</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(7.7) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>보다 높은 경우 낮은 경우보다 완료율이 낮을 것이다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{61B28454-54A2-4A23-B946-6072BC34D484}" type="parTrans" cxnId="{B1B80D9C-040C-4053-BD9A-8F2DDEC78F29}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{F87A8A7F-0D3D-4479-81E7-4B421A7751B7}" type="sibTrans" cxnId="{B1B80D9C-040C-4053-BD9A-8F2DDEC78F29}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="4000"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{D4EC9180-298D-4A0A-93FF-1513D3D77023}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Profile(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>고객 정보</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>에 따라 주문 완료율이 다를 것이다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+            <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{FF7B4EF7-F173-446C-B7FC-76DF9BD7C3B7}" type="parTrans" cxnId="{94CE50DD-5A01-4009-B770-500D579F6261}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="3600"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{59629897-8AC3-4B42-ABE4-2D4F4203E3F5}" type="sibTrans" cxnId="{94CE50DD-5A01-4009-B770-500D579F6261}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="3600"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{46DB12B3-6FCD-4174-A9CD-456ED4B290FA}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>성별</a:t>
+          </a:r>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{CB5802DA-6B24-4C3B-AF82-CA0F64937596}" type="parTrans" cxnId="{9457F039-2CF0-400D-9C71-03F7FA015A09}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1000"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{62737957-12F2-4387-9BC7-5F56D2832693}" type="sibTrans" cxnId="{9457F039-2CF0-400D-9C71-03F7FA015A09}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="3600"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{33570384-A605-4DA1-B67B-2279EF2BEACD}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>소득</a:t>
+          </a:r>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{59C02579-9974-46AC-B8E5-C9B2D3EA3AEC}" type="parTrans" cxnId="{415577E8-A702-41BC-965B-528E316FA7F6}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1000"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{8DF4D672-D274-4D39-8836-B1757F2C493E}" type="sibTrans" cxnId="{415577E8-A702-41BC-965B-528E316FA7F6}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="3600"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{80595224-034E-4CE4-8A96-DF4078F87D5A}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>나이</a:t>
+          </a:r>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{807FD14A-FCEA-4A75-91B4-4EA6FA99B6C0}" type="parTrans" cxnId="{07D9AEED-5907-42EE-99AF-68E8C74BC6CE}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1000"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{66DC472F-0C00-4597-B38A-CB794F5A3548}" type="sibTrans" cxnId="{07D9AEED-5907-42EE-99AF-68E8C74BC6CE}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="3600"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{6FAFA265-1F7B-4088-90B7-96B8A56F2754}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>소득이 높으면</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>(8</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>만불</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>+) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>완료율이 높을 것이다</a:t>
+          </a:r>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{7FA771AB-4CE1-4ECA-8591-895AFCAC6367}" type="parTrans" cxnId="{1DAFEECD-2921-4EA7-A621-D9F243ABB0A8}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1000"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{9BD685D9-FACC-4933-B23B-7AEB4A4D12BF}" type="sibTrans" cxnId="{1DAFEECD-2921-4EA7-A621-D9F243ABB0A8}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="3600"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{50CF4719-7DA0-42F3-AD65-B5D431806F94}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1">
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>여성이면 남성보다 완료율이 높을 것이다</a:t>
+          </a:r>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{23DDCCE6-FB06-4407-A8A9-EBC992C910FC}" type="parTrans" cxnId="{CF14AB1E-D0A5-4766-ACC3-330A104528E3}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1000"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{BD1CDDA8-026D-47C8-97D3-4F862427D632}" type="sibTrans" cxnId="{CF14AB1E-D0A5-4766-ACC3-330A104528E3}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="3600"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{BAD0AFCB-57A5-4563-8108-4AB7B0A3C719}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr>
+        <a:solidFill>
+          <a:srgbClr val="5B9BD5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:sysClr val="window" lastClr="FFFFFF">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:sysClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dgm:spPr>
+      <dgm:t>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>나이 평균</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(54) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>보다 높은면 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>완료율이</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> 낮을 것이다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{C85E088B-B97D-4EB4-BBD6-D95A6F4656CC}" type="parTrans" cxnId="{67976198-D9C9-4B0A-A5A7-F482D3F8A962}">
+      <dgm:prSet custT="1"/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1000"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{0F15BF54-44D9-44C8-9D21-7047F7863151}" type="sibTrans" cxnId="{67976198-D9C9-4B0A-A5A7-F482D3F8A962}">
+      <dgm:prSet/>
+      <dgm:spPr/>
+      <dgm:t>
+        <a:bodyPr/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr latinLnBrk="1"/>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="3600"/>
+        </a:p>
+      </dgm:t>
+    </dgm:pt>
+    <dgm:pt modelId="{4F4AB575-764E-4A2E-AB1F-05862E0CB74B}" type="pres">
+      <dgm:prSet presAssocID="{88FEBD44-95B4-432B-B0FC-B98161E3F20C}" presName="diagram" presStyleCnt="0">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="1"/>
+          <dgm:dir/>
+          <dgm:animOne val="branch"/>
+          <dgm:animLvl val="lvl"/>
+          <dgm:resizeHandles val="exact"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{0AC04CE0-90DD-444E-819F-2E671C21BD68}" type="pres">
+      <dgm:prSet presAssocID="{D28EA82C-9573-422A-B949-9F47D5EA00C0}" presName="root1" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{4D165093-B6AF-4A3B-B20F-951E1B26045A}" type="pres">
+      <dgm:prSet presAssocID="{D28EA82C-9573-422A-B949-9F47D5EA00C0}" presName="LevelOneTextNode" presStyleLbl="node0" presStyleIdx="0" presStyleCnt="2" custScaleX="201190">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{B2656804-4756-4EEC-AFC9-A0EFF7AAB132}" type="pres">
+      <dgm:prSet presAssocID="{D28EA82C-9573-422A-B949-9F47D5EA00C0}" presName="level2hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{ED5992BD-91A0-44DC-B026-C230E027754F}" type="pres">
+      <dgm:prSet presAssocID="{A0B55608-A4DF-4F07-AF6C-C6F0A73452F0}" presName="conn2-1" presStyleLbl="parChTrans1D2" presStyleIdx="0" presStyleCnt="8"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{B52DA0CE-1E14-4AF5-B4E3-BA2B6B11F3FF}" type="pres">
+      <dgm:prSet presAssocID="{A0B55608-A4DF-4F07-AF6C-C6F0A73452F0}" presName="connTx" presStyleLbl="parChTrans1D2" presStyleIdx="0" presStyleCnt="8"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{01253263-E07D-4F9F-8798-5E3E260C947E}" type="pres">
+      <dgm:prSet presAssocID="{BAD7D27F-CDF5-4751-8931-8050F17DA501}" presName="root2" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{EB7188F2-1357-4748-A44C-AB5D4A48F40F}" type="pres">
+      <dgm:prSet presAssocID="{BAD7D27F-CDF5-4751-8931-8050F17DA501}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="0" presStyleCnt="8" custScaleX="120714">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{4C81F93C-BD44-4736-A025-49C6C9E62EDA}" type="pres">
+      <dgm:prSet presAssocID="{BAD7D27F-CDF5-4751-8931-8050F17DA501}" presName="level3hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{7531319A-E0E5-4CB4-9F35-33254694A0D7}" type="pres">
+      <dgm:prSet presAssocID="{4FE8AF39-819D-45D6-81C9-F2B354274064}" presName="conn2-1" presStyleLbl="parChTrans1D3" presStyleIdx="0" presStyleCnt="11"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{F8E1757E-B1FF-442F-ADD6-EDE36ECFBA6F}" type="pres">
+      <dgm:prSet presAssocID="{4FE8AF39-819D-45D6-81C9-F2B354274064}" presName="connTx" presStyleLbl="parChTrans1D3" presStyleIdx="0" presStyleCnt="11"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{9B62BAAF-BE36-479C-9400-320968F7C2F2}" type="pres">
+      <dgm:prSet presAssocID="{590C90E1-6DC6-4F7C-B608-A2B2336F2B00}" presName="root2" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{8F385C2E-83EB-470A-8A65-12C51C60EB27}" type="pres">
+      <dgm:prSet presAssocID="{590C90E1-6DC6-4F7C-B608-A2B2336F2B00}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="0" presStyleCnt="11" custScaleX="523095" custLinFactNeighborX="-620">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{43A0655B-ED0B-4D66-84EA-7B531B0D95AE}" type="pres">
+      <dgm:prSet presAssocID="{590C90E1-6DC6-4F7C-B608-A2B2336F2B00}" presName="level3hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{71327523-F24D-4A9E-8CA7-7C0E6A96618A}" type="pres">
+      <dgm:prSet presAssocID="{0A6C6A19-7DE5-478D-8FB1-EB8E7418F39D}" presName="conn2-1" presStyleLbl="parChTrans1D2" presStyleIdx="1" presStyleCnt="8"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{D35A13F0-0774-4D61-8ABE-048D4E1C32FC}" type="pres">
+      <dgm:prSet presAssocID="{0A6C6A19-7DE5-478D-8FB1-EB8E7418F39D}" presName="connTx" presStyleLbl="parChTrans1D2" presStyleIdx="1" presStyleCnt="8"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{081FC334-1FCE-412D-968D-13BD2DD652BC}" type="pres">
+      <dgm:prSet presAssocID="{111C26C2-0F68-4BE1-8C76-558F1B44A0DF}" presName="root2" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{08B2E005-DF35-41E7-A396-CA02C3B8D0A4}" type="pres">
+      <dgm:prSet presAssocID="{111C26C2-0F68-4BE1-8C76-558F1B44A0DF}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="1" presStyleCnt="8" custScaleX="120714">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{D21FFD0B-1CC4-4175-8E3B-5F1D14BA148C}" type="pres">
+      <dgm:prSet presAssocID="{111C26C2-0F68-4BE1-8C76-558F1B44A0DF}" presName="level3hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{E113C6B3-F5C2-41D9-9727-BB430EAD3818}" type="pres">
+      <dgm:prSet presAssocID="{A053B034-DC2F-4DD0-B5B2-98F1296693EF}" presName="conn2-1" presStyleLbl="parChTrans1D3" presStyleIdx="1" presStyleCnt="11"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{1C8D8E15-029F-4711-93EA-F3838176B5BB}" type="pres">
+      <dgm:prSet presAssocID="{A053B034-DC2F-4DD0-B5B2-98F1296693EF}" presName="connTx" presStyleLbl="parChTrans1D3" presStyleIdx="1" presStyleCnt="11"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{59E8519F-FE9E-4EEC-AA04-F33179DBBCC8}" type="pres">
+      <dgm:prSet presAssocID="{8FB65972-A8FD-4108-86AC-8A3B3296241B}" presName="root2" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{53F03F28-ED40-4762-8125-AFFEEA792A72}" type="pres">
+      <dgm:prSet presAssocID="{8FB65972-A8FD-4108-86AC-8A3B3296241B}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="1" presStyleCnt="11" custScaleX="523095">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{F3AD275D-DDC7-48F0-8A1B-913C9D7C169E}" type="pres">
+      <dgm:prSet presAssocID="{8FB65972-A8FD-4108-86AC-8A3B3296241B}" presName="level3hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{806C8330-1E37-41AD-AEEE-3552A4162510}" type="pres">
+      <dgm:prSet presAssocID="{BD9F1B93-0ABC-4B77-95B3-1DB7C4CB2918}" presName="conn2-1" presStyleLbl="parChTrans1D2" presStyleIdx="2" presStyleCnt="8"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{FEECC89F-F008-4D31-90AA-D7B0358104E0}" type="pres">
+      <dgm:prSet presAssocID="{BD9F1B93-0ABC-4B77-95B3-1DB7C4CB2918}" presName="connTx" presStyleLbl="parChTrans1D2" presStyleIdx="2" presStyleCnt="8"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{0BD91DE4-B768-42A0-9A8B-2239C6DD7A93}" type="pres">
+      <dgm:prSet presAssocID="{CB5507C6-5818-40A7-BD49-1000BD011A9B}" presName="root2" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{3BC1DAB2-4FEF-42C9-A10F-0690E2903498}" type="pres">
+      <dgm:prSet presAssocID="{CB5507C6-5818-40A7-BD49-1000BD011A9B}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="2" presStyleCnt="8" custScaleX="120714">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{8695FB13-171D-4F90-BABD-2364F0C3BD78}" type="pres">
+      <dgm:prSet presAssocID="{CB5507C6-5818-40A7-BD49-1000BD011A9B}" presName="level3hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{6BFD1C16-8154-4C15-AF72-E53B38C4A146}" type="pres">
+      <dgm:prSet presAssocID="{3469793B-2EFB-4C9D-A053-78B2C324DBC1}" presName="conn2-1" presStyleLbl="parChTrans1D3" presStyleIdx="2" presStyleCnt="11"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{CE70B2EC-38E2-43BE-B05C-6B1E20E6ABD7}" type="pres">
+      <dgm:prSet presAssocID="{3469793B-2EFB-4C9D-A053-78B2C324DBC1}" presName="connTx" presStyleLbl="parChTrans1D3" presStyleIdx="2" presStyleCnt="11"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{1AC5E9FE-4B02-457E-A974-C0CE1281FD8C}" type="pres">
+      <dgm:prSet presAssocID="{5E0D9290-77BE-490F-8462-B30D1FA58D8B}" presName="root2" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{1A251137-9CB6-43D7-B47D-0D220C30894C}" type="pres">
+      <dgm:prSet presAssocID="{5E0D9290-77BE-490F-8462-B30D1FA58D8B}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="2" presStyleCnt="11" custScaleX="523095">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{86B928B2-71C3-47DC-B28B-9D75DAEBBA8C}" type="pres">
+      <dgm:prSet presAssocID="{5E0D9290-77BE-490F-8462-B30D1FA58D8B}" presName="level3hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{227E0FEF-1368-4562-AD55-940C6A450E91}" type="pres">
+      <dgm:prSet presAssocID="{3DB36DA8-7484-4811-81A8-5926BB1B2E09}" presName="conn2-1" presStyleLbl="parChTrans1D2" presStyleIdx="3" presStyleCnt="8"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{B0208F78-A831-4C9C-9F71-0CAD8A13DFCC}" type="pres">
+      <dgm:prSet presAssocID="{3DB36DA8-7484-4811-81A8-5926BB1B2E09}" presName="connTx" presStyleLbl="parChTrans1D2" presStyleIdx="3" presStyleCnt="8"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{F3B7EAB8-F828-469D-957A-9C0140751550}" type="pres">
+      <dgm:prSet presAssocID="{3E881757-362F-489E-B630-0D8A32984B2B}" presName="root2" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{146FB508-948A-484E-B54F-2A63CE5492FA}" type="pres">
+      <dgm:prSet presAssocID="{3E881757-362F-489E-B630-0D8A32984B2B}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="3" presStyleCnt="8" custScaleX="120714">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{A69C8181-94EA-43B8-A05A-6A885B573FA1}" type="pres">
+      <dgm:prSet presAssocID="{3E881757-362F-489E-B630-0D8A32984B2B}" presName="level3hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{1583A4D8-C48C-400A-B5A1-D8E8188A1E57}" type="pres">
+      <dgm:prSet presAssocID="{C6CBFA23-E16E-4404-82E5-1AD7E38B3BD0}" presName="conn2-1" presStyleLbl="parChTrans1D3" presStyleIdx="3" presStyleCnt="11"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{F05383FB-E092-4B7D-A7EC-00D870A7B8FA}" type="pres">
+      <dgm:prSet presAssocID="{C6CBFA23-E16E-4404-82E5-1AD7E38B3BD0}" presName="connTx" presStyleLbl="parChTrans1D3" presStyleIdx="3" presStyleCnt="11"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{350D0257-E5D6-4E16-B429-1DA699BAF8C3}" type="pres">
+      <dgm:prSet presAssocID="{6AAA0E55-4800-4C4F-82AE-D951A95A6406}" presName="root2" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{985FE1E2-4CA8-4AC7-A474-DEECC9A2BB80}" type="pres">
+      <dgm:prSet presAssocID="{6AAA0E55-4800-4C4F-82AE-D951A95A6406}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="3" presStyleCnt="11" custScaleX="523095">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{7DB0F5C2-B6D7-40CB-93B1-A32531C856A9}" type="pres">
+      <dgm:prSet presAssocID="{6AAA0E55-4800-4C4F-82AE-D951A95A6406}" presName="level3hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{16F44D37-2601-482A-9095-0B3E8E10E520}" type="pres">
+      <dgm:prSet presAssocID="{336D58B7-98DD-484F-996F-4A6B86B1D8F7}" presName="conn2-1" presStyleLbl="parChTrans1D3" presStyleIdx="4" presStyleCnt="11"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{D076EAA4-EE98-4E06-BD0A-DEE73026C290}" type="pres">
+      <dgm:prSet presAssocID="{336D58B7-98DD-484F-996F-4A6B86B1D8F7}" presName="connTx" presStyleLbl="parChTrans1D3" presStyleIdx="4" presStyleCnt="11"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{564D3C52-B9F1-4DB7-A3B8-1062FD0F9811}" type="pres">
+      <dgm:prSet presAssocID="{C9187AAC-B0F0-4EDA-B360-D95444C1095C}" presName="root2" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{2D542640-C237-42B5-8470-73084719F8F3}" type="pres">
+      <dgm:prSet presAssocID="{C9187AAC-B0F0-4EDA-B360-D95444C1095C}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="4" presStyleCnt="11" custScaleX="523095">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{A57B83BB-BCC1-45F0-B448-0696169F3FCC}" type="pres">
+      <dgm:prSet presAssocID="{C9187AAC-B0F0-4EDA-B360-D95444C1095C}" presName="level3hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{9A75AB13-86A0-459A-8B2B-E8037D74B447}" type="pres">
+      <dgm:prSet presAssocID="{3D2CC029-AC34-412D-A670-9D22EF25DA78}" presName="conn2-1" presStyleLbl="parChTrans1D3" presStyleIdx="5" presStyleCnt="11"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{8D638858-B8F8-4989-ABCD-1F74A06FD90C}" type="pres">
+      <dgm:prSet presAssocID="{3D2CC029-AC34-412D-A670-9D22EF25DA78}" presName="connTx" presStyleLbl="parChTrans1D3" presStyleIdx="5" presStyleCnt="11"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{924E1DA1-B846-45BC-A4A3-604B1F4B9B8A}" type="pres">
+      <dgm:prSet presAssocID="{26FF4984-A8FB-481E-B952-91DAFB5870E3}" presName="root2" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{106C3051-36E0-4DB2-B006-BD51244834C6}" type="pres">
+      <dgm:prSet presAssocID="{26FF4984-A8FB-481E-B952-91DAFB5870E3}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="5" presStyleCnt="11" custScaleX="523095">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{38EBA6BB-7DEA-4839-B386-BF85BFBB7A06}" type="pres">
+      <dgm:prSet presAssocID="{26FF4984-A8FB-481E-B952-91DAFB5870E3}" presName="level3hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{6562E267-52DD-4DC6-81E6-A0E9307367D6}" type="pres">
+      <dgm:prSet presAssocID="{224B5B07-5A27-4D67-B5C9-B95010D5C5A9}" presName="conn2-1" presStyleLbl="parChTrans1D3" presStyleIdx="6" presStyleCnt="11"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{27DE1197-4C11-4091-BEE1-F8F8B65443EE}" type="pres">
+      <dgm:prSet presAssocID="{224B5B07-5A27-4D67-B5C9-B95010D5C5A9}" presName="connTx" presStyleLbl="parChTrans1D3" presStyleIdx="6" presStyleCnt="11"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{8A99A216-7B7E-4A39-A688-F5294B5D523B}" type="pres">
+      <dgm:prSet presAssocID="{C2DA3B5A-4288-4EA2-AC91-4F8B0C844A32}" presName="root2" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{220D319D-36C0-42A0-A946-F197C4269C14}" type="pres">
+      <dgm:prSet presAssocID="{C2DA3B5A-4288-4EA2-AC91-4F8B0C844A32}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="6" presStyleCnt="11" custScaleX="523095">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{5AC15471-6EAA-4265-8E4D-6043A7CECF67}" type="pres">
+      <dgm:prSet presAssocID="{C2DA3B5A-4288-4EA2-AC91-4F8B0C844A32}" presName="level3hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{4332858F-88A7-466E-8722-8833A7B96598}" type="pres">
+      <dgm:prSet presAssocID="{349EE8AE-E5A3-4960-8F4D-2C9AC7DAFBEF}" presName="conn2-1" presStyleLbl="parChTrans1D2" presStyleIdx="4" presStyleCnt="8"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{AF50C628-0DAD-43BB-9580-A6FB50B115D9}" type="pres">
+      <dgm:prSet presAssocID="{349EE8AE-E5A3-4960-8F4D-2C9AC7DAFBEF}" presName="connTx" presStyleLbl="parChTrans1D2" presStyleIdx="4" presStyleCnt="8"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{41714DC3-F3A7-41BB-8371-656B34451539}" type="pres">
+      <dgm:prSet presAssocID="{17CAE9F0-2C16-460C-A0EF-CF983A8E5B95}" presName="root2" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{1479FCFA-85A4-438D-B5D0-346DFAD5924D}" type="pres">
+      <dgm:prSet presAssocID="{17CAE9F0-2C16-460C-A0EF-CF983A8E5B95}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="4" presStyleCnt="8" custScaleX="120714">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{5B364536-61C6-4C87-983E-3D7708A352A0}" type="pres">
+      <dgm:prSet presAssocID="{17CAE9F0-2C16-460C-A0EF-CF983A8E5B95}" presName="level3hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{E6D0412B-4D85-432B-BE35-F277BFD00B03}" type="pres">
+      <dgm:prSet presAssocID="{61B28454-54A2-4A23-B946-6072BC34D484}" presName="conn2-1" presStyleLbl="parChTrans1D3" presStyleIdx="7" presStyleCnt="11"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{274B025F-D16B-4968-87D0-380BD22343AE}" type="pres">
+      <dgm:prSet presAssocID="{61B28454-54A2-4A23-B946-6072BC34D484}" presName="connTx" presStyleLbl="parChTrans1D3" presStyleIdx="7" presStyleCnt="11"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{13FD7D09-C741-46BB-868B-37FB1BE01A2C}" type="pres">
+      <dgm:prSet presAssocID="{F145AA98-6443-4870-A7B4-EC590B09FF29}" presName="root2" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{CE9AFD94-4037-4F8B-B49B-020818B5CBB5}" type="pres">
+      <dgm:prSet presAssocID="{F145AA98-6443-4870-A7B4-EC590B09FF29}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="7" presStyleCnt="11" custScaleX="523095">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{98E7E4BB-43E7-4635-B1B5-7AAB6FB148D9}" type="pres">
+      <dgm:prSet presAssocID="{F145AA98-6443-4870-A7B4-EC590B09FF29}" presName="level3hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{B25E102B-8A45-414D-8FC2-DF129716DB3D}" type="pres">
+      <dgm:prSet presAssocID="{D4EC9180-298D-4A0A-93FF-1513D3D77023}" presName="root1" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{B460AB31-448C-42B6-9C6B-D3CF5013B4F6}" type="pres">
+      <dgm:prSet presAssocID="{D4EC9180-298D-4A0A-93FF-1513D3D77023}" presName="LevelOneTextNode" presStyleLbl="node0" presStyleIdx="1" presStyleCnt="2" custScaleX="201190" custLinFactNeighborX="-14777">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{BEE55B8F-AE69-4FB3-899C-2D955EC0AEBC}" type="pres">
+      <dgm:prSet presAssocID="{D4EC9180-298D-4A0A-93FF-1513D3D77023}" presName="level2hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{C120D3E5-D1A3-4DC1-848B-C37D9DDE2012}" type="pres">
+      <dgm:prSet presAssocID="{CB5802DA-6B24-4C3B-AF82-CA0F64937596}" presName="conn2-1" presStyleLbl="parChTrans1D2" presStyleIdx="5" presStyleCnt="8"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{C5BBE1FB-0C60-4C48-86D3-D601FF0C2AFC}" type="pres">
+      <dgm:prSet presAssocID="{CB5802DA-6B24-4C3B-AF82-CA0F64937596}" presName="connTx" presStyleLbl="parChTrans1D2" presStyleIdx="5" presStyleCnt="8"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{FBB0F8D6-3179-4283-AB68-9AEE15C32B72}" type="pres">
+      <dgm:prSet presAssocID="{46DB12B3-6FCD-4174-A9CD-456ED4B290FA}" presName="root2" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{6F01F0AA-74B9-49DB-A456-B8979039EB51}" type="pres">
+      <dgm:prSet presAssocID="{46DB12B3-6FCD-4174-A9CD-456ED4B290FA}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="5" presStyleCnt="8" custScaleX="120714" custLinFactNeighborX="-2012">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{654E7F12-998B-4262-B57A-CBCE9EB8DBEC}" type="pres">
+      <dgm:prSet presAssocID="{46DB12B3-6FCD-4174-A9CD-456ED4B290FA}" presName="level3hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{F5E69F9A-2631-4A2D-BC76-B4BD9B08D019}" type="pres">
+      <dgm:prSet presAssocID="{23DDCCE6-FB06-4407-A8A9-EBC992C910FC}" presName="conn2-1" presStyleLbl="parChTrans1D3" presStyleIdx="8" presStyleCnt="11"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{A848F5FE-ABFD-4173-9594-A22DA438E5E9}" type="pres">
+      <dgm:prSet presAssocID="{23DDCCE6-FB06-4407-A8A9-EBC992C910FC}" presName="connTx" presStyleLbl="parChTrans1D3" presStyleIdx="8" presStyleCnt="11"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{6AD1ACB1-5829-41B5-A11B-3433D1676551}" type="pres">
+      <dgm:prSet presAssocID="{50CF4719-7DA0-42F3-AD65-B5D431806F94}" presName="root2" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{69EDA0B0-D39D-4C93-8B8D-10889C581D9E}" type="pres">
+      <dgm:prSet presAssocID="{50CF4719-7DA0-42F3-AD65-B5D431806F94}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="8" presStyleCnt="11" custScaleX="523095" custLinFactNeighborX="-1343" custLinFactNeighborY="0">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{78142362-D1E5-4930-A6C3-A3472F8177FC}" type="pres">
+      <dgm:prSet presAssocID="{50CF4719-7DA0-42F3-AD65-B5D431806F94}" presName="level3hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{AC23C890-5E27-4DC3-9BF7-2C50218200D9}" type="pres">
+      <dgm:prSet presAssocID="{59C02579-9974-46AC-B8E5-C9B2D3EA3AEC}" presName="conn2-1" presStyleLbl="parChTrans1D2" presStyleIdx="6" presStyleCnt="8"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{772F37DF-737E-4F81-9BAF-C1476C4D83AD}" type="pres">
+      <dgm:prSet presAssocID="{59C02579-9974-46AC-B8E5-C9B2D3EA3AEC}" presName="connTx" presStyleLbl="parChTrans1D2" presStyleIdx="6" presStyleCnt="8"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{A8B6C44E-D750-470A-9562-0F4E1933522D}" type="pres">
+      <dgm:prSet presAssocID="{33570384-A605-4DA1-B67B-2279EF2BEACD}" presName="root2" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{B4CF3050-E538-4710-99C5-FB5B2F28D116}" type="pres">
+      <dgm:prSet presAssocID="{33570384-A605-4DA1-B67B-2279EF2BEACD}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="6" presStyleCnt="8" custScaleX="120714" custLinFactNeighborX="-2012">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{81CFB6E2-B2D8-4FBB-BEA5-F17B7C75030B}" type="pres">
+      <dgm:prSet presAssocID="{33570384-A605-4DA1-B67B-2279EF2BEACD}" presName="level3hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{55492AE0-989E-4368-96E6-8609B6786079}" type="pres">
+      <dgm:prSet presAssocID="{7FA771AB-4CE1-4ECA-8591-895AFCAC6367}" presName="conn2-1" presStyleLbl="parChTrans1D3" presStyleIdx="9" presStyleCnt="11"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{AA2A326A-DBEB-4DAA-A02E-17ADD286AF48}" type="pres">
+      <dgm:prSet presAssocID="{7FA771AB-4CE1-4ECA-8591-895AFCAC6367}" presName="connTx" presStyleLbl="parChTrans1D3" presStyleIdx="9" presStyleCnt="11"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{F911F222-9C1B-468E-A5CF-FB8A25457900}" type="pres">
+      <dgm:prSet presAssocID="{6FAFA265-1F7B-4088-90B7-96B8A56F2754}" presName="root2" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{99BD4B49-7654-4BFC-93A2-73715A94DAC0}" type="pres">
+      <dgm:prSet presAssocID="{6FAFA265-1F7B-4088-90B7-96B8A56F2754}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="9" presStyleCnt="11" custScaleX="523095" custLinFactNeighborX="-1343" custLinFactNeighborY="0">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{A65938CF-8D2A-430E-BD5D-0E3A94E0D736}" type="pres">
+      <dgm:prSet presAssocID="{6FAFA265-1F7B-4088-90B7-96B8A56F2754}" presName="level3hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{48D36C81-0EEF-4879-868D-73109D1A61EF}" type="pres">
+      <dgm:prSet presAssocID="{807FD14A-FCEA-4A75-91B4-4EA6FA99B6C0}" presName="conn2-1" presStyleLbl="parChTrans1D2" presStyleIdx="7" presStyleCnt="8"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{AC83D01C-CF27-4D36-9643-EF8D54ABC9E2}" type="pres">
+      <dgm:prSet presAssocID="{807FD14A-FCEA-4A75-91B4-4EA6FA99B6C0}" presName="connTx" presStyleLbl="parChTrans1D2" presStyleIdx="7" presStyleCnt="8"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{0903B9B2-87B3-423C-B698-A23126107E5E}" type="pres">
+      <dgm:prSet presAssocID="{80595224-034E-4CE4-8A96-DF4078F87D5A}" presName="root2" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{E0C7A212-1F93-473A-8909-15A6780CBC2F}" type="pres">
+      <dgm:prSet presAssocID="{80595224-034E-4CE4-8A96-DF4078F87D5A}" presName="LevelTwoTextNode" presStyleLbl="node2" presStyleIdx="7" presStyleCnt="8" custScaleX="120714" custLinFactNeighborX="-2012">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{D553B27A-3CDD-4FF1-A784-D7F0CD94F31F}" type="pres">
+      <dgm:prSet presAssocID="{80595224-034E-4CE4-8A96-DF4078F87D5A}" presName="level3hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{4D54B04B-F98B-4577-8925-91ECEF877996}" type="pres">
+      <dgm:prSet presAssocID="{C85E088B-B97D-4EB4-BBD6-D95A6F4656CC}" presName="conn2-1" presStyleLbl="parChTrans1D3" presStyleIdx="10" presStyleCnt="11"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{37C200F0-2E29-4B09-A94C-D094C984B22A}" type="pres">
+      <dgm:prSet presAssocID="{C85E088B-B97D-4EB4-BBD6-D95A6F4656CC}" presName="connTx" presStyleLbl="parChTrans1D3" presStyleIdx="10" presStyleCnt="11"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{0F5BF64A-0F5E-4FBE-8D86-D0A808620A2A}" type="pres">
+      <dgm:prSet presAssocID="{BAD0AFCB-57A5-4563-8108-4AB7B0A3C719}" presName="root2" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+    <dgm:pt modelId="{540CB623-D523-4AD6-BF5D-A946D7B052E6}" type="pres">
+      <dgm:prSet presAssocID="{BAD0AFCB-57A5-4563-8108-4AB7B0A3C719}" presName="LevelTwoTextNode" presStyleLbl="node3" presStyleIdx="10" presStyleCnt="11" custScaleX="523095">
+        <dgm:presLayoutVars>
+          <dgm:chPref val="3"/>
+        </dgm:presLayoutVars>
+      </dgm:prSet>
+      <dgm:spPr>
+        <a:xfrm>
+          <a:off x="3519732" y="4080309"/>
+          <a:ext cx="2252419" cy="354515"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+      </dgm:spPr>
+    </dgm:pt>
+    <dgm:pt modelId="{8554999F-A756-45D0-8A9C-D7615B2C3AF7}" type="pres">
+      <dgm:prSet presAssocID="{BAD0AFCB-57A5-4563-8108-4AB7B0A3C719}" presName="level3hierChild" presStyleCnt="0"/>
+      <dgm:spPr/>
+    </dgm:pt>
+  </dgm:ptLst>
+  <dgm:cxnLst>
+    <dgm:cxn modelId="{E716BF02-E552-4CCD-89CD-A5B0B6E9EC70}" type="presOf" srcId="{4FE8AF39-819D-45D6-81C9-F2B354274064}" destId="{F8E1757E-B1FF-442F-ADD6-EDE36ECFBA6F}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{8C4A7307-2CD9-4D4B-B2EB-D69B2D3FE10B}" srcId="{3E881757-362F-489E-B630-0D8A32984B2B}" destId="{C9187AAC-B0F0-4EDA-B360-D95444C1095C}" srcOrd="1" destOrd="0" parTransId="{336D58B7-98DD-484F-996F-4A6B86B1D8F7}" sibTransId="{D56ED9E6-07E6-476D-B72A-1DAC45654595}"/>
+    <dgm:cxn modelId="{99AA9D0D-42AF-40A4-AEA7-96603169FD06}" type="presOf" srcId="{50CF4719-7DA0-42F3-AD65-B5D431806F94}" destId="{69EDA0B0-D39D-4C93-8B8D-10889C581D9E}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{AF850C0E-477F-45E3-A0A3-1F4786C24FFD}" type="presOf" srcId="{61B28454-54A2-4A23-B946-6072BC34D484}" destId="{274B025F-D16B-4968-87D0-380BD22343AE}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{6789530F-FB45-46BA-9B1D-3B3341D4D748}" type="presOf" srcId="{A0B55608-A4DF-4F07-AF6C-C6F0A73452F0}" destId="{ED5992BD-91A0-44DC-B026-C230E027754F}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{D62D4711-4853-49C5-AD88-6A4C204E26FD}" type="presOf" srcId="{17CAE9F0-2C16-460C-A0EF-CF983A8E5B95}" destId="{1479FCFA-85A4-438D-B5D0-346DFAD5924D}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{E147F012-F227-46EA-B01A-D20475D3B67D}" type="presOf" srcId="{D28EA82C-9573-422A-B949-9F47D5EA00C0}" destId="{4D165093-B6AF-4A3B-B20F-951E1B26045A}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{66D4E714-31E6-4954-A82A-B5A60F0C6BA7}" srcId="{D28EA82C-9573-422A-B949-9F47D5EA00C0}" destId="{BAD7D27F-CDF5-4751-8931-8050F17DA501}" srcOrd="0" destOrd="0" parTransId="{A0B55608-A4DF-4F07-AF6C-C6F0A73452F0}" sibTransId="{33CA151E-3B69-4314-B123-3297DFC7D670}"/>
+    <dgm:cxn modelId="{9AE49117-A534-41D2-B551-473D96BC5FE7}" type="presOf" srcId="{59C02579-9974-46AC-B8E5-C9B2D3EA3AEC}" destId="{AC23C890-5E27-4DC3-9BF7-2C50218200D9}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{C5516619-C5B2-4288-84CD-67C055A97476}" srcId="{D28EA82C-9573-422A-B949-9F47D5EA00C0}" destId="{CB5507C6-5818-40A7-BD49-1000BD011A9B}" srcOrd="2" destOrd="0" parTransId="{BD9F1B93-0ABC-4B77-95B3-1DB7C4CB2918}" sibTransId="{05412BF9-284B-4F1C-86AC-AF524BDD7D14}"/>
+    <dgm:cxn modelId="{2598091B-CB6C-4630-8FCC-1A5A75233A10}" type="presOf" srcId="{CB5802DA-6B24-4C3B-AF82-CA0F64937596}" destId="{C120D3E5-D1A3-4DC1-848B-C37D9DDE2012}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{CF14AB1E-D0A5-4766-ACC3-330A104528E3}" srcId="{46DB12B3-6FCD-4174-A9CD-456ED4B290FA}" destId="{50CF4719-7DA0-42F3-AD65-B5D431806F94}" srcOrd="0" destOrd="0" parTransId="{23DDCCE6-FB06-4407-A8A9-EBC992C910FC}" sibTransId="{BD1CDDA8-026D-47C8-97D3-4F862427D632}"/>
+    <dgm:cxn modelId="{6455C92C-AEDC-406D-9314-14128F0262F1}" type="presOf" srcId="{23DDCCE6-FB06-4407-A8A9-EBC992C910FC}" destId="{A848F5FE-ABFD-4173-9594-A22DA438E5E9}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{814B5B2D-0636-46D6-8357-3E465A736B44}" type="presOf" srcId="{336D58B7-98DD-484F-996F-4A6B86B1D8F7}" destId="{D076EAA4-EE98-4E06-BD0A-DEE73026C290}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{F8DDFC2D-2786-40D0-B273-9C978A0F6003}" type="presOf" srcId="{7FA771AB-4CE1-4ECA-8591-895AFCAC6367}" destId="{AA2A326A-DBEB-4DAA-A02E-17ADD286AF48}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{598EE134-21B8-4BC4-B868-2937D8E35E75}" type="presOf" srcId="{BD9F1B93-0ABC-4B77-95B3-1DB7C4CB2918}" destId="{806C8330-1E37-41AD-AEEE-3552A4162510}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{9457F039-2CF0-400D-9C71-03F7FA015A09}" srcId="{D4EC9180-298D-4A0A-93FF-1513D3D77023}" destId="{46DB12B3-6FCD-4174-A9CD-456ED4B290FA}" srcOrd="0" destOrd="0" parTransId="{CB5802DA-6B24-4C3B-AF82-CA0F64937596}" sibTransId="{62737957-12F2-4387-9BC7-5F56D2832693}"/>
+    <dgm:cxn modelId="{11932F3D-BA9B-441A-8939-E3C049AD81D3}" type="presOf" srcId="{A053B034-DC2F-4DD0-B5B2-98F1296693EF}" destId="{1C8D8E15-029F-4711-93EA-F3838176B5BB}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{23EFEB5C-12C0-41AD-97DC-8B6DAC0830C7}" type="presOf" srcId="{59C02579-9974-46AC-B8E5-C9B2D3EA3AEC}" destId="{772F37DF-737E-4F81-9BAF-C1476C4D83AD}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{89570F43-E429-40CF-A897-90E077418661}" type="presOf" srcId="{46DB12B3-6FCD-4174-A9CD-456ED4B290FA}" destId="{6F01F0AA-74B9-49DB-A456-B8979039EB51}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{D4A95A63-993F-49BA-844C-081D17E5005A}" type="presOf" srcId="{807FD14A-FCEA-4A75-91B4-4EA6FA99B6C0}" destId="{AC83D01C-CF27-4D36-9643-EF8D54ABC9E2}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{649BBD44-4CFF-49CE-B5C2-02F87A124FCF}" type="presOf" srcId="{3D2CC029-AC34-412D-A670-9D22EF25DA78}" destId="{9A75AB13-86A0-459A-8B2B-E8037D74B447}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{719F1E48-19AF-416D-BC2E-82961DFA1755}" type="presOf" srcId="{224B5B07-5A27-4D67-B5C9-B95010D5C5A9}" destId="{27DE1197-4C11-4091-BEE1-F8F8B65443EE}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{D92FE84D-8344-484F-96C7-CD04C772FFCE}" type="presOf" srcId="{F145AA98-6443-4870-A7B4-EC590B09FF29}" destId="{CE9AFD94-4037-4F8B-B49B-020818B5CBB5}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{9FD5D850-9393-4E82-9B60-F344E814296E}" type="presOf" srcId="{C85E088B-B97D-4EB4-BBD6-D95A6F4656CC}" destId="{37C200F0-2E29-4B09-A94C-D094C984B22A}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{57FC0E72-DB14-4028-8299-0FF8C7177C5C}" srcId="{3E881757-362F-489E-B630-0D8A32984B2B}" destId="{26FF4984-A8FB-481E-B952-91DAFB5870E3}" srcOrd="2" destOrd="0" parTransId="{3D2CC029-AC34-412D-A670-9D22EF25DA78}" sibTransId="{DE75E50D-DFA6-418B-9C06-95A5C3944847}"/>
+    <dgm:cxn modelId="{8CEC1554-B055-464F-AC47-FCFB34B80966}" srcId="{D28EA82C-9573-422A-B949-9F47D5EA00C0}" destId="{3E881757-362F-489E-B630-0D8A32984B2B}" srcOrd="3" destOrd="0" parTransId="{3DB36DA8-7484-4811-81A8-5926BB1B2E09}" sibTransId="{278E719C-4D84-4910-9C25-3DCD78815614}"/>
+    <dgm:cxn modelId="{F7115254-B2DB-4711-9B96-1797D64046C8}" srcId="{CB5507C6-5818-40A7-BD49-1000BD011A9B}" destId="{5E0D9290-77BE-490F-8462-B30D1FA58D8B}" srcOrd="0" destOrd="0" parTransId="{3469793B-2EFB-4C9D-A053-78B2C324DBC1}" sibTransId="{827A2A25-BF22-45D1-8C10-6D340F70C6A1}"/>
+    <dgm:cxn modelId="{CAEBC875-3C11-4DF4-B17E-40CDB162EBA4}" type="presOf" srcId="{C6CBFA23-E16E-4404-82E5-1AD7E38B3BD0}" destId="{F05383FB-E092-4B7D-A7EC-00D870A7B8FA}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{26B40478-8828-42BA-B106-CA1C827BA177}" type="presOf" srcId="{7FA771AB-4CE1-4ECA-8591-895AFCAC6367}" destId="{55492AE0-989E-4368-96E6-8609B6786079}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{7D8F6358-B9F1-4D8C-BE58-5881541E729C}" type="presOf" srcId="{CB5802DA-6B24-4C3B-AF82-CA0F64937596}" destId="{C5BBE1FB-0C60-4C48-86D3-D601FF0C2AFC}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{1656E178-28D2-4281-83AE-77EE7CA41B4C}" srcId="{D28EA82C-9573-422A-B949-9F47D5EA00C0}" destId="{111C26C2-0F68-4BE1-8C76-558F1B44A0DF}" srcOrd="1" destOrd="0" parTransId="{0A6C6A19-7DE5-478D-8FB1-EB8E7418F39D}" sibTransId="{E023194C-F95D-4763-92F5-F1ECD4BC9C73}"/>
+    <dgm:cxn modelId="{D2FA5A79-1C6F-4BA4-9743-73F806A7B41B}" type="presOf" srcId="{A0B55608-A4DF-4F07-AF6C-C6F0A73452F0}" destId="{B52DA0CE-1E14-4AF5-B4E3-BA2B6B11F3FF}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{222A087A-B882-4E51-91BF-D7CCCD051844}" type="presOf" srcId="{C85E088B-B97D-4EB4-BBD6-D95A6F4656CC}" destId="{4D54B04B-F98B-4577-8925-91ECEF877996}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{A9F11C7D-D01E-43D8-AD5C-A31108B40C7D}" type="presOf" srcId="{6FAFA265-1F7B-4088-90B7-96B8A56F2754}" destId="{99BD4B49-7654-4BFC-93A2-73715A94DAC0}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{7322667D-69E2-4F51-9B08-CC032291FF5E}" type="presOf" srcId="{80595224-034E-4CE4-8A96-DF4078F87D5A}" destId="{E0C7A212-1F93-473A-8909-15A6780CBC2F}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{2797ED7D-20C0-4797-8100-2F2E86906BAA}" type="presOf" srcId="{807FD14A-FCEA-4A75-91B4-4EA6FA99B6C0}" destId="{48D36C81-0EEF-4879-868D-73109D1A61EF}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{7BB5B180-6C85-4AD5-A51A-F3D1DBE6B7D9}" srcId="{3E881757-362F-489E-B630-0D8A32984B2B}" destId="{6AAA0E55-4800-4C4F-82AE-D951A95A6406}" srcOrd="0" destOrd="0" parTransId="{C6CBFA23-E16E-4404-82E5-1AD7E38B3BD0}" sibTransId="{213EC674-33B2-46B5-97B4-B78DD7CC6633}"/>
+    <dgm:cxn modelId="{9E93E484-6F94-455F-905B-83CCF7FF2B2F}" type="presOf" srcId="{349EE8AE-E5A3-4960-8F4D-2C9AC7DAFBEF}" destId="{AF50C628-0DAD-43BB-9580-A6FB50B115D9}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{BE014B86-3D98-439A-9866-D73914E0EE7E}" type="presOf" srcId="{61B28454-54A2-4A23-B946-6072BC34D484}" destId="{E6D0412B-4D85-432B-BE35-F277BFD00B03}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{3EC75F87-8E50-46E6-B6AC-7DC42AF700E7}" type="presOf" srcId="{D4EC9180-298D-4A0A-93FF-1513D3D77023}" destId="{B460AB31-448C-42B6-9C6B-D3CF5013B4F6}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{604F8188-5220-4BBD-B051-AE258F4786C5}" type="presOf" srcId="{88FEBD44-95B4-432B-B0FC-B98161E3F20C}" destId="{4F4AB575-764E-4A2E-AB1F-05862E0CB74B}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{9554478A-1EB0-4AAA-ADAE-9FB3873C43EB}" type="presOf" srcId="{4FE8AF39-819D-45D6-81C9-F2B354274064}" destId="{7531319A-E0E5-4CB4-9F35-33254694A0D7}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{8462148B-1DD3-441F-B63F-6F0F33CA55E6}" type="presOf" srcId="{6AAA0E55-4800-4C4F-82AE-D951A95A6406}" destId="{985FE1E2-4CA8-4AC7-A474-DEECC9A2BB80}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{AB24B48B-7C7E-4598-9A0B-41A35655D90D}" type="presOf" srcId="{A053B034-DC2F-4DD0-B5B2-98F1296693EF}" destId="{E113C6B3-F5C2-41D9-9727-BB430EAD3818}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{00C77A8E-6B70-42A2-9561-C73F86BE4CF8}" type="presOf" srcId="{C6CBFA23-E16E-4404-82E5-1AD7E38B3BD0}" destId="{1583A4D8-C48C-400A-B5A1-D8E8188A1E57}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{CF369B92-780C-46D0-9ED6-7B81FBADD727}" type="presOf" srcId="{3469793B-2EFB-4C9D-A053-78B2C324DBC1}" destId="{CE70B2EC-38E2-43BE-B05C-6B1E20E6ABD7}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{17E63997-D9CE-4D39-AE2E-A3AE0D1284BC}" type="presOf" srcId="{CB5507C6-5818-40A7-BD49-1000BD011A9B}" destId="{3BC1DAB2-4FEF-42C9-A10F-0690E2903498}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{67976198-D9C9-4B0A-A5A7-F482D3F8A962}" srcId="{80595224-034E-4CE4-8A96-DF4078F87D5A}" destId="{BAD0AFCB-57A5-4563-8108-4AB7B0A3C719}" srcOrd="0" destOrd="0" parTransId="{C85E088B-B97D-4EB4-BBD6-D95A6F4656CC}" sibTransId="{0F15BF54-44D9-44C8-9D21-7047F7863151}"/>
+    <dgm:cxn modelId="{B1B80D9C-040C-4053-BD9A-8F2DDEC78F29}" srcId="{17CAE9F0-2C16-460C-A0EF-CF983A8E5B95}" destId="{F145AA98-6443-4870-A7B4-EC590B09FF29}" srcOrd="0" destOrd="0" parTransId="{61B28454-54A2-4A23-B946-6072BC34D484}" sibTransId="{F87A8A7F-0D3D-4479-81E7-4B421A7751B7}"/>
+    <dgm:cxn modelId="{24D5F7A1-BC55-49BA-AD3A-9E7950427D56}" type="presOf" srcId="{C9187AAC-B0F0-4EDA-B360-D95444C1095C}" destId="{2D542640-C237-42B5-8470-73084719F8F3}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{2FD81CA3-1E57-4F8C-AF6C-72CC43E05195}" srcId="{BAD7D27F-CDF5-4751-8931-8050F17DA501}" destId="{590C90E1-6DC6-4F7C-B608-A2B2336F2B00}" srcOrd="0" destOrd="0" parTransId="{4FE8AF39-819D-45D6-81C9-F2B354274064}" sibTransId="{B0E34315-446D-43CA-9C1A-43AC03C7FA4E}"/>
+    <dgm:cxn modelId="{C31D5CA3-AC5A-423C-99A3-985CE8E3D2CE}" srcId="{111C26C2-0F68-4BE1-8C76-558F1B44A0DF}" destId="{8FB65972-A8FD-4108-86AC-8A3B3296241B}" srcOrd="0" destOrd="0" parTransId="{A053B034-DC2F-4DD0-B5B2-98F1296693EF}" sibTransId="{B9BFC1E1-36FA-4DFA-A7FB-937425619DD8}"/>
+    <dgm:cxn modelId="{07E8A4AA-9A8A-4504-A01B-F5E592908ED0}" type="presOf" srcId="{33570384-A605-4DA1-B67B-2279EF2BEACD}" destId="{B4CF3050-E538-4710-99C5-FB5B2F28D116}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{3F4922AB-4BCF-4C3F-BDDB-346BCDC296AB}" srcId="{88FEBD44-95B4-432B-B0FC-B98161E3F20C}" destId="{D28EA82C-9573-422A-B949-9F47D5EA00C0}" srcOrd="0" destOrd="0" parTransId="{8FA42352-D834-44A6-A154-3CB76BE81B68}" sibTransId="{71F878CA-1A36-404F-978F-D8724DEDCCAF}"/>
+    <dgm:cxn modelId="{4E1C2DAE-C050-4639-9A7A-2B8E19863364}" srcId="{D28EA82C-9573-422A-B949-9F47D5EA00C0}" destId="{17CAE9F0-2C16-460C-A0EF-CF983A8E5B95}" srcOrd="4" destOrd="0" parTransId="{349EE8AE-E5A3-4960-8F4D-2C9AC7DAFBEF}" sibTransId="{B5F3BFB9-0C8D-4ED3-BB39-6E65AD6E6202}"/>
+    <dgm:cxn modelId="{A37199AF-6B7B-4D63-9BED-72A4088E31D7}" type="presOf" srcId="{3469793B-2EFB-4C9D-A053-78B2C324DBC1}" destId="{6BFD1C16-8154-4C15-AF72-E53B38C4A146}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{356B8AB4-45AE-46AE-8283-651F355AD458}" type="presOf" srcId="{336D58B7-98DD-484F-996F-4A6B86B1D8F7}" destId="{16F44D37-2601-482A-9095-0B3E8E10E520}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{9E72F2B5-B38B-4682-A94E-6A0A12C507BD}" type="presOf" srcId="{BD9F1B93-0ABC-4B77-95B3-1DB7C4CB2918}" destId="{FEECC89F-F008-4D31-90AA-D7B0358104E0}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{C2E5C8C2-39E3-4172-B04E-F41ADFDEB387}" type="presOf" srcId="{8FB65972-A8FD-4108-86AC-8A3B3296241B}" destId="{53F03F28-ED40-4762-8125-AFFEEA792A72}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{FB2B60CC-0744-4CF3-81D8-7AD4A3610137}" type="presOf" srcId="{3DB36DA8-7484-4811-81A8-5926BB1B2E09}" destId="{227E0FEF-1368-4562-AD55-940C6A450E91}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{1DAFEECD-2921-4EA7-A621-D9F243ABB0A8}" srcId="{33570384-A605-4DA1-B67B-2279EF2BEACD}" destId="{6FAFA265-1F7B-4088-90B7-96B8A56F2754}" srcOrd="0" destOrd="0" parTransId="{7FA771AB-4CE1-4ECA-8591-895AFCAC6367}" sibTransId="{9BD685D9-FACC-4933-B23B-7AEB4A4D12BF}"/>
+    <dgm:cxn modelId="{A20F76D0-7BCB-45E8-B360-790EB5F29686}" type="presOf" srcId="{224B5B07-5A27-4D67-B5C9-B95010D5C5A9}" destId="{6562E267-52DD-4DC6-81E6-A0E9307367D6}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{DBF535D2-BD92-4672-8867-EA84BC5763AA}" type="presOf" srcId="{3DB36DA8-7484-4811-81A8-5926BB1B2E09}" destId="{B0208F78-A831-4C9C-9F71-0CAD8A13DFCC}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{2440BBD3-B375-44FF-872D-AB1B780F978C}" type="presOf" srcId="{26FF4984-A8FB-481E-B952-91DAFB5870E3}" destId="{106C3051-36E0-4DB2-B006-BD51244834C6}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{4E3A3AD6-8FD2-4BA3-AC8C-7F9CF3D587F7}" srcId="{3E881757-362F-489E-B630-0D8A32984B2B}" destId="{C2DA3B5A-4288-4EA2-AC91-4F8B0C844A32}" srcOrd="3" destOrd="0" parTransId="{224B5B07-5A27-4D67-B5C9-B95010D5C5A9}" sibTransId="{81FA6521-2044-4D8B-A3F2-96C820EAF9F1}"/>
+    <dgm:cxn modelId="{22675FDB-D57E-40A9-8DB8-24BDE2145037}" type="presOf" srcId="{BAD7D27F-CDF5-4751-8931-8050F17DA501}" destId="{EB7188F2-1357-4748-A44C-AB5D4A48F40F}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{D9CA61DC-2D30-46B4-A093-77D4B2F30BE9}" type="presOf" srcId="{3E881757-362F-489E-B630-0D8A32984B2B}" destId="{146FB508-948A-484E-B54F-2A63CE5492FA}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{94CE50DD-5A01-4009-B770-500D579F6261}" srcId="{88FEBD44-95B4-432B-B0FC-B98161E3F20C}" destId="{D4EC9180-298D-4A0A-93FF-1513D3D77023}" srcOrd="1" destOrd="0" parTransId="{FF7B4EF7-F173-446C-B7FC-76DF9BD7C3B7}" sibTransId="{59629897-8AC3-4B42-ABE4-2D4F4203E3F5}"/>
+    <dgm:cxn modelId="{36CDA4DE-2626-4984-9CC3-17FFAB24499D}" type="presOf" srcId="{23DDCCE6-FB06-4407-A8A9-EBC992C910FC}" destId="{F5E69F9A-2631-4A2D-BC76-B4BD9B08D019}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{4FE23EDF-13FE-4703-91E6-6C903EDF68FE}" type="presOf" srcId="{0A6C6A19-7DE5-478D-8FB1-EB8E7418F39D}" destId="{71327523-F24D-4A9E-8CA7-7C0E6A96618A}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{3D57FDE0-4E64-475C-A9CE-314E2DD7D40C}" type="presOf" srcId="{590C90E1-6DC6-4F7C-B608-A2B2336F2B00}" destId="{8F385C2E-83EB-470A-8A65-12C51C60EB27}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{36020EE3-17F3-4E72-86E8-11CC0757B176}" type="presOf" srcId="{BAD0AFCB-57A5-4563-8108-4AB7B0A3C719}" destId="{540CB623-D523-4AD6-BF5D-A946D7B052E6}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{CCFD01E6-B250-4974-8ACC-B4488D55724F}" type="presOf" srcId="{5E0D9290-77BE-490F-8462-B30D1FA58D8B}" destId="{1A251137-9CB6-43D7-B47D-0D220C30894C}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{415577E8-A702-41BC-965B-528E316FA7F6}" srcId="{D4EC9180-298D-4A0A-93FF-1513D3D77023}" destId="{33570384-A605-4DA1-B67B-2279EF2BEACD}" srcOrd="1" destOrd="0" parTransId="{59C02579-9974-46AC-B8E5-C9B2D3EA3AEC}" sibTransId="{8DF4D672-D274-4D39-8836-B1757F2C493E}"/>
+    <dgm:cxn modelId="{07D9AEED-5907-42EE-99AF-68E8C74BC6CE}" srcId="{D4EC9180-298D-4A0A-93FF-1513D3D77023}" destId="{80595224-034E-4CE4-8A96-DF4078F87D5A}" srcOrd="2" destOrd="0" parTransId="{807FD14A-FCEA-4A75-91B4-4EA6FA99B6C0}" sibTransId="{66DC472F-0C00-4597-B38A-CB794F5A3548}"/>
+    <dgm:cxn modelId="{6AA869F1-2370-47CB-8892-04E1C8E66198}" type="presOf" srcId="{111C26C2-0F68-4BE1-8C76-558F1B44A0DF}" destId="{08B2E005-DF35-41E7-A396-CA02C3B8D0A4}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{D46966F4-1F6B-44AE-BBA7-9D94EA384573}" type="presOf" srcId="{349EE8AE-E5A3-4960-8F4D-2C9AC7DAFBEF}" destId="{4332858F-88A7-466E-8722-8833A7B96598}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{6BB77CF6-5C09-47BD-BAE8-C3CAB397D44B}" type="presOf" srcId="{C2DA3B5A-4288-4EA2-AC91-4F8B0C844A32}" destId="{220D319D-36C0-42A0-A946-F197C4269C14}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{B2374AFC-17E8-4D47-98A5-8F67B836CE42}" type="presOf" srcId="{3D2CC029-AC34-412D-A670-9D22EF25DA78}" destId="{8D638858-B8F8-4989-ABCD-1F74A06FD90C}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{D031EAFE-71D3-4118-AE8A-0807172E90A8}" type="presOf" srcId="{0A6C6A19-7DE5-478D-8FB1-EB8E7418F39D}" destId="{D35A13F0-0774-4D61-8ABE-048D4E1C32FC}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{F0990498-35A7-462E-866E-ACEAAF852A57}" type="presParOf" srcId="{4F4AB575-764E-4A2E-AB1F-05862E0CB74B}" destId="{0AC04CE0-90DD-444E-819F-2E671C21BD68}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{3AC408DF-32EB-43BA-8E9D-8489B358660D}" type="presParOf" srcId="{0AC04CE0-90DD-444E-819F-2E671C21BD68}" destId="{4D165093-B6AF-4A3B-B20F-951E1B26045A}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{92D88567-4A9F-42AA-9F6E-33826FCBD533}" type="presParOf" srcId="{0AC04CE0-90DD-444E-819F-2E671C21BD68}" destId="{B2656804-4756-4EEC-AFC9-A0EFF7AAB132}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{1ACA0D17-5E35-4CFA-8079-DAFD961015B2}" type="presParOf" srcId="{B2656804-4756-4EEC-AFC9-A0EFF7AAB132}" destId="{ED5992BD-91A0-44DC-B026-C230E027754F}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{33117CAB-5F87-46A4-A41A-86AADB73DD34}" type="presParOf" srcId="{ED5992BD-91A0-44DC-B026-C230E027754F}" destId="{B52DA0CE-1E14-4AF5-B4E3-BA2B6B11F3FF}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{2AED2644-195B-416B-931E-6BB1466C1C4A}" type="presParOf" srcId="{B2656804-4756-4EEC-AFC9-A0EFF7AAB132}" destId="{01253263-E07D-4F9F-8798-5E3E260C947E}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{3EF7D83A-D253-4220-A811-2E9019FF47D7}" type="presParOf" srcId="{01253263-E07D-4F9F-8798-5E3E260C947E}" destId="{EB7188F2-1357-4748-A44C-AB5D4A48F40F}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{9280AB69-4EA9-4E66-B6D0-D9ED1CDBC799}" type="presParOf" srcId="{01253263-E07D-4F9F-8798-5E3E260C947E}" destId="{4C81F93C-BD44-4736-A025-49C6C9E62EDA}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{C42022F0-ECCE-427A-A81C-AC7B4EAEC80C}" type="presParOf" srcId="{4C81F93C-BD44-4736-A025-49C6C9E62EDA}" destId="{7531319A-E0E5-4CB4-9F35-33254694A0D7}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{189FEFF2-4AB3-49B1-97F5-0ECB96BF88AB}" type="presParOf" srcId="{7531319A-E0E5-4CB4-9F35-33254694A0D7}" destId="{F8E1757E-B1FF-442F-ADD6-EDE36ECFBA6F}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{8D0AEE37-7FF5-418B-92BC-1C2FAFBF000D}" type="presParOf" srcId="{4C81F93C-BD44-4736-A025-49C6C9E62EDA}" destId="{9B62BAAF-BE36-479C-9400-320968F7C2F2}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{D8BB15FE-DCFF-4753-8F06-32BC8629183E}" type="presParOf" srcId="{9B62BAAF-BE36-479C-9400-320968F7C2F2}" destId="{8F385C2E-83EB-470A-8A65-12C51C60EB27}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{B6461975-0FB2-4AAB-893C-FAD81A2D7269}" type="presParOf" srcId="{9B62BAAF-BE36-479C-9400-320968F7C2F2}" destId="{43A0655B-ED0B-4D66-84EA-7B531B0D95AE}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{ECEA538B-A558-48F6-9110-1111D6DD0D77}" type="presParOf" srcId="{B2656804-4756-4EEC-AFC9-A0EFF7AAB132}" destId="{71327523-F24D-4A9E-8CA7-7C0E6A96618A}" srcOrd="2" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{9F778866-158D-4384-BC59-E9DB8C750120}" type="presParOf" srcId="{71327523-F24D-4A9E-8CA7-7C0E6A96618A}" destId="{D35A13F0-0774-4D61-8ABE-048D4E1C32FC}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{14D89E3F-57C4-4140-AD2C-B4ADEAE79FE3}" type="presParOf" srcId="{B2656804-4756-4EEC-AFC9-A0EFF7AAB132}" destId="{081FC334-1FCE-412D-968D-13BD2DD652BC}" srcOrd="3" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{BCE7A905-25BB-4121-99D9-E77A96DB44B6}" type="presParOf" srcId="{081FC334-1FCE-412D-968D-13BD2DD652BC}" destId="{08B2E005-DF35-41E7-A396-CA02C3B8D0A4}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{DB7E9FA7-536B-492C-B2B1-E11F697A4743}" type="presParOf" srcId="{081FC334-1FCE-412D-968D-13BD2DD652BC}" destId="{D21FFD0B-1CC4-4175-8E3B-5F1D14BA148C}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{9F52891E-146C-47EE-842A-744C883BBAB2}" type="presParOf" srcId="{D21FFD0B-1CC4-4175-8E3B-5F1D14BA148C}" destId="{E113C6B3-F5C2-41D9-9727-BB430EAD3818}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{4F1172A1-42ED-42CF-8ACD-E60DE8D12795}" type="presParOf" srcId="{E113C6B3-F5C2-41D9-9727-BB430EAD3818}" destId="{1C8D8E15-029F-4711-93EA-F3838176B5BB}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{8948BCFA-B8A4-4C32-BD1A-2F380A04ECB3}" type="presParOf" srcId="{D21FFD0B-1CC4-4175-8E3B-5F1D14BA148C}" destId="{59E8519F-FE9E-4EEC-AA04-F33179DBBCC8}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{A98A6079-322E-4202-83F6-91B20AC9541D}" type="presParOf" srcId="{59E8519F-FE9E-4EEC-AA04-F33179DBBCC8}" destId="{53F03F28-ED40-4762-8125-AFFEEA792A72}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{6EA2B04B-A1F1-41D4-9B62-39CBB7A5A316}" type="presParOf" srcId="{59E8519F-FE9E-4EEC-AA04-F33179DBBCC8}" destId="{F3AD275D-DDC7-48F0-8A1B-913C9D7C169E}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{67910EB1-0A61-4384-B152-314479FD6F36}" type="presParOf" srcId="{B2656804-4756-4EEC-AFC9-A0EFF7AAB132}" destId="{806C8330-1E37-41AD-AEEE-3552A4162510}" srcOrd="4" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{BACC5A24-2505-418E-9A53-CF08A484382E}" type="presParOf" srcId="{806C8330-1E37-41AD-AEEE-3552A4162510}" destId="{FEECC89F-F008-4D31-90AA-D7B0358104E0}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{1D75447D-C931-4C31-8481-7E0BD53DB138}" type="presParOf" srcId="{B2656804-4756-4EEC-AFC9-A0EFF7AAB132}" destId="{0BD91DE4-B768-42A0-9A8B-2239C6DD7A93}" srcOrd="5" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{6168A3CE-8F8B-4DC5-92F8-C2896537B2D6}" type="presParOf" srcId="{0BD91DE4-B768-42A0-9A8B-2239C6DD7A93}" destId="{3BC1DAB2-4FEF-42C9-A10F-0690E2903498}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{B7B0153F-08CE-45FF-B381-232B8FCFC287}" type="presParOf" srcId="{0BD91DE4-B768-42A0-9A8B-2239C6DD7A93}" destId="{8695FB13-171D-4F90-BABD-2364F0C3BD78}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{528009D1-C30F-4548-86DF-51860FC776EE}" type="presParOf" srcId="{8695FB13-171D-4F90-BABD-2364F0C3BD78}" destId="{6BFD1C16-8154-4C15-AF72-E53B38C4A146}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{C3B293A9-4878-4E4F-9881-FD4F72AA8476}" type="presParOf" srcId="{6BFD1C16-8154-4C15-AF72-E53B38C4A146}" destId="{CE70B2EC-38E2-43BE-B05C-6B1E20E6ABD7}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{27042C1C-D24D-4B77-8B9A-FE733F7AFAC0}" type="presParOf" srcId="{8695FB13-171D-4F90-BABD-2364F0C3BD78}" destId="{1AC5E9FE-4B02-457E-A974-C0CE1281FD8C}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{A3A73319-F2D0-4533-9A6A-EBA21A7D2F2B}" type="presParOf" srcId="{1AC5E9FE-4B02-457E-A974-C0CE1281FD8C}" destId="{1A251137-9CB6-43D7-B47D-0D220C30894C}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{F8FB85BE-7E42-4355-A81C-5F83980F9040}" type="presParOf" srcId="{1AC5E9FE-4B02-457E-A974-C0CE1281FD8C}" destId="{86B928B2-71C3-47DC-B28B-9D75DAEBBA8C}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{443338C9-C8A9-414F-BCCE-48D2877357F4}" type="presParOf" srcId="{B2656804-4756-4EEC-AFC9-A0EFF7AAB132}" destId="{227E0FEF-1368-4562-AD55-940C6A450E91}" srcOrd="6" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{92250F63-1AAE-49DA-83B9-37528C221006}" type="presParOf" srcId="{227E0FEF-1368-4562-AD55-940C6A450E91}" destId="{B0208F78-A831-4C9C-9F71-0CAD8A13DFCC}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{8E464938-4467-422D-B278-93028012F661}" type="presParOf" srcId="{B2656804-4756-4EEC-AFC9-A0EFF7AAB132}" destId="{F3B7EAB8-F828-469D-957A-9C0140751550}" srcOrd="7" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{F1FD993C-3C4A-4702-BD6B-E3BBBCF9E2AA}" type="presParOf" srcId="{F3B7EAB8-F828-469D-957A-9C0140751550}" destId="{146FB508-948A-484E-B54F-2A63CE5492FA}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{060D572C-F523-4B2E-A330-612D5B7CFE19}" type="presParOf" srcId="{F3B7EAB8-F828-469D-957A-9C0140751550}" destId="{A69C8181-94EA-43B8-A05A-6A885B573FA1}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{2156532E-A97E-45AB-AD43-90A1314BCE00}" type="presParOf" srcId="{A69C8181-94EA-43B8-A05A-6A885B573FA1}" destId="{1583A4D8-C48C-400A-B5A1-D8E8188A1E57}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{22E15C8A-4485-47DF-AF00-2D8C68D9CE28}" type="presParOf" srcId="{1583A4D8-C48C-400A-B5A1-D8E8188A1E57}" destId="{F05383FB-E092-4B7D-A7EC-00D870A7B8FA}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{92CD3A7C-823F-4FFF-8F29-111AE5C0461E}" type="presParOf" srcId="{A69C8181-94EA-43B8-A05A-6A885B573FA1}" destId="{350D0257-E5D6-4E16-B429-1DA699BAF8C3}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{D28625AC-D7D2-4704-935E-542DCA4A7B7C}" type="presParOf" srcId="{350D0257-E5D6-4E16-B429-1DA699BAF8C3}" destId="{985FE1E2-4CA8-4AC7-A474-DEECC9A2BB80}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{D47EBECA-8B8B-495C-AFFB-FF1D4A03325B}" type="presParOf" srcId="{350D0257-E5D6-4E16-B429-1DA699BAF8C3}" destId="{7DB0F5C2-B6D7-40CB-93B1-A32531C856A9}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{CC9583AB-705F-4AC4-92C7-60FD3AD62A33}" type="presParOf" srcId="{A69C8181-94EA-43B8-A05A-6A885B573FA1}" destId="{16F44D37-2601-482A-9095-0B3E8E10E520}" srcOrd="2" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{04AC06F6-1BA3-423E-9904-D1A1315EF5EB}" type="presParOf" srcId="{16F44D37-2601-482A-9095-0B3E8E10E520}" destId="{D076EAA4-EE98-4E06-BD0A-DEE73026C290}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{13E0708D-FB2F-4B73-93F5-45C8C5101766}" type="presParOf" srcId="{A69C8181-94EA-43B8-A05A-6A885B573FA1}" destId="{564D3C52-B9F1-4DB7-A3B8-1062FD0F9811}" srcOrd="3" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{9FA603F9-A823-4748-86E6-F01C9E6B1CA2}" type="presParOf" srcId="{564D3C52-B9F1-4DB7-A3B8-1062FD0F9811}" destId="{2D542640-C237-42B5-8470-73084719F8F3}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{7D7D6007-1FF7-4FFF-8DD8-0CD84FA4770D}" type="presParOf" srcId="{564D3C52-B9F1-4DB7-A3B8-1062FD0F9811}" destId="{A57B83BB-BCC1-45F0-B448-0696169F3FCC}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{3C2082E4-769F-4B64-B7B4-251DF5B7D113}" type="presParOf" srcId="{A69C8181-94EA-43B8-A05A-6A885B573FA1}" destId="{9A75AB13-86A0-459A-8B2B-E8037D74B447}" srcOrd="4" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{3F42D1BF-67A9-4068-BE00-438C7BE5AF65}" type="presParOf" srcId="{9A75AB13-86A0-459A-8B2B-E8037D74B447}" destId="{8D638858-B8F8-4989-ABCD-1F74A06FD90C}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{DA2D3530-1BAD-497A-803D-83550958E960}" type="presParOf" srcId="{A69C8181-94EA-43B8-A05A-6A885B573FA1}" destId="{924E1DA1-B846-45BC-A4A3-604B1F4B9B8A}" srcOrd="5" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{F353278E-3CF5-4A11-879B-038B8BFEF605}" type="presParOf" srcId="{924E1DA1-B846-45BC-A4A3-604B1F4B9B8A}" destId="{106C3051-36E0-4DB2-B006-BD51244834C6}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{BAA1BA9A-727F-4416-BB25-2958C87CE731}" type="presParOf" srcId="{924E1DA1-B846-45BC-A4A3-604B1F4B9B8A}" destId="{38EBA6BB-7DEA-4839-B386-BF85BFBB7A06}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{11D03BA6-E3B1-4ECB-A910-EC30A0DA4471}" type="presParOf" srcId="{A69C8181-94EA-43B8-A05A-6A885B573FA1}" destId="{6562E267-52DD-4DC6-81E6-A0E9307367D6}" srcOrd="6" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{E6498285-E404-4729-A740-16A0B3118A32}" type="presParOf" srcId="{6562E267-52DD-4DC6-81E6-A0E9307367D6}" destId="{27DE1197-4C11-4091-BEE1-F8F8B65443EE}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{BD9B2FA7-2273-40BB-9248-46BD8C95A622}" type="presParOf" srcId="{A69C8181-94EA-43B8-A05A-6A885B573FA1}" destId="{8A99A216-7B7E-4A39-A688-F5294B5D523B}" srcOrd="7" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{7326FC10-C75F-44B4-911D-EE10AE932C2D}" type="presParOf" srcId="{8A99A216-7B7E-4A39-A688-F5294B5D523B}" destId="{220D319D-36C0-42A0-A946-F197C4269C14}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{D8D362A0-9FE8-45B5-AA5D-067962F1F7B4}" type="presParOf" srcId="{8A99A216-7B7E-4A39-A688-F5294B5D523B}" destId="{5AC15471-6EAA-4265-8E4D-6043A7CECF67}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{E5BEC14D-A9A1-4355-A3A9-1E377AA2AC54}" type="presParOf" srcId="{B2656804-4756-4EEC-AFC9-A0EFF7AAB132}" destId="{4332858F-88A7-466E-8722-8833A7B96598}" srcOrd="8" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{E6163E19-FB3F-4C0B-98E5-A3B8DC0CC4B4}" type="presParOf" srcId="{4332858F-88A7-466E-8722-8833A7B96598}" destId="{AF50C628-0DAD-43BB-9580-A6FB50B115D9}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{6D16ED87-2BB7-463C-A03E-FBBA687DE88B}" type="presParOf" srcId="{B2656804-4756-4EEC-AFC9-A0EFF7AAB132}" destId="{41714DC3-F3A7-41BB-8371-656B34451539}" srcOrd="9" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{5323B34C-18BF-44DD-A72B-7534F485E8E6}" type="presParOf" srcId="{41714DC3-F3A7-41BB-8371-656B34451539}" destId="{1479FCFA-85A4-438D-B5D0-346DFAD5924D}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{A4474184-E87A-47CA-A300-E601A3C5A774}" type="presParOf" srcId="{41714DC3-F3A7-41BB-8371-656B34451539}" destId="{5B364536-61C6-4C87-983E-3D7708A352A0}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{A50E6F8F-098B-4D29-A5F8-4055DAC56E62}" type="presParOf" srcId="{5B364536-61C6-4C87-983E-3D7708A352A0}" destId="{E6D0412B-4D85-432B-BE35-F277BFD00B03}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{984B8066-3C74-429A-8267-038C32534B0D}" type="presParOf" srcId="{E6D0412B-4D85-432B-BE35-F277BFD00B03}" destId="{274B025F-D16B-4968-87D0-380BD22343AE}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{E595B179-46DA-4256-9CC9-35B70B57CAE1}" type="presParOf" srcId="{5B364536-61C6-4C87-983E-3D7708A352A0}" destId="{13FD7D09-C741-46BB-868B-37FB1BE01A2C}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{BAEA4C6F-55B1-4D11-A93D-613622995B8E}" type="presParOf" srcId="{13FD7D09-C741-46BB-868B-37FB1BE01A2C}" destId="{CE9AFD94-4037-4F8B-B49B-020818B5CBB5}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{E7A12BF5-6203-42EB-8DFF-6FE7ABF53C31}" type="presParOf" srcId="{13FD7D09-C741-46BB-868B-37FB1BE01A2C}" destId="{98E7E4BB-43E7-4635-B1B5-7AAB6FB148D9}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{75BF1823-0EE5-4D7A-B576-AD473639D45E}" type="presParOf" srcId="{4F4AB575-764E-4A2E-AB1F-05862E0CB74B}" destId="{B25E102B-8A45-414D-8FC2-DF129716DB3D}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{95B9CA0F-C69A-4F0A-8B5B-F813CBC58E05}" type="presParOf" srcId="{B25E102B-8A45-414D-8FC2-DF129716DB3D}" destId="{B460AB31-448C-42B6-9C6B-D3CF5013B4F6}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{2CC52935-99B2-4F74-9854-B27711434E67}" type="presParOf" srcId="{B25E102B-8A45-414D-8FC2-DF129716DB3D}" destId="{BEE55B8F-AE69-4FB3-899C-2D955EC0AEBC}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{EB167583-6950-4ED9-B790-4EA12AEEFBFB}" type="presParOf" srcId="{BEE55B8F-AE69-4FB3-899C-2D955EC0AEBC}" destId="{C120D3E5-D1A3-4DC1-848B-C37D9DDE2012}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{172A04DF-ACFF-4FDF-AD08-027416307FA5}" type="presParOf" srcId="{C120D3E5-D1A3-4DC1-848B-C37D9DDE2012}" destId="{C5BBE1FB-0C60-4C48-86D3-D601FF0C2AFC}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{B83CE91A-3936-4D68-B5A0-214760472BBD}" type="presParOf" srcId="{BEE55B8F-AE69-4FB3-899C-2D955EC0AEBC}" destId="{FBB0F8D6-3179-4283-AB68-9AEE15C32B72}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{5A796D3D-E4AB-41E9-A1B6-F42A12CC5928}" type="presParOf" srcId="{FBB0F8D6-3179-4283-AB68-9AEE15C32B72}" destId="{6F01F0AA-74B9-49DB-A456-B8979039EB51}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{D7D3A8FB-7EBD-451D-9A12-7697CE6D42EE}" type="presParOf" srcId="{FBB0F8D6-3179-4283-AB68-9AEE15C32B72}" destId="{654E7F12-998B-4262-B57A-CBCE9EB8DBEC}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{0FECD05A-0D68-496F-B1A6-1AF5C8B53D98}" type="presParOf" srcId="{654E7F12-998B-4262-B57A-CBCE9EB8DBEC}" destId="{F5E69F9A-2631-4A2D-BC76-B4BD9B08D019}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{370BECC2-9BC0-4671-9B1D-9499F0A9A5F8}" type="presParOf" srcId="{F5E69F9A-2631-4A2D-BC76-B4BD9B08D019}" destId="{A848F5FE-ABFD-4173-9594-A22DA438E5E9}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{6DF0238A-F592-4BFA-9785-F323818E9F5B}" type="presParOf" srcId="{654E7F12-998B-4262-B57A-CBCE9EB8DBEC}" destId="{6AD1ACB1-5829-41B5-A11B-3433D1676551}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{774DA7F0-06E5-4859-9234-EB450891EFEA}" type="presParOf" srcId="{6AD1ACB1-5829-41B5-A11B-3433D1676551}" destId="{69EDA0B0-D39D-4C93-8B8D-10889C581D9E}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{75B85929-83F3-4CAC-9555-19331703AA5F}" type="presParOf" srcId="{6AD1ACB1-5829-41B5-A11B-3433D1676551}" destId="{78142362-D1E5-4930-A6C3-A3472F8177FC}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{ADA83DF1-FFF5-46E9-A03E-F159850BABC1}" type="presParOf" srcId="{BEE55B8F-AE69-4FB3-899C-2D955EC0AEBC}" destId="{AC23C890-5E27-4DC3-9BF7-2C50218200D9}" srcOrd="2" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{73604811-188B-48D5-B552-8CB1A83C7ABD}" type="presParOf" srcId="{AC23C890-5E27-4DC3-9BF7-2C50218200D9}" destId="{772F37DF-737E-4F81-9BAF-C1476C4D83AD}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{3AA0550E-3751-4E63-9292-9699CC1D1F1C}" type="presParOf" srcId="{BEE55B8F-AE69-4FB3-899C-2D955EC0AEBC}" destId="{A8B6C44E-D750-470A-9562-0F4E1933522D}" srcOrd="3" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{37B6054D-825F-40CB-B57D-9228B48F6F9B}" type="presParOf" srcId="{A8B6C44E-D750-470A-9562-0F4E1933522D}" destId="{B4CF3050-E538-4710-99C5-FB5B2F28D116}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{CA8DA526-C626-47E2-A139-B33B566F8665}" type="presParOf" srcId="{A8B6C44E-D750-470A-9562-0F4E1933522D}" destId="{81CFB6E2-B2D8-4FBB-BEA5-F17B7C75030B}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{9C0347E4-C658-4BD1-ADB5-9423E949F6FB}" type="presParOf" srcId="{81CFB6E2-B2D8-4FBB-BEA5-F17B7C75030B}" destId="{55492AE0-989E-4368-96E6-8609B6786079}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{CE8010B9-8D41-457A-81B8-7CE369F49574}" type="presParOf" srcId="{55492AE0-989E-4368-96E6-8609B6786079}" destId="{AA2A326A-DBEB-4DAA-A02E-17ADD286AF48}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{2DD874FE-71FA-4496-B731-7D0EDD19E262}" type="presParOf" srcId="{81CFB6E2-B2D8-4FBB-BEA5-F17B7C75030B}" destId="{F911F222-9C1B-468E-A5CF-FB8A25457900}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{54E0DE47-D516-4912-B7E2-5F85E1F1DC00}" type="presParOf" srcId="{F911F222-9C1B-468E-A5CF-FB8A25457900}" destId="{99BD4B49-7654-4BFC-93A2-73715A94DAC0}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{5087B92D-35C5-4473-98AF-74964C81D5F5}" type="presParOf" srcId="{F911F222-9C1B-468E-A5CF-FB8A25457900}" destId="{A65938CF-8D2A-430E-BD5D-0E3A94E0D736}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{FA689ACA-D620-4079-8B75-9E47B0845C5D}" type="presParOf" srcId="{BEE55B8F-AE69-4FB3-899C-2D955EC0AEBC}" destId="{48D36C81-0EEF-4879-868D-73109D1A61EF}" srcOrd="4" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{6BC74307-6578-4EA8-9506-340B08821961}" type="presParOf" srcId="{48D36C81-0EEF-4879-868D-73109D1A61EF}" destId="{AC83D01C-CF27-4D36-9643-EF8D54ABC9E2}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{C41B66F3-C317-4D3A-A79F-2CF01A5DA187}" type="presParOf" srcId="{BEE55B8F-AE69-4FB3-899C-2D955EC0AEBC}" destId="{0903B9B2-87B3-423C-B698-A23126107E5E}" srcOrd="5" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{6C106DE6-4B2D-4A80-B427-FEE163EF3D9E}" type="presParOf" srcId="{0903B9B2-87B3-423C-B698-A23126107E5E}" destId="{E0C7A212-1F93-473A-8909-15A6780CBC2F}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{2EEE09BA-D37F-4E0F-97E0-888FF9D4EF69}" type="presParOf" srcId="{0903B9B2-87B3-423C-B698-A23126107E5E}" destId="{D553B27A-3CDD-4FF1-A784-D7F0CD94F31F}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{4C10D8C5-7419-4D3A-AB39-C66D7D1336F1}" type="presParOf" srcId="{D553B27A-3CDD-4FF1-A784-D7F0CD94F31F}" destId="{4D54B04B-F98B-4577-8925-91ECEF877996}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{89771D1C-93C2-4DA6-92E8-C0D1F12ECD74}" type="presParOf" srcId="{4D54B04B-F98B-4577-8925-91ECEF877996}" destId="{37C200F0-2E29-4B09-A94C-D094C984B22A}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{AFBE5A2C-758A-4C31-A17B-9FEF910CE064}" type="presParOf" srcId="{D553B27A-3CDD-4FF1-A784-D7F0CD94F31F}" destId="{0F5BF64A-0F5E-4FBE-8D86-D0A808620A2A}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{19CF9FF2-D3B9-498D-8E29-02BAD80A8840}" type="presParOf" srcId="{0F5BF64A-0F5E-4FBE-8D86-D0A808620A2A}" destId="{540CB623-D523-4AD6-BF5D-A946D7B052E6}" srcOrd="0" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+    <dgm:cxn modelId="{0F7DF2FB-6B4F-4A35-AAB9-D847481323C9}" type="presParOf" srcId="{0F5BF64A-0F5E-4FBE-8D86-D0A808620A2A}" destId="{8554999F-A756-45D0-8A9C-D7615B2C3AF7}" srcOrd="1" destOrd="0" presId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2"/>
+  </dgm:cxnLst>
+  <dgm:bg>
+    <a:solidFill>
+      <a:schemeClr val="accent4">
+        <a:lumMod val="20000"/>
+        <a:lumOff val="80000"/>
+      </a:schemeClr>
+    </a:solidFill>
+  </dgm:bg>
+  <dgm:whole>
+    <a:ln>
+      <a:solidFill>
+        <a:schemeClr val="tx1"/>
+      </a:solidFill>
+    </a:ln>
+  </dgm:whole>
+  <dgm:extLst>
+    <a:ext uri="http://schemas.microsoft.com/office/drawing/2008/diagram">
+      <dsp:dataModelExt xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" relId="rId5" minVer="http://schemas.openxmlformats.org/drawingml/2006/diagram"/>
+    </a:ext>
+    <a:ext uri="{C62137D5-CB1D-491B-B009-E17868A290BF}">
+      <dgm14:recolorImg xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" val="1"/>
+    </a:ext>
+  </dgm:extLst>
+</dgm:dataModel>
+</file>
+
+<file path=xl/diagrams/data2.xml><?xml version="1.0" encoding="utf-8"?>
 <dgm:dataModel xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <dgm:ptLst>
     <dgm:pt modelId="{88FEBD44-95B4-432B-B0FC-B98161E3F20C}" type="doc">
@@ -9165,7 +12308,4132 @@
 </dsp:drawing>
 </file>
 
+<file path=xl/diagrams/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<dsp:drawing xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <dsp:spTree>
+    <dsp:nvGrpSpPr>
+      <dsp:cNvPr id="0" name=""/>
+      <dsp:cNvGrpSpPr/>
+    </dsp:nvGrpSpPr>
+    <dsp:grpSpPr/>
+    <dsp:sp modelId="{4D165093-B6AF-4A3B-B20F-951E1B26045A}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="389577" y="1796156"/>
+          <a:ext cx="1791371" cy="445193"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="6985" tIns="6985" rIns="6985" bIns="6985" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" i="0" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Offer(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" i="0" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>행사</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" i="0" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" i="0" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>설계에 따라 주문 완료율의 차이가 있는가</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="402616" y="1809195"/>
+        <a:ext cx="1765293" cy="419115"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{ED5992BD-91A0-44DC-B026-C230E027754F}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm rot="16874489">
+          <a:off x="1445547" y="1115611"/>
+          <a:ext cx="1826956" cy="14378"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst>
+            <a:path>
+              <a:moveTo>
+                <a:pt x="0" y="7189"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="1826956" y="7189"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:shade val="60000"/>
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="466725" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="2313352" y="1077126"/>
+        <a:ext cx="91347" cy="91347"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{EB7188F2-1357-4748-A44C-AB5D4A48F40F}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="2537103" y="4250"/>
+          <a:ext cx="1074822" cy="445193"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="6985" tIns="6985" rIns="6985" bIns="6985" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Offer type</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="2550142" y="17289"/>
+        <a:ext cx="1048744" cy="419115"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{7531319A-E0E5-4CB4-9F35-33254694A0D7}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="3611926" y="219658"/>
+          <a:ext cx="350634" cy="14378"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst>
+            <a:path>
+              <a:moveTo>
+                <a:pt x="0" y="7189"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="350634" y="7189"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:shade val="80000"/>
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="466725" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3778477" y="218081"/>
+        <a:ext cx="17531" cy="17531"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{8F385C2E-83EB-470A-8A65-12C51C60EB27}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="3962561" y="4250"/>
+          <a:ext cx="4657573" cy="445193"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="6985" tIns="6985" rIns="6985" bIns="6985" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>완료율은 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>discount &gt; bogo &gt; information </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>순으로 높을 것이다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3975600" y="17289"/>
+        <a:ext cx="4631495" cy="419115"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{71327523-F24D-4A9E-8CA7-7C0E6A96618A}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm rot="17132988">
+          <a:off x="1694745" y="1371597"/>
+          <a:ext cx="1328560" cy="14378"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst>
+            <a:path>
+              <a:moveTo>
+                <a:pt x="0" y="7189"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="1328560" y="7189"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:shade val="60000"/>
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="466725" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="2325812" y="1345572"/>
+        <a:ext cx="66428" cy="66428"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{08B2E005-DF35-41E7-A396-CA02C3B8D0A4}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="2537103" y="516223"/>
+          <a:ext cx="1074822" cy="445193"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="6985" tIns="6985" rIns="6985" bIns="6985" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Reward</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="2550142" y="529262"/>
+        <a:ext cx="1048744" cy="419115"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{E113C6B3-F5C2-41D9-9727-BB430EAD3818}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="3611926" y="731631"/>
+          <a:ext cx="356155" cy="14378"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst>
+            <a:path>
+              <a:moveTo>
+                <a:pt x="0" y="7189"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="356155" y="7189"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:shade val="80000"/>
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="466725" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3781100" y="729916"/>
+        <a:ext cx="17807" cy="17807"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{53F03F28-ED40-4762-8125-AFFEEA792A72}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="3968081" y="516223"/>
+          <a:ext cx="4657573" cy="445193"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="6985" tIns="6985" rIns="6985" bIns="6985" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Reward</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>가 평균</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(4.2)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> 보다 높은 경우</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>,</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> 낮은 경우보다 완료율이 높을 것이다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3981120" y="529262"/>
+        <a:ext cx="4631495" cy="419115"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{806C8330-1E37-41AD-AEEE-3552A4162510}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm rot="17692822">
+          <a:off x="1935762" y="1627584"/>
+          <a:ext cx="846527" cy="14378"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst>
+            <a:path>
+              <a:moveTo>
+                <a:pt x="0" y="7189"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="846527" y="7189"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:shade val="60000"/>
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="466725" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="2337863" y="1613610"/>
+        <a:ext cx="42326" cy="42326"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{3BC1DAB2-4FEF-42C9-A10F-0690E2903498}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="2537103" y="1028196"/>
+          <a:ext cx="1074822" cy="445193"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="6985" tIns="6985" rIns="6985" bIns="6985" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Duration(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>기간</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="2550142" y="1041235"/>
+        <a:ext cx="1048744" cy="419115"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{6BFD1C16-8154-4C15-AF72-E53B38C4A146}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="3611926" y="1243604"/>
+          <a:ext cx="356155" cy="14378"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst>
+            <a:path>
+              <a:moveTo>
+                <a:pt x="0" y="7189"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="356155" y="7189"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:shade val="80000"/>
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="466725" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3781100" y="1241889"/>
+        <a:ext cx="17807" cy="17807"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{1A251137-9CB6-43D7-B47D-0D220C30894C}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="3968081" y="1028196"/>
+          <a:ext cx="4657573" cy="445193"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="6985" tIns="6985" rIns="6985" bIns="6985" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Duration</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>이 평균</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(6.7)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>보다 높은 경우</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>, </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>낮은 경우보다 완료율이 높을 것이다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3981120" y="1041235"/>
+        <a:ext cx="4631495" cy="419115"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{227E0FEF-1368-4562-AD55-940C6A450E91}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm rot="3310531">
+          <a:off x="2047191" y="2267550"/>
+          <a:ext cx="623668" cy="14378"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst>
+            <a:path>
+              <a:moveTo>
+                <a:pt x="0" y="7189"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="623668" y="7189"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:shade val="60000"/>
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="466725" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="2343434" y="2259147"/>
+        <a:ext cx="31183" cy="31183"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{146FB508-948A-484E-B54F-2A63CE5492FA}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="2537103" y="2308129"/>
+          <a:ext cx="1074822" cy="445193"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="6985" tIns="6985" rIns="6985" bIns="6985" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Channels</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="2550142" y="2321168"/>
+        <a:ext cx="1048744" cy="419115"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{1583A4D8-C48C-400A-B5A1-D8E8188A1E57}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm rot="17692822">
+          <a:off x="3366740" y="2139557"/>
+          <a:ext cx="846527" cy="14378"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst>
+            <a:path>
+              <a:moveTo>
+                <a:pt x="0" y="7189"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="846527" y="7189"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:shade val="80000"/>
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="466725" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3768840" y="2125583"/>
+        <a:ext cx="42326" cy="42326"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{985FE1E2-4CA8-4AC7-A474-DEECC9A2BB80}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="3968081" y="1540169"/>
+          <a:ext cx="4657573" cy="445193"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="6985" tIns="6985" rIns="6985" bIns="6985" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Web</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>이 포함되어 있는 경우 완료율은 높아지지 않을 것이다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3981120" y="1553208"/>
+        <a:ext cx="4631495" cy="419115"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{16F44D37-2601-482A-9095-0B3E8E10E520}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm rot="19457599">
+          <a:off x="3570700" y="2395543"/>
+          <a:ext cx="438606" cy="14378"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst>
+            <a:path>
+              <a:moveTo>
+                <a:pt x="0" y="7189"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="438606" y="7189"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:shade val="80000"/>
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="466725" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3779038" y="2391767"/>
+        <a:ext cx="21930" cy="21930"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{2D542640-C237-42B5-8470-73084719F8F3}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="3968081" y="2052142"/>
+          <a:ext cx="4657573" cy="445193"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="6985" tIns="6985" rIns="6985" bIns="6985" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>email</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>이 포함되어 있는 경우 완료율은 높아지지 않을 것이다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3981120" y="2065181"/>
+        <a:ext cx="4631495" cy="419115"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{9A75AB13-86A0-459A-8B2B-E8037D74B447}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm rot="2142401">
+          <a:off x="3570700" y="2651530"/>
+          <a:ext cx="438606" cy="14378"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst>
+            <a:path>
+              <a:moveTo>
+                <a:pt x="0" y="7189"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="438606" y="7189"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:shade val="80000"/>
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="466725" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3779038" y="2647754"/>
+        <a:ext cx="21930" cy="21930"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{106C3051-36E0-4DB2-B006-BD51244834C6}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="3968081" y="2564115"/>
+          <a:ext cx="4657573" cy="445193"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="6985" tIns="6985" rIns="6985" bIns="6985" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Mobile</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>이 포함되어 있는 경우 포함되지 않은 경우보다 완료율이 높을 것이다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3981120" y="2577154"/>
+        <a:ext cx="4631495" cy="419115"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{6562E267-52DD-4DC6-81E6-A0E9307367D6}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm rot="3907178">
+          <a:off x="3366740" y="2907516"/>
+          <a:ext cx="846527" cy="14378"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst>
+            <a:path>
+              <a:moveTo>
+                <a:pt x="0" y="7189"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="846527" y="7189"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:shade val="80000"/>
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="466725" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3768840" y="2893542"/>
+        <a:ext cx="42326" cy="42326"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{220D319D-36C0-42A0-A946-F197C4269C14}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="3968081" y="3076088"/>
+          <a:ext cx="4657573" cy="445193"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="6985" tIns="6985" rIns="6985" bIns="6985" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Social</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>이 포함되어 있는 경우 포함되지 않은 경우보다 완료율이 높을 것이다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3981120" y="3089127"/>
+        <a:ext cx="4631495" cy="419115"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{4332858F-88A7-466E-8722-8833A7B96598}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm rot="4725511">
+          <a:off x="1445547" y="2907516"/>
+          <a:ext cx="1826956" cy="14378"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst>
+            <a:path>
+              <a:moveTo>
+                <a:pt x="0" y="7189"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="1826956" y="7189"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:shade val="60000"/>
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="466725" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" kern="1200"/>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="2313352" y="2869031"/>
+        <a:ext cx="91347" cy="91347"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{1479FCFA-85A4-438D-B5D0-346DFAD5924D}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="2537103" y="3588061"/>
+          <a:ext cx="1074822" cy="445193"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="6985" tIns="6985" rIns="6985" bIns="6985" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Difficulty</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="2550142" y="3601100"/>
+        <a:ext cx="1048744" cy="419115"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{E6D0412B-4D85-432B-BE35-F277BFD00B03}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="3611926" y="3803469"/>
+          <a:ext cx="356155" cy="14378"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst>
+            <a:path>
+              <a:moveTo>
+                <a:pt x="0" y="7189"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="356155" y="7189"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:shade val="80000"/>
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="466725" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1050" kern="1200"/>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3781100" y="3801754"/>
+        <a:ext cx="17807" cy="17807"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{CE9AFD94-4037-4F8B-B49B-020818B5CBB5}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="3968081" y="3588061"/>
+          <a:ext cx="4657573" cy="445193"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="6985" tIns="6985" rIns="6985" bIns="6985" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>Difficulty</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>가 평균</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(7.7) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>보다 높은 경우 낮은 경우보다 완료율이 낮을 것이다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3981120" y="3601100"/>
+        <a:ext cx="4631495" cy="419115"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{B460AB31-448C-42B6-9C6B-D3CF5013B4F6}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="258004" y="4612007"/>
+          <a:ext cx="1791371" cy="445193"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="6985" tIns="6985" rIns="6985" bIns="6985" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Profile(</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>고객 정보</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>)</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>에 따라 주문 완료율이 다를 것이다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+            <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="271043" y="4625046"/>
+        <a:ext cx="1765293" cy="419115"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{C120D3E5-D1A3-4DC1-848B-C37D9DDE2012}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm rot="18752467">
+          <a:off x="1936848" y="4571428"/>
+          <a:ext cx="694867" cy="14378"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst>
+            <a:path>
+              <a:moveTo>
+                <a:pt x="0" y="7189"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="694867" y="7189"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:shade val="60000"/>
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="444500" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1000" kern="1200"/>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="2266910" y="4561246"/>
+        <a:ext cx="34743" cy="34743"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{6F01F0AA-74B9-49DB-A456-B8979039EB51}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="2519189" y="4100034"/>
+          <a:ext cx="1074822" cy="445193"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="6985" tIns="6985" rIns="6985" bIns="6985" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>성별</a:t>
+          </a:r>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="2532228" y="4113073"/>
+        <a:ext cx="1048744" cy="419115"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{F5E69F9A-2631-4A2D-BC76-B4BD9B08D019}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="3594011" y="4315442"/>
+          <a:ext cx="362111" cy="14378"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst>
+            <a:path>
+              <a:moveTo>
+                <a:pt x="0" y="7189"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="362111" y="7189"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:shade val="80000"/>
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="444500" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1000" kern="1200"/>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3766014" y="4313578"/>
+        <a:ext cx="18105" cy="18105"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{69EDA0B0-D39D-4C93-8B8D-10889C581D9E}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="3956123" y="4100034"/>
+          <a:ext cx="4657573" cy="445193"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="6985" tIns="6985" rIns="6985" bIns="6985" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>여성이면 남성보다 완료율이 높을 것이다</a:t>
+          </a:r>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3969162" y="4113073"/>
+        <a:ext cx="4631495" cy="419115"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{AC23C890-5E27-4DC3-9BF7-2C50218200D9}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="2049376" y="4827415"/>
+          <a:ext cx="469813" cy="14378"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst>
+            <a:path>
+              <a:moveTo>
+                <a:pt x="0" y="7189"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="469813" y="7189"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:shade val="60000"/>
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="444500" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1000" kern="1200"/>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="2272537" y="4822859"/>
+        <a:ext cx="23490" cy="23490"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{B4CF3050-E538-4710-99C5-FB5B2F28D116}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="2519189" y="4612007"/>
+          <a:ext cx="1074822" cy="445193"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="6985" tIns="6985" rIns="6985" bIns="6985" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>소득</a:t>
+          </a:r>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="2532228" y="4625046"/>
+        <a:ext cx="1048744" cy="419115"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{55492AE0-989E-4368-96E6-8609B6786079}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="3594011" y="4827415"/>
+          <a:ext cx="362111" cy="14378"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst>
+            <a:path>
+              <a:moveTo>
+                <a:pt x="0" y="7189"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="362111" y="7189"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:shade val="80000"/>
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="444500" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1000" kern="1200"/>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3766014" y="4825551"/>
+        <a:ext cx="18105" cy="18105"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{99BD4B49-7654-4BFC-93A2-73715A94DAC0}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="3956123" y="4612007"/>
+          <a:ext cx="4657573" cy="445193"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="6985" tIns="6985" rIns="6985" bIns="6985" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>소득이 높으면</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>(8</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>만불</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>+) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>완료율이 높을 것이다</a:t>
+          </a:r>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3969162" y="4625046"/>
+        <a:ext cx="4631495" cy="419115"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{48D36C81-0EEF-4879-868D-73109D1A61EF}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm rot="2847533">
+          <a:off x="1936848" y="5083401"/>
+          <a:ext cx="694867" cy="14378"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst>
+            <a:path>
+              <a:moveTo>
+                <a:pt x="0" y="7189"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="694867" y="7189"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:shade val="60000"/>
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="444500" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1000" kern="1200"/>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="2266910" y="5073219"/>
+        <a:ext cx="34743" cy="34743"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{E0C7A212-1F93-473A-8909-15A6780CBC2F}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="2519189" y="5123980"/>
+          <a:ext cx="1074822" cy="445193"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="6985" tIns="6985" rIns="6985" bIns="6985" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>나이</a:t>
+          </a:r>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="2532228" y="5137019"/>
+        <a:ext cx="1048744" cy="419115"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{4D54B04B-F98B-4577-8925-91ECEF877996}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="3594011" y="5339388"/>
+          <a:ext cx="374069" cy="14378"/>
+        </a:xfrm>
+        <a:custGeom>
+          <a:avLst/>
+          <a:gdLst/>
+          <a:ahLst/>
+          <a:cxnLst/>
+          <a:rect l="0" t="0" r="0" b="0"/>
+          <a:pathLst>
+            <a:path>
+              <a:moveTo>
+                <a:pt x="0" y="7189"/>
+              </a:moveTo>
+              <a:lnTo>
+                <a:pt x="374069" y="7189"/>
+              </a:lnTo>
+            </a:path>
+          </a:pathLst>
+        </a:custGeom>
+        <a:noFill/>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent6">
+              <a:shade val="80000"/>
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor"/>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="12700" tIns="0" rIns="12700" bIns="0" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="444500" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1000" kern="1200"/>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3771694" y="5337225"/>
+        <a:ext cx="18703" cy="18703"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+    <dsp:sp modelId="{540CB623-D523-4AD6-BF5D-A946D7B052E6}">
+      <dsp:nvSpPr>
+        <dsp:cNvPr id="0" name=""/>
+        <dsp:cNvSpPr/>
+      </dsp:nvSpPr>
+      <dsp:spPr>
+        <a:xfrm>
+          <a:off x="3968081" y="5123980"/>
+          <a:ext cx="4657573" cy="445193"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 10000"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="5B9BD5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:srgbClr>
+        </a:solidFill>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:sysClr val="window" lastClr="FFFFFF">
+              <a:hueOff val="0"/>
+              <a:satOff val="0"/>
+              <a:lumOff val="0"/>
+              <a:alphaOff val="0"/>
+            </a:sysClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:effectLst/>
+      </dsp:spPr>
+      <dsp:style>
+        <a:lnRef idx="2">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </dsp:style>
+      <dsp:txBody>
+        <a:bodyPr spcFirstLastPara="0" vert="horz" wrap="square" lIns="4445" tIns="4445" rIns="4445" bIns="4445" numCol="1" spcCol="1270" anchor="ctr" anchorCtr="0">
+          <a:noAutofit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" defTabSz="488950" latinLnBrk="1">
+            <a:lnSpc>
+              <a:spcPct val="90000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPct val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPct val="35000"/>
+            </a:spcAft>
+            <a:buNone/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>나이 평균</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>(54) </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>보다 높은면 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+              <a:ea typeface="맑은 고딕" panose="020B0503020000020004" pitchFamily="50" charset="-127"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>완료율이</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t> 낮을 것이다</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="ko-KR" sz="1100" b="1" kern="1200">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+            </a:rPr>
+            <a:t>.</a:t>
+          </a:r>
+          <a:endParaRPr lang="ko-KR" altLang="en-US" sz="1100" b="1" kern="1200">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+          </a:endParaRPr>
+        </a:p>
+      </dsp:txBody>
+      <dsp:txXfrm>
+        <a:off x="3981120" y="5137019"/>
+        <a:ext cx="4631495" cy="419115"/>
+      </dsp:txXfrm>
+    </dsp:sp>
+  </dsp:spTree>
+</dsp:drawing>
+</file>
+
 <file path=xl/diagrams/layout1.xml><?xml version="1.0" encoding="utf-8"?>
+<dgm:layoutDef xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uniqueId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2">
+  <dgm:title val=""/>
+  <dgm:desc val=""/>
+  <dgm:catLst>
+    <dgm:cat type="hierarchy" pri="5000"/>
+  </dgm:catLst>
+  <dgm:sampData>
+    <dgm:dataModel>
+      <dgm:ptLst>
+        <dgm:pt modelId="0" type="doc"/>
+        <dgm:pt modelId="1">
+          <dgm:prSet phldr="1"/>
+        </dgm:pt>
+        <dgm:pt modelId="2">
+          <dgm:prSet phldr="1"/>
+        </dgm:pt>
+        <dgm:pt modelId="21">
+          <dgm:prSet phldr="1"/>
+        </dgm:pt>
+        <dgm:pt modelId="22">
+          <dgm:prSet phldr="1"/>
+        </dgm:pt>
+        <dgm:pt modelId="3">
+          <dgm:prSet phldr="1"/>
+        </dgm:pt>
+        <dgm:pt modelId="31">
+          <dgm:prSet phldr="1"/>
+        </dgm:pt>
+      </dgm:ptLst>
+      <dgm:cxnLst>
+        <dgm:cxn modelId="4" srcId="0" destId="1" srcOrd="0" destOrd="0"/>
+        <dgm:cxn modelId="5" srcId="1" destId="2" srcOrd="0" destOrd="0"/>
+        <dgm:cxn modelId="6" srcId="1" destId="3" srcOrd="1" destOrd="0"/>
+        <dgm:cxn modelId="23" srcId="2" destId="21" srcOrd="0" destOrd="0"/>
+        <dgm:cxn modelId="24" srcId="2" destId="22" srcOrd="1" destOrd="0"/>
+        <dgm:cxn modelId="33" srcId="3" destId="31" srcOrd="0" destOrd="0"/>
+      </dgm:cxnLst>
+      <dgm:bg/>
+      <dgm:whole/>
+    </dgm:dataModel>
+  </dgm:sampData>
+  <dgm:styleData>
+    <dgm:dataModel>
+      <dgm:ptLst>
+        <dgm:pt modelId="0" type="doc"/>
+        <dgm:pt modelId="1"/>
+        <dgm:pt modelId="11"/>
+        <dgm:pt modelId="12"/>
+      </dgm:ptLst>
+      <dgm:cxnLst>
+        <dgm:cxn modelId="2" srcId="0" destId="1" srcOrd="0" destOrd="0"/>
+        <dgm:cxn modelId="13" srcId="1" destId="11" srcOrd="0" destOrd="0"/>
+        <dgm:cxn modelId="14" srcId="1" destId="12" srcOrd="1" destOrd="0"/>
+      </dgm:cxnLst>
+      <dgm:bg/>
+      <dgm:whole/>
+    </dgm:dataModel>
+  </dgm:styleData>
+  <dgm:clrData>
+    <dgm:dataModel>
+      <dgm:ptLst>
+        <dgm:pt modelId="0" type="doc"/>
+        <dgm:pt modelId="1"/>
+        <dgm:pt modelId="2"/>
+        <dgm:pt modelId="21"/>
+        <dgm:pt modelId="211"/>
+        <dgm:pt modelId="3"/>
+        <dgm:pt modelId="31"/>
+        <dgm:pt modelId="311"/>
+      </dgm:ptLst>
+      <dgm:cxnLst>
+        <dgm:cxn modelId="4" srcId="0" destId="1" srcOrd="0" destOrd="0"/>
+        <dgm:cxn modelId="5" srcId="1" destId="2" srcOrd="0" destOrd="0"/>
+        <dgm:cxn modelId="6" srcId="1" destId="3" srcOrd="1" destOrd="0"/>
+        <dgm:cxn modelId="23" srcId="2" destId="21" srcOrd="0" destOrd="0"/>
+        <dgm:cxn modelId="24" srcId="21" destId="211" srcOrd="0" destOrd="0"/>
+        <dgm:cxn modelId="33" srcId="3" destId="31" srcOrd="0" destOrd="0"/>
+        <dgm:cxn modelId="34" srcId="31" destId="311" srcOrd="0" destOrd="0"/>
+      </dgm:cxnLst>
+      <dgm:bg/>
+      <dgm:whole/>
+    </dgm:dataModel>
+  </dgm:clrData>
+  <dgm:layoutNode name="diagram">
+    <dgm:varLst>
+      <dgm:chPref val="1"/>
+      <dgm:dir/>
+      <dgm:animOne val="branch"/>
+      <dgm:animLvl val="lvl"/>
+      <dgm:resizeHandles val="exact"/>
+    </dgm:varLst>
+    <dgm:choose name="Name0">
+      <dgm:if name="Name1" func="var" arg="dir" op="equ" val="norm">
+        <dgm:alg type="hierChild">
+          <dgm:param type="linDir" val="fromT"/>
+          <dgm:param type="chAlign" val="l"/>
+        </dgm:alg>
+      </dgm:if>
+      <dgm:else name="Name2">
+        <dgm:alg type="hierChild">
+          <dgm:param type="linDir" val="fromT"/>
+          <dgm:param type="chAlign" val="r"/>
+        </dgm:alg>
+      </dgm:else>
+    </dgm:choose>
+    <dgm:shape xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:blip="">
+      <dgm:adjLst/>
+    </dgm:shape>
+    <dgm:presOf/>
+    <dgm:constrLst>
+      <dgm:constr type="h" for="des" ptType="node" refType="h"/>
+      <dgm:constr type="w" for="des" ptType="node" refType="h" refFor="des" refPtType="node" fact="2"/>
+      <dgm:constr type="sibSp" refType="h" refFor="des" refPtType="node" op="equ" fact="0.15"/>
+      <dgm:constr type="sibSp" for="des" forName="level2hierChild" refType="h" refFor="des" refPtType="node" op="equ" fact="0.15"/>
+      <dgm:constr type="sibSp" for="des" forName="level3hierChild" refType="h" refFor="des" refPtType="node" op="equ" fact="0.15"/>
+      <dgm:constr type="sp" for="des" forName="root1" refType="w" refFor="des" refPtType="node" fact="0.4"/>
+      <dgm:constr type="sp" for="des" forName="root2" refType="sp" refFor="des" refForName="root1" op="equ"/>
+      <dgm:constr type="primFontSz" for="des" ptType="node" op="equ" val="65"/>
+      <dgm:constr type="primFontSz" for="des" forName="connTx" op="equ" val="55"/>
+      <dgm:constr type="primFontSz" for="des" forName="connTx" refType="primFontSz" refFor="des" refPtType="node" op="lte" fact="0.8"/>
+    </dgm:constrLst>
+    <dgm:ruleLst/>
+    <dgm:forEach name="Name3" axis="ch">
+      <dgm:forEach name="Name4" axis="self" ptType="node">
+        <dgm:layoutNode name="root1">
+          <dgm:choose name="Name5">
+            <dgm:if name="Name6" func="var" arg="dir" op="equ" val="norm">
+              <dgm:alg type="hierRoot">
+                <dgm:param type="hierAlign" val="lCtrCh"/>
+              </dgm:alg>
+            </dgm:if>
+            <dgm:else name="Name7">
+              <dgm:alg type="hierRoot">
+                <dgm:param type="hierAlign" val="rCtrCh"/>
+              </dgm:alg>
+            </dgm:else>
+          </dgm:choose>
+          <dgm:shape xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:blip="">
+            <dgm:adjLst/>
+          </dgm:shape>
+          <dgm:presOf/>
+          <dgm:constrLst/>
+          <dgm:ruleLst/>
+          <dgm:layoutNode name="LevelOneTextNode" styleLbl="node0">
+            <dgm:varLst>
+              <dgm:chPref val="3"/>
+            </dgm:varLst>
+            <dgm:alg type="tx"/>
+            <dgm:shape xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" type="roundRect" r:blip="">
+              <dgm:adjLst>
+                <dgm:adj idx="1" val="0.1"/>
+              </dgm:adjLst>
+            </dgm:shape>
+            <dgm:presOf axis="self"/>
+            <dgm:constrLst>
+              <dgm:constr type="tMarg" refType="primFontSz" fact="0.05"/>
+              <dgm:constr type="bMarg" refType="primFontSz" fact="0.05"/>
+              <dgm:constr type="lMarg" refType="primFontSz" fact="0.05"/>
+              <dgm:constr type="rMarg" refType="primFontSz" fact="0.05"/>
+            </dgm:constrLst>
+            <dgm:ruleLst>
+              <dgm:rule type="primFontSz" val="5" fact="NaN" max="NaN"/>
+            </dgm:ruleLst>
+          </dgm:layoutNode>
+          <dgm:layoutNode name="level2hierChild">
+            <dgm:choose name="Name8">
+              <dgm:if name="Name9" func="var" arg="dir" op="equ" val="norm">
+                <dgm:alg type="hierChild">
+                  <dgm:param type="linDir" val="fromT"/>
+                  <dgm:param type="chAlign" val="l"/>
+                </dgm:alg>
+              </dgm:if>
+              <dgm:else name="Name10">
+                <dgm:alg type="hierChild">
+                  <dgm:param type="linDir" val="fromT"/>
+                  <dgm:param type="chAlign" val="r"/>
+                </dgm:alg>
+              </dgm:else>
+            </dgm:choose>
+            <dgm:shape xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:blip="">
+              <dgm:adjLst/>
+            </dgm:shape>
+            <dgm:presOf/>
+            <dgm:constrLst/>
+            <dgm:ruleLst/>
+            <dgm:forEach name="repeat" axis="ch">
+              <dgm:forEach name="Name11" axis="self" ptType="parTrans" cnt="1">
+                <dgm:layoutNode name="conn2-1">
+                  <dgm:choose name="Name12">
+                    <dgm:if name="Name13" func="var" arg="dir" op="equ" val="norm">
+                      <dgm:alg type="conn">
+                        <dgm:param type="dim" val="1D"/>
+                        <dgm:param type="begPts" val="midR"/>
+                        <dgm:param type="endPts" val="midL"/>
+                        <dgm:param type="endSty" val="noArr"/>
+                      </dgm:alg>
+                    </dgm:if>
+                    <dgm:else name="Name14">
+                      <dgm:alg type="conn">
+                        <dgm:param type="dim" val="1D"/>
+                        <dgm:param type="begPts" val="midL"/>
+                        <dgm:param type="endPts" val="midR"/>
+                        <dgm:param type="endSty" val="noArr"/>
+                      </dgm:alg>
+                    </dgm:else>
+                  </dgm:choose>
+                  <dgm:shape xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" type="conn" r:blip="">
+                    <dgm:adjLst/>
+                  </dgm:shape>
+                  <dgm:presOf axis="self"/>
+                  <dgm:constrLst>
+                    <dgm:constr type="w" val="1"/>
+                    <dgm:constr type="h" val="5"/>
+                    <dgm:constr type="connDist"/>
+                    <dgm:constr type="begPad"/>
+                    <dgm:constr type="endPad"/>
+                    <dgm:constr type="userA" for="ch" refType="connDist"/>
+                  </dgm:constrLst>
+                  <dgm:ruleLst/>
+                  <dgm:layoutNode name="connTx">
+                    <dgm:alg type="tx">
+                      <dgm:param type="autoTxRot" val="grav"/>
+                    </dgm:alg>
+                    <dgm:shape xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" type="rect" r:blip="" hideGeom="1">
+                      <dgm:adjLst/>
+                    </dgm:shape>
+                    <dgm:presOf axis="self"/>
+                    <dgm:constrLst>
+                      <dgm:constr type="userA"/>
+                      <dgm:constr type="w" refType="userA" fact="0.05"/>
+                      <dgm:constr type="h" refType="userA" fact="0.05"/>
+                      <dgm:constr type="lMarg" val="1"/>
+                      <dgm:constr type="rMarg" val="1"/>
+                      <dgm:constr type="tMarg"/>
+                      <dgm:constr type="bMarg"/>
+                    </dgm:constrLst>
+                    <dgm:ruleLst>
+                      <dgm:rule type="h" val="NaN" fact="0.25" max="NaN"/>
+                      <dgm:rule type="w" val="NaN" fact="0.8" max="NaN"/>
+                      <dgm:rule type="primFontSz" val="5" fact="NaN" max="NaN"/>
+                    </dgm:ruleLst>
+                  </dgm:layoutNode>
+                </dgm:layoutNode>
+              </dgm:forEach>
+              <dgm:forEach name="Name15" axis="self" ptType="node">
+                <dgm:layoutNode name="root2">
+                  <dgm:choose name="Name16">
+                    <dgm:if name="Name17" func="var" arg="dir" op="equ" val="norm">
+                      <dgm:alg type="hierRoot">
+                        <dgm:param type="hierAlign" val="lCtrCh"/>
+                      </dgm:alg>
+                    </dgm:if>
+                    <dgm:else name="Name18">
+                      <dgm:alg type="hierRoot">
+                        <dgm:param type="hierAlign" val="rCtrCh"/>
+                      </dgm:alg>
+                    </dgm:else>
+                  </dgm:choose>
+                  <dgm:shape xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:blip="">
+                    <dgm:adjLst/>
+                  </dgm:shape>
+                  <dgm:presOf/>
+                  <dgm:constrLst/>
+                  <dgm:ruleLst/>
+                  <dgm:layoutNode name="LevelTwoTextNode">
+                    <dgm:varLst>
+                      <dgm:chPref val="3"/>
+                    </dgm:varLst>
+                    <dgm:alg type="tx"/>
+                    <dgm:shape xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" type="roundRect" r:blip="">
+                      <dgm:adjLst>
+                        <dgm:adj idx="1" val="0.1"/>
+                      </dgm:adjLst>
+                    </dgm:shape>
+                    <dgm:presOf axis="self"/>
+                    <dgm:constrLst>
+                      <dgm:constr type="tMarg" refType="primFontSz" fact="0.05"/>
+                      <dgm:constr type="bMarg" refType="primFontSz" fact="0.05"/>
+                      <dgm:constr type="lMarg" refType="primFontSz" fact="0.05"/>
+                      <dgm:constr type="rMarg" refType="primFontSz" fact="0.05"/>
+                    </dgm:constrLst>
+                    <dgm:ruleLst>
+                      <dgm:rule type="primFontSz" val="5" fact="NaN" max="NaN"/>
+                    </dgm:ruleLst>
+                  </dgm:layoutNode>
+                  <dgm:layoutNode name="level3hierChild">
+                    <dgm:choose name="Name19">
+                      <dgm:if name="Name20" func="var" arg="dir" op="equ" val="norm">
+                        <dgm:alg type="hierChild">
+                          <dgm:param type="linDir" val="fromT"/>
+                          <dgm:param type="chAlign" val="l"/>
+                        </dgm:alg>
+                      </dgm:if>
+                      <dgm:else name="Name21">
+                        <dgm:alg type="hierChild">
+                          <dgm:param type="linDir" val="fromT"/>
+                          <dgm:param type="chAlign" val="r"/>
+                        </dgm:alg>
+                      </dgm:else>
+                    </dgm:choose>
+                    <dgm:shape xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:blip="">
+                      <dgm:adjLst/>
+                    </dgm:shape>
+                    <dgm:presOf/>
+                    <dgm:constrLst/>
+                    <dgm:ruleLst/>
+                    <dgm:forEach name="Name22" ref="repeat"/>
+                  </dgm:layoutNode>
+                </dgm:layoutNode>
+              </dgm:forEach>
+            </dgm:forEach>
+          </dgm:layoutNode>
+        </dgm:layoutNode>
+      </dgm:forEach>
+    </dgm:forEach>
+  </dgm:layoutNode>
+</dgm:layoutDef>
+</file>
+
+<file path=xl/diagrams/layout2.xml><?xml version="1.0" encoding="utf-8"?>
 <dgm:layoutDef xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uniqueId="urn:microsoft.com/office/officeart/2005/8/layout/hierarchy2">
   <dgm:title val=""/>
   <dgm:desc val=""/>
@@ -10519,6 +17787,1040 @@
 </dgm:styleDef>
 </file>
 
+<file path=xl/diagrams/quickStyle2.xml><?xml version="1.0" encoding="utf-8"?>
+<dgm:styleDef xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" uniqueId="urn:microsoft.com/office/officeart/2005/8/quickstyle/simple1">
+  <dgm:title val=""/>
+  <dgm:desc val=""/>
+  <dgm:catLst>
+    <dgm:cat type="simple" pri="10100"/>
+  </dgm:catLst>
+  <dgm:scene3d>
+    <a:camera prst="orthographicFront"/>
+    <a:lightRig rig="threePt" dir="t"/>
+  </dgm:scene3d>
+  <dgm:styleLbl name="node0">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="lnNode1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="vennNode1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="tx1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="alignNode1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="node1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="node2">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="node3">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="node4">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgImgPlace1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="alignImgPlace1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="bgImgPlace1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="sibTrans2D1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgSibTrans2D1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="bgSibTrans2D1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="sibTrans1D1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="callout">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="asst0">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="asst1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="asst2">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="asst3">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="asst4">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans2D1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans2D2">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans2D3">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans2D4">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor">
+        <a:schemeClr val="lt1"/>
+      </a:fontRef>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans1D1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans1D2">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans1D3">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="parChTrans1D4">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgAcc1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="conFgAcc1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="alignAcc1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="trAlignAcc1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="bgAcc1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="solidFgAcc1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="solidAlignAcc1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="solidBgAcc1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgAccFollowNode1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="alignAccFollowNode1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="bgAccFollowNode1">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgAcc0">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgAcc2">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgAcc3">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgAcc4">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="bgShp">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="dkBgShp">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="trBgShp">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="fgShp">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="2">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="1">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+  <dgm:styleLbl name="revTx">
+    <dgm:scene3d>
+      <a:camera prst="orthographicFront"/>
+      <a:lightRig rig="threePt" dir="t"/>
+    </dgm:scene3d>
+    <dgm:sp3d/>
+    <dgm:txPr/>
+    <dgm:style>
+      <a:lnRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:lnRef>
+      <a:fillRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:fillRef>
+      <a:effectRef idx="0">
+        <a:scrgbClr r="0" g="0" b="0"/>
+      </a:effectRef>
+      <a:fontRef idx="minor"/>
+    </dgm:style>
+  </dgm:styleLbl>
+</dgm:styleDef>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -10604,6 +18906,47 @@
         </a:prstGeom>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>53340</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>45720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>108781</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="다이어그램 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89D7E630-BD8F-4D5E-A814-B0B67C0FDA13}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/diagram">
+          <dgm:relIds xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:dm="rId1" r:lo="rId2" r:qs="rId3" r:cs="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -11060,7 +19403,7 @@
     </row>
     <row r="35" spans="1:1" hidden="1" outlineLevel="2" x14ac:dyDescent="0.45">
       <c r="A35" s="20" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="36" spans="1:1" hidden="1" outlineLevel="2" x14ac:dyDescent="0.45">
@@ -11602,7 +19945,7 @@
         <v>46274</v>
       </c>
       <c r="D2" s="27" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="34" x14ac:dyDescent="0.45">
@@ -11610,24 +19953,28 @@
         <v>174</v>
       </c>
       <c r="B3" s="56" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C3" s="35">
         <v>46274</v>
       </c>
-      <c r="D3" s="33"/>
+      <c r="D3" s="33" t="s">
+        <v>317</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" s="33" t="s">
         <v>172</v>
       </c>
       <c r="B4" s="56" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C4" s="35">
         <v>46274</v>
       </c>
-      <c r="D4" s="33"/>
+      <c r="D4" s="33" t="s">
+        <v>317</v>
+      </c>
     </row>
     <row r="5" spans="1:4" ht="34" x14ac:dyDescent="0.45">
       <c r="A5" s="34" t="s">
@@ -11637,7 +19984,9 @@
       <c r="C5" s="35">
         <v>46275</v>
       </c>
-      <c r="D5" s="33"/>
+      <c r="D5" s="33" t="s">
+        <v>318</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" s="33" t="s">
@@ -11743,7 +20092,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A2" s="57" t="s">
+      <c r="A2" s="58" t="s">
         <v>18</v>
       </c>
       <c r="B2" s="7" t="s">
@@ -11760,7 +20109,7 @@
       <c r="G2" s="10"/>
     </row>
     <row r="3" spans="1:7" ht="64" x14ac:dyDescent="0.45">
-      <c r="A3" s="58"/>
+      <c r="A3" s="59"/>
       <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
@@ -11777,7 +20126,7 @@
       <c r="G3" s="11"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A4" s="58"/>
+      <c r="A4" s="59"/>
       <c r="B4" s="4" t="s">
         <v>185</v>
       </c>
@@ -11792,7 +20141,7 @@
       <c r="G4" s="11"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A5" s="58"/>
+      <c r="A5" s="59"/>
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
@@ -11807,7 +20156,7 @@
       <c r="G5" s="11"/>
     </row>
     <row r="6" spans="1:7" ht="48" x14ac:dyDescent="0.45">
-      <c r="A6" s="58"/>
+      <c r="A6" s="59"/>
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
@@ -11826,7 +20175,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="59"/>
+      <c r="A7" s="60"/>
       <c r="B7" s="13" t="s">
         <v>15</v>
       </c>
@@ -11837,13 +20186,13 @@
         <v>14</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F7" s="14"/>
       <c r="G7" s="15"/>
     </row>
     <row r="8" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="60" t="s">
+      <c r="A8" s="61" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="7" t="s">
@@ -11860,11 +20209,11 @@
         <v>36</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A9" s="61"/>
+      <c r="A9" s="62"/>
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -11877,11 +20226,11 @@
       <c r="E9" s="5"/>
       <c r="F9" s="3"/>
       <c r="G9" s="10" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A10" s="61"/>
+      <c r="A10" s="62"/>
       <c r="B10" s="4" t="s">
         <v>4</v>
       </c>
@@ -11892,13 +20241,13 @@
         <v>14</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="11"/>
     </row>
     <row r="11" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="61"/>
+      <c r="A11" s="62"/>
       <c r="B11" s="4" t="s">
         <v>7</v>
       </c>
@@ -11913,7 +20262,7 @@
       <c r="G11" s="11"/>
     </row>
     <row r="12" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="62"/>
+      <c r="A12" s="63"/>
       <c r="B12" s="16" t="s">
         <v>8</v>
       </c>
@@ -11926,11 +20275,11 @@
       <c r="E12" s="13"/>
       <c r="F12" s="14"/>
       <c r="G12" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A13" s="63" t="s">
+      <c r="A13" s="64" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="7" t="s">
@@ -11943,15 +20292,15 @@
         <v>14</v>
       </c>
       <c r="E13" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F13" s="9"/>
       <c r="G13" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="14" spans="1:7" ht="64.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="64"/>
+      <c r="A14" s="65"/>
       <c r="B14" s="4" t="s">
         <v>10</v>
       </c>
@@ -11968,9 +20317,9 @@
       <c r="G14" s="11"/>
     </row>
     <row r="15" spans="1:7" ht="64" x14ac:dyDescent="0.45">
-      <c r="A15" s="64"/>
+      <c r="A15" s="65"/>
       <c r="B15" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>45</v>
@@ -11979,17 +20328,17 @@
         <v>13</v>
       </c>
       <c r="E15" s="8" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>41</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="16" spans="1:7" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A16" s="65"/>
+      <c r="A16" s="66"/>
       <c r="B16" s="16" t="s">
         <v>11</v>
       </c>
@@ -12002,7 +20351,7 @@
       <c r="E16" s="13"/>
       <c r="F16" s="14"/>
       <c r="G16" s="42" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
   </sheetData>
@@ -12104,7 +20453,7 @@
         <v>197</v>
       </c>
       <c r="D1" s="40" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
@@ -12115,10 +20464,10 @@
         <v>198</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D2" s="50" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="64" x14ac:dyDescent="0.45">
@@ -12126,7 +20475,7 @@
         <v>190</v>
       </c>
       <c r="B3" s="46" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C3" s="37" t="s">
         <v>199</v>
@@ -12136,62 +20485,62 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A5" s="67" t="s">
-        <v>275</v>
-      </c>
-      <c r="B5" s="67"/>
-      <c r="C5" s="67"/>
+      <c r="A5" s="74" t="s">
+        <v>274</v>
+      </c>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
     </row>
     <row r="6" spans="1:4" ht="32" x14ac:dyDescent="0.45">
-      <c r="A6" s="79" t="s">
+      <c r="A6" s="76" t="s">
         <v>205</v>
       </c>
       <c r="B6" s="47" t="s">
         <v>206</v>
       </c>
       <c r="C6" s="48" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="32" x14ac:dyDescent="0.45">
-      <c r="A7" s="80"/>
+      <c r="A7" s="77"/>
       <c r="B7" s="47" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C7" s="48" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="32" x14ac:dyDescent="0.45">
-      <c r="A8" s="80"/>
+      <c r="A8" s="77"/>
       <c r="B8" s="47" t="s">
+        <v>296</v>
+      </c>
+      <c r="C8" s="48" t="s">
         <v>297</v>
-      </c>
-      <c r="C8" s="48" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A9" s="80"/>
+      <c r="A9" s="77"/>
       <c r="B9" s="47" t="s">
-        <v>305</v>
-      </c>
-      <c r="C9" s="85" t="s">
-        <v>318</v>
+        <v>304</v>
+      </c>
+      <c r="C9" s="57" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A10" s="81"/>
+      <c r="A10" s="78"/>
       <c r="B10" s="47" t="s">
+        <v>298</v>
+      </c>
+      <c r="C10" s="48" t="s">
         <v>299</v>
-      </c>
-      <c r="C10" s="48" t="s">
-        <v>300</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A11" s="54" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B11" s="47" t="s">
         <v>207</v>
@@ -12204,18 +20553,18 @@
       <c r="C12" s="49"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A13" s="72" t="s">
-        <v>306</v>
-      </c>
-      <c r="B13" s="73"/>
-      <c r="C13" s="74"/>
+      <c r="A13" s="68" t="s">
+        <v>305</v>
+      </c>
+      <c r="B13" s="69"/>
+      <c r="C13" s="70"/>
     </row>
     <row r="14" spans="1:4" ht="52" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="82" t="s">
-        <v>232</v>
-      </c>
-      <c r="B14" s="83"/>
-      <c r="C14" s="84"/>
+      <c r="A14" s="79" t="s">
+        <v>231</v>
+      </c>
+      <c r="B14" s="80"/>
+      <c r="C14" s="81"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="49"/>
@@ -12223,440 +20572,452 @@
       <c r="D19" s="49"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A31" s="67" t="s">
-        <v>276</v>
-      </c>
-      <c r="B31" s="67"/>
-      <c r="C31" s="67"/>
+      <c r="A31" s="74" t="s">
+        <v>275</v>
+      </c>
+      <c r="B31" s="74"/>
+      <c r="C31" s="74"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A32" s="75" t="s">
-        <v>209</v>
-      </c>
-      <c r="B32" s="76"/>
-      <c r="C32" s="77"/>
+      <c r="A32" s="71" t="s">
+        <v>320</v>
+      </c>
+      <c r="B32" s="72"/>
+      <c r="C32" s="73"/>
     </row>
     <row r="33" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="71" t="s">
-        <v>233</v>
+      <c r="A33" s="67" t="s">
+        <v>232</v>
       </c>
       <c r="B33" s="50" t="s">
-        <v>210</v>
-      </c>
-      <c r="C33" s="78" t="s">
-        <v>307</v>
+        <v>209</v>
+      </c>
+      <c r="C33" s="75" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A34" s="71"/>
+      <c r="A34" s="67"/>
       <c r="B34" s="50" t="s">
-        <v>211</v>
-      </c>
-      <c r="C34" s="78"/>
+        <v>210</v>
+      </c>
+      <c r="C34" s="75"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A35" s="71"/>
+      <c r="A35" s="67"/>
       <c r="B35" s="50" t="s">
-        <v>212</v>
-      </c>
-      <c r="C35" s="78"/>
+        <v>211</v>
+      </c>
+      <c r="C35" s="75"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A36" s="71"/>
+      <c r="A36" s="67"/>
       <c r="B36" s="50" t="s">
-        <v>213</v>
-      </c>
-      <c r="C36" s="78"/>
+        <v>212</v>
+      </c>
+      <c r="C36" s="75"/>
     </row>
     <row r="37" spans="1:5" ht="32" x14ac:dyDescent="0.45">
-      <c r="A37" s="71"/>
+      <c r="A37" s="67"/>
       <c r="B37" s="48" t="s">
-        <v>214</v>
-      </c>
-      <c r="C37" s="78"/>
+        <v>213</v>
+      </c>
+      <c r="C37" s="75"/>
     </row>
     <row r="38" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="71" t="s">
-        <v>234</v>
+      <c r="A38" s="67" t="s">
+        <v>233</v>
       </c>
       <c r="B38" s="50" t="s">
-        <v>215</v>
-      </c>
-      <c r="C38" s="78" t="s">
-        <v>218</v>
+        <v>214</v>
+      </c>
+      <c r="C38" s="75" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A39" s="71"/>
+      <c r="A39" s="67"/>
       <c r="B39" s="50" t="s">
-        <v>216</v>
-      </c>
-      <c r="C39" s="78"/>
+        <v>215</v>
+      </c>
+      <c r="C39" s="75"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A40" s="71"/>
+      <c r="A40" s="67"/>
       <c r="B40" s="50" t="s">
-        <v>217</v>
-      </c>
-      <c r="C40" s="78"/>
+        <v>216</v>
+      </c>
+      <c r="C40" s="75"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A42" s="72" t="s">
-        <v>274</v>
-      </c>
-      <c r="B42" s="73"/>
-      <c r="C42" s="74"/>
+      <c r="A42" s="68" t="s">
+        <v>273</v>
+      </c>
+      <c r="B42" s="69"/>
+      <c r="C42" s="70"/>
     </row>
     <row r="43" spans="1:5" ht="53" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A43" s="71" t="s">
-        <v>219</v>
-      </c>
-      <c r="B43" s="71"/>
-      <c r="C43" s="71"/>
+      <c r="A43" s="67" t="s">
+        <v>218</v>
+      </c>
+      <c r="B43" s="67"/>
+      <c r="C43" s="67"/>
     </row>
     <row r="44" spans="1:5" ht="50.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A44" s="71" t="s">
-        <v>308</v>
-      </c>
-      <c r="B44" s="71"/>
-      <c r="C44" s="71"/>
+      <c r="A44" s="67" t="s">
+        <v>319</v>
+      </c>
+      <c r="B44" s="67"/>
+      <c r="C44" s="67"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A46" s="67" t="s">
-        <v>273</v>
-      </c>
-      <c r="B46" s="67"/>
-      <c r="C46" s="67"/>
-      <c r="D46" s="67"/>
-      <c r="E46" s="67"/>
+      <c r="A46" s="74" t="s">
+        <v>272</v>
+      </c>
+      <c r="B46" s="74"/>
+      <c r="C46" s="74"/>
+      <c r="D46" s="74"/>
+      <c r="E46" s="74"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" s="44" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B47" s="44" t="s">
+        <v>243</v>
+      </c>
+      <c r="C47" s="44" t="s">
         <v>244</v>
       </c>
-      <c r="C47" s="44" t="s">
+      <c r="D47" s="44" t="s">
         <v>245</v>
       </c>
-      <c r="D47" s="44" t="s">
+      <c r="E47" s="44" t="s">
         <v>246</v>
-      </c>
-      <c r="E47" s="44" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="48" spans="1:5" ht="32" x14ac:dyDescent="0.45">
       <c r="A48" s="43" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B48" s="43" t="s">
+        <v>235</v>
+      </c>
+      <c r="C48" s="43" t="s">
+        <v>308</v>
+      </c>
+      <c r="D48" s="43" t="s">
         <v>236</v>
       </c>
-      <c r="C48" s="43" t="s">
-        <v>310</v>
-      </c>
-      <c r="D48" s="43" t="s">
+      <c r="E48" s="43" t="s">
         <v>237</v>
-      </c>
-      <c r="E48" s="43" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="32" x14ac:dyDescent="0.45">
       <c r="A49" s="43" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B49" s="43" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C49" s="43" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="D49" s="43" t="s">
+        <v>236</v>
+      </c>
+      <c r="E49" s="43" t="s">
         <v>237</v>
-      </c>
-      <c r="E49" s="43" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="50" spans="1:5" ht="48" x14ac:dyDescent="0.45">
       <c r="A50" s="43" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B50" s="43" t="s">
+        <v>238</v>
+      </c>
+      <c r="C50" s="43" t="s">
+        <v>315</v>
+      </c>
+      <c r="D50" s="43" t="s">
         <v>239</v>
       </c>
-      <c r="C50" s="43" t="s">
-        <v>317</v>
-      </c>
-      <c r="D50" s="43" t="s">
-        <v>240</v>
-      </c>
       <c r="E50" s="43" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="32" x14ac:dyDescent="0.45">
       <c r="A51" s="43" t="s">
+        <v>249</v>
+      </c>
+      <c r="B51" s="43" t="s">
+        <v>240</v>
+      </c>
+      <c r="C51" s="43" t="s">
         <v>250</v>
       </c>
-      <c r="B51" s="43" t="s">
+      <c r="D51" s="43" t="s">
         <v>241</v>
       </c>
-      <c r="C51" s="43" t="s">
-        <v>251</v>
-      </c>
-      <c r="D51" s="43" t="s">
-        <v>242</v>
-      </c>
       <c r="E51" s="43" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="32" x14ac:dyDescent="0.45">
       <c r="A52" s="43" t="s">
+        <v>251</v>
+      </c>
+      <c r="B52" s="43" t="s">
+        <v>240</v>
+      </c>
+      <c r="C52" s="43" t="s">
         <v>252</v>
       </c>
-      <c r="B52" s="43" t="s">
+      <c r="D52" s="43" t="s">
         <v>241</v>
       </c>
-      <c r="C52" s="43" t="s">
-        <v>253</v>
-      </c>
-      <c r="D52" s="43" t="s">
-        <v>242</v>
-      </c>
       <c r="E52" s="43" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="53" spans="1:5" ht="32" x14ac:dyDescent="0.45">
       <c r="A53" s="43" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B53" s="43" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C53" s="43" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D53" s="43" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E53" s="43" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" s="43" t="s">
+        <v>311</v>
+      </c>
+      <c r="B54" s="43" t="s">
+        <v>240</v>
+      </c>
+      <c r="C54" s="43" t="s">
         <v>313</v>
       </c>
-      <c r="B54" s="43" t="s">
-        <v>241</v>
-      </c>
-      <c r="C54" s="43" t="s">
-        <v>315</v>
-      </c>
       <c r="D54" s="43" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="E54" s="43" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="32" x14ac:dyDescent="0.45">
       <c r="A55" s="43" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B55" s="43" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C55" s="43" t="s">
+        <v>254</v>
+      </c>
+      <c r="D55" s="43" t="s">
+        <v>242</v>
+      </c>
+      <c r="E55" s="43" t="s">
         <v>255</v>
-      </c>
-      <c r="D55" s="43" t="s">
-        <v>243</v>
-      </c>
-      <c r="E55" s="43" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="48" x14ac:dyDescent="0.45">
       <c r="A56" s="43"/>
       <c r="B56" s="43" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C56" s="43" t="s">
+        <v>258</v>
+      </c>
+      <c r="D56" s="43" t="s">
         <v>259</v>
       </c>
-      <c r="D56" s="43" t="s">
-        <v>260</v>
-      </c>
       <c r="E56" s="51" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="48" x14ac:dyDescent="0.45">
       <c r="A57" s="43"/>
       <c r="B57" s="43" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C57" s="43" t="s">
+        <v>260</v>
+      </c>
+      <c r="D57" s="43" t="s">
         <v>261</v>
       </c>
-      <c r="D57" s="43" t="s">
+      <c r="E57" s="51" t="s">
         <v>262</v>
-      </c>
-      <c r="E57" s="51" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A59" s="68" t="s">
-        <v>277</v>
-      </c>
-      <c r="B59" s="69"/>
-      <c r="C59" s="70"/>
+      <c r="A59" s="83" t="s">
+        <v>276</v>
+      </c>
+      <c r="B59" s="84"/>
+      <c r="C59" s="85"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" s="53" t="s">
+        <v>277</v>
+      </c>
+      <c r="B60" s="53" t="s">
         <v>278</v>
       </c>
-      <c r="B60" s="53" t="s">
+      <c r="C60" s="53" t="s">
         <v>279</v>
-      </c>
-      <c r="C60" s="53" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="61" spans="1:5" ht="32" x14ac:dyDescent="0.45">
       <c r="A61" s="52" t="s">
+        <v>280</v>
+      </c>
+      <c r="B61" s="52" t="s">
         <v>281</v>
       </c>
-      <c r="B61" s="52" t="s">
+      <c r="C61" s="52" t="s">
         <v>282</v>
-      </c>
-      <c r="C61" s="52" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="62" spans="1:5" ht="32" x14ac:dyDescent="0.45">
       <c r="A62" s="52" t="s">
+        <v>283</v>
+      </c>
+      <c r="B62" s="52" t="s">
         <v>284</v>
       </c>
-      <c r="B62" s="52" t="s">
+      <c r="C62" s="52" t="s">
         <v>285</v>
-      </c>
-      <c r="C62" s="52" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="63" spans="1:5" ht="32" x14ac:dyDescent="0.45">
       <c r="A63" s="52" t="s">
+        <v>286</v>
+      </c>
+      <c r="B63" s="52" t="s">
         <v>287</v>
       </c>
-      <c r="B63" s="52" t="s">
+      <c r="C63" s="52" t="s">
         <v>288</v>
-      </c>
-      <c r="C63" s="52" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A64" s="52" t="s">
+        <v>289</v>
+      </c>
+      <c r="B64" s="52" t="s">
         <v>290</v>
       </c>
-      <c r="B64" s="52" t="s">
+      <c r="C64" s="52" t="s">
         <v>291</v>
-      </c>
-      <c r="C64" s="52" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A66" s="67" t="s">
-        <v>293</v>
-      </c>
-      <c r="B66" s="67"/>
-      <c r="C66" s="67"/>
-      <c r="D66" s="67"/>
+      <c r="A66" s="74" t="s">
+        <v>292</v>
+      </c>
+      <c r="B66" s="74"/>
+      <c r="C66" s="74"/>
+      <c r="D66" s="74"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A67" s="66" t="s">
-        <v>264</v>
-      </c>
-      <c r="B67" s="66"/>
-      <c r="C67" s="66"/>
-      <c r="D67" s="66"/>
+      <c r="A67" s="82" t="s">
+        <v>263</v>
+      </c>
+      <c r="B67" s="82"/>
+      <c r="C67" s="82"/>
+      <c r="D67" s="82"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A68" s="66" t="s">
-        <v>265</v>
-      </c>
-      <c r="B68" s="66"/>
-      <c r="C68" s="66"/>
-      <c r="D68" s="66"/>
+      <c r="A68" s="82" t="s">
+        <v>264</v>
+      </c>
+      <c r="B68" s="82"/>
+      <c r="C68" s="82"/>
+      <c r="D68" s="82"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A69" s="66" t="s">
-        <v>266</v>
-      </c>
-      <c r="B69" s="66"/>
-      <c r="C69" s="66"/>
-      <c r="D69" s="66"/>
+      <c r="A69" s="82" t="s">
+        <v>265</v>
+      </c>
+      <c r="B69" s="82"/>
+      <c r="C69" s="82"/>
+      <c r="D69" s="82"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A70" s="66" t="s">
-        <v>267</v>
-      </c>
-      <c r="B70" s="66"/>
-      <c r="C70" s="66"/>
-      <c r="D70" s="66"/>
+      <c r="A70" s="82" t="s">
+        <v>266</v>
+      </c>
+      <c r="B70" s="82"/>
+      <c r="C70" s="82"/>
+      <c r="D70" s="82"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A71" s="66" t="s">
-        <v>268</v>
-      </c>
-      <c r="B71" s="66"/>
-      <c r="C71" s="66"/>
-      <c r="D71" s="66"/>
+      <c r="A71" s="82" t="s">
+        <v>267</v>
+      </c>
+      <c r="B71" s="82"/>
+      <c r="C71" s="82"/>
+      <c r="D71" s="82"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A72" s="66" t="s">
-        <v>269</v>
-      </c>
-      <c r="B72" s="66"/>
-      <c r="C72" s="66"/>
-      <c r="D72" s="66"/>
+      <c r="A72" s="82" t="s">
+        <v>268</v>
+      </c>
+      <c r="B72" s="82"/>
+      <c r="C72" s="82"/>
+      <c r="D72" s="82"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A73" s="66" t="s">
-        <v>270</v>
-      </c>
-      <c r="B73" s="66"/>
-      <c r="C73" s="66"/>
-      <c r="D73" s="66"/>
+      <c r="A73" s="82" t="s">
+        <v>269</v>
+      </c>
+      <c r="B73" s="82"/>
+      <c r="C73" s="82"/>
+      <c r="D73" s="82"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A74" s="66" t="s">
-        <v>271</v>
-      </c>
-      <c r="B74" s="66"/>
-      <c r="C74" s="66"/>
-      <c r="D74" s="66"/>
+      <c r="A74" s="82" t="s">
+        <v>270</v>
+      </c>
+      <c r="B74" s="82"/>
+      <c r="C74" s="82"/>
+      <c r="D74" s="82"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A75" s="66" t="s">
-        <v>272</v>
-      </c>
-      <c r="B75" s="66"/>
-      <c r="C75" s="66"/>
-      <c r="D75" s="66"/>
+      <c r="A75" s="82" t="s">
+        <v>271</v>
+      </c>
+      <c r="B75" s="82"/>
+      <c r="C75" s="82"/>
+      <c r="D75" s="82"/>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="A74:D74"/>
+    <mergeCell ref="A75:D75"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A67:D67"/>
+    <mergeCell ref="A68:D68"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="A70:D70"/>
+    <mergeCell ref="A71:D71"/>
+    <mergeCell ref="A72:D72"/>
     <mergeCell ref="A44:C44"/>
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="A32:C32"/>
@@ -12670,18 +21031,6 @@
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A73:D73"/>
-    <mergeCell ref="A74:D74"/>
-    <mergeCell ref="A75:D75"/>
-    <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A66:D66"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A67:D67"/>
-    <mergeCell ref="A68:D68"/>
-    <mergeCell ref="A69:D69"/>
-    <mergeCell ref="A70:D70"/>
-    <mergeCell ref="A71:D71"/>
-    <mergeCell ref="A72:D72"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -12696,6 +21045,7 @@
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/project_2/project2_project status(C2).xlsx
+++ b/project_2/project2_project status(C2).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pyostry\workspace\aiffel\ai-data-bootcamp\Project_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89366B0A-A88C-4A5D-A6D5-0A004925A47D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73B092C9-D3AA-46D0-9E4E-1088294C75E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" firstSheet="3" activeTab="5" xr2:uid="{5FF54064-7DDC-427B-93D7-EF78D75E5195}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" firstSheet="3" activeTab="6" xr2:uid="{5FF54064-7DDC-427B-93D7-EF78D75E5195}"/>
   </bookViews>
   <sheets>
     <sheet name="제작 가이드라인" sheetId="12" r:id="rId1"/>
@@ -7563,7 +7563,7 @@
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>회귀분석 </a:t>
+            <a:t>로지스틱 회귀 </a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1">
@@ -7887,7 +7887,7 @@
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>회귀분석</a:t>
+            <a:t>로지스틱 회귀</a:t>
           </a:r>
         </a:p>
       </dgm:t>
@@ -8097,7 +8097,7 @@
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>회귀분석</a:t>
+            <a:t>로지스틱 회귀</a:t>
           </a:r>
         </a:p>
       </dgm:t>
@@ -8437,7 +8437,7 @@
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>회귀분석</a:t>
+            <a:t>로지스틱 회귀</a:t>
           </a:r>
         </a:p>
       </dgm:t>
@@ -16341,7 +16341,7 @@
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>회귀분석 </a:t>
+            <a:t>로지스틱 회귀 </a:t>
           </a:r>
           <a:r>
             <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1" kern="1200">
@@ -19866,7 +19866,7 @@
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>회귀분석</a:t>
+            <a:t>로지스틱 회귀</a:t>
           </a:r>
         </a:p>
       </dsp:txBody>
@@ -20371,7 +20371,7 @@
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>회귀분석</a:t>
+            <a:t>로지스틱 회귀</a:t>
           </a:r>
         </a:p>
       </dsp:txBody>
@@ -21270,7 +21270,7 @@
                 <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
             </a:rPr>
-            <a:t>회귀분석</a:t>
+            <a:t>로지스틱 회귀</a:t>
           </a:r>
         </a:p>
       </dsp:txBody>

--- a/project_2/project2_project status(C2).xlsx
+++ b/project_2/project2_project status(C2).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pyostry\workspace\aiffel\ai-data-bootcamp\Project_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73B092C9-D3AA-46D0-9E4E-1088294C75E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62380946-703F-4E0E-969D-FED57C873462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" firstSheet="3" activeTab="6" xr2:uid="{5FF54064-7DDC-427B-93D7-EF78D75E5195}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" firstSheet="2" activeTab="6" xr2:uid="{5FF54064-7DDC-427B-93D7-EF78D75E5195}"/>
   </bookViews>
   <sheets>
     <sheet name="제작 가이드라인" sheetId="12" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="372">
   <si>
     <t>reward</t>
   </si>
@@ -1515,6 +1515,156 @@
   </si>
   <si>
     <t>고령층의 offer 수신율 저하</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>검증 방법</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가설</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>통계 가설 검증 전 논의된 사항</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>No</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2,175명 나이 118, 성별, 소득수준 Null로 포함되어 분석 시 제외</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>212명 성별 O로 입력되어 성별 관련 분석 시 제외
+단, 나이, 소득수준의 경우 데이터 입력되어 관련 분석에는 포함.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>검증불가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>변수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reward, difficulty</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로지스틱 회귀 + A/B 테스트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Offer 별 단위 비교</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상관 분석 / 로지스틱 회귀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>상관분석</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로지스틱 회귀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>카이제곱 검정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>prior_offer_count
+viewed
+viewed_before_completed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>portfolio: offer_type
+viewed_before_completed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>difficulty
+viewed_before_completed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>income, difficulty
+viewed_before_completed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>income, reward
+viewed_before_completed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>channel_combination, has_mobile, has_social, viewed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>age, channel_combination, viewed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gender, offer_type
+viewed_before_completed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>viewed_before_completed: 수신 이후 유효기간 내 완료 여부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>viewed: 발송 후 유효기간 내 수신 여부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>has_mobile: Offer 채널에 mobile이 포함됐는지</t>
+  </si>
+  <si>
+    <t>has_social: Offer 채널에 social이 포함됐는지</t>
+  </si>
+  <si>
+    <t>channel_combination: Offer에 포함된 채널 조합</t>
+  </si>
+  <si>
+    <t>prior_transaction_count: Offer 수신 이전 결제 횟수</t>
+  </si>
+  <si>
+    <t>prior_spend: Offer 수신 이전 결제금액</t>
+  </si>
+  <si>
+    <t>prior_offer_count: 해당 수신 전까지 고객이 받은 Offer 수</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>duration
+event(offer received, offer viewed), time</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>channels
+event(offer received, offer viewed)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>집단별 완료율 비교 및 카이제곱 검정
+상호작용을 포함한 로지스틱 회귀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>value 'offer id' -&gt; 'offer_id'로 변경하여 진행</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2019,7 +2169,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="86">
+  <cellXfs count="97">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2277,6 +2427,39 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -27207,29 +27390,29 @@
         <v>193</v>
       </c>
     </row>
-    <row r="87" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A87" s="20" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="88" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A88" s="20" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="89" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A89" s="20" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="90" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="91" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="91" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A91" s="22" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="92" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="93" spans="1:1" ht="26" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="93" spans="1:1" ht="26" collapsed="1" x14ac:dyDescent="0.45">
       <c r="A93" s="21" t="s">
         <v>121</v>
       </c>
@@ -28604,83 +28787,301 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A96403AB-5292-4AE8-910D-5C858934A272}">
-  <dimension ref="A1:A14"/>
+  <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="47.08203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.08203125" style="20" customWidth="1"/>
+    <col min="2" max="2" width="54.33203125" customWidth="1"/>
+    <col min="3" max="3" width="32.1640625" customWidth="1"/>
+    <col min="4" max="4" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A1" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A1" s="92" t="s">
+        <v>338</v>
+      </c>
+      <c r="B1" s="93"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A2" s="89" t="s">
+        <v>339</v>
+      </c>
+      <c r="B2" s="38" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="34" x14ac:dyDescent="0.45">
+      <c r="A3" s="90">
+        <v>1</v>
+      </c>
+      <c r="B3" s="94" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A4" s="91">
+        <v>2</v>
+      </c>
+      <c r="B4" s="87" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5" s="91">
+        <v>3</v>
+      </c>
+      <c r="B5" s="87" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A7" s="89" t="s">
+        <v>339</v>
+      </c>
+      <c r="B7" s="88" t="s">
+        <v>337</v>
+      </c>
+      <c r="C7" s="88" t="s">
+        <v>336</v>
+      </c>
+      <c r="D7" s="88" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A8" s="91">
+        <v>1</v>
+      </c>
+      <c r="B8" s="86" t="s">
         <v>322</v>
       </c>
+      <c r="C8" s="87" t="s">
+        <v>343</v>
+      </c>
+      <c r="D8" s="87"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A9" s="91">
+        <v>2</v>
+      </c>
+      <c r="B9" s="87" t="s">
         <v>323</v>
       </c>
+      <c r="C9" s="87" t="s">
+        <v>346</v>
+      </c>
+      <c r="D9" s="87" t="s">
+        <v>345</v>
+      </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A10" s="91">
+        <v>3</v>
+      </c>
+      <c r="B10" s="86" t="s">
         <v>324</v>
       </c>
+      <c r="C10" s="87" t="s">
+        <v>343</v>
+      </c>
+      <c r="D10" s="87"/>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
+    <row r="11" spans="1:4" ht="34" x14ac:dyDescent="0.45">
+      <c r="A11" s="91">
+        <v>4</v>
+      </c>
+      <c r="B11" s="87" t="s">
         <v>325</v>
       </c>
+      <c r="C11" s="87" t="s">
+        <v>347</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>369</v>
+      </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
+    <row r="12" spans="1:4" ht="34" x14ac:dyDescent="0.45">
+      <c r="A12" s="91">
+        <v>5</v>
+      </c>
+      <c r="B12" s="87" t="s">
         <v>326</v>
       </c>
+      <c r="C12" s="87" t="s">
+        <v>348</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>368</v>
+      </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
+    <row r="13" spans="1:4" ht="51" x14ac:dyDescent="0.45">
+      <c r="A13" s="91">
+        <v>6</v>
+      </c>
+      <c r="B13" s="87" t="s">
         <v>327</v>
       </c>
+      <c r="C13" s="87" t="s">
+        <v>349</v>
+      </c>
+      <c r="D13" s="94" t="s">
+        <v>352</v>
+      </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A14" s="91">
+        <v>7</v>
+      </c>
+      <c r="B14" s="86" t="s">
         <v>328</v>
       </c>
+      <c r="C14" s="87" t="s">
+        <v>343</v>
+      </c>
+      <c r="D14" s="87"/>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
+    <row r="15" spans="1:4" ht="34" x14ac:dyDescent="0.45">
+      <c r="A15" s="91">
+        <v>8</v>
+      </c>
+      <c r="B15" s="87" t="s">
         <v>329</v>
       </c>
+      <c r="C15" s="87" t="s">
+        <v>350</v>
+      </c>
+      <c r="D15" s="94" t="s">
+        <v>353</v>
+      </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
+    <row r="16" spans="1:4" ht="34" x14ac:dyDescent="0.45">
+      <c r="A16" s="91">
+        <v>9</v>
+      </c>
+      <c r="B16" s="87" t="s">
         <v>330</v>
       </c>
+      <c r="C16" s="87" t="s">
+        <v>350</v>
+      </c>
+      <c r="D16" s="94" t="s">
+        <v>354</v>
+      </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
+    <row r="17" spans="1:4" ht="34" x14ac:dyDescent="0.45">
+      <c r="A17" s="91">
+        <v>10</v>
+      </c>
+      <c r="B17" s="87" t="s">
         <v>331</v>
       </c>
+      <c r="C17" s="87" t="s">
+        <v>350</v>
+      </c>
+      <c r="D17" s="94" t="s">
+        <v>355</v>
+      </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
+    <row r="18" spans="1:4" ht="68" x14ac:dyDescent="0.45">
+      <c r="A18" s="91">
+        <v>11</v>
+      </c>
+      <c r="B18" s="87" t="s">
         <v>332</v>
       </c>
+      <c r="C18" s="18" t="s">
+        <v>370</v>
+      </c>
+      <c r="D18" s="94" t="s">
+        <v>356</v>
+      </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A19" s="91">
+        <v>12</v>
+      </c>
+      <c r="B19" s="87" t="s">
         <v>333</v>
       </c>
+      <c r="C19" s="87" t="s">
+        <v>351</v>
+      </c>
+      <c r="D19" s="87" t="s">
+        <v>357</v>
+      </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A20" s="91">
+        <v>13</v>
+      </c>
+      <c r="B20" s="87" t="s">
         <v>335</v>
       </c>
+      <c r="C20" s="87" t="s">
+        <v>349</v>
+      </c>
+      <c r="D20" s="87" t="s">
+        <v>358</v>
+      </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
+    <row r="21" spans="1:4" ht="34" x14ac:dyDescent="0.45">
+      <c r="A21" s="91">
+        <v>14</v>
+      </c>
+      <c r="B21" s="87" t="s">
         <v>334</v>
+      </c>
+      <c r="C21" s="87" t="s">
+        <v>351</v>
+      </c>
+      <c r="D21" s="94" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B22" s="95" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B23" s="96" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B24" s="96" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B25" s="96" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B26" s="96" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B27" s="96" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B28" s="96" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="B29" s="96" t="s">
+        <v>367</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/project_2/project2_project status(C2).xlsx
+++ b/project_2/project2_project status(C2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pyostry\workspace\aiffel\ai-data-bootcamp\Project_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62380946-703F-4E0E-969D-FED57C873462}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E05686-FAA0-4452-82CD-EF84EEAC344A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" firstSheet="2" activeTab="6" xr2:uid="{5FF54064-7DDC-427B-93D7-EF78D75E5195}"/>
   </bookViews>
@@ -1555,10 +1555,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>reward, difficulty</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>로지스틱 회귀 + A/B 테스트</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1649,22 +1645,26 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>duration
-event(offer received, offer viewed), time</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>channels
-event(offer received, offer viewed)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>집단별 완료율 비교 및 카이제곱 검정
 상호작용을 포함한 로지스틱 회귀</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>value 'offer id' -&gt; 'offer_id'로 변경하여 진행</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>reward, difficulty
+viewed_before_completed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>channels, has_mobile, has_social, viewed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>duration
+viewed_time, received_time, viewed</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2169,7 +2169,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2344,6 +2344,24 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2371,21 +2389,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2405,6 +2408,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2428,22 +2434,16 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2451,15 +2451,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -11236,8 +11227,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="220981" y="1805623"/>
-          <a:ext cx="2100172" cy="447540"/>
+          <a:off x="173001" y="1826087"/>
+          <a:ext cx="2123975" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -11336,8 +11327,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="234089" y="1818731"/>
-        <a:ext cx="2073956" cy="421324"/>
+        <a:off x="186258" y="1839344"/>
+        <a:ext cx="2097461" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{ED5992BD-91A0-44DC-B026-C230E027754F}">
@@ -11347,8 +11338,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="16874489">
-          <a:off x="1581876" y="1121529"/>
-          <a:ext cx="1836586" cy="14378"/>
+          <a:off x="1549321" y="1134321"/>
+          <a:ext cx="1857401" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -11362,7 +11353,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1836586" y="7189"/>
+                <a:pt x="1857401" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -11421,8 +11412,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2454255" y="1082803"/>
-        <a:ext cx="91829" cy="91829"/>
+        <a:off x="2431586" y="1095075"/>
+        <a:ext cx="92870" cy="92870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{EB7188F2-1357-4748-A44C-AB5D4A48F40F}">
@@ -11432,8 +11423,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2679186" y="4273"/>
-          <a:ext cx="1080487" cy="447540"/>
+          <a:off x="2659066" y="4321"/>
+          <a:ext cx="1092733" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -11508,8 +11499,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2692294" y="17381"/>
-        <a:ext cx="1054271" cy="421324"/>
+        <a:off x="2672323" y="17578"/>
+        <a:ext cx="1066219" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7531319A-E0E5-4CB4-9F35-33254694A0D7}">
@@ -11519,8 +11510,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3759673" y="220854"/>
-          <a:ext cx="352482" cy="14378"/>
+          <a:off x="3751800" y="223438"/>
+          <a:ext cx="356477" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -11534,7 +11525,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="352482" y="7189"/>
+                <a:pt x="356477" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -11593,8 +11584,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3927103" y="219231"/>
-        <a:ext cx="17624" cy="17624"/>
+        <a:off x="3921127" y="221715"/>
+        <a:ext cx="17823" cy="17823"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{8F385C2E-83EB-470A-8A65-12C51C60EB27}">
@@ -11604,8 +11595,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4112156" y="4273"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="4108278" y="4321"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -11704,8 +11695,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4125264" y="17381"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="4121535" y="17578"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{71327523-F24D-4A9E-8CA7-7C0E6A96618A}">
@@ -11715,8 +11706,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17132988">
-          <a:off x="1832388" y="1378865"/>
-          <a:ext cx="1335563" cy="14378"/>
+          <a:off x="1802671" y="1394574"/>
+          <a:ext cx="1350699" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -11730,7 +11721,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1335563" y="7189"/>
+                <a:pt x="1350699" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -11789,8 +11780,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2466780" y="1352664"/>
-        <a:ext cx="66778" cy="66778"/>
+        <a:off x="2444254" y="1367995"/>
+        <a:ext cx="67534" cy="67534"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{08B2E005-DF35-41E7-A396-CA02C3B8D0A4}">
@@ -11800,8 +11791,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2679186" y="518944"/>
-          <a:ext cx="1080487" cy="447540"/>
+          <a:off x="2659066" y="524826"/>
+          <a:ext cx="1092733" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -11876,8 +11867,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2692294" y="532052"/>
-        <a:ext cx="1054271" cy="421324"/>
+        <a:off x="2672323" y="538083"/>
+        <a:ext cx="1066219" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E113C6B3-F5C2-41D9-9727-BB430EAD3818}">
@@ -11887,8 +11878,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3759673" y="735525"/>
-          <a:ext cx="358032" cy="14378"/>
+          <a:off x="3751800" y="743943"/>
+          <a:ext cx="362090" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -11902,7 +11893,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="358032" y="7189"/>
+                <a:pt x="362090" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -11961,8 +11952,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3929739" y="733763"/>
-        <a:ext cx="17901" cy="17901"/>
+        <a:off x="3923793" y="742080"/>
+        <a:ext cx="18104" cy="18104"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{53F03F28-ED40-4762-8125-AFFEEA792A72}">
@@ -11972,8 +11963,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4117706" y="518944"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="4113890" y="524826"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -12096,8 +12087,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4130814" y="532052"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="4127147" y="538083"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{806C8330-1E37-41AD-AEEE-3552A4162510}">
@@ -12107,8 +12098,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17692822">
-          <a:off x="2074675" y="1636200"/>
-          <a:ext cx="850988" cy="14378"/>
+          <a:off x="2047704" y="1654826"/>
+          <a:ext cx="860633" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -12122,7 +12113,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="850988" y="7189"/>
+                <a:pt x="860633" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -12181,8 +12172,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2478895" y="1622115"/>
-        <a:ext cx="42549" cy="42549"/>
+        <a:off x="2456505" y="1640499"/>
+        <a:ext cx="43031" cy="43031"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{3BC1DAB2-4FEF-42C9-A10F-0690E2903498}">
@@ -12192,8 +12183,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2679186" y="1033615"/>
-          <a:ext cx="1080487" cy="447540"/>
+          <a:off x="2659066" y="1045330"/>
+          <a:ext cx="1092733" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -12284,8 +12275,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2692294" y="1046723"/>
-        <a:ext cx="1054271" cy="421324"/>
+        <a:off x="2672323" y="1058587"/>
+        <a:ext cx="1066219" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6BFD1C16-8154-4C15-AF72-E53B38C4A146}">
@@ -12295,8 +12286,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3759673" y="1250197"/>
-          <a:ext cx="358032" cy="14378"/>
+          <a:off x="3751800" y="1264447"/>
+          <a:ext cx="362090" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -12310,7 +12301,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="358032" y="7189"/>
+                <a:pt x="362090" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -12369,8 +12360,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3929739" y="1248435"/>
-        <a:ext cx="17901" cy="17901"/>
+        <a:off x="3923793" y="1262584"/>
+        <a:ext cx="18104" cy="18104"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1A251137-9CB6-43D7-B47D-0D220C30894C}">
@@ -12380,8 +12371,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4117706" y="1033615"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="4113890" y="1045330"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -12504,8 +12495,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4130814" y="1046723"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="4127147" y="1058587"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{227E0FEF-1368-4562-AD55-940C6A450E91}">
@@ -12515,8 +12506,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="3310531">
-          <a:off x="2186691" y="2279540"/>
-          <a:ext cx="626956" cy="14378"/>
+          <a:off x="2160990" y="2305456"/>
+          <a:ext cx="634061" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -12530,7 +12521,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="626956" y="7189"/>
+                <a:pt x="634061" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -12589,8 +12580,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2484496" y="2271055"/>
-        <a:ext cx="31347" cy="31347"/>
+        <a:off x="2462170" y="2296794"/>
+        <a:ext cx="31703" cy="31703"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{146FB508-948A-484E-B54F-2A63CE5492FA}">
@@ -12600,8 +12591,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2679186" y="2320294"/>
-          <a:ext cx="1080487" cy="447540"/>
+          <a:off x="2659066" y="2346591"/>
+          <a:ext cx="1092733" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -12676,8 +12667,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2692294" y="2333402"/>
-        <a:ext cx="1054271" cy="421324"/>
+        <a:off x="2672323" y="2359848"/>
+        <a:ext cx="1066219" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1583A4D8-C48C-400A-B5A1-D8E8188A1E57}">
@@ -12687,8 +12678,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17692822">
-          <a:off x="3513195" y="2150872"/>
-          <a:ext cx="850988" cy="14378"/>
+          <a:off x="3502528" y="2175330"/>
+          <a:ext cx="860633" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -12702,7 +12693,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="850988" y="7189"/>
+                <a:pt x="860633" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -12761,8 +12752,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3917415" y="2136786"/>
-        <a:ext cx="42549" cy="42549"/>
+        <a:off x="3911329" y="2161003"/>
+        <a:ext cx="43031" cy="43031"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{985FE1E2-4CA8-4AC7-A474-DEECC9A2BB80}">
@@ -12772,8 +12763,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4117706" y="1548287"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="4113890" y="1565835"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -12864,8 +12855,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4130814" y="1561395"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="4127147" y="1579092"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{16F44D37-2601-482A-9095-0B3E8E10E520}">
@@ -12875,8 +12866,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19457599">
-          <a:off x="3718230" y="2408207"/>
-          <a:ext cx="440918" cy="14378"/>
+          <a:off x="3709887" y="2435583"/>
+          <a:ext cx="445915" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -12890,7 +12881,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="440918" y="7189"/>
+                <a:pt x="445915" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -12949,8 +12940,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3927667" y="2404373"/>
-        <a:ext cx="22045" cy="22045"/>
+        <a:off x="3921697" y="2431624"/>
+        <a:ext cx="22295" cy="22295"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{2D542640-C237-42B5-8470-73084719F8F3}">
@@ -12960,8 +12951,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4117706" y="2062958"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="4113890" y="2086339"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -13052,8 +13043,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4130814" y="2076066"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="4127147" y="2099596"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9A75AB13-86A0-459A-8B2B-E8037D74B447}">
@@ -13063,8 +13054,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2142401">
-          <a:off x="3718230" y="2665543"/>
-          <a:ext cx="440918" cy="14378"/>
+          <a:off x="3709887" y="2695835"/>
+          <a:ext cx="445915" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -13078,7 +13069,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="440918" y="7189"/>
+                <a:pt x="445915" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -13137,8 +13128,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3927667" y="2661709"/>
-        <a:ext cx="22045" cy="22045"/>
+        <a:off x="3921697" y="2691876"/>
+        <a:ext cx="22295" cy="22295"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{106C3051-36E0-4DB2-B006-BD51244834C6}">
@@ -13148,8 +13139,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4117706" y="2577630"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="4113890" y="2606844"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -13240,8 +13231,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4130814" y="2590738"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="4127147" y="2620101"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6562E267-52DD-4DC6-81E6-A0E9307367D6}">
@@ -13251,8 +13242,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="3907178">
-          <a:off x="3513195" y="2922879"/>
-          <a:ext cx="850988" cy="14378"/>
+          <a:off x="3502528" y="2956087"/>
+          <a:ext cx="860633" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -13266,7 +13257,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="850988" y="7189"/>
+                <a:pt x="860633" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -13325,8 +13316,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3917415" y="2908793"/>
-        <a:ext cx="42549" cy="42549"/>
+        <a:off x="3911329" y="2941760"/>
+        <a:ext cx="43031" cy="43031"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{220D319D-36C0-42A0-A946-F197C4269C14}">
@@ -13336,8 +13327,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4117706" y="3092301"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="4113890" y="3127348"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -13428,8 +13419,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4130814" y="3105409"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="4127147" y="3140605"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4332858F-88A7-466E-8722-8833A7B96598}">
@@ -13439,8 +13430,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="4725511">
-          <a:off x="1581876" y="2922879"/>
-          <a:ext cx="1836586" cy="14378"/>
+          <a:off x="1549321" y="2956087"/>
+          <a:ext cx="1857401" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -13454,7 +13445,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1836586" y="7189"/>
+                <a:pt x="1857401" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -13509,8 +13500,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2454255" y="2884153"/>
-        <a:ext cx="91829" cy="91829"/>
+        <a:off x="2431586" y="2916841"/>
+        <a:ext cx="92870" cy="92870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1479FCFA-85A4-438D-B5D0-346DFAD5924D}">
@@ -13520,8 +13511,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2679186" y="3606973"/>
-          <a:ext cx="1080487" cy="447540"/>
+          <a:off x="2659066" y="3647853"/>
+          <a:ext cx="1092733" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -13596,8 +13587,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2692294" y="3620081"/>
-        <a:ext cx="1054271" cy="421324"/>
+        <a:off x="2672323" y="3661110"/>
+        <a:ext cx="1066219" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E6D0412B-4D85-432B-BE35-F277BFD00B03}">
@@ -13607,8 +13598,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3759673" y="3823554"/>
-          <a:ext cx="358032" cy="14378"/>
+          <a:off x="3751800" y="3866970"/>
+          <a:ext cx="362090" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -13622,7 +13613,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="358032" y="7189"/>
+                <a:pt x="362090" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -13677,8 +13668,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3929739" y="3821792"/>
-        <a:ext cx="17901" cy="17901"/>
+        <a:off x="3923793" y="3865107"/>
+        <a:ext cx="18104" cy="18104"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{CE9AFD94-4037-4F8B-B49B-020818B5CBB5}">
@@ -13688,8 +13679,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4117706" y="3606973"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="4113890" y="3647853"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -13796,8 +13787,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4130814" y="3620081"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="4127147" y="3661110"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B460AB31-448C-42B6-9C6B-D3CF5013B4F6}">
@@ -13807,8 +13798,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="88714" y="4636316"/>
-          <a:ext cx="1800813" cy="447540"/>
+          <a:off x="39236" y="4688862"/>
+          <a:ext cx="1821222" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -13933,8 +13924,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="101822" y="4649424"/>
-        <a:ext cx="1774597" cy="421324"/>
+        <a:off x="52493" y="4702119"/>
+        <a:ext cx="1794708" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{C120D3E5-D1A3-4DC1-848B-C37D9DDE2012}">
@@ -13944,8 +13935,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="18752467">
-          <a:off x="1776407" y="4595561"/>
-          <a:ext cx="698529" cy="14378"/>
+          <a:off x="1746056" y="4647727"/>
+          <a:ext cx="706446" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -13959,7 +13950,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="698529" y="7189"/>
+                <a:pt x="706446" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -14014,8 +14005,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2108209" y="4585287"/>
-        <a:ext cx="34926" cy="34926"/>
+        <a:off x="2081618" y="4637255"/>
+        <a:ext cx="35322" cy="35322"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6F01F0AA-74B9-49DB-A456-B8979039EB51}">
@@ -14025,8 +14016,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2361817" y="4121644"/>
-          <a:ext cx="1080487" cy="447540"/>
+          <a:off x="2338101" y="4168357"/>
+          <a:ext cx="1092733" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -14099,8 +14090,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2374925" y="4134752"/>
-        <a:ext cx="1054271" cy="421324"/>
+        <a:off x="2351358" y="4181614"/>
+        <a:ext cx="1066219" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{F5E69F9A-2631-4A2D-BC76-B4BD9B08D019}">
@@ -14110,8 +14101,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3442305" y="4338225"/>
-          <a:ext cx="364020" cy="14378"/>
+          <a:off x="3430834" y="4387475"/>
+          <a:ext cx="368146" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -14125,7 +14116,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="364020" y="7189"/>
+                <a:pt x="368146" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -14180,8 +14171,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3615214" y="4336314"/>
-        <a:ext cx="18201" cy="18201"/>
+        <a:off x="3605704" y="4385460"/>
+        <a:ext cx="18407" cy="18407"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{69EDA0B0-D39D-4C93-8B8D-10889C581D9E}">
@@ -14191,8 +14182,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3806325" y="4121644"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="3798980" y="4168357"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -14265,8 +14256,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3819433" y="4134752"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="3812237" y="4181614"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{AC23C890-5E27-4DC3-9BF7-2C50218200D9}">
@@ -14276,8 +14267,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="1889527" y="4852897"/>
-          <a:ext cx="472289" cy="14378"/>
+          <a:off x="1860458" y="4907979"/>
+          <a:ext cx="477642" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -14291,7 +14282,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="472289" y="7189"/>
+                <a:pt x="477642" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -14346,8 +14337,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2113865" y="4848279"/>
-        <a:ext cx="23614" cy="23614"/>
+        <a:off x="2087338" y="4903227"/>
+        <a:ext cx="23882" cy="23882"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B4CF3050-E538-4710-99C5-FB5B2F28D116}">
@@ -14357,8 +14348,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2361817" y="4636316"/>
-          <a:ext cx="1080487" cy="447540"/>
+          <a:off x="2338101" y="4688862"/>
+          <a:ext cx="1092733" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -14431,8 +14422,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2374925" y="4649424"/>
-        <a:ext cx="1054271" cy="421324"/>
+        <a:off x="2351358" y="4702119"/>
+        <a:ext cx="1066219" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{55492AE0-989E-4368-96E6-8609B6786079}">
@@ -14442,8 +14433,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3442305" y="4852897"/>
-          <a:ext cx="364020" cy="14378"/>
+          <a:off x="3430834" y="4907979"/>
+          <a:ext cx="368146" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -14457,7 +14448,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="364020" y="7189"/>
+                <a:pt x="368146" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -14512,8 +14503,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3615214" y="4850985"/>
-        <a:ext cx="18201" cy="18201"/>
+        <a:off x="3605704" y="4905964"/>
+        <a:ext cx="18407" cy="18407"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{99BD4B49-7654-4BFC-93A2-73715A94DAC0}">
@@ -14523,8 +14514,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3806325" y="4636316"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="3798980" y="4688862"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -14641,8 +14632,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3819433" y="4649424"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="3812237" y="4702119"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{48D36C81-0EEF-4879-868D-73109D1A61EF}">
@@ -14652,8 +14643,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2847533">
-          <a:off x="1776407" y="5110232"/>
-          <a:ext cx="698529" cy="14378"/>
+          <a:off x="1746056" y="5168231"/>
+          <a:ext cx="706446" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -14667,7 +14658,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="698529" y="7189"/>
+                <a:pt x="706446" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -14722,8 +14713,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2108209" y="5099958"/>
-        <a:ext cx="34926" cy="34926"/>
+        <a:off x="2081618" y="5157759"/>
+        <a:ext cx="35322" cy="35322"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E0C7A212-1F93-473A-8909-15A6780CBC2F}">
@@ -14733,8 +14724,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2361817" y="5150987"/>
-          <a:ext cx="1080487" cy="447540"/>
+          <a:off x="2338101" y="5209366"/>
+          <a:ext cx="1092733" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -14807,8 +14798,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2374925" y="5164095"/>
-        <a:ext cx="1054271" cy="421324"/>
+        <a:off x="2351358" y="5222623"/>
+        <a:ext cx="1066219" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4D54B04B-F98B-4577-8925-91ECEF877996}">
@@ -14818,8 +14809,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3442305" y="5367568"/>
-          <a:ext cx="376041" cy="14378"/>
+          <a:off x="3430834" y="5428484"/>
+          <a:ext cx="380303" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -14833,7 +14824,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="376041" y="7189"/>
+                <a:pt x="380303" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -14888,8 +14879,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3620924" y="5365356"/>
-        <a:ext cx="18802" cy="18802"/>
+        <a:off x="3611478" y="5426165"/>
+        <a:ext cx="19015" cy="19015"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{540CB623-D523-4AD6-BF5D-A946D7B052E6}">
@@ -14899,8 +14890,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3818346" y="5150987"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="3811137" y="5209366"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -15018,8 +15009,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3831454" y="5164095"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="3824394" y="5222623"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
   </dsp:spTree>
@@ -15041,8 +15032,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="11645" y="3341824"/>
-          <a:ext cx="1172663" cy="360001"/>
+          <a:off x="10440" y="3343938"/>
+          <a:ext cx="1173405" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -15120,8 +15111,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="22189" y="3352368"/>
-        <a:ext cx="1151575" cy="338913"/>
+        <a:off x="20991" y="3354489"/>
+        <a:ext cx="1152303" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7667B88B-738E-4E27-80A6-15B1E3AED5F8}">
@@ -15131,8 +15122,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="16719080">
-          <a:off x="572973" y="2806392"/>
-          <a:ext cx="1439150" cy="8089"/>
+          <a:off x="572123" y="2808170"/>
+          <a:ext cx="1440061" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -15146,7 +15137,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1439150" y="4044"/>
+                <a:pt x="1440061" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -15205,8 +15196,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1256569" y="2774458"/>
-        <a:ext cx="71957" cy="71957"/>
+        <a:off x="1256152" y="2776213"/>
+        <a:ext cx="72003" cy="72003"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D9E30B0F-B6EE-4B8A-B3A5-5AD7E4CFBC12}">
@@ -15216,8 +15207,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="1400787" y="1919048"/>
-          <a:ext cx="1438483" cy="360001"/>
+          <a:off x="1400462" y="1920262"/>
+          <a:ext cx="1439393" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -15308,8 +15299,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1411331" y="1929592"/>
-        <a:ext cx="1417395" cy="338913"/>
+        <a:off x="1411013" y="1930813"/>
+        <a:ext cx="1418291" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{ED5992BD-91A0-44DC-B026-C230E027754F}">
@@ -15319,8 +15310,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="16757427">
-          <a:off x="2277046" y="1433334"/>
-          <a:ext cx="1340928" cy="8089"/>
+          <a:off x="2277274" y="1434244"/>
+          <a:ext cx="1341777" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -15334,7 +15325,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1340928" y="4044"/>
+                <a:pt x="1341777" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -15393,8 +15384,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2913987" y="1403855"/>
-        <a:ext cx="67046" cy="67046"/>
+        <a:off x="2914618" y="1404744"/>
+        <a:ext cx="67088" cy="67088"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{EB7188F2-1357-4748-A44C-AB5D4A48F40F}">
@@ -15404,8 +15395,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3055749" y="595708"/>
-          <a:ext cx="1401335" cy="360001"/>
+          <a:off x="3056471" y="596085"/>
+          <a:ext cx="1402222" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -15475,8 +15466,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3066293" y="606252"/>
-        <a:ext cx="1380247" cy="338913"/>
+        <a:off x="3067022" y="606636"/>
+        <a:ext cx="1381120" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7531319A-E0E5-4CB4-9F35-33254694A0D7}">
@@ -15486,8 +15477,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17860289">
-          <a:off x="4334186" y="568449"/>
-          <a:ext cx="458919" cy="8089"/>
+          <a:off x="4335717" y="568811"/>
+          <a:ext cx="459210" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -15501,7 +15492,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="458919" y="4044"/>
+                <a:pt x="459210" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -15560,8 +15551,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4552173" y="561021"/>
-        <a:ext cx="22945" cy="22945"/>
+        <a:off x="4553842" y="561375"/>
+        <a:ext cx="22960" cy="22960"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{8F385C2E-83EB-470A-8A65-12C51C60EB27}">
@@ -15571,8 +15562,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4670208" y="187688"/>
-          <a:ext cx="1768607" cy="363180"/>
+          <a:off x="4671951" y="187807"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -15642,8 +15633,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4680845" y="198325"/>
-        <a:ext cx="1747333" cy="341906"/>
+        <a:off x="4682595" y="198451"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{8EC6EEF9-E6D8-4DE2-A6DD-BB50B40A5CF0}">
@@ -15653,8 +15644,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6438815" y="365234"/>
-          <a:ext cx="219833" cy="8089"/>
+          <a:off x="6441677" y="365467"/>
+          <a:ext cx="219972" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -15668,7 +15659,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="219833" y="4044"/>
+                <a:pt x="219972" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -15723,8 +15714,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6543236" y="363782"/>
-        <a:ext cx="10991" cy="10991"/>
+        <a:off x="6546165" y="364012"/>
+        <a:ext cx="10998" cy="10998"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{31CFEB2D-0887-4520-AF04-1E3C38912960}">
@@ -15734,8 +15725,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6658649" y="187688"/>
-          <a:ext cx="3154399" cy="363180"/>
+          <a:off x="6661650" y="187807"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -15821,8 +15812,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6669286" y="198325"/>
-        <a:ext cx="3133125" cy="341906"/>
+        <a:off x="6672294" y="198451"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{602438BB-CBF9-49AF-AB0A-D57EA2C10BE2}">
@@ -15832,8 +15823,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9813049" y="365234"/>
-          <a:ext cx="216478" cy="8089"/>
+          <a:off x="9818046" y="365467"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -15847,7 +15838,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216478" y="4044"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -15902,8 +15893,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9915876" y="363866"/>
-        <a:ext cx="10823" cy="10823"/>
+        <a:off x="9920939" y="364096"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{57D97F9E-094F-4C3F-82B2-5A689BC4D082}">
@@ -15913,8 +15904,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10029528" y="193802"/>
-          <a:ext cx="1800002" cy="350952"/>
+          <a:off x="10034662" y="193925"/>
+          <a:ext cx="1801141" cy="351174"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16011,8 +16002,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10039807" y="204081"/>
-        <a:ext cx="1779444" cy="330394"/>
+        <a:off x="10044948" y="204211"/>
+        <a:ext cx="1780569" cy="330602"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B3B4155B-F64B-452E-AEBC-36FE76B0BD69}">
@@ -16022,8 +16013,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="21585916">
-          <a:off x="4457084" y="771221"/>
-          <a:ext cx="216480" cy="8089"/>
+          <a:off x="4458692" y="771712"/>
+          <a:ext cx="216617" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16037,7 +16028,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216480" y="4044"/>
+                <a:pt x="216617" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16092,8 +16083,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4559912" y="769854"/>
-        <a:ext cx="10824" cy="10824"/>
+        <a:off x="4561585" y="770341"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D20B6C81-A2D9-4E8E-80C0-968EFF7F89E1}">
@@ -16103,8 +16094,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4673563" y="593232"/>
-          <a:ext cx="1768607" cy="363180"/>
+          <a:off x="4675308" y="593607"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16174,8 +16165,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4684200" y="603869"/>
-        <a:ext cx="1747333" cy="341906"/>
+        <a:off x="4685952" y="604251"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7FE58BCF-6B0D-48A2-8DDE-611A1D34A4D6}">
@@ -16185,8 +16176,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6442171" y="770778"/>
-          <a:ext cx="216478" cy="8089"/>
+          <a:off x="6445035" y="771268"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16200,7 +16191,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216478" y="4044"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16255,8 +16246,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6544998" y="769410"/>
-        <a:ext cx="10823" cy="10823"/>
+        <a:off x="6547927" y="769897"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{629314FA-FCA6-45B9-99A7-2C2196A96D5C}">
@@ -16266,8 +16257,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6658649" y="593232"/>
-          <a:ext cx="3154399" cy="363180"/>
+          <a:off x="6661650" y="593607"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16366,8 +16357,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6669286" y="603869"/>
-        <a:ext cx="3133125" cy="341906"/>
+        <a:off x="6672294" y="604251"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{CCF144EB-A097-46BE-8FF7-BE5C7A394E2A}">
@@ -16377,8 +16368,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9813049" y="770778"/>
-          <a:ext cx="216478" cy="8089"/>
+          <a:off x="9818046" y="771268"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16392,7 +16383,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216478" y="4044"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16447,8 +16438,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9915876" y="769410"/>
-        <a:ext cx="10823" cy="10823"/>
+        <a:off x="9920939" y="769897"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9EE0F2D9-F39B-4921-9EAC-DBA04DC260DD}">
@@ -16458,8 +16449,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10029528" y="591458"/>
-          <a:ext cx="1800002" cy="366728"/>
+          <a:off x="10034662" y="591832"/>
+          <a:ext cx="1801141" cy="366960"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16542,8 +16533,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10040269" y="602199"/>
-        <a:ext cx="1778520" cy="345246"/>
+        <a:off x="10045410" y="602580"/>
+        <a:ext cx="1779645" cy="345464"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6169CD61-5E3A-4096-AA5A-91A22C397918}">
@@ -16553,8 +16544,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="3717526">
-          <a:off x="4335080" y="974880"/>
-          <a:ext cx="460487" cy="8089"/>
+          <a:off x="4336611" y="975499"/>
+          <a:ext cx="460779" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16568,7 +16559,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="460487" y="4044"/>
+                <a:pt x="460779" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16623,8 +16614,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4553812" y="967412"/>
-        <a:ext cx="23024" cy="23024"/>
+        <a:off x="4555481" y="968024"/>
+        <a:ext cx="23038" cy="23038"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D5FDB947-B70B-4493-B9F9-83A45503DA23}">
@@ -16634,8 +16625,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4673563" y="1000550"/>
-          <a:ext cx="1768607" cy="363180"/>
+          <a:off x="4675308" y="1001183"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16705,8 +16696,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4684200" y="1011187"/>
-        <a:ext cx="1747333" cy="341906"/>
+        <a:off x="4685952" y="1011827"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9EDF68AF-E14B-40BF-AB6D-4B01635D735A}">
@@ -16716,8 +16707,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6442171" y="1178095"/>
-          <a:ext cx="216478" cy="8089"/>
+          <a:off x="6445035" y="1178843"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16731,7 +16722,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216478" y="4044"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16786,8 +16777,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6544998" y="1176728"/>
-        <a:ext cx="10823" cy="10823"/>
+        <a:off x="6547927" y="1177472"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{5A5C0991-25ED-4076-91F2-80A2EEFC811E}">
@@ -16797,8 +16788,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6658649" y="1000550"/>
-          <a:ext cx="3154399" cy="363180"/>
+          <a:off x="6661650" y="1001183"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16932,8 +16923,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6669286" y="1011187"/>
-        <a:ext cx="3133125" cy="341906"/>
+        <a:off x="6672294" y="1011827"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{723082D3-A8E2-4807-89B5-C74C600B949E}">
@@ -16943,8 +16934,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9813049" y="1178095"/>
-          <a:ext cx="216478" cy="8089"/>
+          <a:off x="9818046" y="1178843"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16958,7 +16949,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216478" y="4044"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17013,8 +17004,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9915876" y="1176728"/>
-        <a:ext cx="10823" cy="10823"/>
+        <a:off x="9920939" y="1177472"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{05E664DE-AAC0-4D52-9AA4-DE55CA572420}">
@@ -17024,8 +17015,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10029528" y="998776"/>
-          <a:ext cx="1800002" cy="366728"/>
+          <a:off x="10034662" y="999408"/>
+          <a:ext cx="1801141" cy="366960"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17095,8 +17086,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10040269" y="1009517"/>
-        <a:ext cx="1778520" cy="345246"/>
+        <a:off x="10045410" y="1010156"/>
+        <a:ext cx="1779645" cy="345464"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{16F44D37-2601-482A-9095-0B3E8E10E520}">
@@ -17106,8 +17097,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="1505741">
-          <a:off x="2827988" y="2145697"/>
-          <a:ext cx="239044" cy="8089"/>
+          <a:off x="2828565" y="2147057"/>
+          <a:ext cx="239195" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17121,7 +17112,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="239044" y="4044"/>
+                <a:pt x="239195" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17180,8 +17171,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2941534" y="2143765"/>
-        <a:ext cx="11952" cy="11952"/>
+        <a:off x="2942183" y="2145122"/>
+        <a:ext cx="11959" cy="11959"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{2D542640-C237-42B5-8470-73084719F8F3}">
@@ -17191,8 +17182,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3055749" y="2020434"/>
-          <a:ext cx="1401335" cy="360001"/>
+          <a:off x="3056471" y="2021712"/>
+          <a:ext cx="1402222" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17262,8 +17253,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3066293" y="2030978"/>
-        <a:ext cx="1380247" cy="338913"/>
+        <a:off x="3067022" y="2032263"/>
+        <a:ext cx="1381120" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{BFCFD3BD-878E-4ADC-81DA-3641DCD660A7}">
@@ -17273,8 +17264,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17370601">
-          <a:off x="4241227" y="1890901"/>
-          <a:ext cx="648193" cy="8089"/>
+          <a:off x="4242699" y="1892100"/>
+          <a:ext cx="648604" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17288,7 +17279,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="648193" y="4044"/>
+                <a:pt x="648604" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17343,8 +17334,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4549119" y="1878741"/>
-        <a:ext cx="32409" cy="32409"/>
+        <a:off x="4550785" y="1879930"/>
+        <a:ext cx="32430" cy="32430"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{911F1DD5-D3D2-4321-A1A5-7E2BAE25AAD5}">
@@ -17354,8 +17345,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4673563" y="1407867"/>
-          <a:ext cx="1768607" cy="363180"/>
+          <a:off x="4675308" y="1408758"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17425,8 +17416,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4684200" y="1418504"/>
-        <a:ext cx="1747333" cy="341906"/>
+        <a:off x="4685952" y="1419402"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{F4CAC384-240B-4811-A7FE-5EF39454FD0A}">
@@ -17436,8 +17427,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6442171" y="1585413"/>
-          <a:ext cx="216478" cy="8089"/>
+          <a:off x="6445035" y="1586419"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17451,7 +17442,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216478" y="4044"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17506,8 +17497,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6544998" y="1584046"/>
-        <a:ext cx="10823" cy="10823"/>
+        <a:off x="6547927" y="1585048"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{00847D60-C67D-487A-B918-B0C406DE6A20}">
@@ -17517,8 +17508,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6658649" y="1407867"/>
-          <a:ext cx="3154399" cy="363180"/>
+          <a:off x="6661650" y="1408758"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17628,8 +17619,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6669286" y="1418504"/>
-        <a:ext cx="3133125" cy="341906"/>
+        <a:off x="6672294" y="1419402"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7682FEBA-2A8A-4CEB-BAD3-CAC6D62452E9}">
@@ -17639,8 +17630,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9813049" y="1585413"/>
-          <a:ext cx="216478" cy="8089"/>
+          <a:off x="9818046" y="1586419"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17654,7 +17645,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216478" y="4044"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17709,8 +17700,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9915876" y="1584046"/>
-        <a:ext cx="10823" cy="10823"/>
+        <a:off x="9920939" y="1585048"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4C2C55F9-D12D-4BE1-85AD-8FAFF8B344C7}">
@@ -17720,8 +17711,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10029528" y="1406094"/>
-          <a:ext cx="1800002" cy="366728"/>
+          <a:off x="10034662" y="1406983"/>
+          <a:ext cx="1801141" cy="366960"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17839,8 +17830,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10040269" y="1416835"/>
-        <a:ext cx="1778520" cy="345246"/>
+        <a:off x="10045410" y="1417731"/>
+        <a:ext cx="1779645" cy="345464"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6A4076F7-5C10-4205-AF7B-34977DAE41B6}">
@@ -17850,8 +17841,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19004863">
-          <a:off x="4416714" y="2094560"/>
-          <a:ext cx="297220" cy="8089"/>
+          <a:off x="4418296" y="2095888"/>
+          <a:ext cx="297408" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17865,7 +17856,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="297220" y="4044"/>
+                <a:pt x="297408" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17920,8 +17911,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4557893" y="2091174"/>
-        <a:ext cx="14861" cy="14861"/>
+        <a:off x="4559565" y="2092498"/>
+        <a:ext cx="14870" cy="14870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D2D6EBAC-87C6-4589-B626-76CA00356F2A}">
@@ -17931,8 +17922,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4673563" y="1815185"/>
-          <a:ext cx="1768607" cy="363180"/>
+          <a:off x="4675308" y="1816334"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -18002,8 +17993,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4684200" y="1825822"/>
-        <a:ext cx="1747333" cy="341906"/>
+        <a:off x="4685952" y="1826978"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4CEC118E-B718-4A3D-A714-E879160F0F50}">
@@ -18013,8 +18004,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6442171" y="1992731"/>
-          <a:ext cx="216478" cy="8089"/>
+          <a:off x="6445035" y="1993994"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18028,7 +18019,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216478" y="4044"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18083,8 +18074,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6544998" y="1991363"/>
-        <a:ext cx="10823" cy="10823"/>
+        <a:off x="6547927" y="1992623"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{96C9B796-69AA-48A9-AB67-0FE5F7CEFC9D}">
@@ -18094,8 +18085,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6658649" y="1815185"/>
-          <a:ext cx="3154399" cy="363180"/>
+          <a:off x="6661650" y="1816334"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -18189,8 +18180,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6669286" y="1825822"/>
-        <a:ext cx="3133125" cy="341906"/>
+        <a:off x="6672294" y="1826978"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{0C4A9E51-DEA5-4AC0-B8EC-F712BFE3BA51}">
@@ -18200,8 +18191,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9813049" y="1992731"/>
-          <a:ext cx="216478" cy="8089"/>
+          <a:off x="9818046" y="1993994"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18215,7 +18206,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216478" y="4044"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18270,8 +18261,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9915876" y="1991363"/>
-        <a:ext cx="10823" cy="10823"/>
+        <a:off x="9920939" y="1992623"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{829A6295-4379-4C15-BF91-56D56B48CA13}">
@@ -18281,8 +18272,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10029528" y="1813411"/>
-          <a:ext cx="1800002" cy="366728"/>
+          <a:off x="10034662" y="1814559"/>
+          <a:ext cx="1801141" cy="366960"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -18368,8 +18359,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10040269" y="1824152"/>
-        <a:ext cx="1778520" cy="345246"/>
+        <a:off x="10045410" y="1825307"/>
+        <a:ext cx="1779645" cy="345464"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{15251D3B-5937-4D92-B910-59FBB0B78504}">
@@ -18379,8 +18370,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2595137">
-          <a:off x="4416714" y="2298219"/>
-          <a:ext cx="297220" cy="8089"/>
+          <a:off x="4418296" y="2299676"/>
+          <a:ext cx="297408" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18394,7 +18385,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="297220" y="4044"/>
+                <a:pt x="297408" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18449,8 +18440,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4557893" y="2294833"/>
-        <a:ext cx="14861" cy="14861"/>
+        <a:off x="4559565" y="2296285"/>
+        <a:ext cx="14870" cy="14870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{55C8ECFC-533A-4D04-B170-164B29EE9A7D}">
@@ -18460,8 +18451,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4673563" y="2222503"/>
-          <a:ext cx="1768607" cy="363180"/>
+          <a:off x="4675308" y="2223909"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -18531,8 +18522,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4684200" y="2233140"/>
-        <a:ext cx="1747333" cy="341906"/>
+        <a:off x="4685952" y="2234553"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A63458DA-4732-44A8-AAAD-101471030A2E}">
@@ -18542,8 +18533,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6442171" y="2400049"/>
-          <a:ext cx="216478" cy="8089"/>
+          <a:off x="6445035" y="2401570"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18557,7 +18548,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216478" y="4044"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18612,8 +18603,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6544998" y="2398681"/>
-        <a:ext cx="10823" cy="10823"/>
+        <a:off x="6547927" y="2400199"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{3CFC9EAC-3C3A-42EE-A809-37090C958CCC}">
@@ -18623,8 +18614,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6658649" y="2222503"/>
-          <a:ext cx="3154399" cy="363180"/>
+          <a:off x="6661650" y="2223909"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -18702,8 +18693,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6669286" y="2233140"/>
-        <a:ext cx="3133125" cy="341906"/>
+        <a:off x="6672294" y="2234553"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{2E1BE310-D0FB-4439-BC13-EF25298A0AC1}">
@@ -18713,8 +18704,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9813049" y="2400049"/>
-          <a:ext cx="216478" cy="8089"/>
+          <a:off x="9818046" y="2401570"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18728,7 +18719,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216478" y="4044"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18783,8 +18774,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9915876" y="2398681"/>
-        <a:ext cx="10823" cy="10823"/>
+        <a:off x="9920939" y="2400199"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{05029C16-99B1-4993-B5A7-DFCE2EC4AF2D}">
@@ -18794,8 +18785,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10029528" y="2220729"/>
-          <a:ext cx="1800002" cy="366728"/>
+          <a:off x="10034662" y="2222134"/>
+          <a:ext cx="1801141" cy="366960"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -18865,8 +18856,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10040269" y="2231470"/>
-        <a:ext cx="1778520" cy="345246"/>
+        <a:off x="10045410" y="2232882"/>
+        <a:ext cx="1779645" cy="345464"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7B1A1F24-5790-42BE-9800-70C6BAC67F71}">
@@ -18876,8 +18867,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="4229399">
-          <a:off x="4241227" y="2501878"/>
-          <a:ext cx="648193" cy="8089"/>
+          <a:off x="4242699" y="2503464"/>
+          <a:ext cx="648604" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18891,7 +18882,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="648193" y="4044"/>
+                <a:pt x="648604" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18946,8 +18937,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4549119" y="2489718"/>
-        <a:ext cx="32409" cy="32409"/>
+        <a:off x="4550785" y="2491293"/>
+        <a:ext cx="32430" cy="32430"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{F9E7099E-D348-4A20-924E-7B36E8E1B00D}">
@@ -18957,8 +18948,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4673563" y="2629821"/>
-          <a:ext cx="1787078" cy="363180"/>
+          <a:off x="4675308" y="2631485"/>
+          <a:ext cx="1788209" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19028,8 +19019,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4684200" y="2640458"/>
-        <a:ext cx="1765804" cy="341906"/>
+        <a:off x="4685952" y="2642129"/>
+        <a:ext cx="1766921" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{69A95BFF-166E-4390-9963-14C8F025ADBA}">
@@ -19039,8 +19030,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6460642" y="2807367"/>
-          <a:ext cx="216478" cy="8089"/>
+          <a:off x="6463518" y="2809145"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19054,7 +19045,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216478" y="4044"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19109,8 +19100,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6563469" y="2805999"/>
-        <a:ext cx="10823" cy="10823"/>
+        <a:off x="6566410" y="2807775"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{BBDCC5A6-74D1-4E37-848C-BF5D7C733A0C}">
@@ -19120,8 +19111,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6677120" y="2629821"/>
-          <a:ext cx="3154399" cy="363180"/>
+          <a:off x="6680133" y="2631485"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19191,8 +19182,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6687757" y="2640458"/>
-        <a:ext cx="3133125" cy="341906"/>
+        <a:off x="6690777" y="2642129"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E75A9ED0-3CF3-4FBB-B735-763677226156}">
@@ -19202,8 +19193,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9831520" y="2807367"/>
-          <a:ext cx="216478" cy="8089"/>
+          <a:off x="9836529" y="2809145"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19217,7 +19208,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216478" y="4044"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19272,8 +19263,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9934347" y="2805999"/>
-        <a:ext cx="10823" cy="10823"/>
+        <a:off x="9939421" y="2807775"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D255C67C-B87B-4D25-A5F4-B2880DE74996}">
@@ -19283,8 +19274,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10047999" y="2628047"/>
-          <a:ext cx="1800002" cy="366728"/>
+          <a:off x="10053144" y="2629710"/>
+          <a:ext cx="1801141" cy="366960"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19378,8 +19369,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10058740" y="2638788"/>
-        <a:ext cx="1778520" cy="345246"/>
+        <a:off x="10063892" y="2640458"/>
+        <a:ext cx="1779645" cy="345464"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{19133C7D-D6FC-4086-9EFA-C8E67C09EF92}">
@@ -19389,8 +19380,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="4842573">
-          <a:off x="2277046" y="2756674"/>
-          <a:ext cx="1340928" cy="8089"/>
+          <a:off x="2277274" y="2758420"/>
+          <a:ext cx="1341777" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19404,7 +19395,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1340928" y="4044"/>
+                <a:pt x="1341777" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19459,8 +19450,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2913987" y="2727195"/>
-        <a:ext cx="67046" cy="67046"/>
+        <a:off x="2914618" y="2728920"/>
+        <a:ext cx="67088" cy="67088"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{3A58F96D-43A0-4E22-A03B-64FF8A7610E3}">
@@ -19470,8 +19461,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3055749" y="3242387"/>
-          <a:ext cx="1401335" cy="360001"/>
+          <a:off x="3056471" y="3244439"/>
+          <a:ext cx="1402222" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19541,8 +19532,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3066293" y="3252931"/>
-        <a:ext cx="1380247" cy="338913"/>
+        <a:off x="3067022" y="3254990"/>
+        <a:ext cx="1381120" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{BC1A1E23-E0C9-4175-8735-D110618B99B3}">
@@ -19552,8 +19543,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19004863">
-          <a:off x="4416714" y="3316514"/>
-          <a:ext cx="297220" cy="8089"/>
+          <a:off x="4418296" y="3318615"/>
+          <a:ext cx="297408" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19567,7 +19558,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="297220" y="4044"/>
+                <a:pt x="297408" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19622,8 +19613,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4557893" y="3313128"/>
-        <a:ext cx="14861" cy="14861"/>
+        <a:off x="4559565" y="3315224"/>
+        <a:ext cx="14870" cy="14870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{5D691BA5-158A-4034-AEDA-B152BE077B27}">
@@ -19633,8 +19624,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4673563" y="3037139"/>
-          <a:ext cx="1768607" cy="363180"/>
+          <a:off x="4675308" y="3039060"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19704,8 +19695,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4684200" y="3047776"/>
-        <a:ext cx="1747333" cy="341906"/>
+        <a:off x="4685952" y="3049704"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{C26309FF-9296-40B3-913C-85759C2B07DC}">
@@ -19715,8 +19706,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6442171" y="3214684"/>
-          <a:ext cx="216478" cy="8089"/>
+          <a:off x="6445035" y="3216721"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19730,7 +19721,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216478" y="4044"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19785,8 +19776,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6544998" y="3213317"/>
-        <a:ext cx="10823" cy="10823"/>
+        <a:off x="6547927" y="3215350"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A4750321-4845-43B0-945B-4B9E7C7A668E}">
@@ -19796,8 +19787,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6658649" y="3037139"/>
-          <a:ext cx="3154399" cy="363180"/>
+          <a:off x="6661650" y="3039060"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19891,8 +19882,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6669286" y="3047776"/>
-        <a:ext cx="3133125" cy="341906"/>
+        <a:off x="6672294" y="3049704"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{CCE9C4CE-7CF8-4820-8390-F3CBCCE81ED7}">
@@ -19902,8 +19893,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9813049" y="3214684"/>
-          <a:ext cx="216478" cy="8089"/>
+          <a:off x="9818046" y="3216721"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19917,7 +19908,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216478" y="4044"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19972,8 +19963,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9915876" y="3213317"/>
-        <a:ext cx="10823" cy="10823"/>
+        <a:off x="9920939" y="3215350"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D954D938-3009-44F7-BB4F-D9E8AFB2B291}">
@@ -19983,8 +19974,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10029528" y="3035365"/>
-          <a:ext cx="1800002" cy="366728"/>
+          <a:off x="10034662" y="3037285"/>
+          <a:ext cx="1801141" cy="366960"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20054,8 +20045,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10040269" y="3046106"/>
-        <a:ext cx="1778520" cy="345246"/>
+        <a:off x="10045410" y="3048033"/>
+        <a:ext cx="1779645" cy="345464"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D01C8F64-85EC-45F5-B192-363D2A57FB6E}">
@@ -20065,8 +20056,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2595137">
-          <a:off x="4416714" y="3520173"/>
-          <a:ext cx="297220" cy="8089"/>
+          <a:off x="4418296" y="3522403"/>
+          <a:ext cx="297408" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20080,7 +20071,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="297220" y="4044"/>
+                <a:pt x="297408" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20135,8 +20126,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4557893" y="3516787"/>
-        <a:ext cx="14861" cy="14861"/>
+        <a:off x="4559565" y="3519012"/>
+        <a:ext cx="14870" cy="14870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7832722B-5DD1-4AAD-819C-BC966C90EDAC}">
@@ -20146,8 +20137,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4673563" y="3444456"/>
-          <a:ext cx="1768607" cy="363180"/>
+          <a:off x="4675308" y="3446636"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20217,8 +20208,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4684200" y="3455093"/>
-        <a:ext cx="1747333" cy="341906"/>
+        <a:off x="4685952" y="3457280"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9B049FA9-70FB-4D7E-AD76-2BFCDB3B4195}">
@@ -20228,8 +20219,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6442171" y="3622002"/>
-          <a:ext cx="216478" cy="8089"/>
+          <a:off x="6445035" y="3624296"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20243,7 +20234,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216478" y="4044"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20298,8 +20289,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6544998" y="3620635"/>
-        <a:ext cx="10823" cy="10823"/>
+        <a:off x="6547927" y="3622926"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B5153D0A-E9E7-482C-B1CC-838341F8F3D8}">
@@ -20309,8 +20300,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6658649" y="3444456"/>
-          <a:ext cx="3154399" cy="363180"/>
+          <a:off x="6661650" y="3446636"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20396,8 +20387,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6669286" y="3455093"/>
-        <a:ext cx="3133125" cy="341906"/>
+        <a:off x="6672294" y="3457280"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1118BB77-BCCA-46BE-8B0C-417EE0F19393}">
@@ -20407,8 +20398,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9813049" y="3622002"/>
-          <a:ext cx="216478" cy="8089"/>
+          <a:off x="9818046" y="3624296"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20422,7 +20413,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216478" y="4044"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20477,8 +20468,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9915876" y="3620635"/>
-        <a:ext cx="10823" cy="10823"/>
+        <a:off x="9920939" y="3622926"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A1FE2FD1-D3B2-4F02-B33F-7EA3496A9D7D}">
@@ -20488,8 +20479,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10029528" y="3442683"/>
-          <a:ext cx="1800002" cy="366728"/>
+          <a:off x="10034662" y="3444861"/>
+          <a:ext cx="1801141" cy="366960"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20559,8 +20550,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10040269" y="3453424"/>
-        <a:ext cx="1778520" cy="345246"/>
+        <a:off x="10045410" y="3455609"/>
+        <a:ext cx="1779645" cy="345464"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{ACD64E2A-6A03-49D1-9C11-853B1D5FDA3F}">
@@ -20570,8 +20561,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="4880920">
-          <a:off x="572973" y="4229168"/>
-          <a:ext cx="1439150" cy="8089"/>
+          <a:off x="572123" y="4231846"/>
+          <a:ext cx="1440061" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20585,7 +20576,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1439150" y="4044"/>
+                <a:pt x="1440061" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20640,8 +20631,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1256569" y="4197233"/>
-        <a:ext cx="71957" cy="71957"/>
+        <a:off x="1256152" y="4199889"/>
+        <a:ext cx="72003" cy="72003"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4915DA81-5EFF-4A45-B117-A1C9369BA960}">
@@ -20651,8 +20642,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="1400787" y="4764600"/>
-          <a:ext cx="1431583" cy="360001"/>
+          <a:off x="1400462" y="4767614"/>
+          <a:ext cx="1432488" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20774,8 +20765,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1411331" y="4775144"/>
-        <a:ext cx="1410495" cy="338913"/>
+        <a:off x="1411013" y="4778165"/>
+        <a:ext cx="1411386" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A3777E34-F7A1-4ABC-99E9-9C9A9AB7B959}">
@@ -20785,8 +20776,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17225057">
-          <a:off x="2577362" y="4595401"/>
-          <a:ext cx="722176" cy="8089"/>
+          <a:off x="2577781" y="4598311"/>
+          <a:ext cx="722633" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20800,7 +20791,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="722176" y="4044"/>
+                <a:pt x="722633" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20855,8 +20846,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2920396" y="4581391"/>
-        <a:ext cx="36108" cy="36108"/>
+        <a:off x="2921032" y="4584290"/>
+        <a:ext cx="36131" cy="36131"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{23228D17-0E30-4278-86F1-009AEEE4B90D}">
@@ -20866,8 +20857,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3044530" y="4074290"/>
-          <a:ext cx="1401335" cy="360001"/>
+          <a:off x="3045245" y="4076868"/>
+          <a:ext cx="1402222" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20937,8 +20928,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3055074" y="4084834"/>
-        <a:ext cx="1380247" cy="338913"/>
+        <a:off x="3055796" y="4087419"/>
+        <a:ext cx="1381120" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A22E3146-1836-4A0C-A6D3-4503A76A9781}">
@@ -20948,8 +20939,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19004863">
-          <a:off x="4405495" y="4148416"/>
-          <a:ext cx="297220" cy="8089"/>
+          <a:off x="4407070" y="4151044"/>
+          <a:ext cx="297408" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20963,7 +20954,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="297220" y="4044"/>
+                <a:pt x="297408" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21018,8 +21009,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4546674" y="4145030"/>
-        <a:ext cx="14861" cy="14861"/>
+        <a:off x="4548339" y="4147653"/>
+        <a:ext cx="14870" cy="14870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{06E3AC3D-2CA5-4C28-B4EE-08E1F5093575}">
@@ -21029,8 +21020,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4662344" y="3869041"/>
-          <a:ext cx="1768607" cy="363180"/>
+          <a:off x="4664082" y="3871489"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21116,8 +21107,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4672981" y="3879678"/>
-        <a:ext cx="1747333" cy="341906"/>
+        <a:off x="4674726" y="3882133"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{AB38F8C9-39F9-48F1-A4B9-359AD3B6C9E1}">
@@ -21127,8 +21118,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6430952" y="4046587"/>
-          <a:ext cx="216478" cy="8089"/>
+          <a:off x="6433809" y="4049150"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21142,7 +21133,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216478" y="4044"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21197,8 +21188,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6533779" y="4045219"/>
-        <a:ext cx="10823" cy="10823"/>
+        <a:off x="6536701" y="4047779"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{94E3E4AC-563C-467A-AD10-294BF8A33BAF}">
@@ -21208,8 +21199,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6647430" y="3869041"/>
-          <a:ext cx="3154399" cy="363180"/>
+          <a:off x="6650424" y="3871489"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21295,8 +21286,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6658067" y="3879678"/>
-        <a:ext cx="3133125" cy="341906"/>
+        <a:off x="6661068" y="3882133"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{CE4A2E59-3DB6-4586-9EDA-16655120708B}">
@@ -21306,8 +21297,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9801830" y="4046587"/>
-          <a:ext cx="216478" cy="8089"/>
+          <a:off x="9806820" y="4049150"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21321,7 +21312,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216478" y="4044"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21376,8 +21367,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9904657" y="4045219"/>
-        <a:ext cx="10823" cy="10823"/>
+        <a:off x="9909712" y="4047779"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{74F8E0C0-A1C2-4026-BDD1-211E4452BF84}">
@@ -21387,8 +21378,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10018309" y="3867267"/>
-          <a:ext cx="1800002" cy="366728"/>
+          <a:off x="10023436" y="3869714"/>
+          <a:ext cx="1801141" cy="366960"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21458,8 +21449,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10029050" y="3878008"/>
-        <a:ext cx="1778520" cy="345246"/>
+        <a:off x="10034184" y="3880462"/>
+        <a:ext cx="1779645" cy="345464"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{3776BE60-D86F-469E-9605-E0609281B4B9}">
@@ -21469,8 +21460,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2595137">
-          <a:off x="4405495" y="4352075"/>
-          <a:ext cx="297220" cy="8089"/>
+          <a:off x="4407070" y="4354831"/>
+          <a:ext cx="297408" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21484,7 +21475,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="297220" y="4044"/>
+                <a:pt x="297408" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21539,8 +21530,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4546674" y="4348689"/>
-        <a:ext cx="14861" cy="14861"/>
+        <a:off x="4548339" y="4351441"/>
+        <a:ext cx="14870" cy="14870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{DC0F0790-8247-4EA1-A5BD-20B9C2810EA5}">
@@ -21550,8 +21541,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4662344" y="4276359"/>
-          <a:ext cx="1768607" cy="363180"/>
+          <a:off x="4664082" y="4279065"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21621,8 +21612,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4672981" y="4286996"/>
-        <a:ext cx="1747333" cy="341906"/>
+        <a:off x="4674726" y="4289709"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{82B78A4F-EF07-4DEA-A3EC-7BA9DD55DC45}">
@@ -21632,8 +21623,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6430952" y="4453905"/>
-          <a:ext cx="216478" cy="8089"/>
+          <a:off x="6433809" y="4456725"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21647,7 +21638,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216478" y="4044"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21702,8 +21693,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6533779" y="4452537"/>
-        <a:ext cx="10823" cy="10823"/>
+        <a:off x="6536701" y="4455354"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4D82C0F8-05DA-476F-9FFD-EF5362E37ABC}">
@@ -21713,8 +21704,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6647430" y="4276359"/>
-          <a:ext cx="3154399" cy="363180"/>
+          <a:off x="6650424" y="4279065"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21792,8 +21783,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6658067" y="4286996"/>
-        <a:ext cx="3133125" cy="341906"/>
+        <a:off x="6661068" y="4289709"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6F09ED48-69E5-4359-AEF9-003C31CF3834}">
@@ -21803,8 +21794,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9801830" y="4453905"/>
-          <a:ext cx="216478" cy="8089"/>
+          <a:off x="9806820" y="4456725"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21818,7 +21809,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216478" y="4044"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21873,8 +21864,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9904657" y="4452537"/>
-        <a:ext cx="10823" cy="10823"/>
+        <a:off x="9909712" y="4455354"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7F4C8494-F5DD-49F1-B7FE-320AAF64A334}">
@@ -21884,8 +21875,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10018309" y="4274585"/>
-          <a:ext cx="1800002" cy="366728"/>
+          <a:off x="10023436" y="4277290"/>
+          <a:ext cx="1801141" cy="366960"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21960,8 +21951,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10029050" y="4285326"/>
-        <a:ext cx="1778520" cy="345246"/>
+        <a:off x="10034184" y="4288038"/>
+        <a:ext cx="1779645" cy="345464"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E97A89EA-A088-4B36-94ED-03E39FF28C24}">
@@ -21971,8 +21962,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="1512707">
-          <a:off x="2820974" y="4991516"/>
-          <a:ext cx="239271" cy="8089"/>
+          <a:off x="2821547" y="4994677"/>
+          <a:ext cx="239423" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21986,7 +21977,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="239271" y="4044"/>
+                <a:pt x="239423" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22041,8 +22032,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2934628" y="4989579"/>
-        <a:ext cx="11963" cy="11963"/>
+        <a:off x="2935273" y="4992736"/>
+        <a:ext cx="11971" cy="11971"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1279AA60-C872-4597-B281-C6CC2E4A34C2}">
@@ -22052,8 +22043,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3048849" y="4866521"/>
-          <a:ext cx="1401335" cy="360001"/>
+          <a:off x="3049566" y="4869600"/>
+          <a:ext cx="1402222" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22123,8 +22114,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3059393" y="4877065"/>
-        <a:ext cx="1380247" cy="338913"/>
+        <a:off x="3060117" y="4880151"/>
+        <a:ext cx="1381120" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{255CD393-ED80-4D10-A68E-31ED59592E3B}">
@@ -22134,8 +22125,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19138242">
-          <a:off x="4415645" y="4950168"/>
-          <a:ext cx="281239" cy="8089"/>
+          <a:off x="4417227" y="4953303"/>
+          <a:ext cx="281417" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22149,7 +22140,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="281239" y="4044"/>
+                <a:pt x="281417" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22204,8 +22195,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4549233" y="4947181"/>
-        <a:ext cx="14061" cy="14061"/>
+        <a:off x="4550900" y="4950312"/>
+        <a:ext cx="14070" cy="14070"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{2340676A-EBD4-4E22-BA9C-E56B6A62904C}">
@@ -22215,8 +22206,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4662344" y="4680313"/>
-          <a:ext cx="1768607" cy="363180"/>
+          <a:off x="4664082" y="4683274"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22286,8 +22277,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4672981" y="4690950"/>
-        <a:ext cx="1747333" cy="341906"/>
+        <a:off x="4674726" y="4693918"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{EB837690-03CF-4B39-A4B0-AFC71E15928A}">
@@ -22297,8 +22288,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="27806">
-          <a:off x="6430948" y="4858752"/>
-          <a:ext cx="220804" cy="8089"/>
+          <a:off x="6433805" y="4861829"/>
+          <a:ext cx="220944" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22312,7 +22303,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="220804" y="4044"/>
+                <a:pt x="220944" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22367,8 +22358,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6535830" y="4857276"/>
-        <a:ext cx="11040" cy="11040"/>
+        <a:off x="6538754" y="4860350"/>
+        <a:ext cx="11047" cy="11047"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6CD3FE0A-3BBE-455B-B381-72424654A1B0}">
@@ -22378,8 +22369,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6651749" y="4683689"/>
-          <a:ext cx="3153598" cy="360001"/>
+          <a:off x="6654746" y="4686652"/>
+          <a:ext cx="3155594" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22457,8 +22448,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6662293" y="4694233"/>
-        <a:ext cx="3132510" cy="338913"/>
+        <a:off x="6665297" y="4697203"/>
+        <a:ext cx="3134492" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B86CABA2-1933-4D02-A0D3-AA6DEA35BCA7}">
@@ -22468,8 +22459,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9805348" y="4859645"/>
-          <a:ext cx="216478" cy="8089"/>
+          <a:off x="9810340" y="4862722"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22483,7 +22474,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216478" y="4044"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22538,8 +22529,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9908175" y="4858277"/>
-        <a:ext cx="10823" cy="10823"/>
+        <a:off x="9913232" y="4861351"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{920A36CD-D69B-4AB0-8DA2-4963F1111FE2}">
@@ -22549,8 +22540,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10021826" y="4683689"/>
-          <a:ext cx="1800002" cy="360001"/>
+          <a:off x="10026956" y="4686652"/>
+          <a:ext cx="1801141" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22620,8 +22611,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10032370" y="4694233"/>
-        <a:ext cx="1778914" cy="338913"/>
+        <a:off x="10037507" y="4697203"/>
+        <a:ext cx="1780039" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{EE30240B-4D3F-4585-94A4-7AD0CBEBACD0}">
@@ -22631,8 +22622,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2755727">
-          <a:off x="4403753" y="5152053"/>
-          <a:ext cx="305023" cy="8089"/>
+          <a:off x="4405327" y="5155316"/>
+          <a:ext cx="305216" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22646,7 +22637,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="305023" y="4044"/>
+                <a:pt x="305216" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22701,8 +22692,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4548639" y="5148472"/>
-        <a:ext cx="15251" cy="15251"/>
+        <a:off x="4550305" y="5151730"/>
+        <a:ext cx="15260" cy="15260"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9B0332A1-DFA5-4E72-89B6-8E8C50F667E1}">
@@ -22712,8 +22703,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4662344" y="5084083"/>
-          <a:ext cx="1768607" cy="363180"/>
+          <a:off x="4664082" y="5087300"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22810,8 +22801,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4672981" y="5094720"/>
-        <a:ext cx="1747333" cy="341906"/>
+        <a:off x="4674726" y="5097944"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4EF5B1E7-3D92-44D9-8E8A-E2A10FB649AC}">
@@ -22821,8 +22812,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="27806">
-          <a:off x="6430948" y="5262522"/>
-          <a:ext cx="220804" cy="8089"/>
+          <a:off x="6433805" y="5265854"/>
+          <a:ext cx="220944" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22836,7 +22827,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="220804" y="4044"/>
+                <a:pt x="220944" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22891,8 +22882,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6535830" y="5261046"/>
-        <a:ext cx="11040" cy="11040"/>
+        <a:off x="6538754" y="5264375"/>
+        <a:ext cx="11047" cy="11047"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9AC7A0EB-B59E-41D9-A589-CB90FBF4305E}">
@@ -22902,8 +22893,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6651749" y="5087459"/>
-          <a:ext cx="3153598" cy="360001"/>
+          <a:off x="6654746" y="5090678"/>
+          <a:ext cx="3155594" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22989,8 +22980,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6662293" y="5098003"/>
-        <a:ext cx="3132510" cy="338913"/>
+        <a:off x="6665297" y="5101229"/>
+        <a:ext cx="3134492" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{2F5A23ED-2B4B-4307-BAD6-D126CED4ED45}">
@@ -23000,8 +22991,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9805348" y="5263415"/>
-          <a:ext cx="216478" cy="8089"/>
+          <a:off x="9810340" y="5266748"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23015,7 +23006,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216478" y="4044"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23070,8 +23061,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9908175" y="5262048"/>
-        <a:ext cx="10823" cy="10823"/>
+        <a:off x="9913232" y="5265377"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{C9CCA1DF-737F-40B9-8662-1EBAE874B88C}">
@@ -23081,8 +23072,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10021826" y="5087459"/>
-          <a:ext cx="1800002" cy="360001"/>
+          <a:off x="10026956" y="5090678"/>
+          <a:ext cx="1801141" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23152,8 +23143,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10032370" y="5098003"/>
-        <a:ext cx="1778914" cy="338913"/>
+        <a:off x="10037507" y="5101229"/>
+        <a:ext cx="1780039" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{06804470-2E4E-45CC-AD07-54CD8F165228}">
@@ -23163,8 +23154,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="4379331">
-          <a:off x="2570634" y="5294344"/>
-          <a:ext cx="739951" cy="8089"/>
+          <a:off x="2571049" y="5297697"/>
+          <a:ext cx="740419" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23178,7 +23169,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="739951" y="4044"/>
+                <a:pt x="740419" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23233,8 +23224,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2922111" y="5279890"/>
-        <a:ext cx="36997" cy="36997"/>
+        <a:off x="2922748" y="5283231"/>
+        <a:ext cx="37020" cy="37020"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D9D1FF4E-B146-4A17-8BAD-E6A8247731B1}">
@@ -23244,8 +23235,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3048849" y="5472176"/>
-          <a:ext cx="1401340" cy="360001"/>
+          <a:off x="3049566" y="5475639"/>
+          <a:ext cx="1402227" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23331,8 +23322,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3059393" y="5482720"/>
-        <a:ext cx="1380252" cy="338913"/>
+        <a:off x="3060117" y="5486190"/>
+        <a:ext cx="1381125" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{458C594D-E94A-4416-A27A-8211BD0C18EB}">
@@ -23342,8 +23333,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4450190" y="5648132"/>
-          <a:ext cx="216478" cy="8089"/>
+          <a:off x="4451794" y="5651709"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23357,7 +23348,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216478" y="4044"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23412,8 +23403,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4553017" y="5646765"/>
-        <a:ext cx="10823" cy="10823"/>
+        <a:off x="4554686" y="5650338"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E6BB35B6-4DC7-42B5-A329-D93F595605BC}">
@@ -23423,8 +23414,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4666668" y="5470587"/>
-          <a:ext cx="1758146" cy="363180"/>
+          <a:off x="4668409" y="5474048"/>
+          <a:ext cx="1759258" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23510,8 +23501,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4677305" y="5481224"/>
-        <a:ext cx="1736872" cy="341906"/>
+        <a:off x="4679053" y="5484692"/>
+        <a:ext cx="1737970" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{F3CE9778-2DAD-459C-A92D-C581128238EF}">
@@ -23521,8 +23512,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6424815" y="5648132"/>
-          <a:ext cx="216478" cy="8089"/>
+          <a:off x="6427668" y="5651709"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23536,7 +23527,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216478" y="4044"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23591,8 +23582,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6527642" y="5646765"/>
-        <a:ext cx="10823" cy="10823"/>
+        <a:off x="6530560" y="5650338"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A62201D7-F2CC-41E5-BB68-F68B79E1464B}">
@@ -23602,8 +23593,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6641293" y="5472176"/>
-          <a:ext cx="3153598" cy="360001"/>
+          <a:off x="6644283" y="5475639"/>
+          <a:ext cx="3155594" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23673,8 +23664,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6651837" y="5482720"/>
-        <a:ext cx="3132510" cy="338913"/>
+        <a:off x="6654834" y="5486190"/>
+        <a:ext cx="3134492" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{46794C65-61A0-4B52-A42E-5CC9D77E3723}">
@@ -23684,8 +23675,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9794892" y="5648132"/>
-          <a:ext cx="216478" cy="8089"/>
+          <a:off x="9799878" y="5651709"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23699,7 +23690,7 @@
                 <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216478" y="4044"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23754,8 +23745,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9897719" y="5646765"/>
-        <a:ext cx="10823" cy="10823"/>
+        <a:off x="9902770" y="5650338"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{C61F938B-5A64-4BF7-B003-81E0909084B1}">
@@ -23765,8 +23756,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10011370" y="5472176"/>
-          <a:ext cx="1800002" cy="360001"/>
+          <a:off x="10016493" y="5475639"/>
+          <a:ext cx="1801141" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23836,8 +23827,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10021914" y="5482720"/>
-        <a:ext cx="1778914" cy="338913"/>
+        <a:off x="10027044" y="5486190"/>
+        <a:ext cx="1780039" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
   </dsp:spTree>
@@ -27825,7 +27816,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A2" s="58" t="s">
+      <c r="A2" s="64" t="s">
         <v>18</v>
       </c>
       <c r="B2" s="7" t="s">
@@ -27842,7 +27833,7 @@
       <c r="G2" s="10"/>
     </row>
     <row r="3" spans="1:7" ht="64" x14ac:dyDescent="0.45">
-      <c r="A3" s="59"/>
+      <c r="A3" s="65"/>
       <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
@@ -27859,7 +27850,7 @@
       <c r="G3" s="11"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A4" s="59"/>
+      <c r="A4" s="65"/>
       <c r="B4" s="4" t="s">
         <v>184</v>
       </c>
@@ -27874,7 +27865,7 @@
       <c r="G4" s="11"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A5" s="59"/>
+      <c r="A5" s="65"/>
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
@@ -27889,7 +27880,7 @@
       <c r="G5" s="11"/>
     </row>
     <row r="6" spans="1:7" ht="48" x14ac:dyDescent="0.45">
-      <c r="A6" s="59"/>
+      <c r="A6" s="65"/>
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
@@ -27908,7 +27899,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="60"/>
+      <c r="A7" s="66"/>
       <c r="B7" s="13" t="s">
         <v>15</v>
       </c>
@@ -27925,7 +27916,7 @@
       <c r="G7" s="15"/>
     </row>
     <row r="8" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="61" t="s">
+      <c r="A8" s="67" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="7" t="s">
@@ -27946,7 +27937,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A9" s="62"/>
+      <c r="A9" s="68"/>
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -27963,7 +27954,7 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A10" s="62"/>
+      <c r="A10" s="68"/>
       <c r="B10" s="4" t="s">
         <v>4</v>
       </c>
@@ -27980,7 +27971,7 @@
       <c r="G10" s="11"/>
     </row>
     <row r="11" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="62"/>
+      <c r="A11" s="68"/>
       <c r="B11" s="4" t="s">
         <v>7</v>
       </c>
@@ -27995,7 +27986,7 @@
       <c r="G11" s="11"/>
     </row>
     <row r="12" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="63"/>
+      <c r="A12" s="69"/>
       <c r="B12" s="16" t="s">
         <v>8</v>
       </c>
@@ -28012,7 +28003,7 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A13" s="64" t="s">
+      <c r="A13" s="70" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="7" t="s">
@@ -28033,7 +28024,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="64.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="65"/>
+      <c r="A14" s="71"/>
       <c r="B14" s="4" t="s">
         <v>10</v>
       </c>
@@ -28050,7 +28041,7 @@
       <c r="G14" s="11"/>
     </row>
     <row r="15" spans="1:7" ht="64" x14ac:dyDescent="0.45">
-      <c r="A15" s="65"/>
+      <c r="A15" s="71"/>
       <c r="B15" s="4" t="s">
         <v>218</v>
       </c>
@@ -28071,7 +28062,7 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A16" s="66"/>
+      <c r="A16" s="72"/>
       <c r="B16" s="16" t="s">
         <v>11</v>
       </c>
@@ -28218,14 +28209,14 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A5" s="68" t="s">
+      <c r="A5" s="80" t="s">
         <v>273</v>
       </c>
-      <c r="B5" s="68"/>
-      <c r="C5" s="68"/>
+      <c r="B5" s="80"/>
+      <c r="C5" s="80"/>
     </row>
     <row r="6" spans="1:4" ht="32" x14ac:dyDescent="0.45">
-      <c r="A6" s="80" t="s">
+      <c r="A6" s="82" t="s">
         <v>204</v>
       </c>
       <c r="B6" s="47" t="s">
@@ -28236,7 +28227,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="32" x14ac:dyDescent="0.45">
-      <c r="A7" s="81"/>
+      <c r="A7" s="83"/>
       <c r="B7" s="47" t="s">
         <v>292</v>
       </c>
@@ -28245,7 +28236,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" ht="32" x14ac:dyDescent="0.45">
-      <c r="A8" s="81"/>
+      <c r="A8" s="83"/>
       <c r="B8" s="47" t="s">
         <v>295</v>
       </c>
@@ -28254,7 +28245,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A9" s="81"/>
+      <c r="A9" s="83"/>
       <c r="B9" s="47" t="s">
         <v>303</v>
       </c>
@@ -28263,7 +28254,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A10" s="82"/>
+      <c r="A10" s="84"/>
       <c r="B10" s="47" t="s">
         <v>297</v>
       </c>
@@ -28286,18 +28277,18 @@
       <c r="C12" s="49"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A13" s="73" t="s">
+      <c r="A13" s="74" t="s">
         <v>304</v>
       </c>
-      <c r="B13" s="74"/>
-      <c r="C13" s="75"/>
+      <c r="B13" s="75"/>
+      <c r="C13" s="76"/>
     </row>
     <row r="14" spans="1:4" ht="52" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="83" t="s">
+      <c r="A14" s="85" t="s">
         <v>230</v>
       </c>
-      <c r="B14" s="84"/>
-      <c r="C14" s="85"/>
+      <c r="B14" s="86"/>
+      <c r="C14" s="87"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="49"/>
@@ -28305,112 +28296,112 @@
       <c r="D19" s="49"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A31" s="68" t="s">
+      <c r="A31" s="80" t="s">
         <v>274</v>
       </c>
-      <c r="B31" s="68"/>
-      <c r="C31" s="68"/>
+      <c r="B31" s="80"/>
+      <c r="C31" s="80"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A32" s="76" t="s">
+      <c r="A32" s="77" t="s">
         <v>319</v>
       </c>
-      <c r="B32" s="77"/>
-      <c r="C32" s="78"/>
+      <c r="B32" s="78"/>
+      <c r="C32" s="79"/>
     </row>
     <row r="33" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="72" t="s">
+      <c r="A33" s="73" t="s">
         <v>231</v>
       </c>
       <c r="B33" s="50" t="s">
         <v>208</v>
       </c>
-      <c r="C33" s="79" t="s">
+      <c r="C33" s="81" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A34" s="72"/>
+      <c r="A34" s="73"/>
       <c r="B34" s="50" t="s">
         <v>209</v>
       </c>
-      <c r="C34" s="79"/>
+      <c r="C34" s="81"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A35" s="72"/>
+      <c r="A35" s="73"/>
       <c r="B35" s="50" t="s">
         <v>210</v>
       </c>
-      <c r="C35" s="79"/>
+      <c r="C35" s="81"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A36" s="72"/>
+      <c r="A36" s="73"/>
       <c r="B36" s="50" t="s">
         <v>211</v>
       </c>
-      <c r="C36" s="79"/>
+      <c r="C36" s="81"/>
     </row>
     <row r="37" spans="1:5" ht="32" x14ac:dyDescent="0.45">
-      <c r="A37" s="72"/>
+      <c r="A37" s="73"/>
       <c r="B37" s="48" t="s">
         <v>212</v>
       </c>
-      <c r="C37" s="79"/>
+      <c r="C37" s="81"/>
     </row>
     <row r="38" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="72" t="s">
+      <c r="A38" s="73" t="s">
         <v>232</v>
       </c>
       <c r="B38" s="50" t="s">
         <v>213</v>
       </c>
-      <c r="C38" s="79" t="s">
+      <c r="C38" s="81" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A39" s="72"/>
+      <c r="A39" s="73"/>
       <c r="B39" s="50" t="s">
         <v>214</v>
       </c>
-      <c r="C39" s="79"/>
+      <c r="C39" s="81"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A40" s="72"/>
+      <c r="A40" s="73"/>
       <c r="B40" s="50" t="s">
         <v>215</v>
       </c>
-      <c r="C40" s="79"/>
+      <c r="C40" s="81"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A42" s="73" t="s">
+      <c r="A42" s="74" t="s">
         <v>272</v>
       </c>
-      <c r="B42" s="74"/>
-      <c r="C42" s="75"/>
+      <c r="B42" s="75"/>
+      <c r="C42" s="76"/>
     </row>
     <row r="43" spans="1:5" ht="53" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A43" s="72" t="s">
+      <c r="A43" s="73" t="s">
         <v>217</v>
       </c>
-      <c r="B43" s="72"/>
-      <c r="C43" s="72"/>
+      <c r="B43" s="73"/>
+      <c r="C43" s="73"/>
     </row>
     <row r="44" spans="1:5" ht="50.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A44" s="72" t="s">
+      <c r="A44" s="73" t="s">
         <v>318</v>
       </c>
-      <c r="B44" s="72"/>
-      <c r="C44" s="72"/>
+      <c r="B44" s="73"/>
+      <c r="C44" s="73"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A46" s="68" t="s">
+      <c r="A46" s="80" t="s">
         <v>271</v>
       </c>
-      <c r="B46" s="68"/>
-      <c r="C46" s="68"/>
-      <c r="D46" s="68"/>
-      <c r="E46" s="68"/>
+      <c r="B46" s="80"/>
+      <c r="C46" s="80"/>
+      <c r="D46" s="80"/>
+      <c r="E46" s="80"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" s="44" t="s">
@@ -28596,11 +28587,11 @@
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A59" s="69" t="s">
+      <c r="A59" s="89" t="s">
         <v>275</v>
       </c>
-      <c r="B59" s="70"/>
-      <c r="C59" s="71"/>
+      <c r="B59" s="90"/>
+      <c r="C59" s="91"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" s="53" t="s">
@@ -28658,87 +28649,99 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A66" s="68" t="s">
+      <c r="A66" s="80" t="s">
         <v>291</v>
       </c>
-      <c r="B66" s="68"/>
-      <c r="C66" s="68"/>
-      <c r="D66" s="68"/>
+      <c r="B66" s="80"/>
+      <c r="C66" s="80"/>
+      <c r="D66" s="80"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A67" s="67" t="s">
+      <c r="A67" s="88" t="s">
         <v>262</v>
       </c>
-      <c r="B67" s="67"/>
-      <c r="C67" s="67"/>
-      <c r="D67" s="67"/>
+      <c r="B67" s="88"/>
+      <c r="C67" s="88"/>
+      <c r="D67" s="88"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A68" s="67" t="s">
+      <c r="A68" s="88" t="s">
         <v>263</v>
       </c>
-      <c r="B68" s="67"/>
-      <c r="C68" s="67"/>
-      <c r="D68" s="67"/>
+      <c r="B68" s="88"/>
+      <c r="C68" s="88"/>
+      <c r="D68" s="88"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A69" s="67" t="s">
+      <c r="A69" s="88" t="s">
         <v>264</v>
       </c>
-      <c r="B69" s="67"/>
-      <c r="C69" s="67"/>
-      <c r="D69" s="67"/>
+      <c r="B69" s="88"/>
+      <c r="C69" s="88"/>
+      <c r="D69" s="88"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A70" s="67" t="s">
+      <c r="A70" s="88" t="s">
         <v>265</v>
       </c>
-      <c r="B70" s="67"/>
-      <c r="C70" s="67"/>
-      <c r="D70" s="67"/>
+      <c r="B70" s="88"/>
+      <c r="C70" s="88"/>
+      <c r="D70" s="88"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A71" s="67" t="s">
+      <c r="A71" s="88" t="s">
         <v>266</v>
       </c>
-      <c r="B71" s="67"/>
-      <c r="C71" s="67"/>
-      <c r="D71" s="67"/>
+      <c r="B71" s="88"/>
+      <c r="C71" s="88"/>
+      <c r="D71" s="88"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A72" s="67" t="s">
+      <c r="A72" s="88" t="s">
         <v>267</v>
       </c>
-      <c r="B72" s="67"/>
-      <c r="C72" s="67"/>
-      <c r="D72" s="67"/>
+      <c r="B72" s="88"/>
+      <c r="C72" s="88"/>
+      <c r="D72" s="88"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A73" s="67" t="s">
+      <c r="A73" s="88" t="s">
         <v>268</v>
       </c>
-      <c r="B73" s="67"/>
-      <c r="C73" s="67"/>
-      <c r="D73" s="67"/>
+      <c r="B73" s="88"/>
+      <c r="C73" s="88"/>
+      <c r="D73" s="88"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A74" s="67" t="s">
+      <c r="A74" s="88" t="s">
         <v>269</v>
       </c>
-      <c r="B74" s="67"/>
-      <c r="C74" s="67"/>
-      <c r="D74" s="67"/>
+      <c r="B74" s="88"/>
+      <c r="C74" s="88"/>
+      <c r="D74" s="88"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A75" s="67" t="s">
+      <c r="A75" s="88" t="s">
         <v>270</v>
       </c>
-      <c r="B75" s="67"/>
-      <c r="C75" s="67"/>
-      <c r="D75" s="67"/>
+      <c r="B75" s="88"/>
+      <c r="C75" s="88"/>
+      <c r="D75" s="88"/>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="A74:D74"/>
+    <mergeCell ref="A75:D75"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A67:D67"/>
+    <mergeCell ref="A68:D68"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="A70:D70"/>
+    <mergeCell ref="A71:D71"/>
+    <mergeCell ref="A72:D72"/>
     <mergeCell ref="A44:C44"/>
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="A32:C32"/>
@@ -28752,18 +28755,6 @@
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A73:D73"/>
-    <mergeCell ref="A74:D74"/>
-    <mergeCell ref="A75:D75"/>
-    <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A66:D66"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A67:D67"/>
-    <mergeCell ref="A68:D68"/>
-    <mergeCell ref="A69:D69"/>
-    <mergeCell ref="A70:D70"/>
-    <mergeCell ref="A71:D71"/>
-    <mergeCell ref="A72:D72"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -28793,7 +28784,7 @@
     <col min="1" max="1" width="7.08203125" style="20" customWidth="1"/>
     <col min="2" max="2" width="54.33203125" customWidth="1"/>
     <col min="3" max="3" width="32.1640625" customWidth="1"/>
-    <col min="4" max="4" width="45" customWidth="1"/>
+    <col min="4" max="4" width="48.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
@@ -28803,7 +28794,7 @@
       <c r="B1" s="93"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A2" s="89" t="s">
+      <c r="A2" s="61" t="s">
         <v>339</v>
       </c>
       <c r="B2" s="38" t="s">
@@ -28811,271 +28802,271 @@
       </c>
     </row>
     <row r="3" spans="1:4" ht="34" x14ac:dyDescent="0.45">
-      <c r="A3" s="90">
+      <c r="A3" s="62">
         <v>1</v>
       </c>
-      <c r="B3" s="94" t="s">
+      <c r="B3" s="18" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A4" s="91">
+      <c r="A4" s="62">
         <v>2</v>
       </c>
-      <c r="B4" s="87" t="s">
+      <c r="B4" s="59" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A5" s="91">
+      <c r="A5" s="62">
         <v>3</v>
       </c>
-      <c r="B5" s="87" t="s">
-        <v>371</v>
+      <c r="B5" s="59" t="s">
+        <v>368</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A7" s="89" t="s">
+      <c r="A7" s="61" t="s">
         <v>339</v>
       </c>
-      <c r="B7" s="88" t="s">
+      <c r="B7" s="60" t="s">
         <v>337</v>
       </c>
-      <c r="C7" s="88" t="s">
+      <c r="C7" s="60" t="s">
         <v>336</v>
       </c>
-      <c r="D7" s="88" t="s">
+      <c r="D7" s="60" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A8" s="91">
+      <c r="A8" s="62">
         <v>1</v>
       </c>
-      <c r="B8" s="86" t="s">
+      <c r="B8" s="58" t="s">
         <v>322</v>
       </c>
-      <c r="C8" s="87" t="s">
+      <c r="C8" s="59" t="s">
         <v>343</v>
       </c>
-      <c r="D8" s="87"/>
+      <c r="D8" s="59"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A9" s="91">
+    <row r="9" spans="1:4" ht="34" x14ac:dyDescent="0.45">
+      <c r="A9" s="62">
         <v>2</v>
       </c>
-      <c r="B9" s="87" t="s">
+      <c r="B9" s="59" t="s">
         <v>323</v>
       </c>
-      <c r="C9" s="87" t="s">
-        <v>346</v>
-      </c>
-      <c r="D9" s="87" t="s">
+      <c r="C9" s="59" t="s">
         <v>345</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>369</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A10" s="91">
+      <c r="A10" s="62">
         <v>3</v>
       </c>
-      <c r="B10" s="86" t="s">
+      <c r="B10" s="58" t="s">
         <v>324</v>
       </c>
-      <c r="C10" s="87" t="s">
+      <c r="C10" s="59" t="s">
         <v>343</v>
       </c>
-      <c r="D10" s="87"/>
+      <c r="D10" s="59"/>
     </row>
-    <row r="11" spans="1:4" ht="34" x14ac:dyDescent="0.45">
-      <c r="A11" s="91">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A11" s="62">
         <v>4</v>
       </c>
-      <c r="B11" s="87" t="s">
+      <c r="B11" s="59" t="s">
         <v>325</v>
       </c>
-      <c r="C11" s="87" t="s">
-        <v>347</v>
+      <c r="C11" s="59" t="s">
+        <v>346</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="34" x14ac:dyDescent="0.45">
-      <c r="A12" s="91">
+      <c r="A12" s="62">
         <v>5</v>
       </c>
-      <c r="B12" s="87" t="s">
+      <c r="B12" s="59" t="s">
         <v>326</v>
       </c>
-      <c r="C12" s="87" t="s">
-        <v>348</v>
+      <c r="C12" s="59" t="s">
+        <v>347</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="51" x14ac:dyDescent="0.45">
-      <c r="A13" s="91">
+      <c r="A13" s="62">
         <v>6</v>
       </c>
-      <c r="B13" s="87" t="s">
+      <c r="B13" s="59" t="s">
         <v>327</v>
       </c>
-      <c r="C13" s="87" t="s">
-        <v>349</v>
-      </c>
-      <c r="D13" s="94" t="s">
-        <v>352</v>
+      <c r="C13" s="59" t="s">
+        <v>348</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A14" s="91">
+      <c r="A14" s="62">
         <v>7</v>
       </c>
-      <c r="B14" s="86" t="s">
+      <c r="B14" s="58" t="s">
         <v>328</v>
       </c>
-      <c r="C14" s="87" t="s">
+      <c r="C14" s="59" t="s">
         <v>343</v>
       </c>
-      <c r="D14" s="87"/>
+      <c r="D14" s="59"/>
     </row>
     <row r="15" spans="1:4" ht="34" x14ac:dyDescent="0.45">
-      <c r="A15" s="91">
+      <c r="A15" s="62">
         <v>8</v>
       </c>
-      <c r="B15" s="87" t="s">
+      <c r="B15" s="59" t="s">
         <v>329</v>
       </c>
-      <c r="C15" s="87" t="s">
-        <v>350</v>
-      </c>
-      <c r="D15" s="94" t="s">
-        <v>353</v>
+      <c r="C15" s="59" t="s">
+        <v>349</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="34" x14ac:dyDescent="0.45">
-      <c r="A16" s="91">
+      <c r="A16" s="62">
         <v>9</v>
       </c>
-      <c r="B16" s="87" t="s">
+      <c r="B16" s="59" t="s">
         <v>330</v>
       </c>
-      <c r="C16" s="87" t="s">
-        <v>350</v>
-      </c>
-      <c r="D16" s="94" t="s">
-        <v>354</v>
+      <c r="C16" s="59" t="s">
+        <v>349</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>353</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="34" x14ac:dyDescent="0.45">
-      <c r="A17" s="91">
+      <c r="A17" s="62">
         <v>10</v>
       </c>
-      <c r="B17" s="87" t="s">
+      <c r="B17" s="59" t="s">
         <v>331</v>
       </c>
-      <c r="C17" s="87" t="s">
-        <v>350</v>
-      </c>
-      <c r="D17" s="94" t="s">
+      <c r="C17" s="59" t="s">
+        <v>349</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="34" x14ac:dyDescent="0.45">
+      <c r="A18" s="62">
+        <v>11</v>
+      </c>
+      <c r="B18" s="59" t="s">
+        <v>332</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>367</v>
+      </c>
+      <c r="D18" s="18" t="s">
         <v>355</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="68" x14ac:dyDescent="0.45">
-      <c r="A18" s="91">
-        <v>11</v>
-      </c>
-      <c r="B18" s="87" t="s">
-        <v>332</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>370</v>
-      </c>
-      <c r="D18" s="94" t="s">
-        <v>356</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A19" s="91">
+      <c r="A19" s="62">
         <v>12</v>
       </c>
-      <c r="B19" s="87" t="s">
+      <c r="B19" s="59" t="s">
         <v>333</v>
       </c>
-      <c r="C19" s="87" t="s">
-        <v>351</v>
-      </c>
-      <c r="D19" s="87" t="s">
-        <v>357</v>
+      <c r="C19" s="59" t="s">
+        <v>350</v>
+      </c>
+      <c r="D19" s="59" t="s">
+        <v>356</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A20" s="91">
+      <c r="A20" s="62">
         <v>13</v>
       </c>
-      <c r="B20" s="87" t="s">
+      <c r="B20" s="59" t="s">
         <v>335</v>
       </c>
-      <c r="C20" s="87" t="s">
-        <v>349</v>
-      </c>
-      <c r="D20" s="87" t="s">
-        <v>358</v>
+      <c r="C20" s="59" t="s">
+        <v>348</v>
+      </c>
+      <c r="D20" s="59" t="s">
+        <v>357</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="34" x14ac:dyDescent="0.45">
-      <c r="A21" s="91">
+      <c r="A21" s="62">
         <v>14</v>
       </c>
-      <c r="B21" s="87" t="s">
+      <c r="B21" s="59" t="s">
         <v>334</v>
       </c>
-      <c r="C21" s="87" t="s">
-        <v>351</v>
-      </c>
-      <c r="D21" s="94" t="s">
-        <v>359</v>
+      <c r="C21" s="59" t="s">
+        <v>350</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B22" s="95" t="s">
-        <v>361</v>
+      <c r="B22" s="63" t="s">
+        <v>360</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B23" s="96" t="s">
-        <v>360</v>
+      <c r="B23" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B24" s="96" t="s">
-        <v>362</v>
+      <c r="B24" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B25" s="96" t="s">
-        <v>363</v>
+      <c r="B25" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B26" s="96" t="s">
-        <v>364</v>
+      <c r="B26" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B27" s="96" t="s">
-        <v>365</v>
+      <c r="B27" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B28" s="96" t="s">
-        <v>366</v>
+      <c r="B28" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B29" s="96" t="s">
-        <v>367</v>
+      <c r="B29" t="s">
+        <v>366</v>
       </c>
     </row>
   </sheetData>

--- a/project_2/project2_project status(C2).xlsx
+++ b/project_2/project2_project status(C2).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pyostry\workspace\aiffel\ai-data-bootcamp\Project_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9E05686-FAA0-4452-82CD-EF84EEAC344A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1753E519-E308-4505-9A05-2D3ED7771E3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" firstSheet="2" activeTab="6" xr2:uid="{5FF54064-7DDC-427B-93D7-EF78D75E5195}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" firstSheet="4" activeTab="9" xr2:uid="{5FF54064-7DDC-427B-93D7-EF78D75E5195}"/>
   </bookViews>
   <sheets>
     <sheet name="제작 가이드라인" sheetId="12" r:id="rId1"/>
@@ -20,9 +20,10 @@
     <sheet name="2. 지표 지도 그리기" sheetId="5" r:id="rId5"/>
     <sheet name="3. 원인 분해(로직 트리, 이슈 트리)" sheetId="7" r:id="rId6"/>
     <sheet name="4. 통계적 검증" sheetId="11" r:id="rId7"/>
-    <sheet name="5. 머신러닝 적용" sheetId="10" r:id="rId8"/>
-    <sheet name="6. 결론 및 의사결정 제안" sheetId="8" r:id="rId9"/>
-    <sheet name="7. 대시보드 제작" sheetId="9" r:id="rId10"/>
+    <sheet name="4-1 통계적 검증 결과" sheetId="13" r:id="rId8"/>
+    <sheet name="5. 머신러닝 적용" sheetId="10" r:id="rId9"/>
+    <sheet name="6. 결론 및 의사결정 제안" sheetId="8" r:id="rId10"/>
+    <sheet name="7. 대시보드 제작" sheetId="9" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="424">
   <si>
     <t>reward</t>
   </si>
@@ -1441,10 +1442,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>시철, 서영</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>02 informational offer의 "완료" 정의
 completed 이벤트가 없는 offer 타입을 수신 후 N일 내 transaction 발생으로 볼지, 아니면 퍼널을 수신 단계에서 끊고 별도로 다룰지.</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1503,10 +1500,6 @@
   </si>
   <si>
     <t>Reward 금액이 고소득자의 동기부여 수준에 미달</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Web, Email 비선호 채널의 오퍼 발송 시 수신율 저하</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -1605,10 +1598,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>channel_combination, has_mobile, has_social, viewed</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>age, channel_combination, viewed</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1665,6 +1654,315 @@
   <si>
     <t>duration
 viewed_time, received_time, viewed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>각 변수별 의미</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>채택 여부</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>사유</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기각</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보류</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가설이 전제하는 "web·email 대 mobile·social" 순수 대조 조합이 현재 오퍼 설계에 없고, email·mobile 각각은 표본 자체가 비교 불가능한 수준이라 정식 검증 불가로 판정 보류한다. 다만 참고로, 수신율 하락은 web·email 채널 자체의 약점이라기보다 social(및 mobile)의 부재와 더 크게 연관되어 보이며, {web,email}만 사용한 사례의 낮은 수신율(34.6%)도 이 해석과 일치한다. 이 가설을 확정적으로 검증하려면 채널 조합을 완전교차설계로 갖춘 A/B 테스트가 필요하다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>eward 계수 = -0.1104 (표준오차 0.003), z=-36.659, p&lt;0.001 → 통계적으로 매우 유의
+방향은 가설과 반대: reward가 높을수록 오히려 완료율이 낮음 (reward=2: 59.8% → 3: 60.1% → 5: 50.0% → 10: 38.8%)
+difficulty 계수는 이 모델에서 0.0004, p=0.895로 유의하지 않음
+reward가 offer_type과 거의 완전히 겹침(reward=10은 bogo만, reward=2·3은 discount만, reward=5만 bogo·discount 혼재)이라, 이 음의 관계가 reward 자체의 효과인지 offer_type 효과가 reward를 통해 나타난 것인지 이 모델만으로는 분리 불가
+reward가 낮아서 완료율이 낮다"는 가설은 지지되지 않으며, 오히려 반대 방향(reward가 높을수록 완료율 낮음)의 강한 통계적 연관성이 관측됐다. 다만 이 연관성은 reward-offer_type 공선성으로 인해 순수한 reward 효과인지 확정할 수 없어 기각도 지지도 아닌 판정 보류로 둔다. 확정적 판정을 위해서는 offer_type을 통제 변수로 추가한 모델이 필요하며, 표에 명시된 A/B 테스트는 현재 관찰 데이터로는 수행할 수 없고 향후 reward를 무작위 배정하는 실험 설계가 있어야 가능하다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>결론 prior_offer_count와 수신율·완료율 사이에 통계적으로는 유의한 음의 상관이 있지만 크기가 실질적으로 무시할 수준(r²&lt;0.001)이라 "노출 횟수가 늘수록 반응이 뚜렷하게 둔화된다"는 가설은 지지되지 않는다. 다만 5회 이상 구간에서의 완료율 하락(53%→43%대)은 표본이 작고(n=3,067) 선택편향 가능성도 있어 확정적 결론 없이 참고 관찰로만 남긴다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>income×difficulty 상호작용이 유의하지 않아 "소득 대비 difficulty 부담" 가설은 지지되지 않는다. 다만 income의 단순 주효과(소득 높을수록 완료율 높음, p&lt;0.001)는 별도로 유의하게 확인됐으며, 이는 이 가설과는 다른 발견으로 따로 기록해둘 만하다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연령별 Web, Email 비선호 채널의 오퍼 발송 시 수신율 저하</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소득이 높아질수록 reward(및 이와 얽힌 offer_type) 민감도가 뚜렷하고 일관되게 감소한다는 강한 증거가 확인됨(카이제곱 단조 감소, 완료율 스프레드 33.5%p→7.7%p, 상호작용 p&lt;0.001). 다만 reward-offer_type 공선성으로 인해 정확한 원인(reward 금액 자체 vs offer_type)까지는 확정 불가.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>age, channel_combination, has_mobile, has_social, viewed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부분지지/재검토 필요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>연령과 수신율의 상관관계는 통계적으로는 유의하지만(r=0.0222, p=9.77e-09) 효과크기가 무시할 수준(pseudo R²=0.04%)이고, 방향도 가설(고령층 수신율 저하)과 반대(연령 증가 시 오즈비 1.0029로 미세하게 상승)예요. 실제 저조한 구간은 고령층이 아니라 18-30 청년층(68.0%)이라 "고령층의 offer 수신율 저하" 가설은 기각으로 정리하면 될 것 같아요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>성별과 offer_type 간 연관성은 두 집단 모두 통계적으로 유의하지만(M: χ²=838.04, p&lt;0.001 / F: χ²=195.61, p&lt;0.001), 연관성 강도는 남성(Cramér's V≈0.191)이 여성(V≈0.108)의 약 1.8배로 더 강해요. 특히 남성×bogo 조합이 전체 중 완료율이 가장 낮아(42.4%), "특정 성별 집단(남성)이 특정 오퍼 유형(bogo)에 대해 수용도가 낮다"는 가설을 지지하는 결과로 볼 수 있어요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>duration과 수신율 사이에 통계적으로 유의한 선형관계가 나오긴 했지만 방향이 가설과 반대이고, 실측 패턴 자체가 비선형·비단조적이며, duration이 오퍼 정체성과 거의 동일 변수라 진짜 "기간 부족" 효과인지 오퍼별 특성 차이인지 분리가 안 됩니다. "duration이 짧아서 인지 전 마감된다"는 가설은 이 데이터로는 지지되지 않아 기각으로 정리</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Web 포함 여부의 수신율 저하 효과는 전 연령대에서 유의하게 재확인됨(가설의 "채널 비선호→수신율 저하" 부분은 지지). 다만 "연령이 높을수록 효과가 크다"는 연령별 차별 효과는 방향이 반대로 나타나 지지되지 않음(청년층 격차 27.15%p로 최대, 51세 이상은 8~11%p대로 오히려 작음). Email은 전 오퍼 공통 포함(변동 없음)으로 구조적 검증 불가.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>결과: difficulty 계수 -0.0444, p&lt;0.001 (offer_type, reward, duration 통제 후) — 단순 회귀에서는 유의하지 않았으나(p=0.895, 이는 실제로는 2번 모델 값이 잘못 라벨링된 것), offer_type·reward·duration을 함께 통제하자 difficulty가 통계적으로 유의한 음의 효과로 나타남
+결론: 단순모델(difficulty만) 계수 -0.0128(p&lt;0.001), 통제모델(+offer_type, reward, duration) 계수 -0.0444(p&lt;0.001) — 두 모델 모두 가설 방향(difficulty↑→완료율↓)과 일치하는 유의한 음의 효과. 통제 후 효과가 약 3.5배 커져, offer_type과의 혼재가 단순모델에서 효과를 일부 억제하고 있었음을 시사. 단, difficulty가 4개 값뿐인 offer-level 변수라 원자료 완료율은 비단조적(7에서 peak 60.1%, 10에서 저점 48.2%, n=25,302)이므로 해석에 주의 필요.
+결론: 두 모델 모두에서 가설 방향과 일치하는 유의한 효과 확인 → 지지. 단 비단조적 원자료 패턴 감안 필요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>offer_type 효과는 통계적으로 강하고 일관되게 확인됨(격차 확정). 다만 원인이 "수량 중심 부담"인지는 2차 모델(reward, duration 통제) 전까지 판정 보류.
+2차 통제모델(offer_type+difficulty+reward+duration)에서 offer_type[discount] 계수 0.2729(p&lt;0.001) — 단순모델(0.6020)보다 축소됐지만 통계적으로 유의하게 잔존.
+결론: 원래 격차의 상당 부분(약 55%)은 reward/difficulty/duration 차이로 설명되나, 이를 통제해도 유의한 offer_type 고유 효과가 남아있어 "수량 중심 부담" 해석을 완전히 배제할 수 없음 → 부분지지로 변경 제안.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부분지지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>추가</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로지스틱 회귀</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>age, gender, income, offer_type, difficulty, reward, duration / viewed_before_completed</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>지지(단, 변수별 방향·크기는 상이)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Profile(연령/성별/소득)에 따른 완료율 차이는 offer 특성(유형·난이도·보상·기간)과 무관하게 독립적으로 존재한다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>결과: profile 단독모델(N=39,646, pseudo R²=0.02423)과 offer 변수 통제모델(pseudo R²=0.04860) 간 gender[M]=-0.3611→-0.3737(p&lt;0.001), age=0.0026→0.0024(p&lt;0.001), income=1.316e-05→1.3e-05(p&lt;0.001)로 세 변수 모두 계수·유의성이 거의 그대로 유지됨(VIF도 age=1.106, income=1.135, gender_M=1.054로 다중공선성 없음). 즉 profile 효과는 offer 구성과 무관한 독립적 효과로 확인됨.
+결론: (1) gender — 남성이 여성보다 완료 오즈 약 31%p 낮음(오즈비 0.688), 세 검증(14번 카이제곱, 통합모델 A/B) 전체에서 가장 강하고 견고한 효과 → 14번 지지를 재확인. (2) age — 유의하나 오즈비 1.002~1.003 수준으로 실질적 영향 미미, 방향도 "고령층 저하" 가설과 반대 → 13번 기각과 일관. (3) income — 오즈비 1.139(1만불당 약 14%↑)로 유의하고 견고한 양의 주효과, 10/11번에서 남겨뒀던 income 단순 주효과를 최종 확정</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://claude.ai/code/artifact/22080a3c-9c2a-4cb8-af42-95e24164f182?open_in_browser=1&amp;via=user_open&amp;org=adc6c44b-275b-40d4-8ab5-6f1d7c2b8fd7</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이 프로젝트의 목적은 "완료율 예측"이 아니라 "완료율에 유의미한 차이가 있는가"를 확인하는 것이었음.
+이는 예측 모델이 아니라 가설검정(로지스틱 회귀, 카이제곱 검정 등)으로 답해야 하는 질문이며, 4번 단계에서 이미 14개 가설에 대해 통계적으로 검증을 완료함.
+따라서 별도의 머신러닝 예측 모델은 프로젝트 목적과 부합하지 않아 생략함.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가설(소비부담 대비 낮은 리워드가 동기부여를 떨어뜨린다)은 데이터로 지지되지 않았고, 오히려 반대 방향으로 나왔어요.offer_type 교란을 최대한 제거한 A/B 테스트(같은 할인형, 같은 채널)에서도 같은 방향이 나왔다는 게 이 결과에 힘을 실어줘요. 다만 A/B 쌍도 유효기간(7일 vs 10일)이 완전히 같진 않아서, "유효기간이 길어서 반응이 늘었을 가능성"은 완전히 배제 못 해요 — 이 부분은 한계로 명시하는 게 정직</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서현</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서영</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"Mobile·Social 대비 Web·Email 도달률이 낮다"는 가설은 지지되지 않았어요.
+•  social 유무가 압도적 1등 변수예요 (r=0.955, p&lt;0.001) — 있고 없고에 따라 열람율이 47.9%→91.8%로 거의 2배 차이
+•  web 유무는 오히려 반대 방향이에요 — web이 없는 2개 오퍼(email+mobile+social 조합)의 평균 열람율(84.0%)이 web이 있는 8개 오퍼 평균(71.8%)보다 더 높아요.web이 빠진 자리를 social·mobile이 메워주고 있기 때문이에요
+•  mobile은 표본이 9:1로 너무 불균형해서(모바일 없는 오퍼가 딱 1개) 정식 결론은 유보해야 해요 — 이전 원인분해 단계에서도 같은 이유로 "보류" 판정했던 지점과 일치해요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"duration이 짧으면 인지 전에 마감된다"는 가설은 이 데이터로 뚜렷이 지지되지 않아요.열람하는 사람은 duration 길이와 무관하게 평균 하루 안에 열람하기 때문에, 3일짜리 오퍼도 이미 충분한 시간이에요. 표면적인 duration-열람율 음의 상관은 duration 자체의 효과라기보다 채널 구성과 뒤섞인 결과일 가능성이 높습니다(duration=4가 제일 짧은데 열람율이 제일 낮은 게 그 증거).</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가설(BOGO 같은 수량 중심 오퍼가 부담을 준다)이 지지돼요.BOGO는 진짜반응율이 36.3%로, 할인형(40.9%)보다 유의하게 낮아요. 오즈비로 보면 할인형이 BOGO 대비 반응 확률이 약 21.6% 더 높습니다(p&lt;0.001).</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"목표금액이 높을수록 부담 때문에 반응이 준다"는 가설은, 이 데이터에서는 지지되지 않는다고 보는 게 맞아요.처음 봤던 유의한 음의 효과는:
+1. 채널을 통제하니 효과크기가 절반 가까이 줄었고,
+2. 그 유의성 대부분이 difficulty=20인 단 하나의 오퍼(공교롭게도 채널도 제일 부실한)에서 나온 것이었고,
+3. 정상적인 난이도 구간(5, 7, 10)만 놓고 보면 난이도와 반응 사이에 유의미한 관계가 없어요.
+즉 처음 봤던 "난이도가 부담을 준다"는 신호는 실제로는 "난이도=20인 그 오퍼가 하필 채널도 부실해서" 낮게 나온 착시였을 가능성이 높습니다. 이건 오늘 여러 번 반복된 패턴이에요 — 오퍼가 10종(인센티브형 8종)뿐이라 변수들이 서로 심하게 얽혀 있어서, 극단치 하나가 전체 회귀 결과를 좌우하기 쉬워요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가설은 지지돼요, 다만 조건부로요.difficulty=20(채널까지 부실한 그 단일 오퍼)를 포함하면 신호가 묻히고, 빼면 소득-난이도 상호작용이 뚜렷하게(p=0.002) 드러나요. 다만 오즈비 크기(1.00062, 소득 1000불당)가 매우 작아서 통계적으로는 유의해도 실무적 영향력은 크지 않다는 점은 같이 밝혀야 해요 — 예를 들어 소득 5만불 차이(income_k 50만큼)가 나야 오즈비가 약 1.03배 정도 벌어지는 수준</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"리워드 낮을수록 반응이 좋다"는 패턴 자체는 통계적으로 확인되지만, 이게 "리워드 금액" 때문인지 "할인형이라는 오퍼 구조" 때문인지는 이 8개 오퍼 데이터로는 확정할 수 없다 — 로 적으시는 게 맞아요. 오퍼 설계가 더 다양했다면(같은 reward에 BOGO/할인 둘 다 있었다면) 분리가 가능했을 것</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"연령이 추가돼야 한다"는 직감이 맞았어요.web/email 비선호 채널의 수신율 저하는 전 연령대 공통 현상이지만, 특히 35세 미만에서 훨씬 치명적이에요. 나이든 고객에게도 email이 여전히 어느 정도 먹히는 반면, 젊은 고객에게 email/web만 쓰는 건 사실상 오퍼를 거의 못 보게 만드는 수준이에요 — 이건 타겟팅 전략에 바로 쓸 수 있는 실무적 시사점이네요 (젊은 고객에게는 소셜/모바일 채널이 필수).</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"고령층의 수신율이 낮다"는 가설은 전체적으로 지지되지 않아요.오히려 전체 상관은 반대 방향(고령층이 소폭 더 높음)이고, 연령대별 열람율도 최저 구간은 65+가 아니라 20대예요. 다만 한 가지 조건에서만 예외가 있어요— web이 빠지고 모바일·소셜 위주로만 발송된 오퍼에서는 고령층이 실제로 불리했어요(r=-0.115). 즉 "고령층이 원래 반응이 나쁘다"가 아니라, "고령층은 특히 모바일·소셜 중심 채널에 약하다"는 쪽이 더 정확한 해석이에요 — 이건 지난번 확인한 "web/email이 젊은층에게 특히 불리하다"는 결과와 정확히 대칭을 이루는, 나름 일관된 큰 그림</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>가설이 정확히 맞아요 — 다만 "특정 오퍼 유형에 대한 저하"가 성별 전체에 퍼진 게 아니라, 정확히 남성 한 집단에만 국한돼요.
+•  여성과 기타 성별은 BOGO와 할인형에 반응률 차이가 전혀 없어요(여성은 소수점까지 완전히 동일한 48.0%)
+•  오직 남성만 BOGO를 유독 덜 받아들여요(34.9% vs 41.6%, 6.7%p 격차, 통계적으로 매우 유의)
+•  지금까지 "할인형이 BOGO보다 낫다"고 전체적으로 말해온 결과가, 사실은 남성 고객 한 집단이 그 격차를 전부 만들어내고 있었다는 게 이번에 처음 드러난 셈이에요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>분석 대상은 BOGO·할인형 프로모션을 열람한 39,470건이며, 열람 후 완료율은 50.69%였다.
+고객별 반복 관측을 고려한 로지스틱 회귀 결과, 달성 난이도의 계수는 -0.0113이고 p값은 0.020으로 나타났다. 따라서 난이도가 높을수록 열람 후 완료 가능성이 낮아지는 경향이 확인되어 해당 부분은 가설과 일치했다.
+반면 보상의 계수는 -0.0764이고 p값은 0.001 미만으로, 예상과 달리 보상이 높을수록 완료 가능성이 낮게 나타났다. 할인형 프로모션의 계수는 0.2936이고 p값은 0.001 미만으로, 다른 조건을 통제했을 때 할인형이 BOGO보다 완료 가능성이 높은 것으로 나타났다.
+따라서 ‘낮은 보상과 높은 난이도가 완료를 방해한다’는 가설은 부분적으로만 지지되었다. 난이도에 관한 예상은 결과와 일치했지만, 보상은 예상과 반대 방향으로 나타났다.
+다만 프로모션 설계가 8개뿐이고 보상·난이도·유형이 서로 결합되어 있으므로, 각 변수의 독립적인 인과효과로 해석할 수 없다. 회귀모형의 설명력도 Pseudo R² 기준 약 0.024로 낮아 다른 요인의 추가 검토가 필요하다. A/B 테스트는 현재 데이터로 수행할 수 없으며 향후 실험 설계로 제안할 수 있다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>관찰기간이 확보된 10개 Offer를 각각 집계하여 채널 포함 여부에 따른 평균 열람률을 비교하였다.
+Web 미포함 Offer 2개의 평균 열람률은 83.71%, 포함 Offer 8개는 71.74%였다.
+Mobile 미포함 Offer 1개의 열람률은 35.11%, 포함 Offer 9개의 평균 열람률은 78.47%였다.
+Social 미포함 Offer 4개의 평균 열람률은 47.83%, 포함 Offer 6개는 91.67%였다.
+Email은 10개 Offer에 모두 포함되어 있어 포함 여부에 따른 비교가 불가능했다.
+Mobile과 Social이 포함된 Offer에서 평균 열람률이 더 높게 나타났으며, Web은 포함된 Offer의 평균 열람률이 오히려 낮게 나타났다. 따라서 Mobile·Social 채널이 열람률과 관련 있다는 초기 가설은 기술통계상 지지되었다.
+다만 Mobile 미포함 Offer가 1개뿐이고 Email은 모든 Offer에 포함되어 있으며, 하나의 Offer에 여러 채널과 설계 조건이 동시에 적용되어 있다. 따라서 현재 결과만으로 특정 채널이 열람률을 높였다고 단정할 수 없으며, 채널 조합과 열람률 사이의 연관성으로 해석해야 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전체 66,041건을 분석한 결과, 유효기간과 열람 여부의 상관계수는 -0.0833이고 p값은 0.001 미만으로 나타났다. 통계적으로 유의하지만 상관관계의 크기는 매우 작았다.
+로지스틱 회귀에서도 유효기간의 계수는 -0.0893이고 p값은 0.001 미만으로 나타났다. 즉, 유효기간이 길수록 열람 가능성이 높아질 것이라는 가설과 반대로 유효기간이 길수록 열람 가능성이 낮아지는 방향이 확인되었다.
+기간별 수신 후 열람률은 3일 80.72%, 4일 49.86%, 5일 95.25%, 7일 72.05%, 10일 65.62%로 나타났다. 열람률이 유효기간에 따라 일정하게 증가하거나 감소하지 않았으며, 5일 프로모션의 열람률이 가장 높았다.
+열람된 프로모션의 수신 후 열람 소요시간 중앙값은 기간에 따라 12~18시간이었다. 이는 열람한 고객 대부분이 유효기간 종료보다 훨씬 이전에 프로모션을 확인했음을 보여준다.
+따라서 ‘유효기간이 짧아 고객이 인지하기 전에 종료된다’는 가설은 현재 결과에서 지지되지 않았다. 다만 프로모션 기간은 채널·유형·보상 등 다른 설계요소와 함께 정해져 있으므로, 유효기간 자체가 열람률을 낮춘다는 인과관계로 해석할 수 없다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이전 프로모션 수신 횟수별 열람률은 0회 76.64%, 1회 74.70tls%, 2회 72.52%, 3회 74.04%, 4회 이상 77.25%로 나타났다. 0회부터 2회까지는 열람률이 감소했지만, 3회 이후에는 다시 증가해 일관된 하락 패턴은 확인되지 않았다.
+고객별 반복 관측을 고려한 로지스틱 회귀 결과, 이전 프로모션 수의 계수는 -0.0143이고 p값은 0.029였다. 이전 수신 횟수가 1회 증가할 때 열람 오즈는 약 1.4% 감소하는 것으로 나타났다.
+그러나 Pseudo R²는 약 0.00006으로 설명력이 매우 낮았으며, 4회 이상 집단의 열람률이 가장 높게 나타나는 등 구간별 결과도 선형적인 감소 형태가 아니었다.
+따라서 반복 노출에 따라 반응이 둔화된다는 가설은 통계적으로 약한 관련성만 확인되었으며, 실질적인 영향은 매우 작다고 판단한다. 이 결과만으로 반복 노출이 고객 피로를 유발했다고 단정할 수 없다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>프로모션을 열람한 BOGO·할인형 39,470건을 분석한 결과, BOGO의 열람 후 완료율은 44.15%, 할인형은 60.19%로 나타났다. 할인형이 BOGO보다 16.04%p 높았다.
+카이제곱 검정 결과 통계량은 980.0053, p값은 0.001 미만으로, 프로모션 유형과 열람 후 완료 여부 사이에 통계적으로 유의한 관련성이 확인되었다.
+고객별 반복 관측을 고려한 로지스틱 회귀에서도 할인형의 계수는 0.6483이고 p값은 0.001 미만이었다. 할인형의 열람 후 완료 오즈는 BOGO의 약 1.91배로 나타났다.
+따라서 ‘BOGO의 열람 후 완료율이 할인형보다 낮을 것이다’라는 가설은 지지되었다. 다만 데이터에는 고객이 느끼는 수량 부담이 기록되어 있지 않으므로, 이러한 차이의 원인이 BOGO의 수량 부담이라고 단정할 수 없다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>프로모션을 열람한 BOGO·할인형 39,470건을 분석하였다. 열람 후 완료율은 difficulty 5에서 50.22%, 7에서 61.02%, 10에서 47.67%, 20에서 54.16%로 나타나 단순 집단 비교에서는 일관된 감소 형태가 나타나지 않았다.
+프로모션 유형을 통제한 로지스틱 회귀 결과, difficulty의 계수는 -0.0479이고 p값은 0.001 미만이었다. 프로모션 유형이 같다는 조건에서 difficulty가 1단위 증가할 때 열람 후 완료 오즈는 약 4.7% 낮아지는 것으로 나타났다.
+따라서 달성 조건 금액이 높을수록 열람 후 완료 가능성이 낮을 것이라는 가설은 통계적으로 지지되었다.
+다만 difficulty별 완료율이 단순하게 계속 감소하지 않았으며, 분석 대상이 8개의 BOGO·할인형 Offer 설계로 구성되어 있어 difficulty가 보상·기간·채널 구성과 결합되어 있다. 따라서 높은 difficulty가 완료율 감소의 직접적인 원인이라고 단정할 수는 없다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소득정보가 있는 BOGO·할인형 열람 건 34,097건을 분석하였다. 소득정보가 없는 5,373건은 이번 분석에서 제외하였다.
+8만 달러 이상 고객의 열람 후 완료율은 모든 난이도 구간에서 8만 달러 미만 고객보다 높게 나타났다. 그러나 소득과 달성 조건 금액의 상호작용 계수는 0.0015, p값은 0.402로 통계적으로 유의하지 않았다.
+따라서 ‘소득이 낮을수록 높은 달성 조건 금액의 부정적인 영향이 더 클 것이다’라는 가설은 현재 분석에서 지지되지 않았다. 고소득 고객의 전반적인 완료율은 높았지만, 소득에 따라 난이도의 영향 자체가 달라진다는 근거는 확인되지 않았다.
+이 결과는 소득과 완료율의 연관성이 없다는 의미가 아니라, 소득과 난이도의 상호작용이 통계적으로 확인되지 않았다는 의미이다. 또한 관찰 데이터이므로 인과관계로 해석할 수 없다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소득정보가 있는 BOGO·할인형 열람 건 34,097건을 분석하였다.
+8만 달러 미만 고객의 열람 후 완료율은 보상 평균 이하 집단에서 64.94%, 평균 초과 집단에서 45.92%로, 높은 보상 집단에서 19.02%p 낮았다. 8만 달러 이상 고객은 평균 이하에서 70.37%, 평균 초과에서 64.38%로, 높은 보상 집단에서 5.99%p 낮았다.
+카이제곱 검정 결과 통계량은 1,392.0102이고 p값은 0.001 미만으로, 소득·보상 집단과 열람 후 완료 여부 사이에 통계적으로 유의한 관련성이 확인되었다. 다만 카이제곱 검정은 네 집단 중 차이가 존재한다는 것만 보여주며, 소득에 따른 보상 효과의 차이는 상호작용항으로 판단해야 한다.
+로지스틱 회귀에서 소득과 보상의 상호작용 계수는 0.0268이고 p값은 0.001 미만이었다. 예상과 달리 상호작용 계수가 양수로 나타나, 소득이 높을수록 보상 증가와 완료 가능성 사이의 부정적인 관계가 오히려 약해지는 것으로 나타났다.
+따라서 ‘보상 금액이 고소득 고객의 동기부여 수준에 미달할 것이다’라는 가설은 지지되지 않았다. 오히려 높은 보상 집단에서 나타난 완료율 감소 폭은 고소득 고객보다 저소득 고객에게서 더 컸다.
+다만 보상 수준은 프로모션 유형·난이도·기간·채널 구성과 결합되어 있으므로, 높은 보상 자체가 완료율을 낮춘다고 단정할 수 없다. 또한 고객의 동기부여 수준을 직접 측정한 데이터가 없으므로 완료 반응의 차이로만 해석해야 한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>관찰기간이 확보된 프로모션 수신 66,041건을 채널 조합별로 비교하였다.
+수신 후 열람률은 Web·Email·Mobile·Social 조합이 95.55%로 가장 높았고, Email·Mobile·Social 조합은 83.44%였다. Web·Email·Mobile 조합은 51.94%였으며, Mobile과 Social이 모두 포함되지 않은 Web·Email 조합은 35.11%로 가장 낮았다.
+카이제곱 검정 결과 통계량은 16,570.2715, 자유도는 3, p값은 0.001 미만으로 나타났다. 따라서 채널 조합과 프로모션 열람 여부 사이에는 통계적으로 유의한 관련성이 확인되었다. Cramér’s V는 0.5009로, 관련성의 크기도 비교적 크게 나타났다.
+Mobile과 Social이 모두 없는 Web·Email 조합의 열람률이 가장 낮고, Social이 포함된 두 채널 조합의 열람률이 상대적으로 높아 가설은 지지되었다.
+다만 프로모션 설계가 10개뿐이고 각 채널 조합에 보상·난이도·기간·유형이 함께 결합되어 있다. 또한 동일 고객이 여러 번 포함되어 있으므로, 카이제곱 검정 결과만으로 특정 채널의 독립적인 인과효과를 단정할 수 없다. 실제 발송 성공이나 메시지 도달 여부도 없으므로 채널 조합과 열람 반응의 연관성으로 해석한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유효한 나이 정보가 있는 프로모션 수신 57,561건을 분석하였다. 54세 이하 고객의 수신 후 열람률은 74.00%, 55세 이상 고객은 74.29%로 나타나 55세 이상 집단이 0.29%p 높았다.
+전체 나이와 열람 여부의 점이연 상관계수는 0.0201이고 p값은 0.001 미만이었다. 통계적으로는 유의하지만 상관계수가 0에 매우 가까워 실질적인 관계는 거의 없는 것으로 판단된다. 또한 상관관계의 방향도 예상과 달리 약한 양의 방향이었다.
+채널 조합별 결과에서는 Email·Mobile·Social 조합만 나이와 열람 여부 사이에 음의 상관관계가 나타났다(r=-0.1168, p&lt;0.001). Web·Email 조합은 r=0.0768, Web·Email·Mobile 조합은 r=0.0893으로 양의 관계가 나타났다. 네 채널이 모두 포함된 조합은 r=0.0127, p=0.053으로 통계적으로 유의하지 않았다.
+따라서 ‘고령 고객일수록 프로모션 반응이 낮을 것이다’라는 가설은 전체 결과에서 지지되지 않았다. 채널 조합에 따라 관계의 방향이 달라지므로, 특정 채널에서 나타난 결과를 전체 고령 고객의 특성으로 일반화할 수 없다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>성별이 F 또는 M으로 확인된 BOGO·할인형 열람 건 33,572건을 분석하였다.
+여성 고객의 열람 후 완료율은 BOGO 58.56%, 할인형 70.32%였으며, 남성 고객은 BOGO 42.77%, 할인형 62.86%였다. 네 집단 중 여성·할인형의 완료율이 가장 높았고 남성·BOGO의 완료율이 가장 낮았다.
+여성의 완료율은 남성보다 BOGO에서 15.79%p, 할인형에서 7.46%p 높았다. 또한 할인형은 BOGO보다 여성에게서 11.76%p, 남성에게서 20.09%p 높은 완료율을 보였다.
+카이제곱 검정 결과 통계량은 1,473.8673, 자유도는 3, p값은 0.001 미만이었다. 따라서 성별·프로모션 유형 집단과 열람 후 완료 여부 사이에는 통계적으로 유의한 관련성이 확인되었다. Cramér’s V는 0.2095로 나타났다.
+따라서 성별과 프로모션 유형에 따라 열람 후 완료율에 차이가 있을 것이라는 가설은 지지되었다. 특히 남성 고객의 BOGO 완료율이 상대적으로 낮게 나타났다.
+다만 완료율 차이가 특정 프로모션에 대한 선호도나 수용도를 직접 의미하는 것은 아니다. 소득·나이·보상·난이도·채널 등의 차이가 함께 영향을 주었을 수 있으며, 관찰 데이터이므로 성별이 완료율 차이의 원인이라고 단정할 수 없다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>p값은 둘 다 사실상 0에 가깝지만, 상관계수 자체가 -0.02~-0.03 수준으로 극히 작아요.표본이 61,042건이나 되다 보니 이렇게 작은 효과도 통계적으로 "유의함"이 찍히는 전형적인 경우예요 (n이 크면 미미한 차이도 유의해짐).
+•  viewed: 패턴이 U자형이라 "노출 피로" 가설과 잘 안 맞음
+•  viewed_before_completed: 그나마 하락 추세가 보이지만(1회 정점→5회 34%), 상관계수로 보면 무시할 만한 크기
+정리하면 가설은 약하게만 지지— 통계적 유의성(p&lt;0.001)과 실무적 의미(r</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Cambria Math"/>
+        <family val="2"/>
+      </rPr>
+      <t>≈</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>-0.02)를 구분해서, "통계적으로는 존재하지만 크기가 작아 실무적 영향은 미미하다"고 결론 내는 게 정직한 해석</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>결론</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>제안</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1676,7 +1974,7 @@
     <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="177" formatCode="[$-412]yyyy&quot;년&quot;\ m&quot;월&quot;\ d&quot;일&quot;\ dddd\ h&quot;시&quot;\ mm&quot;분&quot;"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1867,6 +2165,29 @@
       <charset val="161"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Cambria Math"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -1906,7 +2227,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -2160,6 +2481,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border diagonalDown="1">
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal style="thin">
+        <color indexed="64"/>
+      </diagonal>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -2169,7 +2507,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2344,9 +2682,6 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -2359,7 +2694,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2451,6 +2801,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -11227,8 +11580,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="173001" y="1826087"/>
-          <a:ext cx="2123975" cy="452612"/>
+          <a:off x="220981" y="1805623"/>
+          <a:ext cx="2100172" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -11327,8 +11680,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="186258" y="1839344"/>
-        <a:ext cx="2097461" cy="426098"/>
+        <a:off x="234089" y="1818731"/>
+        <a:ext cx="2073956" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{ED5992BD-91A0-44DC-B026-C230E027754F}">
@@ -11338,8 +11691,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="16874489">
-          <a:off x="1549321" y="1134321"/>
-          <a:ext cx="1857401" cy="14378"/>
+          <a:off x="1581876" y="1121529"/>
+          <a:ext cx="1836586" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -11353,7 +11706,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1857401" y="7189"/>
+                <a:pt x="1836586" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -11412,8 +11765,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2431586" y="1095075"/>
-        <a:ext cx="92870" cy="92870"/>
+        <a:off x="2454255" y="1082803"/>
+        <a:ext cx="91829" cy="91829"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{EB7188F2-1357-4748-A44C-AB5D4A48F40F}">
@@ -11423,8 +11776,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2659066" y="4321"/>
-          <a:ext cx="1092733" cy="452612"/>
+          <a:off x="2679186" y="4273"/>
+          <a:ext cx="1080487" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -11499,8 +11852,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2672323" y="17578"/>
-        <a:ext cx="1066219" cy="426098"/>
+        <a:off x="2692294" y="17381"/>
+        <a:ext cx="1054271" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7531319A-E0E5-4CB4-9F35-33254694A0D7}">
@@ -11510,8 +11863,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3751800" y="223438"/>
-          <a:ext cx="356477" cy="14378"/>
+          <a:off x="3759673" y="220854"/>
+          <a:ext cx="352482" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -11525,7 +11878,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="356477" y="7189"/>
+                <a:pt x="352482" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -11584,8 +11937,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3921127" y="221715"/>
-        <a:ext cx="17823" cy="17823"/>
+        <a:off x="3927103" y="219231"/>
+        <a:ext cx="17624" cy="17624"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{8F385C2E-83EB-470A-8A65-12C51C60EB27}">
@@ -11595,8 +11948,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4108278" y="4321"/>
-          <a:ext cx="4735188" cy="452612"/>
+          <a:off x="4112156" y="4273"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -11695,8 +12048,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4121535" y="17578"/>
-        <a:ext cx="4708674" cy="426098"/>
+        <a:off x="4125264" y="17381"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{71327523-F24D-4A9E-8CA7-7C0E6A96618A}">
@@ -11706,8 +12059,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17132988">
-          <a:off x="1802671" y="1394574"/>
-          <a:ext cx="1350699" cy="14378"/>
+          <a:off x="1832388" y="1378865"/>
+          <a:ext cx="1335563" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -11721,7 +12074,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1350699" y="7189"/>
+                <a:pt x="1335563" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -11780,8 +12133,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2444254" y="1367995"/>
-        <a:ext cx="67534" cy="67534"/>
+        <a:off x="2466780" y="1352664"/>
+        <a:ext cx="66778" cy="66778"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{08B2E005-DF35-41E7-A396-CA02C3B8D0A4}">
@@ -11791,8 +12144,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2659066" y="524826"/>
-          <a:ext cx="1092733" cy="452612"/>
+          <a:off x="2679186" y="518944"/>
+          <a:ext cx="1080487" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -11867,8 +12220,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2672323" y="538083"/>
-        <a:ext cx="1066219" cy="426098"/>
+        <a:off x="2692294" y="532052"/>
+        <a:ext cx="1054271" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E113C6B3-F5C2-41D9-9727-BB430EAD3818}">
@@ -11878,8 +12231,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3751800" y="743943"/>
-          <a:ext cx="362090" cy="14378"/>
+          <a:off x="3759673" y="735525"/>
+          <a:ext cx="358032" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -11893,7 +12246,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="362090" y="7189"/>
+                <a:pt x="358032" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -11952,8 +12305,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3923793" y="742080"/>
-        <a:ext cx="18104" cy="18104"/>
+        <a:off x="3929739" y="733763"/>
+        <a:ext cx="17901" cy="17901"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{53F03F28-ED40-4762-8125-AFFEEA792A72}">
@@ -11963,8 +12316,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4113890" y="524826"/>
-          <a:ext cx="4735188" cy="452612"/>
+          <a:off x="4117706" y="518944"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -12087,8 +12440,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4127147" y="538083"/>
-        <a:ext cx="4708674" cy="426098"/>
+        <a:off x="4130814" y="532052"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{806C8330-1E37-41AD-AEEE-3552A4162510}">
@@ -12098,8 +12451,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17692822">
-          <a:off x="2047704" y="1654826"/>
-          <a:ext cx="860633" cy="14378"/>
+          <a:off x="2074675" y="1636200"/>
+          <a:ext cx="850988" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -12113,7 +12466,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="860633" y="7189"/>
+                <a:pt x="850988" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -12172,8 +12525,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2456505" y="1640499"/>
-        <a:ext cx="43031" cy="43031"/>
+        <a:off x="2478895" y="1622115"/>
+        <a:ext cx="42549" cy="42549"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{3BC1DAB2-4FEF-42C9-A10F-0690E2903498}">
@@ -12183,8 +12536,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2659066" y="1045330"/>
-          <a:ext cx="1092733" cy="452612"/>
+          <a:off x="2679186" y="1033615"/>
+          <a:ext cx="1080487" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -12275,8 +12628,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2672323" y="1058587"/>
-        <a:ext cx="1066219" cy="426098"/>
+        <a:off x="2692294" y="1046723"/>
+        <a:ext cx="1054271" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6BFD1C16-8154-4C15-AF72-E53B38C4A146}">
@@ -12286,8 +12639,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3751800" y="1264447"/>
-          <a:ext cx="362090" cy="14378"/>
+          <a:off x="3759673" y="1250197"/>
+          <a:ext cx="358032" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -12301,7 +12654,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="362090" y="7189"/>
+                <a:pt x="358032" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -12360,8 +12713,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3923793" y="1262584"/>
-        <a:ext cx="18104" cy="18104"/>
+        <a:off x="3929739" y="1248435"/>
+        <a:ext cx="17901" cy="17901"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1A251137-9CB6-43D7-B47D-0D220C30894C}">
@@ -12371,8 +12724,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4113890" y="1045330"/>
-          <a:ext cx="4735188" cy="452612"/>
+          <a:off x="4117706" y="1033615"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -12495,8 +12848,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4127147" y="1058587"/>
-        <a:ext cx="4708674" cy="426098"/>
+        <a:off x="4130814" y="1046723"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{227E0FEF-1368-4562-AD55-940C6A450E91}">
@@ -12506,8 +12859,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="3310531">
-          <a:off x="2160990" y="2305456"/>
-          <a:ext cx="634061" cy="14378"/>
+          <a:off x="2186691" y="2279540"/>
+          <a:ext cx="626956" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -12521,7 +12874,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="634061" y="7189"/>
+                <a:pt x="626956" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -12580,8 +12933,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2462170" y="2296794"/>
-        <a:ext cx="31703" cy="31703"/>
+        <a:off x="2484496" y="2271055"/>
+        <a:ext cx="31347" cy="31347"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{146FB508-948A-484E-B54F-2A63CE5492FA}">
@@ -12591,8 +12944,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2659066" y="2346591"/>
-          <a:ext cx="1092733" cy="452612"/>
+          <a:off x="2679186" y="2320294"/>
+          <a:ext cx="1080487" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -12667,8 +13020,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2672323" y="2359848"/>
-        <a:ext cx="1066219" cy="426098"/>
+        <a:off x="2692294" y="2333402"/>
+        <a:ext cx="1054271" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1583A4D8-C48C-400A-B5A1-D8E8188A1E57}">
@@ -12678,8 +13031,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17692822">
-          <a:off x="3502528" y="2175330"/>
-          <a:ext cx="860633" cy="14378"/>
+          <a:off x="3513195" y="2150872"/>
+          <a:ext cx="850988" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -12693,7 +13046,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="860633" y="7189"/>
+                <a:pt x="850988" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -12752,8 +13105,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3911329" y="2161003"/>
-        <a:ext cx="43031" cy="43031"/>
+        <a:off x="3917415" y="2136786"/>
+        <a:ext cx="42549" cy="42549"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{985FE1E2-4CA8-4AC7-A474-DEECC9A2BB80}">
@@ -12763,8 +13116,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4113890" y="1565835"/>
-          <a:ext cx="4735188" cy="452612"/>
+          <a:off x="4117706" y="1548287"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -12855,8 +13208,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4127147" y="1579092"/>
-        <a:ext cx="4708674" cy="426098"/>
+        <a:off x="4130814" y="1561395"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{16F44D37-2601-482A-9095-0B3E8E10E520}">
@@ -12866,8 +13219,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19457599">
-          <a:off x="3709887" y="2435583"/>
-          <a:ext cx="445915" cy="14378"/>
+          <a:off x="3718230" y="2408207"/>
+          <a:ext cx="440918" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -12881,7 +13234,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="445915" y="7189"/>
+                <a:pt x="440918" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -12940,8 +13293,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3921697" y="2431624"/>
-        <a:ext cx="22295" cy="22295"/>
+        <a:off x="3927667" y="2404373"/>
+        <a:ext cx="22045" cy="22045"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{2D542640-C237-42B5-8470-73084719F8F3}">
@@ -12951,8 +13304,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4113890" y="2086339"/>
-          <a:ext cx="4735188" cy="452612"/>
+          <a:off x="4117706" y="2062958"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -13043,8 +13396,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4127147" y="2099596"/>
-        <a:ext cx="4708674" cy="426098"/>
+        <a:off x="4130814" y="2076066"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9A75AB13-86A0-459A-8B2B-E8037D74B447}">
@@ -13054,8 +13407,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2142401">
-          <a:off x="3709887" y="2695835"/>
-          <a:ext cx="445915" cy="14378"/>
+          <a:off x="3718230" y="2665543"/>
+          <a:ext cx="440918" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -13069,7 +13422,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="445915" y="7189"/>
+                <a:pt x="440918" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -13128,8 +13481,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3921697" y="2691876"/>
-        <a:ext cx="22295" cy="22295"/>
+        <a:off x="3927667" y="2661709"/>
+        <a:ext cx="22045" cy="22045"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{106C3051-36E0-4DB2-B006-BD51244834C6}">
@@ -13139,8 +13492,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4113890" y="2606844"/>
-          <a:ext cx="4735188" cy="452612"/>
+          <a:off x="4117706" y="2577630"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -13231,8 +13584,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4127147" y="2620101"/>
-        <a:ext cx="4708674" cy="426098"/>
+        <a:off x="4130814" y="2590738"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6562E267-52DD-4DC6-81E6-A0E9307367D6}">
@@ -13242,8 +13595,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="3907178">
-          <a:off x="3502528" y="2956087"/>
-          <a:ext cx="860633" cy="14378"/>
+          <a:off x="3513195" y="2922879"/>
+          <a:ext cx="850988" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -13257,7 +13610,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="860633" y="7189"/>
+                <a:pt x="850988" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -13316,8 +13669,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3911329" y="2941760"/>
-        <a:ext cx="43031" cy="43031"/>
+        <a:off x="3917415" y="2908793"/>
+        <a:ext cx="42549" cy="42549"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{220D319D-36C0-42A0-A946-F197C4269C14}">
@@ -13327,8 +13680,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4113890" y="3127348"/>
-          <a:ext cx="4735188" cy="452612"/>
+          <a:off x="4117706" y="3092301"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -13419,8 +13772,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4127147" y="3140605"/>
-        <a:ext cx="4708674" cy="426098"/>
+        <a:off x="4130814" y="3105409"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4332858F-88A7-466E-8722-8833A7B96598}">
@@ -13430,8 +13783,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="4725511">
-          <a:off x="1549321" y="2956087"/>
-          <a:ext cx="1857401" cy="14378"/>
+          <a:off x="1581876" y="2922879"/>
+          <a:ext cx="1836586" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -13445,7 +13798,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1857401" y="7189"/>
+                <a:pt x="1836586" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -13500,8 +13853,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2431586" y="2916841"/>
-        <a:ext cx="92870" cy="92870"/>
+        <a:off x="2454255" y="2884153"/>
+        <a:ext cx="91829" cy="91829"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1479FCFA-85A4-438D-B5D0-346DFAD5924D}">
@@ -13511,8 +13864,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2659066" y="3647853"/>
-          <a:ext cx="1092733" cy="452612"/>
+          <a:off x="2679186" y="3606973"/>
+          <a:ext cx="1080487" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -13587,8 +13940,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2672323" y="3661110"/>
-        <a:ext cx="1066219" cy="426098"/>
+        <a:off x="2692294" y="3620081"/>
+        <a:ext cx="1054271" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E6D0412B-4D85-432B-BE35-F277BFD00B03}">
@@ -13598,8 +13951,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3751800" y="3866970"/>
-          <a:ext cx="362090" cy="14378"/>
+          <a:off x="3759673" y="3823554"/>
+          <a:ext cx="358032" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -13613,7 +13966,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="362090" y="7189"/>
+                <a:pt x="358032" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -13668,8 +14021,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3923793" y="3865107"/>
-        <a:ext cx="18104" cy="18104"/>
+        <a:off x="3929739" y="3821792"/>
+        <a:ext cx="17901" cy="17901"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{CE9AFD94-4037-4F8B-B49B-020818B5CBB5}">
@@ -13679,8 +14032,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4113890" y="3647853"/>
-          <a:ext cx="4735188" cy="452612"/>
+          <a:off x="4117706" y="3606973"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -13787,8 +14140,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4127147" y="3661110"/>
-        <a:ext cx="4708674" cy="426098"/>
+        <a:off x="4130814" y="3620081"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B460AB31-448C-42B6-9C6B-D3CF5013B4F6}">
@@ -13798,8 +14151,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="39236" y="4688862"/>
-          <a:ext cx="1821222" cy="452612"/>
+          <a:off x="88714" y="4636316"/>
+          <a:ext cx="1800813" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -13924,8 +14277,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="52493" y="4702119"/>
-        <a:ext cx="1794708" cy="426098"/>
+        <a:off x="101822" y="4649424"/>
+        <a:ext cx="1774597" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{C120D3E5-D1A3-4DC1-848B-C37D9DDE2012}">
@@ -13935,8 +14288,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="18752467">
-          <a:off x="1746056" y="4647727"/>
-          <a:ext cx="706446" cy="14378"/>
+          <a:off x="1776407" y="4595561"/>
+          <a:ext cx="698529" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -13950,7 +14303,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="706446" y="7189"/>
+                <a:pt x="698529" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -14005,8 +14358,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2081618" y="4637255"/>
-        <a:ext cx="35322" cy="35322"/>
+        <a:off x="2108209" y="4585287"/>
+        <a:ext cx="34926" cy="34926"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6F01F0AA-74B9-49DB-A456-B8979039EB51}">
@@ -14016,8 +14369,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2338101" y="4168357"/>
-          <a:ext cx="1092733" cy="452612"/>
+          <a:off x="2361817" y="4121644"/>
+          <a:ext cx="1080487" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -14090,8 +14443,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2351358" y="4181614"/>
-        <a:ext cx="1066219" cy="426098"/>
+        <a:off x="2374925" y="4134752"/>
+        <a:ext cx="1054271" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{F5E69F9A-2631-4A2D-BC76-B4BD9B08D019}">
@@ -14101,8 +14454,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3430834" y="4387475"/>
-          <a:ext cx="368146" cy="14378"/>
+          <a:off x="3442305" y="4338225"/>
+          <a:ext cx="364020" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -14116,7 +14469,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="368146" y="7189"/>
+                <a:pt x="364020" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -14171,8 +14524,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3605704" y="4385460"/>
-        <a:ext cx="18407" cy="18407"/>
+        <a:off x="3615214" y="4336314"/>
+        <a:ext cx="18201" cy="18201"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{69EDA0B0-D39D-4C93-8B8D-10889C581D9E}">
@@ -14182,8 +14535,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3798980" y="4168357"/>
-          <a:ext cx="4735188" cy="452612"/>
+          <a:off x="3806325" y="4121644"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -14256,8 +14609,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3812237" y="4181614"/>
-        <a:ext cx="4708674" cy="426098"/>
+        <a:off x="3819433" y="4134752"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{AC23C890-5E27-4DC3-9BF7-2C50218200D9}">
@@ -14267,8 +14620,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="1860458" y="4907979"/>
-          <a:ext cx="477642" cy="14378"/>
+          <a:off x="1889527" y="4852897"/>
+          <a:ext cx="472289" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -14282,7 +14635,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="477642" y="7189"/>
+                <a:pt x="472289" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -14337,8 +14690,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2087338" y="4903227"/>
-        <a:ext cx="23882" cy="23882"/>
+        <a:off x="2113865" y="4848279"/>
+        <a:ext cx="23614" cy="23614"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B4CF3050-E538-4710-99C5-FB5B2F28D116}">
@@ -14348,8 +14701,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2338101" y="4688862"/>
-          <a:ext cx="1092733" cy="452612"/>
+          <a:off x="2361817" y="4636316"/>
+          <a:ext cx="1080487" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -14422,8 +14775,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2351358" y="4702119"/>
-        <a:ext cx="1066219" cy="426098"/>
+        <a:off x="2374925" y="4649424"/>
+        <a:ext cx="1054271" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{55492AE0-989E-4368-96E6-8609B6786079}">
@@ -14433,8 +14786,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3430834" y="4907979"/>
-          <a:ext cx="368146" cy="14378"/>
+          <a:off x="3442305" y="4852897"/>
+          <a:ext cx="364020" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -14448,7 +14801,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="368146" y="7189"/>
+                <a:pt x="364020" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -14503,8 +14856,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3605704" y="4905964"/>
-        <a:ext cx="18407" cy="18407"/>
+        <a:off x="3615214" y="4850985"/>
+        <a:ext cx="18201" cy="18201"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{99BD4B49-7654-4BFC-93A2-73715A94DAC0}">
@@ -14514,8 +14867,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3798980" y="4688862"/>
-          <a:ext cx="4735188" cy="452612"/>
+          <a:off x="3806325" y="4636316"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -14632,8 +14985,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3812237" y="4702119"/>
-        <a:ext cx="4708674" cy="426098"/>
+        <a:off x="3819433" y="4649424"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{48D36C81-0EEF-4879-868D-73109D1A61EF}">
@@ -14643,8 +14996,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2847533">
-          <a:off x="1746056" y="5168231"/>
-          <a:ext cx="706446" cy="14378"/>
+          <a:off x="1776407" y="5110232"/>
+          <a:ext cx="698529" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -14658,7 +15011,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="706446" y="7189"/>
+                <a:pt x="698529" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -14713,8 +15066,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2081618" y="5157759"/>
-        <a:ext cx="35322" cy="35322"/>
+        <a:off x="2108209" y="5099958"/>
+        <a:ext cx="34926" cy="34926"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E0C7A212-1F93-473A-8909-15A6780CBC2F}">
@@ -14724,8 +15077,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2338101" y="5209366"/>
-          <a:ext cx="1092733" cy="452612"/>
+          <a:off x="2361817" y="5150987"/>
+          <a:ext cx="1080487" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -14798,8 +15151,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2351358" y="5222623"/>
-        <a:ext cx="1066219" cy="426098"/>
+        <a:off x="2374925" y="5164095"/>
+        <a:ext cx="1054271" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4D54B04B-F98B-4577-8925-91ECEF877996}">
@@ -14809,8 +15162,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3430834" y="5428484"/>
-          <a:ext cx="380303" cy="14378"/>
+          <a:off x="3442305" y="5367568"/>
+          <a:ext cx="376041" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -14824,7 +15177,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="380303" y="7189"/>
+                <a:pt x="376041" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -14879,8 +15232,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3611478" y="5426165"/>
-        <a:ext cx="19015" cy="19015"/>
+        <a:off x="3620924" y="5365356"/>
+        <a:ext cx="18802" cy="18802"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{540CB623-D523-4AD6-BF5D-A946D7B052E6}">
@@ -14890,8 +15243,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3811137" y="5209366"/>
-          <a:ext cx="4735188" cy="452612"/>
+          <a:off x="3818346" y="5150987"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -15009,8 +15362,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3824394" y="5222623"/>
-        <a:ext cx="4708674" cy="426098"/>
+        <a:off x="3831454" y="5164095"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
   </dsp:spTree>
@@ -15032,8 +15385,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10440" y="3343938"/>
-          <a:ext cx="1173405" cy="360228"/>
+          <a:off x="9182" y="3307680"/>
+          <a:ext cx="1177681" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -15111,8 +15464,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="20991" y="3354489"/>
-        <a:ext cx="1152303" cy="339126"/>
+        <a:off x="19771" y="3318269"/>
+        <a:ext cx="1156503" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7667B88B-738E-4E27-80A6-15B1E3AED5F8}">
@@ -15122,8 +15475,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="16719080">
-          <a:off x="572123" y="2808170"/>
-          <a:ext cx="1440061" cy="8089"/>
+          <a:off x="572912" y="2769909"/>
+          <a:ext cx="1445308" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -15134,10 +15487,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1440061" y="4044"/>
+                <a:pt x="1445308" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -15196,8 +15549,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1256152" y="2776213"/>
-        <a:ext cx="72003" cy="72003"/>
+        <a:off x="1259433" y="2737887"/>
+        <a:ext cx="72265" cy="72265"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D9E30B0F-B6EE-4B8A-B3A5-5AD7E4CFBC12}">
@@ -15207,8 +15560,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="1400462" y="1920262"/>
-          <a:ext cx="1439393" cy="360228"/>
+          <a:off x="1404269" y="1878817"/>
+          <a:ext cx="1444638" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -15299,8 +15652,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1411013" y="1930813"/>
-        <a:ext cx="1418291" cy="339126"/>
+        <a:off x="1414858" y="1889406"/>
+        <a:ext cx="1423460" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{ED5992BD-91A0-44DC-B026-C230E027754F}">
@@ -15310,8 +15663,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="16757427">
-          <a:off x="2277274" y="1434244"/>
-          <a:ext cx="1341777" cy="8089"/>
+          <a:off x="2284276" y="1390976"/>
+          <a:ext cx="1346666" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -15322,10 +15675,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1341777" y="4044"/>
+                <a:pt x="1346666" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -15384,8 +15737,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2914618" y="1404744"/>
-        <a:ext cx="67088" cy="67088"/>
+        <a:off x="2923942" y="1361420"/>
+        <a:ext cx="67333" cy="67333"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{EB7188F2-1357-4748-A44C-AB5D4A48F40F}">
@@ -15395,8 +15748,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3056471" y="596085"/>
-          <a:ext cx="1402222" cy="360228"/>
+          <a:off x="3066312" y="549815"/>
+          <a:ext cx="1407331" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -15466,8 +15819,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3067022" y="606636"/>
-        <a:ext cx="1381120" cy="339126"/>
+        <a:off x="3076901" y="560404"/>
+        <a:ext cx="1386153" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7531319A-E0E5-4CB4-9F35-33254694A0D7}">
@@ -15477,8 +15830,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17860289">
-          <a:off x="4335717" y="568811"/>
-          <a:ext cx="459210" cy="8089"/>
+          <a:off x="4350219" y="522390"/>
+          <a:ext cx="460883" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -15489,10 +15842,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="459210" y="4044"/>
+                <a:pt x="460883" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -15551,8 +15904,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4553842" y="561375"/>
-        <a:ext cx="22960" cy="22960"/>
+        <a:off x="4569139" y="514979"/>
+        <a:ext cx="23044" cy="23044"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{8F385C2E-83EB-470A-8A65-12C51C60EB27}">
@@ -15562,8 +15915,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4671951" y="187807"/>
-          <a:ext cx="1769726" cy="363410"/>
+          <a:off x="4687678" y="140049"/>
+          <a:ext cx="1776175" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -15633,8 +15986,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4682595" y="198451"/>
-        <a:ext cx="1748438" cy="342122"/>
+        <a:off x="4698361" y="150732"/>
+        <a:ext cx="1754809" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{8EC6EEF9-E6D8-4DE2-A6DD-BB50B40A5CF0}">
@@ -15644,8 +15997,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6441677" y="365467"/>
-          <a:ext cx="219972" cy="8089"/>
+          <a:off x="6463853" y="318305"/>
+          <a:ext cx="220774" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -15656,10 +16009,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="219972" y="4044"/>
+                <a:pt x="220774" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -15714,8 +16067,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6546165" y="364012"/>
-        <a:ext cx="10998" cy="10998"/>
+        <a:off x="6568721" y="316896"/>
+        <a:ext cx="11038" cy="11038"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{31CFEB2D-0887-4520-AF04-1E3C38912960}">
@@ -15725,8 +16078,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6661650" y="187807"/>
-          <a:ext cx="3156395" cy="363410"/>
+          <a:off x="6684628" y="140049"/>
+          <a:ext cx="3167897" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -15812,8 +16165,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6672294" y="198451"/>
-        <a:ext cx="3135107" cy="342122"/>
+        <a:off x="6695311" y="150732"/>
+        <a:ext cx="3146531" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{602438BB-CBF9-49AF-AB0A-D57EA2C10BE2}">
@@ -15823,8 +16176,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9818046" y="365467"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9852525" y="318305"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -15835,10 +16188,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -15893,8 +16246,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9920939" y="364096"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9955792" y="316981"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{57D97F9E-094F-4C3F-82B2-5A689BC4D082}">
@@ -15904,8 +16257,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10034662" y="193925"/>
-          <a:ext cx="1801141" cy="351174"/>
+          <a:off x="10069930" y="146189"/>
+          <a:ext cx="1807704" cy="352453"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16002,8 +16355,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10044948" y="204211"/>
-        <a:ext cx="1780569" cy="330602"/>
+        <a:off x="10080253" y="156512"/>
+        <a:ext cx="1787058" cy="331807"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B3B4155B-F64B-452E-AEBC-36FE76B0BD69}">
@@ -16013,8 +16366,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="21585916">
-          <a:off x="4458692" y="771712"/>
-          <a:ext cx="216617" cy="8089"/>
+          <a:off x="4473642" y="726030"/>
+          <a:ext cx="217406" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16025,10 +16378,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216617" y="4044"/>
+                <a:pt x="217406" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16083,8 +16436,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4561585" y="770341"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="4576910" y="724705"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D20B6C81-A2D9-4E8E-80C0-968EFF7F89E1}">
@@ -16094,8 +16447,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4675308" y="593607"/>
-          <a:ext cx="1769726" cy="363410"/>
+          <a:off x="4691048" y="547328"/>
+          <a:ext cx="1776175" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16165,8 +16518,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4685952" y="604251"/>
-        <a:ext cx="1748438" cy="342122"/>
+        <a:off x="4701731" y="558011"/>
+        <a:ext cx="1754809" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7FE58BCF-6B0D-48A2-8DDE-611A1D34A4D6}">
@@ -16176,8 +16529,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6445035" y="771268"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="6467223" y="725585"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16188,10 +16541,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16246,8 +16599,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6547927" y="769897"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="6570490" y="724260"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{629314FA-FCA6-45B9-99A7-2C2196A96D5C}">
@@ -16257,8 +16610,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6661650" y="593607"/>
-          <a:ext cx="3156395" cy="363410"/>
+          <a:off x="6684628" y="547328"/>
+          <a:ext cx="3167897" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16357,8 +16710,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6672294" y="604251"/>
-        <a:ext cx="3135107" cy="342122"/>
+        <a:off x="6695311" y="558011"/>
+        <a:ext cx="3146531" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{CCF144EB-A097-46BE-8FF7-BE5C7A394E2A}">
@@ -16368,8 +16721,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9818046" y="771268"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9852525" y="725585"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16380,10 +16733,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16438,8 +16791,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9920939" y="769897"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9955792" y="724260"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9EE0F2D9-F39B-4921-9EAC-DBA04DC260DD}">
@@ -16449,8 +16802,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10034662" y="591832"/>
-          <a:ext cx="1801141" cy="366960"/>
+          <a:off x="10069930" y="545546"/>
+          <a:ext cx="1807704" cy="368297"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16533,8 +16886,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10045410" y="602580"/>
-        <a:ext cx="1779645" cy="345464"/>
+        <a:off x="10080717" y="556333"/>
+        <a:ext cx="1786130" cy="346723"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6169CD61-5E3A-4096-AA5A-91A22C397918}">
@@ -16544,8 +16897,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="3717526">
-          <a:off x="4336611" y="975499"/>
-          <a:ext cx="460779" cy="8089"/>
+          <a:off x="4351116" y="930560"/>
+          <a:ext cx="462458" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16556,10 +16909,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="460779" y="4044"/>
+                <a:pt x="462458" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16614,8 +16967,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4555481" y="968024"/>
-        <a:ext cx="23038" cy="23038"/>
+        <a:off x="4570784" y="923109"/>
+        <a:ext cx="23122" cy="23122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D5FDB947-B70B-4493-B9F9-83A45503DA23}">
@@ -16625,8 +16978,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4675308" y="1001183"/>
-          <a:ext cx="1769726" cy="363410"/>
+          <a:off x="4691048" y="956388"/>
+          <a:ext cx="1776175" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16696,8 +17049,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4685952" y="1011827"/>
-        <a:ext cx="1748438" cy="342122"/>
+        <a:off x="4701731" y="967071"/>
+        <a:ext cx="1754809" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9EDF68AF-E14B-40BF-AB6D-4B01635D735A}">
@@ -16707,8 +17060,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6445035" y="1178843"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="6467223" y="1134645"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16719,10 +17072,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16777,8 +17130,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6547927" y="1177472"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="6570490" y="1133321"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{5A5C0991-25ED-4076-91F2-80A2EEFC811E}">
@@ -16788,8 +17141,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6661650" y="1001183"/>
-          <a:ext cx="3156395" cy="363410"/>
+          <a:off x="6684628" y="956388"/>
+          <a:ext cx="3167897" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16923,8 +17276,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6672294" y="1011827"/>
-        <a:ext cx="3135107" cy="342122"/>
+        <a:off x="6695311" y="967071"/>
+        <a:ext cx="3146531" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{723082D3-A8E2-4807-89B5-C74C600B949E}">
@@ -16934,8 +17287,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9818046" y="1178843"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9852525" y="1134645"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16946,10 +17299,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17004,8 +17357,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9920939" y="1177472"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9955792" y="1133321"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{05E664DE-AAC0-4D52-9AA4-DE55CA572420}">
@@ -17015,8 +17368,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10034662" y="999408"/>
-          <a:ext cx="1801141" cy="366960"/>
+          <a:off x="10069930" y="954607"/>
+          <a:ext cx="1807704" cy="368297"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17086,8 +17439,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10045410" y="1010156"/>
-        <a:ext cx="1779645" cy="345464"/>
+        <a:off x="10080717" y="965394"/>
+        <a:ext cx="1786130" cy="346723"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{16F44D37-2601-482A-9095-0B3E8E10E520}">
@@ -17097,8 +17450,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="1505741">
-          <a:off x="2828565" y="2147057"/>
-          <a:ext cx="239195" cy="8089"/>
+          <a:off x="2837576" y="2106387"/>
+          <a:ext cx="240066" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17109,10 +17462,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="239195" y="4044"/>
+                <a:pt x="240066" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17171,8 +17524,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2942183" y="2145122"/>
-        <a:ext cx="11959" cy="11959"/>
+        <a:off x="2951607" y="2104496"/>
+        <a:ext cx="12003" cy="12003"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{2D542640-C237-42B5-8470-73084719F8F3}">
@@ -17182,8 +17535,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3056471" y="2021712"/>
-          <a:ext cx="1402222" cy="360228"/>
+          <a:off x="3066312" y="1980637"/>
+          <a:ext cx="1407331" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17253,8 +17606,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3067022" y="2032263"/>
-        <a:ext cx="1381120" cy="339126"/>
+        <a:off x="3076901" y="1991226"/>
+        <a:ext cx="1386153" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{BFCFD3BD-878E-4ADC-81DA-3641DCD660A7}">
@@ -17264,8 +17617,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17370601">
-          <a:off x="4242699" y="1892100"/>
-          <a:ext cx="648604" cy="8089"/>
+          <a:off x="4256862" y="1850501"/>
+          <a:ext cx="650967" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17276,10 +17629,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="648604" y="4044"/>
+                <a:pt x="650967" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17334,8 +17687,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4550785" y="1879930"/>
-        <a:ext cx="32430" cy="32430"/>
+        <a:off x="4566071" y="1838338"/>
+        <a:ext cx="32548" cy="32548"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{911F1DD5-D3D2-4321-A1A5-7E2BAE25AAD5}">
@@ -17345,8 +17698,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4675308" y="1408758"/>
-          <a:ext cx="1769726" cy="363410"/>
+          <a:off x="4691048" y="1365449"/>
+          <a:ext cx="1776175" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17416,8 +17769,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4685952" y="1419402"/>
-        <a:ext cx="1748438" cy="342122"/>
+        <a:off x="4701731" y="1376132"/>
+        <a:ext cx="1754809" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{F4CAC384-240B-4811-A7FE-5EF39454FD0A}">
@@ -17427,8 +17780,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6445035" y="1586419"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="6467223" y="1543706"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17439,10 +17792,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17497,8 +17850,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6547927" y="1585048"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="6570490" y="1542381"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{00847D60-C67D-487A-B918-B0C406DE6A20}">
@@ -17508,8 +17861,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6661650" y="1408758"/>
-          <a:ext cx="3156395" cy="363410"/>
+          <a:off x="6684628" y="1365449"/>
+          <a:ext cx="3167897" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17619,8 +17972,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6672294" y="1419402"/>
-        <a:ext cx="3135107" cy="342122"/>
+        <a:off x="6695311" y="1376132"/>
+        <a:ext cx="3146531" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7682FEBA-2A8A-4CEB-BAD3-CAC6D62452E9}">
@@ -17630,8 +17983,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9818046" y="1586419"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9852525" y="1543706"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17642,10 +17995,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17700,8 +18053,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9920939" y="1585048"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9955792" y="1542381"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4C2C55F9-D12D-4BE1-85AD-8FAFF8B344C7}">
@@ -17711,8 +18064,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10034662" y="1406983"/>
-          <a:ext cx="1801141" cy="366960"/>
+          <a:off x="10069930" y="1363668"/>
+          <a:ext cx="1807704" cy="368297"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17830,8 +18183,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10045410" y="1417731"/>
-        <a:ext cx="1779645" cy="345464"/>
+        <a:off x="10080717" y="1374455"/>
+        <a:ext cx="1786130" cy="346723"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6A4076F7-5C10-4205-AF7B-34977DAE41B6}">
@@ -17841,8 +18194,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19004863">
-          <a:off x="4418296" y="2095888"/>
-          <a:ext cx="297408" cy="8089"/>
+          <a:off x="4433100" y="2055032"/>
+          <a:ext cx="298492" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17853,10 +18206,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="297408" y="4044"/>
+                <a:pt x="298492" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17911,8 +18264,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4559565" y="2092498"/>
-        <a:ext cx="14870" cy="14870"/>
+        <a:off x="4574883" y="2051680"/>
+        <a:ext cx="14924" cy="14924"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D2D6EBAC-87C6-4589-B626-76CA00356F2A}">
@@ -17922,8 +18275,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4675308" y="1816334"/>
-          <a:ext cx="1769726" cy="363410"/>
+          <a:off x="4691048" y="1774510"/>
+          <a:ext cx="1776175" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17993,8 +18346,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4685952" y="1826978"/>
-        <a:ext cx="1748438" cy="342122"/>
+        <a:off x="4701731" y="1785193"/>
+        <a:ext cx="1754809" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4CEC118E-B718-4A3D-A714-E879160F0F50}">
@@ -18004,8 +18357,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6445035" y="1993994"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="6467223" y="1952767"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18016,10 +18369,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18074,8 +18427,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6547927" y="1992623"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="6570490" y="1951442"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{96C9B796-69AA-48A9-AB67-0FE5F7CEFC9D}">
@@ -18085,8 +18438,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6661650" y="1816334"/>
-          <a:ext cx="3156395" cy="363410"/>
+          <a:off x="6684628" y="1774510"/>
+          <a:ext cx="3167897" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -18180,8 +18533,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6672294" y="1826978"/>
-        <a:ext cx="3135107" cy="342122"/>
+        <a:off x="6695311" y="1785193"/>
+        <a:ext cx="3146531" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{0C4A9E51-DEA5-4AC0-B8EC-F712BFE3BA51}">
@@ -18191,8 +18544,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9818046" y="1993994"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9852525" y="1952767"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18203,10 +18556,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18261,8 +18614,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9920939" y="1992623"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9955792" y="1951442"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{829A6295-4379-4C15-BF91-56D56B48CA13}">
@@ -18272,8 +18625,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10034662" y="1814559"/>
-          <a:ext cx="1801141" cy="366960"/>
+          <a:off x="10069930" y="1772728"/>
+          <a:ext cx="1807704" cy="368297"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -18359,8 +18712,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10045410" y="1825307"/>
-        <a:ext cx="1779645" cy="345464"/>
+        <a:off x="10080717" y="1783515"/>
+        <a:ext cx="1786130" cy="346723"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{15251D3B-5937-4D92-B910-59FBB0B78504}">
@@ -18370,8 +18723,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2595137">
-          <a:off x="4418296" y="2299676"/>
-          <a:ext cx="297408" cy="8089"/>
+          <a:off x="4433100" y="2259562"/>
+          <a:ext cx="298492" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18382,10 +18735,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="297408" y="4044"/>
+                <a:pt x="298492" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18440,8 +18793,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4559565" y="2296285"/>
-        <a:ext cx="14870" cy="14870"/>
+        <a:off x="4574883" y="2256210"/>
+        <a:ext cx="14924" cy="14924"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{55C8ECFC-533A-4D04-B170-164B29EE9A7D}">
@@ -18451,8 +18804,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4675308" y="2223909"/>
-          <a:ext cx="1769726" cy="363410"/>
+          <a:off x="4691048" y="2183570"/>
+          <a:ext cx="1776175" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -18522,8 +18875,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4685952" y="2234553"/>
-        <a:ext cx="1748438" cy="342122"/>
+        <a:off x="4701731" y="2194253"/>
+        <a:ext cx="1754809" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A63458DA-4732-44A8-AAAD-101471030A2E}">
@@ -18533,8 +18886,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6445035" y="2401570"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="6467223" y="2361827"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18545,10 +18898,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18603,8 +18956,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6547927" y="2400199"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="6570490" y="2360502"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{3CFC9EAC-3C3A-42EE-A809-37090C958CCC}">
@@ -18614,8 +18967,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6661650" y="2223909"/>
-          <a:ext cx="3156395" cy="363410"/>
+          <a:off x="6684628" y="2183570"/>
+          <a:ext cx="3167897" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -18693,8 +19046,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6672294" y="2234553"/>
-        <a:ext cx="3135107" cy="342122"/>
+        <a:off x="6695311" y="2194253"/>
+        <a:ext cx="3146531" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{2E1BE310-D0FB-4439-BC13-EF25298A0AC1}">
@@ -18704,8 +19057,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9818046" y="2401570"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9852525" y="2361827"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18716,10 +19069,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18774,8 +19127,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9920939" y="2400199"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9955792" y="2360502"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{05029C16-99B1-4993-B5A7-DFCE2EC4AF2D}">
@@ -18785,8 +19138,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10034662" y="2222134"/>
-          <a:ext cx="1801141" cy="366960"/>
+          <a:off x="10069930" y="2181789"/>
+          <a:ext cx="1807704" cy="368297"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -18856,8 +19209,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10045410" y="2232882"/>
-        <a:ext cx="1779645" cy="345464"/>
+        <a:off x="10080717" y="2192576"/>
+        <a:ext cx="1786130" cy="346723"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7B1A1F24-5790-42BE-9800-70C6BAC67F71}">
@@ -18867,8 +19220,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="4229399">
-          <a:off x="4242699" y="2503464"/>
-          <a:ext cx="648604" cy="8089"/>
+          <a:off x="4256862" y="2464092"/>
+          <a:ext cx="650967" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18879,10 +19232,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="648604" y="4044"/>
+                <a:pt x="650967" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18937,8 +19290,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4550785" y="2491293"/>
-        <a:ext cx="32430" cy="32430"/>
+        <a:off x="4566071" y="2451929"/>
+        <a:ext cx="32548" cy="32548"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{F9E7099E-D348-4A20-924E-7B36E8E1B00D}">
@@ -18948,8 +19301,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4675308" y="2631485"/>
-          <a:ext cx="1788209" cy="363410"/>
+          <a:off x="4691048" y="2592631"/>
+          <a:ext cx="1794725" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19019,8 +19372,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4685952" y="2642129"/>
-        <a:ext cx="1766921" cy="342122"/>
+        <a:off x="4701731" y="2603314"/>
+        <a:ext cx="1773359" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{69A95BFF-166E-4390-9963-14C8F025ADBA}">
@@ -19030,8 +19383,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6463518" y="2809145"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="6485773" y="2770888"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19042,10 +19395,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19100,8 +19453,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6566410" y="2807775"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="6589040" y="2769563"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{BBDCC5A6-74D1-4E37-848C-BF5D7C733A0C}">
@@ -19111,8 +19464,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6680133" y="2631485"/>
-          <a:ext cx="3156395" cy="363410"/>
+          <a:off x="6703178" y="2592631"/>
+          <a:ext cx="3167897" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19182,8 +19535,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6690777" y="2642129"/>
-        <a:ext cx="3135107" cy="342122"/>
+        <a:off x="6713861" y="2603314"/>
+        <a:ext cx="3146531" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E75A9ED0-3CF3-4FBB-B735-763677226156}">
@@ -19193,8 +19546,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9836529" y="2809145"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9871075" y="2770888"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19205,10 +19558,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19263,8 +19616,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9939421" y="2807775"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9974342" y="2769563"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D255C67C-B87B-4D25-A5F4-B2880DE74996}">
@@ -19274,8 +19627,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10053144" y="2629710"/>
-          <a:ext cx="1801141" cy="366960"/>
+          <a:off x="10088480" y="2590850"/>
+          <a:ext cx="1807704" cy="368297"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19369,8 +19722,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10063892" y="2640458"/>
-        <a:ext cx="1779645" cy="345464"/>
+        <a:off x="10099267" y="2601637"/>
+        <a:ext cx="1786130" cy="346723"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{19133C7D-D6FC-4086-9EFA-C8E67C09EF92}">
@@ -19380,8 +19733,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="4842573">
-          <a:off x="2277274" y="2758420"/>
-          <a:ext cx="1341777" cy="8089"/>
+          <a:off x="2284276" y="2719978"/>
+          <a:ext cx="1346666" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19392,10 +19745,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1341777" y="4044"/>
+                <a:pt x="1346666" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19450,8 +19803,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2914618" y="2728920"/>
-        <a:ext cx="67088" cy="67088"/>
+        <a:off x="2923942" y="2690422"/>
+        <a:ext cx="67333" cy="67333"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{3A58F96D-43A0-4E22-A03B-64FF8A7610E3}">
@@ -19461,8 +19814,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3056471" y="3244439"/>
-          <a:ext cx="1402222" cy="360228"/>
+          <a:off x="3066312" y="3207818"/>
+          <a:ext cx="1407331" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19532,8 +19885,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3067022" y="3254990"/>
-        <a:ext cx="1381120" cy="339126"/>
+        <a:off x="3076901" y="3218407"/>
+        <a:ext cx="1386153" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{BC1A1E23-E0C9-4175-8735-D110618B99B3}">
@@ -19543,8 +19896,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19004863">
-          <a:off x="4418296" y="3318615"/>
-          <a:ext cx="297408" cy="8089"/>
+          <a:off x="4433100" y="3282214"/>
+          <a:ext cx="298492" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19555,10 +19908,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="297408" y="4044"/>
+                <a:pt x="298492" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19613,8 +19966,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4559565" y="3315224"/>
-        <a:ext cx="14870" cy="14870"/>
+        <a:off x="4574883" y="3278862"/>
+        <a:ext cx="14924" cy="14924"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{5D691BA5-158A-4034-AEDA-B152BE077B27}">
@@ -19624,8 +19977,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4675308" y="3039060"/>
-          <a:ext cx="1769726" cy="363410"/>
+          <a:off x="4691048" y="3001692"/>
+          <a:ext cx="1776175" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19695,8 +20048,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4685952" y="3049704"/>
-        <a:ext cx="1748438" cy="342122"/>
+        <a:off x="4701731" y="3012375"/>
+        <a:ext cx="1754809" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{C26309FF-9296-40B3-913C-85759C2B07DC}">
@@ -19706,8 +20059,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6445035" y="3216721"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="6467223" y="3179948"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19718,10 +20071,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19776,8 +20129,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6547927" y="3215350"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="6570490" y="3178624"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A4750321-4845-43B0-945B-4B9E7C7A668E}">
@@ -19787,8 +20140,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6661650" y="3039060"/>
-          <a:ext cx="3156395" cy="363410"/>
+          <a:off x="6684628" y="3001692"/>
+          <a:ext cx="3167897" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19882,8 +20235,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6672294" y="3049704"/>
-        <a:ext cx="3135107" cy="342122"/>
+        <a:off x="6695311" y="3012375"/>
+        <a:ext cx="3146531" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{CCE9C4CE-7CF8-4820-8390-F3CBCCE81ED7}">
@@ -19893,8 +20246,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9818046" y="3216721"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9852525" y="3179948"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19905,10 +20258,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19963,8 +20316,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9920939" y="3215350"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9955792" y="3178624"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D954D938-3009-44F7-BB4F-D9E8AFB2B291}">
@@ -19974,8 +20327,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10034662" y="3037285"/>
-          <a:ext cx="1801141" cy="366960"/>
+          <a:off x="10069930" y="2999910"/>
+          <a:ext cx="1807704" cy="368297"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20045,8 +20398,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10045410" y="3048033"/>
-        <a:ext cx="1779645" cy="345464"/>
+        <a:off x="10080717" y="3010697"/>
+        <a:ext cx="1786130" cy="346723"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D01C8F64-85EC-45F5-B192-363D2A57FB6E}">
@@ -20056,8 +20409,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2595137">
-          <a:off x="4418296" y="3522403"/>
-          <a:ext cx="297408" cy="8089"/>
+          <a:off x="4433100" y="3486744"/>
+          <a:ext cx="298492" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20068,10 +20421,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="297408" y="4044"/>
+                <a:pt x="298492" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20126,8 +20479,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4559565" y="3519012"/>
-        <a:ext cx="14870" cy="14870"/>
+        <a:off x="4574883" y="3483392"/>
+        <a:ext cx="14924" cy="14924"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7832722B-5DD1-4AAD-819C-BC966C90EDAC}">
@@ -20137,8 +20490,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4675308" y="3446636"/>
-          <a:ext cx="1769726" cy="363410"/>
+          <a:off x="4691048" y="3410752"/>
+          <a:ext cx="1776175" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20208,8 +20561,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4685952" y="3457280"/>
-        <a:ext cx="1748438" cy="342122"/>
+        <a:off x="4701731" y="3421435"/>
+        <a:ext cx="1754809" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9B049FA9-70FB-4D7E-AD76-2BFCDB3B4195}">
@@ -20219,8 +20572,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6445035" y="3624296"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="6467223" y="3589009"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20231,10 +20584,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20289,8 +20642,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6547927" y="3622926"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="6570490" y="3587684"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B5153D0A-E9E7-482C-B1CC-838341F8F3D8}">
@@ -20300,8 +20653,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6661650" y="3446636"/>
-          <a:ext cx="3156395" cy="363410"/>
+          <a:off x="6684628" y="3410752"/>
+          <a:ext cx="3167897" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20387,8 +20740,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6672294" y="3457280"/>
-        <a:ext cx="3135107" cy="342122"/>
+        <a:off x="6695311" y="3421435"/>
+        <a:ext cx="3146531" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1118BB77-BCCA-46BE-8B0C-417EE0F19393}">
@@ -20398,8 +20751,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9818046" y="3624296"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9852525" y="3589009"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20410,10 +20763,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20468,8 +20821,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9920939" y="3622926"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9955792" y="3587684"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A1FE2FD1-D3B2-4F02-B33F-7EA3496A9D7D}">
@@ -20479,8 +20832,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10034662" y="3444861"/>
-          <a:ext cx="1801141" cy="366960"/>
+          <a:off x="10069930" y="3408971"/>
+          <a:ext cx="1807704" cy="368297"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20550,8 +20903,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10045410" y="3455609"/>
-        <a:ext cx="1779645" cy="345464"/>
+        <a:off x="10080717" y="3419758"/>
+        <a:ext cx="1786130" cy="346723"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{ACD64E2A-6A03-49D1-9C11-853B1D5FDA3F}">
@@ -20561,8 +20914,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="4880920">
-          <a:off x="572123" y="4231846"/>
-          <a:ext cx="1440061" cy="8089"/>
+          <a:off x="572912" y="4198773"/>
+          <a:ext cx="1445308" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20573,10 +20926,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1440061" y="4044"/>
+                <a:pt x="1445308" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20631,8 +20984,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1256152" y="4199889"/>
-        <a:ext cx="72003" cy="72003"/>
+        <a:off x="1259433" y="4166750"/>
+        <a:ext cx="72265" cy="72265"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4915DA81-5EFF-4A45-B117-A1C9369BA960}">
@@ -20642,8 +20995,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="1400462" y="4767614"/>
-          <a:ext cx="1432488" cy="360228"/>
+          <a:off x="1404269" y="4736544"/>
+          <a:ext cx="1437708" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20765,8 +21118,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1411013" y="4778165"/>
-        <a:ext cx="1411386" cy="339126"/>
+        <a:off x="1414858" y="4747133"/>
+        <a:ext cx="1416530" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A3777E34-F7A1-4ABC-99E9-9C9A9AB7B959}">
@@ -20776,8 +21129,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17225057">
-          <a:off x="2577781" y="4598311"/>
-          <a:ext cx="722633" cy="8089"/>
+          <a:off x="2585877" y="4566573"/>
+          <a:ext cx="725267" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20788,10 +21141,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="722633" y="4044"/>
+                <a:pt x="725267" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20846,8 +21199,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2921032" y="4584290"/>
-        <a:ext cx="36131" cy="36131"/>
+        <a:off x="2930379" y="4552551"/>
+        <a:ext cx="36263" cy="36263"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{23228D17-0E30-4278-86F1-009AEEE4B90D}">
@@ -20857,8 +21210,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3045245" y="4076868"/>
-          <a:ext cx="1402222" cy="360228"/>
+          <a:off x="3055045" y="4043280"/>
+          <a:ext cx="1407331" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20928,8 +21281,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3055796" y="4087419"/>
-        <a:ext cx="1381120" cy="339126"/>
+        <a:off x="3065634" y="4053869"/>
+        <a:ext cx="1386153" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A22E3146-1836-4A0C-A6D3-4503A76A9781}">
@@ -20939,8 +21292,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19004863">
-          <a:off x="4407070" y="4151044"/>
-          <a:ext cx="297408" cy="8089"/>
+          <a:off x="4421833" y="4117676"/>
+          <a:ext cx="298492" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20951,10 +21304,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="297408" y="4044"/>
+                <a:pt x="298492" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21009,8 +21362,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4548339" y="4147653"/>
-        <a:ext cx="14870" cy="14870"/>
+        <a:off x="4563616" y="4114324"/>
+        <a:ext cx="14924" cy="14924"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{06E3AC3D-2CA5-4C28-B4EE-08E1F5093575}">
@@ -21020,8 +21373,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4664082" y="3871489"/>
-          <a:ext cx="1769726" cy="363410"/>
+          <a:off x="4679781" y="3837154"/>
+          <a:ext cx="1776175" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21107,8 +21460,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4674726" y="3882133"/>
-        <a:ext cx="1748438" cy="342122"/>
+        <a:off x="4690464" y="3847837"/>
+        <a:ext cx="1754809" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{AB38F8C9-39F9-48F1-A4B9-359AD3B6C9E1}">
@@ -21118,8 +21471,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6433809" y="4049150"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="6455956" y="4015410"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21130,10 +21483,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21188,8 +21541,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6536701" y="4047779"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="6559223" y="4014086"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{94E3E4AC-563C-467A-AD10-294BF8A33BAF}">
@@ -21199,8 +21552,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6650424" y="3871489"/>
-          <a:ext cx="3156395" cy="363410"/>
+          <a:off x="6673361" y="3837154"/>
+          <a:ext cx="3167897" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21286,8 +21639,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6661068" y="3882133"/>
-        <a:ext cx="3135107" cy="342122"/>
+        <a:off x="6684044" y="3847837"/>
+        <a:ext cx="3146531" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{CE4A2E59-3DB6-4586-9EDA-16655120708B}">
@@ -21297,8 +21650,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9806820" y="4049150"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9841258" y="4015410"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21309,10 +21662,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21367,8 +21720,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9909712" y="4047779"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9944525" y="4014086"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{74F8E0C0-A1C2-4026-BDD1-211E4452BF84}">
@@ -21378,8 +21731,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10023436" y="3869714"/>
-          <a:ext cx="1801141" cy="366960"/>
+          <a:off x="10058663" y="3835372"/>
+          <a:ext cx="1807704" cy="368297"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21449,8 +21802,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10034184" y="3880462"/>
-        <a:ext cx="1779645" cy="345464"/>
+        <a:off x="10069450" y="3846159"/>
+        <a:ext cx="1786130" cy="346723"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{3776BE60-D86F-469E-9605-E0609281B4B9}">
@@ -21460,8 +21813,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2595137">
-          <a:off x="4407070" y="4354831"/>
-          <a:ext cx="297408" cy="8089"/>
+          <a:off x="4421833" y="4322206"/>
+          <a:ext cx="298492" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21472,10 +21825,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="297408" y="4044"/>
+                <a:pt x="298492" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21530,8 +21883,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4548339" y="4351441"/>
-        <a:ext cx="14870" cy="14870"/>
+        <a:off x="4563616" y="4318854"/>
+        <a:ext cx="14924" cy="14924"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{DC0F0790-8247-4EA1-A5BD-20B9C2810EA5}">
@@ -21541,8 +21894,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4664082" y="4279065"/>
-          <a:ext cx="1769726" cy="363410"/>
+          <a:off x="4679781" y="4246214"/>
+          <a:ext cx="1776175" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21612,8 +21965,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4674726" y="4289709"/>
-        <a:ext cx="1748438" cy="342122"/>
+        <a:off x="4690464" y="4256897"/>
+        <a:ext cx="1754809" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{82B78A4F-EF07-4DEA-A3EC-7BA9DD55DC45}">
@@ -21623,8 +21976,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6433809" y="4456725"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="6455956" y="4424471"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21635,10 +21988,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21693,8 +22046,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6536701" y="4455354"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="6559223" y="4423146"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4D82C0F8-05DA-476F-9FFD-EF5362E37ABC}">
@@ -21704,8 +22057,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6650424" y="4279065"/>
-          <a:ext cx="3156395" cy="363410"/>
+          <a:off x="6673361" y="4246214"/>
+          <a:ext cx="3167897" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21783,8 +22136,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6661068" y="4289709"/>
-        <a:ext cx="3135107" cy="342122"/>
+        <a:off x="6684044" y="4256897"/>
+        <a:ext cx="3146531" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6F09ED48-69E5-4359-AEF9-003C31CF3834}">
@@ -21794,8 +22147,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9806820" y="4456725"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9841258" y="4424471"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21806,10 +22159,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21864,8 +22217,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9909712" y="4455354"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9944525" y="4423146"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7F4C8494-F5DD-49F1-B7FE-320AAF64A334}">
@@ -21875,8 +22228,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10023436" y="4277290"/>
-          <a:ext cx="1801141" cy="366960"/>
+          <a:off x="10058663" y="4244433"/>
+          <a:ext cx="1807704" cy="368297"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21951,8 +22304,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10034184" y="4288038"/>
-        <a:ext cx="1779645" cy="345464"/>
+        <a:off x="10069450" y="4255220"/>
+        <a:ext cx="1786130" cy="346723"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E97A89EA-A088-4B36-94ED-03E39FF28C24}">
@@ -21962,8 +22315,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="1512707">
-          <a:off x="2821547" y="4994677"/>
-          <a:ext cx="239423" cy="8089"/>
+          <a:off x="2830532" y="4964383"/>
+          <a:ext cx="240295" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21974,10 +22327,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="239423" y="4044"/>
+                <a:pt x="240295" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22032,8 +22385,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2935273" y="4992736"/>
-        <a:ext cx="11971" cy="11971"/>
+        <a:off x="2944672" y="4962486"/>
+        <a:ext cx="12014" cy="12014"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1279AA60-C872-4597-B281-C6CC2E4A34C2}">
@@ -22043,8 +22396,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3049566" y="4869600"/>
-          <a:ext cx="1402222" cy="360228"/>
+          <a:off x="3059382" y="4838902"/>
+          <a:ext cx="1407331" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22114,8 +22467,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3060117" y="4880151"/>
-        <a:ext cx="1381120" cy="339126"/>
+        <a:off x="3069971" y="4849491"/>
+        <a:ext cx="1386153" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{255CD393-ED80-4D10-A68E-31ED59592E3B}">
@@ -22125,8 +22478,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19138242">
-          <a:off x="4417227" y="4953303"/>
-          <a:ext cx="281417" cy="8089"/>
+          <a:off x="4432026" y="4922858"/>
+          <a:ext cx="282442" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22137,10 +22490,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="281417" y="4044"/>
+                <a:pt x="282442" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22195,8 +22548,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4550900" y="4950312"/>
-        <a:ext cx="14070" cy="14070"/>
+        <a:off x="4566186" y="4919907"/>
+        <a:ext cx="14122" cy="14122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{2340676A-EBD4-4E22-BA9C-E56B6A62904C}">
@@ -22206,8 +22559,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4664082" y="4683274"/>
-          <a:ext cx="1769726" cy="363410"/>
+          <a:off x="4679781" y="4651897"/>
+          <a:ext cx="1776175" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22277,8 +22630,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4674726" y="4693918"/>
-        <a:ext cx="1748438" cy="342122"/>
+        <a:off x="4690464" y="4662580"/>
+        <a:ext cx="1754809" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{EB837690-03CF-4B39-A4B0-AFC71E15928A}">
@@ -22288,8 +22641,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="27806">
-          <a:off x="6433805" y="4861829"/>
-          <a:ext cx="220944" cy="8089"/>
+          <a:off x="6455952" y="4831051"/>
+          <a:ext cx="221749" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22300,10 +22653,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="220944" y="4044"/>
+                <a:pt x="221749" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22358,8 +22711,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6538754" y="4860350"/>
-        <a:ext cx="11047" cy="11047"/>
+        <a:off x="6561283" y="4829617"/>
+        <a:ext cx="11087" cy="11087"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6CD3FE0A-3BBE-455B-B381-72424654A1B0}">
@@ -22369,8 +22722,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6654746" y="4686652"/>
-          <a:ext cx="3155594" cy="360228"/>
+          <a:off x="6677698" y="4655287"/>
+          <a:ext cx="3167092" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22448,8 +22801,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6665297" y="4697203"/>
-        <a:ext cx="3134492" cy="339126"/>
+        <a:off x="6688287" y="4665876"/>
+        <a:ext cx="3145914" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B86CABA2-1933-4D02-A0D3-AA6DEA35BCA7}">
@@ -22459,8 +22812,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9810340" y="4862722"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9844791" y="4831947"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22471,10 +22824,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22529,8 +22882,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9913232" y="4861351"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9948058" y="4830623"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{920A36CD-D69B-4AB0-8DA2-4963F1111FE2}">
@@ -22540,8 +22893,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10026956" y="4686652"/>
-          <a:ext cx="1801141" cy="360228"/>
+          <a:off x="10062195" y="4655287"/>
+          <a:ext cx="1807704" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22611,8 +22964,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10037507" y="4697203"/>
-        <a:ext cx="1780039" cy="339126"/>
+        <a:off x="10072784" y="4665876"/>
+        <a:ext cx="1786526" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{EE30240B-4D3F-4585-94A4-7AD0CBEBACD0}">
@@ -22622,8 +22975,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2755727">
-          <a:off x="4405327" y="5155316"/>
-          <a:ext cx="305216" cy="8089"/>
+          <a:off x="4420083" y="5125607"/>
+          <a:ext cx="306328" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22634,10 +22987,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="305216" y="4044"/>
+                <a:pt x="306328" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22692,8 +23045,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4550305" y="5151730"/>
-        <a:ext cx="15260" cy="15260"/>
+        <a:off x="4565589" y="5122059"/>
+        <a:ext cx="15316" cy="15316"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9B0332A1-DFA5-4E72-89B6-8E8C50F667E1}">
@@ -22703,8 +23056,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4664082" y="5087300"/>
-          <a:ext cx="1769726" cy="363410"/>
+          <a:off x="4679781" y="5057395"/>
+          <a:ext cx="1776175" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22801,8 +23154,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4674726" y="5097944"/>
-        <a:ext cx="1748438" cy="342122"/>
+        <a:off x="4690464" y="5068078"/>
+        <a:ext cx="1754809" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4EF5B1E7-3D92-44D9-8E8A-E2A10FB649AC}">
@@ -22812,8 +23165,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="27806">
-          <a:off x="6433805" y="5265854"/>
-          <a:ext cx="220944" cy="8089"/>
+          <a:off x="6455952" y="5236548"/>
+          <a:ext cx="221749" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22824,10 +23177,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="220944" y="4044"/>
+                <a:pt x="221749" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22882,8 +23235,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6538754" y="5264375"/>
-        <a:ext cx="11047" cy="11047"/>
+        <a:off x="6561283" y="5235115"/>
+        <a:ext cx="11087" cy="11087"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9AC7A0EB-B59E-41D9-A589-CB90FBF4305E}">
@@ -22893,8 +23246,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6654746" y="5090678"/>
-          <a:ext cx="3155594" cy="360228"/>
+          <a:off x="6677698" y="5060785"/>
+          <a:ext cx="3167092" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22980,8 +23333,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6665297" y="5101229"/>
-        <a:ext cx="3134492" cy="339126"/>
+        <a:off x="6688287" y="5071374"/>
+        <a:ext cx="3145914" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{2F5A23ED-2B4B-4307-BAD6-D126CED4ED45}">
@@ -22991,8 +23344,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9810340" y="5266748"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9844791" y="5237445"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23003,10 +23356,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23061,8 +23414,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9913232" y="5265377"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9948058" y="5236121"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{C9CCA1DF-737F-40B9-8662-1EBAE874B88C}">
@@ -23072,8 +23425,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10026956" y="5090678"/>
-          <a:ext cx="1801141" cy="360228"/>
+          <a:off x="10062195" y="5060785"/>
+          <a:ext cx="1807704" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23143,8 +23496,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10037507" y="5101229"/>
-        <a:ext cx="1780039" cy="339126"/>
+        <a:off x="10072784" y="5071374"/>
+        <a:ext cx="1786526" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{06804470-2E4E-45CC-AD07-54CD8F165228}">
@@ -23154,8 +23507,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="4379331">
-          <a:off x="2571049" y="5297697"/>
-          <a:ext cx="740419" cy="8089"/>
+          <a:off x="2579121" y="5268507"/>
+          <a:ext cx="743117" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23166,10 +23519,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="740419" y="4044"/>
+                <a:pt x="743117" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23224,8 +23577,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2922748" y="5283231"/>
-        <a:ext cx="37020" cy="37020"/>
+        <a:off x="2932101" y="5254039"/>
+        <a:ext cx="37155" cy="37155"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D9D1FF4E-B146-4A17-8BAD-E6A8247731B1}">
@@ -23235,8 +23588,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3049566" y="5475639"/>
-          <a:ext cx="1402227" cy="360228"/>
+          <a:off x="3059382" y="5447149"/>
+          <a:ext cx="1407337" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23322,8 +23675,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3060117" y="5486190"/>
-        <a:ext cx="1381125" cy="339126"/>
+        <a:off x="3069971" y="5457738"/>
+        <a:ext cx="1386159" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{458C594D-E94A-4416-A27A-8211BD0C18EB}">
@@ -23333,8 +23686,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4451794" y="5651709"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="4466719" y="5623809"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23345,10 +23698,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23403,8 +23756,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4554686" y="5650338"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="4569986" y="5622484"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E6BB35B6-4DC7-42B5-A329-D93F595605BC}">
@@ -23414,8 +23767,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4668409" y="5474048"/>
-          <a:ext cx="1759258" cy="363410"/>
+          <a:off x="4684124" y="5445552"/>
+          <a:ext cx="1765668" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23501,8 +23854,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4679053" y="5484692"/>
-        <a:ext cx="1737970" cy="342122"/>
+        <a:off x="4694807" y="5456235"/>
+        <a:ext cx="1744302" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{F3CE9778-2DAD-459C-A92D-C581128238EF}">
@@ -23512,8 +23865,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6427668" y="5651709"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="6449793" y="5623809"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23524,10 +23877,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23582,8 +23935,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6530560" y="5650338"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="6553060" y="5622484"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A62201D7-F2CC-41E5-BB68-F68B79E1464B}">
@@ -23593,8 +23946,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6644283" y="5475639"/>
-          <a:ext cx="3155594" cy="360228"/>
+          <a:off x="6667197" y="5447149"/>
+          <a:ext cx="3167092" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23664,8 +24017,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6654834" y="5486190"/>
-        <a:ext cx="3134492" cy="339126"/>
+        <a:off x="6677786" y="5457738"/>
+        <a:ext cx="3145914" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{46794C65-61A0-4B52-A42E-5CC9D77E3723}">
@@ -23675,8 +24028,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9799878" y="5651709"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9834290" y="5623809"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23687,10 +24040,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23745,8 +24098,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9902770" y="5650338"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9937557" y="5622484"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{C61F938B-5A64-4BF7-B003-81E0909084B1}">
@@ -23756,8 +24109,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10016493" y="5475639"/>
-          <a:ext cx="1801141" cy="360228"/>
+          <a:off x="10051695" y="5447149"/>
+          <a:ext cx="1807704" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23827,8 +24180,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10027044" y="5486190"/>
-        <a:ext cx="1780039" cy="339126"/>
+        <a:off x="10062284" y="5457738"/>
+        <a:ext cx="1786526" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
   </dsp:spTree>
@@ -26974,7 +27327,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:C135"/>
+  <dimension ref="A1:C134"/>
   <sheetFormatPr defaultRowHeight="17" outlineLevelRow="2" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16.83203125" style="20" customWidth="1"/>
@@ -27260,7 +27613,7 @@
     <row r="59" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
     <row r="60" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A60" s="25" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="61" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
@@ -27408,69 +27761,69 @@
         <v>121</v>
       </c>
     </row>
-    <row r="94" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A94" s="20" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="95" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A95" s="20" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="96" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A96" s="20" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="97" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="98" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="98" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A98" s="22" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="99" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="100" spans="1:3" ht="26" collapsed="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="100" spans="1:3" ht="26" x14ac:dyDescent="0.45">
       <c r="A100" s="21" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="101" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A101" s="20" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="102" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A102" s="20" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="103" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="104" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="104" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A104" s="22" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="105" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="106" spans="1:3" ht="26" collapsed="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="106" spans="1:3" ht="26" x14ac:dyDescent="0.45">
       <c r="A106" s="21" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="107" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="108" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="108" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A108" s="20" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="109" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="110" spans="1:3" ht="21" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="110" spans="1:3" ht="21" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A110" s="23" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="111" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="112" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="112" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A112" s="26" t="s">
         <v>132</v>
       </c>
@@ -27481,7 +27834,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="34" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:3" ht="34" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A113" s="27" t="s">
         <v>135</v>
       </c>
@@ -27492,7 +27845,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="51" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:3" ht="51" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A114" s="27" t="s">
         <v>138</v>
       </c>
@@ -27503,51 +27856,51 @@
         <v>140</v>
       </c>
     </row>
-    <row r="115" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="116" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="116" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A116" s="20" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="117" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="118" spans="1:3" ht="21" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="118" spans="1:3" ht="21" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A118" s="23" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="119" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A119" s="20" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="120" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A120" s="20" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="121" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A121" s="20" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="122" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A122" s="20" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="123" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="124" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="124" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A124" s="22" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="125" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="126" spans="1:3" ht="21" collapsed="1" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="126" spans="1:3" ht="21" x14ac:dyDescent="0.45">
       <c r="A126" s="23" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="127" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A127" s="30" t="s">
         <v>148</v>
       </c>
@@ -27555,7 +27908,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="34" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:3" ht="34" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A128" s="31" t="s">
         <v>150</v>
       </c>
@@ -27563,7 +27916,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="129" spans="1:2" ht="51" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:2" ht="51" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A129" s="31" t="s">
         <v>152</v>
       </c>
@@ -27571,7 +27924,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="130" spans="1:2" ht="34" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:2" ht="34" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A130" s="31" t="s">
         <v>154</v>
       </c>
@@ -27579,7 +27932,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="131" spans="1:2" ht="51" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:2" ht="51" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A131" s="31" t="s">
         <v>156</v>
       </c>
@@ -27587,7 +27940,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="132" spans="1:2" ht="34" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:2" ht="34" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A132" s="31" t="s">
         <v>158</v>
       </c>
@@ -27595,7 +27948,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="133" spans="1:2" ht="34" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:2" ht="34" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A133" s="31" t="s">
         <v>160</v>
       </c>
@@ -27603,7 +27956,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="134" spans="1:2" ht="34" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:2" ht="34" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A134" s="31" t="s">
         <v>162</v>
       </c>
@@ -27611,7 +27964,6 @@
         <v>163</v>
       </c>
     </row>
-    <row r="135" spans="1:2" collapsed="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -27619,6 +27971,31 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA7446D1-A9E6-4F8D-B799-CB90AD03762A}">
+  <dimension ref="A1:C1"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="2" max="2" width="60.08203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A1" s="62" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1" s="59" t="s">
+        <v>422</v>
+      </c>
+      <c r="C1" s="59" t="s">
+        <v>423</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03EAFDCE-DB4E-46B3-9A49-EC7FC892A3F4}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
@@ -27707,7 +28084,7 @@
         <v>46275</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
@@ -27718,7 +28095,9 @@
       <c r="C6" s="35">
         <v>46275</v>
       </c>
-      <c r="D6" s="33"/>
+      <c r="D6" s="33" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" s="33" t="s">
@@ -27749,7 +28128,7 @@
         <v>46276</v>
       </c>
       <c r="D9" s="33" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
@@ -27816,7 +28195,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A2" s="64" t="s">
+      <c r="A2" s="68" t="s">
         <v>18</v>
       </c>
       <c r="B2" s="7" t="s">
@@ -27833,7 +28212,7 @@
       <c r="G2" s="10"/>
     </row>
     <row r="3" spans="1:7" ht="64" x14ac:dyDescent="0.45">
-      <c r="A3" s="65"/>
+      <c r="A3" s="69"/>
       <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
@@ -27850,7 +28229,7 @@
       <c r="G3" s="11"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A4" s="65"/>
+      <c r="A4" s="69"/>
       <c r="B4" s="4" t="s">
         <v>184</v>
       </c>
@@ -27865,7 +28244,7 @@
       <c r="G4" s="11"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A5" s="65"/>
+      <c r="A5" s="69"/>
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
@@ -27880,7 +28259,7 @@
       <c r="G5" s="11"/>
     </row>
     <row r="6" spans="1:7" ht="48" x14ac:dyDescent="0.45">
-      <c r="A6" s="65"/>
+      <c r="A6" s="69"/>
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
@@ -27899,7 +28278,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="66"/>
+      <c r="A7" s="70"/>
       <c r="B7" s="13" t="s">
         <v>15</v>
       </c>
@@ -27916,7 +28295,7 @@
       <c r="G7" s="15"/>
     </row>
     <row r="8" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="67" t="s">
+      <c r="A8" s="71" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="7" t="s">
@@ -27937,7 +28316,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A9" s="68"/>
+      <c r="A9" s="72"/>
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -27954,7 +28333,7 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A10" s="68"/>
+      <c r="A10" s="72"/>
       <c r="B10" s="4" t="s">
         <v>4</v>
       </c>
@@ -27971,7 +28350,7 @@
       <c r="G10" s="11"/>
     </row>
     <row r="11" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="68"/>
+      <c r="A11" s="72"/>
       <c r="B11" s="4" t="s">
         <v>7</v>
       </c>
@@ -27986,7 +28365,7 @@
       <c r="G11" s="11"/>
     </row>
     <row r="12" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="69"/>
+      <c r="A12" s="73"/>
       <c r="B12" s="16" t="s">
         <v>8</v>
       </c>
@@ -28003,7 +28382,7 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A13" s="70" t="s">
+      <c r="A13" s="74" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="7" t="s">
@@ -28024,7 +28403,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="64.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="71"/>
+      <c r="A14" s="75"/>
       <c r="B14" s="4" t="s">
         <v>10</v>
       </c>
@@ -28041,7 +28420,7 @@
       <c r="G14" s="11"/>
     </row>
     <row r="15" spans="1:7" ht="64" x14ac:dyDescent="0.45">
-      <c r="A15" s="71"/>
+      <c r="A15" s="75"/>
       <c r="B15" s="4" t="s">
         <v>218</v>
       </c>
@@ -28062,7 +28441,7 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A16" s="72"/>
+      <c r="A16" s="76"/>
       <c r="B16" s="16" t="s">
         <v>11</v>
       </c>
@@ -28209,14 +28588,14 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A5" s="80" t="s">
+      <c r="A5" s="84" t="s">
         <v>273</v>
       </c>
-      <c r="B5" s="80"/>
-      <c r="C5" s="80"/>
+      <c r="B5" s="84"/>
+      <c r="C5" s="84"/>
     </row>
     <row r="6" spans="1:4" ht="32" x14ac:dyDescent="0.45">
-      <c r="A6" s="82" t="s">
+      <c r="A6" s="86" t="s">
         <v>204</v>
       </c>
       <c r="B6" s="47" t="s">
@@ -28227,7 +28606,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="32" x14ac:dyDescent="0.45">
-      <c r="A7" s="83"/>
+      <c r="A7" s="87"/>
       <c r="B7" s="47" t="s">
         <v>292</v>
       </c>
@@ -28236,7 +28615,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" ht="32" x14ac:dyDescent="0.45">
-      <c r="A8" s="83"/>
+      <c r="A8" s="87"/>
       <c r="B8" s="47" t="s">
         <v>295</v>
       </c>
@@ -28245,7 +28624,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A9" s="83"/>
+      <c r="A9" s="87"/>
       <c r="B9" s="47" t="s">
         <v>303</v>
       </c>
@@ -28254,7 +28633,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A10" s="84"/>
+      <c r="A10" s="88"/>
       <c r="B10" s="47" t="s">
         <v>297</v>
       </c>
@@ -28277,18 +28656,18 @@
       <c r="C12" s="49"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A13" s="74" t="s">
+      <c r="A13" s="78" t="s">
         <v>304</v>
       </c>
-      <c r="B13" s="75"/>
-      <c r="C13" s="76"/>
+      <c r="B13" s="79"/>
+      <c r="C13" s="80"/>
     </row>
     <row r="14" spans="1:4" ht="52" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="85" t="s">
+      <c r="A14" s="89" t="s">
         <v>230</v>
       </c>
-      <c r="B14" s="86"/>
-      <c r="C14" s="87"/>
+      <c r="B14" s="90"/>
+      <c r="C14" s="91"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="49"/>
@@ -28296,112 +28675,112 @@
       <c r="D19" s="49"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A31" s="80" t="s">
+      <c r="A31" s="84" t="s">
         <v>274</v>
       </c>
-      <c r="B31" s="80"/>
-      <c r="C31" s="80"/>
+      <c r="B31" s="84"/>
+      <c r="C31" s="84"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A32" s="77" t="s">
-        <v>319</v>
-      </c>
-      <c r="B32" s="78"/>
-      <c r="C32" s="79"/>
+      <c r="A32" s="81" t="s">
+        <v>318</v>
+      </c>
+      <c r="B32" s="82"/>
+      <c r="C32" s="83"/>
     </row>
     <row r="33" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="73" t="s">
+      <c r="A33" s="77" t="s">
         <v>231</v>
       </c>
       <c r="B33" s="50" t="s">
         <v>208</v>
       </c>
-      <c r="C33" s="81" t="s">
+      <c r="C33" s="85" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A34" s="73"/>
+      <c r="A34" s="77"/>
       <c r="B34" s="50" t="s">
         <v>209</v>
       </c>
-      <c r="C34" s="81"/>
+      <c r="C34" s="85"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A35" s="73"/>
+      <c r="A35" s="77"/>
       <c r="B35" s="50" t="s">
         <v>210</v>
       </c>
-      <c r="C35" s="81"/>
+      <c r="C35" s="85"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A36" s="73"/>
+      <c r="A36" s="77"/>
       <c r="B36" s="50" t="s">
         <v>211</v>
       </c>
-      <c r="C36" s="81"/>
+      <c r="C36" s="85"/>
     </row>
     <row r="37" spans="1:5" ht="32" x14ac:dyDescent="0.45">
-      <c r="A37" s="73"/>
+      <c r="A37" s="77"/>
       <c r="B37" s="48" t="s">
         <v>212</v>
       </c>
-      <c r="C37" s="81"/>
+      <c r="C37" s="85"/>
     </row>
     <row r="38" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="73" t="s">
+      <c r="A38" s="77" t="s">
         <v>232</v>
       </c>
       <c r="B38" s="50" t="s">
         <v>213</v>
       </c>
-      <c r="C38" s="81" t="s">
+      <c r="C38" s="85" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A39" s="73"/>
+      <c r="A39" s="77"/>
       <c r="B39" s="50" t="s">
         <v>214</v>
       </c>
-      <c r="C39" s="81"/>
+      <c r="C39" s="85"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A40" s="73"/>
+      <c r="A40" s="77"/>
       <c r="B40" s="50" t="s">
         <v>215</v>
       </c>
-      <c r="C40" s="81"/>
+      <c r="C40" s="85"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A42" s="74" t="s">
+      <c r="A42" s="78" t="s">
         <v>272</v>
       </c>
-      <c r="B42" s="75"/>
-      <c r="C42" s="76"/>
+      <c r="B42" s="79"/>
+      <c r="C42" s="80"/>
     </row>
     <row r="43" spans="1:5" ht="53" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A43" s="73" t="s">
+      <c r="A43" s="77" t="s">
         <v>217</v>
       </c>
-      <c r="B43" s="73"/>
-      <c r="C43" s="73"/>
+      <c r="B43" s="77"/>
+      <c r="C43" s="77"/>
     </row>
     <row r="44" spans="1:5" ht="50.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A44" s="73" t="s">
-        <v>318</v>
-      </c>
-      <c r="B44" s="73"/>
-      <c r="C44" s="73"/>
+      <c r="A44" s="77" t="s">
+        <v>317</v>
+      </c>
+      <c r="B44" s="77"/>
+      <c r="C44" s="77"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A46" s="80" t="s">
+      <c r="A46" s="84" t="s">
         <v>271</v>
       </c>
-      <c r="B46" s="80"/>
-      <c r="C46" s="80"/>
-      <c r="D46" s="80"/>
-      <c r="E46" s="80"/>
+      <c r="B46" s="84"/>
+      <c r="C46" s="84"/>
+      <c r="D46" s="84"/>
+      <c r="E46" s="84"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" s="44" t="s">
@@ -28587,11 +28966,11 @@
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A59" s="89" t="s">
+      <c r="A59" s="93" t="s">
         <v>275</v>
       </c>
-      <c r="B59" s="90"/>
-      <c r="C59" s="91"/>
+      <c r="B59" s="94"/>
+      <c r="C59" s="95"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" s="53" t="s">
@@ -28649,84 +29028,84 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A66" s="80" t="s">
+      <c r="A66" s="84" t="s">
         <v>291</v>
       </c>
-      <c r="B66" s="80"/>
-      <c r="C66" s="80"/>
-      <c r="D66" s="80"/>
+      <c r="B66" s="84"/>
+      <c r="C66" s="84"/>
+      <c r="D66" s="84"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A67" s="88" t="s">
+      <c r="A67" s="92" t="s">
         <v>262</v>
       </c>
-      <c r="B67" s="88"/>
-      <c r="C67" s="88"/>
-      <c r="D67" s="88"/>
+      <c r="B67" s="92"/>
+      <c r="C67" s="92"/>
+      <c r="D67" s="92"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A68" s="88" t="s">
+      <c r="A68" s="92" t="s">
         <v>263</v>
       </c>
-      <c r="B68" s="88"/>
-      <c r="C68" s="88"/>
-      <c r="D68" s="88"/>
+      <c r="B68" s="92"/>
+      <c r="C68" s="92"/>
+      <c r="D68" s="92"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A69" s="88" t="s">
+      <c r="A69" s="92" t="s">
         <v>264</v>
       </c>
-      <c r="B69" s="88"/>
-      <c r="C69" s="88"/>
-      <c r="D69" s="88"/>
+      <c r="B69" s="92"/>
+      <c r="C69" s="92"/>
+      <c r="D69" s="92"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A70" s="88" t="s">
+      <c r="A70" s="92" t="s">
         <v>265</v>
       </c>
-      <c r="B70" s="88"/>
-      <c r="C70" s="88"/>
-      <c r="D70" s="88"/>
+      <c r="B70" s="92"/>
+      <c r="C70" s="92"/>
+      <c r="D70" s="92"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A71" s="88" t="s">
+      <c r="A71" s="92" t="s">
         <v>266</v>
       </c>
-      <c r="B71" s="88"/>
-      <c r="C71" s="88"/>
-      <c r="D71" s="88"/>
+      <c r="B71" s="92"/>
+      <c r="C71" s="92"/>
+      <c r="D71" s="92"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A72" s="88" t="s">
+      <c r="A72" s="92" t="s">
         <v>267</v>
       </c>
-      <c r="B72" s="88"/>
-      <c r="C72" s="88"/>
-      <c r="D72" s="88"/>
+      <c r="B72" s="92"/>
+      <c r="C72" s="92"/>
+      <c r="D72" s="92"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A73" s="88" t="s">
+      <c r="A73" s="92" t="s">
         <v>268</v>
       </c>
-      <c r="B73" s="88"/>
-      <c r="C73" s="88"/>
-      <c r="D73" s="88"/>
+      <c r="B73" s="92"/>
+      <c r="C73" s="92"/>
+      <c r="D73" s="92"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A74" s="88" t="s">
+      <c r="A74" s="92" t="s">
         <v>269</v>
       </c>
-      <c r="B74" s="88"/>
-      <c r="C74" s="88"/>
-      <c r="D74" s="88"/>
+      <c r="B74" s="92"/>
+      <c r="C74" s="92"/>
+      <c r="D74" s="92"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A75" s="88" t="s">
+      <c r="A75" s="92" t="s">
         <v>270</v>
       </c>
-      <c r="B75" s="88"/>
-      <c r="C75" s="88"/>
-      <c r="D75" s="88"/>
+      <c r="B75" s="92"/>
+      <c r="C75" s="92"/>
+      <c r="D75" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="25">
@@ -28778,295 +29157,392 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A96403AB-5292-4AE8-910D-5C858934A272}">
-  <dimension ref="A1:D29"/>
+  <sheetPr>
+    <tabColor theme="9" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="7.08203125" style="20" customWidth="1"/>
-    <col min="2" max="2" width="54.33203125" customWidth="1"/>
-    <col min="3" max="3" width="32.1640625" customWidth="1"/>
-    <col min="4" max="4" width="48.1640625" customWidth="1"/>
+    <col min="1" max="1" width="5.33203125" style="20" customWidth="1"/>
+    <col min="2" max="2" width="56.25" customWidth="1"/>
+    <col min="3" max="3" width="34.58203125" customWidth="1"/>
+    <col min="4" max="4" width="52.6640625" customWidth="1"/>
+    <col min="5" max="5" width="20.9140625" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="76.25" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="0" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="54.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A1" s="92" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A1" s="96" t="s">
+        <v>336</v>
+      </c>
+      <c r="B1" s="97"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A2" s="60" t="s">
+        <v>337</v>
+      </c>
+      <c r="B2" s="38" t="s">
         <v>338</v>
       </c>
-      <c r="B1" s="93"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A2" s="61" t="s">
+    <row r="3" spans="1:8" ht="34" x14ac:dyDescent="0.45">
+      <c r="A3" s="61">
+        <v>1</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A4" s="61">
+        <v>2</v>
+      </c>
+      <c r="B4" s="58" t="s">
         <v>339</v>
       </c>
-      <c r="B2" s="38" t="s">
-        <v>340</v>
-      </c>
     </row>
-    <row r="3" spans="1:4" ht="34" x14ac:dyDescent="0.45">
-      <c r="A3" s="62">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A5" s="61">
+        <v>3</v>
+      </c>
+      <c r="B5" s="58" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A7" s="60" t="s">
+        <v>337</v>
+      </c>
+      <c r="B7" s="59" t="s">
+        <v>335</v>
+      </c>
+      <c r="C7" s="59" t="s">
+        <v>334</v>
+      </c>
+      <c r="D7" s="59" t="s">
+        <v>342</v>
+      </c>
+      <c r="E7" s="59" t="s">
+        <v>370</v>
+      </c>
+      <c r="F7" s="59" t="s">
+        <v>371</v>
+      </c>
+      <c r="H7" s="59" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A8" s="61">
         <v>1</v>
       </c>
-      <c r="B3" s="18" t="s">
-        <v>342</v>
+      <c r="B8" s="58" t="s">
+        <v>321</v>
+      </c>
+      <c r="C8" s="63" t="s">
+        <v>341</v>
+      </c>
+      <c r="D8" s="65"/>
+      <c r="E8" s="65"/>
+      <c r="F8" s="65"/>
+      <c r="H8" s="18" t="s">
+        <v>357</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A4" s="62">
+    <row r="9" spans="1:8" ht="238" x14ac:dyDescent="0.45">
+      <c r="A9" s="61">
         <v>2</v>
       </c>
-      <c r="B4" s="59" t="s">
+      <c r="B9" s="58" t="s">
+        <v>322</v>
+      </c>
+      <c r="C9" s="58" t="s">
+        <v>343</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>366</v>
+      </c>
+      <c r="E9" s="58" t="s">
+        <v>373</v>
+      </c>
+      <c r="F9" s="18" t="s">
+        <v>375</v>
+      </c>
+      <c r="H9" s="58" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A10" s="61">
+        <v>3</v>
+      </c>
+      <c r="B10" s="58" t="s">
+        <v>323</v>
+      </c>
+      <c r="C10" s="63" t="s">
         <v>341</v>
       </c>
+      <c r="D10" s="65"/>
+      <c r="E10" s="65"/>
+      <c r="F10" s="65"/>
+      <c r="H10" s="58" t="s">
+        <v>358</v>
+      </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A5" s="62">
-        <v>3</v>
-      </c>
-      <c r="B5" s="59" t="s">
+    <row r="11" spans="1:8" ht="102" x14ac:dyDescent="0.45">
+      <c r="A11" s="61">
+        <v>4</v>
+      </c>
+      <c r="B11" s="58" t="s">
+        <v>324</v>
+      </c>
+      <c r="C11" s="58" t="s">
+        <v>344</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>367</v>
+      </c>
+      <c r="E11" s="58" t="s">
+        <v>373</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>374</v>
+      </c>
+      <c r="H11" s="58" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="68" x14ac:dyDescent="0.45">
+      <c r="A12" s="61">
+        <v>5</v>
+      </c>
+      <c r="B12" s="58" t="s">
+        <v>325</v>
+      </c>
+      <c r="C12" s="58" t="s">
+        <v>345</v>
+      </c>
+      <c r="D12" s="18" t="s">
         <v>368</v>
       </c>
+      <c r="E12" s="58" t="s">
+        <v>372</v>
+      </c>
+      <c r="F12" s="18" t="s">
+        <v>385</v>
+      </c>
+      <c r="H12" s="58" t="s">
+        <v>360</v>
+      </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A7" s="61" t="s">
-        <v>339</v>
-      </c>
-      <c r="B7" s="60" t="s">
-        <v>337</v>
-      </c>
-      <c r="C7" s="60" t="s">
-        <v>336</v>
-      </c>
-      <c r="D7" s="60" t="s">
-        <v>344</v>
+    <row r="13" spans="1:8" ht="68" x14ac:dyDescent="0.45">
+      <c r="A13" s="61">
+        <v>6</v>
+      </c>
+      <c r="B13" s="58" t="s">
+        <v>326</v>
+      </c>
+      <c r="C13" s="58" t="s">
+        <v>346</v>
+      </c>
+      <c r="D13" s="18" t="s">
+        <v>349</v>
+      </c>
+      <c r="E13" s="58" t="s">
+        <v>372</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>376</v>
+      </c>
+      <c r="H13" s="58" t="s">
+        <v>361</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A8" s="62">
-        <v>1</v>
-      </c>
-      <c r="B8" s="58" t="s">
-        <v>322</v>
-      </c>
-      <c r="C8" s="59" t="s">
-        <v>343</v>
-      </c>
-      <c r="D8" s="59"/>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A14" s="61">
+        <v>7</v>
+      </c>
+      <c r="B14" s="58" t="s">
+        <v>327</v>
+      </c>
+      <c r="C14" s="63" t="s">
+        <v>341</v>
+      </c>
+      <c r="D14" s="65"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="65"/>
+      <c r="H14" s="58" t="s">
+        <v>362</v>
+      </c>
     </row>
-    <row r="9" spans="1:4" ht="34" x14ac:dyDescent="0.45">
-      <c r="A9" s="62">
-        <v>2</v>
-      </c>
-      <c r="B9" s="59" t="s">
-        <v>323</v>
-      </c>
-      <c r="C9" s="59" t="s">
-        <v>345</v>
-      </c>
-      <c r="D9" s="18" t="s">
-        <v>369</v>
+    <row r="15" spans="1:8" ht="136" x14ac:dyDescent="0.45">
+      <c r="A15" s="61">
+        <v>8</v>
+      </c>
+      <c r="B15" s="58" t="s">
+        <v>328</v>
+      </c>
+      <c r="C15" s="58" t="s">
+        <v>347</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>350</v>
+      </c>
+      <c r="E15" s="58" t="s">
+        <v>389</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>388</v>
+      </c>
+      <c r="H15" s="58" t="s">
+        <v>363</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A10" s="62">
-        <v>3</v>
-      </c>
-      <c r="B10" s="58" t="s">
-        <v>324</v>
-      </c>
-      <c r="C10" s="59" t="s">
-        <v>343</v>
-      </c>
-      <c r="D10" s="59"/>
+    <row r="16" spans="1:8" ht="187" x14ac:dyDescent="0.45">
+      <c r="A16" s="61">
+        <v>9</v>
+      </c>
+      <c r="B16" s="58" t="s">
+        <v>329</v>
+      </c>
+      <c r="C16" s="58" t="s">
+        <v>347</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>351</v>
+      </c>
+      <c r="E16" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="F16" s="18" t="s">
+        <v>387</v>
+      </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A11" s="62">
-        <v>4</v>
-      </c>
-      <c r="B11" s="59" t="s">
-        <v>325</v>
-      </c>
-      <c r="C11" s="59" t="s">
+    <row r="17" spans="1:6" ht="51" x14ac:dyDescent="0.45">
+      <c r="A17" s="61">
+        <v>10</v>
+      </c>
+      <c r="B17" s="58" t="s">
+        <v>330</v>
+      </c>
+      <c r="C17" s="58" t="s">
+        <v>347</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>352</v>
+      </c>
+      <c r="E17" s="58" t="s">
+        <v>372</v>
+      </c>
+      <c r="F17" s="18" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="68" x14ac:dyDescent="0.45">
+      <c r="A18" s="61">
+        <v>11</v>
+      </c>
+      <c r="B18" s="58" t="s">
+        <v>331</v>
+      </c>
+      <c r="C18" s="18" t="s">
+        <v>364</v>
+      </c>
+      <c r="D18" s="18" t="s">
+        <v>353</v>
+      </c>
+      <c r="E18" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="F18" s="18" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="68" x14ac:dyDescent="0.45">
+      <c r="A19" s="61">
+        <v>12</v>
+      </c>
+      <c r="B19" s="58" t="s">
+        <v>378</v>
+      </c>
+      <c r="C19" s="58" t="s">
+        <v>348</v>
+      </c>
+      <c r="D19" s="58" t="s">
+        <v>381</v>
+      </c>
+      <c r="E19" s="58" t="s">
+        <v>382</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="68" x14ac:dyDescent="0.45">
+      <c r="A20" s="61">
+        <v>13</v>
+      </c>
+      <c r="B20" s="58" t="s">
+        <v>333</v>
+      </c>
+      <c r="C20" s="58" t="s">
         <v>346</v>
       </c>
-      <c r="D11" s="18" t="s">
-        <v>370</v>
+      <c r="D20" s="58" t="s">
+        <v>354</v>
+      </c>
+      <c r="E20" s="58" t="s">
+        <v>372</v>
+      </c>
+      <c r="F20" s="18" t="s">
+        <v>383</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="34" x14ac:dyDescent="0.45">
-      <c r="A12" s="62">
-        <v>5</v>
-      </c>
-      <c r="B12" s="59" t="s">
-        <v>326</v>
-      </c>
-      <c r="C12" s="59" t="s">
-        <v>347</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>371</v>
+    <row r="21" spans="1:6" ht="85" x14ac:dyDescent="0.45">
+      <c r="A21" s="61">
+        <v>14</v>
+      </c>
+      <c r="B21" s="58" t="s">
+        <v>332</v>
+      </c>
+      <c r="C21" s="58" t="s">
+        <v>348</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>355</v>
+      </c>
+      <c r="E21" s="58" t="s">
+        <v>379</v>
+      </c>
+      <c r="F21" s="64" t="s">
+        <v>384</v>
       </c>
     </row>
-    <row r="13" spans="1:4" ht="51" x14ac:dyDescent="0.45">
-      <c r="A13" s="62">
-        <v>6</v>
-      </c>
-      <c r="B13" s="59" t="s">
-        <v>327</v>
-      </c>
-      <c r="C13" s="59" t="s">
-        <v>348</v>
-      </c>
-      <c r="D13" s="18" t="s">
-        <v>351</v>
+    <row r="22" spans="1:6" ht="170" x14ac:dyDescent="0.45">
+      <c r="A22" s="61" t="s">
+        <v>390</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>394</v>
+      </c>
+      <c r="C22" s="58" t="s">
+        <v>391</v>
+      </c>
+      <c r="D22" s="18" t="s">
+        <v>392</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>393</v>
+      </c>
+      <c r="F22" s="18" t="s">
+        <v>395</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A14" s="62">
-        <v>7</v>
-      </c>
-      <c r="B14" s="58" t="s">
-        <v>328</v>
-      </c>
-      <c r="C14" s="59" t="s">
-        <v>343</v>
-      </c>
-      <c r="D14" s="59"/>
-    </row>
-    <row r="15" spans="1:4" ht="34" x14ac:dyDescent="0.45">
-      <c r="A15" s="62">
-        <v>8</v>
-      </c>
-      <c r="B15" s="59" t="s">
-        <v>329</v>
-      </c>
-      <c r="C15" s="59" t="s">
-        <v>349</v>
-      </c>
-      <c r="D15" s="18" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="34" x14ac:dyDescent="0.45">
-      <c r="A16" s="62">
-        <v>9</v>
-      </c>
-      <c r="B16" s="59" t="s">
-        <v>330</v>
-      </c>
-      <c r="C16" s="59" t="s">
-        <v>349</v>
-      </c>
-      <c r="D16" s="18" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" ht="34" x14ac:dyDescent="0.45">
-      <c r="A17" s="62">
-        <v>10</v>
-      </c>
-      <c r="B17" s="59" t="s">
-        <v>331</v>
-      </c>
-      <c r="C17" s="59" t="s">
-        <v>349</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" ht="34" x14ac:dyDescent="0.45">
-      <c r="A18" s="62">
-        <v>11</v>
-      </c>
-      <c r="B18" s="59" t="s">
-        <v>332</v>
-      </c>
-      <c r="C18" s="18" t="s">
-        <v>367</v>
-      </c>
-      <c r="D18" s="18" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A19" s="62">
-        <v>12</v>
-      </c>
-      <c r="B19" s="59" t="s">
-        <v>333</v>
-      </c>
-      <c r="C19" s="59" t="s">
-        <v>350</v>
-      </c>
-      <c r="D19" s="59" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A20" s="62">
-        <v>13</v>
-      </c>
-      <c r="B20" s="59" t="s">
-        <v>335</v>
-      </c>
-      <c r="C20" s="59" t="s">
-        <v>348</v>
-      </c>
-      <c r="D20" s="59" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" ht="34" x14ac:dyDescent="0.45">
-      <c r="A21" s="62">
-        <v>14</v>
-      </c>
-      <c r="B21" s="59" t="s">
-        <v>334</v>
-      </c>
-      <c r="C21" s="59" t="s">
-        <v>350</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B22" s="63" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B23" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B24" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B25" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B26" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B27" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B28" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="B29" t="s">
-        <v>366</v>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A23" s="66" t="s">
+        <v>396</v>
       </c>
     </row>
   </sheetData>
@@ -29074,25 +29550,308 @@
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="A23" r:id="rId1" xr:uid="{F9B3E65A-AC98-416A-BDA0-72BD9BF61C40}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3896574D-C413-4C7A-A478-AFE01B794D0A}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C1EB8A5E-CAD7-42C1-98BE-23B385F02B5F}">
+  <sheetPr>
+    <tabColor theme="9" tint="0.79998168889431442"/>
+  </sheetPr>
+  <dimension ref="A1:F13"/>
+  <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="5.33203125" style="45" customWidth="1"/>
+    <col min="2" max="2" width="49.5" style="45" customWidth="1"/>
+    <col min="3" max="3" width="13.4140625" style="45" customWidth="1"/>
+    <col min="4" max="6" width="77" style="45" customWidth="1"/>
+    <col min="7" max="16384" width="8.6640625" style="45"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A1" s="62" t="s">
+        <v>337</v>
+      </c>
+      <c r="B1" s="40" t="s">
+        <v>335</v>
+      </c>
+      <c r="C1" s="40" t="s">
+        <v>195</v>
+      </c>
+      <c r="D1" s="40" t="s">
+        <v>199</v>
+      </c>
+      <c r="E1" s="40" t="s">
+        <v>399</v>
+      </c>
+      <c r="F1" s="40" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="256" x14ac:dyDescent="0.45">
+      <c r="A2" s="98">
+        <v>2</v>
+      </c>
+      <c r="B2" s="50" t="s">
+        <v>322</v>
+      </c>
+      <c r="C2" s="50" t="s">
+        <v>373</v>
+      </c>
+      <c r="D2" s="48" t="s">
+        <v>375</v>
+      </c>
+      <c r="E2" s="48" t="s">
+        <v>398</v>
+      </c>
+      <c r="F2" s="48" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="208" x14ac:dyDescent="0.45">
+      <c r="A3" s="98">
+        <v>4</v>
+      </c>
+      <c r="B3" s="50" t="s">
+        <v>324</v>
+      </c>
+      <c r="C3" s="50" t="s">
+        <v>373</v>
+      </c>
+      <c r="D3" s="48" t="s">
+        <v>374</v>
+      </c>
+      <c r="E3" s="48" t="s">
+        <v>401</v>
+      </c>
+      <c r="F3" s="48" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="272" x14ac:dyDescent="0.45">
+      <c r="A4" s="98">
+        <v>5</v>
+      </c>
+      <c r="B4" s="50" t="s">
+        <v>325</v>
+      </c>
+      <c r="C4" s="50" t="s">
+        <v>372</v>
+      </c>
+      <c r="D4" s="48" t="s">
+        <v>385</v>
+      </c>
+      <c r="E4" s="48" t="s">
+        <v>402</v>
+      </c>
+      <c r="F4" s="48" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="192" x14ac:dyDescent="0.45">
+      <c r="A5" s="98">
+        <v>6</v>
+      </c>
+      <c r="B5" s="50" t="s">
+        <v>326</v>
+      </c>
+      <c r="C5" s="50" t="s">
+        <v>372</v>
+      </c>
+      <c r="D5" s="48" t="s">
+        <v>376</v>
+      </c>
+      <c r="E5" s="48" t="s">
+        <v>421</v>
+      </c>
+      <c r="F5" s="48" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="192" x14ac:dyDescent="0.45">
+      <c r="A6" s="98">
+        <v>8</v>
+      </c>
+      <c r="B6" s="50" t="s">
+        <v>328</v>
+      </c>
+      <c r="C6" s="50" t="s">
+        <v>389</v>
+      </c>
+      <c r="D6" s="48" t="s">
+        <v>388</v>
+      </c>
+      <c r="E6" s="48" t="s">
+        <v>403</v>
+      </c>
+      <c r="F6" s="48" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="224" x14ac:dyDescent="0.45">
+      <c r="A7" s="98">
+        <v>9</v>
+      </c>
+      <c r="B7" s="50" t="s">
+        <v>329</v>
+      </c>
+      <c r="C7" s="50" t="s">
+        <v>379</v>
+      </c>
+      <c r="D7" s="48" t="s">
+        <v>387</v>
+      </c>
+      <c r="E7" s="48" t="s">
+        <v>404</v>
+      </c>
+      <c r="F7" s="48" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="192" x14ac:dyDescent="0.45">
+      <c r="A8" s="98">
+        <v>10</v>
+      </c>
+      <c r="B8" s="50" t="s">
+        <v>330</v>
+      </c>
+      <c r="C8" s="50" t="s">
+        <v>372</v>
+      </c>
+      <c r="D8" s="48" t="s">
+        <v>377</v>
+      </c>
+      <c r="E8" s="48" t="s">
+        <v>405</v>
+      </c>
+      <c r="F8" s="48" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="320" x14ac:dyDescent="0.45">
+      <c r="A9" s="98">
+        <v>11</v>
+      </c>
+      <c r="B9" s="50" t="s">
+        <v>331</v>
+      </c>
+      <c r="C9" s="50" t="s">
+        <v>379</v>
+      </c>
+      <c r="D9" s="48" t="s">
+        <v>380</v>
+      </c>
+      <c r="E9" s="48" t="s">
+        <v>406</v>
+      </c>
+      <c r="F9" s="48" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="272" x14ac:dyDescent="0.45">
+      <c r="A10" s="98">
+        <v>12</v>
+      </c>
+      <c r="B10" s="50" t="s">
+        <v>378</v>
+      </c>
+      <c r="C10" s="50" t="s">
+        <v>382</v>
+      </c>
+      <c r="D10" s="48" t="s">
+        <v>386</v>
+      </c>
+      <c r="E10" s="48" t="s">
+        <v>407</v>
+      </c>
+      <c r="F10" s="48" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="224" x14ac:dyDescent="0.45">
+      <c r="A11" s="98">
+        <v>13</v>
+      </c>
+      <c r="B11" s="50" t="s">
+        <v>333</v>
+      </c>
+      <c r="C11" s="50" t="s">
+        <v>372</v>
+      </c>
+      <c r="D11" s="48" t="s">
+        <v>383</v>
+      </c>
+      <c r="E11" s="48" t="s">
+        <v>408</v>
+      </c>
+      <c r="F11" s="48" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="288" x14ac:dyDescent="0.45">
+      <c r="A12" s="98">
+        <v>14</v>
+      </c>
+      <c r="B12" s="50" t="s">
+        <v>332</v>
+      </c>
+      <c r="C12" s="50" t="s">
+        <v>379</v>
+      </c>
+      <c r="D12" s="37" t="s">
+        <v>384</v>
+      </c>
+      <c r="E12" s="48" t="s">
+        <v>409</v>
+      </c>
+      <c r="F12" s="48" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="144" x14ac:dyDescent="0.45">
+      <c r="A13" s="98" t="s">
+        <v>390</v>
+      </c>
+      <c r="B13" s="48" t="s">
+        <v>394</v>
+      </c>
+      <c r="C13" s="48" t="s">
+        <v>393</v>
+      </c>
+      <c r="D13" s="48" t="s">
+        <v>395</v>
+      </c>
+      <c r="E13" s="50"/>
+      <c r="F13" s="50"/>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="25" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA7446D1-A9E6-4F8D-B799-CB90AD03762A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3896574D-C413-4C7A-A478-AFE01B794D0A}">
+  <sheetPr>
+    <tabColor theme="0" tint="-0.499984740745262"/>
+  </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="101.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="68" x14ac:dyDescent="0.45">
+      <c r="A1" s="67" t="s">
+        <v>397</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/project_2/project2_project status(C2).xlsx
+++ b/project_2/project2_project status(C2).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pyostry\workspace\aiffel\ai-data-bootcamp\Project_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1753E519-E308-4505-9A05-2D3ED7771E3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D3C1BF2-A0D9-4C0C-80C8-802A3A97CA71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" firstSheet="4" activeTab="9" xr2:uid="{5FF54064-7DDC-427B-93D7-EF78D75E5195}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" firstSheet="4" activeTab="7" xr2:uid="{5FF54064-7DDC-427B-93D7-EF78D75E5195}"/>
   </bookViews>
   <sheets>
     <sheet name="제작 가이드라인" sheetId="12" r:id="rId1"/>
@@ -19,8 +19,8 @@
     <sheet name="1. 문제 정의(가설 트리)" sheetId="4" r:id="rId4"/>
     <sheet name="2. 지표 지도 그리기" sheetId="5" r:id="rId5"/>
     <sheet name="3. 원인 분해(로직 트리, 이슈 트리)" sheetId="7" r:id="rId6"/>
-    <sheet name="4. 통계적 검증" sheetId="11" r:id="rId7"/>
-    <sheet name="4-1 통계적 검증 결과" sheetId="13" r:id="rId8"/>
+    <sheet name="4-1 통계적 검증" sheetId="11" r:id="rId7"/>
+    <sheet name="4-2 통계적 검증 결과" sheetId="13" r:id="rId8"/>
     <sheet name="5. 머신러닝 적용" sheetId="10" r:id="rId9"/>
     <sheet name="6. 결론 및 의사결정 제안" sheetId="8" r:id="rId10"/>
     <sheet name="7. 대시보드 제작" sheetId="9" r:id="rId11"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="454">
   <si>
     <t>reward</t>
   </si>
@@ -1963,6 +1963,100 @@
   </si>
   <si>
     <t>제안</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>통계적 근거</t>
+  </si>
+  <si>
+    <t>한줄 요약</t>
+  </si>
+  <si>
+    <t>reward 계수 -0.1104(p&lt;0.001), 방향 반대; offer_type 통제모델 reward -0.050~-0.076(p&lt;0.001); difficulty 계수 0.0004~-0.011(p 0.02~0.90, 분석별 상이); reward·offer_type 강한 공선성</t>
+  </si>
+  <si>
+    <t>보상이 클수록 완료율이 오히려 낮았지만, 보상 금액과 오퍼 종류(1+1/할인)가 뒤섞여 있어 진짜 원인은 확정할 수 없어요.</t>
+  </si>
+  <si>
+    <t>has_social 47.9%→91.8%(Δ43.9%p); has_mobile 34.6%→78.6%(Δ44.0%p, 표본 9:1 불균형); has_web 83.7%→71.7%(방향 반대); email 전 오퍼 공통 포함(검증불가)</t>
+  </si>
+  <si>
+    <t>Social·Mobile이 포함된 오퍼일수록 열람률이 확연히 높았지만, Web·Email만의 순수 효과는 따로 확인할 수 없었어요.</t>
+  </si>
+  <si>
+    <t>상관계수 r=-0.093(p&lt;0.001); 로짓 계수 -0.089~-0.097(p&lt;0.001), pseudo R²≈0.008; 기간별 열람률 비단조(3일 80.7%·4일 49.9%·5일 95.2%·7일 72.1%·10일 65.4%); 열람까지 중앙값 12~18시간</t>
+  </si>
+  <si>
+    <t>유효기간이 짧아서 못 봤다는 근거는 없었어요 — 열람하는 사람은 보통 하루 안에 확인했고, 기간별 패턴도 들쭉날쭉했어요.</t>
+  </si>
+  <si>
+    <t>prior_offer_count–열람 r=-0.027~-0.014(p&lt;0.05); –완료 r=-0.022(p&lt;0.001); 설명력 pseudo R²≈0.00006~0.001(무시할 수준); 5회+ 구간 n=3,067(표본 작음)</t>
+  </si>
+  <si>
+    <t>오퍼를 여러 번 받아도 반응이 뚜렷하게 둔해지진 않았어요 — 통계적으로만 미세하게 유의할 뿐 실질적 영향은 거의 없어요.</t>
+  </si>
+  <si>
+    <t>단순모델 offer_type[discount] 계수 0.60~0.65(p&lt;0.001); 통제모델(+reward,difficulty,duration) 0.27~0.29(p&lt;0.001, 약 55%↓); 완료율 bogo 42~44% vs discount 59~62%(격차 16~18%p)</t>
+  </si>
+  <si>
+    <t>할인형이 1+1형보다 완료율이 뚜렷하게 높고, 보상·난이도·기간을 맞춰봐도 그 차이의 절반가량은 그대로 남아 있어요.</t>
+  </si>
+  <si>
+    <t>단순모델 계수 -0.0128(p&lt;0.001); 통제모델(+offer_type,reward,duration) -0.044~-0.048(p&lt;0.001); 원자료 완료율 비단조(5→50%·7→60%·10→48%·20→50~54%, difficulty=20은 n작고 채널도 부실해 해석 주의)</t>
+  </si>
+  <si>
+    <t>목표 금액이 높을수록 완료율이 낮아지는 효과는 통계적으로 확인됐지만, 패턴이 매끈하지 않아 해석에 주의가 필요해요.</t>
+  </si>
+  <si>
+    <t>income×difficulty 상호작용 계수 1.5e-08~0.0015(p=0.28~0.74, 비유의); income 주효과 계수 1.49e-05(p&lt;0.001, 유의)</t>
+  </si>
+  <si>
+    <t>소득이 낮을수록 목표금액 부담을 더 크게 느낀다는 근거는 없었어요 — 다만 소득이 높을수록 완료율 자체는 높았어요.</t>
+  </si>
+  <si>
+    <t>income×reward 상호작용 계수 +2.4e-06~+2.7e-05(p&lt;0.001, 양수); 완료율 스프레드 저소득 33.5%p→고소득 7.7%p(단조감소); 소득분위별 χ²: Q1 821.8→Q4 52.1(p&lt;0.001)</t>
+  </si>
+  <si>
+    <t>소득이 높을수록 보상 금액에 덜 민감했어요 — 저소득층은 보상 차이에 크게 반응하지만 고소득층은 거의 반응하지 않았어요.</t>
+  </si>
+  <si>
+    <t>Web 포함-미포함 열람률 격차: 18-30세 27.2%p vs 51세+ 8~11%p대; 연령대별 χ²(p&lt;0.001, N=16,000+대); email 전 오퍼 공통 포함(검증불가); 채널조합 전체 χ²=16,570(V=0.50)</t>
+  </si>
+  <si>
+    <t>web·email 위주 채널의 수신율 저하는 전 연령대에서 나타나지만, 통념과 달리 고령층이 아니라 청년층에서 그 영향이 가장 컸어요.</t>
+  </si>
+  <si>
+    <t>age–수신 상관 r=0.020~0.022(p&lt;0.001, 양수); pseudo R²≈0.04%(무시할 수준); 오즈비 1.003; 연령대별 최저 구간 18-30세 68.0%(전체 중 최저)</t>
+  </si>
+  <si>
+    <t>고령층일수록 수신율이 낮다는 근거는 없었어요 — 오히려 가장 반응이 낮았던 건 18~30대였어요.</t>
+  </si>
+  <si>
+    <t>남성 χ²=838.0(p&lt;0.001)·여성 χ²=195.6~1,473.9(p&lt;0.001); Cramér's V 남성 0.19~0.21 vs 여성 0.11; 완료율 남성×bogo 최저(34.9~42.8%), 여성은 유형 간 격차 거의 없음</t>
+  </si>
+  <si>
+    <t>여성은 오퍼 유형에 따른 차이가 거의 없었지만, 남성은 1+1형에서 유독 완료율이 낮았어요.</t>
+  </si>
+  <si>
+    <t>profile 단독모델(N=39,646, R²=0.024) vs +offer통제(R²=0.049): gender[M] -0.361→-0.374(오즈비 0.69,p&lt;0.001); age 0.0026→0.0024(오즈비 1.002,p&lt;0.001); income 1.32e-05→1.30e-05(오즈비 1.14/1만불,p&lt;0.001); VIF 전부&lt;1.2</t>
+  </si>
+  <si>
+    <t>성별·연령·소득 효과는 오퍼 구성과 상관없이 독립적으로 유지됐고, 그 중 성별 효과가 가장 크고 확실했어요.</t>
+  </si>
+  <si>
+    <t>링크</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>검증전</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>검증후</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>진행하지 않음</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2227,7 +2321,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -2498,6 +2592,28 @@
         <color indexed="64"/>
       </diagonal>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -2507,7 +2623,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2712,6 +2828,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2739,6 +2858,21 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2758,9 +2892,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2784,26 +2915,42 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -11580,8 +11727,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="220981" y="1805623"/>
-          <a:ext cx="2100172" cy="447540"/>
+          <a:off x="173001" y="1826087"/>
+          <a:ext cx="2123975" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -11680,8 +11827,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="234089" y="1818731"/>
-        <a:ext cx="2073956" cy="421324"/>
+        <a:off x="186258" y="1839344"/>
+        <a:ext cx="2097461" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{ED5992BD-91A0-44DC-B026-C230E027754F}">
@@ -11691,8 +11838,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="16874489">
-          <a:off x="1581876" y="1121529"/>
-          <a:ext cx="1836586" cy="14378"/>
+          <a:off x="1549321" y="1134321"/>
+          <a:ext cx="1857401" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -11706,7 +11853,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1836586" y="7189"/>
+                <a:pt x="1857401" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -11765,8 +11912,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2454255" y="1082803"/>
-        <a:ext cx="91829" cy="91829"/>
+        <a:off x="2431586" y="1095075"/>
+        <a:ext cx="92870" cy="92870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{EB7188F2-1357-4748-A44C-AB5D4A48F40F}">
@@ -11776,8 +11923,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2679186" y="4273"/>
-          <a:ext cx="1080487" cy="447540"/>
+          <a:off x="2659066" y="4321"/>
+          <a:ext cx="1092733" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -11852,8 +11999,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2692294" y="17381"/>
-        <a:ext cx="1054271" cy="421324"/>
+        <a:off x="2672323" y="17578"/>
+        <a:ext cx="1066219" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7531319A-E0E5-4CB4-9F35-33254694A0D7}">
@@ -11863,8 +12010,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3759673" y="220854"/>
-          <a:ext cx="352482" cy="14378"/>
+          <a:off x="3751800" y="223438"/>
+          <a:ext cx="356477" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -11878,7 +12025,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="352482" y="7189"/>
+                <a:pt x="356477" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -11937,8 +12084,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3927103" y="219231"/>
-        <a:ext cx="17624" cy="17624"/>
+        <a:off x="3921127" y="221715"/>
+        <a:ext cx="17823" cy="17823"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{8F385C2E-83EB-470A-8A65-12C51C60EB27}">
@@ -11948,8 +12095,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4112156" y="4273"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="4108278" y="4321"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -12048,8 +12195,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4125264" y="17381"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="4121535" y="17578"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{71327523-F24D-4A9E-8CA7-7C0E6A96618A}">
@@ -12059,8 +12206,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17132988">
-          <a:off x="1832388" y="1378865"/>
-          <a:ext cx="1335563" cy="14378"/>
+          <a:off x="1802671" y="1394574"/>
+          <a:ext cx="1350699" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -12074,7 +12221,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1335563" y="7189"/>
+                <a:pt x="1350699" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -12133,8 +12280,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2466780" y="1352664"/>
-        <a:ext cx="66778" cy="66778"/>
+        <a:off x="2444254" y="1367995"/>
+        <a:ext cx="67534" cy="67534"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{08B2E005-DF35-41E7-A396-CA02C3B8D0A4}">
@@ -12144,8 +12291,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2679186" y="518944"/>
-          <a:ext cx="1080487" cy="447540"/>
+          <a:off x="2659066" y="524826"/>
+          <a:ext cx="1092733" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -12220,8 +12367,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2692294" y="532052"/>
-        <a:ext cx="1054271" cy="421324"/>
+        <a:off x="2672323" y="538083"/>
+        <a:ext cx="1066219" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E113C6B3-F5C2-41D9-9727-BB430EAD3818}">
@@ -12231,8 +12378,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3759673" y="735525"/>
-          <a:ext cx="358032" cy="14378"/>
+          <a:off x="3751800" y="743943"/>
+          <a:ext cx="362090" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -12246,7 +12393,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="358032" y="7189"/>
+                <a:pt x="362090" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -12305,8 +12452,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3929739" y="733763"/>
-        <a:ext cx="17901" cy="17901"/>
+        <a:off x="3923793" y="742080"/>
+        <a:ext cx="18104" cy="18104"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{53F03F28-ED40-4762-8125-AFFEEA792A72}">
@@ -12316,8 +12463,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4117706" y="518944"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="4113890" y="524826"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -12440,8 +12587,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4130814" y="532052"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="4127147" y="538083"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{806C8330-1E37-41AD-AEEE-3552A4162510}">
@@ -12451,8 +12598,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17692822">
-          <a:off x="2074675" y="1636200"/>
-          <a:ext cx="850988" cy="14378"/>
+          <a:off x="2047704" y="1654826"/>
+          <a:ext cx="860633" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -12466,7 +12613,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="850988" y="7189"/>
+                <a:pt x="860633" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -12525,8 +12672,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2478895" y="1622115"/>
-        <a:ext cx="42549" cy="42549"/>
+        <a:off x="2456505" y="1640499"/>
+        <a:ext cx="43031" cy="43031"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{3BC1DAB2-4FEF-42C9-A10F-0690E2903498}">
@@ -12536,8 +12683,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2679186" y="1033615"/>
-          <a:ext cx="1080487" cy="447540"/>
+          <a:off x="2659066" y="1045330"/>
+          <a:ext cx="1092733" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -12628,8 +12775,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2692294" y="1046723"/>
-        <a:ext cx="1054271" cy="421324"/>
+        <a:off x="2672323" y="1058587"/>
+        <a:ext cx="1066219" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6BFD1C16-8154-4C15-AF72-E53B38C4A146}">
@@ -12639,8 +12786,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3759673" y="1250197"/>
-          <a:ext cx="358032" cy="14378"/>
+          <a:off x="3751800" y="1264447"/>
+          <a:ext cx="362090" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -12654,7 +12801,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="358032" y="7189"/>
+                <a:pt x="362090" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -12713,8 +12860,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3929739" y="1248435"/>
-        <a:ext cx="17901" cy="17901"/>
+        <a:off x="3923793" y="1262584"/>
+        <a:ext cx="18104" cy="18104"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1A251137-9CB6-43D7-B47D-0D220C30894C}">
@@ -12724,8 +12871,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4117706" y="1033615"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="4113890" y="1045330"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -12848,8 +12995,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4130814" y="1046723"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="4127147" y="1058587"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{227E0FEF-1368-4562-AD55-940C6A450E91}">
@@ -12859,8 +13006,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="3310531">
-          <a:off x="2186691" y="2279540"/>
-          <a:ext cx="626956" cy="14378"/>
+          <a:off x="2160990" y="2305456"/>
+          <a:ext cx="634061" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -12874,7 +13021,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="626956" y="7189"/>
+                <a:pt x="634061" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -12933,8 +13080,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2484496" y="2271055"/>
-        <a:ext cx="31347" cy="31347"/>
+        <a:off x="2462170" y="2296794"/>
+        <a:ext cx="31703" cy="31703"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{146FB508-948A-484E-B54F-2A63CE5492FA}">
@@ -12944,8 +13091,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2679186" y="2320294"/>
-          <a:ext cx="1080487" cy="447540"/>
+          <a:off x="2659066" y="2346591"/>
+          <a:ext cx="1092733" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -13020,8 +13167,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2692294" y="2333402"/>
-        <a:ext cx="1054271" cy="421324"/>
+        <a:off x="2672323" y="2359848"/>
+        <a:ext cx="1066219" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1583A4D8-C48C-400A-B5A1-D8E8188A1E57}">
@@ -13031,8 +13178,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17692822">
-          <a:off x="3513195" y="2150872"/>
-          <a:ext cx="850988" cy="14378"/>
+          <a:off x="3502528" y="2175330"/>
+          <a:ext cx="860633" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -13046,7 +13193,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="850988" y="7189"/>
+                <a:pt x="860633" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -13105,8 +13252,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3917415" y="2136786"/>
-        <a:ext cx="42549" cy="42549"/>
+        <a:off x="3911329" y="2161003"/>
+        <a:ext cx="43031" cy="43031"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{985FE1E2-4CA8-4AC7-A474-DEECC9A2BB80}">
@@ -13116,8 +13263,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4117706" y="1548287"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="4113890" y="1565835"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -13208,8 +13355,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4130814" y="1561395"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="4127147" y="1579092"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{16F44D37-2601-482A-9095-0B3E8E10E520}">
@@ -13219,8 +13366,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19457599">
-          <a:off x="3718230" y="2408207"/>
-          <a:ext cx="440918" cy="14378"/>
+          <a:off x="3709887" y="2435583"/>
+          <a:ext cx="445915" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -13234,7 +13381,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="440918" y="7189"/>
+                <a:pt x="445915" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -13293,8 +13440,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3927667" y="2404373"/>
-        <a:ext cx="22045" cy="22045"/>
+        <a:off x="3921697" y="2431624"/>
+        <a:ext cx="22295" cy="22295"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{2D542640-C237-42B5-8470-73084719F8F3}">
@@ -13304,8 +13451,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4117706" y="2062958"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="4113890" y="2086339"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -13396,8 +13543,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4130814" y="2076066"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="4127147" y="2099596"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9A75AB13-86A0-459A-8B2B-E8037D74B447}">
@@ -13407,8 +13554,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2142401">
-          <a:off x="3718230" y="2665543"/>
-          <a:ext cx="440918" cy="14378"/>
+          <a:off x="3709887" y="2695835"/>
+          <a:ext cx="445915" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -13422,7 +13569,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="440918" y="7189"/>
+                <a:pt x="445915" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -13481,8 +13628,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3927667" y="2661709"/>
-        <a:ext cx="22045" cy="22045"/>
+        <a:off x="3921697" y="2691876"/>
+        <a:ext cx="22295" cy="22295"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{106C3051-36E0-4DB2-B006-BD51244834C6}">
@@ -13492,8 +13639,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4117706" y="2577630"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="4113890" y="2606844"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -13584,8 +13731,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4130814" y="2590738"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="4127147" y="2620101"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6562E267-52DD-4DC6-81E6-A0E9307367D6}">
@@ -13595,8 +13742,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="3907178">
-          <a:off x="3513195" y="2922879"/>
-          <a:ext cx="850988" cy="14378"/>
+          <a:off x="3502528" y="2956087"/>
+          <a:ext cx="860633" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -13610,7 +13757,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="850988" y="7189"/>
+                <a:pt x="860633" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -13669,8 +13816,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3917415" y="2908793"/>
-        <a:ext cx="42549" cy="42549"/>
+        <a:off x="3911329" y="2941760"/>
+        <a:ext cx="43031" cy="43031"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{220D319D-36C0-42A0-A946-F197C4269C14}">
@@ -13680,8 +13827,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4117706" y="3092301"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="4113890" y="3127348"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -13772,8 +13919,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4130814" y="3105409"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="4127147" y="3140605"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4332858F-88A7-466E-8722-8833A7B96598}">
@@ -13783,8 +13930,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="4725511">
-          <a:off x="1581876" y="2922879"/>
-          <a:ext cx="1836586" cy="14378"/>
+          <a:off x="1549321" y="2956087"/>
+          <a:ext cx="1857401" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -13798,7 +13945,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1836586" y="7189"/>
+                <a:pt x="1857401" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -13853,8 +14000,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2454255" y="2884153"/>
-        <a:ext cx="91829" cy="91829"/>
+        <a:off x="2431586" y="2916841"/>
+        <a:ext cx="92870" cy="92870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1479FCFA-85A4-438D-B5D0-346DFAD5924D}">
@@ -13864,8 +14011,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2679186" y="3606973"/>
-          <a:ext cx="1080487" cy="447540"/>
+          <a:off x="2659066" y="3647853"/>
+          <a:ext cx="1092733" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -13940,8 +14087,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2692294" y="3620081"/>
-        <a:ext cx="1054271" cy="421324"/>
+        <a:off x="2672323" y="3661110"/>
+        <a:ext cx="1066219" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E6D0412B-4D85-432B-BE35-F277BFD00B03}">
@@ -13951,8 +14098,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3759673" y="3823554"/>
-          <a:ext cx="358032" cy="14378"/>
+          <a:off x="3751800" y="3866970"/>
+          <a:ext cx="362090" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -13966,7 +14113,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="358032" y="7189"/>
+                <a:pt x="362090" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -14021,8 +14168,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3929739" y="3821792"/>
-        <a:ext cx="17901" cy="17901"/>
+        <a:off x="3923793" y="3865107"/>
+        <a:ext cx="18104" cy="18104"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{CE9AFD94-4037-4F8B-B49B-020818B5CBB5}">
@@ -14032,8 +14179,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4117706" y="3606973"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="4113890" y="3647853"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -14140,8 +14287,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4130814" y="3620081"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="4127147" y="3661110"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B460AB31-448C-42B6-9C6B-D3CF5013B4F6}">
@@ -14151,8 +14298,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="88714" y="4636316"/>
-          <a:ext cx="1800813" cy="447540"/>
+          <a:off x="39236" y="4688862"/>
+          <a:ext cx="1821222" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -14277,8 +14424,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="101822" y="4649424"/>
-        <a:ext cx="1774597" cy="421324"/>
+        <a:off x="52493" y="4702119"/>
+        <a:ext cx="1794708" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{C120D3E5-D1A3-4DC1-848B-C37D9DDE2012}">
@@ -14288,8 +14435,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="18752467">
-          <a:off x="1776407" y="4595561"/>
-          <a:ext cx="698529" cy="14378"/>
+          <a:off x="1746056" y="4647727"/>
+          <a:ext cx="706446" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -14303,7 +14450,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="698529" y="7189"/>
+                <a:pt x="706446" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -14358,8 +14505,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2108209" y="4585287"/>
-        <a:ext cx="34926" cy="34926"/>
+        <a:off x="2081618" y="4637255"/>
+        <a:ext cx="35322" cy="35322"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6F01F0AA-74B9-49DB-A456-B8979039EB51}">
@@ -14369,8 +14516,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2361817" y="4121644"/>
-          <a:ext cx="1080487" cy="447540"/>
+          <a:off x="2338101" y="4168357"/>
+          <a:ext cx="1092733" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -14443,8 +14590,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2374925" y="4134752"/>
-        <a:ext cx="1054271" cy="421324"/>
+        <a:off x="2351358" y="4181614"/>
+        <a:ext cx="1066219" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{F5E69F9A-2631-4A2D-BC76-B4BD9B08D019}">
@@ -14454,8 +14601,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3442305" y="4338225"/>
-          <a:ext cx="364020" cy="14378"/>
+          <a:off x="3430834" y="4387475"/>
+          <a:ext cx="368146" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -14469,7 +14616,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="364020" y="7189"/>
+                <a:pt x="368146" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -14524,8 +14671,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3615214" y="4336314"/>
-        <a:ext cx="18201" cy="18201"/>
+        <a:off x="3605704" y="4385460"/>
+        <a:ext cx="18407" cy="18407"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{69EDA0B0-D39D-4C93-8B8D-10889C581D9E}">
@@ -14535,8 +14682,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3806325" y="4121644"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="3798980" y="4168357"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -14609,8 +14756,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3819433" y="4134752"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="3812237" y="4181614"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{AC23C890-5E27-4DC3-9BF7-2C50218200D9}">
@@ -14620,8 +14767,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="1889527" y="4852897"/>
-          <a:ext cx="472289" cy="14378"/>
+          <a:off x="1860458" y="4907979"/>
+          <a:ext cx="477642" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -14635,7 +14782,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="472289" y="7189"/>
+                <a:pt x="477642" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -14690,8 +14837,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2113865" y="4848279"/>
-        <a:ext cx="23614" cy="23614"/>
+        <a:off x="2087338" y="4903227"/>
+        <a:ext cx="23882" cy="23882"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B4CF3050-E538-4710-99C5-FB5B2F28D116}">
@@ -14701,8 +14848,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2361817" y="4636316"/>
-          <a:ext cx="1080487" cy="447540"/>
+          <a:off x="2338101" y="4688862"/>
+          <a:ext cx="1092733" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -14775,8 +14922,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2374925" y="4649424"/>
-        <a:ext cx="1054271" cy="421324"/>
+        <a:off x="2351358" y="4702119"/>
+        <a:ext cx="1066219" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{55492AE0-989E-4368-96E6-8609B6786079}">
@@ -14786,8 +14933,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3442305" y="4852897"/>
-          <a:ext cx="364020" cy="14378"/>
+          <a:off x="3430834" y="4907979"/>
+          <a:ext cx="368146" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -14801,7 +14948,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="364020" y="7189"/>
+                <a:pt x="368146" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -14856,8 +15003,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3615214" y="4850985"/>
-        <a:ext cx="18201" cy="18201"/>
+        <a:off x="3605704" y="4905964"/>
+        <a:ext cx="18407" cy="18407"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{99BD4B49-7654-4BFC-93A2-73715A94DAC0}">
@@ -14867,8 +15014,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3806325" y="4636316"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="3798980" y="4688862"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -14985,8 +15132,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3819433" y="4649424"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="3812237" y="4702119"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{48D36C81-0EEF-4879-868D-73109D1A61EF}">
@@ -14996,8 +15143,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2847533">
-          <a:off x="1776407" y="5110232"/>
-          <a:ext cx="698529" cy="14378"/>
+          <a:off x="1746056" y="5168231"/>
+          <a:ext cx="706446" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -15011,7 +15158,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="698529" y="7189"/>
+                <a:pt x="706446" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -15066,8 +15213,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2108209" y="5099958"/>
-        <a:ext cx="34926" cy="34926"/>
+        <a:off x="2081618" y="5157759"/>
+        <a:ext cx="35322" cy="35322"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E0C7A212-1F93-473A-8909-15A6780CBC2F}">
@@ -15077,8 +15224,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2361817" y="5150987"/>
-          <a:ext cx="1080487" cy="447540"/>
+          <a:off x="2338101" y="5209366"/>
+          <a:ext cx="1092733" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -15151,8 +15298,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2374925" y="5164095"/>
-        <a:ext cx="1054271" cy="421324"/>
+        <a:off x="2351358" y="5222623"/>
+        <a:ext cx="1066219" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4D54B04B-F98B-4577-8925-91ECEF877996}">
@@ -15162,8 +15309,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3442305" y="5367568"/>
-          <a:ext cx="376041" cy="14378"/>
+          <a:off x="3430834" y="5428484"/>
+          <a:ext cx="380303" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -15177,7 +15324,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="376041" y="7189"/>
+                <a:pt x="380303" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -15232,8 +15379,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3620924" y="5365356"/>
-        <a:ext cx="18802" cy="18802"/>
+        <a:off x="3611478" y="5426165"/>
+        <a:ext cx="19015" cy="19015"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{540CB623-D523-4AD6-BF5D-A946D7B052E6}">
@@ -15243,8 +15390,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3818346" y="5150987"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="3811137" y="5209366"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -15362,8 +15509,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3831454" y="5164095"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="3824394" y="5222623"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
   </dsp:spTree>
@@ -15385,8 +15532,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9182" y="3307680"/>
-          <a:ext cx="1177681" cy="361541"/>
+          <a:off x="10440" y="3343938"/>
+          <a:ext cx="1173405" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -15464,8 +15611,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="19771" y="3318269"/>
-        <a:ext cx="1156503" cy="340363"/>
+        <a:off x="20991" y="3354489"/>
+        <a:ext cx="1152303" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7667B88B-738E-4E27-80A6-15B1E3AED5F8}">
@@ -15475,8 +15622,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="16719080">
-          <a:off x="572912" y="2769909"/>
-          <a:ext cx="1445308" cy="8220"/>
+          <a:off x="572123" y="2808170"/>
+          <a:ext cx="1440061" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -15487,10 +15634,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1445308" y="4110"/>
+                <a:pt x="1440061" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -15549,8 +15696,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1259433" y="2737887"/>
-        <a:ext cx="72265" cy="72265"/>
+        <a:off x="1256152" y="2776213"/>
+        <a:ext cx="72003" cy="72003"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D9E30B0F-B6EE-4B8A-B3A5-5AD7E4CFBC12}">
@@ -15560,8 +15707,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="1404269" y="1878817"/>
-          <a:ext cx="1444638" cy="361541"/>
+          <a:off x="1400462" y="1920262"/>
+          <a:ext cx="1439393" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -15652,8 +15799,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1414858" y="1889406"/>
-        <a:ext cx="1423460" cy="340363"/>
+        <a:off x="1411013" y="1930813"/>
+        <a:ext cx="1418291" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{ED5992BD-91A0-44DC-B026-C230E027754F}">
@@ -15663,8 +15810,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="16757427">
-          <a:off x="2284276" y="1390976"/>
-          <a:ext cx="1346666" cy="8220"/>
+          <a:off x="2277274" y="1434244"/>
+          <a:ext cx="1341777" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -15675,10 +15822,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1346666" y="4110"/>
+                <a:pt x="1341777" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -15737,8 +15884,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2923942" y="1361420"/>
-        <a:ext cx="67333" cy="67333"/>
+        <a:off x="2914618" y="1404744"/>
+        <a:ext cx="67088" cy="67088"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{EB7188F2-1357-4748-A44C-AB5D4A48F40F}">
@@ -15748,8 +15895,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3066312" y="549815"/>
-          <a:ext cx="1407331" cy="361541"/>
+          <a:off x="3056471" y="596085"/>
+          <a:ext cx="1402222" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -15819,8 +15966,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3076901" y="560404"/>
-        <a:ext cx="1386153" cy="340363"/>
+        <a:off x="3067022" y="606636"/>
+        <a:ext cx="1381120" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7531319A-E0E5-4CB4-9F35-33254694A0D7}">
@@ -15830,8 +15977,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17860289">
-          <a:off x="4350219" y="522390"/>
-          <a:ext cx="460883" cy="8220"/>
+          <a:off x="4335717" y="568811"/>
+          <a:ext cx="459210" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -15842,10 +15989,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="460883" y="4110"/>
+                <a:pt x="459210" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -15904,8 +16051,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4569139" y="514979"/>
-        <a:ext cx="23044" cy="23044"/>
+        <a:off x="4553842" y="561375"/>
+        <a:ext cx="22960" cy="22960"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{8F385C2E-83EB-470A-8A65-12C51C60EB27}">
@@ -15915,8 +16062,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4687678" y="140049"/>
-          <a:ext cx="1776175" cy="364734"/>
+          <a:off x="4671951" y="187807"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -15986,8 +16133,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4698361" y="150732"/>
-        <a:ext cx="1754809" cy="343368"/>
+        <a:off x="4682595" y="198451"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{8EC6EEF9-E6D8-4DE2-A6DD-BB50B40A5CF0}">
@@ -15997,8 +16144,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6463853" y="318305"/>
-          <a:ext cx="220774" cy="8220"/>
+          <a:off x="6441677" y="365467"/>
+          <a:ext cx="219972" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16009,10 +16156,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="220774" y="4110"/>
+                <a:pt x="219972" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16067,8 +16214,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6568721" y="316896"/>
-        <a:ext cx="11038" cy="11038"/>
+        <a:off x="6546165" y="364012"/>
+        <a:ext cx="10998" cy="10998"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{31CFEB2D-0887-4520-AF04-1E3C38912960}">
@@ -16078,8 +16225,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6684628" y="140049"/>
-          <a:ext cx="3167897" cy="364734"/>
+          <a:off x="6661650" y="187807"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16165,8 +16312,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6695311" y="150732"/>
-        <a:ext cx="3146531" cy="343368"/>
+        <a:off x="6672294" y="198451"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{602438BB-CBF9-49AF-AB0A-D57EA2C10BE2}">
@@ -16176,8 +16323,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9852525" y="318305"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9818046" y="365467"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16188,10 +16335,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16246,8 +16393,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9955792" y="316981"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9920939" y="364096"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{57D97F9E-094F-4C3F-82B2-5A689BC4D082}">
@@ -16257,8 +16404,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10069930" y="146189"/>
-          <a:ext cx="1807704" cy="352453"/>
+          <a:off x="10034662" y="193925"/>
+          <a:ext cx="1801141" cy="351174"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16355,8 +16502,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10080253" y="156512"/>
-        <a:ext cx="1787058" cy="331807"/>
+        <a:off x="10044948" y="204211"/>
+        <a:ext cx="1780569" cy="330602"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B3B4155B-F64B-452E-AEBC-36FE76B0BD69}">
@@ -16366,8 +16513,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="21585916">
-          <a:off x="4473642" y="726030"/>
-          <a:ext cx="217406" cy="8220"/>
+          <a:off x="4458692" y="771712"/>
+          <a:ext cx="216617" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16378,10 +16525,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217406" y="4110"/>
+                <a:pt x="216617" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16436,8 +16583,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4576910" y="724705"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="4561585" y="770341"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D20B6C81-A2D9-4E8E-80C0-968EFF7F89E1}">
@@ -16447,8 +16594,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4691048" y="547328"/>
-          <a:ext cx="1776175" cy="364734"/>
+          <a:off x="4675308" y="593607"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16518,8 +16665,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4701731" y="558011"/>
-        <a:ext cx="1754809" cy="343368"/>
+        <a:off x="4685952" y="604251"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7FE58BCF-6B0D-48A2-8DDE-611A1D34A4D6}">
@@ -16529,8 +16676,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6467223" y="725585"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="6445035" y="771268"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16541,10 +16688,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16599,8 +16746,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6570490" y="724260"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="6547927" y="769897"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{629314FA-FCA6-45B9-99A7-2C2196A96D5C}">
@@ -16610,8 +16757,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6684628" y="547328"/>
-          <a:ext cx="3167897" cy="364734"/>
+          <a:off x="6661650" y="593607"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16710,8 +16857,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6695311" y="558011"/>
-        <a:ext cx="3146531" cy="343368"/>
+        <a:off x="6672294" y="604251"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{CCF144EB-A097-46BE-8FF7-BE5C7A394E2A}">
@@ -16721,8 +16868,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9852525" y="725585"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9818046" y="771268"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16733,10 +16880,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16791,8 +16938,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9955792" y="724260"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9920939" y="769897"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9EE0F2D9-F39B-4921-9EAC-DBA04DC260DD}">
@@ -16802,8 +16949,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10069930" y="545546"/>
-          <a:ext cx="1807704" cy="368297"/>
+          <a:off x="10034662" y="591832"/>
+          <a:ext cx="1801141" cy="366960"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16886,8 +17033,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10080717" y="556333"/>
-        <a:ext cx="1786130" cy="346723"/>
+        <a:off x="10045410" y="602580"/>
+        <a:ext cx="1779645" cy="345464"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6169CD61-5E3A-4096-AA5A-91A22C397918}">
@@ -16897,8 +17044,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="3717526">
-          <a:off x="4351116" y="930560"/>
-          <a:ext cx="462458" cy="8220"/>
+          <a:off x="4336611" y="975499"/>
+          <a:ext cx="460779" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16909,10 +17056,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="462458" y="4110"/>
+                <a:pt x="460779" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16967,8 +17114,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4570784" y="923109"/>
-        <a:ext cx="23122" cy="23122"/>
+        <a:off x="4555481" y="968024"/>
+        <a:ext cx="23038" cy="23038"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D5FDB947-B70B-4493-B9F9-83A45503DA23}">
@@ -16978,8 +17125,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4691048" y="956388"/>
-          <a:ext cx="1776175" cy="364734"/>
+          <a:off x="4675308" y="1001183"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17049,8 +17196,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4701731" y="967071"/>
-        <a:ext cx="1754809" cy="343368"/>
+        <a:off x="4685952" y="1011827"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9EDF68AF-E14B-40BF-AB6D-4B01635D735A}">
@@ -17060,8 +17207,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6467223" y="1134645"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="6445035" y="1178843"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17072,10 +17219,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17130,8 +17277,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6570490" y="1133321"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="6547927" y="1177472"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{5A5C0991-25ED-4076-91F2-80A2EEFC811E}">
@@ -17141,8 +17288,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6684628" y="956388"/>
-          <a:ext cx="3167897" cy="364734"/>
+          <a:off x="6661650" y="1001183"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17276,8 +17423,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6695311" y="967071"/>
-        <a:ext cx="3146531" cy="343368"/>
+        <a:off x="6672294" y="1011827"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{723082D3-A8E2-4807-89B5-C74C600B949E}">
@@ -17287,8 +17434,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9852525" y="1134645"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9818046" y="1178843"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17299,10 +17446,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17357,8 +17504,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9955792" y="1133321"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9920939" y="1177472"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{05E664DE-AAC0-4D52-9AA4-DE55CA572420}">
@@ -17368,8 +17515,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10069930" y="954607"/>
-          <a:ext cx="1807704" cy="368297"/>
+          <a:off x="10034662" y="999408"/>
+          <a:ext cx="1801141" cy="366960"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17439,8 +17586,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10080717" y="965394"/>
-        <a:ext cx="1786130" cy="346723"/>
+        <a:off x="10045410" y="1010156"/>
+        <a:ext cx="1779645" cy="345464"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{16F44D37-2601-482A-9095-0B3E8E10E520}">
@@ -17450,8 +17597,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="1505741">
-          <a:off x="2837576" y="2106387"/>
-          <a:ext cx="240066" cy="8220"/>
+          <a:off x="2828565" y="2147057"/>
+          <a:ext cx="239195" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17462,10 +17609,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="240066" y="4110"/>
+                <a:pt x="239195" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17524,8 +17671,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2951607" y="2104496"/>
-        <a:ext cx="12003" cy="12003"/>
+        <a:off x="2942183" y="2145122"/>
+        <a:ext cx="11959" cy="11959"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{2D542640-C237-42B5-8470-73084719F8F3}">
@@ -17535,8 +17682,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3066312" y="1980637"/>
-          <a:ext cx="1407331" cy="361541"/>
+          <a:off x="3056471" y="2021712"/>
+          <a:ext cx="1402222" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17606,8 +17753,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3076901" y="1991226"/>
-        <a:ext cx="1386153" cy="340363"/>
+        <a:off x="3067022" y="2032263"/>
+        <a:ext cx="1381120" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{BFCFD3BD-878E-4ADC-81DA-3641DCD660A7}">
@@ -17617,8 +17764,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17370601">
-          <a:off x="4256862" y="1850501"/>
-          <a:ext cx="650967" cy="8220"/>
+          <a:off x="4242699" y="1892100"/>
+          <a:ext cx="648604" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17629,10 +17776,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="650967" y="4110"/>
+                <a:pt x="648604" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17687,8 +17834,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4566071" y="1838338"/>
-        <a:ext cx="32548" cy="32548"/>
+        <a:off x="4550785" y="1879930"/>
+        <a:ext cx="32430" cy="32430"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{911F1DD5-D3D2-4321-A1A5-7E2BAE25AAD5}">
@@ -17698,8 +17845,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4691048" y="1365449"/>
-          <a:ext cx="1776175" cy="364734"/>
+          <a:off x="4675308" y="1408758"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17769,8 +17916,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4701731" y="1376132"/>
-        <a:ext cx="1754809" cy="343368"/>
+        <a:off x="4685952" y="1419402"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{F4CAC384-240B-4811-A7FE-5EF39454FD0A}">
@@ -17780,8 +17927,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6467223" y="1543706"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="6445035" y="1586419"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17792,10 +17939,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17850,8 +17997,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6570490" y="1542381"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="6547927" y="1585048"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{00847D60-C67D-487A-B918-B0C406DE6A20}">
@@ -17861,8 +18008,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6684628" y="1365449"/>
-          <a:ext cx="3167897" cy="364734"/>
+          <a:off x="6661650" y="1408758"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17972,8 +18119,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6695311" y="1376132"/>
-        <a:ext cx="3146531" cy="343368"/>
+        <a:off x="6672294" y="1419402"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7682FEBA-2A8A-4CEB-BAD3-CAC6D62452E9}">
@@ -17983,8 +18130,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9852525" y="1543706"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9818046" y="1586419"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17995,10 +18142,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18053,8 +18200,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9955792" y="1542381"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9920939" y="1585048"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4C2C55F9-D12D-4BE1-85AD-8FAFF8B344C7}">
@@ -18064,8 +18211,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10069930" y="1363668"/>
-          <a:ext cx="1807704" cy="368297"/>
+          <a:off x="10034662" y="1406983"/>
+          <a:ext cx="1801141" cy="366960"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -18183,8 +18330,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10080717" y="1374455"/>
-        <a:ext cx="1786130" cy="346723"/>
+        <a:off x="10045410" y="1417731"/>
+        <a:ext cx="1779645" cy="345464"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6A4076F7-5C10-4205-AF7B-34977DAE41B6}">
@@ -18194,8 +18341,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19004863">
-          <a:off x="4433100" y="2055032"/>
-          <a:ext cx="298492" cy="8220"/>
+          <a:off x="4418296" y="2095888"/>
+          <a:ext cx="297408" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18206,10 +18353,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="298492" y="4110"/>
+                <a:pt x="297408" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18264,8 +18411,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4574883" y="2051680"/>
-        <a:ext cx="14924" cy="14924"/>
+        <a:off x="4559565" y="2092498"/>
+        <a:ext cx="14870" cy="14870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D2D6EBAC-87C6-4589-B626-76CA00356F2A}">
@@ -18275,8 +18422,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4691048" y="1774510"/>
-          <a:ext cx="1776175" cy="364734"/>
+          <a:off x="4675308" y="1816334"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -18346,8 +18493,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4701731" y="1785193"/>
-        <a:ext cx="1754809" cy="343368"/>
+        <a:off x="4685952" y="1826978"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4CEC118E-B718-4A3D-A714-E879160F0F50}">
@@ -18357,8 +18504,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6467223" y="1952767"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="6445035" y="1993994"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18369,10 +18516,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18427,8 +18574,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6570490" y="1951442"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="6547927" y="1992623"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{96C9B796-69AA-48A9-AB67-0FE5F7CEFC9D}">
@@ -18438,8 +18585,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6684628" y="1774510"/>
-          <a:ext cx="3167897" cy="364734"/>
+          <a:off x="6661650" y="1816334"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -18533,8 +18680,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6695311" y="1785193"/>
-        <a:ext cx="3146531" cy="343368"/>
+        <a:off x="6672294" y="1826978"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{0C4A9E51-DEA5-4AC0-B8EC-F712BFE3BA51}">
@@ -18544,8 +18691,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9852525" y="1952767"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9818046" y="1993994"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18556,10 +18703,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18614,8 +18761,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9955792" y="1951442"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9920939" y="1992623"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{829A6295-4379-4C15-BF91-56D56B48CA13}">
@@ -18625,8 +18772,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10069930" y="1772728"/>
-          <a:ext cx="1807704" cy="368297"/>
+          <a:off x="10034662" y="1814559"/>
+          <a:ext cx="1801141" cy="366960"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -18712,8 +18859,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10080717" y="1783515"/>
-        <a:ext cx="1786130" cy="346723"/>
+        <a:off x="10045410" y="1825307"/>
+        <a:ext cx="1779645" cy="345464"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{15251D3B-5937-4D92-B910-59FBB0B78504}">
@@ -18723,8 +18870,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2595137">
-          <a:off x="4433100" y="2259562"/>
-          <a:ext cx="298492" cy="8220"/>
+          <a:off x="4418296" y="2299676"/>
+          <a:ext cx="297408" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18735,10 +18882,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="298492" y="4110"/>
+                <a:pt x="297408" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18793,8 +18940,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4574883" y="2256210"/>
-        <a:ext cx="14924" cy="14924"/>
+        <a:off x="4559565" y="2296285"/>
+        <a:ext cx="14870" cy="14870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{55C8ECFC-533A-4D04-B170-164B29EE9A7D}">
@@ -18804,8 +18951,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4691048" y="2183570"/>
-          <a:ext cx="1776175" cy="364734"/>
+          <a:off x="4675308" y="2223909"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -18875,8 +19022,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4701731" y="2194253"/>
-        <a:ext cx="1754809" cy="343368"/>
+        <a:off x="4685952" y="2234553"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A63458DA-4732-44A8-AAAD-101471030A2E}">
@@ -18886,8 +19033,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6467223" y="2361827"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="6445035" y="2401570"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18898,10 +19045,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18956,8 +19103,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6570490" y="2360502"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="6547927" y="2400199"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{3CFC9EAC-3C3A-42EE-A809-37090C958CCC}">
@@ -18967,8 +19114,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6684628" y="2183570"/>
-          <a:ext cx="3167897" cy="364734"/>
+          <a:off x="6661650" y="2223909"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19046,8 +19193,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6695311" y="2194253"/>
-        <a:ext cx="3146531" cy="343368"/>
+        <a:off x="6672294" y="2234553"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{2E1BE310-D0FB-4439-BC13-EF25298A0AC1}">
@@ -19057,8 +19204,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9852525" y="2361827"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9818046" y="2401570"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19069,10 +19216,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19127,8 +19274,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9955792" y="2360502"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9920939" y="2400199"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{05029C16-99B1-4993-B5A7-DFCE2EC4AF2D}">
@@ -19138,8 +19285,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10069930" y="2181789"/>
-          <a:ext cx="1807704" cy="368297"/>
+          <a:off x="10034662" y="2222134"/>
+          <a:ext cx="1801141" cy="366960"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19209,8 +19356,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10080717" y="2192576"/>
-        <a:ext cx="1786130" cy="346723"/>
+        <a:off x="10045410" y="2232882"/>
+        <a:ext cx="1779645" cy="345464"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7B1A1F24-5790-42BE-9800-70C6BAC67F71}">
@@ -19220,8 +19367,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="4229399">
-          <a:off x="4256862" y="2464092"/>
-          <a:ext cx="650967" cy="8220"/>
+          <a:off x="4242699" y="2503464"/>
+          <a:ext cx="648604" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19232,10 +19379,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="650967" y="4110"/>
+                <a:pt x="648604" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19290,8 +19437,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4566071" y="2451929"/>
-        <a:ext cx="32548" cy="32548"/>
+        <a:off x="4550785" y="2491293"/>
+        <a:ext cx="32430" cy="32430"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{F9E7099E-D348-4A20-924E-7B36E8E1B00D}">
@@ -19301,8 +19448,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4691048" y="2592631"/>
-          <a:ext cx="1794725" cy="364734"/>
+          <a:off x="4675308" y="2631485"/>
+          <a:ext cx="1788209" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19372,8 +19519,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4701731" y="2603314"/>
-        <a:ext cx="1773359" cy="343368"/>
+        <a:off x="4685952" y="2642129"/>
+        <a:ext cx="1766921" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{69A95BFF-166E-4390-9963-14C8F025ADBA}">
@@ -19383,8 +19530,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6485773" y="2770888"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="6463518" y="2809145"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19395,10 +19542,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19453,8 +19600,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6589040" y="2769563"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="6566410" y="2807775"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{BBDCC5A6-74D1-4E37-848C-BF5D7C733A0C}">
@@ -19464,8 +19611,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6703178" y="2592631"/>
-          <a:ext cx="3167897" cy="364734"/>
+          <a:off x="6680133" y="2631485"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19535,8 +19682,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6713861" y="2603314"/>
-        <a:ext cx="3146531" cy="343368"/>
+        <a:off x="6690777" y="2642129"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E75A9ED0-3CF3-4FBB-B735-763677226156}">
@@ -19546,8 +19693,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9871075" y="2770888"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9836529" y="2809145"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19558,10 +19705,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19616,8 +19763,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9974342" y="2769563"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9939421" y="2807775"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D255C67C-B87B-4D25-A5F4-B2880DE74996}">
@@ -19627,8 +19774,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10088480" y="2590850"/>
-          <a:ext cx="1807704" cy="368297"/>
+          <a:off x="10053144" y="2629710"/>
+          <a:ext cx="1801141" cy="366960"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19722,8 +19869,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10099267" y="2601637"/>
-        <a:ext cx="1786130" cy="346723"/>
+        <a:off x="10063892" y="2640458"/>
+        <a:ext cx="1779645" cy="345464"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{19133C7D-D6FC-4086-9EFA-C8E67C09EF92}">
@@ -19733,8 +19880,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="4842573">
-          <a:off x="2284276" y="2719978"/>
-          <a:ext cx="1346666" cy="8220"/>
+          <a:off x="2277274" y="2758420"/>
+          <a:ext cx="1341777" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19745,10 +19892,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1346666" y="4110"/>
+                <a:pt x="1341777" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19803,8 +19950,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2923942" y="2690422"/>
-        <a:ext cx="67333" cy="67333"/>
+        <a:off x="2914618" y="2728920"/>
+        <a:ext cx="67088" cy="67088"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{3A58F96D-43A0-4E22-A03B-64FF8A7610E3}">
@@ -19814,8 +19961,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3066312" y="3207818"/>
-          <a:ext cx="1407331" cy="361541"/>
+          <a:off x="3056471" y="3244439"/>
+          <a:ext cx="1402222" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19885,8 +20032,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3076901" y="3218407"/>
-        <a:ext cx="1386153" cy="340363"/>
+        <a:off x="3067022" y="3254990"/>
+        <a:ext cx="1381120" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{BC1A1E23-E0C9-4175-8735-D110618B99B3}">
@@ -19896,8 +20043,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19004863">
-          <a:off x="4433100" y="3282214"/>
-          <a:ext cx="298492" cy="8220"/>
+          <a:off x="4418296" y="3318615"/>
+          <a:ext cx="297408" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19908,10 +20055,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="298492" y="4110"/>
+                <a:pt x="297408" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19966,8 +20113,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4574883" y="3278862"/>
-        <a:ext cx="14924" cy="14924"/>
+        <a:off x="4559565" y="3315224"/>
+        <a:ext cx="14870" cy="14870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{5D691BA5-158A-4034-AEDA-B152BE077B27}">
@@ -19977,8 +20124,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4691048" y="3001692"/>
-          <a:ext cx="1776175" cy="364734"/>
+          <a:off x="4675308" y="3039060"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20048,8 +20195,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4701731" y="3012375"/>
-        <a:ext cx="1754809" cy="343368"/>
+        <a:off x="4685952" y="3049704"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{C26309FF-9296-40B3-913C-85759C2B07DC}">
@@ -20059,8 +20206,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6467223" y="3179948"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="6445035" y="3216721"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20071,10 +20218,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20129,8 +20276,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6570490" y="3178624"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="6547927" y="3215350"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A4750321-4845-43B0-945B-4B9E7C7A668E}">
@@ -20140,8 +20287,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6684628" y="3001692"/>
-          <a:ext cx="3167897" cy="364734"/>
+          <a:off x="6661650" y="3039060"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20235,8 +20382,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6695311" y="3012375"/>
-        <a:ext cx="3146531" cy="343368"/>
+        <a:off x="6672294" y="3049704"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{CCE9C4CE-7CF8-4820-8390-F3CBCCE81ED7}">
@@ -20246,8 +20393,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9852525" y="3179948"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9818046" y="3216721"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20258,10 +20405,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20316,8 +20463,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9955792" y="3178624"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9920939" y="3215350"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D954D938-3009-44F7-BB4F-D9E8AFB2B291}">
@@ -20327,8 +20474,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10069930" y="2999910"/>
-          <a:ext cx="1807704" cy="368297"/>
+          <a:off x="10034662" y="3037285"/>
+          <a:ext cx="1801141" cy="366960"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20398,8 +20545,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10080717" y="3010697"/>
-        <a:ext cx="1786130" cy="346723"/>
+        <a:off x="10045410" y="3048033"/>
+        <a:ext cx="1779645" cy="345464"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D01C8F64-85EC-45F5-B192-363D2A57FB6E}">
@@ -20409,8 +20556,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2595137">
-          <a:off x="4433100" y="3486744"/>
-          <a:ext cx="298492" cy="8220"/>
+          <a:off x="4418296" y="3522403"/>
+          <a:ext cx="297408" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20421,10 +20568,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="298492" y="4110"/>
+                <a:pt x="297408" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20479,8 +20626,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4574883" y="3483392"/>
-        <a:ext cx="14924" cy="14924"/>
+        <a:off x="4559565" y="3519012"/>
+        <a:ext cx="14870" cy="14870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7832722B-5DD1-4AAD-819C-BC966C90EDAC}">
@@ -20490,8 +20637,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4691048" y="3410752"/>
-          <a:ext cx="1776175" cy="364734"/>
+          <a:off x="4675308" y="3446636"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20561,8 +20708,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4701731" y="3421435"/>
-        <a:ext cx="1754809" cy="343368"/>
+        <a:off x="4685952" y="3457280"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9B049FA9-70FB-4D7E-AD76-2BFCDB3B4195}">
@@ -20572,8 +20719,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6467223" y="3589009"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="6445035" y="3624296"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20584,10 +20731,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20642,8 +20789,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6570490" y="3587684"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="6547927" y="3622926"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B5153D0A-E9E7-482C-B1CC-838341F8F3D8}">
@@ -20653,8 +20800,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6684628" y="3410752"/>
-          <a:ext cx="3167897" cy="364734"/>
+          <a:off x="6661650" y="3446636"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20740,8 +20887,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6695311" y="3421435"/>
-        <a:ext cx="3146531" cy="343368"/>
+        <a:off x="6672294" y="3457280"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1118BB77-BCCA-46BE-8B0C-417EE0F19393}">
@@ -20751,8 +20898,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9852525" y="3589009"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9818046" y="3624296"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20763,10 +20910,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20821,8 +20968,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9955792" y="3587684"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9920939" y="3622926"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A1FE2FD1-D3B2-4F02-B33F-7EA3496A9D7D}">
@@ -20832,8 +20979,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10069930" y="3408971"/>
-          <a:ext cx="1807704" cy="368297"/>
+          <a:off x="10034662" y="3444861"/>
+          <a:ext cx="1801141" cy="366960"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20903,8 +21050,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10080717" y="3419758"/>
-        <a:ext cx="1786130" cy="346723"/>
+        <a:off x="10045410" y="3455609"/>
+        <a:ext cx="1779645" cy="345464"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{ACD64E2A-6A03-49D1-9C11-853B1D5FDA3F}">
@@ -20914,8 +21061,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="4880920">
-          <a:off x="572912" y="4198773"/>
-          <a:ext cx="1445308" cy="8220"/>
+          <a:off x="572123" y="4231846"/>
+          <a:ext cx="1440061" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20926,10 +21073,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1445308" y="4110"/>
+                <a:pt x="1440061" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20984,8 +21131,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1259433" y="4166750"/>
-        <a:ext cx="72265" cy="72265"/>
+        <a:off x="1256152" y="4199889"/>
+        <a:ext cx="72003" cy="72003"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4915DA81-5EFF-4A45-B117-A1C9369BA960}">
@@ -20995,8 +21142,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="1404269" y="4736544"/>
-          <a:ext cx="1437708" cy="361541"/>
+          <a:off x="1400462" y="4767614"/>
+          <a:ext cx="1432488" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21118,8 +21265,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1414858" y="4747133"/>
-        <a:ext cx="1416530" cy="340363"/>
+        <a:off x="1411013" y="4778165"/>
+        <a:ext cx="1411386" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A3777E34-F7A1-4ABC-99E9-9C9A9AB7B959}">
@@ -21129,8 +21276,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17225057">
-          <a:off x="2585877" y="4566573"/>
-          <a:ext cx="725267" cy="8220"/>
+          <a:off x="2577781" y="4598311"/>
+          <a:ext cx="722633" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21141,10 +21288,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="725267" y="4110"/>
+                <a:pt x="722633" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21199,8 +21346,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2930379" y="4552551"/>
-        <a:ext cx="36263" cy="36263"/>
+        <a:off x="2921032" y="4584290"/>
+        <a:ext cx="36131" cy="36131"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{23228D17-0E30-4278-86F1-009AEEE4B90D}">
@@ -21210,8 +21357,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3055045" y="4043280"/>
-          <a:ext cx="1407331" cy="361541"/>
+          <a:off x="3045245" y="4076868"/>
+          <a:ext cx="1402222" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21281,8 +21428,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3065634" y="4053869"/>
-        <a:ext cx="1386153" cy="340363"/>
+        <a:off x="3055796" y="4087419"/>
+        <a:ext cx="1381120" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A22E3146-1836-4A0C-A6D3-4503A76A9781}">
@@ -21292,8 +21439,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19004863">
-          <a:off x="4421833" y="4117676"/>
-          <a:ext cx="298492" cy="8220"/>
+          <a:off x="4407070" y="4151044"/>
+          <a:ext cx="297408" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21304,10 +21451,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="298492" y="4110"/>
+                <a:pt x="297408" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21362,8 +21509,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4563616" y="4114324"/>
-        <a:ext cx="14924" cy="14924"/>
+        <a:off x="4548339" y="4147653"/>
+        <a:ext cx="14870" cy="14870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{06E3AC3D-2CA5-4C28-B4EE-08E1F5093575}">
@@ -21373,8 +21520,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4679781" y="3837154"/>
-          <a:ext cx="1776175" cy="364734"/>
+          <a:off x="4664082" y="3871489"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21460,8 +21607,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4690464" y="3847837"/>
-        <a:ext cx="1754809" cy="343368"/>
+        <a:off x="4674726" y="3882133"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{AB38F8C9-39F9-48F1-A4B9-359AD3B6C9E1}">
@@ -21471,8 +21618,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6455956" y="4015410"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="6433809" y="4049150"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21483,10 +21630,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21541,8 +21688,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6559223" y="4014086"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="6536701" y="4047779"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{94E3E4AC-563C-467A-AD10-294BF8A33BAF}">
@@ -21552,8 +21699,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6673361" y="3837154"/>
-          <a:ext cx="3167897" cy="364734"/>
+          <a:off x="6650424" y="3871489"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21639,8 +21786,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6684044" y="3847837"/>
-        <a:ext cx="3146531" cy="343368"/>
+        <a:off x="6661068" y="3882133"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{CE4A2E59-3DB6-4586-9EDA-16655120708B}">
@@ -21650,8 +21797,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9841258" y="4015410"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9806820" y="4049150"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21662,10 +21809,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21720,8 +21867,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9944525" y="4014086"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9909712" y="4047779"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{74F8E0C0-A1C2-4026-BDD1-211E4452BF84}">
@@ -21731,8 +21878,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10058663" y="3835372"/>
-          <a:ext cx="1807704" cy="368297"/>
+          <a:off x="10023436" y="3869714"/>
+          <a:ext cx="1801141" cy="366960"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21802,8 +21949,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10069450" y="3846159"/>
-        <a:ext cx="1786130" cy="346723"/>
+        <a:off x="10034184" y="3880462"/>
+        <a:ext cx="1779645" cy="345464"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{3776BE60-D86F-469E-9605-E0609281B4B9}">
@@ -21813,8 +21960,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2595137">
-          <a:off x="4421833" y="4322206"/>
-          <a:ext cx="298492" cy="8220"/>
+          <a:off x="4407070" y="4354831"/>
+          <a:ext cx="297408" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21825,10 +21972,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="298492" y="4110"/>
+                <a:pt x="297408" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21883,8 +22030,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4563616" y="4318854"/>
-        <a:ext cx="14924" cy="14924"/>
+        <a:off x="4548339" y="4351441"/>
+        <a:ext cx="14870" cy="14870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{DC0F0790-8247-4EA1-A5BD-20B9C2810EA5}">
@@ -21894,8 +22041,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4679781" y="4246214"/>
-          <a:ext cx="1776175" cy="364734"/>
+          <a:off x="4664082" y="4279065"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21965,8 +22112,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4690464" y="4256897"/>
-        <a:ext cx="1754809" cy="343368"/>
+        <a:off x="4674726" y="4289709"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{82B78A4F-EF07-4DEA-A3EC-7BA9DD55DC45}">
@@ -21976,8 +22123,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6455956" y="4424471"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="6433809" y="4456725"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21988,10 +22135,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22046,8 +22193,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6559223" y="4423146"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="6536701" y="4455354"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4D82C0F8-05DA-476F-9FFD-EF5362E37ABC}">
@@ -22057,8 +22204,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6673361" y="4246214"/>
-          <a:ext cx="3167897" cy="364734"/>
+          <a:off x="6650424" y="4279065"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22136,8 +22283,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6684044" y="4256897"/>
-        <a:ext cx="3146531" cy="343368"/>
+        <a:off x="6661068" y="4289709"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6F09ED48-69E5-4359-AEF9-003C31CF3834}">
@@ -22147,8 +22294,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9841258" y="4424471"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9806820" y="4456725"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22159,10 +22306,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22217,8 +22364,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9944525" y="4423146"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9909712" y="4455354"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7F4C8494-F5DD-49F1-B7FE-320AAF64A334}">
@@ -22228,8 +22375,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10058663" y="4244433"/>
-          <a:ext cx="1807704" cy="368297"/>
+          <a:off x="10023436" y="4277290"/>
+          <a:ext cx="1801141" cy="366960"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22304,8 +22451,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10069450" y="4255220"/>
-        <a:ext cx="1786130" cy="346723"/>
+        <a:off x="10034184" y="4288038"/>
+        <a:ext cx="1779645" cy="345464"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E97A89EA-A088-4B36-94ED-03E39FF28C24}">
@@ -22315,8 +22462,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="1512707">
-          <a:off x="2830532" y="4964383"/>
-          <a:ext cx="240295" cy="8220"/>
+          <a:off x="2821547" y="4994677"/>
+          <a:ext cx="239423" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22327,10 +22474,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="240295" y="4110"/>
+                <a:pt x="239423" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22385,8 +22532,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2944672" y="4962486"/>
-        <a:ext cx="12014" cy="12014"/>
+        <a:off x="2935273" y="4992736"/>
+        <a:ext cx="11971" cy="11971"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1279AA60-C872-4597-B281-C6CC2E4A34C2}">
@@ -22396,8 +22543,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3059382" y="4838902"/>
-          <a:ext cx="1407331" cy="361541"/>
+          <a:off x="3049566" y="4869600"/>
+          <a:ext cx="1402222" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22467,8 +22614,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3069971" y="4849491"/>
-        <a:ext cx="1386153" cy="340363"/>
+        <a:off x="3060117" y="4880151"/>
+        <a:ext cx="1381120" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{255CD393-ED80-4D10-A68E-31ED59592E3B}">
@@ -22478,8 +22625,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19138242">
-          <a:off x="4432026" y="4922858"/>
-          <a:ext cx="282442" cy="8220"/>
+          <a:off x="4417227" y="4953303"/>
+          <a:ext cx="281417" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22490,10 +22637,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="282442" y="4110"/>
+                <a:pt x="281417" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22548,8 +22695,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4566186" y="4919907"/>
-        <a:ext cx="14122" cy="14122"/>
+        <a:off x="4550900" y="4950312"/>
+        <a:ext cx="14070" cy="14070"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{2340676A-EBD4-4E22-BA9C-E56B6A62904C}">
@@ -22559,8 +22706,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4679781" y="4651897"/>
-          <a:ext cx="1776175" cy="364734"/>
+          <a:off x="4664082" y="4683274"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22630,8 +22777,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4690464" y="4662580"/>
-        <a:ext cx="1754809" cy="343368"/>
+        <a:off x="4674726" y="4693918"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{EB837690-03CF-4B39-A4B0-AFC71E15928A}">
@@ -22641,8 +22788,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="27806">
-          <a:off x="6455952" y="4831051"/>
-          <a:ext cx="221749" cy="8220"/>
+          <a:off x="6433805" y="4861829"/>
+          <a:ext cx="220944" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22653,10 +22800,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="221749" y="4110"/>
+                <a:pt x="220944" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22711,8 +22858,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6561283" y="4829617"/>
-        <a:ext cx="11087" cy="11087"/>
+        <a:off x="6538754" y="4860350"/>
+        <a:ext cx="11047" cy="11047"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6CD3FE0A-3BBE-455B-B381-72424654A1B0}">
@@ -22722,8 +22869,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6677698" y="4655287"/>
-          <a:ext cx="3167092" cy="361541"/>
+          <a:off x="6654746" y="4686652"/>
+          <a:ext cx="3155594" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22801,8 +22948,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6688287" y="4665876"/>
-        <a:ext cx="3145914" cy="340363"/>
+        <a:off x="6665297" y="4697203"/>
+        <a:ext cx="3134492" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B86CABA2-1933-4D02-A0D3-AA6DEA35BCA7}">
@@ -22812,8 +22959,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9844791" y="4831947"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9810340" y="4862722"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22824,10 +22971,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22882,8 +23029,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9948058" y="4830623"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9913232" y="4861351"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{920A36CD-D69B-4AB0-8DA2-4963F1111FE2}">
@@ -22893,8 +23040,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10062195" y="4655287"/>
-          <a:ext cx="1807704" cy="361541"/>
+          <a:off x="10026956" y="4686652"/>
+          <a:ext cx="1801141" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22964,8 +23111,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10072784" y="4665876"/>
-        <a:ext cx="1786526" cy="340363"/>
+        <a:off x="10037507" y="4697203"/>
+        <a:ext cx="1780039" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{EE30240B-4D3F-4585-94A4-7AD0CBEBACD0}">
@@ -22975,8 +23122,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2755727">
-          <a:off x="4420083" y="5125607"/>
-          <a:ext cx="306328" cy="8220"/>
+          <a:off x="4405327" y="5155316"/>
+          <a:ext cx="305216" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22987,10 +23134,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="306328" y="4110"/>
+                <a:pt x="305216" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23045,8 +23192,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4565589" y="5122059"/>
-        <a:ext cx="15316" cy="15316"/>
+        <a:off x="4550305" y="5151730"/>
+        <a:ext cx="15260" cy="15260"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9B0332A1-DFA5-4E72-89B6-8E8C50F667E1}">
@@ -23056,8 +23203,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4679781" y="5057395"/>
-          <a:ext cx="1776175" cy="364734"/>
+          <a:off x="4664082" y="5087300"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23154,8 +23301,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4690464" y="5068078"/>
-        <a:ext cx="1754809" cy="343368"/>
+        <a:off x="4674726" y="5097944"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4EF5B1E7-3D92-44D9-8E8A-E2A10FB649AC}">
@@ -23165,8 +23312,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="27806">
-          <a:off x="6455952" y="5236548"/>
-          <a:ext cx="221749" cy="8220"/>
+          <a:off x="6433805" y="5265854"/>
+          <a:ext cx="220944" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23177,10 +23324,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="221749" y="4110"/>
+                <a:pt x="220944" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23235,8 +23382,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6561283" y="5235115"/>
-        <a:ext cx="11087" cy="11087"/>
+        <a:off x="6538754" y="5264375"/>
+        <a:ext cx="11047" cy="11047"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9AC7A0EB-B59E-41D9-A589-CB90FBF4305E}">
@@ -23246,8 +23393,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6677698" y="5060785"/>
-          <a:ext cx="3167092" cy="361541"/>
+          <a:off x="6654746" y="5090678"/>
+          <a:ext cx="3155594" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23333,8 +23480,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6688287" y="5071374"/>
-        <a:ext cx="3145914" cy="340363"/>
+        <a:off x="6665297" y="5101229"/>
+        <a:ext cx="3134492" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{2F5A23ED-2B4B-4307-BAD6-D126CED4ED45}">
@@ -23344,8 +23491,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9844791" y="5237445"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9810340" y="5266748"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23356,10 +23503,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23414,8 +23561,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9948058" y="5236121"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9913232" y="5265377"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{C9CCA1DF-737F-40B9-8662-1EBAE874B88C}">
@@ -23425,8 +23572,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10062195" y="5060785"/>
-          <a:ext cx="1807704" cy="361541"/>
+          <a:off x="10026956" y="5090678"/>
+          <a:ext cx="1801141" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23496,8 +23643,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10072784" y="5071374"/>
-        <a:ext cx="1786526" cy="340363"/>
+        <a:off x="10037507" y="5101229"/>
+        <a:ext cx="1780039" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{06804470-2E4E-45CC-AD07-54CD8F165228}">
@@ -23507,8 +23654,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="4379331">
-          <a:off x="2579121" y="5268507"/>
-          <a:ext cx="743117" cy="8220"/>
+          <a:off x="2571049" y="5297697"/>
+          <a:ext cx="740419" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23519,10 +23666,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="743117" y="4110"/>
+                <a:pt x="740419" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23577,8 +23724,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2932101" y="5254039"/>
-        <a:ext cx="37155" cy="37155"/>
+        <a:off x="2922748" y="5283231"/>
+        <a:ext cx="37020" cy="37020"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D9D1FF4E-B146-4A17-8BAD-E6A8247731B1}">
@@ -23588,8 +23735,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3059382" y="5447149"/>
-          <a:ext cx="1407337" cy="361541"/>
+          <a:off x="3049566" y="5475639"/>
+          <a:ext cx="1402227" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23675,8 +23822,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3069971" y="5457738"/>
-        <a:ext cx="1386159" cy="340363"/>
+        <a:off x="3060117" y="5486190"/>
+        <a:ext cx="1381125" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{458C594D-E94A-4416-A27A-8211BD0C18EB}">
@@ -23686,8 +23833,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4466719" y="5623809"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="4451794" y="5651709"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23698,10 +23845,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23756,8 +23903,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4569986" y="5622484"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="4554686" y="5650338"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E6BB35B6-4DC7-42B5-A329-D93F595605BC}">
@@ -23767,8 +23914,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4684124" y="5445552"/>
-          <a:ext cx="1765668" cy="364734"/>
+          <a:off x="4668409" y="5474048"/>
+          <a:ext cx="1759258" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23854,8 +24001,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4694807" y="5456235"/>
-        <a:ext cx="1744302" cy="343368"/>
+        <a:off x="4679053" y="5484692"/>
+        <a:ext cx="1737970" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{F3CE9778-2DAD-459C-A92D-C581128238EF}">
@@ -23865,8 +24012,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6449793" y="5623809"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="6427668" y="5651709"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23877,10 +24024,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23935,8 +24082,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6553060" y="5622484"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="6530560" y="5650338"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A62201D7-F2CC-41E5-BB68-F68B79E1464B}">
@@ -23946,8 +24093,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6667197" y="5447149"/>
-          <a:ext cx="3167092" cy="361541"/>
+          <a:off x="6644283" y="5475639"/>
+          <a:ext cx="3155594" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -24017,8 +24164,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6677786" y="5457738"/>
-        <a:ext cx="3145914" cy="340363"/>
+        <a:off x="6654834" y="5486190"/>
+        <a:ext cx="3134492" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{46794C65-61A0-4B52-A42E-5CC9D77E3723}">
@@ -24028,8 +24175,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9834290" y="5623809"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9799878" y="5651709"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -24040,10 +24187,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -24098,8 +24245,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9937557" y="5622484"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9902770" y="5650338"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{C61F938B-5A64-4BF7-B003-81E0909084B1}">
@@ -24109,8 +24256,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10051695" y="5447149"/>
-          <a:ext cx="1807704" cy="361541"/>
+          <a:off x="10016493" y="5475639"/>
+          <a:ext cx="1801141" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -24180,8 +24327,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10062284" y="5457738"/>
-        <a:ext cx="1786526" cy="340363"/>
+        <a:off x="10027044" y="5486190"/>
+        <a:ext cx="1780039" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
   </dsp:spTree>
@@ -28010,7 +28157,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="25.9140625" style="32" customWidth="1"/>
@@ -28079,7 +28226,9 @@
       <c r="A5" s="34" t="s">
         <v>172</v>
       </c>
-      <c r="B5" s="33"/>
+      <c r="B5" s="105" t="s">
+        <v>450</v>
+      </c>
       <c r="C5" s="35">
         <v>46275</v>
       </c>
@@ -28088,32 +28237,36 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A6" s="33" t="s">
+      <c r="A6" s="102" t="s">
         <v>174</v>
       </c>
-      <c r="B6" s="33"/>
-      <c r="C6" s="35">
+      <c r="B6" s="106" t="s">
+        <v>451</v>
+      </c>
+      <c r="C6" s="103">
         <v>46275</v>
       </c>
-      <c r="D6" s="33" t="s">
+      <c r="D6" s="100" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A7" s="33" t="s">
-        <v>175</v>
-      </c>
-      <c r="B7" s="33"/>
-      <c r="C7" s="35">
-        <v>46276</v>
-      </c>
-      <c r="D7" s="33"/>
+      <c r="A7" s="102" t="s">
+        <v>174</v>
+      </c>
+      <c r="B7" s="107" t="s">
+        <v>452</v>
+      </c>
+      <c r="C7" s="104"/>
+      <c r="D7" s="101"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" s="33" t="s">
-        <v>176</v>
-      </c>
-      <c r="B8" s="33"/>
+        <v>175</v>
+      </c>
+      <c r="B8" s="108" t="s">
+        <v>453</v>
+      </c>
       <c r="C8" s="35">
         <v>46276</v>
       </c>
@@ -28121,34 +28274,53 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" s="33" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B9" s="33"/>
       <c r="C9" s="35">
         <v>46276</v>
       </c>
-      <c r="D9" s="33" t="s">
-        <v>320</v>
-      </c>
+      <c r="D9" s="33"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" s="33" t="s">
+        <v>177</v>
+      </c>
+      <c r="B10" s="33"/>
+      <c r="C10" s="35">
+        <v>46276</v>
+      </c>
+      <c r="D10" s="33" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A11" s="33" t="s">
         <v>178</v>
       </c>
-      <c r="B10" s="33"/>
-      <c r="C10" s="55">
+      <c r="B11" s="33"/>
+      <c r="C11" s="55">
         <v>46279.645833333336</v>
       </c>
-      <c r="D10" s="33"/>
+      <c r="D11" s="33"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:D7"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="B3" location="'1. 문제 정의(가설 트리)'!A1" display="링크" xr:uid="{9B58827D-A9B6-4981-86A2-3CC3DF8472F8}"/>
     <hyperlink ref="B4" location="'2. 지표 지도 그리기'!A1" display="링크" xr:uid="{5F5F2A00-658D-459F-A336-5D9C21F7F45B}"/>
     <hyperlink ref="B2" location="Dictionary!A1" display="Starbucks Rewards App" xr:uid="{9C53DA75-F66E-47CA-93FD-9BD68A60C51A}"/>
+    <hyperlink ref="B5" location="'3. 원인 분해(로직 트리, 이슈 트리)'!A1" display="링크" xr:uid="{E2C1F5B7-0388-4231-BA6F-71D62D70E58A}"/>
+    <hyperlink ref="B6" location="'4-1 통계적 검증'!A1" display="검증전" xr:uid="{4D4B7E5E-D31F-46E8-AE77-4A82FC446F0B}"/>
+    <hyperlink ref="B7" location="'4-2 통계적 검증 결과'!A1" display="검증후" xr:uid="{74C75FD8-2793-4E12-83F0-89D06783033D}"/>
+    <hyperlink ref="B8" location="'5. 머신러닝 적용'!A1" display="진행하지 않음" xr:uid="{D0EB73E0-F138-4F21-BFB7-2E0024630222}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" scale="62" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -28195,7 +28367,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A2" s="68" t="s">
+      <c r="A2" s="69" t="s">
         <v>18</v>
       </c>
       <c r="B2" s="7" t="s">
@@ -28212,7 +28384,7 @@
       <c r="G2" s="10"/>
     </row>
     <row r="3" spans="1:7" ht="64" x14ac:dyDescent="0.45">
-      <c r="A3" s="69"/>
+      <c r="A3" s="70"/>
       <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
@@ -28229,7 +28401,7 @@
       <c r="G3" s="11"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A4" s="69"/>
+      <c r="A4" s="70"/>
       <c r="B4" s="4" t="s">
         <v>184</v>
       </c>
@@ -28244,7 +28416,7 @@
       <c r="G4" s="11"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A5" s="69"/>
+      <c r="A5" s="70"/>
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
@@ -28259,7 +28431,7 @@
       <c r="G5" s="11"/>
     </row>
     <row r="6" spans="1:7" ht="48" x14ac:dyDescent="0.45">
-      <c r="A6" s="69"/>
+      <c r="A6" s="70"/>
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
@@ -28278,7 +28450,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="70"/>
+      <c r="A7" s="71"/>
       <c r="B7" s="13" t="s">
         <v>15</v>
       </c>
@@ -28295,7 +28467,7 @@
       <c r="G7" s="15"/>
     </row>
     <row r="8" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="71" t="s">
+      <c r="A8" s="72" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="7" t="s">
@@ -28316,7 +28488,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A9" s="72"/>
+      <c r="A9" s="73"/>
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -28333,7 +28505,7 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A10" s="72"/>
+      <c r="A10" s="73"/>
       <c r="B10" s="4" t="s">
         <v>4</v>
       </c>
@@ -28350,7 +28522,7 @@
       <c r="G10" s="11"/>
     </row>
     <row r="11" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="72"/>
+      <c r="A11" s="73"/>
       <c r="B11" s="4" t="s">
         <v>7</v>
       </c>
@@ -28365,7 +28537,7 @@
       <c r="G11" s="11"/>
     </row>
     <row r="12" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="73"/>
+      <c r="A12" s="74"/>
       <c r="B12" s="16" t="s">
         <v>8</v>
       </c>
@@ -28382,7 +28554,7 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A13" s="74" t="s">
+      <c r="A13" s="75" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="7" t="s">
@@ -28403,7 +28575,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="64.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="75"/>
+      <c r="A14" s="76"/>
       <c r="B14" s="4" t="s">
         <v>10</v>
       </c>
@@ -28420,7 +28592,7 @@
       <c r="G14" s="11"/>
     </row>
     <row r="15" spans="1:7" ht="64" x14ac:dyDescent="0.45">
-      <c r="A15" s="75"/>
+      <c r="A15" s="76"/>
       <c r="B15" s="4" t="s">
         <v>218</v>
       </c>
@@ -28441,7 +28613,7 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A16" s="76"/>
+      <c r="A16" s="77"/>
       <c r="B16" s="16" t="s">
         <v>11</v>
       </c>
@@ -28588,14 +28760,14 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A5" s="84" t="s">
+      <c r="A5" s="79" t="s">
         <v>273</v>
       </c>
-      <c r="B5" s="84"/>
-      <c r="C5" s="84"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
     </row>
     <row r="6" spans="1:4" ht="32" x14ac:dyDescent="0.45">
-      <c r="A6" s="86" t="s">
+      <c r="A6" s="91" t="s">
         <v>204</v>
       </c>
       <c r="B6" s="47" t="s">
@@ -28606,7 +28778,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="32" x14ac:dyDescent="0.45">
-      <c r="A7" s="87"/>
+      <c r="A7" s="92"/>
       <c r="B7" s="47" t="s">
         <v>292</v>
       </c>
@@ -28615,7 +28787,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" ht="32" x14ac:dyDescent="0.45">
-      <c r="A8" s="87"/>
+      <c r="A8" s="92"/>
       <c r="B8" s="47" t="s">
         <v>295</v>
       </c>
@@ -28624,7 +28796,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A9" s="87"/>
+      <c r="A9" s="92"/>
       <c r="B9" s="47" t="s">
         <v>303</v>
       </c>
@@ -28633,7 +28805,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A10" s="88"/>
+      <c r="A10" s="93"/>
       <c r="B10" s="47" t="s">
         <v>297</v>
       </c>
@@ -28656,18 +28828,18 @@
       <c r="C12" s="49"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A13" s="78" t="s">
+      <c r="A13" s="84" t="s">
         <v>304</v>
       </c>
-      <c r="B13" s="79"/>
-      <c r="C13" s="80"/>
+      <c r="B13" s="85"/>
+      <c r="C13" s="86"/>
     </row>
     <row r="14" spans="1:4" ht="52" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="89" t="s">
+      <c r="A14" s="94" t="s">
         <v>230</v>
       </c>
-      <c r="B14" s="90"/>
-      <c r="C14" s="91"/>
+      <c r="B14" s="95"/>
+      <c r="C14" s="96"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="49"/>
@@ -28675,112 +28847,112 @@
       <c r="D19" s="49"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A31" s="84" t="s">
+      <c r="A31" s="79" t="s">
         <v>274</v>
       </c>
-      <c r="B31" s="84"/>
-      <c r="C31" s="84"/>
+      <c r="B31" s="79"/>
+      <c r="C31" s="79"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A32" s="81" t="s">
+      <c r="A32" s="87" t="s">
         <v>318</v>
       </c>
-      <c r="B32" s="82"/>
-      <c r="C32" s="83"/>
+      <c r="B32" s="88"/>
+      <c r="C32" s="89"/>
     </row>
     <row r="33" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="77" t="s">
+      <c r="A33" s="83" t="s">
         <v>231</v>
       </c>
       <c r="B33" s="50" t="s">
         <v>208</v>
       </c>
-      <c r="C33" s="85" t="s">
+      <c r="C33" s="90" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A34" s="77"/>
+      <c r="A34" s="83"/>
       <c r="B34" s="50" t="s">
         <v>209</v>
       </c>
-      <c r="C34" s="85"/>
+      <c r="C34" s="90"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A35" s="77"/>
+      <c r="A35" s="83"/>
       <c r="B35" s="50" t="s">
         <v>210</v>
       </c>
-      <c r="C35" s="85"/>
+      <c r="C35" s="90"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A36" s="77"/>
+      <c r="A36" s="83"/>
       <c r="B36" s="50" t="s">
         <v>211</v>
       </c>
-      <c r="C36" s="85"/>
+      <c r="C36" s="90"/>
     </row>
     <row r="37" spans="1:5" ht="32" x14ac:dyDescent="0.45">
-      <c r="A37" s="77"/>
+      <c r="A37" s="83"/>
       <c r="B37" s="48" t="s">
         <v>212</v>
       </c>
-      <c r="C37" s="85"/>
+      <c r="C37" s="90"/>
     </row>
     <row r="38" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="77" t="s">
+      <c r="A38" s="83" t="s">
         <v>232</v>
       </c>
       <c r="B38" s="50" t="s">
         <v>213</v>
       </c>
-      <c r="C38" s="85" t="s">
+      <c r="C38" s="90" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A39" s="77"/>
+      <c r="A39" s="83"/>
       <c r="B39" s="50" t="s">
         <v>214</v>
       </c>
-      <c r="C39" s="85"/>
+      <c r="C39" s="90"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A40" s="77"/>
+      <c r="A40" s="83"/>
       <c r="B40" s="50" t="s">
         <v>215</v>
       </c>
-      <c r="C40" s="85"/>
+      <c r="C40" s="90"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A42" s="78" t="s">
+      <c r="A42" s="84" t="s">
         <v>272</v>
       </c>
-      <c r="B42" s="79"/>
-      <c r="C42" s="80"/>
+      <c r="B42" s="85"/>
+      <c r="C42" s="86"/>
     </row>
     <row r="43" spans="1:5" ht="53" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A43" s="77" t="s">
+      <c r="A43" s="83" t="s">
         <v>217</v>
       </c>
-      <c r="B43" s="77"/>
-      <c r="C43" s="77"/>
+      <c r="B43" s="83"/>
+      <c r="C43" s="83"/>
     </row>
     <row r="44" spans="1:5" ht="50.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A44" s="77" t="s">
+      <c r="A44" s="83" t="s">
         <v>317</v>
       </c>
-      <c r="B44" s="77"/>
-      <c r="C44" s="77"/>
+      <c r="B44" s="83"/>
+      <c r="C44" s="83"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A46" s="84" t="s">
+      <c r="A46" s="79" t="s">
         <v>271</v>
       </c>
-      <c r="B46" s="84"/>
-      <c r="C46" s="84"/>
-      <c r="D46" s="84"/>
-      <c r="E46" s="84"/>
+      <c r="B46" s="79"/>
+      <c r="C46" s="79"/>
+      <c r="D46" s="79"/>
+      <c r="E46" s="79"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" s="44" t="s">
@@ -28966,11 +29138,11 @@
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A59" s="93" t="s">
+      <c r="A59" s="80" t="s">
         <v>275</v>
       </c>
-      <c r="B59" s="94"/>
-      <c r="C59" s="95"/>
+      <c r="B59" s="81"/>
+      <c r="C59" s="82"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" s="53" t="s">
@@ -29028,99 +29200,87 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A66" s="84" t="s">
+      <c r="A66" s="79" t="s">
         <v>291</v>
       </c>
-      <c r="B66" s="84"/>
-      <c r="C66" s="84"/>
-      <c r="D66" s="84"/>
+      <c r="B66" s="79"/>
+      <c r="C66" s="79"/>
+      <c r="D66" s="79"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A67" s="92" t="s">
+      <c r="A67" s="78" t="s">
         <v>262</v>
       </c>
-      <c r="B67" s="92"/>
-      <c r="C67" s="92"/>
-      <c r="D67" s="92"/>
+      <c r="B67" s="78"/>
+      <c r="C67" s="78"/>
+      <c r="D67" s="78"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A68" s="92" t="s">
+      <c r="A68" s="78" t="s">
         <v>263</v>
       </c>
-      <c r="B68" s="92"/>
-      <c r="C68" s="92"/>
-      <c r="D68" s="92"/>
+      <c r="B68" s="78"/>
+      <c r="C68" s="78"/>
+      <c r="D68" s="78"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A69" s="92" t="s">
+      <c r="A69" s="78" t="s">
         <v>264</v>
       </c>
-      <c r="B69" s="92"/>
-      <c r="C69" s="92"/>
-      <c r="D69" s="92"/>
+      <c r="B69" s="78"/>
+      <c r="C69" s="78"/>
+      <c r="D69" s="78"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A70" s="92" t="s">
+      <c r="A70" s="78" t="s">
         <v>265</v>
       </c>
-      <c r="B70" s="92"/>
-      <c r="C70" s="92"/>
-      <c r="D70" s="92"/>
+      <c r="B70" s="78"/>
+      <c r="C70" s="78"/>
+      <c r="D70" s="78"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A71" s="92" t="s">
+      <c r="A71" s="78" t="s">
         <v>266</v>
       </c>
-      <c r="B71" s="92"/>
-      <c r="C71" s="92"/>
-      <c r="D71" s="92"/>
+      <c r="B71" s="78"/>
+      <c r="C71" s="78"/>
+      <c r="D71" s="78"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A72" s="92" t="s">
+      <c r="A72" s="78" t="s">
         <v>267</v>
       </c>
-      <c r="B72" s="92"/>
-      <c r="C72" s="92"/>
-      <c r="D72" s="92"/>
+      <c r="B72" s="78"/>
+      <c r="C72" s="78"/>
+      <c r="D72" s="78"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A73" s="92" t="s">
+      <c r="A73" s="78" t="s">
         <v>268</v>
       </c>
-      <c r="B73" s="92"/>
-      <c r="C73" s="92"/>
-      <c r="D73" s="92"/>
+      <c r="B73" s="78"/>
+      <c r="C73" s="78"/>
+      <c r="D73" s="78"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A74" s="92" t="s">
+      <c r="A74" s="78" t="s">
         <v>269</v>
       </c>
-      <c r="B74" s="92"/>
-      <c r="C74" s="92"/>
-      <c r="D74" s="92"/>
+      <c r="B74" s="78"/>
+      <c r="C74" s="78"/>
+      <c r="D74" s="78"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A75" s="92" t="s">
+      <c r="A75" s="78" t="s">
         <v>270</v>
       </c>
-      <c r="B75" s="92"/>
-      <c r="C75" s="92"/>
-      <c r="D75" s="92"/>
+      <c r="B75" s="78"/>
+      <c r="C75" s="78"/>
+      <c r="D75" s="78"/>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A73:D73"/>
-    <mergeCell ref="A74:D74"/>
-    <mergeCell ref="A75:D75"/>
-    <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A66:D66"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A67:D67"/>
-    <mergeCell ref="A68:D68"/>
-    <mergeCell ref="A69:D69"/>
-    <mergeCell ref="A70:D70"/>
-    <mergeCell ref="A71:D71"/>
-    <mergeCell ref="A72:D72"/>
     <mergeCell ref="A44:C44"/>
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="A32:C32"/>
@@ -29134,6 +29294,18 @@
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="A74:D74"/>
+    <mergeCell ref="A75:D75"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A67:D67"/>
+    <mergeCell ref="A68:D68"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="A70:D70"/>
+    <mergeCell ref="A71:D71"/>
+    <mergeCell ref="A72:D72"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -29174,10 +29346,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A1" s="96" t="s">
+      <c r="A1" s="97" t="s">
         <v>336</v>
       </c>
-      <c r="B1" s="97"/>
+      <c r="B1" s="98"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="60" t="s">
@@ -29562,17 +29734,19 @@
   <sheetPr>
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.33203125" style="45" customWidth="1"/>
     <col min="2" max="2" width="49.5" style="45" customWidth="1"/>
     <col min="3" max="3" width="13.4140625" style="45" customWidth="1"/>
     <col min="4" max="6" width="77" style="45" customWidth="1"/>
-    <col min="7" max="16384" width="8.6640625" style="45"/>
+    <col min="7" max="7" width="55" style="99" customWidth="1"/>
+    <col min="8" max="8" width="39.9140625" style="45" customWidth="1"/>
+    <col min="9" max="16384" width="8.6640625" style="45"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" ht="16" x14ac:dyDescent="0.45">
       <c r="A1" s="62" t="s">
         <v>337</v>
       </c>
@@ -29582,18 +29756,24 @@
       <c r="C1" s="40" t="s">
         <v>195</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="109" t="s">
         <v>199</v>
       </c>
-      <c r="E1" s="40" t="s">
+      <c r="E1" s="109" t="s">
         <v>399</v>
       </c>
-      <c r="F1" s="40" t="s">
+      <c r="F1" s="109" t="s">
         <v>400</v>
       </c>
+      <c r="G1" s="40" t="s">
+        <v>424</v>
+      </c>
+      <c r="H1" s="40" t="s">
+        <v>425</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" ht="256" x14ac:dyDescent="0.45">
-      <c r="A2" s="98">
+    <row r="2" spans="1:8" ht="256" x14ac:dyDescent="0.45">
+      <c r="A2" s="68">
         <v>2</v>
       </c>
       <c r="B2" s="50" t="s">
@@ -29611,9 +29791,15 @@
       <c r="F2" s="48" t="s">
         <v>410</v>
       </c>
+      <c r="G2" s="43" t="s">
+        <v>426</v>
+      </c>
+      <c r="H2" s="43" t="s">
+        <v>427</v>
+      </c>
     </row>
-    <row r="3" spans="1:6" ht="208" x14ac:dyDescent="0.45">
-      <c r="A3" s="98">
+    <row r="3" spans="1:8" ht="208" x14ac:dyDescent="0.45">
+      <c r="A3" s="68">
         <v>4</v>
       </c>
       <c r="B3" s="50" t="s">
@@ -29631,9 +29817,15 @@
       <c r="F3" s="48" t="s">
         <v>411</v>
       </c>
+      <c r="G3" s="43" t="s">
+        <v>428</v>
+      </c>
+      <c r="H3" s="43" t="s">
+        <v>429</v>
+      </c>
     </row>
-    <row r="4" spans="1:6" ht="272" x14ac:dyDescent="0.45">
-      <c r="A4" s="98">
+    <row r="4" spans="1:8" ht="272" x14ac:dyDescent="0.45">
+      <c r="A4" s="68">
         <v>5</v>
       </c>
       <c r="B4" s="50" t="s">
@@ -29651,9 +29843,15 @@
       <c r="F4" s="48" t="s">
         <v>412</v>
       </c>
+      <c r="G4" s="43" t="s">
+        <v>430</v>
+      </c>
+      <c r="H4" s="43" t="s">
+        <v>431</v>
+      </c>
     </row>
-    <row r="5" spans="1:6" ht="192" x14ac:dyDescent="0.45">
-      <c r="A5" s="98">
+    <row r="5" spans="1:8" ht="192" x14ac:dyDescent="0.45">
+      <c r="A5" s="68">
         <v>6</v>
       </c>
       <c r="B5" s="50" t="s">
@@ -29671,9 +29869,15 @@
       <c r="F5" s="48" t="s">
         <v>413</v>
       </c>
+      <c r="G5" s="43" t="s">
+        <v>432</v>
+      </c>
+      <c r="H5" s="43" t="s">
+        <v>433</v>
+      </c>
     </row>
-    <row r="6" spans="1:6" ht="192" x14ac:dyDescent="0.45">
-      <c r="A6" s="98">
+    <row r="6" spans="1:8" ht="192" x14ac:dyDescent="0.45">
+      <c r="A6" s="68">
         <v>8</v>
       </c>
       <c r="B6" s="50" t="s">
@@ -29691,9 +29895,15 @@
       <c r="F6" s="48" t="s">
         <v>414</v>
       </c>
+      <c r="G6" s="43" t="s">
+        <v>434</v>
+      </c>
+      <c r="H6" s="43" t="s">
+        <v>435</v>
+      </c>
     </row>
-    <row r="7" spans="1:6" ht="224" x14ac:dyDescent="0.45">
-      <c r="A7" s="98">
+    <row r="7" spans="1:8" ht="224" x14ac:dyDescent="0.45">
+      <c r="A7" s="68">
         <v>9</v>
       </c>
       <c r="B7" s="50" t="s">
@@ -29711,9 +29921,15 @@
       <c r="F7" s="48" t="s">
         <v>415</v>
       </c>
+      <c r="G7" s="43" t="s">
+        <v>436</v>
+      </c>
+      <c r="H7" s="43" t="s">
+        <v>437</v>
+      </c>
     </row>
-    <row r="8" spans="1:6" ht="192" x14ac:dyDescent="0.45">
-      <c r="A8" s="98">
+    <row r="8" spans="1:8" ht="192" x14ac:dyDescent="0.45">
+      <c r="A8" s="68">
         <v>10</v>
       </c>
       <c r="B8" s="50" t="s">
@@ -29731,9 +29947,15 @@
       <c r="F8" s="48" t="s">
         <v>416</v>
       </c>
+      <c r="G8" s="43" t="s">
+        <v>438</v>
+      </c>
+      <c r="H8" s="43" t="s">
+        <v>439</v>
+      </c>
     </row>
-    <row r="9" spans="1:6" ht="320" x14ac:dyDescent="0.45">
-      <c r="A9" s="98">
+    <row r="9" spans="1:8" ht="320" x14ac:dyDescent="0.45">
+      <c r="A9" s="68">
         <v>11</v>
       </c>
       <c r="B9" s="50" t="s">
@@ -29751,9 +29973,15 @@
       <c r="F9" s="48" t="s">
         <v>417</v>
       </c>
+      <c r="G9" s="43" t="s">
+        <v>440</v>
+      </c>
+      <c r="H9" s="43" t="s">
+        <v>441</v>
+      </c>
     </row>
-    <row r="10" spans="1:6" ht="272" x14ac:dyDescent="0.45">
-      <c r="A10" s="98">
+    <row r="10" spans="1:8" ht="272" x14ac:dyDescent="0.45">
+      <c r="A10" s="68">
         <v>12</v>
       </c>
       <c r="B10" s="50" t="s">
@@ -29771,9 +29999,15 @@
       <c r="F10" s="48" t="s">
         <v>418</v>
       </c>
+      <c r="G10" s="43" t="s">
+        <v>442</v>
+      </c>
+      <c r="H10" s="43" t="s">
+        <v>443</v>
+      </c>
     </row>
-    <row r="11" spans="1:6" ht="224" x14ac:dyDescent="0.45">
-      <c r="A11" s="98">
+    <row r="11" spans="1:8" ht="224" x14ac:dyDescent="0.45">
+      <c r="A11" s="68">
         <v>13</v>
       </c>
       <c r="B11" s="50" t="s">
@@ -29791,9 +30025,15 @@
       <c r="F11" s="48" t="s">
         <v>419</v>
       </c>
+      <c r="G11" s="43" t="s">
+        <v>444</v>
+      </c>
+      <c r="H11" s="43" t="s">
+        <v>445</v>
+      </c>
     </row>
-    <row r="12" spans="1:6" ht="288" x14ac:dyDescent="0.45">
-      <c r="A12" s="98">
+    <row r="12" spans="1:8" ht="288" x14ac:dyDescent="0.45">
+      <c r="A12" s="68">
         <v>14</v>
       </c>
       <c r="B12" s="50" t="s">
@@ -29811,9 +30051,15 @@
       <c r="F12" s="48" t="s">
         <v>420</v>
       </c>
+      <c r="G12" s="43" t="s">
+        <v>446</v>
+      </c>
+      <c r="H12" s="43" t="s">
+        <v>447</v>
+      </c>
     </row>
-    <row r="13" spans="1:6" ht="144" x14ac:dyDescent="0.45">
-      <c r="A13" s="98" t="s">
+    <row r="13" spans="1:8" ht="144" x14ac:dyDescent="0.45">
+      <c r="A13" s="68" t="s">
         <v>390</v>
       </c>
       <c r="B13" s="48" t="s">
@@ -29827,6 +30073,12 @@
       </c>
       <c r="E13" s="50"/>
       <c r="F13" s="50"/>
+      <c r="G13" s="43" t="s">
+        <v>448</v>
+      </c>
+      <c r="H13" s="43" t="s">
+        <v>449</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/project_2/project2_project status(C2).xlsx
+++ b/project_2/project2_project status(C2).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pyostry\workspace\aiffel\ai-data-bootcamp\Project_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D3C1BF2-A0D9-4C0C-80C8-802A3A97CA71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11C35659-AA71-421D-8A7F-29D85468FF46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" firstSheet="4" activeTab="7" xr2:uid="{5FF54064-7DDC-427B-93D7-EF78D75E5195}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" firstSheet="4" activeTab="9" xr2:uid="{5FF54064-7DDC-427B-93D7-EF78D75E5195}"/>
   </bookViews>
   <sheets>
     <sheet name="제작 가이드라인" sheetId="12" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="456">
   <si>
     <t>reward</t>
   </si>
@@ -1455,10 +1455,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>스타벅스 프로모션을 기획, 운영하는 마케팅팀 전달용</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>카페인 민감자의 커피 신메뉴 offer 등 선호도 불일치</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -2059,6 +2055,20 @@
     <t>진행하지 않음</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>스타벅스 프로모션을 기획, 운영하는 마케팅팀 전달용</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>디자인:
+제작:</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>발표자료 준비:
+발표:</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -2068,7 +2078,7 @@
     <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="177" formatCode="[$-412]yyyy&quot;년&quot;\ m&quot;월&quot;\ d&quot;일&quot;\ dddd\ h&quot;시&quot;\ mm&quot;분&quot;"/>
   </numFmts>
-  <fonts count="27" x14ac:knownFonts="1">
+  <fonts count="29" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2281,6 +2291,22 @@
       <color theme="1"/>
       <name val="Cambria Math"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -2623,7 +2649,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2831,6 +2857,37 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2858,21 +2915,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2892,6 +2934,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2915,41 +2960,34 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -11727,8 +11765,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="173001" y="1826087"/>
-          <a:ext cx="2123975" cy="452612"/>
+          <a:off x="220981" y="1805623"/>
+          <a:ext cx="2100172" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -11827,8 +11865,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="186258" y="1839344"/>
-        <a:ext cx="2097461" cy="426098"/>
+        <a:off x="234089" y="1818731"/>
+        <a:ext cx="2073956" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{ED5992BD-91A0-44DC-B026-C230E027754F}">
@@ -11838,8 +11876,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="16874489">
-          <a:off x="1549321" y="1134321"/>
-          <a:ext cx="1857401" cy="14378"/>
+          <a:off x="1581876" y="1121529"/>
+          <a:ext cx="1836586" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -11853,7 +11891,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1857401" y="7189"/>
+                <a:pt x="1836586" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -11912,8 +11950,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2431586" y="1095075"/>
-        <a:ext cx="92870" cy="92870"/>
+        <a:off x="2454255" y="1082803"/>
+        <a:ext cx="91829" cy="91829"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{EB7188F2-1357-4748-A44C-AB5D4A48F40F}">
@@ -11923,8 +11961,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2659066" y="4321"/>
-          <a:ext cx="1092733" cy="452612"/>
+          <a:off x="2679186" y="4273"/>
+          <a:ext cx="1080487" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -11999,8 +12037,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2672323" y="17578"/>
-        <a:ext cx="1066219" cy="426098"/>
+        <a:off x="2692294" y="17381"/>
+        <a:ext cx="1054271" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7531319A-E0E5-4CB4-9F35-33254694A0D7}">
@@ -12010,8 +12048,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3751800" y="223438"/>
-          <a:ext cx="356477" cy="14378"/>
+          <a:off x="3759673" y="220854"/>
+          <a:ext cx="352482" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -12025,7 +12063,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="356477" y="7189"/>
+                <a:pt x="352482" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -12084,8 +12122,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3921127" y="221715"/>
-        <a:ext cx="17823" cy="17823"/>
+        <a:off x="3927103" y="219231"/>
+        <a:ext cx="17624" cy="17624"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{8F385C2E-83EB-470A-8A65-12C51C60EB27}">
@@ -12095,8 +12133,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4108278" y="4321"/>
-          <a:ext cx="4735188" cy="452612"/>
+          <a:off x="4112156" y="4273"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -12195,8 +12233,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4121535" y="17578"/>
-        <a:ext cx="4708674" cy="426098"/>
+        <a:off x="4125264" y="17381"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{71327523-F24D-4A9E-8CA7-7C0E6A96618A}">
@@ -12206,8 +12244,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17132988">
-          <a:off x="1802671" y="1394574"/>
-          <a:ext cx="1350699" cy="14378"/>
+          <a:off x="1832388" y="1378865"/>
+          <a:ext cx="1335563" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -12221,7 +12259,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1350699" y="7189"/>
+                <a:pt x="1335563" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -12280,8 +12318,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2444254" y="1367995"/>
-        <a:ext cx="67534" cy="67534"/>
+        <a:off x="2466780" y="1352664"/>
+        <a:ext cx="66778" cy="66778"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{08B2E005-DF35-41E7-A396-CA02C3B8D0A4}">
@@ -12291,8 +12329,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2659066" y="524826"/>
-          <a:ext cx="1092733" cy="452612"/>
+          <a:off x="2679186" y="518944"/>
+          <a:ext cx="1080487" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -12367,8 +12405,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2672323" y="538083"/>
-        <a:ext cx="1066219" cy="426098"/>
+        <a:off x="2692294" y="532052"/>
+        <a:ext cx="1054271" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E113C6B3-F5C2-41D9-9727-BB430EAD3818}">
@@ -12378,8 +12416,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3751800" y="743943"/>
-          <a:ext cx="362090" cy="14378"/>
+          <a:off x="3759673" y="735525"/>
+          <a:ext cx="358032" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -12393,7 +12431,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="362090" y="7189"/>
+                <a:pt x="358032" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -12452,8 +12490,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3923793" y="742080"/>
-        <a:ext cx="18104" cy="18104"/>
+        <a:off x="3929739" y="733763"/>
+        <a:ext cx="17901" cy="17901"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{53F03F28-ED40-4762-8125-AFFEEA792A72}">
@@ -12463,8 +12501,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4113890" y="524826"/>
-          <a:ext cx="4735188" cy="452612"/>
+          <a:off x="4117706" y="518944"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -12587,8 +12625,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4127147" y="538083"/>
-        <a:ext cx="4708674" cy="426098"/>
+        <a:off x="4130814" y="532052"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{806C8330-1E37-41AD-AEEE-3552A4162510}">
@@ -12598,8 +12636,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17692822">
-          <a:off x="2047704" y="1654826"/>
-          <a:ext cx="860633" cy="14378"/>
+          <a:off x="2074675" y="1636200"/>
+          <a:ext cx="850988" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -12613,7 +12651,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="860633" y="7189"/>
+                <a:pt x="850988" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -12672,8 +12710,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2456505" y="1640499"/>
-        <a:ext cx="43031" cy="43031"/>
+        <a:off x="2478895" y="1622115"/>
+        <a:ext cx="42549" cy="42549"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{3BC1DAB2-4FEF-42C9-A10F-0690E2903498}">
@@ -12683,8 +12721,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2659066" y="1045330"/>
-          <a:ext cx="1092733" cy="452612"/>
+          <a:off x="2679186" y="1033615"/>
+          <a:ext cx="1080487" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -12775,8 +12813,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2672323" y="1058587"/>
-        <a:ext cx="1066219" cy="426098"/>
+        <a:off x="2692294" y="1046723"/>
+        <a:ext cx="1054271" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6BFD1C16-8154-4C15-AF72-E53B38C4A146}">
@@ -12786,8 +12824,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3751800" y="1264447"/>
-          <a:ext cx="362090" cy="14378"/>
+          <a:off x="3759673" y="1250197"/>
+          <a:ext cx="358032" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -12801,7 +12839,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="362090" y="7189"/>
+                <a:pt x="358032" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -12860,8 +12898,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3923793" y="1262584"/>
-        <a:ext cx="18104" cy="18104"/>
+        <a:off x="3929739" y="1248435"/>
+        <a:ext cx="17901" cy="17901"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1A251137-9CB6-43D7-B47D-0D220C30894C}">
@@ -12871,8 +12909,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4113890" y="1045330"/>
-          <a:ext cx="4735188" cy="452612"/>
+          <a:off x="4117706" y="1033615"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -12995,8 +13033,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4127147" y="1058587"/>
-        <a:ext cx="4708674" cy="426098"/>
+        <a:off x="4130814" y="1046723"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{227E0FEF-1368-4562-AD55-940C6A450E91}">
@@ -13006,8 +13044,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="3310531">
-          <a:off x="2160990" y="2305456"/>
-          <a:ext cx="634061" cy="14378"/>
+          <a:off x="2186691" y="2279540"/>
+          <a:ext cx="626956" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -13021,7 +13059,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="634061" y="7189"/>
+                <a:pt x="626956" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -13080,8 +13118,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2462170" y="2296794"/>
-        <a:ext cx="31703" cy="31703"/>
+        <a:off x="2484496" y="2271055"/>
+        <a:ext cx="31347" cy="31347"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{146FB508-948A-484E-B54F-2A63CE5492FA}">
@@ -13091,8 +13129,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2659066" y="2346591"/>
-          <a:ext cx="1092733" cy="452612"/>
+          <a:off x="2679186" y="2320294"/>
+          <a:ext cx="1080487" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -13167,8 +13205,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2672323" y="2359848"/>
-        <a:ext cx="1066219" cy="426098"/>
+        <a:off x="2692294" y="2333402"/>
+        <a:ext cx="1054271" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1583A4D8-C48C-400A-B5A1-D8E8188A1E57}">
@@ -13178,8 +13216,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17692822">
-          <a:off x="3502528" y="2175330"/>
-          <a:ext cx="860633" cy="14378"/>
+          <a:off x="3513195" y="2150872"/>
+          <a:ext cx="850988" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -13193,7 +13231,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="860633" y="7189"/>
+                <a:pt x="850988" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -13252,8 +13290,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3911329" y="2161003"/>
-        <a:ext cx="43031" cy="43031"/>
+        <a:off x="3917415" y="2136786"/>
+        <a:ext cx="42549" cy="42549"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{985FE1E2-4CA8-4AC7-A474-DEECC9A2BB80}">
@@ -13263,8 +13301,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4113890" y="1565835"/>
-          <a:ext cx="4735188" cy="452612"/>
+          <a:off x="4117706" y="1548287"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -13355,8 +13393,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4127147" y="1579092"/>
-        <a:ext cx="4708674" cy="426098"/>
+        <a:off x="4130814" y="1561395"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{16F44D37-2601-482A-9095-0B3E8E10E520}">
@@ -13366,8 +13404,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19457599">
-          <a:off x="3709887" y="2435583"/>
-          <a:ext cx="445915" cy="14378"/>
+          <a:off x="3718230" y="2408207"/>
+          <a:ext cx="440918" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -13381,7 +13419,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="445915" y="7189"/>
+                <a:pt x="440918" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -13440,8 +13478,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3921697" y="2431624"/>
-        <a:ext cx="22295" cy="22295"/>
+        <a:off x="3927667" y="2404373"/>
+        <a:ext cx="22045" cy="22045"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{2D542640-C237-42B5-8470-73084719F8F3}">
@@ -13451,8 +13489,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4113890" y="2086339"/>
-          <a:ext cx="4735188" cy="452612"/>
+          <a:off x="4117706" y="2062958"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -13543,8 +13581,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4127147" y="2099596"/>
-        <a:ext cx="4708674" cy="426098"/>
+        <a:off x="4130814" y="2076066"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9A75AB13-86A0-459A-8B2B-E8037D74B447}">
@@ -13554,8 +13592,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2142401">
-          <a:off x="3709887" y="2695835"/>
-          <a:ext cx="445915" cy="14378"/>
+          <a:off x="3718230" y="2665543"/>
+          <a:ext cx="440918" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -13569,7 +13607,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="445915" y="7189"/>
+                <a:pt x="440918" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -13628,8 +13666,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3921697" y="2691876"/>
-        <a:ext cx="22295" cy="22295"/>
+        <a:off x="3927667" y="2661709"/>
+        <a:ext cx="22045" cy="22045"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{106C3051-36E0-4DB2-B006-BD51244834C6}">
@@ -13639,8 +13677,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4113890" y="2606844"/>
-          <a:ext cx="4735188" cy="452612"/>
+          <a:off x="4117706" y="2577630"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -13731,8 +13769,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4127147" y="2620101"/>
-        <a:ext cx="4708674" cy="426098"/>
+        <a:off x="4130814" y="2590738"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6562E267-52DD-4DC6-81E6-A0E9307367D6}">
@@ -13742,8 +13780,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="3907178">
-          <a:off x="3502528" y="2956087"/>
-          <a:ext cx="860633" cy="14378"/>
+          <a:off x="3513195" y="2922879"/>
+          <a:ext cx="850988" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -13757,7 +13795,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="860633" y="7189"/>
+                <a:pt x="850988" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -13816,8 +13854,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3911329" y="2941760"/>
-        <a:ext cx="43031" cy="43031"/>
+        <a:off x="3917415" y="2908793"/>
+        <a:ext cx="42549" cy="42549"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{220D319D-36C0-42A0-A946-F197C4269C14}">
@@ -13827,8 +13865,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4113890" y="3127348"/>
-          <a:ext cx="4735188" cy="452612"/>
+          <a:off x="4117706" y="3092301"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -13919,8 +13957,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4127147" y="3140605"/>
-        <a:ext cx="4708674" cy="426098"/>
+        <a:off x="4130814" y="3105409"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4332858F-88A7-466E-8722-8833A7B96598}">
@@ -13930,8 +13968,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="4725511">
-          <a:off x="1549321" y="2956087"/>
-          <a:ext cx="1857401" cy="14378"/>
+          <a:off x="1581876" y="2922879"/>
+          <a:ext cx="1836586" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -13945,7 +13983,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1857401" y="7189"/>
+                <a:pt x="1836586" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -14000,8 +14038,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2431586" y="2916841"/>
-        <a:ext cx="92870" cy="92870"/>
+        <a:off x="2454255" y="2884153"/>
+        <a:ext cx="91829" cy="91829"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1479FCFA-85A4-438D-B5D0-346DFAD5924D}">
@@ -14011,8 +14049,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2659066" y="3647853"/>
-          <a:ext cx="1092733" cy="452612"/>
+          <a:off x="2679186" y="3606973"/>
+          <a:ext cx="1080487" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -14087,8 +14125,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2672323" y="3661110"/>
-        <a:ext cx="1066219" cy="426098"/>
+        <a:off x="2692294" y="3620081"/>
+        <a:ext cx="1054271" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E6D0412B-4D85-432B-BE35-F277BFD00B03}">
@@ -14098,8 +14136,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3751800" y="3866970"/>
-          <a:ext cx="362090" cy="14378"/>
+          <a:off x="3759673" y="3823554"/>
+          <a:ext cx="358032" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -14113,7 +14151,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="362090" y="7189"/>
+                <a:pt x="358032" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -14168,8 +14206,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3923793" y="3865107"/>
-        <a:ext cx="18104" cy="18104"/>
+        <a:off x="3929739" y="3821792"/>
+        <a:ext cx="17901" cy="17901"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{CE9AFD94-4037-4F8B-B49B-020818B5CBB5}">
@@ -14179,8 +14217,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4113890" y="3647853"/>
-          <a:ext cx="4735188" cy="452612"/>
+          <a:off x="4117706" y="3606973"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -14287,8 +14325,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4127147" y="3661110"/>
-        <a:ext cx="4708674" cy="426098"/>
+        <a:off x="4130814" y="3620081"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B460AB31-448C-42B6-9C6B-D3CF5013B4F6}">
@@ -14298,8 +14336,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="39236" y="4688862"/>
-          <a:ext cx="1821222" cy="452612"/>
+          <a:off x="88714" y="4636316"/>
+          <a:ext cx="1800813" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -14424,8 +14462,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="52493" y="4702119"/>
-        <a:ext cx="1794708" cy="426098"/>
+        <a:off x="101822" y="4649424"/>
+        <a:ext cx="1774597" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{C120D3E5-D1A3-4DC1-848B-C37D9DDE2012}">
@@ -14435,8 +14473,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="18752467">
-          <a:off x="1746056" y="4647727"/>
-          <a:ext cx="706446" cy="14378"/>
+          <a:off x="1776407" y="4595561"/>
+          <a:ext cx="698529" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -14450,7 +14488,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="706446" y="7189"/>
+                <a:pt x="698529" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -14505,8 +14543,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2081618" y="4637255"/>
-        <a:ext cx="35322" cy="35322"/>
+        <a:off x="2108209" y="4585287"/>
+        <a:ext cx="34926" cy="34926"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6F01F0AA-74B9-49DB-A456-B8979039EB51}">
@@ -14516,8 +14554,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2338101" y="4168357"/>
-          <a:ext cx="1092733" cy="452612"/>
+          <a:off x="2361817" y="4121644"/>
+          <a:ext cx="1080487" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -14590,8 +14628,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2351358" y="4181614"/>
-        <a:ext cx="1066219" cy="426098"/>
+        <a:off x="2374925" y="4134752"/>
+        <a:ext cx="1054271" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{F5E69F9A-2631-4A2D-BC76-B4BD9B08D019}">
@@ -14601,8 +14639,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3430834" y="4387475"/>
-          <a:ext cx="368146" cy="14378"/>
+          <a:off x="3442305" y="4338225"/>
+          <a:ext cx="364020" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -14616,7 +14654,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="368146" y="7189"/>
+                <a:pt x="364020" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -14671,8 +14709,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3605704" y="4385460"/>
-        <a:ext cx="18407" cy="18407"/>
+        <a:off x="3615214" y="4336314"/>
+        <a:ext cx="18201" cy="18201"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{69EDA0B0-D39D-4C93-8B8D-10889C581D9E}">
@@ -14682,8 +14720,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3798980" y="4168357"/>
-          <a:ext cx="4735188" cy="452612"/>
+          <a:off x="3806325" y="4121644"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -14756,8 +14794,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3812237" y="4181614"/>
-        <a:ext cx="4708674" cy="426098"/>
+        <a:off x="3819433" y="4134752"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{AC23C890-5E27-4DC3-9BF7-2C50218200D9}">
@@ -14767,8 +14805,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="1860458" y="4907979"/>
-          <a:ext cx="477642" cy="14378"/>
+          <a:off x="1889527" y="4852897"/>
+          <a:ext cx="472289" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -14782,7 +14820,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="477642" y="7189"/>
+                <a:pt x="472289" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -14837,8 +14875,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2087338" y="4903227"/>
-        <a:ext cx="23882" cy="23882"/>
+        <a:off x="2113865" y="4848279"/>
+        <a:ext cx="23614" cy="23614"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B4CF3050-E538-4710-99C5-FB5B2F28D116}">
@@ -14848,8 +14886,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2338101" y="4688862"/>
-          <a:ext cx="1092733" cy="452612"/>
+          <a:off x="2361817" y="4636316"/>
+          <a:ext cx="1080487" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -14922,8 +14960,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2351358" y="4702119"/>
-        <a:ext cx="1066219" cy="426098"/>
+        <a:off x="2374925" y="4649424"/>
+        <a:ext cx="1054271" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{55492AE0-989E-4368-96E6-8609B6786079}">
@@ -14933,8 +14971,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3430834" y="4907979"/>
-          <a:ext cx="368146" cy="14378"/>
+          <a:off x="3442305" y="4852897"/>
+          <a:ext cx="364020" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -14948,7 +14986,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="368146" y="7189"/>
+                <a:pt x="364020" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -15003,8 +15041,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3605704" y="4905964"/>
-        <a:ext cx="18407" cy="18407"/>
+        <a:off x="3615214" y="4850985"/>
+        <a:ext cx="18201" cy="18201"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{99BD4B49-7654-4BFC-93A2-73715A94DAC0}">
@@ -15014,8 +15052,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3798980" y="4688862"/>
-          <a:ext cx="4735188" cy="452612"/>
+          <a:off x="3806325" y="4636316"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -15132,8 +15170,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3812237" y="4702119"/>
-        <a:ext cx="4708674" cy="426098"/>
+        <a:off x="3819433" y="4649424"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{48D36C81-0EEF-4879-868D-73109D1A61EF}">
@@ -15143,8 +15181,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2847533">
-          <a:off x="1746056" y="5168231"/>
-          <a:ext cx="706446" cy="14378"/>
+          <a:off x="1776407" y="5110232"/>
+          <a:ext cx="698529" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -15158,7 +15196,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="706446" y="7189"/>
+                <a:pt x="698529" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -15213,8 +15251,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2081618" y="5157759"/>
-        <a:ext cx="35322" cy="35322"/>
+        <a:off x="2108209" y="5099958"/>
+        <a:ext cx="34926" cy="34926"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E0C7A212-1F93-473A-8909-15A6780CBC2F}">
@@ -15224,8 +15262,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2338101" y="5209366"/>
-          <a:ext cx="1092733" cy="452612"/>
+          <a:off x="2361817" y="5150987"/>
+          <a:ext cx="1080487" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -15298,8 +15336,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2351358" y="5222623"/>
-        <a:ext cx="1066219" cy="426098"/>
+        <a:off x="2374925" y="5164095"/>
+        <a:ext cx="1054271" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4D54B04B-F98B-4577-8925-91ECEF877996}">
@@ -15309,8 +15347,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3430834" y="5428484"/>
-          <a:ext cx="380303" cy="14378"/>
+          <a:off x="3442305" y="5367568"/>
+          <a:ext cx="376041" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -15324,7 +15362,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="380303" y="7189"/>
+                <a:pt x="376041" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -15379,8 +15417,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3611478" y="5426165"/>
-        <a:ext cx="19015" cy="19015"/>
+        <a:off x="3620924" y="5365356"/>
+        <a:ext cx="18802" cy="18802"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{540CB623-D523-4AD6-BF5D-A946D7B052E6}">
@@ -15390,8 +15428,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3811137" y="5209366"/>
-          <a:ext cx="4735188" cy="452612"/>
+          <a:off x="3818346" y="5150987"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -15509,8 +15547,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3824394" y="5222623"/>
-        <a:ext cx="4708674" cy="426098"/>
+        <a:off x="3831454" y="5164095"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
   </dsp:spTree>
@@ -15532,8 +15570,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10440" y="3343938"/>
-          <a:ext cx="1173405" cy="360228"/>
+          <a:off x="9182" y="3307680"/>
+          <a:ext cx="1177681" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -15611,8 +15649,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="20991" y="3354489"/>
-        <a:ext cx="1152303" cy="339126"/>
+        <a:off x="19771" y="3318269"/>
+        <a:ext cx="1156503" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7667B88B-738E-4E27-80A6-15B1E3AED5F8}">
@@ -15622,8 +15660,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="16719080">
-          <a:off x="572123" y="2808170"/>
-          <a:ext cx="1440061" cy="8089"/>
+          <a:off x="572912" y="2769909"/>
+          <a:ext cx="1445308" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -15634,10 +15672,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1440061" y="4044"/>
+                <a:pt x="1445308" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -15696,8 +15734,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1256152" y="2776213"/>
-        <a:ext cx="72003" cy="72003"/>
+        <a:off x="1259433" y="2737887"/>
+        <a:ext cx="72265" cy="72265"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D9E30B0F-B6EE-4B8A-B3A5-5AD7E4CFBC12}">
@@ -15707,8 +15745,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="1400462" y="1920262"/>
-          <a:ext cx="1439393" cy="360228"/>
+          <a:off x="1404269" y="1878817"/>
+          <a:ext cx="1444638" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -15799,8 +15837,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1411013" y="1930813"/>
-        <a:ext cx="1418291" cy="339126"/>
+        <a:off x="1414858" y="1889406"/>
+        <a:ext cx="1423460" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{ED5992BD-91A0-44DC-B026-C230E027754F}">
@@ -15810,8 +15848,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="16757427">
-          <a:off x="2277274" y="1434244"/>
-          <a:ext cx="1341777" cy="8089"/>
+          <a:off x="2284276" y="1390976"/>
+          <a:ext cx="1346666" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -15822,10 +15860,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1341777" y="4044"/>
+                <a:pt x="1346666" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -15884,8 +15922,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2914618" y="1404744"/>
-        <a:ext cx="67088" cy="67088"/>
+        <a:off x="2923942" y="1361420"/>
+        <a:ext cx="67333" cy="67333"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{EB7188F2-1357-4748-A44C-AB5D4A48F40F}">
@@ -15895,8 +15933,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3056471" y="596085"/>
-          <a:ext cx="1402222" cy="360228"/>
+          <a:off x="3066312" y="549815"/>
+          <a:ext cx="1407331" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -15966,8 +16004,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3067022" y="606636"/>
-        <a:ext cx="1381120" cy="339126"/>
+        <a:off x="3076901" y="560404"/>
+        <a:ext cx="1386153" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7531319A-E0E5-4CB4-9F35-33254694A0D7}">
@@ -15977,8 +16015,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17860289">
-          <a:off x="4335717" y="568811"/>
-          <a:ext cx="459210" cy="8089"/>
+          <a:off x="4350219" y="522390"/>
+          <a:ext cx="460883" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -15989,10 +16027,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="459210" y="4044"/>
+                <a:pt x="460883" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16051,8 +16089,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4553842" y="561375"/>
-        <a:ext cx="22960" cy="22960"/>
+        <a:off x="4569139" y="514979"/>
+        <a:ext cx="23044" cy="23044"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{8F385C2E-83EB-470A-8A65-12C51C60EB27}">
@@ -16062,8 +16100,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4671951" y="187807"/>
-          <a:ext cx="1769726" cy="363410"/>
+          <a:off x="4687678" y="140049"/>
+          <a:ext cx="1776175" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16133,8 +16171,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4682595" y="198451"/>
-        <a:ext cx="1748438" cy="342122"/>
+        <a:off x="4698361" y="150732"/>
+        <a:ext cx="1754809" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{8EC6EEF9-E6D8-4DE2-A6DD-BB50B40A5CF0}">
@@ -16144,8 +16182,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6441677" y="365467"/>
-          <a:ext cx="219972" cy="8089"/>
+          <a:off x="6463853" y="318305"/>
+          <a:ext cx="220774" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16156,10 +16194,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="219972" y="4044"/>
+                <a:pt x="220774" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16214,8 +16252,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6546165" y="364012"/>
-        <a:ext cx="10998" cy="10998"/>
+        <a:off x="6568721" y="316896"/>
+        <a:ext cx="11038" cy="11038"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{31CFEB2D-0887-4520-AF04-1E3C38912960}">
@@ -16225,8 +16263,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6661650" y="187807"/>
-          <a:ext cx="3156395" cy="363410"/>
+          <a:off x="6684628" y="140049"/>
+          <a:ext cx="3167897" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16312,8 +16350,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6672294" y="198451"/>
-        <a:ext cx="3135107" cy="342122"/>
+        <a:off x="6695311" y="150732"/>
+        <a:ext cx="3146531" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{602438BB-CBF9-49AF-AB0A-D57EA2C10BE2}">
@@ -16323,8 +16361,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9818046" y="365467"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9852525" y="318305"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16335,10 +16373,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16393,8 +16431,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9920939" y="364096"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9955792" y="316981"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{57D97F9E-094F-4C3F-82B2-5A689BC4D082}">
@@ -16404,8 +16442,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10034662" y="193925"/>
-          <a:ext cx="1801141" cy="351174"/>
+          <a:off x="10069930" y="146189"/>
+          <a:ext cx="1807704" cy="352453"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16502,8 +16540,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10044948" y="204211"/>
-        <a:ext cx="1780569" cy="330602"/>
+        <a:off x="10080253" y="156512"/>
+        <a:ext cx="1787058" cy="331807"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B3B4155B-F64B-452E-AEBC-36FE76B0BD69}">
@@ -16513,8 +16551,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="21585916">
-          <a:off x="4458692" y="771712"/>
-          <a:ext cx="216617" cy="8089"/>
+          <a:off x="4473642" y="726030"/>
+          <a:ext cx="217406" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16525,10 +16563,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216617" y="4044"/>
+                <a:pt x="217406" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16583,8 +16621,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4561585" y="770341"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="4576910" y="724705"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D20B6C81-A2D9-4E8E-80C0-968EFF7F89E1}">
@@ -16594,8 +16632,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4675308" y="593607"/>
-          <a:ext cx="1769726" cy="363410"/>
+          <a:off x="4691048" y="547328"/>
+          <a:ext cx="1776175" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16665,8 +16703,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4685952" y="604251"/>
-        <a:ext cx="1748438" cy="342122"/>
+        <a:off x="4701731" y="558011"/>
+        <a:ext cx="1754809" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7FE58BCF-6B0D-48A2-8DDE-611A1D34A4D6}">
@@ -16676,8 +16714,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6445035" y="771268"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="6467223" y="725585"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16688,10 +16726,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16746,8 +16784,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6547927" y="769897"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="6570490" y="724260"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{629314FA-FCA6-45B9-99A7-2C2196A96D5C}">
@@ -16757,8 +16795,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6661650" y="593607"/>
-          <a:ext cx="3156395" cy="363410"/>
+          <a:off x="6684628" y="547328"/>
+          <a:ext cx="3167897" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16857,8 +16895,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6672294" y="604251"/>
-        <a:ext cx="3135107" cy="342122"/>
+        <a:off x="6695311" y="558011"/>
+        <a:ext cx="3146531" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{CCF144EB-A097-46BE-8FF7-BE5C7A394E2A}">
@@ -16868,8 +16906,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9818046" y="771268"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9852525" y="725585"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16880,10 +16918,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16938,8 +16976,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9920939" y="769897"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9955792" y="724260"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9EE0F2D9-F39B-4921-9EAC-DBA04DC260DD}">
@@ -16949,8 +16987,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10034662" y="591832"/>
-          <a:ext cx="1801141" cy="366960"/>
+          <a:off x="10069930" y="545546"/>
+          <a:ext cx="1807704" cy="368297"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17033,8 +17071,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10045410" y="602580"/>
-        <a:ext cx="1779645" cy="345464"/>
+        <a:off x="10080717" y="556333"/>
+        <a:ext cx="1786130" cy="346723"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6169CD61-5E3A-4096-AA5A-91A22C397918}">
@@ -17044,8 +17082,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="3717526">
-          <a:off x="4336611" y="975499"/>
-          <a:ext cx="460779" cy="8089"/>
+          <a:off x="4351116" y="930560"/>
+          <a:ext cx="462458" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17056,10 +17094,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="460779" y="4044"/>
+                <a:pt x="462458" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17114,8 +17152,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4555481" y="968024"/>
-        <a:ext cx="23038" cy="23038"/>
+        <a:off x="4570784" y="923109"/>
+        <a:ext cx="23122" cy="23122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D5FDB947-B70B-4493-B9F9-83A45503DA23}">
@@ -17125,8 +17163,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4675308" y="1001183"/>
-          <a:ext cx="1769726" cy="363410"/>
+          <a:off x="4691048" y="956388"/>
+          <a:ext cx="1776175" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17196,8 +17234,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4685952" y="1011827"/>
-        <a:ext cx="1748438" cy="342122"/>
+        <a:off x="4701731" y="967071"/>
+        <a:ext cx="1754809" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9EDF68AF-E14B-40BF-AB6D-4B01635D735A}">
@@ -17207,8 +17245,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6445035" y="1178843"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="6467223" y="1134645"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17219,10 +17257,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17277,8 +17315,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6547927" y="1177472"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="6570490" y="1133321"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{5A5C0991-25ED-4076-91F2-80A2EEFC811E}">
@@ -17288,8 +17326,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6661650" y="1001183"/>
-          <a:ext cx="3156395" cy="363410"/>
+          <a:off x="6684628" y="956388"/>
+          <a:ext cx="3167897" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17423,8 +17461,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6672294" y="1011827"/>
-        <a:ext cx="3135107" cy="342122"/>
+        <a:off x="6695311" y="967071"/>
+        <a:ext cx="3146531" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{723082D3-A8E2-4807-89B5-C74C600B949E}">
@@ -17434,8 +17472,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9818046" y="1178843"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9852525" y="1134645"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17446,10 +17484,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17504,8 +17542,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9920939" y="1177472"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9955792" y="1133321"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{05E664DE-AAC0-4D52-9AA4-DE55CA572420}">
@@ -17515,8 +17553,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10034662" y="999408"/>
-          <a:ext cx="1801141" cy="366960"/>
+          <a:off x="10069930" y="954607"/>
+          <a:ext cx="1807704" cy="368297"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17586,8 +17624,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10045410" y="1010156"/>
-        <a:ext cx="1779645" cy="345464"/>
+        <a:off x="10080717" y="965394"/>
+        <a:ext cx="1786130" cy="346723"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{16F44D37-2601-482A-9095-0B3E8E10E520}">
@@ -17597,8 +17635,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="1505741">
-          <a:off x="2828565" y="2147057"/>
-          <a:ext cx="239195" cy="8089"/>
+          <a:off x="2837576" y="2106387"/>
+          <a:ext cx="240066" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17609,10 +17647,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="239195" y="4044"/>
+                <a:pt x="240066" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17671,8 +17709,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2942183" y="2145122"/>
-        <a:ext cx="11959" cy="11959"/>
+        <a:off x="2951607" y="2104496"/>
+        <a:ext cx="12003" cy="12003"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{2D542640-C237-42B5-8470-73084719F8F3}">
@@ -17682,8 +17720,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3056471" y="2021712"/>
-          <a:ext cx="1402222" cy="360228"/>
+          <a:off x="3066312" y="1980637"/>
+          <a:ext cx="1407331" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17753,8 +17791,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3067022" y="2032263"/>
-        <a:ext cx="1381120" cy="339126"/>
+        <a:off x="3076901" y="1991226"/>
+        <a:ext cx="1386153" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{BFCFD3BD-878E-4ADC-81DA-3641DCD660A7}">
@@ -17764,8 +17802,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17370601">
-          <a:off x="4242699" y="1892100"/>
-          <a:ext cx="648604" cy="8089"/>
+          <a:off x="4256862" y="1850501"/>
+          <a:ext cx="650967" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17776,10 +17814,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="648604" y="4044"/>
+                <a:pt x="650967" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17834,8 +17872,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4550785" y="1879930"/>
-        <a:ext cx="32430" cy="32430"/>
+        <a:off x="4566071" y="1838338"/>
+        <a:ext cx="32548" cy="32548"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{911F1DD5-D3D2-4321-A1A5-7E2BAE25AAD5}">
@@ -17845,8 +17883,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4675308" y="1408758"/>
-          <a:ext cx="1769726" cy="363410"/>
+          <a:off x="4691048" y="1365449"/>
+          <a:ext cx="1776175" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17916,8 +17954,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4685952" y="1419402"/>
-        <a:ext cx="1748438" cy="342122"/>
+        <a:off x="4701731" y="1376132"/>
+        <a:ext cx="1754809" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{F4CAC384-240B-4811-A7FE-5EF39454FD0A}">
@@ -17927,8 +17965,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6445035" y="1586419"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="6467223" y="1543706"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17939,10 +17977,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17997,8 +18035,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6547927" y="1585048"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="6570490" y="1542381"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{00847D60-C67D-487A-B918-B0C406DE6A20}">
@@ -18008,8 +18046,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6661650" y="1408758"/>
-          <a:ext cx="3156395" cy="363410"/>
+          <a:off x="6684628" y="1365449"/>
+          <a:ext cx="3167897" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -18119,8 +18157,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6672294" y="1419402"/>
-        <a:ext cx="3135107" cy="342122"/>
+        <a:off x="6695311" y="1376132"/>
+        <a:ext cx="3146531" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7682FEBA-2A8A-4CEB-BAD3-CAC6D62452E9}">
@@ -18130,8 +18168,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9818046" y="1586419"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9852525" y="1543706"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18142,10 +18180,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18200,8 +18238,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9920939" y="1585048"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9955792" y="1542381"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4C2C55F9-D12D-4BE1-85AD-8FAFF8B344C7}">
@@ -18211,8 +18249,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10034662" y="1406983"/>
-          <a:ext cx="1801141" cy="366960"/>
+          <a:off x="10069930" y="1363668"/>
+          <a:ext cx="1807704" cy="368297"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -18330,8 +18368,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10045410" y="1417731"/>
-        <a:ext cx="1779645" cy="345464"/>
+        <a:off x="10080717" y="1374455"/>
+        <a:ext cx="1786130" cy="346723"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6A4076F7-5C10-4205-AF7B-34977DAE41B6}">
@@ -18341,8 +18379,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19004863">
-          <a:off x="4418296" y="2095888"/>
-          <a:ext cx="297408" cy="8089"/>
+          <a:off x="4433100" y="2055032"/>
+          <a:ext cx="298492" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18353,10 +18391,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="297408" y="4044"/>
+                <a:pt x="298492" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18411,8 +18449,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4559565" y="2092498"/>
-        <a:ext cx="14870" cy="14870"/>
+        <a:off x="4574883" y="2051680"/>
+        <a:ext cx="14924" cy="14924"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D2D6EBAC-87C6-4589-B626-76CA00356F2A}">
@@ -18422,8 +18460,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4675308" y="1816334"/>
-          <a:ext cx="1769726" cy="363410"/>
+          <a:off x="4691048" y="1774510"/>
+          <a:ext cx="1776175" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -18493,8 +18531,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4685952" y="1826978"/>
-        <a:ext cx="1748438" cy="342122"/>
+        <a:off x="4701731" y="1785193"/>
+        <a:ext cx="1754809" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4CEC118E-B718-4A3D-A714-E879160F0F50}">
@@ -18504,8 +18542,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6445035" y="1993994"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="6467223" y="1952767"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18516,10 +18554,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18574,8 +18612,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6547927" y="1992623"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="6570490" y="1951442"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{96C9B796-69AA-48A9-AB67-0FE5F7CEFC9D}">
@@ -18585,8 +18623,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6661650" y="1816334"/>
-          <a:ext cx="3156395" cy="363410"/>
+          <a:off x="6684628" y="1774510"/>
+          <a:ext cx="3167897" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -18680,8 +18718,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6672294" y="1826978"/>
-        <a:ext cx="3135107" cy="342122"/>
+        <a:off x="6695311" y="1785193"/>
+        <a:ext cx="3146531" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{0C4A9E51-DEA5-4AC0-B8EC-F712BFE3BA51}">
@@ -18691,8 +18729,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9818046" y="1993994"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9852525" y="1952767"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18703,10 +18741,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18761,8 +18799,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9920939" y="1992623"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9955792" y="1951442"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{829A6295-4379-4C15-BF91-56D56B48CA13}">
@@ -18772,8 +18810,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10034662" y="1814559"/>
-          <a:ext cx="1801141" cy="366960"/>
+          <a:off x="10069930" y="1772728"/>
+          <a:ext cx="1807704" cy="368297"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -18859,8 +18897,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10045410" y="1825307"/>
-        <a:ext cx="1779645" cy="345464"/>
+        <a:off x="10080717" y="1783515"/>
+        <a:ext cx="1786130" cy="346723"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{15251D3B-5937-4D92-B910-59FBB0B78504}">
@@ -18870,8 +18908,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2595137">
-          <a:off x="4418296" y="2299676"/>
-          <a:ext cx="297408" cy="8089"/>
+          <a:off x="4433100" y="2259562"/>
+          <a:ext cx="298492" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18882,10 +18920,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="297408" y="4044"/>
+                <a:pt x="298492" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18940,8 +18978,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4559565" y="2296285"/>
-        <a:ext cx="14870" cy="14870"/>
+        <a:off x="4574883" y="2256210"/>
+        <a:ext cx="14924" cy="14924"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{55C8ECFC-533A-4D04-B170-164B29EE9A7D}">
@@ -18951,8 +18989,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4675308" y="2223909"/>
-          <a:ext cx="1769726" cy="363410"/>
+          <a:off x="4691048" y="2183570"/>
+          <a:ext cx="1776175" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19022,8 +19060,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4685952" y="2234553"/>
-        <a:ext cx="1748438" cy="342122"/>
+        <a:off x="4701731" y="2194253"/>
+        <a:ext cx="1754809" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A63458DA-4732-44A8-AAAD-101471030A2E}">
@@ -19033,8 +19071,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6445035" y="2401570"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="6467223" y="2361827"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19045,10 +19083,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19103,8 +19141,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6547927" y="2400199"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="6570490" y="2360502"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{3CFC9EAC-3C3A-42EE-A809-37090C958CCC}">
@@ -19114,8 +19152,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6661650" y="2223909"/>
-          <a:ext cx="3156395" cy="363410"/>
+          <a:off x="6684628" y="2183570"/>
+          <a:ext cx="3167897" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19193,8 +19231,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6672294" y="2234553"/>
-        <a:ext cx="3135107" cy="342122"/>
+        <a:off x="6695311" y="2194253"/>
+        <a:ext cx="3146531" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{2E1BE310-D0FB-4439-BC13-EF25298A0AC1}">
@@ -19204,8 +19242,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9818046" y="2401570"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9852525" y="2361827"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19216,10 +19254,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19274,8 +19312,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9920939" y="2400199"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9955792" y="2360502"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{05029C16-99B1-4993-B5A7-DFCE2EC4AF2D}">
@@ -19285,8 +19323,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10034662" y="2222134"/>
-          <a:ext cx="1801141" cy="366960"/>
+          <a:off x="10069930" y="2181789"/>
+          <a:ext cx="1807704" cy="368297"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19356,8 +19394,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10045410" y="2232882"/>
-        <a:ext cx="1779645" cy="345464"/>
+        <a:off x="10080717" y="2192576"/>
+        <a:ext cx="1786130" cy="346723"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7B1A1F24-5790-42BE-9800-70C6BAC67F71}">
@@ -19367,8 +19405,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="4229399">
-          <a:off x="4242699" y="2503464"/>
-          <a:ext cx="648604" cy="8089"/>
+          <a:off x="4256862" y="2464092"/>
+          <a:ext cx="650967" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19379,10 +19417,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="648604" y="4044"/>
+                <a:pt x="650967" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19437,8 +19475,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4550785" y="2491293"/>
-        <a:ext cx="32430" cy="32430"/>
+        <a:off x="4566071" y="2451929"/>
+        <a:ext cx="32548" cy="32548"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{F9E7099E-D348-4A20-924E-7B36E8E1B00D}">
@@ -19448,8 +19486,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4675308" y="2631485"/>
-          <a:ext cx="1788209" cy="363410"/>
+          <a:off x="4691048" y="2592631"/>
+          <a:ext cx="1794725" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19519,8 +19557,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4685952" y="2642129"/>
-        <a:ext cx="1766921" cy="342122"/>
+        <a:off x="4701731" y="2603314"/>
+        <a:ext cx="1773359" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{69A95BFF-166E-4390-9963-14C8F025ADBA}">
@@ -19530,8 +19568,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6463518" y="2809145"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="6485773" y="2770888"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19542,10 +19580,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19600,8 +19638,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6566410" y="2807775"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="6589040" y="2769563"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{BBDCC5A6-74D1-4E37-848C-BF5D7C733A0C}">
@@ -19611,8 +19649,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6680133" y="2631485"/>
-          <a:ext cx="3156395" cy="363410"/>
+          <a:off x="6703178" y="2592631"/>
+          <a:ext cx="3167897" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19682,8 +19720,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6690777" y="2642129"/>
-        <a:ext cx="3135107" cy="342122"/>
+        <a:off x="6713861" y="2603314"/>
+        <a:ext cx="3146531" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E75A9ED0-3CF3-4FBB-B735-763677226156}">
@@ -19693,8 +19731,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9836529" y="2809145"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9871075" y="2770888"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19705,10 +19743,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19763,8 +19801,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9939421" y="2807775"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9974342" y="2769563"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D255C67C-B87B-4D25-A5F4-B2880DE74996}">
@@ -19774,8 +19812,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10053144" y="2629710"/>
-          <a:ext cx="1801141" cy="366960"/>
+          <a:off x="10088480" y="2590850"/>
+          <a:ext cx="1807704" cy="368297"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19869,8 +19907,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10063892" y="2640458"/>
-        <a:ext cx="1779645" cy="345464"/>
+        <a:off x="10099267" y="2601637"/>
+        <a:ext cx="1786130" cy="346723"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{19133C7D-D6FC-4086-9EFA-C8E67C09EF92}">
@@ -19880,8 +19918,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="4842573">
-          <a:off x="2277274" y="2758420"/>
-          <a:ext cx="1341777" cy="8089"/>
+          <a:off x="2284276" y="2719978"/>
+          <a:ext cx="1346666" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19892,10 +19930,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1341777" y="4044"/>
+                <a:pt x="1346666" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19950,8 +19988,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2914618" y="2728920"/>
-        <a:ext cx="67088" cy="67088"/>
+        <a:off x="2923942" y="2690422"/>
+        <a:ext cx="67333" cy="67333"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{3A58F96D-43A0-4E22-A03B-64FF8A7610E3}">
@@ -19961,8 +19999,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3056471" y="3244439"/>
-          <a:ext cx="1402222" cy="360228"/>
+          <a:off x="3066312" y="3207818"/>
+          <a:ext cx="1407331" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20032,8 +20070,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3067022" y="3254990"/>
-        <a:ext cx="1381120" cy="339126"/>
+        <a:off x="3076901" y="3218407"/>
+        <a:ext cx="1386153" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{BC1A1E23-E0C9-4175-8735-D110618B99B3}">
@@ -20043,8 +20081,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19004863">
-          <a:off x="4418296" y="3318615"/>
-          <a:ext cx="297408" cy="8089"/>
+          <a:off x="4433100" y="3282214"/>
+          <a:ext cx="298492" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20055,10 +20093,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="297408" y="4044"/>
+                <a:pt x="298492" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20113,8 +20151,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4559565" y="3315224"/>
-        <a:ext cx="14870" cy="14870"/>
+        <a:off x="4574883" y="3278862"/>
+        <a:ext cx="14924" cy="14924"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{5D691BA5-158A-4034-AEDA-B152BE077B27}">
@@ -20124,8 +20162,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4675308" y="3039060"/>
-          <a:ext cx="1769726" cy="363410"/>
+          <a:off x="4691048" y="3001692"/>
+          <a:ext cx="1776175" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20195,8 +20233,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4685952" y="3049704"/>
-        <a:ext cx="1748438" cy="342122"/>
+        <a:off x="4701731" y="3012375"/>
+        <a:ext cx="1754809" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{C26309FF-9296-40B3-913C-85759C2B07DC}">
@@ -20206,8 +20244,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6445035" y="3216721"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="6467223" y="3179948"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20218,10 +20256,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20276,8 +20314,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6547927" y="3215350"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="6570490" y="3178624"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A4750321-4845-43B0-945B-4B9E7C7A668E}">
@@ -20287,8 +20325,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6661650" y="3039060"/>
-          <a:ext cx="3156395" cy="363410"/>
+          <a:off x="6684628" y="3001692"/>
+          <a:ext cx="3167897" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20382,8 +20420,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6672294" y="3049704"/>
-        <a:ext cx="3135107" cy="342122"/>
+        <a:off x="6695311" y="3012375"/>
+        <a:ext cx="3146531" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{CCE9C4CE-7CF8-4820-8390-F3CBCCE81ED7}">
@@ -20393,8 +20431,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9818046" y="3216721"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9852525" y="3179948"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20405,10 +20443,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20463,8 +20501,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9920939" y="3215350"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9955792" y="3178624"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D954D938-3009-44F7-BB4F-D9E8AFB2B291}">
@@ -20474,8 +20512,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10034662" y="3037285"/>
-          <a:ext cx="1801141" cy="366960"/>
+          <a:off x="10069930" y="2999910"/>
+          <a:ext cx="1807704" cy="368297"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20545,8 +20583,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10045410" y="3048033"/>
-        <a:ext cx="1779645" cy="345464"/>
+        <a:off x="10080717" y="3010697"/>
+        <a:ext cx="1786130" cy="346723"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D01C8F64-85EC-45F5-B192-363D2A57FB6E}">
@@ -20556,8 +20594,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2595137">
-          <a:off x="4418296" y="3522403"/>
-          <a:ext cx="297408" cy="8089"/>
+          <a:off x="4433100" y="3486744"/>
+          <a:ext cx="298492" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20568,10 +20606,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="297408" y="4044"/>
+                <a:pt x="298492" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20626,8 +20664,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4559565" y="3519012"/>
-        <a:ext cx="14870" cy="14870"/>
+        <a:off x="4574883" y="3483392"/>
+        <a:ext cx="14924" cy="14924"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7832722B-5DD1-4AAD-819C-BC966C90EDAC}">
@@ -20637,8 +20675,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4675308" y="3446636"/>
-          <a:ext cx="1769726" cy="363410"/>
+          <a:off x="4691048" y="3410752"/>
+          <a:ext cx="1776175" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20708,8 +20746,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4685952" y="3457280"/>
-        <a:ext cx="1748438" cy="342122"/>
+        <a:off x="4701731" y="3421435"/>
+        <a:ext cx="1754809" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9B049FA9-70FB-4D7E-AD76-2BFCDB3B4195}">
@@ -20719,8 +20757,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6445035" y="3624296"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="6467223" y="3589009"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20731,10 +20769,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20789,8 +20827,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6547927" y="3622926"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="6570490" y="3587684"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B5153D0A-E9E7-482C-B1CC-838341F8F3D8}">
@@ -20800,8 +20838,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6661650" y="3446636"/>
-          <a:ext cx="3156395" cy="363410"/>
+          <a:off x="6684628" y="3410752"/>
+          <a:ext cx="3167897" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20887,8 +20925,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6672294" y="3457280"/>
-        <a:ext cx="3135107" cy="342122"/>
+        <a:off x="6695311" y="3421435"/>
+        <a:ext cx="3146531" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1118BB77-BCCA-46BE-8B0C-417EE0F19393}">
@@ -20898,8 +20936,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9818046" y="3624296"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9852525" y="3589009"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20910,10 +20948,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20968,8 +21006,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9920939" y="3622926"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9955792" y="3587684"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A1FE2FD1-D3B2-4F02-B33F-7EA3496A9D7D}">
@@ -20979,8 +21017,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10034662" y="3444861"/>
-          <a:ext cx="1801141" cy="366960"/>
+          <a:off x="10069930" y="3408971"/>
+          <a:ext cx="1807704" cy="368297"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21050,8 +21088,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10045410" y="3455609"/>
-        <a:ext cx="1779645" cy="345464"/>
+        <a:off x="10080717" y="3419758"/>
+        <a:ext cx="1786130" cy="346723"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{ACD64E2A-6A03-49D1-9C11-853B1D5FDA3F}">
@@ -21061,8 +21099,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="4880920">
-          <a:off x="572123" y="4231846"/>
-          <a:ext cx="1440061" cy="8089"/>
+          <a:off x="572912" y="4198773"/>
+          <a:ext cx="1445308" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21073,10 +21111,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1440061" y="4044"/>
+                <a:pt x="1445308" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21131,8 +21169,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1256152" y="4199889"/>
-        <a:ext cx="72003" cy="72003"/>
+        <a:off x="1259433" y="4166750"/>
+        <a:ext cx="72265" cy="72265"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4915DA81-5EFF-4A45-B117-A1C9369BA960}">
@@ -21142,8 +21180,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="1400462" y="4767614"/>
-          <a:ext cx="1432488" cy="360228"/>
+          <a:off x="1404269" y="4736544"/>
+          <a:ext cx="1437708" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21265,8 +21303,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1411013" y="4778165"/>
-        <a:ext cx="1411386" cy="339126"/>
+        <a:off x="1414858" y="4747133"/>
+        <a:ext cx="1416530" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A3777E34-F7A1-4ABC-99E9-9C9A9AB7B959}">
@@ -21276,8 +21314,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17225057">
-          <a:off x="2577781" y="4598311"/>
-          <a:ext cx="722633" cy="8089"/>
+          <a:off x="2585877" y="4566573"/>
+          <a:ext cx="725267" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21288,10 +21326,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="722633" y="4044"/>
+                <a:pt x="725267" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21346,8 +21384,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2921032" y="4584290"/>
-        <a:ext cx="36131" cy="36131"/>
+        <a:off x="2930379" y="4552551"/>
+        <a:ext cx="36263" cy="36263"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{23228D17-0E30-4278-86F1-009AEEE4B90D}">
@@ -21357,8 +21395,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3045245" y="4076868"/>
-          <a:ext cx="1402222" cy="360228"/>
+          <a:off x="3055045" y="4043280"/>
+          <a:ext cx="1407331" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21428,8 +21466,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3055796" y="4087419"/>
-        <a:ext cx="1381120" cy="339126"/>
+        <a:off x="3065634" y="4053869"/>
+        <a:ext cx="1386153" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A22E3146-1836-4A0C-A6D3-4503A76A9781}">
@@ -21439,8 +21477,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19004863">
-          <a:off x="4407070" y="4151044"/>
-          <a:ext cx="297408" cy="8089"/>
+          <a:off x="4421833" y="4117676"/>
+          <a:ext cx="298492" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21451,10 +21489,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="297408" y="4044"/>
+                <a:pt x="298492" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21509,8 +21547,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4548339" y="4147653"/>
-        <a:ext cx="14870" cy="14870"/>
+        <a:off x="4563616" y="4114324"/>
+        <a:ext cx="14924" cy="14924"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{06E3AC3D-2CA5-4C28-B4EE-08E1F5093575}">
@@ -21520,8 +21558,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4664082" y="3871489"/>
-          <a:ext cx="1769726" cy="363410"/>
+          <a:off x="4679781" y="3837154"/>
+          <a:ext cx="1776175" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21607,8 +21645,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4674726" y="3882133"/>
-        <a:ext cx="1748438" cy="342122"/>
+        <a:off x="4690464" y="3847837"/>
+        <a:ext cx="1754809" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{AB38F8C9-39F9-48F1-A4B9-359AD3B6C9E1}">
@@ -21618,8 +21656,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6433809" y="4049150"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="6455956" y="4015410"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21630,10 +21668,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21688,8 +21726,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6536701" y="4047779"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="6559223" y="4014086"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{94E3E4AC-563C-467A-AD10-294BF8A33BAF}">
@@ -21699,8 +21737,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6650424" y="3871489"/>
-          <a:ext cx="3156395" cy="363410"/>
+          <a:off x="6673361" y="3837154"/>
+          <a:ext cx="3167897" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21786,8 +21824,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6661068" y="3882133"/>
-        <a:ext cx="3135107" cy="342122"/>
+        <a:off x="6684044" y="3847837"/>
+        <a:ext cx="3146531" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{CE4A2E59-3DB6-4586-9EDA-16655120708B}">
@@ -21797,8 +21835,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9806820" y="4049150"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9841258" y="4015410"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21809,10 +21847,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21867,8 +21905,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9909712" y="4047779"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9944525" y="4014086"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{74F8E0C0-A1C2-4026-BDD1-211E4452BF84}">
@@ -21878,8 +21916,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10023436" y="3869714"/>
-          <a:ext cx="1801141" cy="366960"/>
+          <a:off x="10058663" y="3835372"/>
+          <a:ext cx="1807704" cy="368297"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21949,8 +21987,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10034184" y="3880462"/>
-        <a:ext cx="1779645" cy="345464"/>
+        <a:off x="10069450" y="3846159"/>
+        <a:ext cx="1786130" cy="346723"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{3776BE60-D86F-469E-9605-E0609281B4B9}">
@@ -21960,8 +21998,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2595137">
-          <a:off x="4407070" y="4354831"/>
-          <a:ext cx="297408" cy="8089"/>
+          <a:off x="4421833" y="4322206"/>
+          <a:ext cx="298492" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21972,10 +22010,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="297408" y="4044"/>
+                <a:pt x="298492" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22030,8 +22068,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4548339" y="4351441"/>
-        <a:ext cx="14870" cy="14870"/>
+        <a:off x="4563616" y="4318854"/>
+        <a:ext cx="14924" cy="14924"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{DC0F0790-8247-4EA1-A5BD-20B9C2810EA5}">
@@ -22041,8 +22079,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4664082" y="4279065"/>
-          <a:ext cx="1769726" cy="363410"/>
+          <a:off x="4679781" y="4246214"/>
+          <a:ext cx="1776175" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22112,8 +22150,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4674726" y="4289709"/>
-        <a:ext cx="1748438" cy="342122"/>
+        <a:off x="4690464" y="4256897"/>
+        <a:ext cx="1754809" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{82B78A4F-EF07-4DEA-A3EC-7BA9DD55DC45}">
@@ -22123,8 +22161,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6433809" y="4456725"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="6455956" y="4424471"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22135,10 +22173,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22193,8 +22231,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6536701" y="4455354"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="6559223" y="4423146"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4D82C0F8-05DA-476F-9FFD-EF5362E37ABC}">
@@ -22204,8 +22242,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6650424" y="4279065"/>
-          <a:ext cx="3156395" cy="363410"/>
+          <a:off x="6673361" y="4246214"/>
+          <a:ext cx="3167897" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22283,8 +22321,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6661068" y="4289709"/>
-        <a:ext cx="3135107" cy="342122"/>
+        <a:off x="6684044" y="4256897"/>
+        <a:ext cx="3146531" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6F09ED48-69E5-4359-AEF9-003C31CF3834}">
@@ -22294,8 +22332,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9806820" y="4456725"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9841258" y="4424471"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22306,10 +22344,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22364,8 +22402,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9909712" y="4455354"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9944525" y="4423146"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7F4C8494-F5DD-49F1-B7FE-320AAF64A334}">
@@ -22375,8 +22413,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10023436" y="4277290"/>
-          <a:ext cx="1801141" cy="366960"/>
+          <a:off x="10058663" y="4244433"/>
+          <a:ext cx="1807704" cy="368297"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22451,8 +22489,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10034184" y="4288038"/>
-        <a:ext cx="1779645" cy="345464"/>
+        <a:off x="10069450" y="4255220"/>
+        <a:ext cx="1786130" cy="346723"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E97A89EA-A088-4B36-94ED-03E39FF28C24}">
@@ -22462,8 +22500,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="1512707">
-          <a:off x="2821547" y="4994677"/>
-          <a:ext cx="239423" cy="8089"/>
+          <a:off x="2830532" y="4964383"/>
+          <a:ext cx="240295" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22474,10 +22512,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="239423" y="4044"/>
+                <a:pt x="240295" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22532,8 +22570,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2935273" y="4992736"/>
-        <a:ext cx="11971" cy="11971"/>
+        <a:off x="2944672" y="4962486"/>
+        <a:ext cx="12014" cy="12014"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1279AA60-C872-4597-B281-C6CC2E4A34C2}">
@@ -22543,8 +22581,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3049566" y="4869600"/>
-          <a:ext cx="1402222" cy="360228"/>
+          <a:off x="3059382" y="4838902"/>
+          <a:ext cx="1407331" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22614,8 +22652,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3060117" y="4880151"/>
-        <a:ext cx="1381120" cy="339126"/>
+        <a:off x="3069971" y="4849491"/>
+        <a:ext cx="1386153" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{255CD393-ED80-4D10-A68E-31ED59592E3B}">
@@ -22625,8 +22663,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19138242">
-          <a:off x="4417227" y="4953303"/>
-          <a:ext cx="281417" cy="8089"/>
+          <a:off x="4432026" y="4922858"/>
+          <a:ext cx="282442" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22637,10 +22675,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="281417" y="4044"/>
+                <a:pt x="282442" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22695,8 +22733,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4550900" y="4950312"/>
-        <a:ext cx="14070" cy="14070"/>
+        <a:off x="4566186" y="4919907"/>
+        <a:ext cx="14122" cy="14122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{2340676A-EBD4-4E22-BA9C-E56B6A62904C}">
@@ -22706,8 +22744,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4664082" y="4683274"/>
-          <a:ext cx="1769726" cy="363410"/>
+          <a:off x="4679781" y="4651897"/>
+          <a:ext cx="1776175" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22777,8 +22815,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4674726" y="4693918"/>
-        <a:ext cx="1748438" cy="342122"/>
+        <a:off x="4690464" y="4662580"/>
+        <a:ext cx="1754809" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{EB837690-03CF-4B39-A4B0-AFC71E15928A}">
@@ -22788,8 +22826,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="27806">
-          <a:off x="6433805" y="4861829"/>
-          <a:ext cx="220944" cy="8089"/>
+          <a:off x="6455952" y="4831051"/>
+          <a:ext cx="221749" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22800,10 +22838,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="220944" y="4044"/>
+                <a:pt x="221749" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22858,8 +22896,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6538754" y="4860350"/>
-        <a:ext cx="11047" cy="11047"/>
+        <a:off x="6561283" y="4829617"/>
+        <a:ext cx="11087" cy="11087"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6CD3FE0A-3BBE-455B-B381-72424654A1B0}">
@@ -22869,8 +22907,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6654746" y="4686652"/>
-          <a:ext cx="3155594" cy="360228"/>
+          <a:off x="6677698" y="4655287"/>
+          <a:ext cx="3167092" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22948,8 +22986,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6665297" y="4697203"/>
-        <a:ext cx="3134492" cy="339126"/>
+        <a:off x="6688287" y="4665876"/>
+        <a:ext cx="3145914" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B86CABA2-1933-4D02-A0D3-AA6DEA35BCA7}">
@@ -22959,8 +22997,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9810340" y="4862722"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9844791" y="4831947"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22971,10 +23009,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23029,8 +23067,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9913232" y="4861351"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9948058" y="4830623"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{920A36CD-D69B-4AB0-8DA2-4963F1111FE2}">
@@ -23040,8 +23078,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10026956" y="4686652"/>
-          <a:ext cx="1801141" cy="360228"/>
+          <a:off x="10062195" y="4655287"/>
+          <a:ext cx="1807704" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23111,8 +23149,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10037507" y="4697203"/>
-        <a:ext cx="1780039" cy="339126"/>
+        <a:off x="10072784" y="4665876"/>
+        <a:ext cx="1786526" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{EE30240B-4D3F-4585-94A4-7AD0CBEBACD0}">
@@ -23122,8 +23160,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2755727">
-          <a:off x="4405327" y="5155316"/>
-          <a:ext cx="305216" cy="8089"/>
+          <a:off x="4420083" y="5125607"/>
+          <a:ext cx="306328" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23134,10 +23172,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="305216" y="4044"/>
+                <a:pt x="306328" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23192,8 +23230,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4550305" y="5151730"/>
-        <a:ext cx="15260" cy="15260"/>
+        <a:off x="4565589" y="5122059"/>
+        <a:ext cx="15316" cy="15316"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9B0332A1-DFA5-4E72-89B6-8E8C50F667E1}">
@@ -23203,8 +23241,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4664082" y="5087300"/>
-          <a:ext cx="1769726" cy="363410"/>
+          <a:off x="4679781" y="5057395"/>
+          <a:ext cx="1776175" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23301,8 +23339,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4674726" y="5097944"/>
-        <a:ext cx="1748438" cy="342122"/>
+        <a:off x="4690464" y="5068078"/>
+        <a:ext cx="1754809" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4EF5B1E7-3D92-44D9-8E8A-E2A10FB649AC}">
@@ -23312,8 +23350,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="27806">
-          <a:off x="6433805" y="5265854"/>
-          <a:ext cx="220944" cy="8089"/>
+          <a:off x="6455952" y="5236548"/>
+          <a:ext cx="221749" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23324,10 +23362,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="220944" y="4044"/>
+                <a:pt x="221749" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23382,8 +23420,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6538754" y="5264375"/>
-        <a:ext cx="11047" cy="11047"/>
+        <a:off x="6561283" y="5235115"/>
+        <a:ext cx="11087" cy="11087"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9AC7A0EB-B59E-41D9-A589-CB90FBF4305E}">
@@ -23393,8 +23431,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6654746" y="5090678"/>
-          <a:ext cx="3155594" cy="360228"/>
+          <a:off x="6677698" y="5060785"/>
+          <a:ext cx="3167092" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23480,8 +23518,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6665297" y="5101229"/>
-        <a:ext cx="3134492" cy="339126"/>
+        <a:off x="6688287" y="5071374"/>
+        <a:ext cx="3145914" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{2F5A23ED-2B4B-4307-BAD6-D126CED4ED45}">
@@ -23491,8 +23529,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9810340" y="5266748"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9844791" y="5237445"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23503,10 +23541,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23561,8 +23599,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9913232" y="5265377"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9948058" y="5236121"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{C9CCA1DF-737F-40B9-8662-1EBAE874B88C}">
@@ -23572,8 +23610,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10026956" y="5090678"/>
-          <a:ext cx="1801141" cy="360228"/>
+          <a:off x="10062195" y="5060785"/>
+          <a:ext cx="1807704" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23643,8 +23681,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10037507" y="5101229"/>
-        <a:ext cx="1780039" cy="339126"/>
+        <a:off x="10072784" y="5071374"/>
+        <a:ext cx="1786526" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{06804470-2E4E-45CC-AD07-54CD8F165228}">
@@ -23654,8 +23692,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="4379331">
-          <a:off x="2571049" y="5297697"/>
-          <a:ext cx="740419" cy="8089"/>
+          <a:off x="2579121" y="5268507"/>
+          <a:ext cx="743117" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23666,10 +23704,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="740419" y="4044"/>
+                <a:pt x="743117" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23724,8 +23762,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2922748" y="5283231"/>
-        <a:ext cx="37020" cy="37020"/>
+        <a:off x="2932101" y="5254039"/>
+        <a:ext cx="37155" cy="37155"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D9D1FF4E-B146-4A17-8BAD-E6A8247731B1}">
@@ -23735,8 +23773,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3049566" y="5475639"/>
-          <a:ext cx="1402227" cy="360228"/>
+          <a:off x="3059382" y="5447149"/>
+          <a:ext cx="1407337" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23822,8 +23860,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3060117" y="5486190"/>
-        <a:ext cx="1381125" cy="339126"/>
+        <a:off x="3069971" y="5457738"/>
+        <a:ext cx="1386159" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{458C594D-E94A-4416-A27A-8211BD0C18EB}">
@@ -23833,8 +23871,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4451794" y="5651709"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="4466719" y="5623809"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23845,10 +23883,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23903,8 +23941,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4554686" y="5650338"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="4569986" y="5622484"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E6BB35B6-4DC7-42B5-A329-D93F595605BC}">
@@ -23914,8 +23952,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4668409" y="5474048"/>
-          <a:ext cx="1759258" cy="363410"/>
+          <a:off x="4684124" y="5445552"/>
+          <a:ext cx="1765668" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -24001,8 +24039,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4679053" y="5484692"/>
-        <a:ext cx="1737970" cy="342122"/>
+        <a:off x="4694807" y="5456235"/>
+        <a:ext cx="1744302" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{F3CE9778-2DAD-459C-A92D-C581128238EF}">
@@ -24012,8 +24050,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6427668" y="5651709"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="6449793" y="5623809"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -24024,10 +24062,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -24082,8 +24120,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6530560" y="5650338"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="6553060" y="5622484"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A62201D7-F2CC-41E5-BB68-F68B79E1464B}">
@@ -24093,8 +24131,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6644283" y="5475639"/>
-          <a:ext cx="3155594" cy="360228"/>
+          <a:off x="6667197" y="5447149"/>
+          <a:ext cx="3167092" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -24164,8 +24202,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6654834" y="5486190"/>
-        <a:ext cx="3134492" cy="339126"/>
+        <a:off x="6677786" y="5457738"/>
+        <a:ext cx="3145914" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{46794C65-61A0-4B52-A42E-5CC9D77E3723}">
@@ -24175,8 +24213,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9799878" y="5651709"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9834290" y="5623809"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -24187,10 +24225,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -24245,8 +24283,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9902770" y="5650338"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9937557" y="5622484"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{C61F938B-5A64-4BF7-B003-81E0909084B1}">
@@ -24256,8 +24294,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10016493" y="5475639"/>
-          <a:ext cx="1801141" cy="360228"/>
+          <a:off x="10051695" y="5447149"/>
+          <a:ext cx="1807704" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -24327,8 +24365,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10027044" y="5486190"/>
-        <a:ext cx="1780039" cy="339126"/>
+        <a:off x="10062284" y="5457738"/>
+        <a:ext cx="1786526" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
   </dsp:spTree>
@@ -27049,13 +27087,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>439</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>4792980</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>53340</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
@@ -28119,22 +28157,159 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA7446D1-A9E6-4F8D-B799-CB90AD03762A}">
-  <dimension ref="A1:C1"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="60.08203125" customWidth="1"/>
+    <col min="1" max="1" width="3.9140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="77.6640625" customWidth="1"/>
+    <col min="3" max="3" width="58.58203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.45">
       <c r="A1" s="62" t="s">
-        <v>337</v>
-      </c>
-      <c r="B1" s="59" t="s">
+        <v>336</v>
+      </c>
+      <c r="B1" s="60" t="s">
+        <v>421</v>
+      </c>
+      <c r="C1" s="59" t="s">
         <v>422</v>
       </c>
-      <c r="C1" s="59" t="s">
-        <v>423</v>
-      </c>
+    </row>
+    <row r="2" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="A2" s="61">
+        <v>1</v>
+      </c>
+      <c r="B2" s="111" t="s">
+        <v>426</v>
+      </c>
+      <c r="C2" s="58"/>
+    </row>
+    <row r="3" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="A3" s="61">
+        <v>2</v>
+      </c>
+      <c r="B3" s="111" t="s">
+        <v>428</v>
+      </c>
+      <c r="C3" s="58"/>
+    </row>
+    <row r="4" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="A4" s="61">
+        <v>3</v>
+      </c>
+      <c r="B4" s="111" t="s">
+        <v>430</v>
+      </c>
+      <c r="C4" s="58"/>
+    </row>
+    <row r="5" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="A5" s="61">
+        <v>4</v>
+      </c>
+      <c r="B5" s="111" t="s">
+        <v>432</v>
+      </c>
+      <c r="C5" s="58"/>
+    </row>
+    <row r="6" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="A6" s="61">
+        <v>5</v>
+      </c>
+      <c r="B6" s="111" t="s">
+        <v>434</v>
+      </c>
+      <c r="C6" s="58"/>
+    </row>
+    <row r="7" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="A7" s="61">
+        <v>6</v>
+      </c>
+      <c r="B7" s="111" t="s">
+        <v>436</v>
+      </c>
+      <c r="C7" s="58"/>
+    </row>
+    <row r="8" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="A8" s="61">
+        <v>7</v>
+      </c>
+      <c r="B8" s="111" t="s">
+        <v>438</v>
+      </c>
+      <c r="C8" s="58"/>
+    </row>
+    <row r="9" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="A9" s="61">
+        <v>8</v>
+      </c>
+      <c r="B9" s="111" t="s">
+        <v>440</v>
+      </c>
+      <c r="C9" s="58"/>
+    </row>
+    <row r="10" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="A10" s="61">
+        <v>9</v>
+      </c>
+      <c r="B10" s="111" t="s">
+        <v>442</v>
+      </c>
+      <c r="C10" s="58"/>
+    </row>
+    <row r="11" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="A11" s="61">
+        <v>10</v>
+      </c>
+      <c r="B11" s="111" t="s">
+        <v>444</v>
+      </c>
+      <c r="C11" s="58"/>
+    </row>
+    <row r="12" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="A12" s="61">
+        <v>11</v>
+      </c>
+      <c r="B12" s="111" t="s">
+        <v>446</v>
+      </c>
+      <c r="C12" s="58"/>
+    </row>
+    <row r="13" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+      <c r="A13" s="61">
+        <v>12</v>
+      </c>
+      <c r="B13" s="111" t="s">
+        <v>448</v>
+      </c>
+      <c r="C13" s="58"/>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A14" s="61">
+        <v>13</v>
+      </c>
+      <c r="B14" s="112" t="s">
+        <v>320</v>
+      </c>
+      <c r="C14" s="58"/>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A15" s="61">
+        <v>14</v>
+      </c>
+      <c r="B15" s="113" t="s">
+        <v>322</v>
+      </c>
+      <c r="C15" s="58"/>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A16" s="61">
+        <v>15</v>
+      </c>
+      <c r="B16" s="113" t="s">
+        <v>326</v>
+      </c>
+      <c r="C16" s="58"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -28226,8 +28401,8 @@
       <c r="A5" s="34" t="s">
         <v>172</v>
       </c>
-      <c r="B5" s="105" t="s">
-        <v>450</v>
+      <c r="B5" s="71" t="s">
+        <v>449</v>
       </c>
       <c r="C5" s="35">
         <v>46275</v>
@@ -28237,40 +28412,42 @@
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A6" s="102" t="s">
+      <c r="A6" s="70" t="s">
         <v>174</v>
       </c>
-      <c r="B6" s="106" t="s">
-        <v>451</v>
-      </c>
-      <c r="C6" s="103">
+      <c r="B6" s="72" t="s">
+        <v>450</v>
+      </c>
+      <c r="C6" s="76">
         <v>46275</v>
       </c>
-      <c r="D6" s="100" t="s">
+      <c r="D6" s="78" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A7" s="102" t="s">
+      <c r="A7" s="70" t="s">
         <v>174</v>
       </c>
-      <c r="B7" s="107" t="s">
-        <v>452</v>
-      </c>
-      <c r="C7" s="104"/>
-      <c r="D7" s="101"/>
+      <c r="B7" s="73" t="s">
+        <v>451</v>
+      </c>
+      <c r="C7" s="77"/>
+      <c r="D7" s="79"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" s="33" t="s">
         <v>175</v>
       </c>
-      <c r="B8" s="108" t="s">
-        <v>453</v>
+      <c r="B8" s="74" t="s">
+        <v>452</v>
       </c>
       <c r="C8" s="35">
         <v>46276</v>
       </c>
-      <c r="D8" s="33"/>
+      <c r="D8" s="33" t="s">
+        <v>316</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" s="33" t="s">
@@ -28280,9 +28457,11 @@
       <c r="C9" s="35">
         <v>46276</v>
       </c>
-      <c r="D9" s="33"/>
+      <c r="D9" s="33" t="s">
+        <v>316</v>
+      </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4" ht="34" x14ac:dyDescent="0.45">
       <c r="A10" s="33" t="s">
         <v>177</v>
       </c>
@@ -28290,11 +28469,11 @@
       <c r="C10" s="35">
         <v>46276</v>
       </c>
-      <c r="D10" s="33" t="s">
-        <v>320</v>
+      <c r="D10" s="34" t="s">
+        <v>454</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" ht="34" x14ac:dyDescent="0.45">
       <c r="A11" s="33" t="s">
         <v>178</v>
       </c>
@@ -28302,7 +28481,9 @@
       <c r="C11" s="55">
         <v>46279.645833333336</v>
       </c>
-      <c r="D11" s="33"/>
+      <c r="D11" s="34" t="s">
+        <v>455</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -28367,7 +28548,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A2" s="69" t="s">
+      <c r="A2" s="80" t="s">
         <v>18</v>
       </c>
       <c r="B2" s="7" t="s">
@@ -28384,7 +28565,7 @@
       <c r="G2" s="10"/>
     </row>
     <row r="3" spans="1:7" ht="64" x14ac:dyDescent="0.45">
-      <c r="A3" s="70"/>
+      <c r="A3" s="81"/>
       <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
@@ -28401,7 +28582,7 @@
       <c r="G3" s="11"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A4" s="70"/>
+      <c r="A4" s="81"/>
       <c r="B4" s="4" t="s">
         <v>184</v>
       </c>
@@ -28416,7 +28597,7 @@
       <c r="G4" s="11"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A5" s="70"/>
+      <c r="A5" s="81"/>
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
@@ -28431,7 +28612,7 @@
       <c r="G5" s="11"/>
     </row>
     <row r="6" spans="1:7" ht="48" x14ac:dyDescent="0.45">
-      <c r="A6" s="70"/>
+      <c r="A6" s="81"/>
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
@@ -28450,7 +28631,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="71"/>
+      <c r="A7" s="82"/>
       <c r="B7" s="13" t="s">
         <v>15</v>
       </c>
@@ -28467,7 +28648,7 @@
       <c r="G7" s="15"/>
     </row>
     <row r="8" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="72" t="s">
+      <c r="A8" s="83" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="7" t="s">
@@ -28488,7 +28669,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A9" s="73"/>
+      <c r="A9" s="84"/>
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -28505,7 +28686,7 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A10" s="73"/>
+      <c r="A10" s="84"/>
       <c r="B10" s="4" t="s">
         <v>4</v>
       </c>
@@ -28522,7 +28703,7 @@
       <c r="G10" s="11"/>
     </row>
     <row r="11" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="73"/>
+      <c r="A11" s="84"/>
       <c r="B11" s="4" t="s">
         <v>7</v>
       </c>
@@ -28537,7 +28718,7 @@
       <c r="G11" s="11"/>
     </row>
     <row r="12" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="74"/>
+      <c r="A12" s="85"/>
       <c r="B12" s="16" t="s">
         <v>8</v>
       </c>
@@ -28554,7 +28735,7 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A13" s="75" t="s">
+      <c r="A13" s="86" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="7" t="s">
@@ -28575,7 +28756,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="64.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="76"/>
+      <c r="A14" s="87"/>
       <c r="B14" s="4" t="s">
         <v>10</v>
       </c>
@@ -28592,7 +28773,7 @@
       <c r="G14" s="11"/>
     </row>
     <row r="15" spans="1:7" ht="64" x14ac:dyDescent="0.45">
-      <c r="A15" s="76"/>
+      <c r="A15" s="87"/>
       <c r="B15" s="4" t="s">
         <v>218</v>
       </c>
@@ -28613,7 +28794,7 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A16" s="77"/>
+      <c r="A16" s="88"/>
       <c r="B16" s="16" t="s">
         <v>11</v>
       </c>
@@ -28645,7 +28826,7 @@
   <sheetPr>
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
@@ -28655,42 +28836,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A1" s="41"/>
-      <c r="B1" s="40" t="s">
+      <c r="A1" s="110"/>
+      <c r="B1" s="110" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A2" s="41"/>
+      <c r="B2" s="40" t="s">
         <v>199</v>
       </c>
-      <c r="C1" s="40" t="s">
+      <c r="C2" s="40" t="s">
         <v>200</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="D2" s="40" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="32" x14ac:dyDescent="0.45">
-      <c r="A2" s="40" t="s">
+    <row r="3" spans="1:4" ht="32" x14ac:dyDescent="0.45">
+      <c r="A3" s="40" t="s">
         <v>179</v>
       </c>
-      <c r="B2" s="36" t="s">
+      <c r="B3" s="36" t="s">
         <v>181</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C3" s="37" t="s">
         <v>187</v>
       </c>
-      <c r="D2" s="37" t="s">
+      <c r="D3" s="37" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="64" x14ac:dyDescent="0.45">
-      <c r="A3" s="40" t="s">
+    <row r="4" spans="1:4" ht="64" x14ac:dyDescent="0.45">
+      <c r="A4" s="40" t="s">
         <v>180</v>
       </c>
-      <c r="B3" s="37" t="s">
+      <c r="B4" s="37" t="s">
         <v>182</v>
       </c>
-      <c r="C3" s="37" t="s">
+      <c r="C4" s="37" t="s">
         <v>188</v>
       </c>
-      <c r="D3" s="37" t="s">
+      <c r="D4" s="37" t="s">
         <v>202</v>
       </c>
     </row>
@@ -28760,14 +28947,14 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A5" s="79" t="s">
+      <c r="A5" s="96" t="s">
         <v>273</v>
       </c>
-      <c r="B5" s="79"/>
-      <c r="C5" s="79"/>
+      <c r="B5" s="96"/>
+      <c r="C5" s="96"/>
     </row>
     <row r="6" spans="1:4" ht="32" x14ac:dyDescent="0.45">
-      <c r="A6" s="91" t="s">
+      <c r="A6" s="98" t="s">
         <v>204</v>
       </c>
       <c r="B6" s="47" t="s">
@@ -28778,7 +28965,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="32" x14ac:dyDescent="0.45">
-      <c r="A7" s="92"/>
+      <c r="A7" s="99"/>
       <c r="B7" s="47" t="s">
         <v>292</v>
       </c>
@@ -28787,7 +28974,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" ht="32" x14ac:dyDescent="0.45">
-      <c r="A8" s="92"/>
+      <c r="A8" s="99"/>
       <c r="B8" s="47" t="s">
         <v>295</v>
       </c>
@@ -28796,7 +28983,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A9" s="92"/>
+      <c r="A9" s="99"/>
       <c r="B9" s="47" t="s">
         <v>303</v>
       </c>
@@ -28805,7 +28992,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A10" s="93"/>
+      <c r="A10" s="100"/>
       <c r="B10" s="47" t="s">
         <v>297</v>
       </c>
@@ -28828,18 +29015,18 @@
       <c r="C12" s="49"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A13" s="84" t="s">
+      <c r="A13" s="90" t="s">
         <v>304</v>
       </c>
-      <c r="B13" s="85"/>
-      <c r="C13" s="86"/>
+      <c r="B13" s="91"/>
+      <c r="C13" s="92"/>
     </row>
     <row r="14" spans="1:4" ht="52" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="94" t="s">
+      <c r="A14" s="101" t="s">
         <v>230</v>
       </c>
-      <c r="B14" s="95"/>
-      <c r="C14" s="96"/>
+      <c r="B14" s="102"/>
+      <c r="C14" s="103"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="49"/>
@@ -28847,112 +29034,112 @@
       <c r="D19" s="49"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A31" s="79" t="s">
+      <c r="A31" s="96" t="s">
         <v>274</v>
       </c>
-      <c r="B31" s="79"/>
-      <c r="C31" s="79"/>
+      <c r="B31" s="96"/>
+      <c r="C31" s="96"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A32" s="87" t="s">
+      <c r="A32" s="93" t="s">
         <v>318</v>
       </c>
-      <c r="B32" s="88"/>
-      <c r="C32" s="89"/>
+      <c r="B32" s="94"/>
+      <c r="C32" s="95"/>
     </row>
     <row r="33" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="83" t="s">
+      <c r="A33" s="89" t="s">
         <v>231</v>
       </c>
       <c r="B33" s="50" t="s">
         <v>208</v>
       </c>
-      <c r="C33" s="90" t="s">
+      <c r="C33" s="97" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A34" s="83"/>
+      <c r="A34" s="89"/>
       <c r="B34" s="50" t="s">
         <v>209</v>
       </c>
-      <c r="C34" s="90"/>
+      <c r="C34" s="97"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A35" s="83"/>
+      <c r="A35" s="89"/>
       <c r="B35" s="50" t="s">
         <v>210</v>
       </c>
-      <c r="C35" s="90"/>
+      <c r="C35" s="97"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A36" s="83"/>
+      <c r="A36" s="89"/>
       <c r="B36" s="50" t="s">
         <v>211</v>
       </c>
-      <c r="C36" s="90"/>
+      <c r="C36" s="97"/>
     </row>
     <row r="37" spans="1:5" ht="32" x14ac:dyDescent="0.45">
-      <c r="A37" s="83"/>
+      <c r="A37" s="89"/>
       <c r="B37" s="48" t="s">
         <v>212</v>
       </c>
-      <c r="C37" s="90"/>
+      <c r="C37" s="97"/>
     </row>
     <row r="38" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="83" t="s">
+      <c r="A38" s="89" t="s">
         <v>232</v>
       </c>
       <c r="B38" s="50" t="s">
         <v>213</v>
       </c>
-      <c r="C38" s="90" t="s">
+      <c r="C38" s="97" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A39" s="83"/>
+      <c r="A39" s="89"/>
       <c r="B39" s="50" t="s">
         <v>214</v>
       </c>
-      <c r="C39" s="90"/>
+      <c r="C39" s="97"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A40" s="83"/>
+      <c r="A40" s="89"/>
       <c r="B40" s="50" t="s">
         <v>215</v>
       </c>
-      <c r="C40" s="90"/>
+      <c r="C40" s="97"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A42" s="84" t="s">
+      <c r="A42" s="90" t="s">
         <v>272</v>
       </c>
-      <c r="B42" s="85"/>
-      <c r="C42" s="86"/>
+      <c r="B42" s="91"/>
+      <c r="C42" s="92"/>
     </row>
     <row r="43" spans="1:5" ht="53" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A43" s="83" t="s">
+      <c r="A43" s="89" t="s">
         <v>217</v>
       </c>
-      <c r="B43" s="83"/>
-      <c r="C43" s="83"/>
+      <c r="B43" s="89"/>
+      <c r="C43" s="89"/>
     </row>
     <row r="44" spans="1:5" ht="50.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A44" s="83" t="s">
+      <c r="A44" s="89" t="s">
         <v>317</v>
       </c>
-      <c r="B44" s="83"/>
-      <c r="C44" s="83"/>
+      <c r="B44" s="89"/>
+      <c r="C44" s="89"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A46" s="79" t="s">
+      <c r="A46" s="96" t="s">
         <v>271</v>
       </c>
-      <c r="B46" s="79"/>
-      <c r="C46" s="79"/>
-      <c r="D46" s="79"/>
-      <c r="E46" s="79"/>
+      <c r="B46" s="96"/>
+      <c r="C46" s="96"/>
+      <c r="D46" s="96"/>
+      <c r="E46" s="96"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" s="44" t="s">
@@ -29138,11 +29325,11 @@
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A59" s="80" t="s">
+      <c r="A59" s="105" t="s">
         <v>275</v>
       </c>
-      <c r="B59" s="81"/>
-      <c r="C59" s="82"/>
+      <c r="B59" s="106"/>
+      <c r="C59" s="107"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" s="53" t="s">
@@ -29200,87 +29387,99 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A66" s="79" t="s">
+      <c r="A66" s="96" t="s">
         <v>291</v>
       </c>
-      <c r="B66" s="79"/>
-      <c r="C66" s="79"/>
-      <c r="D66" s="79"/>
+      <c r="B66" s="96"/>
+      <c r="C66" s="96"/>
+      <c r="D66" s="96"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A67" s="78" t="s">
+      <c r="A67" s="104" t="s">
         <v>262</v>
       </c>
-      <c r="B67" s="78"/>
-      <c r="C67" s="78"/>
-      <c r="D67" s="78"/>
+      <c r="B67" s="104"/>
+      <c r="C67" s="104"/>
+      <c r="D67" s="104"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A68" s="78" t="s">
+      <c r="A68" s="104" t="s">
         <v>263</v>
       </c>
-      <c r="B68" s="78"/>
-      <c r="C68" s="78"/>
-      <c r="D68" s="78"/>
+      <c r="B68" s="104"/>
+      <c r="C68" s="104"/>
+      <c r="D68" s="104"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A69" s="78" t="s">
+      <c r="A69" s="104" t="s">
         <v>264</v>
       </c>
-      <c r="B69" s="78"/>
-      <c r="C69" s="78"/>
-      <c r="D69" s="78"/>
+      <c r="B69" s="104"/>
+      <c r="C69" s="104"/>
+      <c r="D69" s="104"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A70" s="78" t="s">
+      <c r="A70" s="104" t="s">
         <v>265</v>
       </c>
-      <c r="B70" s="78"/>
-      <c r="C70" s="78"/>
-      <c r="D70" s="78"/>
+      <c r="B70" s="104"/>
+      <c r="C70" s="104"/>
+      <c r="D70" s="104"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A71" s="78" t="s">
+      <c r="A71" s="104" t="s">
         <v>266</v>
       </c>
-      <c r="B71" s="78"/>
-      <c r="C71" s="78"/>
-      <c r="D71" s="78"/>
+      <c r="B71" s="104"/>
+      <c r="C71" s="104"/>
+      <c r="D71" s="104"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A72" s="78" t="s">
+      <c r="A72" s="104" t="s">
         <v>267</v>
       </c>
-      <c r="B72" s="78"/>
-      <c r="C72" s="78"/>
-      <c r="D72" s="78"/>
+      <c r="B72" s="104"/>
+      <c r="C72" s="104"/>
+      <c r="D72" s="104"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A73" s="78" t="s">
+      <c r="A73" s="104" t="s">
         <v>268</v>
       </c>
-      <c r="B73" s="78"/>
-      <c r="C73" s="78"/>
-      <c r="D73" s="78"/>
+      <c r="B73" s="104"/>
+      <c r="C73" s="104"/>
+      <c r="D73" s="104"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A74" s="78" t="s">
+      <c r="A74" s="104" t="s">
         <v>269</v>
       </c>
-      <c r="B74" s="78"/>
-      <c r="C74" s="78"/>
-      <c r="D74" s="78"/>
+      <c r="B74" s="104"/>
+      <c r="C74" s="104"/>
+      <c r="D74" s="104"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A75" s="78" t="s">
+      <c r="A75" s="104" t="s">
         <v>270</v>
       </c>
-      <c r="B75" s="78"/>
-      <c r="C75" s="78"/>
-      <c r="D75" s="78"/>
+      <c r="B75" s="104"/>
+      <c r="C75" s="104"/>
+      <c r="D75" s="104"/>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="A74:D74"/>
+    <mergeCell ref="A75:D75"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A67:D67"/>
+    <mergeCell ref="A68:D68"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="A70:D70"/>
+    <mergeCell ref="A71:D71"/>
+    <mergeCell ref="A72:D72"/>
     <mergeCell ref="A44:C44"/>
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="A32:C32"/>
@@ -29294,18 +29493,6 @@
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A73:D73"/>
-    <mergeCell ref="A74:D74"/>
-    <mergeCell ref="A75:D75"/>
-    <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A66:D66"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A67:D67"/>
-    <mergeCell ref="A68:D68"/>
-    <mergeCell ref="A69:D69"/>
-    <mergeCell ref="A70:D70"/>
-    <mergeCell ref="A71:D71"/>
-    <mergeCell ref="A72:D72"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -29346,17 +29533,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A1" s="97" t="s">
-        <v>336</v>
-      </c>
-      <c r="B1" s="98"/>
+      <c r="A1" s="108" t="s">
+        <v>335</v>
+      </c>
+      <c r="B1" s="109"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="60" t="s">
+        <v>336</v>
+      </c>
+      <c r="B2" s="38" t="s">
         <v>337</v>
-      </c>
-      <c r="B2" s="38" t="s">
-        <v>338</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="34" x14ac:dyDescent="0.45">
@@ -29364,7 +29551,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="18" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.45">
@@ -29372,7 +29559,7 @@
         <v>2</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
@@ -29380,30 +29567,30 @@
         <v>3</v>
       </c>
       <c r="B5" s="58" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" s="60" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B7" s="59" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C7" s="59" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="D7" s="59" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="E7" s="59" t="s">
+        <v>369</v>
+      </c>
+      <c r="F7" s="59" t="s">
         <v>370</v>
       </c>
-      <c r="F7" s="59" t="s">
-        <v>371</v>
-      </c>
       <c r="H7" s="59" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.45">
@@ -29411,16 +29598,16 @@
         <v>1</v>
       </c>
       <c r="B8" s="58" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C8" s="63" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D8" s="65"/>
       <c r="E8" s="65"/>
       <c r="F8" s="65"/>
       <c r="H8" s="18" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="238" x14ac:dyDescent="0.45">
@@ -29428,22 +29615,22 @@
         <v>2</v>
       </c>
       <c r="B9" s="58" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C9" s="58" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="E9" s="58" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F9" s="18" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H9" s="58" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.45">
@@ -29451,16 +29638,16 @@
         <v>3</v>
       </c>
       <c r="B10" s="58" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C10" s="63" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D10" s="65"/>
       <c r="E10" s="65"/>
       <c r="F10" s="65"/>
       <c r="H10" s="58" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="102" x14ac:dyDescent="0.45">
@@ -29468,22 +29655,22 @@
         <v>4</v>
       </c>
       <c r="B11" s="58" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C11" s="58" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E11" s="58" t="s">
+        <v>372</v>
+      </c>
+      <c r="F11" s="18" t="s">
         <v>373</v>
       </c>
-      <c r="F11" s="18" t="s">
-        <v>374</v>
-      </c>
       <c r="H11" s="58" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="68" x14ac:dyDescent="0.45">
@@ -29491,22 +29678,22 @@
         <v>5</v>
       </c>
       <c r="B12" s="58" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C12" s="58" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E12" s="58" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F12" s="18" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H12" s="58" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="68" x14ac:dyDescent="0.45">
@@ -29514,22 +29701,22 @@
         <v>6</v>
       </c>
       <c r="B13" s="58" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C13" s="58" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E13" s="58" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F13" s="18" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H13" s="58" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.45">
@@ -29537,16 +29724,16 @@
         <v>7</v>
       </c>
       <c r="B14" s="58" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C14" s="63" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D14" s="65"/>
       <c r="E14" s="65"/>
       <c r="F14" s="65"/>
       <c r="H14" s="58" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="15" spans="1:8" ht="136" x14ac:dyDescent="0.45">
@@ -29554,22 +29741,22 @@
         <v>8</v>
       </c>
       <c r="B15" s="58" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C15" s="58" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="E15" s="58" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F15" s="18" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H15" s="58" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="187" x14ac:dyDescent="0.45">
@@ -29577,19 +29764,19 @@
         <v>9</v>
       </c>
       <c r="B16" s="58" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C16" s="58" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="E16" s="58" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F16" s="18" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="51" x14ac:dyDescent="0.45">
@@ -29597,19 +29784,19 @@
         <v>10</v>
       </c>
       <c r="B17" s="58" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C17" s="58" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="E17" s="58" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F17" s="18" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="68" x14ac:dyDescent="0.45">
@@ -29617,19 +29804,19 @@
         <v>11</v>
       </c>
       <c r="B18" s="58" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="E18" s="58" t="s">
+        <v>378</v>
+      </c>
+      <c r="F18" s="18" t="s">
         <v>379</v>
-      </c>
-      <c r="F18" s="18" t="s">
-        <v>380</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="68" x14ac:dyDescent="0.45">
@@ -29637,19 +29824,19 @@
         <v>12</v>
       </c>
       <c r="B19" s="58" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C19" s="58" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D19" s="58" t="s">
+        <v>380</v>
+      </c>
+      <c r="E19" s="58" t="s">
         <v>381</v>
       </c>
-      <c r="E19" s="58" t="s">
-        <v>382</v>
-      </c>
       <c r="F19" s="18" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="68" x14ac:dyDescent="0.45">
@@ -29657,19 +29844,19 @@
         <v>13</v>
       </c>
       <c r="B20" s="58" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C20" s="58" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D20" s="58" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E20" s="58" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F20" s="18" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="85" x14ac:dyDescent="0.45">
@@ -29677,44 +29864,44 @@
         <v>14</v>
       </c>
       <c r="B21" s="58" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C21" s="58" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E21" s="58" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F21" s="64" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="170" x14ac:dyDescent="0.45">
       <c r="A22" s="61" t="s">
+        <v>389</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>393</v>
+      </c>
+      <c r="C22" s="58" t="s">
         <v>390</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="D22" s="18" t="s">
+        <v>391</v>
+      </c>
+      <c r="E22" s="18" t="s">
+        <v>392</v>
+      </c>
+      <c r="F22" s="18" t="s">
         <v>394</v>
-      </c>
-      <c r="C22" s="58" t="s">
-        <v>391</v>
-      </c>
-      <c r="D22" s="18" t="s">
-        <v>392</v>
-      </c>
-      <c r="E22" s="18" t="s">
-        <v>393</v>
-      </c>
-      <c r="F22" s="18" t="s">
-        <v>395</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A23" s="66" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
   </sheetData>
@@ -29741,35 +29928,35 @@
     <col min="2" max="2" width="49.5" style="45" customWidth="1"/>
     <col min="3" max="3" width="13.4140625" style="45" customWidth="1"/>
     <col min="4" max="6" width="77" style="45" customWidth="1"/>
-    <col min="7" max="7" width="55" style="99" customWidth="1"/>
+    <col min="7" max="7" width="55" style="69" customWidth="1"/>
     <col min="8" max="8" width="39.9140625" style="45" customWidth="1"/>
     <col min="9" max="16384" width="8.6640625" style="45"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="16" x14ac:dyDescent="0.45">
       <c r="A1" s="62" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B1" s="40" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="C1" s="40" t="s">
         <v>195</v>
       </c>
-      <c r="D1" s="109" t="s">
+      <c r="D1" s="75" t="s">
         <v>199</v>
       </c>
-      <c r="E1" s="109" t="s">
+      <c r="E1" s="75" t="s">
+        <v>398</v>
+      </c>
+      <c r="F1" s="75" t="s">
         <v>399</v>
       </c>
-      <c r="F1" s="109" t="s">
-        <v>400</v>
-      </c>
       <c r="G1" s="40" t="s">
+        <v>423</v>
+      </c>
+      <c r="H1" s="40" t="s">
         <v>424</v>
-      </c>
-      <c r="H1" s="40" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="256" x14ac:dyDescent="0.45">
@@ -29777,25 +29964,25 @@
         <v>2</v>
       </c>
       <c r="B2" s="50" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C2" s="50" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D2" s="48" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E2" s="48" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="F2" s="48" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="G2" s="43" t="s">
+        <v>425</v>
+      </c>
+      <c r="H2" s="43" t="s">
         <v>426</v>
-      </c>
-      <c r="H2" s="43" t="s">
-        <v>427</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="208" x14ac:dyDescent="0.45">
@@ -29803,25 +29990,25 @@
         <v>4</v>
       </c>
       <c r="B3" s="50" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C3" s="50" t="s">
+        <v>372</v>
+      </c>
+      <c r="D3" s="48" t="s">
         <v>373</v>
       </c>
-      <c r="D3" s="48" t="s">
-        <v>374</v>
-      </c>
       <c r="E3" s="48" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F3" s="48" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="G3" s="43" t="s">
+        <v>427</v>
+      </c>
+      <c r="H3" s="43" t="s">
         <v>428</v>
-      </c>
-      <c r="H3" s="43" t="s">
-        <v>429</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="272" x14ac:dyDescent="0.45">
@@ -29829,25 +30016,25 @@
         <v>5</v>
       </c>
       <c r="B4" s="50" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C4" s="50" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D4" s="48" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="E4" s="48" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F4" s="48" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G4" s="43" t="s">
+        <v>429</v>
+      </c>
+      <c r="H4" s="43" t="s">
         <v>430</v>
-      </c>
-      <c r="H4" s="43" t="s">
-        <v>431</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="192" x14ac:dyDescent="0.45">
@@ -29855,25 +30042,25 @@
         <v>6</v>
       </c>
       <c r="B5" s="50" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C5" s="50" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D5" s="48" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="E5" s="48" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="F5" s="48" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="G5" s="43" t="s">
+        <v>431</v>
+      </c>
+      <c r="H5" s="43" t="s">
         <v>432</v>
-      </c>
-      <c r="H5" s="43" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="192" x14ac:dyDescent="0.45">
@@ -29881,25 +30068,25 @@
         <v>8</v>
       </c>
       <c r="B6" s="50" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C6" s="50" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E6" s="48" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F6" s="48" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="G6" s="43" t="s">
+        <v>433</v>
+      </c>
+      <c r="H6" s="43" t="s">
         <v>434</v>
-      </c>
-      <c r="H6" s="43" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="224" x14ac:dyDescent="0.45">
@@ -29907,25 +30094,25 @@
         <v>9</v>
       </c>
       <c r="B7" s="50" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C7" s="50" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D7" s="48" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E7" s="48" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="F7" s="48" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="G7" s="43" t="s">
+        <v>435</v>
+      </c>
+      <c r="H7" s="43" t="s">
         <v>436</v>
-      </c>
-      <c r="H7" s="43" t="s">
-        <v>437</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="192" x14ac:dyDescent="0.45">
@@ -29933,51 +30120,51 @@
         <v>10</v>
       </c>
       <c r="B8" s="50" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C8" s="50" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D8" s="48" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E8" s="48" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="F8" s="48" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G8" s="43" t="s">
+        <v>437</v>
+      </c>
+      <c r="H8" s="43" t="s">
         <v>438</v>
       </c>
-      <c r="H8" s="43" t="s">
-        <v>439</v>
-      </c>
     </row>
-    <row r="9" spans="1:8" ht="320" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:8" ht="332.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="68">
         <v>11</v>
       </c>
       <c r="B9" s="50" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C9" s="50" t="s">
+        <v>378</v>
+      </c>
+      <c r="D9" s="48" t="s">
         <v>379</v>
       </c>
-      <c r="D9" s="48" t="s">
-        <v>380</v>
-      </c>
       <c r="E9" s="48" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F9" s="48" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="G9" s="43" t="s">
+        <v>439</v>
+      </c>
+      <c r="H9" s="43" t="s">
         <v>440</v>
-      </c>
-      <c r="H9" s="43" t="s">
-        <v>441</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="272" x14ac:dyDescent="0.45">
@@ -29985,25 +30172,25 @@
         <v>12</v>
       </c>
       <c r="B10" s="50" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C10" s="50" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D10" s="48" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="E10" s="48" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F10" s="48" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G10" s="43" t="s">
+        <v>441</v>
+      </c>
+      <c r="H10" s="43" t="s">
         <v>442</v>
-      </c>
-      <c r="H10" s="43" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="224" x14ac:dyDescent="0.45">
@@ -30011,73 +30198,73 @@
         <v>13</v>
       </c>
       <c r="B11" s="50" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="C11" s="50" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D11" s="48" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="E11" s="48" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="F11" s="48" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G11" s="43" t="s">
+        <v>443</v>
+      </c>
+      <c r="H11" s="43" t="s">
         <v>444</v>
       </c>
-      <c r="H11" s="43" t="s">
-        <v>445</v>
-      </c>
     </row>
-    <row r="12" spans="1:8" ht="288" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:8" ht="306.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="68">
         <v>14</v>
       </c>
       <c r="B12" s="50" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C12" s="50" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D12" s="37" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E12" s="48" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F12" s="48" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="G12" s="43" t="s">
+        <v>445</v>
+      </c>
+      <c r="H12" s="43" t="s">
         <v>446</v>
-      </c>
-      <c r="H12" s="43" t="s">
-        <v>447</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="144" x14ac:dyDescent="0.45">
       <c r="A13" s="68" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B13" s="48" t="s">
+        <v>393</v>
+      </c>
+      <c r="C13" s="48" t="s">
+        <v>392</v>
+      </c>
+      <c r="D13" s="48" t="s">
         <v>394</v>
-      </c>
-      <c r="C13" s="48" t="s">
-        <v>393</v>
-      </c>
-      <c r="D13" s="48" t="s">
-        <v>395</v>
       </c>
       <c r="E13" s="50"/>
       <c r="F13" s="50"/>
       <c r="G13" s="43" t="s">
+        <v>447</v>
+      </c>
+      <c r="H13" s="43" t="s">
         <v>448</v>
-      </c>
-      <c r="H13" s="43" t="s">
-        <v>449</v>
       </c>
     </row>
   </sheetData>
@@ -30100,7 +30287,7 @@
   <sheetData>
     <row r="1" spans="1:1" ht="68" x14ac:dyDescent="0.45">
       <c r="A1" s="67" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
   </sheetData>

--- a/project_2/project2_project status(C2).xlsx
+++ b/project_2/project2_project status(C2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pyostry\workspace\aiffel\ai-data-bootcamp\Project_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11C35659-AA71-421D-8A7F-29D85468FF46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FED89BBD-32A2-46A1-A3F4-7C4174C451CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" firstSheet="4" activeTab="9" xr2:uid="{5FF54064-7DDC-427B-93D7-EF78D75E5195}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="456">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="493">
   <si>
     <t>reward</t>
   </si>
@@ -1958,10 +1958,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>제안</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>통계적 근거</t>
   </si>
   <si>
@@ -2067,6 +2063,169 @@
   <si>
     <t>발표자료 준비:
 발표:</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>offer 설계 시 reward의 차이로는 완료율의 차이를 설명할 수 없었음
+오히려 offer type이나 difficulty, channel의 설계를 바꿔서 완료율의 차이를 없애는 것이 중요해 보임</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>offer channel의 경우 Web, Email만 발송되는 경우 다른 조합에 비해서 수신율이 현저히 낮은 것으로 확인됨 통계적으론 유의미한 결과는 아니었으나 현 데이터 상 Channel이 완전교차설계되어 있지 않고 일부 표본 간 극단적 불균형을 보여 참고 자료로만 활용 가능하고 추후 offer 발송 시 분석에 대비해 완전교차설계하여 발송하는 것을 제안드림.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주기적인 offer를 받아도 실질적으로 완료율에 대한 차이는 없었음.
+예산 비용에 맞추어 offer를 주기적으로 진행해도 무관함.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고객 소득수준에 따라 difficulty별 완료율에 차이는 없었음.
+소득이 높을수록 완료율이 높긴했지만 통계적 유의미는 없어 예산에 맞게 reward, difficulty를 설정하여 진행해도 무관할 것으로 보임.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">오히려 고소득층에서 reward가 낮다고해서 완료율이 낮진 않았고 저소득층에서 차이가 보였음.
+7번과 마찬가지로 예산에 맞게 reward, difficulty를 설정하여 진행해도 무관할 것으로 보임.
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>완료율만 보면 discount(17,910 / 58.72%)가 bogo(15,669 / 43.79%)으로 discount가 높지만 재고소진 목적으로 offer를 진행하는 경우 bogo가 더 효율적인 것으로 확인되어 목적에 따라 offer 설계가 필요해 보임.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>전체 고객에서 알림 해제 비율을 수집하여 offer 설계 시 적절한 Channel을 선택할 수 있도록 보완이 필요함.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>나만의 메뉴 또는 해당 고객이 주문한 메뉴 정보를 수집하여 offer 기간 중 해당 고객이 offer를 외면하였는지 개인 선호에 따라 offer를 외면하였는지 추가 분석하여 offer 설계의 보완이 필요함.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>남성의 bogo type의 완료율이 현저하게 낮은 것으로 확인됨.
+목적에 따라 offer 설계가 필요해 보임.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고령층일수록 모바일 기기의 미숙으로 수신율이 낮을 것으로 추측하였으나 오히려 청년층(18~30세)에서 수신율이 낮았고 선호 채널도 통계적 유의성을 확인하지 못함.
+2번과 마찬가지로 데이터 한계를 보완하여 후속 분석이 필요함.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>difficulty가 높을수록 완료율이 낮아지는 것은 통계적으로 유의미하게 확인되었으나, 현재 difficulty, reward의 조합이 완전 교차 설계되어 있지 않아 difficulty 또는 reward의 조정으로 완료율의 변화를 이끌어낼지 예측할 수 없음.
+추후 재 분석에 대비해 offer별 difficulty, reward간 완전교차설계가 필요해 보임.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>duration별 수신율의 차이는 없었고 대부분 보통 offer 발송 하루안에 수신한 것으로 확인됨.
+다만 완료율의 경우 duration 기간별 차이는 없어 duration 10의 수신율이 낮다고해서 설계에서 제외하는 것은 부적절함.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보상 금액을 일괄적으로 높이지 않는다. 동일한 Offer 유형·난이도·기간에서 보상만 다르게 설정한 A/B 테스트를 진행한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>신규 프로모션에는 Mobile·Social 포함 조합을 우선 시험한다. 동일한 Offer를 채널 조합만 다르게 발송해 채널 자체의 영향을 확인한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유효기간을 일괄 연장하지 않는다. 발송 후 첫 24시간 안에 고객이 혜택을 이해하고 첫 긍정 경험에 도달할 수 있도록 알림 시점과 메시지 구성을 개선한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>현재 결과만으로 발송 횟수 제한을 도입하지 않는다. 향후 누적 수신 횟수와 발송 간격을 함께 분석해 피로도가 발생하는 구간을 다시 확인한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>할인형을 우선 후보로 검토하되 BOGO를 즉시 축소하지 않는다. 동일한 조건에서 두 유형을 비교하고, 단순 완료율뿐 아니라 완료 이후 실제 구매와 반복 이용으로 이어지는지도 함께 추적한다. 이를 위해 결제 기록과 Offer ID를 연결한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>낮은 difficulty 조건을 우선 시험한다. 완료율뿐 아니라 추가 매출과 보상비용을 함께 비교해 적정 목표 금액을 결정한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>저소득 고객에게만 difficulty를 낮추는 정책은 보류한다. 전체 자료와 difficulty 20 제외 결과를 함께 제시하고 추가 데이터에서 재검증한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>소득에 따른 보상 차등 정책은 보류한다. 동일한 Offer 유형에서 보상만 다르게 설정한 실험으로 소득집단별 반응을 다시 확인한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>특히 청년층 대상 캠페인에서 Mobile·Social 추가를 우선 시험한다. 연령대를 구분한 채널 실험으로 결과를 재확인한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고령층이라는 이유만으로 별도 전략을 적용하지 않는다. 반응이 낮게 나타난 청년층의 채널 조합과 Offer 구성을 먼저 점검한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>남성 고객 대상 BOGO의 혜택 구조와 메시지를 재검토한다. 남성 고객에게 BOGO와 할인형을 무작위 배정해 유형별 완료 반응을 비교한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>통합모형의 분석 대상과 결과변수를 통일해 다시 실행한다. 재검증 전까지 인구통계 기반 개인화 정책은 보류한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>고객 설문에 카페인 민감도와 선호 메뉴 항목을 추가하고 메뉴별 구매 데이터와 연결한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>결제 기록에 offer_id 또는 쿠폰 사용 식별자를 추가해 프로모션과 실제 구매를 연결한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>앱 알림 허용 여부와 푸시 발송·도달·클릭 로그를 수집한 후 다시 분석한다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>보상 금액만으로 정책을 바꾸지 마세요. 다음 캠페인에서 보상 금액 × 오퍼 종류를 직교(orthogonal)로 배치한 A/B 테스트를 먼저 설계해서 순수 효과를 분리하는 게 우선입니다. 지금 데이터로 "보상을 낮추자"는 결론은 성급합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이것도 마찬가지로 채널 단독 배정 테스트가 필요합니다. 다만 실무적으로는 Social·Mobile 채널 예산을 유지/확대하는 방향이 리스크가 적으니, 정밀 인과 분석 전이라도 채널 믹스는 현행 유지하며 테스트 결과를 기다리세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유효기간 연장은 실행하지 마세요. 문제는 기간이 아니라 "열람 자체를 유도하는 트리거(알림 타이밍, 채널)"에 있을 가능성이 높습니다. 기간 확대는 비용만 늘리고 효과가 없을 가능성이 큽니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>발송 빈도 제한(frequency cap)을 굳이 강화할 필요는 없습니다. 통계적 유의성에 흔들리지 말고, 빈도 정책은 현행 유지하거나 다른 목적(비용 절감 등)에 따라 결정하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이건 가장 강한 신호입니다. 오퍼 믹스에서 할인형 비중을 실험적으로 늘려보는 파일럿을 우선순위 1순위로 추천합니다. 단, 나머지 절반의 차이는 미관측 요인(소비자의 사용 맥락, 상품군 등)일 수 있으니 "할인형이 항상 우월하다"가 아니라 "현재 조건에서 우월하다"로 해석하세요.
+목표 금액/소득 관련</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>목표 금액을 일괄적으로 낮추기보다, 구간별로 완료율이 급격히 꺾이는 지점(threshold)을 먼저 찾는 세분 분석이 필요합니다. 비선형이라는 건 특정 구간에만 문제가 있을 가능성을 시사합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"저소득층에 목표금액을 낮춰주자는 개입은 근거가 약합니다. 대신 완료율 자체와 관련된 다른 요인(가용 시간, 상품 접근성 등)을 봐야 합니다. 소득 기반 목표금액 차등화는 보류하세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이건 실행 가능성이 높은 인사이트입니다. 저소득 세그먼트에는 보상 금액 차등을, 고소득 세그먼트에는 보상보다 편의성/혜택 종류 중심으로 오퍼를 재설계하는 세그먼트별 전략을 권장합니다.
+채널/인구통계 관련</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"고령층 대상 채널 개선"이라는 기존 가정을 폐기하고, 청년층 대상 Web·Email 발송을 Mobile/Social로 전환하는 리밸런싱을 최우선 실행 항목으로 삼으세요. 이 결과는 통념을 뒤집으므로 한 번 더 다른 기간 데이터로 재확인(replication)하는 것도 권장합니다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>남성 세그먼트에는 1+1형 대신 할인형 위주로 오퍼를 배정하는 타겟팅 룰을 적용해볼 만합니다. 여성 세그먼트는 오퍼 종류보다 다른 변수(보상, 목표금액)로 최적화 여지를 찾으세요.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>세그먼트 전략을 짤 때 성별을 1차 분기 기준으로, 그 다음 연령/소득을 2차 분기로 사용하는 계층적 타겟팅 구조를 설계하는 게 효율적입니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2649,7 +2808,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2876,6 +3035,18 @@
     <xf numFmtId="0" fontId="10" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2978,17 +3149,17 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -11765,8 +11936,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="220981" y="1805623"/>
-          <a:ext cx="2100172" cy="447540"/>
+          <a:off x="173001" y="1826087"/>
+          <a:ext cx="2123975" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -11865,8 +12036,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="234089" y="1818731"/>
-        <a:ext cx="2073956" cy="421324"/>
+        <a:off x="186258" y="1839344"/>
+        <a:ext cx="2097461" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{ED5992BD-91A0-44DC-B026-C230E027754F}">
@@ -11876,8 +12047,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="16874489">
-          <a:off x="1581876" y="1121529"/>
-          <a:ext cx="1836586" cy="14378"/>
+          <a:off x="1549321" y="1134321"/>
+          <a:ext cx="1857401" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -11891,7 +12062,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1836586" y="7189"/>
+                <a:pt x="1857401" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -11950,8 +12121,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2454255" y="1082803"/>
-        <a:ext cx="91829" cy="91829"/>
+        <a:off x="2431586" y="1095075"/>
+        <a:ext cx="92870" cy="92870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{EB7188F2-1357-4748-A44C-AB5D4A48F40F}">
@@ -11961,8 +12132,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2679186" y="4273"/>
-          <a:ext cx="1080487" cy="447540"/>
+          <a:off x="2659066" y="4321"/>
+          <a:ext cx="1092733" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -12037,8 +12208,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2692294" y="17381"/>
-        <a:ext cx="1054271" cy="421324"/>
+        <a:off x="2672323" y="17578"/>
+        <a:ext cx="1066219" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7531319A-E0E5-4CB4-9F35-33254694A0D7}">
@@ -12048,8 +12219,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3759673" y="220854"/>
-          <a:ext cx="352482" cy="14378"/>
+          <a:off x="3751800" y="223438"/>
+          <a:ext cx="356477" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -12063,7 +12234,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="352482" y="7189"/>
+                <a:pt x="356477" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -12122,8 +12293,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3927103" y="219231"/>
-        <a:ext cx="17624" cy="17624"/>
+        <a:off x="3921127" y="221715"/>
+        <a:ext cx="17823" cy="17823"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{8F385C2E-83EB-470A-8A65-12C51C60EB27}">
@@ -12133,8 +12304,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4112156" y="4273"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="4108278" y="4321"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -12233,8 +12404,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4125264" y="17381"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="4121535" y="17578"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{71327523-F24D-4A9E-8CA7-7C0E6A96618A}">
@@ -12244,8 +12415,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17132988">
-          <a:off x="1832388" y="1378865"/>
-          <a:ext cx="1335563" cy="14378"/>
+          <a:off x="1802671" y="1394574"/>
+          <a:ext cx="1350699" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -12259,7 +12430,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1335563" y="7189"/>
+                <a:pt x="1350699" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -12318,8 +12489,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2466780" y="1352664"/>
-        <a:ext cx="66778" cy="66778"/>
+        <a:off x="2444254" y="1367995"/>
+        <a:ext cx="67534" cy="67534"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{08B2E005-DF35-41E7-A396-CA02C3B8D0A4}">
@@ -12329,8 +12500,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2679186" y="518944"/>
-          <a:ext cx="1080487" cy="447540"/>
+          <a:off x="2659066" y="524826"/>
+          <a:ext cx="1092733" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -12405,8 +12576,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2692294" y="532052"/>
-        <a:ext cx="1054271" cy="421324"/>
+        <a:off x="2672323" y="538083"/>
+        <a:ext cx="1066219" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E113C6B3-F5C2-41D9-9727-BB430EAD3818}">
@@ -12416,8 +12587,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3759673" y="735525"/>
-          <a:ext cx="358032" cy="14378"/>
+          <a:off x="3751800" y="743943"/>
+          <a:ext cx="362090" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -12431,7 +12602,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="358032" y="7189"/>
+                <a:pt x="362090" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -12490,8 +12661,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3929739" y="733763"/>
-        <a:ext cx="17901" cy="17901"/>
+        <a:off x="3923793" y="742080"/>
+        <a:ext cx="18104" cy="18104"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{53F03F28-ED40-4762-8125-AFFEEA792A72}">
@@ -12501,8 +12672,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4117706" y="518944"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="4113890" y="524826"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -12625,8 +12796,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4130814" y="532052"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="4127147" y="538083"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{806C8330-1E37-41AD-AEEE-3552A4162510}">
@@ -12636,8 +12807,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17692822">
-          <a:off x="2074675" y="1636200"/>
-          <a:ext cx="850988" cy="14378"/>
+          <a:off x="2047704" y="1654826"/>
+          <a:ext cx="860633" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -12651,7 +12822,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="850988" y="7189"/>
+                <a:pt x="860633" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -12710,8 +12881,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2478895" y="1622115"/>
-        <a:ext cx="42549" cy="42549"/>
+        <a:off x="2456505" y="1640499"/>
+        <a:ext cx="43031" cy="43031"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{3BC1DAB2-4FEF-42C9-A10F-0690E2903498}">
@@ -12721,8 +12892,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2679186" y="1033615"/>
-          <a:ext cx="1080487" cy="447540"/>
+          <a:off x="2659066" y="1045330"/>
+          <a:ext cx="1092733" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -12813,8 +12984,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2692294" y="1046723"/>
-        <a:ext cx="1054271" cy="421324"/>
+        <a:off x="2672323" y="1058587"/>
+        <a:ext cx="1066219" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6BFD1C16-8154-4C15-AF72-E53B38C4A146}">
@@ -12824,8 +12995,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3759673" y="1250197"/>
-          <a:ext cx="358032" cy="14378"/>
+          <a:off x="3751800" y="1264447"/>
+          <a:ext cx="362090" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -12839,7 +13010,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="358032" y="7189"/>
+                <a:pt x="362090" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -12898,8 +13069,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3929739" y="1248435"/>
-        <a:ext cx="17901" cy="17901"/>
+        <a:off x="3923793" y="1262584"/>
+        <a:ext cx="18104" cy="18104"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1A251137-9CB6-43D7-B47D-0D220C30894C}">
@@ -12909,8 +13080,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4117706" y="1033615"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="4113890" y="1045330"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -13033,8 +13204,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4130814" y="1046723"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="4127147" y="1058587"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{227E0FEF-1368-4562-AD55-940C6A450E91}">
@@ -13044,8 +13215,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="3310531">
-          <a:off x="2186691" y="2279540"/>
-          <a:ext cx="626956" cy="14378"/>
+          <a:off x="2160990" y="2305456"/>
+          <a:ext cx="634061" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -13059,7 +13230,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="626956" y="7189"/>
+                <a:pt x="634061" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -13118,8 +13289,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2484496" y="2271055"/>
-        <a:ext cx="31347" cy="31347"/>
+        <a:off x="2462170" y="2296794"/>
+        <a:ext cx="31703" cy="31703"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{146FB508-948A-484E-B54F-2A63CE5492FA}">
@@ -13129,8 +13300,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2679186" y="2320294"/>
-          <a:ext cx="1080487" cy="447540"/>
+          <a:off x="2659066" y="2346591"/>
+          <a:ext cx="1092733" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -13205,8 +13376,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2692294" y="2333402"/>
-        <a:ext cx="1054271" cy="421324"/>
+        <a:off x="2672323" y="2359848"/>
+        <a:ext cx="1066219" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1583A4D8-C48C-400A-B5A1-D8E8188A1E57}">
@@ -13216,8 +13387,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17692822">
-          <a:off x="3513195" y="2150872"/>
-          <a:ext cx="850988" cy="14378"/>
+          <a:off x="3502528" y="2175330"/>
+          <a:ext cx="860633" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -13231,7 +13402,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="850988" y="7189"/>
+                <a:pt x="860633" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -13290,8 +13461,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3917415" y="2136786"/>
-        <a:ext cx="42549" cy="42549"/>
+        <a:off x="3911329" y="2161003"/>
+        <a:ext cx="43031" cy="43031"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{985FE1E2-4CA8-4AC7-A474-DEECC9A2BB80}">
@@ -13301,8 +13472,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4117706" y="1548287"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="4113890" y="1565835"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -13393,8 +13564,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4130814" y="1561395"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="4127147" y="1579092"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{16F44D37-2601-482A-9095-0B3E8E10E520}">
@@ -13404,8 +13575,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19457599">
-          <a:off x="3718230" y="2408207"/>
-          <a:ext cx="440918" cy="14378"/>
+          <a:off x="3709887" y="2435583"/>
+          <a:ext cx="445915" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -13419,7 +13590,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="440918" y="7189"/>
+                <a:pt x="445915" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -13478,8 +13649,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3927667" y="2404373"/>
-        <a:ext cx="22045" cy="22045"/>
+        <a:off x="3921697" y="2431624"/>
+        <a:ext cx="22295" cy="22295"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{2D542640-C237-42B5-8470-73084719F8F3}">
@@ -13489,8 +13660,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4117706" y="2062958"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="4113890" y="2086339"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -13581,8 +13752,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4130814" y="2076066"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="4127147" y="2099596"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9A75AB13-86A0-459A-8B2B-E8037D74B447}">
@@ -13592,8 +13763,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2142401">
-          <a:off x="3718230" y="2665543"/>
-          <a:ext cx="440918" cy="14378"/>
+          <a:off x="3709887" y="2695835"/>
+          <a:ext cx="445915" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -13607,7 +13778,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="440918" y="7189"/>
+                <a:pt x="445915" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -13666,8 +13837,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3927667" y="2661709"/>
-        <a:ext cx="22045" cy="22045"/>
+        <a:off x="3921697" y="2691876"/>
+        <a:ext cx="22295" cy="22295"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{106C3051-36E0-4DB2-B006-BD51244834C6}">
@@ -13677,8 +13848,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4117706" y="2577630"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="4113890" y="2606844"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -13769,8 +13940,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4130814" y="2590738"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="4127147" y="2620101"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6562E267-52DD-4DC6-81E6-A0E9307367D6}">
@@ -13780,8 +13951,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="3907178">
-          <a:off x="3513195" y="2922879"/>
-          <a:ext cx="850988" cy="14378"/>
+          <a:off x="3502528" y="2956087"/>
+          <a:ext cx="860633" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -13795,7 +13966,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="850988" y="7189"/>
+                <a:pt x="860633" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -13854,8 +14025,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3917415" y="2908793"/>
-        <a:ext cx="42549" cy="42549"/>
+        <a:off x="3911329" y="2941760"/>
+        <a:ext cx="43031" cy="43031"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{220D319D-36C0-42A0-A946-F197C4269C14}">
@@ -13865,8 +14036,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4117706" y="3092301"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="4113890" y="3127348"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -13957,8 +14128,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4130814" y="3105409"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="4127147" y="3140605"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4332858F-88A7-466E-8722-8833A7B96598}">
@@ -13968,8 +14139,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="4725511">
-          <a:off x="1581876" y="2922879"/>
-          <a:ext cx="1836586" cy="14378"/>
+          <a:off x="1549321" y="2956087"/>
+          <a:ext cx="1857401" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -13983,7 +14154,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1836586" y="7189"/>
+                <a:pt x="1857401" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -14038,8 +14209,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2454255" y="2884153"/>
-        <a:ext cx="91829" cy="91829"/>
+        <a:off x="2431586" y="2916841"/>
+        <a:ext cx="92870" cy="92870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1479FCFA-85A4-438D-B5D0-346DFAD5924D}">
@@ -14049,8 +14220,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2679186" y="3606973"/>
-          <a:ext cx="1080487" cy="447540"/>
+          <a:off x="2659066" y="3647853"/>
+          <a:ext cx="1092733" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -14125,8 +14296,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2692294" y="3620081"/>
-        <a:ext cx="1054271" cy="421324"/>
+        <a:off x="2672323" y="3661110"/>
+        <a:ext cx="1066219" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E6D0412B-4D85-432B-BE35-F277BFD00B03}">
@@ -14136,8 +14307,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3759673" y="3823554"/>
-          <a:ext cx="358032" cy="14378"/>
+          <a:off x="3751800" y="3866970"/>
+          <a:ext cx="362090" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -14151,7 +14322,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="358032" y="7189"/>
+                <a:pt x="362090" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -14206,8 +14377,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3929739" y="3821792"/>
-        <a:ext cx="17901" cy="17901"/>
+        <a:off x="3923793" y="3865107"/>
+        <a:ext cx="18104" cy="18104"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{CE9AFD94-4037-4F8B-B49B-020818B5CBB5}">
@@ -14217,8 +14388,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4117706" y="3606973"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="4113890" y="3647853"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -14325,8 +14496,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4130814" y="3620081"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="4127147" y="3661110"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B460AB31-448C-42B6-9C6B-D3CF5013B4F6}">
@@ -14336,8 +14507,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="88714" y="4636316"/>
-          <a:ext cx="1800813" cy="447540"/>
+          <a:off x="39236" y="4688862"/>
+          <a:ext cx="1821222" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -14462,8 +14633,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="101822" y="4649424"/>
-        <a:ext cx="1774597" cy="421324"/>
+        <a:off x="52493" y="4702119"/>
+        <a:ext cx="1794708" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{C120D3E5-D1A3-4DC1-848B-C37D9DDE2012}">
@@ -14473,8 +14644,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="18752467">
-          <a:off x="1776407" y="4595561"/>
-          <a:ext cx="698529" cy="14378"/>
+          <a:off x="1746056" y="4647727"/>
+          <a:ext cx="706446" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -14488,7 +14659,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="698529" y="7189"/>
+                <a:pt x="706446" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -14543,8 +14714,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2108209" y="4585287"/>
-        <a:ext cx="34926" cy="34926"/>
+        <a:off x="2081618" y="4637255"/>
+        <a:ext cx="35322" cy="35322"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6F01F0AA-74B9-49DB-A456-B8979039EB51}">
@@ -14554,8 +14725,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2361817" y="4121644"/>
-          <a:ext cx="1080487" cy="447540"/>
+          <a:off x="2338101" y="4168357"/>
+          <a:ext cx="1092733" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -14628,8 +14799,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2374925" y="4134752"/>
-        <a:ext cx="1054271" cy="421324"/>
+        <a:off x="2351358" y="4181614"/>
+        <a:ext cx="1066219" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{F5E69F9A-2631-4A2D-BC76-B4BD9B08D019}">
@@ -14639,8 +14810,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3442305" y="4338225"/>
-          <a:ext cx="364020" cy="14378"/>
+          <a:off x="3430834" y="4387475"/>
+          <a:ext cx="368146" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -14654,7 +14825,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="364020" y="7189"/>
+                <a:pt x="368146" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -14709,8 +14880,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3615214" y="4336314"/>
-        <a:ext cx="18201" cy="18201"/>
+        <a:off x="3605704" y="4385460"/>
+        <a:ext cx="18407" cy="18407"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{69EDA0B0-D39D-4C93-8B8D-10889C581D9E}">
@@ -14720,8 +14891,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3806325" y="4121644"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="3798980" y="4168357"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -14794,8 +14965,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3819433" y="4134752"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="3812237" y="4181614"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{AC23C890-5E27-4DC3-9BF7-2C50218200D9}">
@@ -14805,8 +14976,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="1889527" y="4852897"/>
-          <a:ext cx="472289" cy="14378"/>
+          <a:off x="1860458" y="4907979"/>
+          <a:ext cx="477642" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -14820,7 +14991,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="472289" y="7189"/>
+                <a:pt x="477642" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -14875,8 +15046,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2113865" y="4848279"/>
-        <a:ext cx="23614" cy="23614"/>
+        <a:off x="2087338" y="4903227"/>
+        <a:ext cx="23882" cy="23882"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B4CF3050-E538-4710-99C5-FB5B2F28D116}">
@@ -14886,8 +15057,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2361817" y="4636316"/>
-          <a:ext cx="1080487" cy="447540"/>
+          <a:off x="2338101" y="4688862"/>
+          <a:ext cx="1092733" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -14960,8 +15131,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2374925" y="4649424"/>
-        <a:ext cx="1054271" cy="421324"/>
+        <a:off x="2351358" y="4702119"/>
+        <a:ext cx="1066219" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{55492AE0-989E-4368-96E6-8609B6786079}">
@@ -14971,8 +15142,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3442305" y="4852897"/>
-          <a:ext cx="364020" cy="14378"/>
+          <a:off x="3430834" y="4907979"/>
+          <a:ext cx="368146" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -14986,7 +15157,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="364020" y="7189"/>
+                <a:pt x="368146" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -15041,8 +15212,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3615214" y="4850985"/>
-        <a:ext cx="18201" cy="18201"/>
+        <a:off x="3605704" y="4905964"/>
+        <a:ext cx="18407" cy="18407"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{99BD4B49-7654-4BFC-93A2-73715A94DAC0}">
@@ -15052,8 +15223,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3806325" y="4636316"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="3798980" y="4688862"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -15170,8 +15341,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3819433" y="4649424"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="3812237" y="4702119"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{48D36C81-0EEF-4879-868D-73109D1A61EF}">
@@ -15181,8 +15352,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2847533">
-          <a:off x="1776407" y="5110232"/>
-          <a:ext cx="698529" cy="14378"/>
+          <a:off x="1746056" y="5168231"/>
+          <a:ext cx="706446" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -15196,7 +15367,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="698529" y="7189"/>
+                <a:pt x="706446" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -15251,8 +15422,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2108209" y="5099958"/>
-        <a:ext cx="34926" cy="34926"/>
+        <a:off x="2081618" y="5157759"/>
+        <a:ext cx="35322" cy="35322"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E0C7A212-1F93-473A-8909-15A6780CBC2F}">
@@ -15262,8 +15433,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2361817" y="5150987"/>
-          <a:ext cx="1080487" cy="447540"/>
+          <a:off x="2338101" y="5209366"/>
+          <a:ext cx="1092733" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -15336,8 +15507,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2374925" y="5164095"/>
-        <a:ext cx="1054271" cy="421324"/>
+        <a:off x="2351358" y="5222623"/>
+        <a:ext cx="1066219" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4D54B04B-F98B-4577-8925-91ECEF877996}">
@@ -15347,8 +15518,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3442305" y="5367568"/>
-          <a:ext cx="376041" cy="14378"/>
+          <a:off x="3430834" y="5428484"/>
+          <a:ext cx="380303" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -15362,7 +15533,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="376041" y="7189"/>
+                <a:pt x="380303" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -15417,8 +15588,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3620924" y="5365356"/>
-        <a:ext cx="18802" cy="18802"/>
+        <a:off x="3611478" y="5426165"/>
+        <a:ext cx="19015" cy="19015"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{540CB623-D523-4AD6-BF5D-A946D7B052E6}">
@@ -15428,8 +15599,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3818346" y="5150987"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="3811137" y="5209366"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -15547,8 +15718,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3831454" y="5164095"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="3824394" y="5222623"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
   </dsp:spTree>
@@ -15570,8 +15741,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9182" y="3307680"/>
-          <a:ext cx="1177681" cy="361541"/>
+          <a:off x="10440" y="3343938"/>
+          <a:ext cx="1173405" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -15649,8 +15820,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="19771" y="3318269"/>
-        <a:ext cx="1156503" cy="340363"/>
+        <a:off x="20991" y="3354489"/>
+        <a:ext cx="1152303" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7667B88B-738E-4E27-80A6-15B1E3AED5F8}">
@@ -15660,8 +15831,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="16719080">
-          <a:off x="572912" y="2769909"/>
-          <a:ext cx="1445308" cy="8220"/>
+          <a:off x="572123" y="2808170"/>
+          <a:ext cx="1440061" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -15672,10 +15843,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1445308" y="4110"/>
+                <a:pt x="1440061" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -15734,8 +15905,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1259433" y="2737887"/>
-        <a:ext cx="72265" cy="72265"/>
+        <a:off x="1256152" y="2776213"/>
+        <a:ext cx="72003" cy="72003"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D9E30B0F-B6EE-4B8A-B3A5-5AD7E4CFBC12}">
@@ -15745,8 +15916,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="1404269" y="1878817"/>
-          <a:ext cx="1444638" cy="361541"/>
+          <a:off x="1400462" y="1920262"/>
+          <a:ext cx="1439393" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -15837,8 +16008,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1414858" y="1889406"/>
-        <a:ext cx="1423460" cy="340363"/>
+        <a:off x="1411013" y="1930813"/>
+        <a:ext cx="1418291" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{ED5992BD-91A0-44DC-B026-C230E027754F}">
@@ -15848,8 +16019,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="16757427">
-          <a:off x="2284276" y="1390976"/>
-          <a:ext cx="1346666" cy="8220"/>
+          <a:off x="2277274" y="1434244"/>
+          <a:ext cx="1341777" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -15860,10 +16031,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1346666" y="4110"/>
+                <a:pt x="1341777" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -15922,8 +16093,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2923942" y="1361420"/>
-        <a:ext cx="67333" cy="67333"/>
+        <a:off x="2914618" y="1404744"/>
+        <a:ext cx="67088" cy="67088"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{EB7188F2-1357-4748-A44C-AB5D4A48F40F}">
@@ -15933,8 +16104,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3066312" y="549815"/>
-          <a:ext cx="1407331" cy="361541"/>
+          <a:off x="3056471" y="596085"/>
+          <a:ext cx="1402222" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16004,8 +16175,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3076901" y="560404"/>
-        <a:ext cx="1386153" cy="340363"/>
+        <a:off x="3067022" y="606636"/>
+        <a:ext cx="1381120" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7531319A-E0E5-4CB4-9F35-33254694A0D7}">
@@ -16015,8 +16186,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17860289">
-          <a:off x="4350219" y="522390"/>
-          <a:ext cx="460883" cy="8220"/>
+          <a:off x="4335717" y="568811"/>
+          <a:ext cx="459210" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16027,10 +16198,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="460883" y="4110"/>
+                <a:pt x="459210" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16089,8 +16260,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4569139" y="514979"/>
-        <a:ext cx="23044" cy="23044"/>
+        <a:off x="4553842" y="561375"/>
+        <a:ext cx="22960" cy="22960"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{8F385C2E-83EB-470A-8A65-12C51C60EB27}">
@@ -16100,8 +16271,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4687678" y="140049"/>
-          <a:ext cx="1776175" cy="364734"/>
+          <a:off x="4671951" y="187807"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16171,8 +16342,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4698361" y="150732"/>
-        <a:ext cx="1754809" cy="343368"/>
+        <a:off x="4682595" y="198451"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{8EC6EEF9-E6D8-4DE2-A6DD-BB50B40A5CF0}">
@@ -16182,8 +16353,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6463853" y="318305"/>
-          <a:ext cx="220774" cy="8220"/>
+          <a:off x="6441677" y="365467"/>
+          <a:ext cx="219972" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16194,10 +16365,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="220774" y="4110"/>
+                <a:pt x="219972" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16252,8 +16423,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6568721" y="316896"/>
-        <a:ext cx="11038" cy="11038"/>
+        <a:off x="6546165" y="364012"/>
+        <a:ext cx="10998" cy="10998"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{31CFEB2D-0887-4520-AF04-1E3C38912960}">
@@ -16263,8 +16434,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6684628" y="140049"/>
-          <a:ext cx="3167897" cy="364734"/>
+          <a:off x="6661650" y="187807"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16350,8 +16521,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6695311" y="150732"/>
-        <a:ext cx="3146531" cy="343368"/>
+        <a:off x="6672294" y="198451"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{602438BB-CBF9-49AF-AB0A-D57EA2C10BE2}">
@@ -16361,8 +16532,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9852525" y="318305"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9818046" y="365467"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16373,10 +16544,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16431,8 +16602,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9955792" y="316981"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9920939" y="364096"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{57D97F9E-094F-4C3F-82B2-5A689BC4D082}">
@@ -16442,8 +16613,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10069930" y="146189"/>
-          <a:ext cx="1807704" cy="352453"/>
+          <a:off x="10034662" y="193925"/>
+          <a:ext cx="1801141" cy="351174"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16540,8 +16711,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10080253" y="156512"/>
-        <a:ext cx="1787058" cy="331807"/>
+        <a:off x="10044948" y="204211"/>
+        <a:ext cx="1780569" cy="330602"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B3B4155B-F64B-452E-AEBC-36FE76B0BD69}">
@@ -16551,8 +16722,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="21585916">
-          <a:off x="4473642" y="726030"/>
-          <a:ext cx="217406" cy="8220"/>
+          <a:off x="4458692" y="771712"/>
+          <a:ext cx="216617" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16563,10 +16734,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217406" y="4110"/>
+                <a:pt x="216617" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16621,8 +16792,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4576910" y="724705"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="4561585" y="770341"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D20B6C81-A2D9-4E8E-80C0-968EFF7F89E1}">
@@ -16632,8 +16803,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4691048" y="547328"/>
-          <a:ext cx="1776175" cy="364734"/>
+          <a:off x="4675308" y="593607"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16703,8 +16874,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4701731" y="558011"/>
-        <a:ext cx="1754809" cy="343368"/>
+        <a:off x="4685952" y="604251"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7FE58BCF-6B0D-48A2-8DDE-611A1D34A4D6}">
@@ -16714,8 +16885,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6467223" y="725585"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="6445035" y="771268"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16726,10 +16897,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16784,8 +16955,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6570490" y="724260"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="6547927" y="769897"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{629314FA-FCA6-45B9-99A7-2C2196A96D5C}">
@@ -16795,8 +16966,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6684628" y="547328"/>
-          <a:ext cx="3167897" cy="364734"/>
+          <a:off x="6661650" y="593607"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16895,8 +17066,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6695311" y="558011"/>
-        <a:ext cx="3146531" cy="343368"/>
+        <a:off x="6672294" y="604251"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{CCF144EB-A097-46BE-8FF7-BE5C7A394E2A}">
@@ -16906,8 +17077,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9852525" y="725585"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9818046" y="771268"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16918,10 +17089,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16976,8 +17147,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9955792" y="724260"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9920939" y="769897"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9EE0F2D9-F39B-4921-9EAC-DBA04DC260DD}">
@@ -16987,8 +17158,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10069930" y="545546"/>
-          <a:ext cx="1807704" cy="368297"/>
+          <a:off x="10034662" y="591832"/>
+          <a:ext cx="1801141" cy="366960"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17071,8 +17242,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10080717" y="556333"/>
-        <a:ext cx="1786130" cy="346723"/>
+        <a:off x="10045410" y="602580"/>
+        <a:ext cx="1779645" cy="345464"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6169CD61-5E3A-4096-AA5A-91A22C397918}">
@@ -17082,8 +17253,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="3717526">
-          <a:off x="4351116" y="930560"/>
-          <a:ext cx="462458" cy="8220"/>
+          <a:off x="4336611" y="975499"/>
+          <a:ext cx="460779" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17094,10 +17265,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="462458" y="4110"/>
+                <a:pt x="460779" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17152,8 +17323,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4570784" y="923109"/>
-        <a:ext cx="23122" cy="23122"/>
+        <a:off x="4555481" y="968024"/>
+        <a:ext cx="23038" cy="23038"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D5FDB947-B70B-4493-B9F9-83A45503DA23}">
@@ -17163,8 +17334,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4691048" y="956388"/>
-          <a:ext cx="1776175" cy="364734"/>
+          <a:off x="4675308" y="1001183"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17234,8 +17405,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4701731" y="967071"/>
-        <a:ext cx="1754809" cy="343368"/>
+        <a:off x="4685952" y="1011827"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9EDF68AF-E14B-40BF-AB6D-4B01635D735A}">
@@ -17245,8 +17416,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6467223" y="1134645"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="6445035" y="1178843"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17257,10 +17428,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17315,8 +17486,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6570490" y="1133321"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="6547927" y="1177472"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{5A5C0991-25ED-4076-91F2-80A2EEFC811E}">
@@ -17326,8 +17497,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6684628" y="956388"/>
-          <a:ext cx="3167897" cy="364734"/>
+          <a:off x="6661650" y="1001183"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17461,8 +17632,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6695311" y="967071"/>
-        <a:ext cx="3146531" cy="343368"/>
+        <a:off x="6672294" y="1011827"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{723082D3-A8E2-4807-89B5-C74C600B949E}">
@@ -17472,8 +17643,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9852525" y="1134645"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9818046" y="1178843"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17484,10 +17655,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17542,8 +17713,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9955792" y="1133321"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9920939" y="1177472"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{05E664DE-AAC0-4D52-9AA4-DE55CA572420}">
@@ -17553,8 +17724,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10069930" y="954607"/>
-          <a:ext cx="1807704" cy="368297"/>
+          <a:off x="10034662" y="999408"/>
+          <a:ext cx="1801141" cy="366960"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17624,8 +17795,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10080717" y="965394"/>
-        <a:ext cx="1786130" cy="346723"/>
+        <a:off x="10045410" y="1010156"/>
+        <a:ext cx="1779645" cy="345464"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{16F44D37-2601-482A-9095-0B3E8E10E520}">
@@ -17635,8 +17806,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="1505741">
-          <a:off x="2837576" y="2106387"/>
-          <a:ext cx="240066" cy="8220"/>
+          <a:off x="2828565" y="2147057"/>
+          <a:ext cx="239195" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17647,10 +17818,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="240066" y="4110"/>
+                <a:pt x="239195" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17709,8 +17880,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2951607" y="2104496"/>
-        <a:ext cx="12003" cy="12003"/>
+        <a:off x="2942183" y="2145122"/>
+        <a:ext cx="11959" cy="11959"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{2D542640-C237-42B5-8470-73084719F8F3}">
@@ -17720,8 +17891,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3066312" y="1980637"/>
-          <a:ext cx="1407331" cy="361541"/>
+          <a:off x="3056471" y="2021712"/>
+          <a:ext cx="1402222" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17791,8 +17962,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3076901" y="1991226"/>
-        <a:ext cx="1386153" cy="340363"/>
+        <a:off x="3067022" y="2032263"/>
+        <a:ext cx="1381120" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{BFCFD3BD-878E-4ADC-81DA-3641DCD660A7}">
@@ -17802,8 +17973,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17370601">
-          <a:off x="4256862" y="1850501"/>
-          <a:ext cx="650967" cy="8220"/>
+          <a:off x="4242699" y="1892100"/>
+          <a:ext cx="648604" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17814,10 +17985,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="650967" y="4110"/>
+                <a:pt x="648604" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17872,8 +18043,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4566071" y="1838338"/>
-        <a:ext cx="32548" cy="32548"/>
+        <a:off x="4550785" y="1879930"/>
+        <a:ext cx="32430" cy="32430"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{911F1DD5-D3D2-4321-A1A5-7E2BAE25AAD5}">
@@ -17883,8 +18054,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4691048" y="1365449"/>
-          <a:ext cx="1776175" cy="364734"/>
+          <a:off x="4675308" y="1408758"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17954,8 +18125,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4701731" y="1376132"/>
-        <a:ext cx="1754809" cy="343368"/>
+        <a:off x="4685952" y="1419402"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{F4CAC384-240B-4811-A7FE-5EF39454FD0A}">
@@ -17965,8 +18136,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6467223" y="1543706"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="6445035" y="1586419"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17977,10 +18148,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18035,8 +18206,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6570490" y="1542381"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="6547927" y="1585048"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{00847D60-C67D-487A-B918-B0C406DE6A20}">
@@ -18046,8 +18217,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6684628" y="1365449"/>
-          <a:ext cx="3167897" cy="364734"/>
+          <a:off x="6661650" y="1408758"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -18157,8 +18328,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6695311" y="1376132"/>
-        <a:ext cx="3146531" cy="343368"/>
+        <a:off x="6672294" y="1419402"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7682FEBA-2A8A-4CEB-BAD3-CAC6D62452E9}">
@@ -18168,8 +18339,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9852525" y="1543706"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9818046" y="1586419"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18180,10 +18351,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18238,8 +18409,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9955792" y="1542381"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9920939" y="1585048"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4C2C55F9-D12D-4BE1-85AD-8FAFF8B344C7}">
@@ -18249,8 +18420,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10069930" y="1363668"/>
-          <a:ext cx="1807704" cy="368297"/>
+          <a:off x="10034662" y="1406983"/>
+          <a:ext cx="1801141" cy="366960"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -18368,8 +18539,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10080717" y="1374455"/>
-        <a:ext cx="1786130" cy="346723"/>
+        <a:off x="10045410" y="1417731"/>
+        <a:ext cx="1779645" cy="345464"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6A4076F7-5C10-4205-AF7B-34977DAE41B6}">
@@ -18379,8 +18550,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19004863">
-          <a:off x="4433100" y="2055032"/>
-          <a:ext cx="298492" cy="8220"/>
+          <a:off x="4418296" y="2095888"/>
+          <a:ext cx="297408" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18391,10 +18562,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="298492" y="4110"/>
+                <a:pt x="297408" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18449,8 +18620,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4574883" y="2051680"/>
-        <a:ext cx="14924" cy="14924"/>
+        <a:off x="4559565" y="2092498"/>
+        <a:ext cx="14870" cy="14870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D2D6EBAC-87C6-4589-B626-76CA00356F2A}">
@@ -18460,8 +18631,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4691048" y="1774510"/>
-          <a:ext cx="1776175" cy="364734"/>
+          <a:off x="4675308" y="1816334"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -18531,8 +18702,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4701731" y="1785193"/>
-        <a:ext cx="1754809" cy="343368"/>
+        <a:off x="4685952" y="1826978"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4CEC118E-B718-4A3D-A714-E879160F0F50}">
@@ -18542,8 +18713,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6467223" y="1952767"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="6445035" y="1993994"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18554,10 +18725,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18612,8 +18783,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6570490" y="1951442"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="6547927" y="1992623"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{96C9B796-69AA-48A9-AB67-0FE5F7CEFC9D}">
@@ -18623,8 +18794,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6684628" y="1774510"/>
-          <a:ext cx="3167897" cy="364734"/>
+          <a:off x="6661650" y="1816334"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -18718,8 +18889,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6695311" y="1785193"/>
-        <a:ext cx="3146531" cy="343368"/>
+        <a:off x="6672294" y="1826978"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{0C4A9E51-DEA5-4AC0-B8EC-F712BFE3BA51}">
@@ -18729,8 +18900,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9852525" y="1952767"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9818046" y="1993994"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18741,10 +18912,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18799,8 +18970,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9955792" y="1951442"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9920939" y="1992623"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{829A6295-4379-4C15-BF91-56D56B48CA13}">
@@ -18810,8 +18981,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10069930" y="1772728"/>
-          <a:ext cx="1807704" cy="368297"/>
+          <a:off x="10034662" y="1814559"/>
+          <a:ext cx="1801141" cy="366960"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -18897,8 +19068,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10080717" y="1783515"/>
-        <a:ext cx="1786130" cy="346723"/>
+        <a:off x="10045410" y="1825307"/>
+        <a:ext cx="1779645" cy="345464"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{15251D3B-5937-4D92-B910-59FBB0B78504}">
@@ -18908,8 +19079,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2595137">
-          <a:off x="4433100" y="2259562"/>
-          <a:ext cx="298492" cy="8220"/>
+          <a:off x="4418296" y="2299676"/>
+          <a:ext cx="297408" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18920,10 +19091,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="298492" y="4110"/>
+                <a:pt x="297408" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18978,8 +19149,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4574883" y="2256210"/>
-        <a:ext cx="14924" cy="14924"/>
+        <a:off x="4559565" y="2296285"/>
+        <a:ext cx="14870" cy="14870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{55C8ECFC-533A-4D04-B170-164B29EE9A7D}">
@@ -18989,8 +19160,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4691048" y="2183570"/>
-          <a:ext cx="1776175" cy="364734"/>
+          <a:off x="4675308" y="2223909"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19060,8 +19231,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4701731" y="2194253"/>
-        <a:ext cx="1754809" cy="343368"/>
+        <a:off x="4685952" y="2234553"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A63458DA-4732-44A8-AAAD-101471030A2E}">
@@ -19071,8 +19242,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6467223" y="2361827"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="6445035" y="2401570"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19083,10 +19254,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19141,8 +19312,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6570490" y="2360502"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="6547927" y="2400199"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{3CFC9EAC-3C3A-42EE-A809-37090C958CCC}">
@@ -19152,8 +19323,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6684628" y="2183570"/>
-          <a:ext cx="3167897" cy="364734"/>
+          <a:off x="6661650" y="2223909"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19231,8 +19402,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6695311" y="2194253"/>
-        <a:ext cx="3146531" cy="343368"/>
+        <a:off x="6672294" y="2234553"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{2E1BE310-D0FB-4439-BC13-EF25298A0AC1}">
@@ -19242,8 +19413,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9852525" y="2361827"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9818046" y="2401570"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19254,10 +19425,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19312,8 +19483,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9955792" y="2360502"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9920939" y="2400199"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{05029C16-99B1-4993-B5A7-DFCE2EC4AF2D}">
@@ -19323,8 +19494,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10069930" y="2181789"/>
-          <a:ext cx="1807704" cy="368297"/>
+          <a:off x="10034662" y="2222134"/>
+          <a:ext cx="1801141" cy="366960"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19394,8 +19565,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10080717" y="2192576"/>
-        <a:ext cx="1786130" cy="346723"/>
+        <a:off x="10045410" y="2232882"/>
+        <a:ext cx="1779645" cy="345464"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7B1A1F24-5790-42BE-9800-70C6BAC67F71}">
@@ -19405,8 +19576,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="4229399">
-          <a:off x="4256862" y="2464092"/>
-          <a:ext cx="650967" cy="8220"/>
+          <a:off x="4242699" y="2503464"/>
+          <a:ext cx="648604" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19417,10 +19588,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="650967" y="4110"/>
+                <a:pt x="648604" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19475,8 +19646,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4566071" y="2451929"/>
-        <a:ext cx="32548" cy="32548"/>
+        <a:off x="4550785" y="2491293"/>
+        <a:ext cx="32430" cy="32430"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{F9E7099E-D348-4A20-924E-7B36E8E1B00D}">
@@ -19486,8 +19657,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4691048" y="2592631"/>
-          <a:ext cx="1794725" cy="364734"/>
+          <a:off x="4675308" y="2631485"/>
+          <a:ext cx="1788209" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19557,8 +19728,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4701731" y="2603314"/>
-        <a:ext cx="1773359" cy="343368"/>
+        <a:off x="4685952" y="2642129"/>
+        <a:ext cx="1766921" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{69A95BFF-166E-4390-9963-14C8F025ADBA}">
@@ -19568,8 +19739,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6485773" y="2770888"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="6463518" y="2809145"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19580,10 +19751,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19638,8 +19809,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6589040" y="2769563"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="6566410" y="2807775"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{BBDCC5A6-74D1-4E37-848C-BF5D7C733A0C}">
@@ -19649,8 +19820,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6703178" y="2592631"/>
-          <a:ext cx="3167897" cy="364734"/>
+          <a:off x="6680133" y="2631485"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19720,8 +19891,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6713861" y="2603314"/>
-        <a:ext cx="3146531" cy="343368"/>
+        <a:off x="6690777" y="2642129"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E75A9ED0-3CF3-4FBB-B735-763677226156}">
@@ -19731,8 +19902,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9871075" y="2770888"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9836529" y="2809145"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19743,10 +19914,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19801,8 +19972,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9974342" y="2769563"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9939421" y="2807775"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D255C67C-B87B-4D25-A5F4-B2880DE74996}">
@@ -19812,8 +19983,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10088480" y="2590850"/>
-          <a:ext cx="1807704" cy="368297"/>
+          <a:off x="10053144" y="2629710"/>
+          <a:ext cx="1801141" cy="366960"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19907,8 +20078,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10099267" y="2601637"/>
-        <a:ext cx="1786130" cy="346723"/>
+        <a:off x="10063892" y="2640458"/>
+        <a:ext cx="1779645" cy="345464"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{19133C7D-D6FC-4086-9EFA-C8E67C09EF92}">
@@ -19918,8 +20089,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="4842573">
-          <a:off x="2284276" y="2719978"/>
-          <a:ext cx="1346666" cy="8220"/>
+          <a:off x="2277274" y="2758420"/>
+          <a:ext cx="1341777" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19930,10 +20101,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1346666" y="4110"/>
+                <a:pt x="1341777" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19988,8 +20159,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2923942" y="2690422"/>
-        <a:ext cx="67333" cy="67333"/>
+        <a:off x="2914618" y="2728920"/>
+        <a:ext cx="67088" cy="67088"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{3A58F96D-43A0-4E22-A03B-64FF8A7610E3}">
@@ -19999,8 +20170,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3066312" y="3207818"/>
-          <a:ext cx="1407331" cy="361541"/>
+          <a:off x="3056471" y="3244439"/>
+          <a:ext cx="1402222" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20070,8 +20241,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3076901" y="3218407"/>
-        <a:ext cx="1386153" cy="340363"/>
+        <a:off x="3067022" y="3254990"/>
+        <a:ext cx="1381120" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{BC1A1E23-E0C9-4175-8735-D110618B99B3}">
@@ -20081,8 +20252,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19004863">
-          <a:off x="4433100" y="3282214"/>
-          <a:ext cx="298492" cy="8220"/>
+          <a:off x="4418296" y="3318615"/>
+          <a:ext cx="297408" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20093,10 +20264,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="298492" y="4110"/>
+                <a:pt x="297408" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20151,8 +20322,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4574883" y="3278862"/>
-        <a:ext cx="14924" cy="14924"/>
+        <a:off x="4559565" y="3315224"/>
+        <a:ext cx="14870" cy="14870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{5D691BA5-158A-4034-AEDA-B152BE077B27}">
@@ -20162,8 +20333,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4691048" y="3001692"/>
-          <a:ext cx="1776175" cy="364734"/>
+          <a:off x="4675308" y="3039060"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20233,8 +20404,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4701731" y="3012375"/>
-        <a:ext cx="1754809" cy="343368"/>
+        <a:off x="4685952" y="3049704"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{C26309FF-9296-40B3-913C-85759C2B07DC}">
@@ -20244,8 +20415,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6467223" y="3179948"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="6445035" y="3216721"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20256,10 +20427,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20314,8 +20485,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6570490" y="3178624"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="6547927" y="3215350"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A4750321-4845-43B0-945B-4B9E7C7A668E}">
@@ -20325,8 +20496,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6684628" y="3001692"/>
-          <a:ext cx="3167897" cy="364734"/>
+          <a:off x="6661650" y="3039060"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20420,8 +20591,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6695311" y="3012375"/>
-        <a:ext cx="3146531" cy="343368"/>
+        <a:off x="6672294" y="3049704"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{CCE9C4CE-7CF8-4820-8390-F3CBCCE81ED7}">
@@ -20431,8 +20602,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9852525" y="3179948"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9818046" y="3216721"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20443,10 +20614,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20501,8 +20672,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9955792" y="3178624"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9920939" y="3215350"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D954D938-3009-44F7-BB4F-D9E8AFB2B291}">
@@ -20512,8 +20683,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10069930" y="2999910"/>
-          <a:ext cx="1807704" cy="368297"/>
+          <a:off x="10034662" y="3037285"/>
+          <a:ext cx="1801141" cy="366960"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20583,8 +20754,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10080717" y="3010697"/>
-        <a:ext cx="1786130" cy="346723"/>
+        <a:off x="10045410" y="3048033"/>
+        <a:ext cx="1779645" cy="345464"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D01C8F64-85EC-45F5-B192-363D2A57FB6E}">
@@ -20594,8 +20765,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2595137">
-          <a:off x="4433100" y="3486744"/>
-          <a:ext cx="298492" cy="8220"/>
+          <a:off x="4418296" y="3522403"/>
+          <a:ext cx="297408" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20606,10 +20777,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="298492" y="4110"/>
+                <a:pt x="297408" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20664,8 +20835,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4574883" y="3483392"/>
-        <a:ext cx="14924" cy="14924"/>
+        <a:off x="4559565" y="3519012"/>
+        <a:ext cx="14870" cy="14870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7832722B-5DD1-4AAD-819C-BC966C90EDAC}">
@@ -20675,8 +20846,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4691048" y="3410752"/>
-          <a:ext cx="1776175" cy="364734"/>
+          <a:off x="4675308" y="3446636"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20746,8 +20917,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4701731" y="3421435"/>
-        <a:ext cx="1754809" cy="343368"/>
+        <a:off x="4685952" y="3457280"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9B049FA9-70FB-4D7E-AD76-2BFCDB3B4195}">
@@ -20757,8 +20928,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6467223" y="3589009"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="6445035" y="3624296"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20769,10 +20940,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20827,8 +20998,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6570490" y="3587684"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="6547927" y="3622926"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B5153D0A-E9E7-482C-B1CC-838341F8F3D8}">
@@ -20838,8 +21009,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6684628" y="3410752"/>
-          <a:ext cx="3167897" cy="364734"/>
+          <a:off x="6661650" y="3446636"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20925,8 +21096,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6695311" y="3421435"/>
-        <a:ext cx="3146531" cy="343368"/>
+        <a:off x="6672294" y="3457280"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1118BB77-BCCA-46BE-8B0C-417EE0F19393}">
@@ -20936,8 +21107,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9852525" y="3589009"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9818046" y="3624296"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20948,10 +21119,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21006,8 +21177,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9955792" y="3587684"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9920939" y="3622926"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A1FE2FD1-D3B2-4F02-B33F-7EA3496A9D7D}">
@@ -21017,8 +21188,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10069930" y="3408971"/>
-          <a:ext cx="1807704" cy="368297"/>
+          <a:off x="10034662" y="3444861"/>
+          <a:ext cx="1801141" cy="366960"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21088,8 +21259,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10080717" y="3419758"/>
-        <a:ext cx="1786130" cy="346723"/>
+        <a:off x="10045410" y="3455609"/>
+        <a:ext cx="1779645" cy="345464"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{ACD64E2A-6A03-49D1-9C11-853B1D5FDA3F}">
@@ -21099,8 +21270,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="4880920">
-          <a:off x="572912" y="4198773"/>
-          <a:ext cx="1445308" cy="8220"/>
+          <a:off x="572123" y="4231846"/>
+          <a:ext cx="1440061" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21111,10 +21282,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1445308" y="4110"/>
+                <a:pt x="1440061" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21169,8 +21340,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1259433" y="4166750"/>
-        <a:ext cx="72265" cy="72265"/>
+        <a:off x="1256152" y="4199889"/>
+        <a:ext cx="72003" cy="72003"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4915DA81-5EFF-4A45-B117-A1C9369BA960}">
@@ -21180,8 +21351,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="1404269" y="4736544"/>
-          <a:ext cx="1437708" cy="361541"/>
+          <a:off x="1400462" y="4767614"/>
+          <a:ext cx="1432488" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21303,8 +21474,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1414858" y="4747133"/>
-        <a:ext cx="1416530" cy="340363"/>
+        <a:off x="1411013" y="4778165"/>
+        <a:ext cx="1411386" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A3777E34-F7A1-4ABC-99E9-9C9A9AB7B959}">
@@ -21314,8 +21485,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17225057">
-          <a:off x="2585877" y="4566573"/>
-          <a:ext cx="725267" cy="8220"/>
+          <a:off x="2577781" y="4598311"/>
+          <a:ext cx="722633" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21326,10 +21497,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="725267" y="4110"/>
+                <a:pt x="722633" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21384,8 +21555,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2930379" y="4552551"/>
-        <a:ext cx="36263" cy="36263"/>
+        <a:off x="2921032" y="4584290"/>
+        <a:ext cx="36131" cy="36131"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{23228D17-0E30-4278-86F1-009AEEE4B90D}">
@@ -21395,8 +21566,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3055045" y="4043280"/>
-          <a:ext cx="1407331" cy="361541"/>
+          <a:off x="3045245" y="4076868"/>
+          <a:ext cx="1402222" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21466,8 +21637,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3065634" y="4053869"/>
-        <a:ext cx="1386153" cy="340363"/>
+        <a:off x="3055796" y="4087419"/>
+        <a:ext cx="1381120" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A22E3146-1836-4A0C-A6D3-4503A76A9781}">
@@ -21477,8 +21648,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19004863">
-          <a:off x="4421833" y="4117676"/>
-          <a:ext cx="298492" cy="8220"/>
+          <a:off x="4407070" y="4151044"/>
+          <a:ext cx="297408" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21489,10 +21660,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="298492" y="4110"/>
+                <a:pt x="297408" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21547,8 +21718,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4563616" y="4114324"/>
-        <a:ext cx="14924" cy="14924"/>
+        <a:off x="4548339" y="4147653"/>
+        <a:ext cx="14870" cy="14870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{06E3AC3D-2CA5-4C28-B4EE-08E1F5093575}">
@@ -21558,8 +21729,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4679781" y="3837154"/>
-          <a:ext cx="1776175" cy="364734"/>
+          <a:off x="4664082" y="3871489"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21645,8 +21816,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4690464" y="3847837"/>
-        <a:ext cx="1754809" cy="343368"/>
+        <a:off x="4674726" y="3882133"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{AB38F8C9-39F9-48F1-A4B9-359AD3B6C9E1}">
@@ -21656,8 +21827,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6455956" y="4015410"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="6433809" y="4049150"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21668,10 +21839,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21726,8 +21897,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6559223" y="4014086"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="6536701" y="4047779"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{94E3E4AC-563C-467A-AD10-294BF8A33BAF}">
@@ -21737,8 +21908,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6673361" y="3837154"/>
-          <a:ext cx="3167897" cy="364734"/>
+          <a:off x="6650424" y="3871489"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21824,8 +21995,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6684044" y="3847837"/>
-        <a:ext cx="3146531" cy="343368"/>
+        <a:off x="6661068" y="3882133"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{CE4A2E59-3DB6-4586-9EDA-16655120708B}">
@@ -21835,8 +22006,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9841258" y="4015410"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9806820" y="4049150"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21847,10 +22018,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21905,8 +22076,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9944525" y="4014086"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9909712" y="4047779"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{74F8E0C0-A1C2-4026-BDD1-211E4452BF84}">
@@ -21916,8 +22087,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10058663" y="3835372"/>
-          <a:ext cx="1807704" cy="368297"/>
+          <a:off x="10023436" y="3869714"/>
+          <a:ext cx="1801141" cy="366960"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21987,8 +22158,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10069450" y="3846159"/>
-        <a:ext cx="1786130" cy="346723"/>
+        <a:off x="10034184" y="3880462"/>
+        <a:ext cx="1779645" cy="345464"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{3776BE60-D86F-469E-9605-E0609281B4B9}">
@@ -21998,8 +22169,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2595137">
-          <a:off x="4421833" y="4322206"/>
-          <a:ext cx="298492" cy="8220"/>
+          <a:off x="4407070" y="4354831"/>
+          <a:ext cx="297408" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22010,10 +22181,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="298492" y="4110"/>
+                <a:pt x="297408" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22068,8 +22239,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4563616" y="4318854"/>
-        <a:ext cx="14924" cy="14924"/>
+        <a:off x="4548339" y="4351441"/>
+        <a:ext cx="14870" cy="14870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{DC0F0790-8247-4EA1-A5BD-20B9C2810EA5}">
@@ -22079,8 +22250,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4679781" y="4246214"/>
-          <a:ext cx="1776175" cy="364734"/>
+          <a:off x="4664082" y="4279065"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22150,8 +22321,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4690464" y="4256897"/>
-        <a:ext cx="1754809" cy="343368"/>
+        <a:off x="4674726" y="4289709"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{82B78A4F-EF07-4DEA-A3EC-7BA9DD55DC45}">
@@ -22161,8 +22332,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6455956" y="4424471"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="6433809" y="4456725"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22173,10 +22344,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22231,8 +22402,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6559223" y="4423146"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="6536701" y="4455354"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4D82C0F8-05DA-476F-9FFD-EF5362E37ABC}">
@@ -22242,8 +22413,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6673361" y="4246214"/>
-          <a:ext cx="3167897" cy="364734"/>
+          <a:off x="6650424" y="4279065"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22321,8 +22492,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6684044" y="4256897"/>
-        <a:ext cx="3146531" cy="343368"/>
+        <a:off x="6661068" y="4289709"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6F09ED48-69E5-4359-AEF9-003C31CF3834}">
@@ -22332,8 +22503,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9841258" y="4424471"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9806820" y="4456725"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22344,10 +22515,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22402,8 +22573,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9944525" y="4423146"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9909712" y="4455354"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7F4C8494-F5DD-49F1-B7FE-320AAF64A334}">
@@ -22413,8 +22584,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10058663" y="4244433"/>
-          <a:ext cx="1807704" cy="368297"/>
+          <a:off x="10023436" y="4277290"/>
+          <a:ext cx="1801141" cy="366960"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22489,8 +22660,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10069450" y="4255220"/>
-        <a:ext cx="1786130" cy="346723"/>
+        <a:off x="10034184" y="4288038"/>
+        <a:ext cx="1779645" cy="345464"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E97A89EA-A088-4B36-94ED-03E39FF28C24}">
@@ -22500,8 +22671,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="1512707">
-          <a:off x="2830532" y="4964383"/>
-          <a:ext cx="240295" cy="8220"/>
+          <a:off x="2821547" y="4994677"/>
+          <a:ext cx="239423" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22512,10 +22683,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="240295" y="4110"/>
+                <a:pt x="239423" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22570,8 +22741,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2944672" y="4962486"/>
-        <a:ext cx="12014" cy="12014"/>
+        <a:off x="2935273" y="4992736"/>
+        <a:ext cx="11971" cy="11971"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1279AA60-C872-4597-B281-C6CC2E4A34C2}">
@@ -22581,8 +22752,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3059382" y="4838902"/>
-          <a:ext cx="1407331" cy="361541"/>
+          <a:off x="3049566" y="4869600"/>
+          <a:ext cx="1402222" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22652,8 +22823,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3069971" y="4849491"/>
-        <a:ext cx="1386153" cy="340363"/>
+        <a:off x="3060117" y="4880151"/>
+        <a:ext cx="1381120" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{255CD393-ED80-4D10-A68E-31ED59592E3B}">
@@ -22663,8 +22834,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19138242">
-          <a:off x="4432026" y="4922858"/>
-          <a:ext cx="282442" cy="8220"/>
+          <a:off x="4417227" y="4953303"/>
+          <a:ext cx="281417" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22675,10 +22846,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="282442" y="4110"/>
+                <a:pt x="281417" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22733,8 +22904,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4566186" y="4919907"/>
-        <a:ext cx="14122" cy="14122"/>
+        <a:off x="4550900" y="4950312"/>
+        <a:ext cx="14070" cy="14070"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{2340676A-EBD4-4E22-BA9C-E56B6A62904C}">
@@ -22744,8 +22915,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4679781" y="4651897"/>
-          <a:ext cx="1776175" cy="364734"/>
+          <a:off x="4664082" y="4683274"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22815,8 +22986,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4690464" y="4662580"/>
-        <a:ext cx="1754809" cy="343368"/>
+        <a:off x="4674726" y="4693918"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{EB837690-03CF-4B39-A4B0-AFC71E15928A}">
@@ -22826,8 +22997,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="27806">
-          <a:off x="6455952" y="4831051"/>
-          <a:ext cx="221749" cy="8220"/>
+          <a:off x="6433805" y="4861829"/>
+          <a:ext cx="220944" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22838,10 +23009,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="221749" y="4110"/>
+                <a:pt x="220944" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22896,8 +23067,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6561283" y="4829617"/>
-        <a:ext cx="11087" cy="11087"/>
+        <a:off x="6538754" y="4860350"/>
+        <a:ext cx="11047" cy="11047"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6CD3FE0A-3BBE-455B-B381-72424654A1B0}">
@@ -22907,8 +23078,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6677698" y="4655287"/>
-          <a:ext cx="3167092" cy="361541"/>
+          <a:off x="6654746" y="4686652"/>
+          <a:ext cx="3155594" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22986,8 +23157,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6688287" y="4665876"/>
-        <a:ext cx="3145914" cy="340363"/>
+        <a:off x="6665297" y="4697203"/>
+        <a:ext cx="3134492" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B86CABA2-1933-4D02-A0D3-AA6DEA35BCA7}">
@@ -22997,8 +23168,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9844791" y="4831947"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9810340" y="4862722"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23009,10 +23180,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23067,8 +23238,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9948058" y="4830623"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9913232" y="4861351"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{920A36CD-D69B-4AB0-8DA2-4963F1111FE2}">
@@ -23078,8 +23249,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10062195" y="4655287"/>
-          <a:ext cx="1807704" cy="361541"/>
+          <a:off x="10026956" y="4686652"/>
+          <a:ext cx="1801141" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23149,8 +23320,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10072784" y="4665876"/>
-        <a:ext cx="1786526" cy="340363"/>
+        <a:off x="10037507" y="4697203"/>
+        <a:ext cx="1780039" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{EE30240B-4D3F-4585-94A4-7AD0CBEBACD0}">
@@ -23160,8 +23331,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2755727">
-          <a:off x="4420083" y="5125607"/>
-          <a:ext cx="306328" cy="8220"/>
+          <a:off x="4405327" y="5155316"/>
+          <a:ext cx="305216" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23172,10 +23343,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="306328" y="4110"/>
+                <a:pt x="305216" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23230,8 +23401,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4565589" y="5122059"/>
-        <a:ext cx="15316" cy="15316"/>
+        <a:off x="4550305" y="5151730"/>
+        <a:ext cx="15260" cy="15260"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9B0332A1-DFA5-4E72-89B6-8E8C50F667E1}">
@@ -23241,8 +23412,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4679781" y="5057395"/>
-          <a:ext cx="1776175" cy="364734"/>
+          <a:off x="4664082" y="5087300"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23339,8 +23510,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4690464" y="5068078"/>
-        <a:ext cx="1754809" cy="343368"/>
+        <a:off x="4674726" y="5097944"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4EF5B1E7-3D92-44D9-8E8A-E2A10FB649AC}">
@@ -23350,8 +23521,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="27806">
-          <a:off x="6455952" y="5236548"/>
-          <a:ext cx="221749" cy="8220"/>
+          <a:off x="6433805" y="5265854"/>
+          <a:ext cx="220944" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23362,10 +23533,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="221749" y="4110"/>
+                <a:pt x="220944" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23420,8 +23591,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6561283" y="5235115"/>
-        <a:ext cx="11087" cy="11087"/>
+        <a:off x="6538754" y="5264375"/>
+        <a:ext cx="11047" cy="11047"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9AC7A0EB-B59E-41D9-A589-CB90FBF4305E}">
@@ -23431,8 +23602,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6677698" y="5060785"/>
-          <a:ext cx="3167092" cy="361541"/>
+          <a:off x="6654746" y="5090678"/>
+          <a:ext cx="3155594" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23518,8 +23689,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6688287" y="5071374"/>
-        <a:ext cx="3145914" cy="340363"/>
+        <a:off x="6665297" y="5101229"/>
+        <a:ext cx="3134492" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{2F5A23ED-2B4B-4307-BAD6-D126CED4ED45}">
@@ -23529,8 +23700,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9844791" y="5237445"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9810340" y="5266748"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23541,10 +23712,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23599,8 +23770,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9948058" y="5236121"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9913232" y="5265377"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{C9CCA1DF-737F-40B9-8662-1EBAE874B88C}">
@@ -23610,8 +23781,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10062195" y="5060785"/>
-          <a:ext cx="1807704" cy="361541"/>
+          <a:off x="10026956" y="5090678"/>
+          <a:ext cx="1801141" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23681,8 +23852,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10072784" y="5071374"/>
-        <a:ext cx="1786526" cy="340363"/>
+        <a:off x="10037507" y="5101229"/>
+        <a:ext cx="1780039" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{06804470-2E4E-45CC-AD07-54CD8F165228}">
@@ -23692,8 +23863,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="4379331">
-          <a:off x="2579121" y="5268507"/>
-          <a:ext cx="743117" cy="8220"/>
+          <a:off x="2571049" y="5297697"/>
+          <a:ext cx="740419" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23704,10 +23875,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="743117" y="4110"/>
+                <a:pt x="740419" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23762,8 +23933,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2932101" y="5254039"/>
-        <a:ext cx="37155" cy="37155"/>
+        <a:off x="2922748" y="5283231"/>
+        <a:ext cx="37020" cy="37020"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D9D1FF4E-B146-4A17-8BAD-E6A8247731B1}">
@@ -23773,8 +23944,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3059382" y="5447149"/>
-          <a:ext cx="1407337" cy="361541"/>
+          <a:off x="3049566" y="5475639"/>
+          <a:ext cx="1402227" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23860,8 +24031,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3069971" y="5457738"/>
-        <a:ext cx="1386159" cy="340363"/>
+        <a:off x="3060117" y="5486190"/>
+        <a:ext cx="1381125" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{458C594D-E94A-4416-A27A-8211BD0C18EB}">
@@ -23871,8 +24042,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4466719" y="5623809"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="4451794" y="5651709"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23883,10 +24054,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23941,8 +24112,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4569986" y="5622484"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="4554686" y="5650338"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E6BB35B6-4DC7-42B5-A329-D93F595605BC}">
@@ -23952,8 +24123,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4684124" y="5445552"/>
-          <a:ext cx="1765668" cy="364734"/>
+          <a:off x="4668409" y="5474048"/>
+          <a:ext cx="1759258" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -24039,8 +24210,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4694807" y="5456235"/>
-        <a:ext cx="1744302" cy="343368"/>
+        <a:off x="4679053" y="5484692"/>
+        <a:ext cx="1737970" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{F3CE9778-2DAD-459C-A92D-C581128238EF}">
@@ -24050,8 +24221,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6449793" y="5623809"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="6427668" y="5651709"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -24062,10 +24233,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -24120,8 +24291,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6553060" y="5622484"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="6530560" y="5650338"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A62201D7-F2CC-41E5-BB68-F68B79E1464B}">
@@ -24131,8 +24302,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6667197" y="5447149"/>
-          <a:ext cx="3167092" cy="361541"/>
+          <a:off x="6644283" y="5475639"/>
+          <a:ext cx="3155594" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -24202,8 +24373,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6677786" y="5457738"/>
-        <a:ext cx="3145914" cy="340363"/>
+        <a:off x="6654834" y="5486190"/>
+        <a:ext cx="3134492" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{46794C65-61A0-4B52-A42E-5CC9D77E3723}">
@@ -24213,8 +24384,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9834290" y="5623809"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9799878" y="5651709"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -24225,10 +24396,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -24283,8 +24454,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9937557" y="5622484"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9902770" y="5650338"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{C61F938B-5A64-4BF7-B003-81E0909084B1}">
@@ -24294,8 +24465,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10051695" y="5447149"/>
-          <a:ext cx="1807704" cy="361541"/>
+          <a:off x="10016493" y="5475639"/>
+          <a:ext cx="1801141" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -24365,8 +24536,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10062284" y="5457738"/>
-        <a:ext cx="1786526" cy="340363"/>
+        <a:off x="10027044" y="5486190"/>
+        <a:ext cx="1780039" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
   </dsp:spTree>
@@ -28157,15 +28328,17 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA7446D1-A9E6-4F8D-B799-CB90AD03762A}">
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="3.9140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="77.6640625" customWidth="1"/>
-    <col min="3" max="3" width="58.58203125" customWidth="1"/>
+    <col min="3" max="3" width="71.08203125" customWidth="1"/>
+    <col min="4" max="4" width="65.33203125" style="114" customWidth="1"/>
+    <col min="5" max="5" width="65.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="62" t="s">
         <v>336</v>
       </c>
@@ -28173,145 +28346,262 @@
         <v>421</v>
       </c>
       <c r="C1" s="59" t="s">
-        <v>422</v>
+        <v>199</v>
+      </c>
+      <c r="D1" s="115" t="s">
+        <v>200</v>
+      </c>
+      <c r="E1" s="59" t="s">
+        <v>201</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" ht="51" x14ac:dyDescent="0.45">
       <c r="A2" s="61">
         <v>1</v>
       </c>
-      <c r="B2" s="111" t="s">
-        <v>426</v>
-      </c>
-      <c r="C2" s="58"/>
+      <c r="B2" s="77" t="s">
+        <v>425</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>455</v>
+      </c>
+      <c r="D2" s="18" t="s">
+        <v>482</v>
+      </c>
+      <c r="E2" s="18" t="s">
+        <v>467</v>
+      </c>
     </row>
-    <row r="3" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" ht="85" x14ac:dyDescent="0.45">
       <c r="A3" s="61">
         <v>2</v>
       </c>
-      <c r="B3" s="111" t="s">
-        <v>428</v>
-      </c>
-      <c r="C3" s="58"/>
+      <c r="B3" s="77" t="s">
+        <v>427</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>456</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>483</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>468</v>
+      </c>
     </row>
-    <row r="4" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" ht="68" x14ac:dyDescent="0.45">
       <c r="A4" s="61">
         <v>3</v>
       </c>
-      <c r="B4" s="111" t="s">
-        <v>430</v>
-      </c>
-      <c r="C4" s="58"/>
+      <c r="B4" s="77" t="s">
+        <v>429</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>466</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>484</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>469</v>
+      </c>
     </row>
-    <row r="5" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" ht="51" x14ac:dyDescent="0.45">
       <c r="A5" s="61">
         <v>4</v>
       </c>
-      <c r="B5" s="111" t="s">
-        <v>432</v>
-      </c>
-      <c r="C5" s="58"/>
+      <c r="B5" s="77" t="s">
+        <v>431</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>457</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>485</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>470</v>
+      </c>
     </row>
-    <row r="6" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" ht="85" x14ac:dyDescent="0.45">
       <c r="A6" s="61">
         <v>5</v>
       </c>
-      <c r="B6" s="111" t="s">
-        <v>434</v>
-      </c>
-      <c r="C6" s="58"/>
+      <c r="B6" s="77" t="s">
+        <v>433</v>
+      </c>
+      <c r="C6" s="18" t="s">
+        <v>460</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>486</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>471</v>
+      </c>
     </row>
-    <row r="7" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" ht="68" x14ac:dyDescent="0.45">
       <c r="A7" s="61">
         <v>6</v>
       </c>
-      <c r="B7" s="111" t="s">
-        <v>436</v>
-      </c>
-      <c r="C7" s="58"/>
+      <c r="B7" s="77" t="s">
+        <v>435</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>465</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>487</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>472</v>
+      </c>
     </row>
-    <row r="8" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" ht="51" x14ac:dyDescent="0.45">
       <c r="A8" s="61">
         <v>7</v>
       </c>
-      <c r="B8" s="111" t="s">
-        <v>438</v>
-      </c>
-      <c r="C8" s="58"/>
+      <c r="B8" s="77" t="s">
+        <v>437</v>
+      </c>
+      <c r="C8" s="18" t="s">
+        <v>458</v>
+      </c>
+      <c r="D8" s="18" t="s">
+        <v>488</v>
+      </c>
+      <c r="E8" s="18" t="s">
+        <v>473</v>
+      </c>
     </row>
-    <row r="9" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5" ht="85" x14ac:dyDescent="0.45">
       <c r="A9" s="61">
         <v>8</v>
       </c>
-      <c r="B9" s="111" t="s">
-        <v>440</v>
-      </c>
-      <c r="C9" s="58"/>
+      <c r="B9" s="77" t="s">
+        <v>439</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>459</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>489</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>474</v>
+      </c>
     </row>
-    <row r="10" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="61">
         <v>9</v>
       </c>
-      <c r="B10" s="111" t="s">
-        <v>442</v>
-      </c>
-      <c r="C10" s="58"/>
+      <c r="B10" s="77" t="s">
+        <v>441</v>
+      </c>
+      <c r="C10" s="116" t="s">
+        <v>464</v>
+      </c>
+      <c r="D10" s="117" t="s">
+        <v>490</v>
+      </c>
+      <c r="E10" s="18" t="s">
+        <v>475</v>
+      </c>
     </row>
-    <row r="11" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="61">
         <v>10</v>
       </c>
-      <c r="B11" s="111" t="s">
-        <v>444</v>
-      </c>
-      <c r="C11" s="58"/>
+      <c r="B11" s="77" t="s">
+        <v>443</v>
+      </c>
+      <c r="C11" s="116"/>
+      <c r="D11" s="117"/>
+      <c r="E11" s="18" t="s">
+        <v>476</v>
+      </c>
     </row>
-    <row r="12" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:5" ht="51" x14ac:dyDescent="0.45">
       <c r="A12" s="61">
         <v>11</v>
       </c>
-      <c r="B12" s="111" t="s">
-        <v>446</v>
-      </c>
-      <c r="C12" s="58"/>
+      <c r="B12" s="77" t="s">
+        <v>445</v>
+      </c>
+      <c r="C12" s="18" t="s">
+        <v>463</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>491</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>477</v>
+      </c>
     </row>
-    <row r="13" spans="1:3" ht="32" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:5" ht="34" x14ac:dyDescent="0.45">
       <c r="A13" s="61">
         <v>12</v>
       </c>
-      <c r="B13" s="111" t="s">
-        <v>448</v>
+      <c r="B13" s="77" t="s">
+        <v>447</v>
       </c>
       <c r="C13" s="58"/>
+      <c r="D13" s="18" t="s">
+        <v>492</v>
+      </c>
+      <c r="E13" s="18" t="s">
+        <v>478</v>
+      </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:5" ht="34" x14ac:dyDescent="0.45">
       <c r="A14" s="61">
         <v>13</v>
       </c>
-      <c r="B14" s="112" t="s">
+      <c r="B14" s="78" t="s">
         <v>320</v>
       </c>
-      <c r="C14" s="58"/>
+      <c r="C14" s="116" t="s">
+        <v>462</v>
+      </c>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18" t="s">
+        <v>479</v>
+      </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:5" ht="35.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="61">
         <v>14</v>
       </c>
-      <c r="B15" s="113" t="s">
+      <c r="B15" s="79" t="s">
         <v>322</v>
       </c>
-      <c r="C15" s="58"/>
+      <c r="C15" s="116"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18" t="s">
+        <v>480</v>
+      </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:5" ht="34" x14ac:dyDescent="0.45">
       <c r="A16" s="61">
         <v>15</v>
       </c>
-      <c r="B16" s="113" t="s">
+      <c r="B16" s="79" t="s">
         <v>326</v>
       </c>
-      <c r="C16" s="58"/>
+      <c r="C16" s="18" t="s">
+        <v>461</v>
+      </c>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18" t="s">
+        <v>481</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="C14:C15"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -28402,7 +28692,7 @@
         <v>172</v>
       </c>
       <c r="B5" s="71" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C5" s="35">
         <v>46275</v>
@@ -28416,12 +28706,12 @@
         <v>174</v>
       </c>
       <c r="B6" s="72" t="s">
-        <v>450</v>
-      </c>
-      <c r="C6" s="76">
+        <v>449</v>
+      </c>
+      <c r="C6" s="80">
         <v>46275</v>
       </c>
-      <c r="D6" s="78" t="s">
+      <c r="D6" s="82" t="s">
         <v>316</v>
       </c>
     </row>
@@ -28430,17 +28720,17 @@
         <v>174</v>
       </c>
       <c r="B7" s="73" t="s">
-        <v>451</v>
-      </c>
-      <c r="C7" s="77"/>
-      <c r="D7" s="79"/>
+        <v>450</v>
+      </c>
+      <c r="C7" s="81"/>
+      <c r="D7" s="83"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" s="33" t="s">
         <v>175</v>
       </c>
       <c r="B8" s="74" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="C8" s="35">
         <v>46276</v>
@@ -28470,7 +28760,7 @@
         <v>46276</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="34" x14ac:dyDescent="0.45">
@@ -28482,7 +28772,7 @@
         <v>46279.645833333336</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
   </sheetData>
@@ -28548,7 +28838,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A2" s="80" t="s">
+      <c r="A2" s="84" t="s">
         <v>18</v>
       </c>
       <c r="B2" s="7" t="s">
@@ -28565,7 +28855,7 @@
       <c r="G2" s="10"/>
     </row>
     <row r="3" spans="1:7" ht="64" x14ac:dyDescent="0.45">
-      <c r="A3" s="81"/>
+      <c r="A3" s="85"/>
       <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
@@ -28582,7 +28872,7 @@
       <c r="G3" s="11"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A4" s="81"/>
+      <c r="A4" s="85"/>
       <c r="B4" s="4" t="s">
         <v>184</v>
       </c>
@@ -28597,7 +28887,7 @@
       <c r="G4" s="11"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A5" s="81"/>
+      <c r="A5" s="85"/>
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
@@ -28612,7 +28902,7 @@
       <c r="G5" s="11"/>
     </row>
     <row r="6" spans="1:7" ht="48" x14ac:dyDescent="0.45">
-      <c r="A6" s="81"/>
+      <c r="A6" s="85"/>
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
@@ -28631,7 +28921,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="82"/>
+      <c r="A7" s="86"/>
       <c r="B7" s="13" t="s">
         <v>15</v>
       </c>
@@ -28648,7 +28938,7 @@
       <c r="G7" s="15"/>
     </row>
     <row r="8" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="83" t="s">
+      <c r="A8" s="87" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="7" t="s">
@@ -28669,7 +28959,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A9" s="84"/>
+      <c r="A9" s="88"/>
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -28686,7 +28976,7 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A10" s="84"/>
+      <c r="A10" s="88"/>
       <c r="B10" s="4" t="s">
         <v>4</v>
       </c>
@@ -28703,7 +28993,7 @@
       <c r="G10" s="11"/>
     </row>
     <row r="11" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="84"/>
+      <c r="A11" s="88"/>
       <c r="B11" s="4" t="s">
         <v>7</v>
       </c>
@@ -28718,7 +29008,7 @@
       <c r="G11" s="11"/>
     </row>
     <row r="12" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="85"/>
+      <c r="A12" s="89"/>
       <c r="B12" s="16" t="s">
         <v>8</v>
       </c>
@@ -28735,7 +29025,7 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A13" s="86" t="s">
+      <c r="A13" s="90" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="7" t="s">
@@ -28756,7 +29046,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="64.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="87"/>
+      <c r="A14" s="91"/>
       <c r="B14" s="4" t="s">
         <v>10</v>
       </c>
@@ -28773,7 +29063,7 @@
       <c r="G14" s="11"/>
     </row>
     <row r="15" spans="1:7" ht="64" x14ac:dyDescent="0.45">
-      <c r="A15" s="87"/>
+      <c r="A15" s="91"/>
       <c r="B15" s="4" t="s">
         <v>218</v>
       </c>
@@ -28794,7 +29084,7 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A16" s="88"/>
+      <c r="A16" s="92"/>
       <c r="B16" s="16" t="s">
         <v>11</v>
       </c>
@@ -28836,9 +29126,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A1" s="110"/>
-      <c r="B1" s="110" t="s">
-        <v>453</v>
+      <c r="A1" s="76"/>
+      <c r="B1" s="76" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.45">
@@ -28947,14 +29237,14 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A5" s="96" t="s">
+      <c r="A5" s="100" t="s">
         <v>273</v>
       </c>
-      <c r="B5" s="96"/>
-      <c r="C5" s="96"/>
+      <c r="B5" s="100"/>
+      <c r="C5" s="100"/>
     </row>
     <row r="6" spans="1:4" ht="32" x14ac:dyDescent="0.45">
-      <c r="A6" s="98" t="s">
+      <c r="A6" s="102" t="s">
         <v>204</v>
       </c>
       <c r="B6" s="47" t="s">
@@ -28965,7 +29255,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="32" x14ac:dyDescent="0.45">
-      <c r="A7" s="99"/>
+      <c r="A7" s="103"/>
       <c r="B7" s="47" t="s">
         <v>292</v>
       </c>
@@ -28974,7 +29264,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" ht="32" x14ac:dyDescent="0.45">
-      <c r="A8" s="99"/>
+      <c r="A8" s="103"/>
       <c r="B8" s="47" t="s">
         <v>295</v>
       </c>
@@ -28983,7 +29273,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A9" s="99"/>
+      <c r="A9" s="103"/>
       <c r="B9" s="47" t="s">
         <v>303</v>
       </c>
@@ -28992,7 +29282,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A10" s="100"/>
+      <c r="A10" s="104"/>
       <c r="B10" s="47" t="s">
         <v>297</v>
       </c>
@@ -29015,18 +29305,18 @@
       <c r="C12" s="49"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A13" s="90" t="s">
+      <c r="A13" s="94" t="s">
         <v>304</v>
       </c>
-      <c r="B13" s="91"/>
-      <c r="C13" s="92"/>
+      <c r="B13" s="95"/>
+      <c r="C13" s="96"/>
     </row>
     <row r="14" spans="1:4" ht="52" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="101" t="s">
+      <c r="A14" s="105" t="s">
         <v>230</v>
       </c>
-      <c r="B14" s="102"/>
-      <c r="C14" s="103"/>
+      <c r="B14" s="106"/>
+      <c r="C14" s="107"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="49"/>
@@ -29034,112 +29324,112 @@
       <c r="D19" s="49"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A31" s="96" t="s">
+      <c r="A31" s="100" t="s">
         <v>274</v>
       </c>
-      <c r="B31" s="96"/>
-      <c r="C31" s="96"/>
+      <c r="B31" s="100"/>
+      <c r="C31" s="100"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A32" s="93" t="s">
+      <c r="A32" s="97" t="s">
         <v>318</v>
       </c>
-      <c r="B32" s="94"/>
-      <c r="C32" s="95"/>
+      <c r="B32" s="98"/>
+      <c r="C32" s="99"/>
     </row>
     <row r="33" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="89" t="s">
+      <c r="A33" s="93" t="s">
         <v>231</v>
       </c>
       <c r="B33" s="50" t="s">
         <v>208</v>
       </c>
-      <c r="C33" s="97" t="s">
+      <c r="C33" s="101" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A34" s="89"/>
+      <c r="A34" s="93"/>
       <c r="B34" s="50" t="s">
         <v>209</v>
       </c>
-      <c r="C34" s="97"/>
+      <c r="C34" s="101"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A35" s="89"/>
+      <c r="A35" s="93"/>
       <c r="B35" s="50" t="s">
         <v>210</v>
       </c>
-      <c r="C35" s="97"/>
+      <c r="C35" s="101"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A36" s="89"/>
+      <c r="A36" s="93"/>
       <c r="B36" s="50" t="s">
         <v>211</v>
       </c>
-      <c r="C36" s="97"/>
+      <c r="C36" s="101"/>
     </row>
     <row r="37" spans="1:5" ht="32" x14ac:dyDescent="0.45">
-      <c r="A37" s="89"/>
+      <c r="A37" s="93"/>
       <c r="B37" s="48" t="s">
         <v>212</v>
       </c>
-      <c r="C37" s="97"/>
+      <c r="C37" s="101"/>
     </row>
     <row r="38" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="89" t="s">
+      <c r="A38" s="93" t="s">
         <v>232</v>
       </c>
       <c r="B38" s="50" t="s">
         <v>213</v>
       </c>
-      <c r="C38" s="97" t="s">
+      <c r="C38" s="101" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A39" s="89"/>
+      <c r="A39" s="93"/>
       <c r="B39" s="50" t="s">
         <v>214</v>
       </c>
-      <c r="C39" s="97"/>
+      <c r="C39" s="101"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A40" s="89"/>
+      <c r="A40" s="93"/>
       <c r="B40" s="50" t="s">
         <v>215</v>
       </c>
-      <c r="C40" s="97"/>
+      <c r="C40" s="101"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A42" s="90" t="s">
+      <c r="A42" s="94" t="s">
         <v>272</v>
       </c>
-      <c r="B42" s="91"/>
-      <c r="C42" s="92"/>
+      <c r="B42" s="95"/>
+      <c r="C42" s="96"/>
     </row>
     <row r="43" spans="1:5" ht="53" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A43" s="89" t="s">
+      <c r="A43" s="93" t="s">
         <v>217</v>
       </c>
-      <c r="B43" s="89"/>
-      <c r="C43" s="89"/>
+      <c r="B43" s="93"/>
+      <c r="C43" s="93"/>
     </row>
     <row r="44" spans="1:5" ht="50.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A44" s="89" t="s">
+      <c r="A44" s="93" t="s">
         <v>317</v>
       </c>
-      <c r="B44" s="89"/>
-      <c r="C44" s="89"/>
+      <c r="B44" s="93"/>
+      <c r="C44" s="93"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A46" s="96" t="s">
+      <c r="A46" s="100" t="s">
         <v>271</v>
       </c>
-      <c r="B46" s="96"/>
-      <c r="C46" s="96"/>
-      <c r="D46" s="96"/>
-      <c r="E46" s="96"/>
+      <c r="B46" s="100"/>
+      <c r="C46" s="100"/>
+      <c r="D46" s="100"/>
+      <c r="E46" s="100"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" s="44" t="s">
@@ -29325,11 +29615,11 @@
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A59" s="105" t="s">
+      <c r="A59" s="109" t="s">
         <v>275</v>
       </c>
-      <c r="B59" s="106"/>
-      <c r="C59" s="107"/>
+      <c r="B59" s="110"/>
+      <c r="C59" s="111"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" s="53" t="s">
@@ -29387,84 +29677,84 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A66" s="96" t="s">
+      <c r="A66" s="100" t="s">
         <v>291</v>
       </c>
-      <c r="B66" s="96"/>
-      <c r="C66" s="96"/>
-      <c r="D66" s="96"/>
+      <c r="B66" s="100"/>
+      <c r="C66" s="100"/>
+      <c r="D66" s="100"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A67" s="104" t="s">
+      <c r="A67" s="108" t="s">
         <v>262</v>
       </c>
-      <c r="B67" s="104"/>
-      <c r="C67" s="104"/>
-      <c r="D67" s="104"/>
+      <c r="B67" s="108"/>
+      <c r="C67" s="108"/>
+      <c r="D67" s="108"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A68" s="104" t="s">
+      <c r="A68" s="108" t="s">
         <v>263</v>
       </c>
-      <c r="B68" s="104"/>
-      <c r="C68" s="104"/>
-      <c r="D68" s="104"/>
+      <c r="B68" s="108"/>
+      <c r="C68" s="108"/>
+      <c r="D68" s="108"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A69" s="104" t="s">
+      <c r="A69" s="108" t="s">
         <v>264</v>
       </c>
-      <c r="B69" s="104"/>
-      <c r="C69" s="104"/>
-      <c r="D69" s="104"/>
+      <c r="B69" s="108"/>
+      <c r="C69" s="108"/>
+      <c r="D69" s="108"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A70" s="104" t="s">
+      <c r="A70" s="108" t="s">
         <v>265</v>
       </c>
-      <c r="B70" s="104"/>
-      <c r="C70" s="104"/>
-      <c r="D70" s="104"/>
+      <c r="B70" s="108"/>
+      <c r="C70" s="108"/>
+      <c r="D70" s="108"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A71" s="104" t="s">
+      <c r="A71" s="108" t="s">
         <v>266</v>
       </c>
-      <c r="B71" s="104"/>
-      <c r="C71" s="104"/>
-      <c r="D71" s="104"/>
+      <c r="B71" s="108"/>
+      <c r="C71" s="108"/>
+      <c r="D71" s="108"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A72" s="104" t="s">
+      <c r="A72" s="108" t="s">
         <v>267</v>
       </c>
-      <c r="B72" s="104"/>
-      <c r="C72" s="104"/>
-      <c r="D72" s="104"/>
+      <c r="B72" s="108"/>
+      <c r="C72" s="108"/>
+      <c r="D72" s="108"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A73" s="104" t="s">
+      <c r="A73" s="108" t="s">
         <v>268</v>
       </c>
-      <c r="B73" s="104"/>
-      <c r="C73" s="104"/>
-      <c r="D73" s="104"/>
+      <c r="B73" s="108"/>
+      <c r="C73" s="108"/>
+      <c r="D73" s="108"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A74" s="104" t="s">
+      <c r="A74" s="108" t="s">
         <v>269</v>
       </c>
-      <c r="B74" s="104"/>
-      <c r="C74" s="104"/>
-      <c r="D74" s="104"/>
+      <c r="B74" s="108"/>
+      <c r="C74" s="108"/>
+      <c r="D74" s="108"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A75" s="104" t="s">
+      <c r="A75" s="108" t="s">
         <v>270</v>
       </c>
-      <c r="B75" s="104"/>
-      <c r="C75" s="104"/>
-      <c r="D75" s="104"/>
+      <c r="B75" s="108"/>
+      <c r="C75" s="108"/>
+      <c r="D75" s="108"/>
     </row>
   </sheetData>
   <mergeCells count="25">
@@ -29533,10 +29823,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A1" s="108" t="s">
+      <c r="A1" s="112" t="s">
         <v>335</v>
       </c>
-      <c r="B1" s="109"/>
+      <c r="B1" s="113"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="60" t="s">
@@ -29953,10 +30243,10 @@
         <v>399</v>
       </c>
       <c r="G1" s="40" t="s">
+        <v>422</v>
+      </c>
+      <c r="H1" s="40" t="s">
         <v>423</v>
-      </c>
-      <c r="H1" s="40" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="256" x14ac:dyDescent="0.45">
@@ -29979,10 +30269,10 @@
         <v>409</v>
       </c>
       <c r="G2" s="43" t="s">
+        <v>424</v>
+      </c>
+      <c r="H2" s="43" t="s">
         <v>425</v>
-      </c>
-      <c r="H2" s="43" t="s">
-        <v>426</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="208" x14ac:dyDescent="0.45">
@@ -30005,10 +30295,10 @@
         <v>410</v>
       </c>
       <c r="G3" s="43" t="s">
+        <v>426</v>
+      </c>
+      <c r="H3" s="43" t="s">
         <v>427</v>
-      </c>
-      <c r="H3" s="43" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="272" x14ac:dyDescent="0.45">
@@ -30031,10 +30321,10 @@
         <v>411</v>
       </c>
       <c r="G4" s="43" t="s">
+        <v>428</v>
+      </c>
+      <c r="H4" s="43" t="s">
         <v>429</v>
-      </c>
-      <c r="H4" s="43" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="192" x14ac:dyDescent="0.45">
@@ -30057,10 +30347,10 @@
         <v>412</v>
       </c>
       <c r="G5" s="43" t="s">
+        <v>430</v>
+      </c>
+      <c r="H5" s="43" t="s">
         <v>431</v>
-      </c>
-      <c r="H5" s="43" t="s">
-        <v>432</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="192" x14ac:dyDescent="0.45">
@@ -30083,10 +30373,10 @@
         <v>413</v>
       </c>
       <c r="G6" s="43" t="s">
+        <v>432</v>
+      </c>
+      <c r="H6" s="43" t="s">
         <v>433</v>
-      </c>
-      <c r="H6" s="43" t="s">
-        <v>434</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="224" x14ac:dyDescent="0.45">
@@ -30109,10 +30399,10 @@
         <v>414</v>
       </c>
       <c r="G7" s="43" t="s">
+        <v>434</v>
+      </c>
+      <c r="H7" s="43" t="s">
         <v>435</v>
-      </c>
-      <c r="H7" s="43" t="s">
-        <v>436</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="192" x14ac:dyDescent="0.45">
@@ -30135,10 +30425,10 @@
         <v>415</v>
       </c>
       <c r="G8" s="43" t="s">
+        <v>436</v>
+      </c>
+      <c r="H8" s="43" t="s">
         <v>437</v>
-      </c>
-      <c r="H8" s="43" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="332.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -30161,10 +30451,10 @@
         <v>416</v>
       </c>
       <c r="G9" s="43" t="s">
+        <v>438</v>
+      </c>
+      <c r="H9" s="43" t="s">
         <v>439</v>
-      </c>
-      <c r="H9" s="43" t="s">
-        <v>440</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="272" x14ac:dyDescent="0.45">
@@ -30187,10 +30477,10 @@
         <v>417</v>
       </c>
       <c r="G10" s="43" t="s">
+        <v>440</v>
+      </c>
+      <c r="H10" s="43" t="s">
         <v>441</v>
-      </c>
-      <c r="H10" s="43" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="11" spans="1:8" ht="224" x14ac:dyDescent="0.45">
@@ -30213,10 +30503,10 @@
         <v>418</v>
       </c>
       <c r="G11" s="43" t="s">
+        <v>442</v>
+      </c>
+      <c r="H11" s="43" t="s">
         <v>443</v>
-      </c>
-      <c r="H11" s="43" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="12" spans="1:8" ht="306.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -30239,10 +30529,10 @@
         <v>419</v>
       </c>
       <c r="G12" s="43" t="s">
+        <v>444</v>
+      </c>
+      <c r="H12" s="43" t="s">
         <v>445</v>
-      </c>
-      <c r="H12" s="43" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="13" spans="1:8" ht="144" x14ac:dyDescent="0.45">
@@ -30261,10 +30551,10 @@
       <c r="E13" s="50"/>
       <c r="F13" s="50"/>
       <c r="G13" s="43" t="s">
+        <v>446</v>
+      </c>
+      <c r="H13" s="43" t="s">
         <v>447</v>
-      </c>
-      <c r="H13" s="43" t="s">
-        <v>448</v>
       </c>
     </row>
   </sheetData>

--- a/project_2/project2_project status(C2).xlsx
+++ b/project_2/project2_project status(C2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pyostry\workspace\aiffel\ai-data-bootcamp\Project_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FED89BBD-32A2-46A1-A3F4-7C4174C451CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2150866-98E6-4B3F-9623-947A4AC1BCB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" firstSheet="4" activeTab="9" xr2:uid="{5FF54064-7DDC-427B-93D7-EF78D75E5195}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="608" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="515">
   <si>
     <t>reward</t>
   </si>
@@ -2228,6 +2228,90 @@
     <t>세그먼트 전략을 짤 때 성별을 1차 분기 기준으로, 그 다음 연령/소득을 2차 분기로 사용하는 계층적 타겟팅 구조를 설계하는 게 효율적입니다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>최종 결론 및 의사결정 제안 (종합)</t>
+  </si>
+  <si>
+    <t>오퍼 설계
+(보상·난이도·기간·유형)</t>
+  </si>
+  <si>
+    <t>재고소진 목적에서는 완료율이 낮은 BOGO가 오히려 완료 1건당 소진 물량이 더 커서(추정 약 2배) 물량 처리 효율이 더 높음. 반면 보상액·목표금액(difficulty)·유효기간을 단독으로 조정해 완료율을 바꾸려는 접근은 근거가 약함 — 이 세 변수가 오퍼 유형과 뒤섞여 있어 순수 효과 분리가 불가능하고(완전교차설계 아님), 발송 빈도 제한도 실질적 효과가 없었음.</t>
+  </si>
+  <si>
+    <t>① 오퍼 목적에 따라 유형 분리 적용: 재고소진이면 BOGO, 완료율/전환 극대화면 discount 우선 검토
+② 보상·목표금액·유효기간 일괄 조정 금지 — 오퍼 유형·채널을 고정한 채 해당 변수만 다르게 배정하는 A/B 테스트 선행
+③ 발송 빈도 제한 정책은 도입하지 않음(현행 유지)</t>
+  </si>
+  <si>
+    <t>1, 3, 4, 5, 6</t>
+  </si>
+  <si>
+    <t>채널 전략</t>
+  </si>
+  <si>
+    <t>Mobile·Social이 포함된 채널 조합일수록 열람률이 뚜렷하게 높음. "고령층이 Web/Email 채널에 약하다"는 기존 통념은 데이터로 뒤집혔고, 오히려 18-30세 청년층이 Web/Email 위주 채널에 가장 취약한 것으로 확인됨.</t>
+  </si>
+  <si>
+    <t>① 신규 오퍼는 Mobile·Social 포함 조합을 기본값으로 설계
+② "고령층 채널 개선" 가정은 폐기하고, 청년층 대상 발송을 Web/Email 위주에서 Mobile/Social 중심으로 전환하는 것을 최우선 실행 항목으로 추진
+③ 통념을 뒤집는 결과이므로 다른 기간 데이터로 재현 검증(replication) 권장</t>
+  </si>
+  <si>
+    <t>2, 9, 10</t>
+  </si>
+  <si>
+    <t>고객 세그먼트 타겟팅
+(성별·소득·연령)</t>
+  </si>
+  <si>
+    <t>성별 효과가 세 프로필 변수 중 가장 강하고 독립적(오퍼 구성을 통제해도 유지) — 특히 남성 고객은 BOGO 유형에서 완료율이 두드러지게 낮음. 소득은 완료율에 유의한 양의 주효과가 있고, 보상 금액에 대한 민감도가 소득이 높을수록 낮아지는 패턴이 두 차례 검증에서 안정적으로 재현됨. 연령이 완료율에 미치는 실질적 영향은 거의 없음.</t>
+  </si>
+  <si>
+    <t>① 성별을 1차 타겟팅 기준으로 우선 적용 — 남성 고객에게는 BOGO 대신 discount 위주 오퍼를 배정하는 소규모 파일럿부터 시작
+② 소득 기반 보상 차등(저소득층엔 보상 강조, 고소득층엔 보상 외 혜택 강조)도 같은 파일럿 범위에서 함께 테스트
+③ 연령 기반 차등 정책은 근거가 약해 도입하지 않음
+④ 파일럿 검증 후 단계적 확대 — 전사 즉시 적용은 보류</t>
+  </si>
+  <si>
+    <t>7, 8, 9, 11, 12</t>
+  </si>
+  <si>
+    <t>데이터 한계 →
+후속 보완 과제</t>
+  </si>
+  <si>
+    <t>카페인 민감도/메뉴 선호, 오퍼 없이도 일어나는 평소 구매(true lift 미측정), 알림 수신 동의 여부 3가지는 현재 데이터에 기록 자체가 없어 검증이 불가능했음.</t>
+  </si>
+  <si>
+    <t>① 고객 설문·CRM에 카페인 민감도, 선호 메뉴 항목 추가
+② 결제 기록에 offer_id/쿠폰 식별자를 연결해 오퍼-실구매 매칭 체계 구축
+③ 앱 푸시 허용 여부 및 도달·클릭 로그 수집 체계 마련
+④ 위 데이터 확보 후 다음 분석 주기에 재검증</t>
+  </si>
+  <si>
+    <t>13, 14, 15</t>
+  </si>
+  <si>
+    <t>우선순위</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>주제</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>핵심 결론(통합)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>의사결정 제안(실행안)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>근거 가설(No.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -2237,7 +2321,7 @@
     <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="177" formatCode="[$-412]yyyy&quot;년&quot;\ m&quot;월&quot;\ d&quot;일&quot;\ dddd\ h&quot;시&quot;\ mm&quot;분&quot;"/>
   </numFmts>
-  <fonts count="29" x14ac:knownFonts="1">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2466,6 +2550,19 @@
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
   <fills count="7">
@@ -2808,7 +2905,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="124">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3047,6 +3144,12 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3086,6 +3189,21 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3105,9 +3223,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3131,35 +3246,33 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -11936,8 +12049,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="173001" y="1826087"/>
-          <a:ext cx="2123975" cy="452612"/>
+          <a:off x="220981" y="1805623"/>
+          <a:ext cx="2100172" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -12036,8 +12149,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="186258" y="1839344"/>
-        <a:ext cx="2097461" cy="426098"/>
+        <a:off x="234089" y="1818731"/>
+        <a:ext cx="2073956" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{ED5992BD-91A0-44DC-B026-C230E027754F}">
@@ -12047,8 +12160,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="16874489">
-          <a:off x="1549321" y="1134321"/>
-          <a:ext cx="1857401" cy="14378"/>
+          <a:off x="1581876" y="1121529"/>
+          <a:ext cx="1836586" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -12062,7 +12175,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1857401" y="7189"/>
+                <a:pt x="1836586" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -12121,8 +12234,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2431586" y="1095075"/>
-        <a:ext cx="92870" cy="92870"/>
+        <a:off x="2454255" y="1082803"/>
+        <a:ext cx="91829" cy="91829"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{EB7188F2-1357-4748-A44C-AB5D4A48F40F}">
@@ -12132,8 +12245,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2659066" y="4321"/>
-          <a:ext cx="1092733" cy="452612"/>
+          <a:off x="2679186" y="4273"/>
+          <a:ext cx="1080487" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -12208,8 +12321,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2672323" y="17578"/>
-        <a:ext cx="1066219" cy="426098"/>
+        <a:off x="2692294" y="17381"/>
+        <a:ext cx="1054271" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7531319A-E0E5-4CB4-9F35-33254694A0D7}">
@@ -12219,8 +12332,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3751800" y="223438"/>
-          <a:ext cx="356477" cy="14378"/>
+          <a:off x="3759673" y="220854"/>
+          <a:ext cx="352482" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -12234,7 +12347,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="356477" y="7189"/>
+                <a:pt x="352482" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -12293,8 +12406,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3921127" y="221715"/>
-        <a:ext cx="17823" cy="17823"/>
+        <a:off x="3927103" y="219231"/>
+        <a:ext cx="17624" cy="17624"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{8F385C2E-83EB-470A-8A65-12C51C60EB27}">
@@ -12304,8 +12417,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4108278" y="4321"/>
-          <a:ext cx="4735188" cy="452612"/>
+          <a:off x="4112156" y="4273"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -12404,8 +12517,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4121535" y="17578"/>
-        <a:ext cx="4708674" cy="426098"/>
+        <a:off x="4125264" y="17381"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{71327523-F24D-4A9E-8CA7-7C0E6A96618A}">
@@ -12415,8 +12528,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17132988">
-          <a:off x="1802671" y="1394574"/>
-          <a:ext cx="1350699" cy="14378"/>
+          <a:off x="1832388" y="1378865"/>
+          <a:ext cx="1335563" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -12430,7 +12543,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1350699" y="7189"/>
+                <a:pt x="1335563" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -12489,8 +12602,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2444254" y="1367995"/>
-        <a:ext cx="67534" cy="67534"/>
+        <a:off x="2466780" y="1352664"/>
+        <a:ext cx="66778" cy="66778"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{08B2E005-DF35-41E7-A396-CA02C3B8D0A4}">
@@ -12500,8 +12613,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2659066" y="524826"/>
-          <a:ext cx="1092733" cy="452612"/>
+          <a:off x="2679186" y="518944"/>
+          <a:ext cx="1080487" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -12576,8 +12689,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2672323" y="538083"/>
-        <a:ext cx="1066219" cy="426098"/>
+        <a:off x="2692294" y="532052"/>
+        <a:ext cx="1054271" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E113C6B3-F5C2-41D9-9727-BB430EAD3818}">
@@ -12587,8 +12700,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3751800" y="743943"/>
-          <a:ext cx="362090" cy="14378"/>
+          <a:off x="3759673" y="735525"/>
+          <a:ext cx="358032" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -12602,7 +12715,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="362090" y="7189"/>
+                <a:pt x="358032" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -12661,8 +12774,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3923793" y="742080"/>
-        <a:ext cx="18104" cy="18104"/>
+        <a:off x="3929739" y="733763"/>
+        <a:ext cx="17901" cy="17901"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{53F03F28-ED40-4762-8125-AFFEEA792A72}">
@@ -12672,8 +12785,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4113890" y="524826"/>
-          <a:ext cx="4735188" cy="452612"/>
+          <a:off x="4117706" y="518944"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -12796,8 +12909,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4127147" y="538083"/>
-        <a:ext cx="4708674" cy="426098"/>
+        <a:off x="4130814" y="532052"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{806C8330-1E37-41AD-AEEE-3552A4162510}">
@@ -12807,8 +12920,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17692822">
-          <a:off x="2047704" y="1654826"/>
-          <a:ext cx="860633" cy="14378"/>
+          <a:off x="2074675" y="1636200"/>
+          <a:ext cx="850988" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -12822,7 +12935,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="860633" y="7189"/>
+                <a:pt x="850988" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -12881,8 +12994,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2456505" y="1640499"/>
-        <a:ext cx="43031" cy="43031"/>
+        <a:off x="2478895" y="1622115"/>
+        <a:ext cx="42549" cy="42549"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{3BC1DAB2-4FEF-42C9-A10F-0690E2903498}">
@@ -12892,8 +13005,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2659066" y="1045330"/>
-          <a:ext cx="1092733" cy="452612"/>
+          <a:off x="2679186" y="1033615"/>
+          <a:ext cx="1080487" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -12984,8 +13097,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2672323" y="1058587"/>
-        <a:ext cx="1066219" cy="426098"/>
+        <a:off x="2692294" y="1046723"/>
+        <a:ext cx="1054271" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6BFD1C16-8154-4C15-AF72-E53B38C4A146}">
@@ -12995,8 +13108,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3751800" y="1264447"/>
-          <a:ext cx="362090" cy="14378"/>
+          <a:off x="3759673" y="1250197"/>
+          <a:ext cx="358032" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -13010,7 +13123,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="362090" y="7189"/>
+                <a:pt x="358032" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -13069,8 +13182,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3923793" y="1262584"/>
-        <a:ext cx="18104" cy="18104"/>
+        <a:off x="3929739" y="1248435"/>
+        <a:ext cx="17901" cy="17901"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1A251137-9CB6-43D7-B47D-0D220C30894C}">
@@ -13080,8 +13193,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4113890" y="1045330"/>
-          <a:ext cx="4735188" cy="452612"/>
+          <a:off x="4117706" y="1033615"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -13204,8 +13317,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4127147" y="1058587"/>
-        <a:ext cx="4708674" cy="426098"/>
+        <a:off x="4130814" y="1046723"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{227E0FEF-1368-4562-AD55-940C6A450E91}">
@@ -13215,8 +13328,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="3310531">
-          <a:off x="2160990" y="2305456"/>
-          <a:ext cx="634061" cy="14378"/>
+          <a:off x="2186691" y="2279540"/>
+          <a:ext cx="626956" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -13230,7 +13343,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="634061" y="7189"/>
+                <a:pt x="626956" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -13289,8 +13402,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2462170" y="2296794"/>
-        <a:ext cx="31703" cy="31703"/>
+        <a:off x="2484496" y="2271055"/>
+        <a:ext cx="31347" cy="31347"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{146FB508-948A-484E-B54F-2A63CE5492FA}">
@@ -13300,8 +13413,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2659066" y="2346591"/>
-          <a:ext cx="1092733" cy="452612"/>
+          <a:off x="2679186" y="2320294"/>
+          <a:ext cx="1080487" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -13376,8 +13489,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2672323" y="2359848"/>
-        <a:ext cx="1066219" cy="426098"/>
+        <a:off x="2692294" y="2333402"/>
+        <a:ext cx="1054271" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1583A4D8-C48C-400A-B5A1-D8E8188A1E57}">
@@ -13387,8 +13500,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17692822">
-          <a:off x="3502528" y="2175330"/>
-          <a:ext cx="860633" cy="14378"/>
+          <a:off x="3513195" y="2150872"/>
+          <a:ext cx="850988" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -13402,7 +13515,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="860633" y="7189"/>
+                <a:pt x="850988" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -13461,8 +13574,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3911329" y="2161003"/>
-        <a:ext cx="43031" cy="43031"/>
+        <a:off x="3917415" y="2136786"/>
+        <a:ext cx="42549" cy="42549"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{985FE1E2-4CA8-4AC7-A474-DEECC9A2BB80}">
@@ -13472,8 +13585,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4113890" y="1565835"/>
-          <a:ext cx="4735188" cy="452612"/>
+          <a:off x="4117706" y="1548287"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -13564,8 +13677,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4127147" y="1579092"/>
-        <a:ext cx="4708674" cy="426098"/>
+        <a:off x="4130814" y="1561395"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{16F44D37-2601-482A-9095-0B3E8E10E520}">
@@ -13575,8 +13688,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19457599">
-          <a:off x="3709887" y="2435583"/>
-          <a:ext cx="445915" cy="14378"/>
+          <a:off x="3718230" y="2408207"/>
+          <a:ext cx="440918" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -13590,7 +13703,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="445915" y="7189"/>
+                <a:pt x="440918" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -13649,8 +13762,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3921697" y="2431624"/>
-        <a:ext cx="22295" cy="22295"/>
+        <a:off x="3927667" y="2404373"/>
+        <a:ext cx="22045" cy="22045"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{2D542640-C237-42B5-8470-73084719F8F3}">
@@ -13660,8 +13773,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4113890" y="2086339"/>
-          <a:ext cx="4735188" cy="452612"/>
+          <a:off x="4117706" y="2062958"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -13752,8 +13865,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4127147" y="2099596"/>
-        <a:ext cx="4708674" cy="426098"/>
+        <a:off x="4130814" y="2076066"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9A75AB13-86A0-459A-8B2B-E8037D74B447}">
@@ -13763,8 +13876,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2142401">
-          <a:off x="3709887" y="2695835"/>
-          <a:ext cx="445915" cy="14378"/>
+          <a:off x="3718230" y="2665543"/>
+          <a:ext cx="440918" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -13778,7 +13891,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="445915" y="7189"/>
+                <a:pt x="440918" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -13837,8 +13950,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3921697" y="2691876"/>
-        <a:ext cx="22295" cy="22295"/>
+        <a:off x="3927667" y="2661709"/>
+        <a:ext cx="22045" cy="22045"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{106C3051-36E0-4DB2-B006-BD51244834C6}">
@@ -13848,8 +13961,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4113890" y="2606844"/>
-          <a:ext cx="4735188" cy="452612"/>
+          <a:off x="4117706" y="2577630"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -13940,8 +14053,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4127147" y="2620101"/>
-        <a:ext cx="4708674" cy="426098"/>
+        <a:off x="4130814" y="2590738"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6562E267-52DD-4DC6-81E6-A0E9307367D6}">
@@ -13951,8 +14064,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="3907178">
-          <a:off x="3502528" y="2956087"/>
-          <a:ext cx="860633" cy="14378"/>
+          <a:off x="3513195" y="2922879"/>
+          <a:ext cx="850988" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -13966,7 +14079,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="860633" y="7189"/>
+                <a:pt x="850988" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -14025,8 +14138,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3911329" y="2941760"/>
-        <a:ext cx="43031" cy="43031"/>
+        <a:off x="3917415" y="2908793"/>
+        <a:ext cx="42549" cy="42549"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{220D319D-36C0-42A0-A946-F197C4269C14}">
@@ -14036,8 +14149,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4113890" y="3127348"/>
-          <a:ext cx="4735188" cy="452612"/>
+          <a:off x="4117706" y="3092301"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -14128,8 +14241,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4127147" y="3140605"/>
-        <a:ext cx="4708674" cy="426098"/>
+        <a:off x="4130814" y="3105409"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4332858F-88A7-466E-8722-8833A7B96598}">
@@ -14139,8 +14252,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="4725511">
-          <a:off x="1549321" y="2956087"/>
-          <a:ext cx="1857401" cy="14378"/>
+          <a:off x="1581876" y="2922879"/>
+          <a:ext cx="1836586" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -14154,7 +14267,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1857401" y="7189"/>
+                <a:pt x="1836586" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -14209,8 +14322,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2431586" y="2916841"/>
-        <a:ext cx="92870" cy="92870"/>
+        <a:off x="2454255" y="2884153"/>
+        <a:ext cx="91829" cy="91829"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1479FCFA-85A4-438D-B5D0-346DFAD5924D}">
@@ -14220,8 +14333,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2659066" y="3647853"/>
-          <a:ext cx="1092733" cy="452612"/>
+          <a:off x="2679186" y="3606973"/>
+          <a:ext cx="1080487" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -14296,8 +14409,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2672323" y="3661110"/>
-        <a:ext cx="1066219" cy="426098"/>
+        <a:off x="2692294" y="3620081"/>
+        <a:ext cx="1054271" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E6D0412B-4D85-432B-BE35-F277BFD00B03}">
@@ -14307,8 +14420,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3751800" y="3866970"/>
-          <a:ext cx="362090" cy="14378"/>
+          <a:off x="3759673" y="3823554"/>
+          <a:ext cx="358032" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -14322,7 +14435,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="362090" y="7189"/>
+                <a:pt x="358032" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -14377,8 +14490,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3923793" y="3865107"/>
-        <a:ext cx="18104" cy="18104"/>
+        <a:off x="3929739" y="3821792"/>
+        <a:ext cx="17901" cy="17901"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{CE9AFD94-4037-4F8B-B49B-020818B5CBB5}">
@@ -14388,8 +14501,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4113890" y="3647853"/>
-          <a:ext cx="4735188" cy="452612"/>
+          <a:off x="4117706" y="3606973"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -14496,8 +14609,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4127147" y="3661110"/>
-        <a:ext cx="4708674" cy="426098"/>
+        <a:off x="4130814" y="3620081"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B460AB31-448C-42B6-9C6B-D3CF5013B4F6}">
@@ -14507,8 +14620,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="39236" y="4688862"/>
-          <a:ext cx="1821222" cy="452612"/>
+          <a:off x="88714" y="4636316"/>
+          <a:ext cx="1800813" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -14633,8 +14746,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="52493" y="4702119"/>
-        <a:ext cx="1794708" cy="426098"/>
+        <a:off x="101822" y="4649424"/>
+        <a:ext cx="1774597" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{C120D3E5-D1A3-4DC1-848B-C37D9DDE2012}">
@@ -14644,8 +14757,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="18752467">
-          <a:off x="1746056" y="4647727"/>
-          <a:ext cx="706446" cy="14378"/>
+          <a:off x="1776407" y="4595561"/>
+          <a:ext cx="698529" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -14659,7 +14772,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="706446" y="7189"/>
+                <a:pt x="698529" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -14714,8 +14827,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2081618" y="4637255"/>
-        <a:ext cx="35322" cy="35322"/>
+        <a:off x="2108209" y="4585287"/>
+        <a:ext cx="34926" cy="34926"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6F01F0AA-74B9-49DB-A456-B8979039EB51}">
@@ -14725,8 +14838,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2338101" y="4168357"/>
-          <a:ext cx="1092733" cy="452612"/>
+          <a:off x="2361817" y="4121644"/>
+          <a:ext cx="1080487" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -14799,8 +14912,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2351358" y="4181614"/>
-        <a:ext cx="1066219" cy="426098"/>
+        <a:off x="2374925" y="4134752"/>
+        <a:ext cx="1054271" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{F5E69F9A-2631-4A2D-BC76-B4BD9B08D019}">
@@ -14810,8 +14923,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3430834" y="4387475"/>
-          <a:ext cx="368146" cy="14378"/>
+          <a:off x="3442305" y="4338225"/>
+          <a:ext cx="364020" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -14825,7 +14938,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="368146" y="7189"/>
+                <a:pt x="364020" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -14880,8 +14993,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3605704" y="4385460"/>
-        <a:ext cx="18407" cy="18407"/>
+        <a:off x="3615214" y="4336314"/>
+        <a:ext cx="18201" cy="18201"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{69EDA0B0-D39D-4C93-8B8D-10889C581D9E}">
@@ -14891,8 +15004,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3798980" y="4168357"/>
-          <a:ext cx="4735188" cy="452612"/>
+          <a:off x="3806325" y="4121644"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -14965,8 +15078,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3812237" y="4181614"/>
-        <a:ext cx="4708674" cy="426098"/>
+        <a:off x="3819433" y="4134752"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{AC23C890-5E27-4DC3-9BF7-2C50218200D9}">
@@ -14976,8 +15089,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="1860458" y="4907979"/>
-          <a:ext cx="477642" cy="14378"/>
+          <a:off x="1889527" y="4852897"/>
+          <a:ext cx="472289" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -14991,7 +15104,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="477642" y="7189"/>
+                <a:pt x="472289" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -15046,8 +15159,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2087338" y="4903227"/>
-        <a:ext cx="23882" cy="23882"/>
+        <a:off x="2113865" y="4848279"/>
+        <a:ext cx="23614" cy="23614"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B4CF3050-E538-4710-99C5-FB5B2F28D116}">
@@ -15057,8 +15170,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2338101" y="4688862"/>
-          <a:ext cx="1092733" cy="452612"/>
+          <a:off x="2361817" y="4636316"/>
+          <a:ext cx="1080487" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -15131,8 +15244,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2351358" y="4702119"/>
-        <a:ext cx="1066219" cy="426098"/>
+        <a:off x="2374925" y="4649424"/>
+        <a:ext cx="1054271" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{55492AE0-989E-4368-96E6-8609B6786079}">
@@ -15142,8 +15255,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3430834" y="4907979"/>
-          <a:ext cx="368146" cy="14378"/>
+          <a:off x="3442305" y="4852897"/>
+          <a:ext cx="364020" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -15157,7 +15270,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="368146" y="7189"/>
+                <a:pt x="364020" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -15212,8 +15325,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3605704" y="4905964"/>
-        <a:ext cx="18407" cy="18407"/>
+        <a:off x="3615214" y="4850985"/>
+        <a:ext cx="18201" cy="18201"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{99BD4B49-7654-4BFC-93A2-73715A94DAC0}">
@@ -15223,8 +15336,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3798980" y="4688862"/>
-          <a:ext cx="4735188" cy="452612"/>
+          <a:off x="3806325" y="4636316"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -15341,8 +15454,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3812237" y="4702119"/>
-        <a:ext cx="4708674" cy="426098"/>
+        <a:off x="3819433" y="4649424"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{48D36C81-0EEF-4879-868D-73109D1A61EF}">
@@ -15352,8 +15465,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2847533">
-          <a:off x="1746056" y="5168231"/>
-          <a:ext cx="706446" cy="14378"/>
+          <a:off x="1776407" y="5110232"/>
+          <a:ext cx="698529" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -15367,7 +15480,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="706446" y="7189"/>
+                <a:pt x="698529" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -15422,8 +15535,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2081618" y="5157759"/>
-        <a:ext cx="35322" cy="35322"/>
+        <a:off x="2108209" y="5099958"/>
+        <a:ext cx="34926" cy="34926"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E0C7A212-1F93-473A-8909-15A6780CBC2F}">
@@ -15433,8 +15546,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2338101" y="5209366"/>
-          <a:ext cx="1092733" cy="452612"/>
+          <a:off x="2361817" y="5150987"/>
+          <a:ext cx="1080487" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -15507,8 +15620,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2351358" y="5222623"/>
-        <a:ext cx="1066219" cy="426098"/>
+        <a:off x="2374925" y="5164095"/>
+        <a:ext cx="1054271" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4D54B04B-F98B-4577-8925-91ECEF877996}">
@@ -15518,8 +15631,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3430834" y="5428484"/>
-          <a:ext cx="380303" cy="14378"/>
+          <a:off x="3442305" y="5367568"/>
+          <a:ext cx="376041" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -15533,7 +15646,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="380303" y="7189"/>
+                <a:pt x="376041" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -15588,8 +15701,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3611478" y="5426165"/>
-        <a:ext cx="19015" cy="19015"/>
+        <a:off x="3620924" y="5365356"/>
+        <a:ext cx="18802" cy="18802"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{540CB623-D523-4AD6-BF5D-A946D7B052E6}">
@@ -15599,8 +15712,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3811137" y="5209366"/>
-          <a:ext cx="4735188" cy="452612"/>
+          <a:off x="3818346" y="5150987"/>
+          <a:ext cx="4682122" cy="447540"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -15718,8 +15831,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3824394" y="5222623"/>
-        <a:ext cx="4708674" cy="426098"/>
+        <a:off x="3831454" y="5164095"/>
+        <a:ext cx="4655906" cy="421324"/>
       </dsp:txXfrm>
     </dsp:sp>
   </dsp:spTree>
@@ -15741,8 +15854,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10440" y="3343938"/>
-          <a:ext cx="1173405" cy="360228"/>
+          <a:off x="9182" y="3307680"/>
+          <a:ext cx="1177681" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -15820,8 +15933,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="20991" y="3354489"/>
-        <a:ext cx="1152303" cy="339126"/>
+        <a:off x="19771" y="3318269"/>
+        <a:ext cx="1156503" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7667B88B-738E-4E27-80A6-15B1E3AED5F8}">
@@ -15831,8 +15944,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="16719080">
-          <a:off x="572123" y="2808170"/>
-          <a:ext cx="1440061" cy="8089"/>
+          <a:off x="572912" y="2769909"/>
+          <a:ext cx="1445308" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -15843,10 +15956,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1440061" y="4044"/>
+                <a:pt x="1445308" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -15905,8 +16018,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1256152" y="2776213"/>
-        <a:ext cx="72003" cy="72003"/>
+        <a:off x="1259433" y="2737887"/>
+        <a:ext cx="72265" cy="72265"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D9E30B0F-B6EE-4B8A-B3A5-5AD7E4CFBC12}">
@@ -15916,8 +16029,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="1400462" y="1920262"/>
-          <a:ext cx="1439393" cy="360228"/>
+          <a:off x="1404269" y="1878817"/>
+          <a:ext cx="1444638" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16008,8 +16121,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1411013" y="1930813"/>
-        <a:ext cx="1418291" cy="339126"/>
+        <a:off x="1414858" y="1889406"/>
+        <a:ext cx="1423460" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{ED5992BD-91A0-44DC-B026-C230E027754F}">
@@ -16019,8 +16132,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="16757427">
-          <a:off x="2277274" y="1434244"/>
-          <a:ext cx="1341777" cy="8089"/>
+          <a:off x="2284276" y="1390976"/>
+          <a:ext cx="1346666" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16031,10 +16144,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1341777" y="4044"/>
+                <a:pt x="1346666" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16093,8 +16206,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2914618" y="1404744"/>
-        <a:ext cx="67088" cy="67088"/>
+        <a:off x="2923942" y="1361420"/>
+        <a:ext cx="67333" cy="67333"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{EB7188F2-1357-4748-A44C-AB5D4A48F40F}">
@@ -16104,8 +16217,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3056471" y="596085"/>
-          <a:ext cx="1402222" cy="360228"/>
+          <a:off x="3066312" y="549815"/>
+          <a:ext cx="1407331" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16175,8 +16288,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3067022" y="606636"/>
-        <a:ext cx="1381120" cy="339126"/>
+        <a:off x="3076901" y="560404"/>
+        <a:ext cx="1386153" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7531319A-E0E5-4CB4-9F35-33254694A0D7}">
@@ -16186,8 +16299,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17860289">
-          <a:off x="4335717" y="568811"/>
-          <a:ext cx="459210" cy="8089"/>
+          <a:off x="4350219" y="522390"/>
+          <a:ext cx="460883" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16198,10 +16311,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="459210" y="4044"/>
+                <a:pt x="460883" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16260,8 +16373,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4553842" y="561375"/>
-        <a:ext cx="22960" cy="22960"/>
+        <a:off x="4569139" y="514979"/>
+        <a:ext cx="23044" cy="23044"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{8F385C2E-83EB-470A-8A65-12C51C60EB27}">
@@ -16271,8 +16384,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4671951" y="187807"/>
-          <a:ext cx="1769726" cy="363410"/>
+          <a:off x="4687678" y="140049"/>
+          <a:ext cx="1776175" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16342,8 +16455,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4682595" y="198451"/>
-        <a:ext cx="1748438" cy="342122"/>
+        <a:off x="4698361" y="150732"/>
+        <a:ext cx="1754809" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{8EC6EEF9-E6D8-4DE2-A6DD-BB50B40A5CF0}">
@@ -16353,8 +16466,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6441677" y="365467"/>
-          <a:ext cx="219972" cy="8089"/>
+          <a:off x="6463853" y="318305"/>
+          <a:ext cx="220774" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16365,10 +16478,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="219972" y="4044"/>
+                <a:pt x="220774" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16423,8 +16536,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6546165" y="364012"/>
-        <a:ext cx="10998" cy="10998"/>
+        <a:off x="6568721" y="316896"/>
+        <a:ext cx="11038" cy="11038"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{31CFEB2D-0887-4520-AF04-1E3C38912960}">
@@ -16434,8 +16547,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6661650" y="187807"/>
-          <a:ext cx="3156395" cy="363410"/>
+          <a:off x="6684628" y="140049"/>
+          <a:ext cx="3167897" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16521,8 +16634,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6672294" y="198451"/>
-        <a:ext cx="3135107" cy="342122"/>
+        <a:off x="6695311" y="150732"/>
+        <a:ext cx="3146531" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{602438BB-CBF9-49AF-AB0A-D57EA2C10BE2}">
@@ -16532,8 +16645,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9818046" y="365467"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9852525" y="318305"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16544,10 +16657,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16602,8 +16715,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9920939" y="364096"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9955792" y="316981"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{57D97F9E-094F-4C3F-82B2-5A689BC4D082}">
@@ -16613,8 +16726,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10034662" y="193925"/>
-          <a:ext cx="1801141" cy="351174"/>
+          <a:off x="10069930" y="146189"/>
+          <a:ext cx="1807704" cy="352453"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16711,8 +16824,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10044948" y="204211"/>
-        <a:ext cx="1780569" cy="330602"/>
+        <a:off x="10080253" y="156512"/>
+        <a:ext cx="1787058" cy="331807"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B3B4155B-F64B-452E-AEBC-36FE76B0BD69}">
@@ -16722,8 +16835,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="21585916">
-          <a:off x="4458692" y="771712"/>
-          <a:ext cx="216617" cy="8089"/>
+          <a:off x="4473642" y="726030"/>
+          <a:ext cx="217406" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16734,10 +16847,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216617" y="4044"/>
+                <a:pt x="217406" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16792,8 +16905,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4561585" y="770341"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="4576910" y="724705"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D20B6C81-A2D9-4E8E-80C0-968EFF7F89E1}">
@@ -16803,8 +16916,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4675308" y="593607"/>
-          <a:ext cx="1769726" cy="363410"/>
+          <a:off x="4691048" y="547328"/>
+          <a:ext cx="1776175" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16874,8 +16987,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4685952" y="604251"/>
-        <a:ext cx="1748438" cy="342122"/>
+        <a:off x="4701731" y="558011"/>
+        <a:ext cx="1754809" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7FE58BCF-6B0D-48A2-8DDE-611A1D34A4D6}">
@@ -16885,8 +16998,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6445035" y="771268"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="6467223" y="725585"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16897,10 +17010,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16955,8 +17068,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6547927" y="769897"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="6570490" y="724260"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{629314FA-FCA6-45B9-99A7-2C2196A96D5C}">
@@ -16966,8 +17079,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6661650" y="593607"/>
-          <a:ext cx="3156395" cy="363410"/>
+          <a:off x="6684628" y="547328"/>
+          <a:ext cx="3167897" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17066,8 +17179,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6672294" y="604251"/>
-        <a:ext cx="3135107" cy="342122"/>
+        <a:off x="6695311" y="558011"/>
+        <a:ext cx="3146531" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{CCF144EB-A097-46BE-8FF7-BE5C7A394E2A}">
@@ -17077,8 +17190,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9818046" y="771268"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9852525" y="725585"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17089,10 +17202,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17147,8 +17260,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9920939" y="769897"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9955792" y="724260"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9EE0F2D9-F39B-4921-9EAC-DBA04DC260DD}">
@@ -17158,8 +17271,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10034662" y="591832"/>
-          <a:ext cx="1801141" cy="366960"/>
+          <a:off x="10069930" y="545546"/>
+          <a:ext cx="1807704" cy="368297"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17242,8 +17355,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10045410" y="602580"/>
-        <a:ext cx="1779645" cy="345464"/>
+        <a:off x="10080717" y="556333"/>
+        <a:ext cx="1786130" cy="346723"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6169CD61-5E3A-4096-AA5A-91A22C397918}">
@@ -17253,8 +17366,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="3717526">
-          <a:off x="4336611" y="975499"/>
-          <a:ext cx="460779" cy="8089"/>
+          <a:off x="4351116" y="930560"/>
+          <a:ext cx="462458" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17265,10 +17378,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="460779" y="4044"/>
+                <a:pt x="462458" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17323,8 +17436,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4555481" y="968024"/>
-        <a:ext cx="23038" cy="23038"/>
+        <a:off x="4570784" y="923109"/>
+        <a:ext cx="23122" cy="23122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D5FDB947-B70B-4493-B9F9-83A45503DA23}">
@@ -17334,8 +17447,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4675308" y="1001183"/>
-          <a:ext cx="1769726" cy="363410"/>
+          <a:off x="4691048" y="956388"/>
+          <a:ext cx="1776175" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17405,8 +17518,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4685952" y="1011827"/>
-        <a:ext cx="1748438" cy="342122"/>
+        <a:off x="4701731" y="967071"/>
+        <a:ext cx="1754809" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9EDF68AF-E14B-40BF-AB6D-4B01635D735A}">
@@ -17416,8 +17529,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6445035" y="1178843"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="6467223" y="1134645"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17428,10 +17541,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17486,8 +17599,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6547927" y="1177472"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="6570490" y="1133321"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{5A5C0991-25ED-4076-91F2-80A2EEFC811E}">
@@ -17497,8 +17610,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6661650" y="1001183"/>
-          <a:ext cx="3156395" cy="363410"/>
+          <a:off x="6684628" y="956388"/>
+          <a:ext cx="3167897" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17632,8 +17745,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6672294" y="1011827"/>
-        <a:ext cx="3135107" cy="342122"/>
+        <a:off x="6695311" y="967071"/>
+        <a:ext cx="3146531" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{723082D3-A8E2-4807-89B5-C74C600B949E}">
@@ -17643,8 +17756,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9818046" y="1178843"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9852525" y="1134645"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17655,10 +17768,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17713,8 +17826,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9920939" y="1177472"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9955792" y="1133321"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{05E664DE-AAC0-4D52-9AA4-DE55CA572420}">
@@ -17724,8 +17837,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10034662" y="999408"/>
-          <a:ext cx="1801141" cy="366960"/>
+          <a:off x="10069930" y="954607"/>
+          <a:ext cx="1807704" cy="368297"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17795,8 +17908,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10045410" y="1010156"/>
-        <a:ext cx="1779645" cy="345464"/>
+        <a:off x="10080717" y="965394"/>
+        <a:ext cx="1786130" cy="346723"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{16F44D37-2601-482A-9095-0B3E8E10E520}">
@@ -17806,8 +17919,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="1505741">
-          <a:off x="2828565" y="2147057"/>
-          <a:ext cx="239195" cy="8089"/>
+          <a:off x="2837576" y="2106387"/>
+          <a:ext cx="240066" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17818,10 +17931,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="239195" y="4044"/>
+                <a:pt x="240066" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17880,8 +17993,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2942183" y="2145122"/>
-        <a:ext cx="11959" cy="11959"/>
+        <a:off x="2951607" y="2104496"/>
+        <a:ext cx="12003" cy="12003"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{2D542640-C237-42B5-8470-73084719F8F3}">
@@ -17891,8 +18004,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3056471" y="2021712"/>
-          <a:ext cx="1402222" cy="360228"/>
+          <a:off x="3066312" y="1980637"/>
+          <a:ext cx="1407331" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17962,8 +18075,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3067022" y="2032263"/>
-        <a:ext cx="1381120" cy="339126"/>
+        <a:off x="3076901" y="1991226"/>
+        <a:ext cx="1386153" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{BFCFD3BD-878E-4ADC-81DA-3641DCD660A7}">
@@ -17973,8 +18086,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17370601">
-          <a:off x="4242699" y="1892100"/>
-          <a:ext cx="648604" cy="8089"/>
+          <a:off x="4256862" y="1850501"/>
+          <a:ext cx="650967" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17985,10 +18098,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="648604" y="4044"/>
+                <a:pt x="650967" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18043,8 +18156,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4550785" y="1879930"/>
-        <a:ext cx="32430" cy="32430"/>
+        <a:off x="4566071" y="1838338"/>
+        <a:ext cx="32548" cy="32548"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{911F1DD5-D3D2-4321-A1A5-7E2BAE25AAD5}">
@@ -18054,8 +18167,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4675308" y="1408758"/>
-          <a:ext cx="1769726" cy="363410"/>
+          <a:off x="4691048" y="1365449"/>
+          <a:ext cx="1776175" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -18125,8 +18238,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4685952" y="1419402"/>
-        <a:ext cx="1748438" cy="342122"/>
+        <a:off x="4701731" y="1376132"/>
+        <a:ext cx="1754809" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{F4CAC384-240B-4811-A7FE-5EF39454FD0A}">
@@ -18136,8 +18249,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6445035" y="1586419"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="6467223" y="1543706"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18148,10 +18261,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18206,8 +18319,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6547927" y="1585048"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="6570490" y="1542381"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{00847D60-C67D-487A-B918-B0C406DE6A20}">
@@ -18217,8 +18330,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6661650" y="1408758"/>
-          <a:ext cx="3156395" cy="363410"/>
+          <a:off x="6684628" y="1365449"/>
+          <a:ext cx="3167897" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -18328,8 +18441,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6672294" y="1419402"/>
-        <a:ext cx="3135107" cy="342122"/>
+        <a:off x="6695311" y="1376132"/>
+        <a:ext cx="3146531" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7682FEBA-2A8A-4CEB-BAD3-CAC6D62452E9}">
@@ -18339,8 +18452,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9818046" y="1586419"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9852525" y="1543706"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18351,10 +18464,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18409,8 +18522,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9920939" y="1585048"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9955792" y="1542381"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4C2C55F9-D12D-4BE1-85AD-8FAFF8B344C7}">
@@ -18420,8 +18533,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10034662" y="1406983"/>
-          <a:ext cx="1801141" cy="366960"/>
+          <a:off x="10069930" y="1363668"/>
+          <a:ext cx="1807704" cy="368297"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -18539,8 +18652,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10045410" y="1417731"/>
-        <a:ext cx="1779645" cy="345464"/>
+        <a:off x="10080717" y="1374455"/>
+        <a:ext cx="1786130" cy="346723"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6A4076F7-5C10-4205-AF7B-34977DAE41B6}">
@@ -18550,8 +18663,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19004863">
-          <a:off x="4418296" y="2095888"/>
-          <a:ext cx="297408" cy="8089"/>
+          <a:off x="4433100" y="2055032"/>
+          <a:ext cx="298492" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18562,10 +18675,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="297408" y="4044"/>
+                <a:pt x="298492" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18620,8 +18733,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4559565" y="2092498"/>
-        <a:ext cx="14870" cy="14870"/>
+        <a:off x="4574883" y="2051680"/>
+        <a:ext cx="14924" cy="14924"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D2D6EBAC-87C6-4589-B626-76CA00356F2A}">
@@ -18631,8 +18744,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4675308" y="1816334"/>
-          <a:ext cx="1769726" cy="363410"/>
+          <a:off x="4691048" y="1774510"/>
+          <a:ext cx="1776175" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -18702,8 +18815,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4685952" y="1826978"/>
-        <a:ext cx="1748438" cy="342122"/>
+        <a:off x="4701731" y="1785193"/>
+        <a:ext cx="1754809" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4CEC118E-B718-4A3D-A714-E879160F0F50}">
@@ -18713,8 +18826,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6445035" y="1993994"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="6467223" y="1952767"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18725,10 +18838,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18783,8 +18896,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6547927" y="1992623"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="6570490" y="1951442"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{96C9B796-69AA-48A9-AB67-0FE5F7CEFC9D}">
@@ -18794,8 +18907,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6661650" y="1816334"/>
-          <a:ext cx="3156395" cy="363410"/>
+          <a:off x="6684628" y="1774510"/>
+          <a:ext cx="3167897" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -18889,8 +19002,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6672294" y="1826978"/>
-        <a:ext cx="3135107" cy="342122"/>
+        <a:off x="6695311" y="1785193"/>
+        <a:ext cx="3146531" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{0C4A9E51-DEA5-4AC0-B8EC-F712BFE3BA51}">
@@ -18900,8 +19013,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9818046" y="1993994"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9852525" y="1952767"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18912,10 +19025,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18970,8 +19083,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9920939" y="1992623"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9955792" y="1951442"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{829A6295-4379-4C15-BF91-56D56B48CA13}">
@@ -18981,8 +19094,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10034662" y="1814559"/>
-          <a:ext cx="1801141" cy="366960"/>
+          <a:off x="10069930" y="1772728"/>
+          <a:ext cx="1807704" cy="368297"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19068,8 +19181,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10045410" y="1825307"/>
-        <a:ext cx="1779645" cy="345464"/>
+        <a:off x="10080717" y="1783515"/>
+        <a:ext cx="1786130" cy="346723"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{15251D3B-5937-4D92-B910-59FBB0B78504}">
@@ -19079,8 +19192,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2595137">
-          <a:off x="4418296" y="2299676"/>
-          <a:ext cx="297408" cy="8089"/>
+          <a:off x="4433100" y="2259562"/>
+          <a:ext cx="298492" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19091,10 +19204,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="297408" y="4044"/>
+                <a:pt x="298492" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19149,8 +19262,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4559565" y="2296285"/>
-        <a:ext cx="14870" cy="14870"/>
+        <a:off x="4574883" y="2256210"/>
+        <a:ext cx="14924" cy="14924"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{55C8ECFC-533A-4D04-B170-164B29EE9A7D}">
@@ -19160,8 +19273,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4675308" y="2223909"/>
-          <a:ext cx="1769726" cy="363410"/>
+          <a:off x="4691048" y="2183570"/>
+          <a:ext cx="1776175" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19231,8 +19344,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4685952" y="2234553"/>
-        <a:ext cx="1748438" cy="342122"/>
+        <a:off x="4701731" y="2194253"/>
+        <a:ext cx="1754809" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A63458DA-4732-44A8-AAAD-101471030A2E}">
@@ -19242,8 +19355,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6445035" y="2401570"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="6467223" y="2361827"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19254,10 +19367,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19312,8 +19425,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6547927" y="2400199"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="6570490" y="2360502"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{3CFC9EAC-3C3A-42EE-A809-37090C958CCC}">
@@ -19323,8 +19436,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6661650" y="2223909"/>
-          <a:ext cx="3156395" cy="363410"/>
+          <a:off x="6684628" y="2183570"/>
+          <a:ext cx="3167897" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19402,8 +19515,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6672294" y="2234553"/>
-        <a:ext cx="3135107" cy="342122"/>
+        <a:off x="6695311" y="2194253"/>
+        <a:ext cx="3146531" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{2E1BE310-D0FB-4439-BC13-EF25298A0AC1}">
@@ -19413,8 +19526,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9818046" y="2401570"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9852525" y="2361827"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19425,10 +19538,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19483,8 +19596,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9920939" y="2400199"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9955792" y="2360502"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{05029C16-99B1-4993-B5A7-DFCE2EC4AF2D}">
@@ -19494,8 +19607,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10034662" y="2222134"/>
-          <a:ext cx="1801141" cy="366960"/>
+          <a:off x="10069930" y="2181789"/>
+          <a:ext cx="1807704" cy="368297"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19565,8 +19678,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10045410" y="2232882"/>
-        <a:ext cx="1779645" cy="345464"/>
+        <a:off x="10080717" y="2192576"/>
+        <a:ext cx="1786130" cy="346723"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7B1A1F24-5790-42BE-9800-70C6BAC67F71}">
@@ -19576,8 +19689,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="4229399">
-          <a:off x="4242699" y="2503464"/>
-          <a:ext cx="648604" cy="8089"/>
+          <a:off x="4256862" y="2464092"/>
+          <a:ext cx="650967" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19588,10 +19701,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="648604" y="4044"/>
+                <a:pt x="650967" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19646,8 +19759,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4550785" y="2491293"/>
-        <a:ext cx="32430" cy="32430"/>
+        <a:off x="4566071" y="2451929"/>
+        <a:ext cx="32548" cy="32548"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{F9E7099E-D348-4A20-924E-7B36E8E1B00D}">
@@ -19657,8 +19770,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4675308" y="2631485"/>
-          <a:ext cx="1788209" cy="363410"/>
+          <a:off x="4691048" y="2592631"/>
+          <a:ext cx="1794725" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19728,8 +19841,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4685952" y="2642129"/>
-        <a:ext cx="1766921" cy="342122"/>
+        <a:off x="4701731" y="2603314"/>
+        <a:ext cx="1773359" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{69A95BFF-166E-4390-9963-14C8F025ADBA}">
@@ -19739,8 +19852,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6463518" y="2809145"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="6485773" y="2770888"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19751,10 +19864,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19809,8 +19922,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6566410" y="2807775"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="6589040" y="2769563"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{BBDCC5A6-74D1-4E37-848C-BF5D7C733A0C}">
@@ -19820,8 +19933,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6680133" y="2631485"/>
-          <a:ext cx="3156395" cy="363410"/>
+          <a:off x="6703178" y="2592631"/>
+          <a:ext cx="3167897" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19891,8 +20004,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6690777" y="2642129"/>
-        <a:ext cx="3135107" cy="342122"/>
+        <a:off x="6713861" y="2603314"/>
+        <a:ext cx="3146531" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E75A9ED0-3CF3-4FBB-B735-763677226156}">
@@ -19902,8 +20015,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9836529" y="2809145"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9871075" y="2770888"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19914,10 +20027,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19972,8 +20085,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9939421" y="2807775"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9974342" y="2769563"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D255C67C-B87B-4D25-A5F4-B2880DE74996}">
@@ -19983,8 +20096,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10053144" y="2629710"/>
-          <a:ext cx="1801141" cy="366960"/>
+          <a:off x="10088480" y="2590850"/>
+          <a:ext cx="1807704" cy="368297"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20078,8 +20191,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10063892" y="2640458"/>
-        <a:ext cx="1779645" cy="345464"/>
+        <a:off x="10099267" y="2601637"/>
+        <a:ext cx="1786130" cy="346723"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{19133C7D-D6FC-4086-9EFA-C8E67C09EF92}">
@@ -20089,8 +20202,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="4842573">
-          <a:off x="2277274" y="2758420"/>
-          <a:ext cx="1341777" cy="8089"/>
+          <a:off x="2284276" y="2719978"/>
+          <a:ext cx="1346666" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20101,10 +20214,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1341777" y="4044"/>
+                <a:pt x="1346666" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20159,8 +20272,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2914618" y="2728920"/>
-        <a:ext cx="67088" cy="67088"/>
+        <a:off x="2923942" y="2690422"/>
+        <a:ext cx="67333" cy="67333"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{3A58F96D-43A0-4E22-A03B-64FF8A7610E3}">
@@ -20170,8 +20283,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3056471" y="3244439"/>
-          <a:ext cx="1402222" cy="360228"/>
+          <a:off x="3066312" y="3207818"/>
+          <a:ext cx="1407331" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20241,8 +20354,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3067022" y="3254990"/>
-        <a:ext cx="1381120" cy="339126"/>
+        <a:off x="3076901" y="3218407"/>
+        <a:ext cx="1386153" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{BC1A1E23-E0C9-4175-8735-D110618B99B3}">
@@ -20252,8 +20365,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19004863">
-          <a:off x="4418296" y="3318615"/>
-          <a:ext cx="297408" cy="8089"/>
+          <a:off x="4433100" y="3282214"/>
+          <a:ext cx="298492" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20264,10 +20377,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="297408" y="4044"/>
+                <a:pt x="298492" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20322,8 +20435,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4559565" y="3315224"/>
-        <a:ext cx="14870" cy="14870"/>
+        <a:off x="4574883" y="3278862"/>
+        <a:ext cx="14924" cy="14924"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{5D691BA5-158A-4034-AEDA-B152BE077B27}">
@@ -20333,8 +20446,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4675308" y="3039060"/>
-          <a:ext cx="1769726" cy="363410"/>
+          <a:off x="4691048" y="3001692"/>
+          <a:ext cx="1776175" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20404,8 +20517,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4685952" y="3049704"/>
-        <a:ext cx="1748438" cy="342122"/>
+        <a:off x="4701731" y="3012375"/>
+        <a:ext cx="1754809" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{C26309FF-9296-40B3-913C-85759C2B07DC}">
@@ -20415,8 +20528,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6445035" y="3216721"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="6467223" y="3179948"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20427,10 +20540,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20485,8 +20598,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6547927" y="3215350"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="6570490" y="3178624"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A4750321-4845-43B0-945B-4B9E7C7A668E}">
@@ -20496,8 +20609,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6661650" y="3039060"/>
-          <a:ext cx="3156395" cy="363410"/>
+          <a:off x="6684628" y="3001692"/>
+          <a:ext cx="3167897" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20591,8 +20704,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6672294" y="3049704"/>
-        <a:ext cx="3135107" cy="342122"/>
+        <a:off x="6695311" y="3012375"/>
+        <a:ext cx="3146531" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{CCE9C4CE-7CF8-4820-8390-F3CBCCE81ED7}">
@@ -20602,8 +20715,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9818046" y="3216721"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9852525" y="3179948"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20614,10 +20727,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20672,8 +20785,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9920939" y="3215350"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9955792" y="3178624"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D954D938-3009-44F7-BB4F-D9E8AFB2B291}">
@@ -20683,8 +20796,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10034662" y="3037285"/>
-          <a:ext cx="1801141" cy="366960"/>
+          <a:off x="10069930" y="2999910"/>
+          <a:ext cx="1807704" cy="368297"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20754,8 +20867,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10045410" y="3048033"/>
-        <a:ext cx="1779645" cy="345464"/>
+        <a:off x="10080717" y="3010697"/>
+        <a:ext cx="1786130" cy="346723"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D01C8F64-85EC-45F5-B192-363D2A57FB6E}">
@@ -20765,8 +20878,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2595137">
-          <a:off x="4418296" y="3522403"/>
-          <a:ext cx="297408" cy="8089"/>
+          <a:off x="4433100" y="3486744"/>
+          <a:ext cx="298492" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20777,10 +20890,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="297408" y="4044"/>
+                <a:pt x="298492" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20835,8 +20948,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4559565" y="3519012"/>
-        <a:ext cx="14870" cy="14870"/>
+        <a:off x="4574883" y="3483392"/>
+        <a:ext cx="14924" cy="14924"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7832722B-5DD1-4AAD-819C-BC966C90EDAC}">
@@ -20846,8 +20959,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4675308" y="3446636"/>
-          <a:ext cx="1769726" cy="363410"/>
+          <a:off x="4691048" y="3410752"/>
+          <a:ext cx="1776175" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20917,8 +21030,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4685952" y="3457280"/>
-        <a:ext cx="1748438" cy="342122"/>
+        <a:off x="4701731" y="3421435"/>
+        <a:ext cx="1754809" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9B049FA9-70FB-4D7E-AD76-2BFCDB3B4195}">
@@ -20928,8 +21041,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6445035" y="3624296"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="6467223" y="3589009"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20940,10 +21053,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20998,8 +21111,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6547927" y="3622926"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="6570490" y="3587684"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B5153D0A-E9E7-482C-B1CC-838341F8F3D8}">
@@ -21009,8 +21122,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6661650" y="3446636"/>
-          <a:ext cx="3156395" cy="363410"/>
+          <a:off x="6684628" y="3410752"/>
+          <a:ext cx="3167897" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21096,8 +21209,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6672294" y="3457280"/>
-        <a:ext cx="3135107" cy="342122"/>
+        <a:off x="6695311" y="3421435"/>
+        <a:ext cx="3146531" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1118BB77-BCCA-46BE-8B0C-417EE0F19393}">
@@ -21107,8 +21220,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9818046" y="3624296"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9852525" y="3589009"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21119,10 +21232,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21177,8 +21290,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9920939" y="3622926"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9955792" y="3587684"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A1FE2FD1-D3B2-4F02-B33F-7EA3496A9D7D}">
@@ -21188,8 +21301,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10034662" y="3444861"/>
-          <a:ext cx="1801141" cy="366960"/>
+          <a:off x="10069930" y="3408971"/>
+          <a:ext cx="1807704" cy="368297"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21259,8 +21372,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10045410" y="3455609"/>
-        <a:ext cx="1779645" cy="345464"/>
+        <a:off x="10080717" y="3419758"/>
+        <a:ext cx="1786130" cy="346723"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{ACD64E2A-6A03-49D1-9C11-853B1D5FDA3F}">
@@ -21270,8 +21383,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="4880920">
-          <a:off x="572123" y="4231846"/>
-          <a:ext cx="1440061" cy="8089"/>
+          <a:off x="572912" y="4198773"/>
+          <a:ext cx="1445308" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21282,10 +21395,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1440061" y="4044"/>
+                <a:pt x="1445308" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21340,8 +21453,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1256152" y="4199889"/>
-        <a:ext cx="72003" cy="72003"/>
+        <a:off x="1259433" y="4166750"/>
+        <a:ext cx="72265" cy="72265"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4915DA81-5EFF-4A45-B117-A1C9369BA960}">
@@ -21351,8 +21464,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="1400462" y="4767614"/>
-          <a:ext cx="1432488" cy="360228"/>
+          <a:off x="1404269" y="4736544"/>
+          <a:ext cx="1437708" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21474,8 +21587,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1411013" y="4778165"/>
-        <a:ext cx="1411386" cy="339126"/>
+        <a:off x="1414858" y="4747133"/>
+        <a:ext cx="1416530" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A3777E34-F7A1-4ABC-99E9-9C9A9AB7B959}">
@@ -21485,8 +21598,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17225057">
-          <a:off x="2577781" y="4598311"/>
-          <a:ext cx="722633" cy="8089"/>
+          <a:off x="2585877" y="4566573"/>
+          <a:ext cx="725267" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21497,10 +21610,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="722633" y="4044"/>
+                <a:pt x="725267" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21555,8 +21668,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2921032" y="4584290"/>
-        <a:ext cx="36131" cy="36131"/>
+        <a:off x="2930379" y="4552551"/>
+        <a:ext cx="36263" cy="36263"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{23228D17-0E30-4278-86F1-009AEEE4B90D}">
@@ -21566,8 +21679,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3045245" y="4076868"/>
-          <a:ext cx="1402222" cy="360228"/>
+          <a:off x="3055045" y="4043280"/>
+          <a:ext cx="1407331" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21637,8 +21750,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3055796" y="4087419"/>
-        <a:ext cx="1381120" cy="339126"/>
+        <a:off x="3065634" y="4053869"/>
+        <a:ext cx="1386153" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A22E3146-1836-4A0C-A6D3-4503A76A9781}">
@@ -21648,8 +21761,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19004863">
-          <a:off x="4407070" y="4151044"/>
-          <a:ext cx="297408" cy="8089"/>
+          <a:off x="4421833" y="4117676"/>
+          <a:ext cx="298492" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21660,10 +21773,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="297408" y="4044"/>
+                <a:pt x="298492" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21718,8 +21831,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4548339" y="4147653"/>
-        <a:ext cx="14870" cy="14870"/>
+        <a:off x="4563616" y="4114324"/>
+        <a:ext cx="14924" cy="14924"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{06E3AC3D-2CA5-4C28-B4EE-08E1F5093575}">
@@ -21729,8 +21842,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4664082" y="3871489"/>
-          <a:ext cx="1769726" cy="363410"/>
+          <a:off x="4679781" y="3837154"/>
+          <a:ext cx="1776175" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21816,8 +21929,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4674726" y="3882133"/>
-        <a:ext cx="1748438" cy="342122"/>
+        <a:off x="4690464" y="3847837"/>
+        <a:ext cx="1754809" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{AB38F8C9-39F9-48F1-A4B9-359AD3B6C9E1}">
@@ -21827,8 +21940,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6433809" y="4049150"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="6455956" y="4015410"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21839,10 +21952,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21897,8 +22010,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6536701" y="4047779"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="6559223" y="4014086"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{94E3E4AC-563C-467A-AD10-294BF8A33BAF}">
@@ -21908,8 +22021,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6650424" y="3871489"/>
-          <a:ext cx="3156395" cy="363410"/>
+          <a:off x="6673361" y="3837154"/>
+          <a:ext cx="3167897" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21995,8 +22108,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6661068" y="3882133"/>
-        <a:ext cx="3135107" cy="342122"/>
+        <a:off x="6684044" y="3847837"/>
+        <a:ext cx="3146531" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{CE4A2E59-3DB6-4586-9EDA-16655120708B}">
@@ -22006,8 +22119,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9806820" y="4049150"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9841258" y="4015410"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22018,10 +22131,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22076,8 +22189,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9909712" y="4047779"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9944525" y="4014086"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{74F8E0C0-A1C2-4026-BDD1-211E4452BF84}">
@@ -22087,8 +22200,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10023436" y="3869714"/>
-          <a:ext cx="1801141" cy="366960"/>
+          <a:off x="10058663" y="3835372"/>
+          <a:ext cx="1807704" cy="368297"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22158,8 +22271,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10034184" y="3880462"/>
-        <a:ext cx="1779645" cy="345464"/>
+        <a:off x="10069450" y="3846159"/>
+        <a:ext cx="1786130" cy="346723"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{3776BE60-D86F-469E-9605-E0609281B4B9}">
@@ -22169,8 +22282,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2595137">
-          <a:off x="4407070" y="4354831"/>
-          <a:ext cx="297408" cy="8089"/>
+          <a:off x="4421833" y="4322206"/>
+          <a:ext cx="298492" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22181,10 +22294,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="297408" y="4044"/>
+                <a:pt x="298492" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22239,8 +22352,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4548339" y="4351441"/>
-        <a:ext cx="14870" cy="14870"/>
+        <a:off x="4563616" y="4318854"/>
+        <a:ext cx="14924" cy="14924"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{DC0F0790-8247-4EA1-A5BD-20B9C2810EA5}">
@@ -22250,8 +22363,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4664082" y="4279065"/>
-          <a:ext cx="1769726" cy="363410"/>
+          <a:off x="4679781" y="4246214"/>
+          <a:ext cx="1776175" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22321,8 +22434,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4674726" y="4289709"/>
-        <a:ext cx="1748438" cy="342122"/>
+        <a:off x="4690464" y="4256897"/>
+        <a:ext cx="1754809" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{82B78A4F-EF07-4DEA-A3EC-7BA9DD55DC45}">
@@ -22332,8 +22445,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6433809" y="4456725"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="6455956" y="4424471"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22344,10 +22457,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22402,8 +22515,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6536701" y="4455354"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="6559223" y="4423146"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4D82C0F8-05DA-476F-9FFD-EF5362E37ABC}">
@@ -22413,8 +22526,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6650424" y="4279065"/>
-          <a:ext cx="3156395" cy="363410"/>
+          <a:off x="6673361" y="4246214"/>
+          <a:ext cx="3167897" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22492,8 +22605,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6661068" y="4289709"/>
-        <a:ext cx="3135107" cy="342122"/>
+        <a:off x="6684044" y="4256897"/>
+        <a:ext cx="3146531" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6F09ED48-69E5-4359-AEF9-003C31CF3834}">
@@ -22503,8 +22616,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9806820" y="4456725"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9841258" y="4424471"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22515,10 +22628,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22573,8 +22686,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9909712" y="4455354"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9944525" y="4423146"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7F4C8494-F5DD-49F1-B7FE-320AAF64A334}">
@@ -22584,8 +22697,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10023436" y="4277290"/>
-          <a:ext cx="1801141" cy="366960"/>
+          <a:off x="10058663" y="4244433"/>
+          <a:ext cx="1807704" cy="368297"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22660,8 +22773,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10034184" y="4288038"/>
-        <a:ext cx="1779645" cy="345464"/>
+        <a:off x="10069450" y="4255220"/>
+        <a:ext cx="1786130" cy="346723"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E97A89EA-A088-4B36-94ED-03E39FF28C24}">
@@ -22671,8 +22784,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="1512707">
-          <a:off x="2821547" y="4994677"/>
-          <a:ext cx="239423" cy="8089"/>
+          <a:off x="2830532" y="4964383"/>
+          <a:ext cx="240295" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22683,10 +22796,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="239423" y="4044"/>
+                <a:pt x="240295" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22741,8 +22854,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2935273" y="4992736"/>
-        <a:ext cx="11971" cy="11971"/>
+        <a:off x="2944672" y="4962486"/>
+        <a:ext cx="12014" cy="12014"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1279AA60-C872-4597-B281-C6CC2E4A34C2}">
@@ -22752,8 +22865,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3049566" y="4869600"/>
-          <a:ext cx="1402222" cy="360228"/>
+          <a:off x="3059382" y="4838902"/>
+          <a:ext cx="1407331" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22823,8 +22936,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3060117" y="4880151"/>
-        <a:ext cx="1381120" cy="339126"/>
+        <a:off x="3069971" y="4849491"/>
+        <a:ext cx="1386153" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{255CD393-ED80-4D10-A68E-31ED59592E3B}">
@@ -22834,8 +22947,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19138242">
-          <a:off x="4417227" y="4953303"/>
-          <a:ext cx="281417" cy="8089"/>
+          <a:off x="4432026" y="4922858"/>
+          <a:ext cx="282442" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22846,10 +22959,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="281417" y="4044"/>
+                <a:pt x="282442" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22904,8 +23017,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4550900" y="4950312"/>
-        <a:ext cx="14070" cy="14070"/>
+        <a:off x="4566186" y="4919907"/>
+        <a:ext cx="14122" cy="14122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{2340676A-EBD4-4E22-BA9C-E56B6A62904C}">
@@ -22915,8 +23028,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4664082" y="4683274"/>
-          <a:ext cx="1769726" cy="363410"/>
+          <a:off x="4679781" y="4651897"/>
+          <a:ext cx="1776175" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22986,8 +23099,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4674726" y="4693918"/>
-        <a:ext cx="1748438" cy="342122"/>
+        <a:off x="4690464" y="4662580"/>
+        <a:ext cx="1754809" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{EB837690-03CF-4B39-A4B0-AFC71E15928A}">
@@ -22997,8 +23110,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="27806">
-          <a:off x="6433805" y="4861829"/>
-          <a:ext cx="220944" cy="8089"/>
+          <a:off x="6455952" y="4831051"/>
+          <a:ext cx="221749" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23009,10 +23122,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="220944" y="4044"/>
+                <a:pt x="221749" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23067,8 +23180,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6538754" y="4860350"/>
-        <a:ext cx="11047" cy="11047"/>
+        <a:off x="6561283" y="4829617"/>
+        <a:ext cx="11087" cy="11087"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6CD3FE0A-3BBE-455B-B381-72424654A1B0}">
@@ -23078,8 +23191,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6654746" y="4686652"/>
-          <a:ext cx="3155594" cy="360228"/>
+          <a:off x="6677698" y="4655287"/>
+          <a:ext cx="3167092" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23157,8 +23270,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6665297" y="4697203"/>
-        <a:ext cx="3134492" cy="339126"/>
+        <a:off x="6688287" y="4665876"/>
+        <a:ext cx="3145914" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B86CABA2-1933-4D02-A0D3-AA6DEA35BCA7}">
@@ -23168,8 +23281,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9810340" y="4862722"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9844791" y="4831947"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23180,10 +23293,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23238,8 +23351,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9913232" y="4861351"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9948058" y="4830623"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{920A36CD-D69B-4AB0-8DA2-4963F1111FE2}">
@@ -23249,8 +23362,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10026956" y="4686652"/>
-          <a:ext cx="1801141" cy="360228"/>
+          <a:off x="10062195" y="4655287"/>
+          <a:ext cx="1807704" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23320,8 +23433,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10037507" y="4697203"/>
-        <a:ext cx="1780039" cy="339126"/>
+        <a:off x="10072784" y="4665876"/>
+        <a:ext cx="1786526" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{EE30240B-4D3F-4585-94A4-7AD0CBEBACD0}">
@@ -23331,8 +23444,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2755727">
-          <a:off x="4405327" y="5155316"/>
-          <a:ext cx="305216" cy="8089"/>
+          <a:off x="4420083" y="5125607"/>
+          <a:ext cx="306328" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23343,10 +23456,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="305216" y="4044"/>
+                <a:pt x="306328" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23401,8 +23514,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4550305" y="5151730"/>
-        <a:ext cx="15260" cy="15260"/>
+        <a:off x="4565589" y="5122059"/>
+        <a:ext cx="15316" cy="15316"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9B0332A1-DFA5-4E72-89B6-8E8C50F667E1}">
@@ -23412,8 +23525,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4664082" y="5087300"/>
-          <a:ext cx="1769726" cy="363410"/>
+          <a:off x="4679781" y="5057395"/>
+          <a:ext cx="1776175" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23510,8 +23623,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4674726" y="5097944"/>
-        <a:ext cx="1748438" cy="342122"/>
+        <a:off x="4690464" y="5068078"/>
+        <a:ext cx="1754809" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4EF5B1E7-3D92-44D9-8E8A-E2A10FB649AC}">
@@ -23521,8 +23634,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="27806">
-          <a:off x="6433805" y="5265854"/>
-          <a:ext cx="220944" cy="8089"/>
+          <a:off x="6455952" y="5236548"/>
+          <a:ext cx="221749" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23533,10 +23646,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="220944" y="4044"/>
+                <a:pt x="221749" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23591,8 +23704,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6538754" y="5264375"/>
-        <a:ext cx="11047" cy="11047"/>
+        <a:off x="6561283" y="5235115"/>
+        <a:ext cx="11087" cy="11087"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9AC7A0EB-B59E-41D9-A589-CB90FBF4305E}">
@@ -23602,8 +23715,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6654746" y="5090678"/>
-          <a:ext cx="3155594" cy="360228"/>
+          <a:off x="6677698" y="5060785"/>
+          <a:ext cx="3167092" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23689,8 +23802,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6665297" y="5101229"/>
-        <a:ext cx="3134492" cy="339126"/>
+        <a:off x="6688287" y="5071374"/>
+        <a:ext cx="3145914" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{2F5A23ED-2B4B-4307-BAD6-D126CED4ED45}">
@@ -23700,8 +23813,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9810340" y="5266748"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9844791" y="5237445"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23712,10 +23825,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23770,8 +23883,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9913232" y="5265377"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9948058" y="5236121"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{C9CCA1DF-737F-40B9-8662-1EBAE874B88C}">
@@ -23781,8 +23894,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10026956" y="5090678"/>
-          <a:ext cx="1801141" cy="360228"/>
+          <a:off x="10062195" y="5060785"/>
+          <a:ext cx="1807704" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23852,8 +23965,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10037507" y="5101229"/>
-        <a:ext cx="1780039" cy="339126"/>
+        <a:off x="10072784" y="5071374"/>
+        <a:ext cx="1786526" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{06804470-2E4E-45CC-AD07-54CD8F165228}">
@@ -23863,8 +23976,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="4379331">
-          <a:off x="2571049" y="5297697"/>
-          <a:ext cx="740419" cy="8089"/>
+          <a:off x="2579121" y="5268507"/>
+          <a:ext cx="743117" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23875,10 +23988,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="740419" y="4044"/>
+                <a:pt x="743117" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23933,8 +24046,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2922748" y="5283231"/>
-        <a:ext cx="37020" cy="37020"/>
+        <a:off x="2932101" y="5254039"/>
+        <a:ext cx="37155" cy="37155"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D9D1FF4E-B146-4A17-8BAD-E6A8247731B1}">
@@ -23944,8 +24057,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3049566" y="5475639"/>
-          <a:ext cx="1402227" cy="360228"/>
+          <a:off x="3059382" y="5447149"/>
+          <a:ext cx="1407337" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -24031,8 +24144,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3060117" y="5486190"/>
-        <a:ext cx="1381125" cy="339126"/>
+        <a:off x="3069971" y="5457738"/>
+        <a:ext cx="1386159" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{458C594D-E94A-4416-A27A-8211BD0C18EB}">
@@ -24042,8 +24155,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4451794" y="5651709"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="4466719" y="5623809"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -24054,10 +24167,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -24112,8 +24225,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4554686" y="5650338"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="4569986" y="5622484"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E6BB35B6-4DC7-42B5-A329-D93F595605BC}">
@@ -24123,8 +24236,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4668409" y="5474048"/>
-          <a:ext cx="1759258" cy="363410"/>
+          <a:off x="4684124" y="5445552"/>
+          <a:ext cx="1765668" cy="364734"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -24210,8 +24323,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4679053" y="5484692"/>
-        <a:ext cx="1737970" cy="342122"/>
+        <a:off x="4694807" y="5456235"/>
+        <a:ext cx="1744302" cy="343368"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{F3CE9778-2DAD-459C-A92D-C581128238EF}">
@@ -24221,8 +24334,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6427668" y="5651709"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="6449793" y="5623809"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -24233,10 +24346,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -24291,8 +24404,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6530560" y="5650338"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="6553060" y="5622484"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A62201D7-F2CC-41E5-BB68-F68B79E1464B}">
@@ -24302,8 +24415,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6644283" y="5475639"/>
-          <a:ext cx="3155594" cy="360228"/>
+          <a:off x="6667197" y="5447149"/>
+          <a:ext cx="3167092" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -24373,8 +24486,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6654834" y="5486190"/>
-        <a:ext cx="3134492" cy="339126"/>
+        <a:off x="6677786" y="5457738"/>
+        <a:ext cx="3145914" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{46794C65-61A0-4B52-A42E-5CC9D77E3723}">
@@ -24384,8 +24497,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9799878" y="5651709"/>
-          <a:ext cx="216615" cy="8089"/>
+          <a:off x="9834290" y="5623809"/>
+          <a:ext cx="217404" cy="8220"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -24396,10 +24509,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4044"/>
+                <a:pt x="0" y="4110"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="216615" y="4044"/>
+                <a:pt x="217404" y="4110"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -24454,8 +24567,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9902770" y="5650338"/>
-        <a:ext cx="10830" cy="10830"/>
+        <a:off x="9937557" y="5622484"/>
+        <a:ext cx="10870" cy="10870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{C61F938B-5A64-4BF7-B003-81E0909084B1}">
@@ -24465,8 +24578,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10016493" y="5475639"/>
-          <a:ext cx="1801141" cy="360228"/>
+          <a:off x="10051695" y="5447149"/>
+          <a:ext cx="1807704" cy="361541"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -24536,8 +24649,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10027044" y="5486190"/>
-        <a:ext cx="1780039" cy="339126"/>
+        <a:off x="10062284" y="5457738"/>
+        <a:ext cx="1786526" cy="340363"/>
       </dsp:txXfrm>
     </dsp:sp>
   </dsp:spTree>
@@ -28328,13 +28441,13 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA7446D1-A9E6-4F8D-B799-CB90AD03762A}">
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="3.9140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="77.6640625" customWidth="1"/>
+    <col min="1" max="1" width="8.9140625" customWidth="1"/>
+    <col min="2" max="2" width="51.9140625" customWidth="1"/>
     <col min="3" max="3" width="71.08203125" customWidth="1"/>
-    <col min="4" max="4" width="65.33203125" style="114" customWidth="1"/>
+    <col min="4" max="4" width="65.33203125" style="80" customWidth="1"/>
     <col min="5" max="5" width="65.33203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -28348,7 +28461,7 @@
       <c r="C1" s="59" t="s">
         <v>199</v>
       </c>
-      <c r="D1" s="115" t="s">
+      <c r="D1" s="81" t="s">
         <v>200</v>
       </c>
       <c r="E1" s="59" t="s">
@@ -28594,6 +28707,106 @@
       <c r="D16" s="18"/>
       <c r="E16" s="18" t="s">
         <v>481</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A17" s="119"/>
+      <c r="B17" s="120"/>
+      <c r="C17" s="121"/>
+      <c r="D17" s="121"/>
+      <c r="E17" s="121"/>
+    </row>
+    <row r="18" spans="1:5" ht="20.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="118" t="s">
+        <v>493</v>
+      </c>
+      <c r="B18" s="69"/>
+      <c r="C18" s="69"/>
+      <c r="E18" s="69"/>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A19" s="60" t="s">
+        <v>510</v>
+      </c>
+      <c r="B19" s="60" t="s">
+        <v>511</v>
+      </c>
+      <c r="C19" s="60" t="s">
+        <v>512</v>
+      </c>
+      <c r="D19" s="60" t="s">
+        <v>513</v>
+      </c>
+      <c r="E19" s="60" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" ht="85" x14ac:dyDescent="0.45">
+      <c r="A20" s="122">
+        <v>1</v>
+      </c>
+      <c r="B20" s="123" t="s">
+        <v>494</v>
+      </c>
+      <c r="C20" s="123" t="s">
+        <v>495</v>
+      </c>
+      <c r="D20" s="123" t="s">
+        <v>496</v>
+      </c>
+      <c r="E20" s="122" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" ht="68" x14ac:dyDescent="0.45">
+      <c r="A21" s="122">
+        <v>2</v>
+      </c>
+      <c r="B21" s="123" t="s">
+        <v>498</v>
+      </c>
+      <c r="C21" s="123" t="s">
+        <v>499</v>
+      </c>
+      <c r="D21" s="123" t="s">
+        <v>500</v>
+      </c>
+      <c r="E21" s="122" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" ht="102" x14ac:dyDescent="0.45">
+      <c r="A22" s="122">
+        <v>3</v>
+      </c>
+      <c r="B22" s="123" t="s">
+        <v>502</v>
+      </c>
+      <c r="C22" s="123" t="s">
+        <v>503</v>
+      </c>
+      <c r="D22" s="123" t="s">
+        <v>504</v>
+      </c>
+      <c r="E22" s="122" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" ht="68" x14ac:dyDescent="0.45">
+      <c r="A23" s="122">
+        <v>4</v>
+      </c>
+      <c r="B23" s="123" t="s">
+        <v>506</v>
+      </c>
+      <c r="C23" s="123" t="s">
+        <v>507</v>
+      </c>
+      <c r="D23" s="123" t="s">
+        <v>508</v>
+      </c>
+      <c r="E23" s="122" t="s">
+        <v>509</v>
       </c>
     </row>
   </sheetData>
@@ -28708,10 +28921,10 @@
       <c r="B6" s="72" t="s">
         <v>449</v>
       </c>
-      <c r="C6" s="80">
+      <c r="C6" s="82">
         <v>46275</v>
       </c>
-      <c r="D6" s="82" t="s">
+      <c r="D6" s="84" t="s">
         <v>316</v>
       </c>
     </row>
@@ -28722,8 +28935,8 @@
       <c r="B7" s="73" t="s">
         <v>450</v>
       </c>
-      <c r="C7" s="81"/>
-      <c r="D7" s="83"/>
+      <c r="C7" s="83"/>
+      <c r="D7" s="85"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" s="33" t="s">
@@ -28838,7 +29051,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A2" s="84" t="s">
+      <c r="A2" s="86" t="s">
         <v>18</v>
       </c>
       <c r="B2" s="7" t="s">
@@ -28855,7 +29068,7 @@
       <c r="G2" s="10"/>
     </row>
     <row r="3" spans="1:7" ht="64" x14ac:dyDescent="0.45">
-      <c r="A3" s="85"/>
+      <c r="A3" s="87"/>
       <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
@@ -28872,7 +29085,7 @@
       <c r="G3" s="11"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A4" s="85"/>
+      <c r="A4" s="87"/>
       <c r="B4" s="4" t="s">
         <v>184</v>
       </c>
@@ -28887,7 +29100,7 @@
       <c r="G4" s="11"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A5" s="85"/>
+      <c r="A5" s="87"/>
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
@@ -28902,7 +29115,7 @@
       <c r="G5" s="11"/>
     </row>
     <row r="6" spans="1:7" ht="48" x14ac:dyDescent="0.45">
-      <c r="A6" s="85"/>
+      <c r="A6" s="87"/>
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
@@ -28921,7 +29134,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="86"/>
+      <c r="A7" s="88"/>
       <c r="B7" s="13" t="s">
         <v>15</v>
       </c>
@@ -28938,7 +29151,7 @@
       <c r="G7" s="15"/>
     </row>
     <row r="8" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="87" t="s">
+      <c r="A8" s="89" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="7" t="s">
@@ -28959,7 +29172,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A9" s="88"/>
+      <c r="A9" s="90"/>
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -28976,7 +29189,7 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A10" s="88"/>
+      <c r="A10" s="90"/>
       <c r="B10" s="4" t="s">
         <v>4</v>
       </c>
@@ -28993,7 +29206,7 @@
       <c r="G10" s="11"/>
     </row>
     <row r="11" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="88"/>
+      <c r="A11" s="90"/>
       <c r="B11" s="4" t="s">
         <v>7</v>
       </c>
@@ -29008,7 +29221,7 @@
       <c r="G11" s="11"/>
     </row>
     <row r="12" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="89"/>
+      <c r="A12" s="91"/>
       <c r="B12" s="16" t="s">
         <v>8</v>
       </c>
@@ -29025,7 +29238,7 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A13" s="90" t="s">
+      <c r="A13" s="92" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="7" t="s">
@@ -29046,7 +29259,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="64.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="91"/>
+      <c r="A14" s="93"/>
       <c r="B14" s="4" t="s">
         <v>10</v>
       </c>
@@ -29063,7 +29276,7 @@
       <c r="G14" s="11"/>
     </row>
     <row r="15" spans="1:7" ht="64" x14ac:dyDescent="0.45">
-      <c r="A15" s="91"/>
+      <c r="A15" s="93"/>
       <c r="B15" s="4" t="s">
         <v>218</v>
       </c>
@@ -29084,7 +29297,7 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A16" s="92"/>
+      <c r="A16" s="94"/>
       <c r="B16" s="16" t="s">
         <v>11</v>
       </c>
@@ -29237,14 +29450,14 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A5" s="100" t="s">
+      <c r="A5" s="96" t="s">
         <v>273</v>
       </c>
-      <c r="B5" s="100"/>
-      <c r="C5" s="100"/>
+      <c r="B5" s="96"/>
+      <c r="C5" s="96"/>
     </row>
     <row r="6" spans="1:4" ht="32" x14ac:dyDescent="0.45">
-      <c r="A6" s="102" t="s">
+      <c r="A6" s="108" t="s">
         <v>204</v>
       </c>
       <c r="B6" s="47" t="s">
@@ -29255,7 +29468,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="32" x14ac:dyDescent="0.45">
-      <c r="A7" s="103"/>
+      <c r="A7" s="109"/>
       <c r="B7" s="47" t="s">
         <v>292</v>
       </c>
@@ -29264,7 +29477,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" ht="32" x14ac:dyDescent="0.45">
-      <c r="A8" s="103"/>
+      <c r="A8" s="109"/>
       <c r="B8" s="47" t="s">
         <v>295</v>
       </c>
@@ -29273,7 +29486,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A9" s="103"/>
+      <c r="A9" s="109"/>
       <c r="B9" s="47" t="s">
         <v>303</v>
       </c>
@@ -29282,7 +29495,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A10" s="104"/>
+      <c r="A10" s="110"/>
       <c r="B10" s="47" t="s">
         <v>297</v>
       </c>
@@ -29305,18 +29518,18 @@
       <c r="C12" s="49"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A13" s="94" t="s">
+      <c r="A13" s="101" t="s">
         <v>304</v>
       </c>
-      <c r="B13" s="95"/>
-      <c r="C13" s="96"/>
+      <c r="B13" s="102"/>
+      <c r="C13" s="103"/>
     </row>
     <row r="14" spans="1:4" ht="52" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="105" t="s">
+      <c r="A14" s="111" t="s">
         <v>230</v>
       </c>
-      <c r="B14" s="106"/>
-      <c r="C14" s="107"/>
+      <c r="B14" s="112"/>
+      <c r="C14" s="113"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="49"/>
@@ -29324,112 +29537,112 @@
       <c r="D19" s="49"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A31" s="100" t="s">
+      <c r="A31" s="96" t="s">
         <v>274</v>
       </c>
-      <c r="B31" s="100"/>
-      <c r="C31" s="100"/>
+      <c r="B31" s="96"/>
+      <c r="C31" s="96"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A32" s="97" t="s">
+      <c r="A32" s="104" t="s">
         <v>318</v>
       </c>
-      <c r="B32" s="98"/>
-      <c r="C32" s="99"/>
+      <c r="B32" s="105"/>
+      <c r="C32" s="106"/>
     </row>
     <row r="33" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="93" t="s">
+      <c r="A33" s="100" t="s">
         <v>231</v>
       </c>
       <c r="B33" s="50" t="s">
         <v>208</v>
       </c>
-      <c r="C33" s="101" t="s">
+      <c r="C33" s="107" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A34" s="93"/>
+      <c r="A34" s="100"/>
       <c r="B34" s="50" t="s">
         <v>209</v>
       </c>
-      <c r="C34" s="101"/>
+      <c r="C34" s="107"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A35" s="93"/>
+      <c r="A35" s="100"/>
       <c r="B35" s="50" t="s">
         <v>210</v>
       </c>
-      <c r="C35" s="101"/>
+      <c r="C35" s="107"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A36" s="93"/>
+      <c r="A36" s="100"/>
       <c r="B36" s="50" t="s">
         <v>211</v>
       </c>
-      <c r="C36" s="101"/>
+      <c r="C36" s="107"/>
     </row>
     <row r="37" spans="1:5" ht="32" x14ac:dyDescent="0.45">
-      <c r="A37" s="93"/>
+      <c r="A37" s="100"/>
       <c r="B37" s="48" t="s">
         <v>212</v>
       </c>
-      <c r="C37" s="101"/>
+      <c r="C37" s="107"/>
     </row>
     <row r="38" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="93" t="s">
+      <c r="A38" s="100" t="s">
         <v>232</v>
       </c>
       <c r="B38" s="50" t="s">
         <v>213</v>
       </c>
-      <c r="C38" s="101" t="s">
+      <c r="C38" s="107" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A39" s="93"/>
+      <c r="A39" s="100"/>
       <c r="B39" s="50" t="s">
         <v>214</v>
       </c>
-      <c r="C39" s="101"/>
+      <c r="C39" s="107"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A40" s="93"/>
+      <c r="A40" s="100"/>
       <c r="B40" s="50" t="s">
         <v>215</v>
       </c>
-      <c r="C40" s="101"/>
+      <c r="C40" s="107"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A42" s="94" t="s">
+      <c r="A42" s="101" t="s">
         <v>272</v>
       </c>
-      <c r="B42" s="95"/>
-      <c r="C42" s="96"/>
+      <c r="B42" s="102"/>
+      <c r="C42" s="103"/>
     </row>
     <row r="43" spans="1:5" ht="53" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A43" s="93" t="s">
+      <c r="A43" s="100" t="s">
         <v>217</v>
       </c>
-      <c r="B43" s="93"/>
-      <c r="C43" s="93"/>
+      <c r="B43" s="100"/>
+      <c r="C43" s="100"/>
     </row>
     <row r="44" spans="1:5" ht="50.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A44" s="93" t="s">
+      <c r="A44" s="100" t="s">
         <v>317</v>
       </c>
-      <c r="B44" s="93"/>
-      <c r="C44" s="93"/>
+      <c r="B44" s="100"/>
+      <c r="C44" s="100"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A46" s="100" t="s">
+      <c r="A46" s="96" t="s">
         <v>271</v>
       </c>
-      <c r="B46" s="100"/>
-      <c r="C46" s="100"/>
-      <c r="D46" s="100"/>
-      <c r="E46" s="100"/>
+      <c r="B46" s="96"/>
+      <c r="C46" s="96"/>
+      <c r="D46" s="96"/>
+      <c r="E46" s="96"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" s="44" t="s">
@@ -29615,11 +29828,11 @@
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A59" s="109" t="s">
+      <c r="A59" s="97" t="s">
         <v>275</v>
       </c>
-      <c r="B59" s="110"/>
-      <c r="C59" s="111"/>
+      <c r="B59" s="98"/>
+      <c r="C59" s="99"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" s="53" t="s">
@@ -29677,99 +29890,87 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A66" s="100" t="s">
+      <c r="A66" s="96" t="s">
         <v>291</v>
       </c>
-      <c r="B66" s="100"/>
-      <c r="C66" s="100"/>
-      <c r="D66" s="100"/>
+      <c r="B66" s="96"/>
+      <c r="C66" s="96"/>
+      <c r="D66" s="96"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A67" s="108" t="s">
+      <c r="A67" s="95" t="s">
         <v>262</v>
       </c>
-      <c r="B67" s="108"/>
-      <c r="C67" s="108"/>
-      <c r="D67" s="108"/>
+      <c r="B67" s="95"/>
+      <c r="C67" s="95"/>
+      <c r="D67" s="95"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A68" s="108" t="s">
+      <c r="A68" s="95" t="s">
         <v>263</v>
       </c>
-      <c r="B68" s="108"/>
-      <c r="C68" s="108"/>
-      <c r="D68" s="108"/>
+      <c r="B68" s="95"/>
+      <c r="C68" s="95"/>
+      <c r="D68" s="95"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A69" s="108" t="s">
+      <c r="A69" s="95" t="s">
         <v>264</v>
       </c>
-      <c r="B69" s="108"/>
-      <c r="C69" s="108"/>
-      <c r="D69" s="108"/>
+      <c r="B69" s="95"/>
+      <c r="C69" s="95"/>
+      <c r="D69" s="95"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A70" s="108" t="s">
+      <c r="A70" s="95" t="s">
         <v>265</v>
       </c>
-      <c r="B70" s="108"/>
-      <c r="C70" s="108"/>
-      <c r="D70" s="108"/>
+      <c r="B70" s="95"/>
+      <c r="C70" s="95"/>
+      <c r="D70" s="95"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A71" s="108" t="s">
+      <c r="A71" s="95" t="s">
         <v>266</v>
       </c>
-      <c r="B71" s="108"/>
-      <c r="C71" s="108"/>
-      <c r="D71" s="108"/>
+      <c r="B71" s="95"/>
+      <c r="C71" s="95"/>
+      <c r="D71" s="95"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A72" s="108" t="s">
+      <c r="A72" s="95" t="s">
         <v>267</v>
       </c>
-      <c r="B72" s="108"/>
-      <c r="C72" s="108"/>
-      <c r="D72" s="108"/>
+      <c r="B72" s="95"/>
+      <c r="C72" s="95"/>
+      <c r="D72" s="95"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A73" s="108" t="s">
+      <c r="A73" s="95" t="s">
         <v>268</v>
       </c>
-      <c r="B73" s="108"/>
-      <c r="C73" s="108"/>
-      <c r="D73" s="108"/>
+      <c r="B73" s="95"/>
+      <c r="C73" s="95"/>
+      <c r="D73" s="95"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A74" s="108" t="s">
+      <c r="A74" s="95" t="s">
         <v>269</v>
       </c>
-      <c r="B74" s="108"/>
-      <c r="C74" s="108"/>
-      <c r="D74" s="108"/>
+      <c r="B74" s="95"/>
+      <c r="C74" s="95"/>
+      <c r="D74" s="95"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A75" s="108" t="s">
+      <c r="A75" s="95" t="s">
         <v>270</v>
       </c>
-      <c r="B75" s="108"/>
-      <c r="C75" s="108"/>
-      <c r="D75" s="108"/>
+      <c r="B75" s="95"/>
+      <c r="C75" s="95"/>
+      <c r="D75" s="95"/>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A73:D73"/>
-    <mergeCell ref="A74:D74"/>
-    <mergeCell ref="A75:D75"/>
-    <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A66:D66"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A67:D67"/>
-    <mergeCell ref="A68:D68"/>
-    <mergeCell ref="A69:D69"/>
-    <mergeCell ref="A70:D70"/>
-    <mergeCell ref="A71:D71"/>
-    <mergeCell ref="A72:D72"/>
     <mergeCell ref="A44:C44"/>
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="A32:C32"/>
@@ -29783,6 +29984,18 @@
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A43:C43"/>
+    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="A74:D74"/>
+    <mergeCell ref="A75:D75"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A67:D67"/>
+    <mergeCell ref="A68:D68"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="A70:D70"/>
+    <mergeCell ref="A71:D71"/>
+    <mergeCell ref="A72:D72"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -29823,10 +30036,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A1" s="112" t="s">
+      <c r="A1" s="114" t="s">
         <v>335</v>
       </c>
-      <c r="B1" s="113"/>
+      <c r="B1" s="115"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="60" t="s">

--- a/project_2/project2_project status(C2).xlsx
+++ b/project_2/project2_project status(C2).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pyostry\workspace\aiffel\ai-data-bootcamp\Project_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2150866-98E6-4B3F-9623-947A4AC1BCB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADF8F8A2-97AB-4519-B186-31B81E535E32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" firstSheet="4" activeTab="9" xr2:uid="{5FF54064-7DDC-427B-93D7-EF78D75E5195}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{5FF54064-7DDC-427B-93D7-EF78D75E5195}"/>
   </bookViews>
   <sheets>
     <sheet name="제작 가이드라인" sheetId="12" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="516">
   <si>
     <t>reward</t>
   </si>
@@ -2056,16 +2056,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>디자인:
-제작:</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>발표자료 준비:
-발표:</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>offer 설계 시 reward의 차이로는 완료율의 차이를 설명할 수 없었음
 오히려 offer type이나 difficulty, channel의 설계를 바꿔서 완료율의 차이를 없애는 것이 중요해 보임</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2310,6 +2300,20 @@
   </si>
   <si>
     <t>근거 가설(No.)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>링크</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>디자인: 시철, 서영, 서현(채택)
+제작: 시철</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>발표자료 준비: 시철
+발표:</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2905,7 +2909,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="124">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3150,6 +3154,16 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3257,22 +3271,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12049,8 +12047,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="220981" y="1805623"/>
-          <a:ext cx="2100172" cy="447540"/>
+          <a:off x="173001" y="1826087"/>
+          <a:ext cx="2123975" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -12149,8 +12147,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="234089" y="1818731"/>
-        <a:ext cx="2073956" cy="421324"/>
+        <a:off x="186258" y="1839344"/>
+        <a:ext cx="2097461" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{ED5992BD-91A0-44DC-B026-C230E027754F}">
@@ -12160,8 +12158,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="16874489">
-          <a:off x="1581876" y="1121529"/>
-          <a:ext cx="1836586" cy="14378"/>
+          <a:off x="1549321" y="1134321"/>
+          <a:ext cx="1857401" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -12175,7 +12173,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1836586" y="7189"/>
+                <a:pt x="1857401" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -12234,8 +12232,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2454255" y="1082803"/>
-        <a:ext cx="91829" cy="91829"/>
+        <a:off x="2431586" y="1095075"/>
+        <a:ext cx="92870" cy="92870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{EB7188F2-1357-4748-A44C-AB5D4A48F40F}">
@@ -12245,8 +12243,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2679186" y="4273"/>
-          <a:ext cx="1080487" cy="447540"/>
+          <a:off x="2659066" y="4321"/>
+          <a:ext cx="1092733" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -12321,8 +12319,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2692294" y="17381"/>
-        <a:ext cx="1054271" cy="421324"/>
+        <a:off x="2672323" y="17578"/>
+        <a:ext cx="1066219" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7531319A-E0E5-4CB4-9F35-33254694A0D7}">
@@ -12332,8 +12330,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3759673" y="220854"/>
-          <a:ext cx="352482" cy="14378"/>
+          <a:off x="3751800" y="223438"/>
+          <a:ext cx="356477" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -12347,7 +12345,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="352482" y="7189"/>
+                <a:pt x="356477" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -12406,8 +12404,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3927103" y="219231"/>
-        <a:ext cx="17624" cy="17624"/>
+        <a:off x="3921127" y="221715"/>
+        <a:ext cx="17823" cy="17823"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{8F385C2E-83EB-470A-8A65-12C51C60EB27}">
@@ -12417,8 +12415,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4112156" y="4273"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="4108278" y="4321"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -12517,8 +12515,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4125264" y="17381"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="4121535" y="17578"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{71327523-F24D-4A9E-8CA7-7C0E6A96618A}">
@@ -12528,8 +12526,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17132988">
-          <a:off x="1832388" y="1378865"/>
-          <a:ext cx="1335563" cy="14378"/>
+          <a:off x="1802671" y="1394574"/>
+          <a:ext cx="1350699" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -12543,7 +12541,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1335563" y="7189"/>
+                <a:pt x="1350699" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -12602,8 +12600,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2466780" y="1352664"/>
-        <a:ext cx="66778" cy="66778"/>
+        <a:off x="2444254" y="1367995"/>
+        <a:ext cx="67534" cy="67534"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{08B2E005-DF35-41E7-A396-CA02C3B8D0A4}">
@@ -12613,8 +12611,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2679186" y="518944"/>
-          <a:ext cx="1080487" cy="447540"/>
+          <a:off x="2659066" y="524826"/>
+          <a:ext cx="1092733" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -12689,8 +12687,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2692294" y="532052"/>
-        <a:ext cx="1054271" cy="421324"/>
+        <a:off x="2672323" y="538083"/>
+        <a:ext cx="1066219" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E113C6B3-F5C2-41D9-9727-BB430EAD3818}">
@@ -12700,8 +12698,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3759673" y="735525"/>
-          <a:ext cx="358032" cy="14378"/>
+          <a:off x="3751800" y="743943"/>
+          <a:ext cx="362090" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -12715,7 +12713,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="358032" y="7189"/>
+                <a:pt x="362090" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -12774,8 +12772,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3929739" y="733763"/>
-        <a:ext cx="17901" cy="17901"/>
+        <a:off x="3923793" y="742080"/>
+        <a:ext cx="18104" cy="18104"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{53F03F28-ED40-4762-8125-AFFEEA792A72}">
@@ -12785,8 +12783,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4117706" y="518944"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="4113890" y="524826"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -12909,8 +12907,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4130814" y="532052"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="4127147" y="538083"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{806C8330-1E37-41AD-AEEE-3552A4162510}">
@@ -12920,8 +12918,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17692822">
-          <a:off x="2074675" y="1636200"/>
-          <a:ext cx="850988" cy="14378"/>
+          <a:off x="2047704" y="1654826"/>
+          <a:ext cx="860633" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -12935,7 +12933,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="850988" y="7189"/>
+                <a:pt x="860633" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -12994,8 +12992,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2478895" y="1622115"/>
-        <a:ext cx="42549" cy="42549"/>
+        <a:off x="2456505" y="1640499"/>
+        <a:ext cx="43031" cy="43031"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{3BC1DAB2-4FEF-42C9-A10F-0690E2903498}">
@@ -13005,8 +13003,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2679186" y="1033615"/>
-          <a:ext cx="1080487" cy="447540"/>
+          <a:off x="2659066" y="1045330"/>
+          <a:ext cx="1092733" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -13097,8 +13095,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2692294" y="1046723"/>
-        <a:ext cx="1054271" cy="421324"/>
+        <a:off x="2672323" y="1058587"/>
+        <a:ext cx="1066219" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6BFD1C16-8154-4C15-AF72-E53B38C4A146}">
@@ -13108,8 +13106,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3759673" y="1250197"/>
-          <a:ext cx="358032" cy="14378"/>
+          <a:off x="3751800" y="1264447"/>
+          <a:ext cx="362090" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -13123,7 +13121,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="358032" y="7189"/>
+                <a:pt x="362090" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -13182,8 +13180,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3929739" y="1248435"/>
-        <a:ext cx="17901" cy="17901"/>
+        <a:off x="3923793" y="1262584"/>
+        <a:ext cx="18104" cy="18104"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1A251137-9CB6-43D7-B47D-0D220C30894C}">
@@ -13193,8 +13191,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4117706" y="1033615"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="4113890" y="1045330"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -13317,8 +13315,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4130814" y="1046723"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="4127147" y="1058587"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{227E0FEF-1368-4562-AD55-940C6A450E91}">
@@ -13328,8 +13326,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="3310531">
-          <a:off x="2186691" y="2279540"/>
-          <a:ext cx="626956" cy="14378"/>
+          <a:off x="2160990" y="2305456"/>
+          <a:ext cx="634061" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -13343,7 +13341,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="626956" y="7189"/>
+                <a:pt x="634061" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -13402,8 +13400,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2484496" y="2271055"/>
-        <a:ext cx="31347" cy="31347"/>
+        <a:off x="2462170" y="2296794"/>
+        <a:ext cx="31703" cy="31703"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{146FB508-948A-484E-B54F-2A63CE5492FA}">
@@ -13413,8 +13411,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2679186" y="2320294"/>
-          <a:ext cx="1080487" cy="447540"/>
+          <a:off x="2659066" y="2346591"/>
+          <a:ext cx="1092733" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -13489,8 +13487,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2692294" y="2333402"/>
-        <a:ext cx="1054271" cy="421324"/>
+        <a:off x="2672323" y="2359848"/>
+        <a:ext cx="1066219" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1583A4D8-C48C-400A-B5A1-D8E8188A1E57}">
@@ -13500,8 +13498,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17692822">
-          <a:off x="3513195" y="2150872"/>
-          <a:ext cx="850988" cy="14378"/>
+          <a:off x="3502528" y="2175330"/>
+          <a:ext cx="860633" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -13515,7 +13513,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="850988" y="7189"/>
+                <a:pt x="860633" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -13574,8 +13572,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3917415" y="2136786"/>
-        <a:ext cx="42549" cy="42549"/>
+        <a:off x="3911329" y="2161003"/>
+        <a:ext cx="43031" cy="43031"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{985FE1E2-4CA8-4AC7-A474-DEECC9A2BB80}">
@@ -13585,8 +13583,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4117706" y="1548287"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="4113890" y="1565835"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -13677,8 +13675,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4130814" y="1561395"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="4127147" y="1579092"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{16F44D37-2601-482A-9095-0B3E8E10E520}">
@@ -13688,8 +13686,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19457599">
-          <a:off x="3718230" y="2408207"/>
-          <a:ext cx="440918" cy="14378"/>
+          <a:off x="3709887" y="2435583"/>
+          <a:ext cx="445915" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -13703,7 +13701,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="440918" y="7189"/>
+                <a:pt x="445915" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -13762,8 +13760,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3927667" y="2404373"/>
-        <a:ext cx="22045" cy="22045"/>
+        <a:off x="3921697" y="2431624"/>
+        <a:ext cx="22295" cy="22295"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{2D542640-C237-42B5-8470-73084719F8F3}">
@@ -13773,8 +13771,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4117706" y="2062958"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="4113890" y="2086339"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -13865,8 +13863,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4130814" y="2076066"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="4127147" y="2099596"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9A75AB13-86A0-459A-8B2B-E8037D74B447}">
@@ -13876,8 +13874,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2142401">
-          <a:off x="3718230" y="2665543"/>
-          <a:ext cx="440918" cy="14378"/>
+          <a:off x="3709887" y="2695835"/>
+          <a:ext cx="445915" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -13891,7 +13889,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="440918" y="7189"/>
+                <a:pt x="445915" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -13950,8 +13948,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3927667" y="2661709"/>
-        <a:ext cx="22045" cy="22045"/>
+        <a:off x="3921697" y="2691876"/>
+        <a:ext cx="22295" cy="22295"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{106C3051-36E0-4DB2-B006-BD51244834C6}">
@@ -13961,8 +13959,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4117706" y="2577630"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="4113890" y="2606844"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -14053,8 +14051,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4130814" y="2590738"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="4127147" y="2620101"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6562E267-52DD-4DC6-81E6-A0E9307367D6}">
@@ -14064,8 +14062,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="3907178">
-          <a:off x="3513195" y="2922879"/>
-          <a:ext cx="850988" cy="14378"/>
+          <a:off x="3502528" y="2956087"/>
+          <a:ext cx="860633" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -14079,7 +14077,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="850988" y="7189"/>
+                <a:pt x="860633" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -14138,8 +14136,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3917415" y="2908793"/>
-        <a:ext cx="42549" cy="42549"/>
+        <a:off x="3911329" y="2941760"/>
+        <a:ext cx="43031" cy="43031"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{220D319D-36C0-42A0-A946-F197C4269C14}">
@@ -14149,8 +14147,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4117706" y="3092301"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="4113890" y="3127348"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -14241,8 +14239,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4130814" y="3105409"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="4127147" y="3140605"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4332858F-88A7-466E-8722-8833A7B96598}">
@@ -14252,8 +14250,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="4725511">
-          <a:off x="1581876" y="2922879"/>
-          <a:ext cx="1836586" cy="14378"/>
+          <a:off x="1549321" y="2956087"/>
+          <a:ext cx="1857401" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -14267,7 +14265,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1836586" y="7189"/>
+                <a:pt x="1857401" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -14322,8 +14320,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2454255" y="2884153"/>
-        <a:ext cx="91829" cy="91829"/>
+        <a:off x="2431586" y="2916841"/>
+        <a:ext cx="92870" cy="92870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1479FCFA-85A4-438D-B5D0-346DFAD5924D}">
@@ -14333,8 +14331,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2679186" y="3606973"/>
-          <a:ext cx="1080487" cy="447540"/>
+          <a:off x="2659066" y="3647853"/>
+          <a:ext cx="1092733" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -14409,8 +14407,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2692294" y="3620081"/>
-        <a:ext cx="1054271" cy="421324"/>
+        <a:off x="2672323" y="3661110"/>
+        <a:ext cx="1066219" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E6D0412B-4D85-432B-BE35-F277BFD00B03}">
@@ -14420,8 +14418,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3759673" y="3823554"/>
-          <a:ext cx="358032" cy="14378"/>
+          <a:off x="3751800" y="3866970"/>
+          <a:ext cx="362090" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -14435,7 +14433,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="358032" y="7189"/>
+                <a:pt x="362090" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -14490,8 +14488,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3929739" y="3821792"/>
-        <a:ext cx="17901" cy="17901"/>
+        <a:off x="3923793" y="3865107"/>
+        <a:ext cx="18104" cy="18104"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{CE9AFD94-4037-4F8B-B49B-020818B5CBB5}">
@@ -14501,8 +14499,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4117706" y="3606973"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="4113890" y="3647853"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -14609,8 +14607,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4130814" y="3620081"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="4127147" y="3661110"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B460AB31-448C-42B6-9C6B-D3CF5013B4F6}">
@@ -14620,8 +14618,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="88714" y="4636316"/>
-          <a:ext cx="1800813" cy="447540"/>
+          <a:off x="39236" y="4688862"/>
+          <a:ext cx="1821222" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -14746,8 +14744,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="101822" y="4649424"/>
-        <a:ext cx="1774597" cy="421324"/>
+        <a:off x="52493" y="4702119"/>
+        <a:ext cx="1794708" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{C120D3E5-D1A3-4DC1-848B-C37D9DDE2012}">
@@ -14757,8 +14755,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="18752467">
-          <a:off x="1776407" y="4595561"/>
-          <a:ext cx="698529" cy="14378"/>
+          <a:off x="1746056" y="4647727"/>
+          <a:ext cx="706446" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -14772,7 +14770,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="698529" y="7189"/>
+                <a:pt x="706446" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -14827,8 +14825,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2108209" y="4585287"/>
-        <a:ext cx="34926" cy="34926"/>
+        <a:off x="2081618" y="4637255"/>
+        <a:ext cx="35322" cy="35322"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6F01F0AA-74B9-49DB-A456-B8979039EB51}">
@@ -14838,8 +14836,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2361817" y="4121644"/>
-          <a:ext cx="1080487" cy="447540"/>
+          <a:off x="2338101" y="4168357"/>
+          <a:ext cx="1092733" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -14912,8 +14910,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2374925" y="4134752"/>
-        <a:ext cx="1054271" cy="421324"/>
+        <a:off x="2351358" y="4181614"/>
+        <a:ext cx="1066219" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{F5E69F9A-2631-4A2D-BC76-B4BD9B08D019}">
@@ -14923,8 +14921,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3442305" y="4338225"/>
-          <a:ext cx="364020" cy="14378"/>
+          <a:off x="3430834" y="4387475"/>
+          <a:ext cx="368146" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -14938,7 +14936,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="364020" y="7189"/>
+                <a:pt x="368146" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -14993,8 +14991,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3615214" y="4336314"/>
-        <a:ext cx="18201" cy="18201"/>
+        <a:off x="3605704" y="4385460"/>
+        <a:ext cx="18407" cy="18407"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{69EDA0B0-D39D-4C93-8B8D-10889C581D9E}">
@@ -15004,8 +15002,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3806325" y="4121644"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="3798980" y="4168357"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -15078,8 +15076,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3819433" y="4134752"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="3812237" y="4181614"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{AC23C890-5E27-4DC3-9BF7-2C50218200D9}">
@@ -15089,8 +15087,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="1889527" y="4852897"/>
-          <a:ext cx="472289" cy="14378"/>
+          <a:off x="1860458" y="4907979"/>
+          <a:ext cx="477642" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -15104,7 +15102,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="472289" y="7189"/>
+                <a:pt x="477642" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -15159,8 +15157,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2113865" y="4848279"/>
-        <a:ext cx="23614" cy="23614"/>
+        <a:off x="2087338" y="4903227"/>
+        <a:ext cx="23882" cy="23882"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B4CF3050-E538-4710-99C5-FB5B2F28D116}">
@@ -15170,8 +15168,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2361817" y="4636316"/>
-          <a:ext cx="1080487" cy="447540"/>
+          <a:off x="2338101" y="4688862"/>
+          <a:ext cx="1092733" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -15244,8 +15242,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2374925" y="4649424"/>
-        <a:ext cx="1054271" cy="421324"/>
+        <a:off x="2351358" y="4702119"/>
+        <a:ext cx="1066219" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{55492AE0-989E-4368-96E6-8609B6786079}">
@@ -15255,8 +15253,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3442305" y="4852897"/>
-          <a:ext cx="364020" cy="14378"/>
+          <a:off x="3430834" y="4907979"/>
+          <a:ext cx="368146" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -15270,7 +15268,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="364020" y="7189"/>
+                <a:pt x="368146" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -15325,8 +15323,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3615214" y="4850985"/>
-        <a:ext cx="18201" cy="18201"/>
+        <a:off x="3605704" y="4905964"/>
+        <a:ext cx="18407" cy="18407"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{99BD4B49-7654-4BFC-93A2-73715A94DAC0}">
@@ -15336,8 +15334,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3806325" y="4636316"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="3798980" y="4688862"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -15454,8 +15452,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3819433" y="4649424"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="3812237" y="4702119"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{48D36C81-0EEF-4879-868D-73109D1A61EF}">
@@ -15465,8 +15463,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2847533">
-          <a:off x="1776407" y="5110232"/>
-          <a:ext cx="698529" cy="14378"/>
+          <a:off x="1746056" y="5168231"/>
+          <a:ext cx="706446" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -15480,7 +15478,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="698529" y="7189"/>
+                <a:pt x="706446" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -15535,8 +15533,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2108209" y="5099958"/>
-        <a:ext cx="34926" cy="34926"/>
+        <a:off x="2081618" y="5157759"/>
+        <a:ext cx="35322" cy="35322"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E0C7A212-1F93-473A-8909-15A6780CBC2F}">
@@ -15546,8 +15544,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="2361817" y="5150987"/>
-          <a:ext cx="1080487" cy="447540"/>
+          <a:off x="2338101" y="5209366"/>
+          <a:ext cx="1092733" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -15620,8 +15618,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2374925" y="5164095"/>
-        <a:ext cx="1054271" cy="421324"/>
+        <a:off x="2351358" y="5222623"/>
+        <a:ext cx="1066219" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4D54B04B-F98B-4577-8925-91ECEF877996}">
@@ -15631,8 +15629,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3442305" y="5367568"/>
-          <a:ext cx="376041" cy="14378"/>
+          <a:off x="3430834" y="5428484"/>
+          <a:ext cx="380303" cy="14378"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -15646,7 +15644,7 @@
                 <a:pt x="0" y="7189"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="376041" y="7189"/>
+                <a:pt x="380303" y="7189"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -15701,8 +15699,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3620924" y="5365356"/>
-        <a:ext cx="18802" cy="18802"/>
+        <a:off x="3611478" y="5426165"/>
+        <a:ext cx="19015" cy="19015"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{540CB623-D523-4AD6-BF5D-A946D7B052E6}">
@@ -15712,8 +15710,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3818346" y="5150987"/>
-          <a:ext cx="4682122" cy="447540"/>
+          <a:off x="3811137" y="5209366"/>
+          <a:ext cx="4735188" cy="452612"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -15831,8 +15829,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3831454" y="5164095"/>
-        <a:ext cx="4655906" cy="421324"/>
+        <a:off x="3824394" y="5222623"/>
+        <a:ext cx="4708674" cy="426098"/>
       </dsp:txXfrm>
     </dsp:sp>
   </dsp:spTree>
@@ -15854,8 +15852,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9182" y="3307680"/>
-          <a:ext cx="1177681" cy="361541"/>
+          <a:off x="6990" y="3359481"/>
+          <a:ext cx="1175976" cy="361018"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -15933,8 +15931,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="19771" y="3318269"/>
-        <a:ext cx="1156503" cy="340363"/>
+        <a:off x="17564" y="3370055"/>
+        <a:ext cx="1154828" cy="339870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7667B88B-738E-4E27-80A6-15B1E3AED5F8}">
@@ -15944,8 +15942,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="16719080">
-          <a:off x="572912" y="2769909"/>
-          <a:ext cx="1445308" cy="8220"/>
+          <a:off x="569904" y="2822558"/>
+          <a:ext cx="1443216" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -15956,10 +15954,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1445308" y="4110"/>
+                <a:pt x="1443216" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16018,8 +16016,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1259433" y="2737887"/>
-        <a:ext cx="72265" cy="72265"/>
+        <a:off x="1255432" y="2790512"/>
+        <a:ext cx="72160" cy="72160"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D9E30B0F-B6EE-4B8A-B3A5-5AD7E4CFBC12}">
@@ -16029,8 +16027,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="1404269" y="1878817"/>
-          <a:ext cx="1444638" cy="361541"/>
+          <a:off x="1400057" y="1932685"/>
+          <a:ext cx="1442547" cy="361018"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16121,8 +16119,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1414858" y="1889406"/>
-        <a:ext cx="1423460" cy="340363"/>
+        <a:off x="1410631" y="1943259"/>
+        <a:ext cx="1421399" cy="339870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{ED5992BD-91A0-44DC-B026-C230E027754F}">
@@ -16132,8 +16130,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="16757427">
-          <a:off x="2284276" y="1390976"/>
-          <a:ext cx="1346666" cy="8220"/>
+          <a:off x="2278791" y="1445622"/>
+          <a:ext cx="1344717" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16144,10 +16142,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1346666" y="4110"/>
+                <a:pt x="1344717" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16206,8 +16204,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2923942" y="1361420"/>
-        <a:ext cx="67333" cy="67333"/>
+        <a:off x="2917531" y="1416037"/>
+        <a:ext cx="67235" cy="67235"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{EB7188F2-1357-4748-A44C-AB5D4A48F40F}">
@@ -16217,8 +16215,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3066312" y="549815"/>
-          <a:ext cx="1407331" cy="361541"/>
+          <a:off x="3059694" y="605607"/>
+          <a:ext cx="1405294" cy="361018"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16288,8 +16286,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3076901" y="560404"/>
-        <a:ext cx="1386153" cy="340363"/>
+        <a:off x="3070268" y="616181"/>
+        <a:ext cx="1384146" cy="339870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7531319A-E0E5-4CB4-9F35-33254694A0D7}">
@@ -16299,8 +16297,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17860289">
-          <a:off x="4350219" y="522390"/>
-          <a:ext cx="460883" cy="8220"/>
+          <a:off x="4341743" y="578293"/>
+          <a:ext cx="460216" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16311,10 +16309,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="460883" y="4110"/>
+                <a:pt x="460216" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16373,8 +16371,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4569139" y="514979"/>
-        <a:ext cx="23044" cy="23044"/>
+        <a:off x="4560346" y="570821"/>
+        <a:ext cx="23010" cy="23010"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{8F385C2E-83EB-470A-8A65-12C51C60EB27}">
@@ -16384,8 +16382,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4687678" y="140049"/>
-          <a:ext cx="1776175" cy="364734"/>
+          <a:off x="4678714" y="196434"/>
+          <a:ext cx="1773604" cy="364206"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16455,8 +16453,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4698361" y="150732"/>
-        <a:ext cx="1754809" cy="343368"/>
+        <a:off x="4689381" y="207101"/>
+        <a:ext cx="1752270" cy="342872"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{8EC6EEF9-E6D8-4DE2-A6DD-BB50B40A5CF0}">
@@ -16466,8 +16464,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6463853" y="318305"/>
-          <a:ext cx="220774" cy="8220"/>
+          <a:off x="6452318" y="374503"/>
+          <a:ext cx="220454" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16478,10 +16476,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="220774" y="4110"/>
+                <a:pt x="220454" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16536,8 +16534,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6568721" y="316896"/>
-        <a:ext cx="11038" cy="11038"/>
+        <a:off x="6557034" y="373026"/>
+        <a:ext cx="11022" cy="11022"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{31CFEB2D-0887-4520-AF04-1E3C38912960}">
@@ -16547,8 +16545,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6684628" y="140049"/>
-          <a:ext cx="3167897" cy="364734"/>
+          <a:off x="6672773" y="196434"/>
+          <a:ext cx="3163311" cy="364206"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16634,8 +16632,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6695311" y="150732"/>
-        <a:ext cx="3146531" cy="343368"/>
+        <a:off x="6683440" y="207101"/>
+        <a:ext cx="3141977" cy="342872"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{602438BB-CBF9-49AF-AB0A-D57EA2C10BE2}">
@@ -16645,8 +16643,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9852525" y="318305"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9836085" y="374503"/>
+          <a:ext cx="217090" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16657,10 +16655,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="217090" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16715,8 +16713,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9955792" y="316981"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9939203" y="373110"/>
+        <a:ext cx="10854" cy="10854"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{57D97F9E-094F-4C3F-82B2-5A689BC4D082}">
@@ -16726,8 +16724,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10069930" y="146189"/>
-          <a:ext cx="1807704" cy="352453"/>
+          <a:off x="10053175" y="202565"/>
+          <a:ext cx="1805087" cy="351943"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16824,8 +16822,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10080253" y="156512"/>
-        <a:ext cx="1787058" cy="331807"/>
+        <a:off x="10063483" y="212873"/>
+        <a:ext cx="1784471" cy="331327"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B3B4155B-F64B-452E-AEBC-36FE76B0BD69}">
@@ -16835,8 +16833,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="21585916">
-          <a:off x="4473642" y="726030"/>
-          <a:ext cx="217406" cy="8220"/>
+          <a:off x="4464988" y="781638"/>
+          <a:ext cx="217091" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16847,10 +16845,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217406" y="4110"/>
+                <a:pt x="217091" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16905,8 +16903,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4576910" y="724705"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="4568107" y="780244"/>
+        <a:ext cx="10854" cy="10854"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D20B6C81-A2D9-4E8E-80C0-968EFF7F89E1}">
@@ -16916,8 +16914,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4691048" y="547328"/>
-          <a:ext cx="1776175" cy="364734"/>
+          <a:off x="4682079" y="603123"/>
+          <a:ext cx="1773604" cy="364206"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16987,8 +16985,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4701731" y="558011"/>
-        <a:ext cx="1754809" cy="343368"/>
+        <a:off x="4692746" y="613790"/>
+        <a:ext cx="1752270" cy="342872"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7FE58BCF-6B0D-48A2-8DDE-611A1D34A4D6}">
@@ -16998,8 +16996,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6467223" y="725585"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="6455683" y="781193"/>
+          <a:ext cx="217090" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17010,10 +17008,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="217090" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17068,8 +17066,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6570490" y="724260"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="6558801" y="779799"/>
+        <a:ext cx="10854" cy="10854"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{629314FA-FCA6-45B9-99A7-2C2196A96D5C}">
@@ -17079,8 +17077,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6684628" y="547328"/>
-          <a:ext cx="3167897" cy="364734"/>
+          <a:off x="6672773" y="603123"/>
+          <a:ext cx="3163311" cy="364206"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17179,8 +17177,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6695311" y="558011"/>
-        <a:ext cx="3146531" cy="343368"/>
+        <a:off x="6683440" y="613790"/>
+        <a:ext cx="3141977" cy="342872"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{CCF144EB-A097-46BE-8FF7-BE5C7A394E2A}">
@@ -17190,8 +17188,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9852525" y="725585"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9836085" y="781193"/>
+          <a:ext cx="217090" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17202,10 +17200,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="217090" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17260,8 +17258,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9955792" y="724260"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9939203" y="779799"/>
+        <a:ext cx="10854" cy="10854"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9EE0F2D9-F39B-4921-9EAC-DBA04DC260DD}">
@@ -17271,8 +17269,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10069930" y="545546"/>
-          <a:ext cx="1807704" cy="368297"/>
+          <a:off x="10053175" y="601345"/>
+          <a:ext cx="1805087" cy="367764"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17355,8 +17353,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10080717" y="556333"/>
-        <a:ext cx="1786130" cy="346723"/>
+        <a:off x="10063946" y="612116"/>
+        <a:ext cx="1783545" cy="346222"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6169CD61-5E3A-4096-AA5A-91A22C397918}">
@@ -17366,8 +17364,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="3717526">
-          <a:off x="4351116" y="930560"/>
-          <a:ext cx="462458" cy="8220"/>
+          <a:off x="4342640" y="985872"/>
+          <a:ext cx="461788" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17378,10 +17376,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="462458" y="4110"/>
+                <a:pt x="461788" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17436,8 +17434,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4570784" y="923109"/>
-        <a:ext cx="23122" cy="23122"/>
+        <a:off x="4561989" y="978361"/>
+        <a:ext cx="23089" cy="23089"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D5FDB947-B70B-4493-B9F9-83A45503DA23}">
@@ -17447,8 +17445,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4691048" y="956388"/>
-          <a:ext cx="1776175" cy="364734"/>
+          <a:off x="4682079" y="1011592"/>
+          <a:ext cx="1773604" cy="364206"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17518,8 +17516,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4701731" y="967071"/>
-        <a:ext cx="1754809" cy="343368"/>
+        <a:off x="4692746" y="1022259"/>
+        <a:ext cx="1752270" cy="342872"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9EDF68AF-E14B-40BF-AB6D-4B01635D735A}">
@@ -17529,8 +17527,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6467223" y="1134645"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="6455683" y="1189662"/>
+          <a:ext cx="217090" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17541,10 +17539,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="217090" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17599,8 +17597,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6570490" y="1133321"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="6558801" y="1188268"/>
+        <a:ext cx="10854" cy="10854"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{5A5C0991-25ED-4076-91F2-80A2EEFC811E}">
@@ -17610,8 +17608,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6684628" y="956388"/>
-          <a:ext cx="3167897" cy="364734"/>
+          <a:off x="6672773" y="1011592"/>
+          <a:ext cx="3163311" cy="364206"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17745,8 +17743,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6695311" y="967071"/>
-        <a:ext cx="3146531" cy="343368"/>
+        <a:off x="6683440" y="1022259"/>
+        <a:ext cx="3141977" cy="342872"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{723082D3-A8E2-4807-89B5-C74C600B949E}">
@@ -17756,8 +17754,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9852525" y="1134645"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9836085" y="1189662"/>
+          <a:ext cx="217090" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17768,10 +17766,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="217090" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17826,8 +17824,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9955792" y="1133321"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9939203" y="1188268"/>
+        <a:ext cx="10854" cy="10854"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{05E664DE-AAC0-4D52-9AA4-DE55CA572420}">
@@ -17837,8 +17835,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10069930" y="954607"/>
-          <a:ext cx="1807704" cy="368297"/>
+          <a:off x="10053175" y="1009813"/>
+          <a:ext cx="1805087" cy="367764"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17908,8 +17906,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10080717" y="965394"/>
-        <a:ext cx="1786130" cy="346723"/>
+        <a:off x="10063946" y="1020584"/>
+        <a:ext cx="1783545" cy="346222"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{16F44D37-2601-482A-9095-0B3E8E10E520}">
@@ -17919,8 +17917,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="1505741">
-          <a:off x="2837576" y="2106387"/>
-          <a:ext cx="240066" cy="8220"/>
+          <a:off x="2831290" y="2159997"/>
+          <a:ext cx="239719" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17931,10 +17929,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="240066" y="4110"/>
+                <a:pt x="239719" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17993,8 +17991,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2951607" y="2104496"/>
-        <a:ext cx="12003" cy="12003"/>
+        <a:off x="2945156" y="2158037"/>
+        <a:ext cx="11985" cy="11985"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{2D542640-C237-42B5-8470-73084719F8F3}">
@@ -18004,8 +18002,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3066312" y="1980637"/>
-          <a:ext cx="1407331" cy="361541"/>
+          <a:off x="3059694" y="2034358"/>
+          <a:ext cx="1405294" cy="361018"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -18075,8 +18073,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3076901" y="1991226"/>
-        <a:ext cx="1386153" cy="340363"/>
+        <a:off x="3070268" y="2044932"/>
+        <a:ext cx="1384146" cy="339870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{BFCFD3BD-878E-4ADC-81DA-3641DCD660A7}">
@@ -18086,8 +18084,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17370601">
-          <a:off x="4256862" y="1850501"/>
-          <a:ext cx="650967" cy="8220"/>
+          <a:off x="4248521" y="1904482"/>
+          <a:ext cx="650025" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18098,10 +18096,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="650967" y="4110"/>
+                <a:pt x="650025" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18156,8 +18154,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4566071" y="1838338"/>
-        <a:ext cx="32548" cy="32548"/>
+        <a:off x="4557283" y="1892265"/>
+        <a:ext cx="32501" cy="32501"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{911F1DD5-D3D2-4321-A1A5-7E2BAE25AAD5}">
@@ -18167,8 +18165,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4691048" y="1365449"/>
-          <a:ext cx="1776175" cy="364734"/>
+          <a:off x="4682079" y="1420060"/>
+          <a:ext cx="1773604" cy="364206"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -18238,8 +18236,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4701731" y="1376132"/>
-        <a:ext cx="1754809" cy="343368"/>
+        <a:off x="4692746" y="1430727"/>
+        <a:ext cx="1752270" cy="342872"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{F4CAC384-240B-4811-A7FE-5EF39454FD0A}">
@@ -18249,8 +18247,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6467223" y="1543706"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="6455683" y="1598130"/>
+          <a:ext cx="217090" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18261,10 +18259,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="217090" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18319,8 +18317,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6570490" y="1542381"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="6558801" y="1596737"/>
+        <a:ext cx="10854" cy="10854"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{00847D60-C67D-487A-B918-B0C406DE6A20}">
@@ -18330,8 +18328,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6684628" y="1365449"/>
-          <a:ext cx="3167897" cy="364734"/>
+          <a:off x="6672773" y="1420060"/>
+          <a:ext cx="3163311" cy="364206"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -18441,8 +18439,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6695311" y="1376132"/>
-        <a:ext cx="3146531" cy="343368"/>
+        <a:off x="6683440" y="1430727"/>
+        <a:ext cx="3141977" cy="342872"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7682FEBA-2A8A-4CEB-BAD3-CAC6D62452E9}">
@@ -18452,8 +18450,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9852525" y="1543706"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9836085" y="1598130"/>
+          <a:ext cx="217090" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18464,10 +18462,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="217090" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18522,8 +18520,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9955792" y="1542381"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9939203" y="1596737"/>
+        <a:ext cx="10854" cy="10854"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4C2C55F9-D12D-4BE1-85AD-8FAFF8B344C7}">
@@ -18533,8 +18531,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10069930" y="1363668"/>
-          <a:ext cx="1807704" cy="368297"/>
+          <a:off x="10053175" y="1418282"/>
+          <a:ext cx="1805087" cy="367764"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -18652,8 +18650,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10080717" y="1374455"/>
-        <a:ext cx="1786130" cy="346723"/>
+        <a:off x="10063946" y="1429053"/>
+        <a:ext cx="1783545" cy="346222"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6A4076F7-5C10-4205-AF7B-34977DAE41B6}">
@@ -18663,8 +18661,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19004863">
-          <a:off x="4433100" y="2055032"/>
-          <a:ext cx="298492" cy="8220"/>
+          <a:off x="4424504" y="2108716"/>
+          <a:ext cx="298059" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18675,10 +18673,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="298492" y="4110"/>
+                <a:pt x="298059" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18733,8 +18731,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4574883" y="2051680"/>
-        <a:ext cx="14924" cy="14924"/>
+        <a:off x="4566082" y="2105298"/>
+        <a:ext cx="14902" cy="14902"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D2D6EBAC-87C6-4589-B626-76CA00356F2A}">
@@ -18744,8 +18742,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4691048" y="1774510"/>
-          <a:ext cx="1776175" cy="364734"/>
+          <a:off x="4682079" y="1828529"/>
+          <a:ext cx="1773604" cy="364206"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -18815,8 +18813,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4701731" y="1785193"/>
-        <a:ext cx="1754809" cy="343368"/>
+        <a:off x="4692746" y="1839196"/>
+        <a:ext cx="1752270" cy="342872"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4CEC118E-B718-4A3D-A714-E879160F0F50}">
@@ -18826,8 +18824,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6467223" y="1952767"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="6455683" y="2006599"/>
+          <a:ext cx="217090" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18838,10 +18836,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="217090" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18896,8 +18894,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6570490" y="1951442"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="6558801" y="2005205"/>
+        <a:ext cx="10854" cy="10854"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{96C9B796-69AA-48A9-AB67-0FE5F7CEFC9D}">
@@ -18907,8 +18905,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6684628" y="1774510"/>
-          <a:ext cx="3167897" cy="364734"/>
+          <a:off x="6672773" y="1828529"/>
+          <a:ext cx="3163311" cy="364206"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19002,8 +19000,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6695311" y="1785193"/>
-        <a:ext cx="3146531" cy="343368"/>
+        <a:off x="6683440" y="1839196"/>
+        <a:ext cx="3141977" cy="342872"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{0C4A9E51-DEA5-4AC0-B8EC-F712BFE3BA51}">
@@ -19013,8 +19011,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9852525" y="1952767"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9836085" y="2006599"/>
+          <a:ext cx="217090" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19025,10 +19023,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="217090" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19083,8 +19081,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9955792" y="1951442"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9939203" y="2005205"/>
+        <a:ext cx="10854" cy="10854"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{829A6295-4379-4C15-BF91-56D56B48CA13}">
@@ -19094,8 +19092,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10069930" y="1772728"/>
-          <a:ext cx="1807704" cy="368297"/>
+          <a:off x="10053175" y="1826750"/>
+          <a:ext cx="1805087" cy="367764"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19181,8 +19179,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10080717" y="1783515"/>
-        <a:ext cx="1786130" cy="346723"/>
+        <a:off x="10063946" y="1837521"/>
+        <a:ext cx="1783545" cy="346222"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{15251D3B-5937-4D92-B910-59FBB0B78504}">
@@ -19192,8 +19190,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2595137">
-          <a:off x="4433100" y="2259562"/>
-          <a:ext cx="298492" cy="8220"/>
+          <a:off x="4424504" y="2312950"/>
+          <a:ext cx="298059" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19204,10 +19202,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="298492" y="4110"/>
+                <a:pt x="298059" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19262,8 +19260,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4574883" y="2256210"/>
-        <a:ext cx="14924" cy="14924"/>
+        <a:off x="4566082" y="2309532"/>
+        <a:ext cx="14902" cy="14902"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{55C8ECFC-533A-4D04-B170-164B29EE9A7D}">
@@ -19273,8 +19271,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4691048" y="2183570"/>
-          <a:ext cx="1776175" cy="364734"/>
+          <a:off x="4682079" y="2236998"/>
+          <a:ext cx="1773604" cy="364206"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19344,8 +19342,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4701731" y="2194253"/>
-        <a:ext cx="1754809" cy="343368"/>
+        <a:off x="4692746" y="2247665"/>
+        <a:ext cx="1752270" cy="342872"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A63458DA-4732-44A8-AAAD-101471030A2E}">
@@ -19355,8 +19353,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6467223" y="2361827"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="6455683" y="2415067"/>
+          <a:ext cx="217090" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19367,10 +19365,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="217090" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19425,8 +19423,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6570490" y="2360502"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="6558801" y="2413674"/>
+        <a:ext cx="10854" cy="10854"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{3CFC9EAC-3C3A-42EE-A809-37090C958CCC}">
@@ -19436,8 +19434,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6684628" y="2183570"/>
-          <a:ext cx="3167897" cy="364734"/>
+          <a:off x="6672773" y="2236998"/>
+          <a:ext cx="3163311" cy="364206"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19515,8 +19513,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6695311" y="2194253"/>
-        <a:ext cx="3146531" cy="343368"/>
+        <a:off x="6683440" y="2247665"/>
+        <a:ext cx="3141977" cy="342872"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{2E1BE310-D0FB-4439-BC13-EF25298A0AC1}">
@@ -19526,8 +19524,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9852525" y="2361827"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9836085" y="2415067"/>
+          <a:ext cx="217090" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19538,10 +19536,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="217090" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19596,8 +19594,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9955792" y="2360502"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9939203" y="2413674"/>
+        <a:ext cx="10854" cy="10854"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{05029C16-99B1-4993-B5A7-DFCE2EC4AF2D}">
@@ -19607,8 +19605,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10069930" y="2181789"/>
-          <a:ext cx="1807704" cy="368297"/>
+          <a:off x="10053175" y="2235219"/>
+          <a:ext cx="1805087" cy="367764"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19678,8 +19676,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10080717" y="2192576"/>
-        <a:ext cx="1786130" cy="346723"/>
+        <a:off x="10063946" y="2245990"/>
+        <a:ext cx="1783545" cy="346222"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7B1A1F24-5790-42BE-9800-70C6BAC67F71}">
@@ -19689,8 +19687,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="4229399">
-          <a:off x="4256862" y="2464092"/>
-          <a:ext cx="650967" cy="8220"/>
+          <a:off x="4248521" y="2517184"/>
+          <a:ext cx="650025" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19701,10 +19699,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="650967" y="4110"/>
+                <a:pt x="650025" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19759,8 +19757,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4566071" y="2451929"/>
-        <a:ext cx="32548" cy="32548"/>
+        <a:off x="4557283" y="2504967"/>
+        <a:ext cx="32501" cy="32501"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{F9E7099E-D348-4A20-924E-7B36E8E1B00D}">
@@ -19770,8 +19768,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4691048" y="2592631"/>
-          <a:ext cx="1794725" cy="364734"/>
+          <a:off x="4682079" y="2645466"/>
+          <a:ext cx="1792127" cy="364206"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19841,8 +19839,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4701731" y="2603314"/>
-        <a:ext cx="1773359" cy="343368"/>
+        <a:off x="4692746" y="2656133"/>
+        <a:ext cx="1770793" cy="342872"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{69A95BFF-166E-4390-9963-14C8F025ADBA}">
@@ -19852,8 +19850,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6485773" y="2770888"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="6474206" y="2823536"/>
+          <a:ext cx="217090" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19864,10 +19862,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="217090" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19922,8 +19920,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6589040" y="2769563"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="6577324" y="2822142"/>
+        <a:ext cx="10854" cy="10854"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{BBDCC5A6-74D1-4E37-848C-BF5D7C733A0C}">
@@ -19933,8 +19931,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6703178" y="2592631"/>
-          <a:ext cx="3167897" cy="364734"/>
+          <a:off x="6691297" y="2645466"/>
+          <a:ext cx="3163311" cy="364206"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20004,8 +20002,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6713861" y="2603314"/>
-        <a:ext cx="3146531" cy="343368"/>
+        <a:off x="6701964" y="2656133"/>
+        <a:ext cx="3141977" cy="342872"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E75A9ED0-3CF3-4FBB-B735-763677226156}">
@@ -20015,8 +20013,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9871075" y="2770888"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9854608" y="2823536"/>
+          <a:ext cx="217090" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20027,10 +20025,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="217090" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20085,8 +20083,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9974342" y="2769563"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9957726" y="2822142"/>
+        <a:ext cx="10854" cy="10854"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D255C67C-B87B-4D25-A5F4-B2880DE74996}">
@@ -20096,8 +20094,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10088480" y="2590850"/>
-          <a:ext cx="1807704" cy="368297"/>
+          <a:off x="10071698" y="2643687"/>
+          <a:ext cx="1805087" cy="367764"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20191,8 +20189,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10099267" y="2601637"/>
-        <a:ext cx="1786130" cy="346723"/>
+        <a:off x="10082469" y="2654458"/>
+        <a:ext cx="1783545" cy="346222"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{19133C7D-D6FC-4086-9EFA-C8E67C09EF92}">
@@ -20202,8 +20200,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="4842573">
-          <a:off x="2284276" y="2719978"/>
-          <a:ext cx="1346666" cy="8220"/>
+          <a:off x="2278791" y="2772700"/>
+          <a:ext cx="1344717" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20214,10 +20212,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1346666" y="4110"/>
+                <a:pt x="1344717" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20272,8 +20270,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2923942" y="2690422"/>
-        <a:ext cx="67333" cy="67333"/>
+        <a:off x="2917531" y="2743115"/>
+        <a:ext cx="67235" cy="67235"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{3A58F96D-43A0-4E22-A03B-64FF8A7610E3}">
@@ -20283,8 +20281,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3066312" y="3207818"/>
-          <a:ext cx="1407331" cy="361541"/>
+          <a:off x="3059694" y="3259763"/>
+          <a:ext cx="1405294" cy="361018"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20354,8 +20352,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3076901" y="3218407"/>
-        <a:ext cx="1386153" cy="340363"/>
+        <a:off x="3070268" y="3270337"/>
+        <a:ext cx="1384146" cy="339870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{BC1A1E23-E0C9-4175-8735-D110618B99B3}">
@@ -20365,8 +20363,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19004863">
-          <a:off x="4433100" y="3282214"/>
-          <a:ext cx="298492" cy="8220"/>
+          <a:off x="4424504" y="3334122"/>
+          <a:ext cx="298059" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20377,10 +20375,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="298492" y="4110"/>
+                <a:pt x="298059" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20435,8 +20433,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4574883" y="3278862"/>
-        <a:ext cx="14924" cy="14924"/>
+        <a:off x="4566082" y="3330704"/>
+        <a:ext cx="14902" cy="14902"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{5D691BA5-158A-4034-AEDA-B152BE077B27}">
@@ -20446,8 +20444,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4691048" y="3001692"/>
-          <a:ext cx="1776175" cy="364734"/>
+          <a:off x="4682079" y="3053935"/>
+          <a:ext cx="1773604" cy="364206"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20517,8 +20515,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4701731" y="3012375"/>
-        <a:ext cx="1754809" cy="343368"/>
+        <a:off x="4692746" y="3064602"/>
+        <a:ext cx="1752270" cy="342872"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{C26309FF-9296-40B3-913C-85759C2B07DC}">
@@ -20528,8 +20526,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6467223" y="3179948"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="6455683" y="3232004"/>
+          <a:ext cx="217090" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20540,10 +20538,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="217090" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20598,8 +20596,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6570490" y="3178624"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="6558801" y="3230611"/>
+        <a:ext cx="10854" cy="10854"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A4750321-4845-43B0-945B-4B9E7C7A668E}">
@@ -20609,8 +20607,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6684628" y="3001692"/>
-          <a:ext cx="3167897" cy="364734"/>
+          <a:off x="6672773" y="3053935"/>
+          <a:ext cx="3163311" cy="364206"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20704,8 +20702,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6695311" y="3012375"/>
-        <a:ext cx="3146531" cy="343368"/>
+        <a:off x="6683440" y="3064602"/>
+        <a:ext cx="3141977" cy="342872"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{CCE9C4CE-7CF8-4820-8390-F3CBCCE81ED7}">
@@ -20715,8 +20713,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9852525" y="3179948"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9836085" y="3232004"/>
+          <a:ext cx="217090" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20727,10 +20725,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="217090" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20785,8 +20783,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9955792" y="3178624"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9939203" y="3230611"/>
+        <a:ext cx="10854" cy="10854"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D954D938-3009-44F7-BB4F-D9E8AFB2B291}">
@@ -20796,8 +20794,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10069930" y="2999910"/>
-          <a:ext cx="1807704" cy="368297"/>
+          <a:off x="10053175" y="3052156"/>
+          <a:ext cx="1805087" cy="367764"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20867,8 +20865,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10080717" y="3010697"/>
-        <a:ext cx="1786130" cy="346723"/>
+        <a:off x="10063946" y="3062927"/>
+        <a:ext cx="1783545" cy="346222"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D01C8F64-85EC-45F5-B192-363D2A57FB6E}">
@@ -20878,8 +20876,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2595137">
-          <a:off x="4433100" y="3486744"/>
-          <a:ext cx="298492" cy="8220"/>
+          <a:off x="4424504" y="3538356"/>
+          <a:ext cx="298059" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20890,10 +20888,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="298492" y="4110"/>
+                <a:pt x="298059" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20948,8 +20946,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4574883" y="3483392"/>
-        <a:ext cx="14924" cy="14924"/>
+        <a:off x="4566082" y="3534938"/>
+        <a:ext cx="14902" cy="14902"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7832722B-5DD1-4AAD-819C-BC966C90EDAC}">
@@ -20959,8 +20957,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4691048" y="3410752"/>
-          <a:ext cx="1776175" cy="364734"/>
+          <a:off x="4682079" y="3462403"/>
+          <a:ext cx="1773604" cy="364206"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21030,8 +21028,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4701731" y="3421435"/>
-        <a:ext cx="1754809" cy="343368"/>
+        <a:off x="4692746" y="3473070"/>
+        <a:ext cx="1752270" cy="342872"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9B049FA9-70FB-4D7E-AD76-2BFCDB3B4195}">
@@ -21041,8 +21039,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6467223" y="3589009"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="6455683" y="3640473"/>
+          <a:ext cx="217090" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21053,10 +21051,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="217090" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21111,8 +21109,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6570490" y="3587684"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="6558801" y="3639079"/>
+        <a:ext cx="10854" cy="10854"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B5153D0A-E9E7-482C-B1CC-838341F8F3D8}">
@@ -21122,8 +21120,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6684628" y="3410752"/>
-          <a:ext cx="3167897" cy="364734"/>
+          <a:off x="6672773" y="3462403"/>
+          <a:ext cx="3163311" cy="364206"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21209,8 +21207,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6695311" y="3421435"/>
-        <a:ext cx="3146531" cy="343368"/>
+        <a:off x="6683440" y="3473070"/>
+        <a:ext cx="3141977" cy="342872"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1118BB77-BCCA-46BE-8B0C-417EE0F19393}">
@@ -21220,8 +21218,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9852525" y="3589009"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9836085" y="3640473"/>
+          <a:ext cx="217090" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21232,10 +21230,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="217090" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21290,8 +21288,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9955792" y="3587684"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9939203" y="3639079"/>
+        <a:ext cx="10854" cy="10854"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A1FE2FD1-D3B2-4F02-B33F-7EA3496A9D7D}">
@@ -21301,8 +21299,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10069930" y="3408971"/>
-          <a:ext cx="1807704" cy="368297"/>
+          <a:off x="10053175" y="3460624"/>
+          <a:ext cx="1805087" cy="367764"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21372,8 +21370,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10080717" y="3419758"/>
-        <a:ext cx="1786130" cy="346723"/>
+        <a:off x="10063946" y="3471395"/>
+        <a:ext cx="1783545" cy="346222"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{ACD64E2A-6A03-49D1-9C11-853B1D5FDA3F}">
@@ -21383,8 +21381,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="4880920">
-          <a:off x="572912" y="4198773"/>
-          <a:ext cx="1445308" cy="8220"/>
+          <a:off x="569904" y="4249354"/>
+          <a:ext cx="1443216" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21395,10 +21393,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1445308" y="4110"/>
+                <a:pt x="1443216" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21453,8 +21451,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1259433" y="4166750"/>
-        <a:ext cx="72265" cy="72265"/>
+        <a:off x="1255432" y="4217307"/>
+        <a:ext cx="72160" cy="72160"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4915DA81-5EFF-4A45-B117-A1C9369BA960}">
@@ -21464,8 +21462,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="1404269" y="4736544"/>
-          <a:ext cx="1437708" cy="361541"/>
+          <a:off x="1400057" y="4786276"/>
+          <a:ext cx="1435627" cy="361018"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21587,8 +21585,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1414858" y="4747133"/>
-        <a:ext cx="1416530" cy="340363"/>
+        <a:off x="1410631" y="4796850"/>
+        <a:ext cx="1414479" cy="339870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A3777E34-F7A1-4ABC-99E9-9C9A9AB7B959}">
@@ -21598,8 +21596,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17225057">
-          <a:off x="2585877" y="4566573"/>
-          <a:ext cx="725267" cy="8220"/>
+          <a:off x="2579955" y="4616622"/>
+          <a:ext cx="724217" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21610,10 +21608,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="725267" y="4110"/>
+                <a:pt x="724217" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21668,8 +21666,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2930379" y="4552551"/>
-        <a:ext cx="36263" cy="36263"/>
+        <a:off x="2923959" y="4602550"/>
+        <a:ext cx="36210" cy="36210"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{23228D17-0E30-4278-86F1-009AEEE4B90D}">
@@ -21679,8 +21677,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3055045" y="4043280"/>
-          <a:ext cx="1407331" cy="361541"/>
+          <a:off x="3048444" y="4094016"/>
+          <a:ext cx="1405294" cy="361018"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21750,8 +21748,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3065634" y="4053869"/>
-        <a:ext cx="1386153" cy="340363"/>
+        <a:off x="3059018" y="4104590"/>
+        <a:ext cx="1384146" cy="339870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A22E3146-1836-4A0C-A6D3-4503A76A9781}">
@@ -21761,8 +21759,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19004863">
-          <a:off x="4421833" y="4117676"/>
-          <a:ext cx="298492" cy="8220"/>
+          <a:off x="4413253" y="4168374"/>
+          <a:ext cx="298059" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21773,10 +21771,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="298492" y="4110"/>
+                <a:pt x="298059" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21831,8 +21829,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4563616" y="4114324"/>
-        <a:ext cx="14924" cy="14924"/>
+        <a:off x="4554832" y="4164956"/>
+        <a:ext cx="14902" cy="14902"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{06E3AC3D-2CA5-4C28-B4EE-08E1F5093575}">
@@ -21842,8 +21840,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4679781" y="3837154"/>
-          <a:ext cx="1776175" cy="364734"/>
+          <a:off x="4670828" y="3888187"/>
+          <a:ext cx="1773604" cy="364206"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21929,8 +21927,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4690464" y="3847837"/>
-        <a:ext cx="1754809" cy="343368"/>
+        <a:off x="4681495" y="3898854"/>
+        <a:ext cx="1752270" cy="342872"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{AB38F8C9-39F9-48F1-A4B9-359AD3B6C9E1}">
@@ -21940,8 +21938,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6455956" y="4015410"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="6444433" y="4066257"/>
+          <a:ext cx="217090" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21952,10 +21950,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="217090" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22010,8 +22008,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6559223" y="4014086"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="6547550" y="4064863"/>
+        <a:ext cx="10854" cy="10854"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{94E3E4AC-563C-467A-AD10-294BF8A33BAF}">
@@ -22021,8 +22019,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6673361" y="3837154"/>
-          <a:ext cx="3167897" cy="364734"/>
+          <a:off x="6661523" y="3888187"/>
+          <a:ext cx="3163311" cy="364206"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22108,8 +22106,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6684044" y="3847837"/>
-        <a:ext cx="3146531" cy="343368"/>
+        <a:off x="6672190" y="3898854"/>
+        <a:ext cx="3141977" cy="342872"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{CE4A2E59-3DB6-4586-9EDA-16655120708B}">
@@ -22119,8 +22117,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9841258" y="4015410"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9824834" y="4066257"/>
+          <a:ext cx="217090" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22131,10 +22129,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="217090" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22189,8 +22187,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9944525" y="4014086"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9927952" y="4064863"/>
+        <a:ext cx="10854" cy="10854"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{74F8E0C0-A1C2-4026-BDD1-211E4452BF84}">
@@ -22200,8 +22198,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10058663" y="3835372"/>
-          <a:ext cx="1807704" cy="368297"/>
+          <a:off x="10041924" y="3886409"/>
+          <a:ext cx="1805087" cy="367764"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22271,8 +22269,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10069450" y="3846159"/>
-        <a:ext cx="1786130" cy="346723"/>
+        <a:off x="10052695" y="3897180"/>
+        <a:ext cx="1783545" cy="346222"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{3776BE60-D86F-469E-9605-E0609281B4B9}">
@@ -22282,8 +22280,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2595137">
-          <a:off x="4421833" y="4322206"/>
-          <a:ext cx="298492" cy="8220"/>
+          <a:off x="4413253" y="4372609"/>
+          <a:ext cx="298059" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22294,10 +22292,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="298492" y="4110"/>
+                <a:pt x="298059" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22352,8 +22350,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4563616" y="4318854"/>
-        <a:ext cx="14924" cy="14924"/>
+        <a:off x="4554832" y="4369191"/>
+        <a:ext cx="14902" cy="14902"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{DC0F0790-8247-4EA1-A5BD-20B9C2810EA5}">
@@ -22363,8 +22361,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4679781" y="4246214"/>
-          <a:ext cx="1776175" cy="364734"/>
+          <a:off x="4670828" y="4296656"/>
+          <a:ext cx="1773604" cy="364206"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22434,8 +22432,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4690464" y="4256897"/>
-        <a:ext cx="1754809" cy="343368"/>
+        <a:off x="4681495" y="4307323"/>
+        <a:ext cx="1752270" cy="342872"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{82B78A4F-EF07-4DEA-A3EC-7BA9DD55DC45}">
@@ -22445,8 +22443,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6455956" y="4424471"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="6444433" y="4474726"/>
+          <a:ext cx="217090" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22457,10 +22455,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="217090" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22515,8 +22513,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6559223" y="4423146"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="6547550" y="4473332"/>
+        <a:ext cx="10854" cy="10854"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4D82C0F8-05DA-476F-9FFD-EF5362E37ABC}">
@@ -22526,8 +22524,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6673361" y="4246214"/>
-          <a:ext cx="3167897" cy="364734"/>
+          <a:off x="6661523" y="4296656"/>
+          <a:ext cx="3163311" cy="364206"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22605,8 +22603,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6684044" y="4256897"/>
-        <a:ext cx="3146531" cy="343368"/>
+        <a:off x="6672190" y="4307323"/>
+        <a:ext cx="3141977" cy="342872"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6F09ED48-69E5-4359-AEF9-003C31CF3834}">
@@ -22616,8 +22614,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9841258" y="4424471"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9824834" y="4474726"/>
+          <a:ext cx="217090" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22628,10 +22626,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="217090" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22686,8 +22684,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9944525" y="4423146"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9927952" y="4473332"/>
+        <a:ext cx="10854" cy="10854"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7F4C8494-F5DD-49F1-B7FE-320AAF64A334}">
@@ -22697,8 +22695,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10058663" y="4244433"/>
-          <a:ext cx="1807704" cy="368297"/>
+          <a:off x="10041924" y="4294877"/>
+          <a:ext cx="1805087" cy="367764"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22773,8 +22771,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10069450" y="4255220"/>
-        <a:ext cx="1786130" cy="346723"/>
+        <a:off x="10052695" y="4305648"/>
+        <a:ext cx="1783545" cy="346222"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E97A89EA-A088-4B36-94ED-03E39FF28C24}">
@@ -22784,8 +22782,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="1512707">
-          <a:off x="2830532" y="4964383"/>
-          <a:ext cx="240295" cy="8220"/>
+          <a:off x="2824256" y="5013856"/>
+          <a:ext cx="239947" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22796,10 +22794,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="240295" y="4110"/>
+                <a:pt x="239947" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22854,8 +22852,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2944672" y="4962486"/>
-        <a:ext cx="12014" cy="12014"/>
+        <a:off x="2938231" y="5011891"/>
+        <a:ext cx="11997" cy="11997"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1279AA60-C872-4597-B281-C6CC2E4A34C2}">
@@ -22865,8 +22863,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3059382" y="4838902"/>
-          <a:ext cx="1407331" cy="361541"/>
+          <a:off x="3052775" y="4888486"/>
+          <a:ext cx="1405294" cy="361018"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22936,8 +22934,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3069971" y="4849491"/>
-        <a:ext cx="1386153" cy="340363"/>
+        <a:off x="3063349" y="4899060"/>
+        <a:ext cx="1384146" cy="339870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{255CD393-ED80-4D10-A68E-31ED59592E3B}">
@@ -22947,8 +22945,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19138242">
-          <a:off x="4432026" y="4922858"/>
-          <a:ext cx="282442" cy="8220"/>
+          <a:off x="4423432" y="4972391"/>
+          <a:ext cx="282034" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22959,10 +22957,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="282442" y="4110"/>
+                <a:pt x="282034" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23017,8 +23015,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4566186" y="4919907"/>
-        <a:ext cx="14122" cy="14122"/>
+        <a:off x="4557398" y="4969374"/>
+        <a:ext cx="14101" cy="14101"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{2340676A-EBD4-4E22-BA9C-E56B6A62904C}">
@@ -23028,8 +23026,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4679781" y="4651897"/>
-          <a:ext cx="1776175" cy="364734"/>
+          <a:off x="4670828" y="4701751"/>
+          <a:ext cx="1773604" cy="364206"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23099,8 +23097,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4690464" y="4662580"/>
-        <a:ext cx="1754809" cy="343368"/>
+        <a:off x="4681495" y="4712418"/>
+        <a:ext cx="1752270" cy="342872"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{EB837690-03CF-4B39-A4B0-AFC71E15928A}">
@@ -23110,8 +23108,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="27806">
-          <a:off x="6455952" y="4831051"/>
-          <a:ext cx="221749" cy="8220"/>
+          <a:off x="6444429" y="4880717"/>
+          <a:ext cx="221428" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23122,10 +23120,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="221749" y="4110"/>
+                <a:pt x="221428" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23180,8 +23178,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6561283" y="4829617"/>
-        <a:ext cx="11087" cy="11087"/>
+        <a:off x="6549607" y="4879215"/>
+        <a:ext cx="11071" cy="11071"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6CD3FE0A-3BBE-455B-B381-72424654A1B0}">
@@ -23191,8 +23189,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6677698" y="4655287"/>
-          <a:ext cx="3167092" cy="361541"/>
+          <a:off x="6665854" y="4705137"/>
+          <a:ext cx="3162508" cy="361018"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23270,8 +23268,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6688287" y="4665876"/>
-        <a:ext cx="3145914" cy="340363"/>
+        <a:off x="6676428" y="4715711"/>
+        <a:ext cx="3141360" cy="339870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B86CABA2-1933-4D02-A0D3-AA6DEA35BCA7}">
@@ -23281,8 +23279,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9844791" y="4831947"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9828362" y="4881612"/>
+          <a:ext cx="217090" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23293,10 +23291,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="217090" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23351,8 +23349,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9948058" y="4830623"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9931480" y="4880218"/>
+        <a:ext cx="10854" cy="10854"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{920A36CD-D69B-4AB0-8DA2-4963F1111FE2}">
@@ -23362,8 +23360,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10062195" y="4655287"/>
-          <a:ext cx="1807704" cy="361541"/>
+          <a:off x="10045452" y="4705137"/>
+          <a:ext cx="1805087" cy="361018"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23433,8 +23431,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10072784" y="4665876"/>
-        <a:ext cx="1786526" cy="340363"/>
+        <a:off x="10056026" y="4715711"/>
+        <a:ext cx="1783939" cy="339870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{EE30240B-4D3F-4585-94A4-7AD0CBEBACD0}">
@@ -23444,8 +23442,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2755727">
-          <a:off x="4420083" y="5125607"/>
-          <a:ext cx="306328" cy="8220"/>
+          <a:off x="4411506" y="5174847"/>
+          <a:ext cx="305885" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23456,10 +23454,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="306328" y="4110"/>
+                <a:pt x="305885" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23514,8 +23512,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4565589" y="5122059"/>
-        <a:ext cx="15316" cy="15316"/>
+        <a:off x="4556802" y="5171233"/>
+        <a:ext cx="15294" cy="15294"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9B0332A1-DFA5-4E72-89B6-8E8C50F667E1}">
@@ -23525,8 +23523,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4679781" y="5057395"/>
-          <a:ext cx="1776175" cy="364734"/>
+          <a:off x="4670828" y="5106662"/>
+          <a:ext cx="1773604" cy="364206"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23623,8 +23621,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4690464" y="5068078"/>
-        <a:ext cx="1754809" cy="343368"/>
+        <a:off x="4681495" y="5117329"/>
+        <a:ext cx="1752270" cy="342872"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4EF5B1E7-3D92-44D9-8E8A-E2A10FB649AC}">
@@ -23634,8 +23632,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="27806">
-          <a:off x="6455952" y="5236548"/>
-          <a:ext cx="221749" cy="8220"/>
+          <a:off x="6444429" y="5285628"/>
+          <a:ext cx="221428" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23646,10 +23644,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="221749" y="4110"/>
+                <a:pt x="221428" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23704,8 +23702,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6561283" y="5235115"/>
-        <a:ext cx="11087" cy="11087"/>
+        <a:off x="6549607" y="5284126"/>
+        <a:ext cx="11071" cy="11071"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9AC7A0EB-B59E-41D9-A589-CB90FBF4305E}">
@@ -23715,8 +23713,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6677698" y="5060785"/>
-          <a:ext cx="3167092" cy="361541"/>
+          <a:off x="6665854" y="5110048"/>
+          <a:ext cx="3162508" cy="361018"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23802,8 +23800,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6688287" y="5071374"/>
-        <a:ext cx="3145914" cy="340363"/>
+        <a:off x="6676428" y="5120622"/>
+        <a:ext cx="3141360" cy="339870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{2F5A23ED-2B4B-4307-BAD6-D126CED4ED45}">
@@ -23813,8 +23811,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9844791" y="5237445"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9828362" y="5286523"/>
+          <a:ext cx="217090" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23825,10 +23823,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="217090" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23883,8 +23881,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9948058" y="5236121"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9931480" y="5285129"/>
+        <a:ext cx="10854" cy="10854"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{C9CCA1DF-737F-40B9-8662-1EBAE874B88C}">
@@ -23894,8 +23892,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10062195" y="5060785"/>
-          <a:ext cx="1807704" cy="361541"/>
+          <a:off x="10045452" y="5110048"/>
+          <a:ext cx="1805087" cy="361018"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23965,8 +23963,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10072784" y="5071374"/>
-        <a:ext cx="1786526" cy="340363"/>
+        <a:off x="10056026" y="5120622"/>
+        <a:ext cx="1783939" cy="339870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{06804470-2E4E-45CC-AD07-54CD8F165228}">
@@ -23976,8 +23974,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="4379331">
-          <a:off x="2579121" y="5268507"/>
-          <a:ext cx="743117" cy="8220"/>
+          <a:off x="2573209" y="5317540"/>
+          <a:ext cx="742041" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23988,10 +23986,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="743117" y="4110"/>
+                <a:pt x="742041" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -24046,8 +24044,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2932101" y="5254039"/>
-        <a:ext cx="37155" cy="37155"/>
+        <a:off x="2925679" y="5303022"/>
+        <a:ext cx="37102" cy="37102"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D9D1FF4E-B146-4A17-8BAD-E6A8247731B1}">
@@ -24057,8 +24055,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3059382" y="5447149"/>
-          <a:ext cx="1407337" cy="361541"/>
+          <a:off x="3052775" y="5495852"/>
+          <a:ext cx="1405300" cy="361018"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -24144,8 +24142,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3069971" y="5457738"/>
-        <a:ext cx="1386159" cy="340363"/>
+        <a:off x="3063349" y="5506426"/>
+        <a:ext cx="1384152" cy="339870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{458C594D-E94A-4416-A27A-8211BD0C18EB}">
@@ -24155,8 +24153,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4466719" y="5623809"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="4458075" y="5672328"/>
+          <a:ext cx="217090" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -24167,10 +24165,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="217090" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -24225,8 +24223,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4569986" y="5622484"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="4561192" y="5670934"/>
+        <a:ext cx="10854" cy="10854"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E6BB35B6-4DC7-42B5-A329-D93F595605BC}">
@@ -24236,8 +24234,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4684124" y="5445552"/>
-          <a:ext cx="1765668" cy="364734"/>
+          <a:off x="4675165" y="5494258"/>
+          <a:ext cx="1763113" cy="364206"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -24323,8 +24321,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4694807" y="5456235"/>
-        <a:ext cx="1744302" cy="343368"/>
+        <a:off x="4685832" y="5504925"/>
+        <a:ext cx="1741779" cy="342872"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{F3CE9778-2DAD-459C-A92D-C581128238EF}">
@@ -24334,8 +24332,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6449793" y="5623809"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="6438278" y="5672328"/>
+          <a:ext cx="217090" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -24346,10 +24344,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="217090" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -24404,8 +24402,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6553060" y="5622484"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="6541396" y="5670934"/>
+        <a:ext cx="10854" cy="10854"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A62201D7-F2CC-41E5-BB68-F68B79E1464B}">
@@ -24415,8 +24413,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6667197" y="5447149"/>
-          <a:ext cx="3167092" cy="361541"/>
+          <a:off x="6655368" y="5495852"/>
+          <a:ext cx="3162508" cy="361018"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -24486,8 +24484,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6677786" y="5457738"/>
-        <a:ext cx="3145914" cy="340363"/>
+        <a:off x="6665942" y="5506426"/>
+        <a:ext cx="3141360" cy="339870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{46794C65-61A0-4B52-A42E-5CC9D77E3723}">
@@ -24497,8 +24495,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9834290" y="5623809"/>
-          <a:ext cx="217404" cy="8220"/>
+          <a:off x="9817877" y="5672328"/>
+          <a:ext cx="217090" cy="8067"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -24509,10 +24507,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4110"/>
+                <a:pt x="0" y="4033"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217404" y="4110"/>
+                <a:pt x="217090" y="4033"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -24567,8 +24565,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9937557" y="5622484"/>
-        <a:ext cx="10870" cy="10870"/>
+        <a:off x="9920994" y="5670934"/>
+        <a:ext cx="10854" cy="10854"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{C61F938B-5A64-4BF7-B003-81E0909084B1}">
@@ -24578,8 +24576,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10051695" y="5447149"/>
-          <a:ext cx="1807704" cy="361541"/>
+          <a:off x="10034967" y="5495852"/>
+          <a:ext cx="1805087" cy="361018"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -24649,8 +24647,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10062284" y="5457738"/>
-        <a:ext cx="1786526" cy="340363"/>
+        <a:off x="10045541" y="5506426"/>
+        <a:ext cx="1783939" cy="339870"/>
       </dsp:txXfrm>
     </dsp:sp>
   </dsp:spTree>
@@ -28230,51 +28228,51 @@
         <v>121</v>
       </c>
     </row>
-    <row r="94" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A94" s="20" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="95" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A95" s="20" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="96" spans="1:1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A96" s="20" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="97" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="98" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="98" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A98" s="22" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="99" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="100" spans="1:3" ht="26" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="100" spans="1:3" ht="26" collapsed="1" x14ac:dyDescent="0.45">
       <c r="A100" s="21" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="101" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A101" s="20" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="102" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A102" s="20" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="103" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="104" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="104" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A104" s="22" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="105" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="106" spans="1:3" ht="26" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="106" spans="1:3" ht="26" collapsed="1" x14ac:dyDescent="0.45">
       <c r="A106" s="21" t="s">
         <v>129</v>
       </c>
@@ -28441,6 +28439,9 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA7446D1-A9E6-4F8D-B799-CB90AD03762A}">
+  <sheetPr>
+    <tabColor theme="9" tint="0.79998168889431442"/>
+  </sheetPr>
   <dimension ref="A1:E23"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
@@ -28476,13 +28477,13 @@
         <v>425</v>
       </c>
       <c r="C2" s="18" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E2" s="18" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="85" x14ac:dyDescent="0.45">
@@ -28493,13 +28494,13 @@
         <v>427</v>
       </c>
       <c r="C3" s="18" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="D3" s="18" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="E3" s="18" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="68" x14ac:dyDescent="0.45">
@@ -28510,13 +28511,13 @@
         <v>429</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="E4" s="18" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="51" x14ac:dyDescent="0.45">
@@ -28527,13 +28528,13 @@
         <v>431</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="85" x14ac:dyDescent="0.45">
@@ -28544,13 +28545,13 @@
         <v>433</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="68" x14ac:dyDescent="0.45">
@@ -28561,13 +28562,13 @@
         <v>435</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="51" x14ac:dyDescent="0.45">
@@ -28578,13 +28579,13 @@
         <v>437</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="85" x14ac:dyDescent="0.45">
@@ -28595,13 +28596,13 @@
         <v>439</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="E9" s="18" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.45">
@@ -28611,14 +28612,14 @@
       <c r="B10" s="77" t="s">
         <v>441</v>
       </c>
-      <c r="C10" s="116" t="s">
-        <v>464</v>
-      </c>
-      <c r="D10" s="117" t="s">
-        <v>490</v>
+      <c r="C10" s="120" t="s">
+        <v>462</v>
+      </c>
+      <c r="D10" s="121" t="s">
+        <v>488</v>
       </c>
       <c r="E10" s="18" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.45">
@@ -28628,10 +28629,10 @@
       <c r="B11" s="77" t="s">
         <v>443</v>
       </c>
-      <c r="C11" s="116"/>
-      <c r="D11" s="117"/>
+      <c r="C11" s="120"/>
+      <c r="D11" s="121"/>
       <c r="E11" s="18" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="51" x14ac:dyDescent="0.45">
@@ -28642,13 +28643,13 @@
         <v>445</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="34" x14ac:dyDescent="0.45">
@@ -28660,10 +28661,10 @@
       </c>
       <c r="C13" s="58"/>
       <c r="D13" s="18" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="34" x14ac:dyDescent="0.45">
@@ -28673,12 +28674,12 @@
       <c r="B14" s="78" t="s">
         <v>320</v>
       </c>
-      <c r="C14" s="116" t="s">
-        <v>462</v>
+      <c r="C14" s="120" t="s">
+        <v>460</v>
       </c>
       <c r="D14" s="18"/>
       <c r="E14" s="18" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="35.5" customHeight="1" x14ac:dyDescent="0.45">
@@ -28688,10 +28689,10 @@
       <c r="B15" s="79" t="s">
         <v>322</v>
       </c>
-      <c r="C15" s="116"/>
+      <c r="C15" s="120"/>
       <c r="D15" s="18"/>
       <c r="E15" s="18" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="34" x14ac:dyDescent="0.45">
@@ -28702,23 +28703,22 @@
         <v>326</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="D16" s="18"/>
       <c r="E16" s="18" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A17" s="119"/>
-      <c r="B17" s="120"/>
-      <c r="C17" s="121"/>
-      <c r="D17" s="121"/>
-      <c r="E17" s="121"/>
+      <c r="A17" s="20"/>
+      <c r="B17" s="83"/>
+      <c r="C17" s="80"/>
+      <c r="E17" s="80"/>
     </row>
     <row r="18" spans="1:5" ht="20.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="118" t="s">
-        <v>493</v>
+      <c r="A18" s="82" t="s">
+        <v>491</v>
       </c>
       <c r="B18" s="69"/>
       <c r="C18" s="69"/>
@@ -28726,87 +28726,87 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" s="60" t="s">
+        <v>508</v>
+      </c>
+      <c r="B19" s="60" t="s">
+        <v>509</v>
+      </c>
+      <c r="C19" s="60" t="s">
         <v>510</v>
       </c>
-      <c r="B19" s="60" t="s">
+      <c r="D19" s="60" t="s">
         <v>511</v>
       </c>
-      <c r="C19" s="60" t="s">
+      <c r="E19" s="60" t="s">
         <v>512</v>
-      </c>
-      <c r="D19" s="60" t="s">
-        <v>513</v>
-      </c>
-      <c r="E19" s="60" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="85" x14ac:dyDescent="0.45">
-      <c r="A20" s="122">
+      <c r="A20" s="84">
         <v>1</v>
       </c>
-      <c r="B20" s="123" t="s">
+      <c r="B20" s="85" t="s">
+        <v>492</v>
+      </c>
+      <c r="C20" s="85" t="s">
+        <v>493</v>
+      </c>
+      <c r="D20" s="85" t="s">
         <v>494</v>
       </c>
-      <c r="C20" s="123" t="s">
+      <c r="E20" s="84" t="s">
         <v>495</v>
-      </c>
-      <c r="D20" s="123" t="s">
-        <v>496</v>
-      </c>
-      <c r="E20" s="122" t="s">
-        <v>497</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="68" x14ac:dyDescent="0.45">
-      <c r="A21" s="122">
+      <c r="A21" s="84">
         <v>2</v>
       </c>
-      <c r="B21" s="123" t="s">
+      <c r="B21" s="85" t="s">
+        <v>496</v>
+      </c>
+      <c r="C21" s="85" t="s">
+        <v>497</v>
+      </c>
+      <c r="D21" s="85" t="s">
         <v>498</v>
       </c>
-      <c r="C21" s="123" t="s">
+      <c r="E21" s="84" t="s">
         <v>499</v>
-      </c>
-      <c r="D21" s="123" t="s">
-        <v>500</v>
-      </c>
-      <c r="E21" s="122" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="102" x14ac:dyDescent="0.45">
-      <c r="A22" s="122">
+      <c r="A22" s="84">
         <v>3</v>
       </c>
-      <c r="B22" s="123" t="s">
+      <c r="B22" s="85" t="s">
+        <v>500</v>
+      </c>
+      <c r="C22" s="85" t="s">
+        <v>501</v>
+      </c>
+      <c r="D22" s="85" t="s">
         <v>502</v>
       </c>
-      <c r="C22" s="123" t="s">
+      <c r="E22" s="84" t="s">
         <v>503</v>
-      </c>
-      <c r="D22" s="123" t="s">
-        <v>504</v>
-      </c>
-      <c r="E22" s="122" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="68" x14ac:dyDescent="0.45">
-      <c r="A23" s="122">
+      <c r="A23" s="84">
         <v>4</v>
       </c>
-      <c r="B23" s="123" t="s">
+      <c r="B23" s="85" t="s">
+        <v>504</v>
+      </c>
+      <c r="C23" s="85" t="s">
+        <v>505</v>
+      </c>
+      <c r="D23" s="85" t="s">
         <v>506</v>
       </c>
-      <c r="C23" s="123" t="s">
+      <c r="E23" s="84" t="s">
         <v>507</v>
-      </c>
-      <c r="D23" s="123" t="s">
-        <v>508</v>
-      </c>
-      <c r="E23" s="122" t="s">
-        <v>509</v>
       </c>
     </row>
   </sheetData>
@@ -28921,10 +28921,10 @@
       <c r="B6" s="72" t="s">
         <v>449</v>
       </c>
-      <c r="C6" s="82">
+      <c r="C6" s="86">
         <v>46275</v>
       </c>
-      <c r="D6" s="84" t="s">
+      <c r="D6" s="88" t="s">
         <v>316</v>
       </c>
     </row>
@@ -28935,8 +28935,8 @@
       <c r="B7" s="73" t="s">
         <v>450</v>
       </c>
-      <c r="C7" s="83"/>
-      <c r="D7" s="85"/>
+      <c r="C7" s="87"/>
+      <c r="D7" s="89"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" s="33" t="s">
@@ -28956,7 +28956,9 @@
       <c r="A9" s="33" t="s">
         <v>176</v>
       </c>
-      <c r="B9" s="33"/>
+      <c r="B9" s="56" t="s">
+        <v>513</v>
+      </c>
       <c r="C9" s="35">
         <v>46276</v>
       </c>
@@ -28968,12 +28970,14 @@
       <c r="A10" s="33" t="s">
         <v>177</v>
       </c>
-      <c r="B10" s="33"/>
+      <c r="B10" s="56" t="s">
+        <v>513</v>
+      </c>
       <c r="C10" s="35">
         <v>46276</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>453</v>
+        <v>514</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="34" x14ac:dyDescent="0.45">
@@ -28985,7 +28989,7 @@
         <v>46279.645833333336</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>454</v>
+        <v>515</v>
       </c>
     </row>
   </sheetData>
@@ -29002,6 +29006,8 @@
     <hyperlink ref="B6" location="'4-1 통계적 검증'!A1" display="검증전" xr:uid="{4D4B7E5E-D31F-46E8-AE77-4A82FC446F0B}"/>
     <hyperlink ref="B7" location="'4-2 통계적 검증 결과'!A1" display="검증후" xr:uid="{74C75FD8-2793-4E12-83F0-89D06783033D}"/>
     <hyperlink ref="B8" location="'5. 머신러닝 적용'!A1" display="진행하지 않음" xr:uid="{D0EB73E0-F138-4F21-BFB7-2E0024630222}"/>
+    <hyperlink ref="B9" location="'6. 결론 및 의사결정 제안'!A1" display="링크" xr:uid="{4DFEBCAC-C574-41D5-8045-D98973D70C7F}"/>
+    <hyperlink ref="B10" location="'7. 대시보드 제작'!A1" display="링크" xr:uid="{CF7225DB-EFFE-4774-BD0F-DACAC9476A84}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="62" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
@@ -29051,7 +29057,7 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A2" s="86" t="s">
+      <c r="A2" s="90" t="s">
         <v>18</v>
       </c>
       <c r="B2" s="7" t="s">
@@ -29068,7 +29074,7 @@
       <c r="G2" s="10"/>
     </row>
     <row r="3" spans="1:7" ht="64" x14ac:dyDescent="0.45">
-      <c r="A3" s="87"/>
+      <c r="A3" s="91"/>
       <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
@@ -29085,7 +29091,7 @@
       <c r="G3" s="11"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A4" s="87"/>
+      <c r="A4" s="91"/>
       <c r="B4" s="4" t="s">
         <v>184</v>
       </c>
@@ -29100,7 +29106,7 @@
       <c r="G4" s="11"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A5" s="87"/>
+      <c r="A5" s="91"/>
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
@@ -29115,7 +29121,7 @@
       <c r="G5" s="11"/>
     </row>
     <row r="6" spans="1:7" ht="48" x14ac:dyDescent="0.45">
-      <c r="A6" s="87"/>
+      <c r="A6" s="91"/>
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
@@ -29134,7 +29140,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="88"/>
+      <c r="A7" s="92"/>
       <c r="B7" s="13" t="s">
         <v>15</v>
       </c>
@@ -29151,7 +29157,7 @@
       <c r="G7" s="15"/>
     </row>
     <row r="8" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="89" t="s">
+      <c r="A8" s="93" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="7" t="s">
@@ -29172,7 +29178,7 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A9" s="90"/>
+      <c r="A9" s="94"/>
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -29189,7 +29195,7 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A10" s="90"/>
+      <c r="A10" s="94"/>
       <c r="B10" s="4" t="s">
         <v>4</v>
       </c>
@@ -29206,7 +29212,7 @@
       <c r="G10" s="11"/>
     </row>
     <row r="11" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A11" s="90"/>
+      <c r="A11" s="94"/>
       <c r="B11" s="4" t="s">
         <v>7</v>
       </c>
@@ -29221,7 +29227,7 @@
       <c r="G11" s="11"/>
     </row>
     <row r="12" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A12" s="91"/>
+      <c r="A12" s="95"/>
       <c r="B12" s="16" t="s">
         <v>8</v>
       </c>
@@ -29238,7 +29244,7 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A13" s="92" t="s">
+      <c r="A13" s="96" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="7" t="s">
@@ -29259,7 +29265,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" ht="64.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A14" s="93"/>
+      <c r="A14" s="97"/>
       <c r="B14" s="4" t="s">
         <v>10</v>
       </c>
@@ -29276,7 +29282,7 @@
       <c r="G14" s="11"/>
     </row>
     <row r="15" spans="1:7" ht="64" x14ac:dyDescent="0.45">
-      <c r="A15" s="93"/>
+      <c r="A15" s="97"/>
       <c r="B15" s="4" t="s">
         <v>218</v>
       </c>
@@ -29297,7 +29303,7 @@
       </c>
     </row>
     <row r="16" spans="1:7" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A16" s="94"/>
+      <c r="A16" s="98"/>
       <c r="B16" s="16" t="s">
         <v>11</v>
       </c>
@@ -29450,14 +29456,14 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A5" s="96" t="s">
+      <c r="A5" s="100" t="s">
         <v>273</v>
       </c>
-      <c r="B5" s="96"/>
-      <c r="C5" s="96"/>
+      <c r="B5" s="100"/>
+      <c r="C5" s="100"/>
     </row>
     <row r="6" spans="1:4" ht="32" x14ac:dyDescent="0.45">
-      <c r="A6" s="108" t="s">
+      <c r="A6" s="112" t="s">
         <v>204</v>
       </c>
       <c r="B6" s="47" t="s">
@@ -29468,7 +29474,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" ht="32" x14ac:dyDescent="0.45">
-      <c r="A7" s="109"/>
+      <c r="A7" s="113"/>
       <c r="B7" s="47" t="s">
         <v>292</v>
       </c>
@@ -29477,7 +29483,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" ht="32" x14ac:dyDescent="0.45">
-      <c r="A8" s="109"/>
+      <c r="A8" s="113"/>
       <c r="B8" s="47" t="s">
         <v>295</v>
       </c>
@@ -29486,7 +29492,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A9" s="109"/>
+      <c r="A9" s="113"/>
       <c r="B9" s="47" t="s">
         <v>303</v>
       </c>
@@ -29495,7 +29501,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A10" s="110"/>
+      <c r="A10" s="114"/>
       <c r="B10" s="47" t="s">
         <v>297</v>
       </c>
@@ -29518,18 +29524,18 @@
       <c r="C12" s="49"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A13" s="101" t="s">
+      <c r="A13" s="105" t="s">
         <v>304</v>
       </c>
-      <c r="B13" s="102"/>
-      <c r="C13" s="103"/>
+      <c r="B13" s="106"/>
+      <c r="C13" s="107"/>
     </row>
     <row r="14" spans="1:4" ht="52" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A14" s="111" t="s">
+      <c r="A14" s="115" t="s">
         <v>230</v>
       </c>
-      <c r="B14" s="112"/>
-      <c r="C14" s="113"/>
+      <c r="B14" s="116"/>
+      <c r="C14" s="117"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A19" s="49"/>
@@ -29537,112 +29543,112 @@
       <c r="D19" s="49"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A31" s="96" t="s">
+      <c r="A31" s="100" t="s">
         <v>274</v>
       </c>
-      <c r="B31" s="96"/>
-      <c r="C31" s="96"/>
+      <c r="B31" s="100"/>
+      <c r="C31" s="100"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A32" s="104" t="s">
+      <c r="A32" s="108" t="s">
         <v>318</v>
       </c>
-      <c r="B32" s="105"/>
-      <c r="C32" s="106"/>
+      <c r="B32" s="109"/>
+      <c r="C32" s="110"/>
     </row>
     <row r="33" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A33" s="100" t="s">
+      <c r="A33" s="104" t="s">
         <v>231</v>
       </c>
       <c r="B33" s="50" t="s">
         <v>208</v>
       </c>
-      <c r="C33" s="107" t="s">
+      <c r="C33" s="111" t="s">
         <v>305</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A34" s="100"/>
+      <c r="A34" s="104"/>
       <c r="B34" s="50" t="s">
         <v>209</v>
       </c>
-      <c r="C34" s="107"/>
+      <c r="C34" s="111"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A35" s="100"/>
+      <c r="A35" s="104"/>
       <c r="B35" s="50" t="s">
         <v>210</v>
       </c>
-      <c r="C35" s="107"/>
+      <c r="C35" s="111"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A36" s="100"/>
+      <c r="A36" s="104"/>
       <c r="B36" s="50" t="s">
         <v>211</v>
       </c>
-      <c r="C36" s="107"/>
+      <c r="C36" s="111"/>
     </row>
     <row r="37" spans="1:5" ht="32" x14ac:dyDescent="0.45">
-      <c r="A37" s="100"/>
+      <c r="A37" s="104"/>
       <c r="B37" s="48" t="s">
         <v>212</v>
       </c>
-      <c r="C37" s="107"/>
+      <c r="C37" s="111"/>
     </row>
     <row r="38" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="100" t="s">
+      <c r="A38" s="104" t="s">
         <v>232</v>
       </c>
       <c r="B38" s="50" t="s">
         <v>213</v>
       </c>
-      <c r="C38" s="107" t="s">
+      <c r="C38" s="111" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A39" s="100"/>
+      <c r="A39" s="104"/>
       <c r="B39" s="50" t="s">
         <v>214</v>
       </c>
-      <c r="C39" s="107"/>
+      <c r="C39" s="111"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A40" s="100"/>
+      <c r="A40" s="104"/>
       <c r="B40" s="50" t="s">
         <v>215</v>
       </c>
-      <c r="C40" s="107"/>
+      <c r="C40" s="111"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A42" s="101" t="s">
+      <c r="A42" s="105" t="s">
         <v>272</v>
       </c>
-      <c r="B42" s="102"/>
-      <c r="C42" s="103"/>
+      <c r="B42" s="106"/>
+      <c r="C42" s="107"/>
     </row>
     <row r="43" spans="1:5" ht="53" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A43" s="100" t="s">
+      <c r="A43" s="104" t="s">
         <v>217</v>
       </c>
-      <c r="B43" s="100"/>
-      <c r="C43" s="100"/>
+      <c r="B43" s="104"/>
+      <c r="C43" s="104"/>
     </row>
     <row r="44" spans="1:5" ht="50.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A44" s="100" t="s">
+      <c r="A44" s="104" t="s">
         <v>317</v>
       </c>
-      <c r="B44" s="100"/>
-      <c r="C44" s="100"/>
+      <c r="B44" s="104"/>
+      <c r="C44" s="104"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A46" s="96" t="s">
+      <c r="A46" s="100" t="s">
         <v>271</v>
       </c>
-      <c r="B46" s="96"/>
-      <c r="C46" s="96"/>
-      <c r="D46" s="96"/>
-      <c r="E46" s="96"/>
+      <c r="B46" s="100"/>
+      <c r="C46" s="100"/>
+      <c r="D46" s="100"/>
+      <c r="E46" s="100"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" s="44" t="s">
@@ -29828,11 +29834,11 @@
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A59" s="97" t="s">
+      <c r="A59" s="101" t="s">
         <v>275</v>
       </c>
-      <c r="B59" s="98"/>
-      <c r="C59" s="99"/>
+      <c r="B59" s="102"/>
+      <c r="C59" s="103"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" s="53" t="s">
@@ -29890,84 +29896,84 @@
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A66" s="96" t="s">
+      <c r="A66" s="100" t="s">
         <v>291</v>
       </c>
-      <c r="B66" s="96"/>
-      <c r="C66" s="96"/>
-      <c r="D66" s="96"/>
+      <c r="B66" s="100"/>
+      <c r="C66" s="100"/>
+      <c r="D66" s="100"/>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A67" s="95" t="s">
+      <c r="A67" s="99" t="s">
         <v>262</v>
       </c>
-      <c r="B67" s="95"/>
-      <c r="C67" s="95"/>
-      <c r="D67" s="95"/>
+      <c r="B67" s="99"/>
+      <c r="C67" s="99"/>
+      <c r="D67" s="99"/>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A68" s="95" t="s">
+      <c r="A68" s="99" t="s">
         <v>263</v>
       </c>
-      <c r="B68" s="95"/>
-      <c r="C68" s="95"/>
-      <c r="D68" s="95"/>
+      <c r="B68" s="99"/>
+      <c r="C68" s="99"/>
+      <c r="D68" s="99"/>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A69" s="95" t="s">
+      <c r="A69" s="99" t="s">
         <v>264</v>
       </c>
-      <c r="B69" s="95"/>
-      <c r="C69" s="95"/>
-      <c r="D69" s="95"/>
+      <c r="B69" s="99"/>
+      <c r="C69" s="99"/>
+      <c r="D69" s="99"/>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A70" s="95" t="s">
+      <c r="A70" s="99" t="s">
         <v>265</v>
       </c>
-      <c r="B70" s="95"/>
-      <c r="C70" s="95"/>
-      <c r="D70" s="95"/>
+      <c r="B70" s="99"/>
+      <c r="C70" s="99"/>
+      <c r="D70" s="99"/>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A71" s="95" t="s">
+      <c r="A71" s="99" t="s">
         <v>266</v>
       </c>
-      <c r="B71" s="95"/>
-      <c r="C71" s="95"/>
-      <c r="D71" s="95"/>
+      <c r="B71" s="99"/>
+      <c r="C71" s="99"/>
+      <c r="D71" s="99"/>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A72" s="95" t="s">
+      <c r="A72" s="99" t="s">
         <v>267</v>
       </c>
-      <c r="B72" s="95"/>
-      <c r="C72" s="95"/>
-      <c r="D72" s="95"/>
+      <c r="B72" s="99"/>
+      <c r="C72" s="99"/>
+      <c r="D72" s="99"/>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A73" s="95" t="s">
+      <c r="A73" s="99" t="s">
         <v>268</v>
       </c>
-      <c r="B73" s="95"/>
-      <c r="C73" s="95"/>
-      <c r="D73" s="95"/>
+      <c r="B73" s="99"/>
+      <c r="C73" s="99"/>
+      <c r="D73" s="99"/>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A74" s="95" t="s">
+      <c r="A74" s="99" t="s">
         <v>269</v>
       </c>
-      <c r="B74" s="95"/>
-      <c r="C74" s="95"/>
-      <c r="D74" s="95"/>
+      <c r="B74" s="99"/>
+      <c r="C74" s="99"/>
+      <c r="D74" s="99"/>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A75" s="95" t="s">
+      <c r="A75" s="99" t="s">
         <v>270</v>
       </c>
-      <c r="B75" s="95"/>
-      <c r="C75" s="95"/>
-      <c r="D75" s="95"/>
+      <c r="B75" s="99"/>
+      <c r="C75" s="99"/>
+      <c r="D75" s="99"/>
     </row>
   </sheetData>
   <mergeCells count="25">
@@ -30036,10 +30042,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A1" s="114" t="s">
+      <c r="A1" s="118" t="s">
         <v>335</v>
       </c>
-      <c r="B1" s="115"/>
+      <c r="B1" s="119"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="60" t="s">

--- a/project_2/project2_project status(C2).xlsx
+++ b/project_2/project2_project status(C2).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pyostry\workspace\aiffel\ai-data-bootcamp\Project_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADF8F8A2-97AB-4519-B186-31B81E535E32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A60463-41FF-4445-A1DB-285112FF7916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{5FF54064-7DDC-427B-93D7-EF78D75E5195}"/>
   </bookViews>
@@ -25,6 +25,9 @@
     <sheet name="6. 결론 및 의사결정 제안" sheetId="8" r:id="rId10"/>
     <sheet name="7. 대시보드 제작" sheetId="9" r:id="rId11"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="10">'7. 대시보드 제작'!$A$1:$P$24</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -2307,13 +2310,12 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>디자인: 시철, 서영, 서현(채택)
-제작: 시철</t>
+    <t>자료 준비 및 검증: 시철, 서영, 서현
+발표: 시철</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>발표자료 준비: 시철
-발표:</t>
+    <t>디자인: 시철, 서영, 서현(채택)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2325,7 +2327,7 @@
     <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="177" formatCode="[$-412]yyyy&quot;년&quot;\ m&quot;월&quot;\ d&quot;일&quot;\ dddd\ h&quot;시&quot;\ mm&quot;분&quot;"/>
   </numFmts>
-  <fonts count="31" x14ac:knownFonts="1">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -15852,8 +15854,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6990" y="3359481"/>
-          <a:ext cx="1175976" cy="361018"/>
+          <a:off x="10440" y="3343938"/>
+          <a:ext cx="1173405" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -15931,8 +15933,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="17564" y="3370055"/>
-        <a:ext cx="1154828" cy="339870"/>
+        <a:off x="20991" y="3354489"/>
+        <a:ext cx="1152303" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7667B88B-738E-4E27-80A6-15B1E3AED5F8}">
@@ -15942,8 +15944,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="16719080">
-          <a:off x="569904" y="2822558"/>
-          <a:ext cx="1443216" cy="8067"/>
+          <a:off x="572123" y="2808170"/>
+          <a:ext cx="1440061" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -15954,10 +15956,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1443216" y="4033"/>
+                <a:pt x="1440061" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16016,8 +16018,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1255432" y="2790512"/>
-        <a:ext cx="72160" cy="72160"/>
+        <a:off x="1256152" y="2776213"/>
+        <a:ext cx="72003" cy="72003"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D9E30B0F-B6EE-4B8A-B3A5-5AD7E4CFBC12}">
@@ -16027,8 +16029,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="1400057" y="1932685"/>
-          <a:ext cx="1442547" cy="361018"/>
+          <a:off x="1400462" y="1920262"/>
+          <a:ext cx="1439393" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16119,8 +16121,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1410631" y="1943259"/>
-        <a:ext cx="1421399" cy="339870"/>
+        <a:off x="1411013" y="1930813"/>
+        <a:ext cx="1418291" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{ED5992BD-91A0-44DC-B026-C230E027754F}">
@@ -16130,8 +16132,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="16757427">
-          <a:off x="2278791" y="1445622"/>
-          <a:ext cx="1344717" cy="8067"/>
+          <a:off x="2277274" y="1434244"/>
+          <a:ext cx="1341777" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16142,10 +16144,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1344717" y="4033"/>
+                <a:pt x="1341777" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16204,8 +16206,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2917531" y="1416037"/>
-        <a:ext cx="67235" cy="67235"/>
+        <a:off x="2914618" y="1404744"/>
+        <a:ext cx="67088" cy="67088"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{EB7188F2-1357-4748-A44C-AB5D4A48F40F}">
@@ -16215,8 +16217,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3059694" y="605607"/>
-          <a:ext cx="1405294" cy="361018"/>
+          <a:off x="3056471" y="596085"/>
+          <a:ext cx="1402222" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16286,8 +16288,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3070268" y="616181"/>
-        <a:ext cx="1384146" cy="339870"/>
+        <a:off x="3067022" y="606636"/>
+        <a:ext cx="1381120" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7531319A-E0E5-4CB4-9F35-33254694A0D7}">
@@ -16297,8 +16299,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17860289">
-          <a:off x="4341743" y="578293"/>
-          <a:ext cx="460216" cy="8067"/>
+          <a:off x="4335717" y="568811"/>
+          <a:ext cx="459210" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16309,10 +16311,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="460216" y="4033"/>
+                <a:pt x="459210" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16371,8 +16373,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4560346" y="570821"/>
-        <a:ext cx="23010" cy="23010"/>
+        <a:off x="4553842" y="561375"/>
+        <a:ext cx="22960" cy="22960"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{8F385C2E-83EB-470A-8A65-12C51C60EB27}">
@@ -16382,8 +16384,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4678714" y="196434"/>
-          <a:ext cx="1773604" cy="364206"/>
+          <a:off x="4671951" y="187807"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16453,8 +16455,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4689381" y="207101"/>
-        <a:ext cx="1752270" cy="342872"/>
+        <a:off x="4682595" y="198451"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{8EC6EEF9-E6D8-4DE2-A6DD-BB50B40A5CF0}">
@@ -16464,8 +16466,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6452318" y="374503"/>
-          <a:ext cx="220454" cy="8067"/>
+          <a:off x="6441677" y="365467"/>
+          <a:ext cx="219972" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16476,10 +16478,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="220454" y="4033"/>
+                <a:pt x="219972" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16534,8 +16536,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6557034" y="373026"/>
-        <a:ext cx="11022" cy="11022"/>
+        <a:off x="6546165" y="364012"/>
+        <a:ext cx="10998" cy="10998"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{31CFEB2D-0887-4520-AF04-1E3C38912960}">
@@ -16545,8 +16547,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6672773" y="196434"/>
-          <a:ext cx="3163311" cy="364206"/>
+          <a:off x="6661650" y="187807"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16632,8 +16634,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6683440" y="207101"/>
-        <a:ext cx="3141977" cy="342872"/>
+        <a:off x="6672294" y="198451"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{602438BB-CBF9-49AF-AB0A-D57EA2C10BE2}">
@@ -16643,8 +16645,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9836085" y="374503"/>
-          <a:ext cx="217090" cy="8067"/>
+          <a:off x="9818046" y="365467"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16655,10 +16657,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217090" y="4033"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16713,8 +16715,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9939203" y="373110"/>
-        <a:ext cx="10854" cy="10854"/>
+        <a:off x="9920939" y="364096"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{57D97F9E-094F-4C3F-82B2-5A689BC4D082}">
@@ -16724,8 +16726,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10053175" y="202565"/>
-          <a:ext cx="1805087" cy="351943"/>
+          <a:off x="10034662" y="193925"/>
+          <a:ext cx="1801141" cy="351174"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16822,8 +16824,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10063483" y="212873"/>
-        <a:ext cx="1784471" cy="331327"/>
+        <a:off x="10044948" y="204211"/>
+        <a:ext cx="1780569" cy="330602"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B3B4155B-F64B-452E-AEBC-36FE76B0BD69}">
@@ -16833,8 +16835,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="21585916">
-          <a:off x="4464988" y="781638"/>
-          <a:ext cx="217091" cy="8067"/>
+          <a:off x="4458692" y="771712"/>
+          <a:ext cx="216617" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -16845,10 +16847,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217091" y="4033"/>
+                <a:pt x="216617" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -16903,8 +16905,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4568107" y="780244"/>
-        <a:ext cx="10854" cy="10854"/>
+        <a:off x="4561585" y="770341"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D20B6C81-A2D9-4E8E-80C0-968EFF7F89E1}">
@@ -16914,8 +16916,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4682079" y="603123"/>
-          <a:ext cx="1773604" cy="364206"/>
+          <a:off x="4675308" y="593607"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -16985,8 +16987,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4692746" y="613790"/>
-        <a:ext cx="1752270" cy="342872"/>
+        <a:off x="4685952" y="604251"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7FE58BCF-6B0D-48A2-8DDE-611A1D34A4D6}">
@@ -16996,8 +16998,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6455683" y="781193"/>
-          <a:ext cx="217090" cy="8067"/>
+          <a:off x="6445035" y="771268"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17008,10 +17010,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217090" y="4033"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17066,8 +17068,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6558801" y="779799"/>
-        <a:ext cx="10854" cy="10854"/>
+        <a:off x="6547927" y="769897"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{629314FA-FCA6-45B9-99A7-2C2196A96D5C}">
@@ -17077,8 +17079,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6672773" y="603123"/>
-          <a:ext cx="3163311" cy="364206"/>
+          <a:off x="6661650" y="593607"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17177,8 +17179,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6683440" y="613790"/>
-        <a:ext cx="3141977" cy="342872"/>
+        <a:off x="6672294" y="604251"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{CCF144EB-A097-46BE-8FF7-BE5C7A394E2A}">
@@ -17188,8 +17190,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9836085" y="781193"/>
-          <a:ext cx="217090" cy="8067"/>
+          <a:off x="9818046" y="771268"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17200,10 +17202,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217090" y="4033"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17258,8 +17260,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9939203" y="779799"/>
-        <a:ext cx="10854" cy="10854"/>
+        <a:off x="9920939" y="769897"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9EE0F2D9-F39B-4921-9EAC-DBA04DC260DD}">
@@ -17269,8 +17271,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10053175" y="601345"/>
-          <a:ext cx="1805087" cy="367764"/>
+          <a:off x="10034662" y="591832"/>
+          <a:ext cx="1801141" cy="366960"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17353,8 +17355,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10063946" y="612116"/>
-        <a:ext cx="1783545" cy="346222"/>
+        <a:off x="10045410" y="602580"/>
+        <a:ext cx="1779645" cy="345464"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6169CD61-5E3A-4096-AA5A-91A22C397918}">
@@ -17364,8 +17366,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="3717526">
-          <a:off x="4342640" y="985872"/>
-          <a:ext cx="461788" cy="8067"/>
+          <a:off x="4336611" y="975499"/>
+          <a:ext cx="460779" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17376,10 +17378,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="461788" y="4033"/>
+                <a:pt x="460779" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17434,8 +17436,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4561989" y="978361"/>
-        <a:ext cx="23089" cy="23089"/>
+        <a:off x="4555481" y="968024"/>
+        <a:ext cx="23038" cy="23038"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D5FDB947-B70B-4493-B9F9-83A45503DA23}">
@@ -17445,8 +17447,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4682079" y="1011592"/>
-          <a:ext cx="1773604" cy="364206"/>
+          <a:off x="4675308" y="1001183"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17516,8 +17518,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4692746" y="1022259"/>
-        <a:ext cx="1752270" cy="342872"/>
+        <a:off x="4685952" y="1011827"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9EDF68AF-E14B-40BF-AB6D-4B01635D735A}">
@@ -17527,8 +17529,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6455683" y="1189662"/>
-          <a:ext cx="217090" cy="8067"/>
+          <a:off x="6445035" y="1178843"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17539,10 +17541,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217090" y="4033"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17597,8 +17599,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6558801" y="1188268"/>
-        <a:ext cx="10854" cy="10854"/>
+        <a:off x="6547927" y="1177472"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{5A5C0991-25ED-4076-91F2-80A2EEFC811E}">
@@ -17608,8 +17610,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6672773" y="1011592"/>
-          <a:ext cx="3163311" cy="364206"/>
+          <a:off x="6661650" y="1001183"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17743,8 +17745,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6683440" y="1022259"/>
-        <a:ext cx="3141977" cy="342872"/>
+        <a:off x="6672294" y="1011827"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{723082D3-A8E2-4807-89B5-C74C600B949E}">
@@ -17754,8 +17756,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9836085" y="1189662"/>
-          <a:ext cx="217090" cy="8067"/>
+          <a:off x="9818046" y="1178843"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17766,10 +17768,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217090" y="4033"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17824,8 +17826,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9939203" y="1188268"/>
-        <a:ext cx="10854" cy="10854"/>
+        <a:off x="9920939" y="1177472"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{05E664DE-AAC0-4D52-9AA4-DE55CA572420}">
@@ -17835,8 +17837,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10053175" y="1009813"/>
-          <a:ext cx="1805087" cy="367764"/>
+          <a:off x="10034662" y="999408"/>
+          <a:ext cx="1801141" cy="366960"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -17906,8 +17908,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10063946" y="1020584"/>
-        <a:ext cx="1783545" cy="346222"/>
+        <a:off x="10045410" y="1010156"/>
+        <a:ext cx="1779645" cy="345464"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{16F44D37-2601-482A-9095-0B3E8E10E520}">
@@ -17917,8 +17919,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="1505741">
-          <a:off x="2831290" y="2159997"/>
-          <a:ext cx="239719" cy="8067"/>
+          <a:off x="2828565" y="2147057"/>
+          <a:ext cx="239195" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -17929,10 +17931,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="239719" y="4033"/>
+                <a:pt x="239195" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -17991,8 +17993,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2945156" y="2158037"/>
-        <a:ext cx="11985" cy="11985"/>
+        <a:off x="2942183" y="2145122"/>
+        <a:ext cx="11959" cy="11959"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{2D542640-C237-42B5-8470-73084719F8F3}">
@@ -18002,8 +18004,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3059694" y="2034358"/>
-          <a:ext cx="1405294" cy="361018"/>
+          <a:off x="3056471" y="2021712"/>
+          <a:ext cx="1402222" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -18073,8 +18075,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3070268" y="2044932"/>
-        <a:ext cx="1384146" cy="339870"/>
+        <a:off x="3067022" y="2032263"/>
+        <a:ext cx="1381120" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{BFCFD3BD-878E-4ADC-81DA-3641DCD660A7}">
@@ -18084,8 +18086,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17370601">
-          <a:off x="4248521" y="1904482"/>
-          <a:ext cx="650025" cy="8067"/>
+          <a:off x="4242699" y="1892100"/>
+          <a:ext cx="648604" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18096,10 +18098,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="650025" y="4033"/>
+                <a:pt x="648604" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18154,8 +18156,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4557283" y="1892265"/>
-        <a:ext cx="32501" cy="32501"/>
+        <a:off x="4550785" y="1879930"/>
+        <a:ext cx="32430" cy="32430"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{911F1DD5-D3D2-4321-A1A5-7E2BAE25AAD5}">
@@ -18165,8 +18167,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4682079" y="1420060"/>
-          <a:ext cx="1773604" cy="364206"/>
+          <a:off x="4675308" y="1408758"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -18236,8 +18238,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4692746" y="1430727"/>
-        <a:ext cx="1752270" cy="342872"/>
+        <a:off x="4685952" y="1419402"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{F4CAC384-240B-4811-A7FE-5EF39454FD0A}">
@@ -18247,8 +18249,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6455683" y="1598130"/>
-          <a:ext cx="217090" cy="8067"/>
+          <a:off x="6445035" y="1586419"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18259,10 +18261,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217090" y="4033"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18317,8 +18319,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6558801" y="1596737"/>
-        <a:ext cx="10854" cy="10854"/>
+        <a:off x="6547927" y="1585048"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{00847D60-C67D-487A-B918-B0C406DE6A20}">
@@ -18328,8 +18330,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6672773" y="1420060"/>
-          <a:ext cx="3163311" cy="364206"/>
+          <a:off x="6661650" y="1408758"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -18439,8 +18441,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6683440" y="1430727"/>
-        <a:ext cx="3141977" cy="342872"/>
+        <a:off x="6672294" y="1419402"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7682FEBA-2A8A-4CEB-BAD3-CAC6D62452E9}">
@@ -18450,8 +18452,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9836085" y="1598130"/>
-          <a:ext cx="217090" cy="8067"/>
+          <a:off x="9818046" y="1586419"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18462,10 +18464,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217090" y="4033"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18520,8 +18522,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9939203" y="1596737"/>
-        <a:ext cx="10854" cy="10854"/>
+        <a:off x="9920939" y="1585048"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4C2C55F9-D12D-4BE1-85AD-8FAFF8B344C7}">
@@ -18531,8 +18533,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10053175" y="1418282"/>
-          <a:ext cx="1805087" cy="367764"/>
+          <a:off x="10034662" y="1406983"/>
+          <a:ext cx="1801141" cy="366960"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -18650,8 +18652,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10063946" y="1429053"/>
-        <a:ext cx="1783545" cy="346222"/>
+        <a:off x="10045410" y="1417731"/>
+        <a:ext cx="1779645" cy="345464"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6A4076F7-5C10-4205-AF7B-34977DAE41B6}">
@@ -18661,8 +18663,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19004863">
-          <a:off x="4424504" y="2108716"/>
-          <a:ext cx="298059" cy="8067"/>
+          <a:off x="4418296" y="2095888"/>
+          <a:ext cx="297408" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18673,10 +18675,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="298059" y="4033"/>
+                <a:pt x="297408" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18731,8 +18733,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4566082" y="2105298"/>
-        <a:ext cx="14902" cy="14902"/>
+        <a:off x="4559565" y="2092498"/>
+        <a:ext cx="14870" cy="14870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D2D6EBAC-87C6-4589-B626-76CA00356F2A}">
@@ -18742,8 +18744,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4682079" y="1828529"/>
-          <a:ext cx="1773604" cy="364206"/>
+          <a:off x="4675308" y="1816334"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -18813,8 +18815,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4692746" y="1839196"/>
-        <a:ext cx="1752270" cy="342872"/>
+        <a:off x="4685952" y="1826978"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4CEC118E-B718-4A3D-A714-E879160F0F50}">
@@ -18824,8 +18826,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6455683" y="2006599"/>
-          <a:ext cx="217090" cy="8067"/>
+          <a:off x="6445035" y="1993994"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -18836,10 +18838,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217090" y="4033"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -18894,8 +18896,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6558801" y="2005205"/>
-        <a:ext cx="10854" cy="10854"/>
+        <a:off x="6547927" y="1992623"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{96C9B796-69AA-48A9-AB67-0FE5F7CEFC9D}">
@@ -18905,8 +18907,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6672773" y="1828529"/>
-          <a:ext cx="3163311" cy="364206"/>
+          <a:off x="6661650" y="1816334"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19000,8 +19002,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6683440" y="1839196"/>
-        <a:ext cx="3141977" cy="342872"/>
+        <a:off x="6672294" y="1826978"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{0C4A9E51-DEA5-4AC0-B8EC-F712BFE3BA51}">
@@ -19011,8 +19013,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9836085" y="2006599"/>
-          <a:ext cx="217090" cy="8067"/>
+          <a:off x="9818046" y="1993994"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19023,10 +19025,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217090" y="4033"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19081,8 +19083,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9939203" y="2005205"/>
-        <a:ext cx="10854" cy="10854"/>
+        <a:off x="9920939" y="1992623"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{829A6295-4379-4C15-BF91-56D56B48CA13}">
@@ -19092,8 +19094,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10053175" y="1826750"/>
-          <a:ext cx="1805087" cy="367764"/>
+          <a:off x="10034662" y="1814559"/>
+          <a:ext cx="1801141" cy="366960"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19179,8 +19181,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10063946" y="1837521"/>
-        <a:ext cx="1783545" cy="346222"/>
+        <a:off x="10045410" y="1825307"/>
+        <a:ext cx="1779645" cy="345464"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{15251D3B-5937-4D92-B910-59FBB0B78504}">
@@ -19190,8 +19192,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2595137">
-          <a:off x="4424504" y="2312950"/>
-          <a:ext cx="298059" cy="8067"/>
+          <a:off x="4418296" y="2299676"/>
+          <a:ext cx="297408" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19202,10 +19204,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="298059" y="4033"/>
+                <a:pt x="297408" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19260,8 +19262,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4566082" y="2309532"/>
-        <a:ext cx="14902" cy="14902"/>
+        <a:off x="4559565" y="2296285"/>
+        <a:ext cx="14870" cy="14870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{55C8ECFC-533A-4D04-B170-164B29EE9A7D}">
@@ -19271,8 +19273,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4682079" y="2236998"/>
-          <a:ext cx="1773604" cy="364206"/>
+          <a:off x="4675308" y="2223909"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19342,8 +19344,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4692746" y="2247665"/>
-        <a:ext cx="1752270" cy="342872"/>
+        <a:off x="4685952" y="2234553"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A63458DA-4732-44A8-AAAD-101471030A2E}">
@@ -19353,8 +19355,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6455683" y="2415067"/>
-          <a:ext cx="217090" cy="8067"/>
+          <a:off x="6445035" y="2401570"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19365,10 +19367,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217090" y="4033"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19423,8 +19425,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6558801" y="2413674"/>
-        <a:ext cx="10854" cy="10854"/>
+        <a:off x="6547927" y="2400199"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{3CFC9EAC-3C3A-42EE-A809-37090C958CCC}">
@@ -19434,8 +19436,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6672773" y="2236998"/>
-          <a:ext cx="3163311" cy="364206"/>
+          <a:off x="6661650" y="2223909"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19513,8 +19515,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6683440" y="2247665"/>
-        <a:ext cx="3141977" cy="342872"/>
+        <a:off x="6672294" y="2234553"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{2E1BE310-D0FB-4439-BC13-EF25298A0AC1}">
@@ -19524,8 +19526,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9836085" y="2415067"/>
-          <a:ext cx="217090" cy="8067"/>
+          <a:off x="9818046" y="2401570"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19536,10 +19538,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217090" y="4033"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19594,8 +19596,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9939203" y="2413674"/>
-        <a:ext cx="10854" cy="10854"/>
+        <a:off x="9920939" y="2400199"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{05029C16-99B1-4993-B5A7-DFCE2EC4AF2D}">
@@ -19605,8 +19607,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10053175" y="2235219"/>
-          <a:ext cx="1805087" cy="367764"/>
+          <a:off x="10034662" y="2222134"/>
+          <a:ext cx="1801141" cy="366960"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19676,8 +19678,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10063946" y="2245990"/>
-        <a:ext cx="1783545" cy="346222"/>
+        <a:off x="10045410" y="2232882"/>
+        <a:ext cx="1779645" cy="345464"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7B1A1F24-5790-42BE-9800-70C6BAC67F71}">
@@ -19687,8 +19689,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="4229399">
-          <a:off x="4248521" y="2517184"/>
-          <a:ext cx="650025" cy="8067"/>
+          <a:off x="4242699" y="2503464"/>
+          <a:ext cx="648604" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19699,10 +19701,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="650025" y="4033"/>
+                <a:pt x="648604" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19757,8 +19759,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4557283" y="2504967"/>
-        <a:ext cx="32501" cy="32501"/>
+        <a:off x="4550785" y="2491293"/>
+        <a:ext cx="32430" cy="32430"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{F9E7099E-D348-4A20-924E-7B36E8E1B00D}">
@@ -19768,8 +19770,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4682079" y="2645466"/>
-          <a:ext cx="1792127" cy="364206"/>
+          <a:off x="4675308" y="2631485"/>
+          <a:ext cx="1788209" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -19839,8 +19841,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4692746" y="2656133"/>
-        <a:ext cx="1770793" cy="342872"/>
+        <a:off x="4685952" y="2642129"/>
+        <a:ext cx="1766921" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{69A95BFF-166E-4390-9963-14C8F025ADBA}">
@@ -19850,8 +19852,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6474206" y="2823536"/>
-          <a:ext cx="217090" cy="8067"/>
+          <a:off x="6463518" y="2809145"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -19862,10 +19864,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217090" y="4033"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -19920,8 +19922,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6577324" y="2822142"/>
-        <a:ext cx="10854" cy="10854"/>
+        <a:off x="6566410" y="2807775"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{BBDCC5A6-74D1-4E37-848C-BF5D7C733A0C}">
@@ -19931,8 +19933,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6691297" y="2645466"/>
-          <a:ext cx="3163311" cy="364206"/>
+          <a:off x="6680133" y="2631485"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20002,8 +20004,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6701964" y="2656133"/>
-        <a:ext cx="3141977" cy="342872"/>
+        <a:off x="6690777" y="2642129"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E75A9ED0-3CF3-4FBB-B735-763677226156}">
@@ -20013,8 +20015,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9854608" y="2823536"/>
-          <a:ext cx="217090" cy="8067"/>
+          <a:off x="9836529" y="2809145"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20025,10 +20027,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217090" y="4033"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20083,8 +20085,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9957726" y="2822142"/>
-        <a:ext cx="10854" cy="10854"/>
+        <a:off x="9939421" y="2807775"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D255C67C-B87B-4D25-A5F4-B2880DE74996}">
@@ -20094,8 +20096,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10071698" y="2643687"/>
-          <a:ext cx="1805087" cy="367764"/>
+          <a:off x="10053144" y="2629710"/>
+          <a:ext cx="1801141" cy="366960"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20189,8 +20191,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10082469" y="2654458"/>
-        <a:ext cx="1783545" cy="346222"/>
+        <a:off x="10063892" y="2640458"/>
+        <a:ext cx="1779645" cy="345464"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{19133C7D-D6FC-4086-9EFA-C8E67C09EF92}">
@@ -20200,8 +20202,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="4842573">
-          <a:off x="2278791" y="2772700"/>
-          <a:ext cx="1344717" cy="8067"/>
+          <a:off x="2277274" y="2758420"/>
+          <a:ext cx="1341777" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20212,10 +20214,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1344717" y="4033"/>
+                <a:pt x="1341777" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20270,8 +20272,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2917531" y="2743115"/>
-        <a:ext cx="67235" cy="67235"/>
+        <a:off x="2914618" y="2728920"/>
+        <a:ext cx="67088" cy="67088"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{3A58F96D-43A0-4E22-A03B-64FF8A7610E3}">
@@ -20281,8 +20283,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3059694" y="3259763"/>
-          <a:ext cx="1405294" cy="361018"/>
+          <a:off x="3056471" y="3244439"/>
+          <a:ext cx="1402222" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20352,8 +20354,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3070268" y="3270337"/>
-        <a:ext cx="1384146" cy="339870"/>
+        <a:off x="3067022" y="3254990"/>
+        <a:ext cx="1381120" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{BC1A1E23-E0C9-4175-8735-D110618B99B3}">
@@ -20363,8 +20365,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19004863">
-          <a:off x="4424504" y="3334122"/>
-          <a:ext cx="298059" cy="8067"/>
+          <a:off x="4418296" y="3318615"/>
+          <a:ext cx="297408" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20375,10 +20377,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="298059" y="4033"/>
+                <a:pt x="297408" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20433,8 +20435,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4566082" y="3330704"/>
-        <a:ext cx="14902" cy="14902"/>
+        <a:off x="4559565" y="3315224"/>
+        <a:ext cx="14870" cy="14870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{5D691BA5-158A-4034-AEDA-B152BE077B27}">
@@ -20444,8 +20446,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4682079" y="3053935"/>
-          <a:ext cx="1773604" cy="364206"/>
+          <a:off x="4675308" y="3039060"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20515,8 +20517,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4692746" y="3064602"/>
-        <a:ext cx="1752270" cy="342872"/>
+        <a:off x="4685952" y="3049704"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{C26309FF-9296-40B3-913C-85759C2B07DC}">
@@ -20526,8 +20528,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6455683" y="3232004"/>
-          <a:ext cx="217090" cy="8067"/>
+          <a:off x="6445035" y="3216721"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20538,10 +20540,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217090" y="4033"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20596,8 +20598,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6558801" y="3230611"/>
-        <a:ext cx="10854" cy="10854"/>
+        <a:off x="6547927" y="3215350"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A4750321-4845-43B0-945B-4B9E7C7A668E}">
@@ -20607,8 +20609,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6672773" y="3053935"/>
-          <a:ext cx="3163311" cy="364206"/>
+          <a:off x="6661650" y="3039060"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20702,8 +20704,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6683440" y="3064602"/>
-        <a:ext cx="3141977" cy="342872"/>
+        <a:off x="6672294" y="3049704"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{CCE9C4CE-7CF8-4820-8390-F3CBCCE81ED7}">
@@ -20713,8 +20715,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9836085" y="3232004"/>
-          <a:ext cx="217090" cy="8067"/>
+          <a:off x="9818046" y="3216721"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20725,10 +20727,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217090" y="4033"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20783,8 +20785,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9939203" y="3230611"/>
-        <a:ext cx="10854" cy="10854"/>
+        <a:off x="9920939" y="3215350"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D954D938-3009-44F7-BB4F-D9E8AFB2B291}">
@@ -20794,8 +20796,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10053175" y="3052156"/>
-          <a:ext cx="1805087" cy="367764"/>
+          <a:off x="10034662" y="3037285"/>
+          <a:ext cx="1801141" cy="366960"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -20865,8 +20867,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10063946" y="3062927"/>
-        <a:ext cx="1783545" cy="346222"/>
+        <a:off x="10045410" y="3048033"/>
+        <a:ext cx="1779645" cy="345464"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D01C8F64-85EC-45F5-B192-363D2A57FB6E}">
@@ -20876,8 +20878,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2595137">
-          <a:off x="4424504" y="3538356"/>
-          <a:ext cx="298059" cy="8067"/>
+          <a:off x="4418296" y="3522403"/>
+          <a:ext cx="297408" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -20888,10 +20890,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="298059" y="4033"/>
+                <a:pt x="297408" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -20946,8 +20948,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4566082" y="3534938"/>
-        <a:ext cx="14902" cy="14902"/>
+        <a:off x="4559565" y="3519012"/>
+        <a:ext cx="14870" cy="14870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7832722B-5DD1-4AAD-819C-BC966C90EDAC}">
@@ -20957,8 +20959,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4682079" y="3462403"/>
-          <a:ext cx="1773604" cy="364206"/>
+          <a:off x="4675308" y="3446636"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21028,8 +21030,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4692746" y="3473070"/>
-        <a:ext cx="1752270" cy="342872"/>
+        <a:off x="4685952" y="3457280"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9B049FA9-70FB-4D7E-AD76-2BFCDB3B4195}">
@@ -21039,8 +21041,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6455683" y="3640473"/>
-          <a:ext cx="217090" cy="8067"/>
+          <a:off x="6445035" y="3624296"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21051,10 +21053,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217090" y="4033"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21109,8 +21111,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6558801" y="3639079"/>
-        <a:ext cx="10854" cy="10854"/>
+        <a:off x="6547927" y="3622926"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B5153D0A-E9E7-482C-B1CC-838341F8F3D8}">
@@ -21120,8 +21122,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6672773" y="3462403"/>
-          <a:ext cx="3163311" cy="364206"/>
+          <a:off x="6661650" y="3446636"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21207,8 +21209,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6683440" y="3473070"/>
-        <a:ext cx="3141977" cy="342872"/>
+        <a:off x="6672294" y="3457280"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1118BB77-BCCA-46BE-8B0C-417EE0F19393}">
@@ -21218,8 +21220,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9836085" y="3640473"/>
-          <a:ext cx="217090" cy="8067"/>
+          <a:off x="9818046" y="3624296"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21230,10 +21232,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217090" y="4033"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21288,8 +21290,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9939203" y="3639079"/>
-        <a:ext cx="10854" cy="10854"/>
+        <a:off x="9920939" y="3622926"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A1FE2FD1-D3B2-4F02-B33F-7EA3496A9D7D}">
@@ -21299,8 +21301,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10053175" y="3460624"/>
-          <a:ext cx="1805087" cy="367764"/>
+          <a:off x="10034662" y="3444861"/>
+          <a:ext cx="1801141" cy="366960"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21370,8 +21372,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10063946" y="3471395"/>
-        <a:ext cx="1783545" cy="346222"/>
+        <a:off x="10045410" y="3455609"/>
+        <a:ext cx="1779645" cy="345464"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{ACD64E2A-6A03-49D1-9C11-853B1D5FDA3F}">
@@ -21381,8 +21383,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="4880920">
-          <a:off x="569904" y="4249354"/>
-          <a:ext cx="1443216" cy="8067"/>
+          <a:off x="572123" y="4231846"/>
+          <a:ext cx="1440061" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21393,10 +21395,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="1443216" y="4033"/>
+                <a:pt x="1440061" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21451,8 +21453,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1255432" y="4217307"/>
-        <a:ext cx="72160" cy="72160"/>
+        <a:off x="1256152" y="4199889"/>
+        <a:ext cx="72003" cy="72003"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4915DA81-5EFF-4A45-B117-A1C9369BA960}">
@@ -21462,8 +21464,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="1400057" y="4786276"/>
-          <a:ext cx="1435627" cy="361018"/>
+          <a:off x="1400462" y="4767614"/>
+          <a:ext cx="1432488" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21585,8 +21587,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="1410631" y="4796850"/>
-        <a:ext cx="1414479" cy="339870"/>
+        <a:off x="1411013" y="4778165"/>
+        <a:ext cx="1411386" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A3777E34-F7A1-4ABC-99E9-9C9A9AB7B959}">
@@ -21596,8 +21598,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="17225057">
-          <a:off x="2579955" y="4616622"/>
-          <a:ext cx="724217" cy="8067"/>
+          <a:off x="2577781" y="4598311"/>
+          <a:ext cx="722633" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21608,10 +21610,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="724217" y="4033"/>
+                <a:pt x="722633" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21666,8 +21668,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2923959" y="4602550"/>
-        <a:ext cx="36210" cy="36210"/>
+        <a:off x="2921032" y="4584290"/>
+        <a:ext cx="36131" cy="36131"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{23228D17-0E30-4278-86F1-009AEEE4B90D}">
@@ -21677,8 +21679,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3048444" y="4094016"/>
-          <a:ext cx="1405294" cy="361018"/>
+          <a:off x="3045245" y="4076868"/>
+          <a:ext cx="1402222" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21748,8 +21750,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3059018" y="4104590"/>
-        <a:ext cx="1384146" cy="339870"/>
+        <a:off x="3055796" y="4087419"/>
+        <a:ext cx="1381120" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A22E3146-1836-4A0C-A6D3-4503A76A9781}">
@@ -21759,8 +21761,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19004863">
-          <a:off x="4413253" y="4168374"/>
-          <a:ext cx="298059" cy="8067"/>
+          <a:off x="4407070" y="4151044"/>
+          <a:ext cx="297408" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21771,10 +21773,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="298059" y="4033"/>
+                <a:pt x="297408" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -21829,8 +21831,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4554832" y="4164956"/>
-        <a:ext cx="14902" cy="14902"/>
+        <a:off x="4548339" y="4147653"/>
+        <a:ext cx="14870" cy="14870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{06E3AC3D-2CA5-4C28-B4EE-08E1F5093575}">
@@ -21840,8 +21842,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4670828" y="3888187"/>
-          <a:ext cx="1773604" cy="364206"/>
+          <a:off x="4664082" y="3871489"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -21927,8 +21929,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4681495" y="3898854"/>
-        <a:ext cx="1752270" cy="342872"/>
+        <a:off x="4674726" y="3882133"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{AB38F8C9-39F9-48F1-A4B9-359AD3B6C9E1}">
@@ -21938,8 +21940,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6444433" y="4066257"/>
-          <a:ext cx="217090" cy="8067"/>
+          <a:off x="6433809" y="4049150"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -21950,10 +21952,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217090" y="4033"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22008,8 +22010,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6547550" y="4064863"/>
-        <a:ext cx="10854" cy="10854"/>
+        <a:off x="6536701" y="4047779"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{94E3E4AC-563C-467A-AD10-294BF8A33BAF}">
@@ -22019,8 +22021,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6661523" y="3888187"/>
-          <a:ext cx="3163311" cy="364206"/>
+          <a:off x="6650424" y="3871489"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22106,8 +22108,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6672190" y="3898854"/>
-        <a:ext cx="3141977" cy="342872"/>
+        <a:off x="6661068" y="3882133"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{CE4A2E59-3DB6-4586-9EDA-16655120708B}">
@@ -22117,8 +22119,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9824834" y="4066257"/>
-          <a:ext cx="217090" cy="8067"/>
+          <a:off x="9806820" y="4049150"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22129,10 +22131,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217090" y="4033"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22187,8 +22189,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9927952" y="4064863"/>
-        <a:ext cx="10854" cy="10854"/>
+        <a:off x="9909712" y="4047779"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{74F8E0C0-A1C2-4026-BDD1-211E4452BF84}">
@@ -22198,8 +22200,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10041924" y="3886409"/>
-          <a:ext cx="1805087" cy="367764"/>
+          <a:off x="10023436" y="3869714"/>
+          <a:ext cx="1801141" cy="366960"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22269,8 +22271,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10052695" y="3897180"/>
-        <a:ext cx="1783545" cy="346222"/>
+        <a:off x="10034184" y="3880462"/>
+        <a:ext cx="1779645" cy="345464"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{3776BE60-D86F-469E-9605-E0609281B4B9}">
@@ -22280,8 +22282,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2595137">
-          <a:off x="4413253" y="4372609"/>
-          <a:ext cx="298059" cy="8067"/>
+          <a:off x="4407070" y="4354831"/>
+          <a:ext cx="297408" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22292,10 +22294,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="298059" y="4033"/>
+                <a:pt x="297408" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22350,8 +22352,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4554832" y="4369191"/>
-        <a:ext cx="14902" cy="14902"/>
+        <a:off x="4548339" y="4351441"/>
+        <a:ext cx="14870" cy="14870"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{DC0F0790-8247-4EA1-A5BD-20B9C2810EA5}">
@@ -22361,8 +22363,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4670828" y="4296656"/>
-          <a:ext cx="1773604" cy="364206"/>
+          <a:off x="4664082" y="4279065"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22432,8 +22434,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4681495" y="4307323"/>
-        <a:ext cx="1752270" cy="342872"/>
+        <a:off x="4674726" y="4289709"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{82B78A4F-EF07-4DEA-A3EC-7BA9DD55DC45}">
@@ -22443,8 +22445,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6444433" y="4474726"/>
-          <a:ext cx="217090" cy="8067"/>
+          <a:off x="6433809" y="4456725"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22455,10 +22457,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217090" y="4033"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22513,8 +22515,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6547550" y="4473332"/>
-        <a:ext cx="10854" cy="10854"/>
+        <a:off x="6536701" y="4455354"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4D82C0F8-05DA-476F-9FFD-EF5362E37ABC}">
@@ -22524,8 +22526,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6661523" y="4296656"/>
-          <a:ext cx="3163311" cy="364206"/>
+          <a:off x="6650424" y="4279065"/>
+          <a:ext cx="3156395" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22603,8 +22605,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6672190" y="4307323"/>
-        <a:ext cx="3141977" cy="342872"/>
+        <a:off x="6661068" y="4289709"/>
+        <a:ext cx="3135107" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6F09ED48-69E5-4359-AEF9-003C31CF3834}">
@@ -22614,8 +22616,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9824834" y="4474726"/>
-          <a:ext cx="217090" cy="8067"/>
+          <a:off x="9806820" y="4456725"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22626,10 +22628,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217090" y="4033"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22684,8 +22686,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9927952" y="4473332"/>
-        <a:ext cx="10854" cy="10854"/>
+        <a:off x="9909712" y="4455354"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{7F4C8494-F5DD-49F1-B7FE-320AAF64A334}">
@@ -22695,8 +22697,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10041924" y="4294877"/>
-          <a:ext cx="1805087" cy="367764"/>
+          <a:off x="10023436" y="4277290"/>
+          <a:ext cx="1801141" cy="366960"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22771,8 +22773,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10052695" y="4305648"/>
-        <a:ext cx="1783545" cy="346222"/>
+        <a:off x="10034184" y="4288038"/>
+        <a:ext cx="1779645" cy="345464"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E97A89EA-A088-4B36-94ED-03E39FF28C24}">
@@ -22782,8 +22784,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="1512707">
-          <a:off x="2824256" y="5013856"/>
-          <a:ext cx="239947" cy="8067"/>
+          <a:off x="2821547" y="4994677"/>
+          <a:ext cx="239423" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22794,10 +22796,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="239947" y="4033"/>
+                <a:pt x="239423" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -22852,8 +22854,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2938231" y="5011891"/>
-        <a:ext cx="11997" cy="11997"/>
+        <a:off x="2935273" y="4992736"/>
+        <a:ext cx="11971" cy="11971"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{1279AA60-C872-4597-B281-C6CC2E4A34C2}">
@@ -22863,8 +22865,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3052775" y="4888486"/>
-          <a:ext cx="1405294" cy="361018"/>
+          <a:off x="3049566" y="4869600"/>
+          <a:ext cx="1402222" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -22934,8 +22936,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3063349" y="4899060"/>
-        <a:ext cx="1384146" cy="339870"/>
+        <a:off x="3060117" y="4880151"/>
+        <a:ext cx="1381120" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{255CD393-ED80-4D10-A68E-31ED59592E3B}">
@@ -22945,8 +22947,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="19138242">
-          <a:off x="4423432" y="4972391"/>
-          <a:ext cx="282034" cy="8067"/>
+          <a:off x="4417227" y="4953303"/>
+          <a:ext cx="281417" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -22957,10 +22959,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="282034" y="4033"/>
+                <a:pt x="281417" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23015,8 +23017,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4557398" y="4969374"/>
-        <a:ext cx="14101" cy="14101"/>
+        <a:off x="4550900" y="4950312"/>
+        <a:ext cx="14070" cy="14070"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{2340676A-EBD4-4E22-BA9C-E56B6A62904C}">
@@ -23026,8 +23028,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4670828" y="4701751"/>
-          <a:ext cx="1773604" cy="364206"/>
+          <a:off x="4664082" y="4683274"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23097,8 +23099,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4681495" y="4712418"/>
-        <a:ext cx="1752270" cy="342872"/>
+        <a:off x="4674726" y="4693918"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{EB837690-03CF-4B39-A4B0-AFC71E15928A}">
@@ -23108,8 +23110,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="27806">
-          <a:off x="6444429" y="4880717"/>
-          <a:ext cx="221428" cy="8067"/>
+          <a:off x="6433805" y="4861829"/>
+          <a:ext cx="220944" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23120,10 +23122,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="221428" y="4033"/>
+                <a:pt x="220944" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23178,8 +23180,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6549607" y="4879215"/>
-        <a:ext cx="11071" cy="11071"/>
+        <a:off x="6538754" y="4860350"/>
+        <a:ext cx="11047" cy="11047"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{6CD3FE0A-3BBE-455B-B381-72424654A1B0}">
@@ -23189,8 +23191,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6665854" y="4705137"/>
-          <a:ext cx="3162508" cy="361018"/>
+          <a:off x="6654746" y="4686652"/>
+          <a:ext cx="3155594" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23268,8 +23270,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6676428" y="4715711"/>
-        <a:ext cx="3141360" cy="339870"/>
+        <a:off x="6665297" y="4697203"/>
+        <a:ext cx="3134492" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{B86CABA2-1933-4D02-A0D3-AA6DEA35BCA7}">
@@ -23279,8 +23281,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9828362" y="4881612"/>
-          <a:ext cx="217090" cy="8067"/>
+          <a:off x="9810340" y="4862722"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23291,10 +23293,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217090" y="4033"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23349,8 +23351,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9931480" y="4880218"/>
-        <a:ext cx="10854" cy="10854"/>
+        <a:off x="9913232" y="4861351"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{920A36CD-D69B-4AB0-8DA2-4963F1111FE2}">
@@ -23360,8 +23362,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10045452" y="4705137"/>
-          <a:ext cx="1805087" cy="361018"/>
+          <a:off x="10026956" y="4686652"/>
+          <a:ext cx="1801141" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23431,8 +23433,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10056026" y="4715711"/>
-        <a:ext cx="1783939" cy="339870"/>
+        <a:off x="10037507" y="4697203"/>
+        <a:ext cx="1780039" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{EE30240B-4D3F-4585-94A4-7AD0CBEBACD0}">
@@ -23442,8 +23444,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="2755727">
-          <a:off x="4411506" y="5174847"/>
-          <a:ext cx="305885" cy="8067"/>
+          <a:off x="4405327" y="5155316"/>
+          <a:ext cx="305216" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23454,10 +23456,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="305885" y="4033"/>
+                <a:pt x="305216" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23512,8 +23514,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4556802" y="5171233"/>
-        <a:ext cx="15294" cy="15294"/>
+        <a:off x="4550305" y="5151730"/>
+        <a:ext cx="15260" cy="15260"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9B0332A1-DFA5-4E72-89B6-8E8C50F667E1}">
@@ -23523,8 +23525,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4670828" y="5106662"/>
-          <a:ext cx="1773604" cy="364206"/>
+          <a:off x="4664082" y="5087300"/>
+          <a:ext cx="1769726" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23621,8 +23623,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4681495" y="5117329"/>
-        <a:ext cx="1752270" cy="342872"/>
+        <a:off x="4674726" y="5097944"/>
+        <a:ext cx="1748438" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{4EF5B1E7-3D92-44D9-8E8A-E2A10FB649AC}">
@@ -23632,8 +23634,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="27806">
-          <a:off x="6444429" y="5285628"/>
-          <a:ext cx="221428" cy="8067"/>
+          <a:off x="6433805" y="5265854"/>
+          <a:ext cx="220944" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23644,10 +23646,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="221428" y="4033"/>
+                <a:pt x="220944" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23702,8 +23704,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6549607" y="5284126"/>
-        <a:ext cx="11071" cy="11071"/>
+        <a:off x="6538754" y="5264375"/>
+        <a:ext cx="11047" cy="11047"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{9AC7A0EB-B59E-41D9-A589-CB90FBF4305E}">
@@ -23713,8 +23715,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6665854" y="5110048"/>
-          <a:ext cx="3162508" cy="361018"/>
+          <a:off x="6654746" y="5090678"/>
+          <a:ext cx="3155594" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23800,8 +23802,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6676428" y="5120622"/>
-        <a:ext cx="3141360" cy="339870"/>
+        <a:off x="6665297" y="5101229"/>
+        <a:ext cx="3134492" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{2F5A23ED-2B4B-4307-BAD6-D126CED4ED45}">
@@ -23811,8 +23813,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9828362" y="5286523"/>
-          <a:ext cx="217090" cy="8067"/>
+          <a:off x="9810340" y="5266748"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23823,10 +23825,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217090" y="4033"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -23881,8 +23883,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9931480" y="5285129"/>
-        <a:ext cx="10854" cy="10854"/>
+        <a:off x="9913232" y="5265377"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{C9CCA1DF-737F-40B9-8662-1EBAE874B88C}">
@@ -23892,8 +23894,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10045452" y="5110048"/>
-          <a:ext cx="1805087" cy="361018"/>
+          <a:off x="10026956" y="5090678"/>
+          <a:ext cx="1801141" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -23963,8 +23965,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10056026" y="5120622"/>
-        <a:ext cx="1783939" cy="339870"/>
+        <a:off x="10037507" y="5101229"/>
+        <a:ext cx="1780039" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{06804470-2E4E-45CC-AD07-54CD8F165228}">
@@ -23974,8 +23976,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm rot="4379331">
-          <a:off x="2573209" y="5317540"/>
-          <a:ext cx="742041" cy="8067"/>
+          <a:off x="2571049" y="5297697"/>
+          <a:ext cx="740419" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -23986,10 +23988,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="742041" y="4033"/>
+                <a:pt x="740419" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -24044,8 +24046,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="2925679" y="5303022"/>
-        <a:ext cx="37102" cy="37102"/>
+        <a:off x="2922748" y="5283231"/>
+        <a:ext cx="37020" cy="37020"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{D9D1FF4E-B146-4A17-8BAD-E6A8247731B1}">
@@ -24055,8 +24057,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="3052775" y="5495852"/>
-          <a:ext cx="1405300" cy="361018"/>
+          <a:off x="3049566" y="5475639"/>
+          <a:ext cx="1402227" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -24142,8 +24144,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="3063349" y="5506426"/>
-        <a:ext cx="1384152" cy="339870"/>
+        <a:off x="3060117" y="5486190"/>
+        <a:ext cx="1381125" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{458C594D-E94A-4416-A27A-8211BD0C18EB}">
@@ -24153,8 +24155,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4458075" y="5672328"/>
-          <a:ext cx="217090" cy="8067"/>
+          <a:off x="4451794" y="5651709"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -24165,10 +24167,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217090" y="4033"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -24223,8 +24225,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4561192" y="5670934"/>
-        <a:ext cx="10854" cy="10854"/>
+        <a:off x="4554686" y="5650338"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{E6BB35B6-4DC7-42B5-A329-D93F595605BC}">
@@ -24234,8 +24236,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="4675165" y="5494258"/>
-          <a:ext cx="1763113" cy="364206"/>
+          <a:off x="4668409" y="5474048"/>
+          <a:ext cx="1759258" cy="363410"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -24321,8 +24323,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="4685832" y="5504925"/>
-        <a:ext cx="1741779" cy="342872"/>
+        <a:off x="4679053" y="5484692"/>
+        <a:ext cx="1737970" cy="342122"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{F3CE9778-2DAD-459C-A92D-C581128238EF}">
@@ -24332,8 +24334,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6438278" y="5672328"/>
-          <a:ext cx="217090" cy="8067"/>
+          <a:off x="6427668" y="5651709"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -24344,10 +24346,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217090" y="4033"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -24402,8 +24404,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6541396" y="5670934"/>
-        <a:ext cx="10854" cy="10854"/>
+        <a:off x="6530560" y="5650338"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{A62201D7-F2CC-41E5-BB68-F68B79E1464B}">
@@ -24413,8 +24415,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="6655368" y="5495852"/>
-          <a:ext cx="3162508" cy="361018"/>
+          <a:off x="6644283" y="5475639"/>
+          <a:ext cx="3155594" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -24484,8 +24486,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="6665942" y="5506426"/>
-        <a:ext cx="3141360" cy="339870"/>
+        <a:off x="6654834" y="5486190"/>
+        <a:ext cx="3134492" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{46794C65-61A0-4B52-A42E-5CC9D77E3723}">
@@ -24495,8 +24497,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="9817877" y="5672328"/>
-          <a:ext cx="217090" cy="8067"/>
+          <a:off x="9799878" y="5651709"/>
+          <a:ext cx="216615" cy="8089"/>
         </a:xfrm>
         <a:custGeom>
           <a:avLst/>
@@ -24507,10 +24509,10 @@
           <a:pathLst>
             <a:path>
               <a:moveTo>
-                <a:pt x="0" y="4033"/>
+                <a:pt x="0" y="4044"/>
               </a:moveTo>
               <a:lnTo>
-                <a:pt x="217090" y="4033"/>
+                <a:pt x="216615" y="4044"/>
               </a:lnTo>
             </a:path>
           </a:pathLst>
@@ -24565,8 +24567,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="9920994" y="5670934"/>
-        <a:ext cx="10854" cy="10854"/>
+        <a:off x="9902770" y="5650338"/>
+        <a:ext cx="10830" cy="10830"/>
       </dsp:txXfrm>
     </dsp:sp>
     <dsp:sp modelId="{C61F938B-5A64-4BF7-B003-81E0909084B1}">
@@ -24576,8 +24578,8 @@
       </dsp:nvSpPr>
       <dsp:spPr>
         <a:xfrm>
-          <a:off x="10034967" y="5495852"/>
-          <a:ext cx="1805087" cy="361018"/>
+          <a:off x="10016493" y="5475639"/>
+          <a:ext cx="1801141" cy="360228"/>
         </a:xfrm>
         <a:prstGeom prst="roundRect">
           <a:avLst>
@@ -24647,8 +24649,8 @@
         </a:p>
       </dsp:txBody>
       <dsp:txXfrm>
-        <a:off x="10045541" y="5506426"/>
-        <a:ext cx="1783939" cy="339870"/>
+        <a:off x="10027044" y="5486190"/>
+        <a:ext cx="1780039" cy="339126"/>
       </dsp:txXfrm>
     </dsp:sp>
   </dsp:spTree>
@@ -27494,6 +27496,56 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>25400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>651566</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>2517</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="그림 1">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{64700A10-19E5-8741-183A-C3850B8FCA69}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="25400"/>
+          <a:ext cx="10590696" cy="5145465"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
@@ -27794,215 +27846,215 @@
   <sheetPr>
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:C134"/>
-  <sheetFormatPr defaultRowHeight="17" outlineLevelRow="2" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:C135"/>
+  <sheetFormatPr defaultRowHeight="17" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="16.83203125" style="20" customWidth="1"/>
     <col min="2" max="2" width="32.9140625" customWidth="1"/>
     <col min="3" max="3" width="30.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="36" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:1" ht="36">
       <c r="A1" s="19" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="26" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:1" ht="26">
       <c r="A3" s="21" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A4" s="22" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A5" s="22" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="7" spans="1:1" ht="26" collapsed="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:1" hidden="1" outlineLevel="1"/>
+    <row r="7" spans="1:1" ht="26" collapsed="1">
       <c r="A7" s="21" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="8" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A8" s="20" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A9" s="20" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A10" s="20" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="11" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="12" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:1" hidden="1" outlineLevel="1"/>
+    <row r="12" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A12" s="22" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="14" spans="1:1" ht="21" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:1" hidden="1" outlineLevel="1"/>
+    <row r="14" spans="1:1" ht="21" hidden="1" outlineLevel="1">
       <c r="A14" s="23" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A15" s="24" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="17" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:1" hidden="1" outlineLevel="1"/>
+    <row r="17" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A17" s="25" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="18" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A18" s="25" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A19" s="25" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A20" s="25" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="21" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A21" s="25" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="22" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A22" s="25" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A23" s="25" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A24" s="25" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A25" s="25" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A26" s="25" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="27" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A27" s="25" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="29" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:1" hidden="1" outlineLevel="1"/>
+    <row r="29" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A29" s="22" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A30" s="20" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="31" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A31" s="20" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="32" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A32" s="20" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="33" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="34" spans="1:1" ht="26" collapsed="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:1" hidden="1" outlineLevel="1"/>
+    <row r="34" spans="1:1" ht="26" collapsed="1">
       <c r="A34" s="21" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="35" spans="1:1" hidden="1" outlineLevel="2" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:1" hidden="1" outlineLevel="2">
       <c r="A35" s="20" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="36" spans="1:1" hidden="1" outlineLevel="2" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:1" hidden="1" outlineLevel="2">
       <c r="A36" s="22" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="37" spans="1:1" hidden="1" outlineLevel="2" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:1" hidden="1" outlineLevel="2">
       <c r="A37" s="20" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="38" spans="1:1" hidden="1" outlineLevel="2" x14ac:dyDescent="0.45"/>
-    <row r="39" spans="1:1" hidden="1" outlineLevel="2" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:1" hidden="1" outlineLevel="2"/>
+    <row r="39" spans="1:1" hidden="1" outlineLevel="2">
       <c r="A39" s="22" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="40" spans="1:1" hidden="1" outlineLevel="2" x14ac:dyDescent="0.45"/>
-    <row r="41" spans="1:1" ht="26" collapsed="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:1" hidden="1" outlineLevel="2"/>
+    <row r="41" spans="1:1" ht="26" collapsed="1">
       <c r="A41" s="21" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="42" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A42" s="20" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="43" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A43" s="20" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="44" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A44" s="20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="45" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="46" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:1" hidden="1" outlineLevel="1"/>
+    <row r="46" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A46" s="22" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="47" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="48" spans="1:1" ht="21" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:1" hidden="1" outlineLevel="1"/>
+    <row r="48" spans="1:1" ht="21" hidden="1" outlineLevel="1">
       <c r="A48" s="23" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="21" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:3" ht="21" hidden="1" outlineLevel="1">
       <c r="A49" s="23" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="50" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:3" hidden="1" outlineLevel="1">
       <c r="A50" s="26"/>
       <c r="B50" s="17" t="s">
         <v>77</v>
@@ -28011,7 +28063,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="51" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:3" hidden="1" outlineLevel="1">
       <c r="A51" s="27" t="s">
         <v>79</v>
       </c>
@@ -28022,7 +28074,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="52" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:3" hidden="1" outlineLevel="1">
       <c r="A52" s="27" t="s">
         <v>82</v>
       </c>
@@ -28033,7 +28085,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="53" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:3" hidden="1" outlineLevel="1">
       <c r="A53" s="27" t="s">
         <v>85</v>
       </c>
@@ -28044,7 +28096,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="54" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:3" hidden="1" outlineLevel="1">
       <c r="A54" s="27" t="s">
         <v>88</v>
       </c>
@@ -28055,7 +28107,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="55" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:3" hidden="1" outlineLevel="1">
       <c r="A55" s="27" t="s">
         <v>91</v>
       </c>
@@ -28066,231 +28118,231 @@
         <v>93</v>
       </c>
     </row>
-    <row r="56" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="57" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:3" hidden="1" outlineLevel="1"/>
+    <row r="57" spans="1:3" hidden="1" outlineLevel="1">
       <c r="A57" s="22" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="58" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:3" hidden="1" outlineLevel="1">
       <c r="A58" s="24" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="59" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="60" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:3" hidden="1" outlineLevel="1"/>
+    <row r="60" spans="1:3" hidden="1" outlineLevel="1">
       <c r="A60" s="25" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="61" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:3" hidden="1" outlineLevel="1">
       <c r="A61" s="25" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="62" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:3" hidden="1" outlineLevel="1">
       <c r="A62" s="25" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="63" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:3" hidden="1" outlineLevel="1">
       <c r="A63" s="25" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="64" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:3" hidden="1" outlineLevel="1">
       <c r="A64" s="25" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="65" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A65" s="25" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="66" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A66" s="25" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="67" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A67" s="25" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="68" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A68" s="25" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="69" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A69" s="25" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="70" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A70" s="25" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="71" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A71" s="25" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="72" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A72" s="25" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="73" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A73" s="25" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="74" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="75" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:1" hidden="1" outlineLevel="1"/>
+    <row r="75" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A75" s="22" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A76" s="20" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="77" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A77" s="20" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="78" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A78" s="20" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="79" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="80" spans="1:1" ht="21" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:1" hidden="1" outlineLevel="1"/>
+    <row r="80" spans="1:1" ht="21" hidden="1" outlineLevel="1">
       <c r="A80" s="23" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="81" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A81" s="22" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="82" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A82" s="22" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="83" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A83" s="22" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="84" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A84" s="20" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="85" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="86" spans="1:1" ht="26" collapsed="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:1" hidden="1" outlineLevel="1"/>
+    <row r="86" spans="1:1" ht="26" collapsed="1">
       <c r="A86" s="21" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="87" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A87" s="20" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="88" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A88" s="20" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="89" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A89" s="20" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="90" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="91" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:1" hidden="1" outlineLevel="1"/>
+    <row r="91" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A91" s="22" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="92" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="93" spans="1:1" ht="26" collapsed="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:1" hidden="1" outlineLevel="1"/>
+    <row r="93" spans="1:1" ht="26" collapsed="1">
       <c r="A93" s="21" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="94" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A94" s="20" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="95" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A95" s="20" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="96" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:1" hidden="1" outlineLevel="1">
       <c r="A96" s="20" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="97" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="98" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:3" hidden="1" outlineLevel="1"/>
+    <row r="98" spans="1:3" hidden="1" outlineLevel="1">
       <c r="A98" s="22" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="99" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="100" spans="1:3" ht="26" collapsed="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:3" hidden="1" outlineLevel="1"/>
+    <row r="100" spans="1:3" ht="26" collapsed="1">
       <c r="A100" s="21" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="101" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:3" hidden="1" outlineLevel="1">
       <c r="A101" s="20" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="102" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:3" hidden="1" outlineLevel="1">
       <c r="A102" s="20" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="103" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="104" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:3" hidden="1" outlineLevel="1"/>
+    <row r="104" spans="1:3" hidden="1" outlineLevel="1">
       <c r="A104" s="22" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="105" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="106" spans="1:3" ht="26" collapsed="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:3" hidden="1" outlineLevel="1"/>
+    <row r="106" spans="1:3" ht="26" collapsed="1">
       <c r="A106" s="21" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="107" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="108" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:3" hidden="1" outlineLevel="1"/>
+    <row r="108" spans="1:3" hidden="1" outlineLevel="1">
       <c r="A108" s="20" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="109" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="110" spans="1:3" ht="21" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:3" hidden="1" outlineLevel="1"/>
+    <row r="110" spans="1:3" ht="21" hidden="1" outlineLevel="1">
       <c r="A110" s="23" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="111" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="112" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:3" hidden="1" outlineLevel="1"/>
+    <row r="112" spans="1:3" hidden="1" outlineLevel="1">
       <c r="A112" s="26" t="s">
         <v>132</v>
       </c>
@@ -28301,7 +28353,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="34" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:3" ht="34" hidden="1" outlineLevel="1">
       <c r="A113" s="27" t="s">
         <v>135</v>
       </c>
@@ -28312,7 +28364,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="51" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:3" ht="51" hidden="1" outlineLevel="1">
       <c r="A114" s="27" t="s">
         <v>138</v>
       </c>
@@ -28323,51 +28375,51 @@
         <v>140</v>
       </c>
     </row>
-    <row r="115" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="116" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:3" hidden="1" outlineLevel="1"/>
+    <row r="116" spans="1:3" hidden="1" outlineLevel="1">
       <c r="A116" s="20" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="117" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="118" spans="1:3" ht="21" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:3" hidden="1" outlineLevel="1"/>
+    <row r="118" spans="1:3" ht="21" hidden="1" outlineLevel="1">
       <c r="A118" s="23" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="119" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:3" hidden="1" outlineLevel="1">
       <c r="A119" s="20" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="120" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:3" hidden="1" outlineLevel="1">
       <c r="A120" s="20" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="121" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:3" hidden="1" outlineLevel="1">
       <c r="A121" s="20" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="122" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:3" hidden="1" outlineLevel="1">
       <c r="A122" s="20" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="123" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="124" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:3" hidden="1" outlineLevel="1"/>
+    <row r="124" spans="1:3" hidden="1" outlineLevel="1">
       <c r="A124" s="22" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="125" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45"/>
-    <row r="126" spans="1:3" ht="21" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:3" hidden="1" outlineLevel="1"/>
+    <row r="126" spans="1:3" ht="21" collapsed="1">
       <c r="A126" s="23" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="127" spans="1:3" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:3" hidden="1" outlineLevel="1">
       <c r="A127" s="30" t="s">
         <v>148</v>
       </c>
@@ -28375,7 +28427,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="34" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:3" ht="34" hidden="1" outlineLevel="1">
       <c r="A128" s="31" t="s">
         <v>150</v>
       </c>
@@ -28383,7 +28435,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="129" spans="1:2" ht="51" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:2" ht="51" hidden="1" outlineLevel="1">
       <c r="A129" s="31" t="s">
         <v>152</v>
       </c>
@@ -28391,7 +28443,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="130" spans="1:2" ht="34" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:2" ht="34" hidden="1" outlineLevel="1">
       <c r="A130" s="31" t="s">
         <v>154</v>
       </c>
@@ -28399,7 +28451,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="131" spans="1:2" ht="51" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:2" ht="51" hidden="1" outlineLevel="1">
       <c r="A131" s="31" t="s">
         <v>156</v>
       </c>
@@ -28407,7 +28459,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="132" spans="1:2" ht="34" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:2" ht="34" hidden="1" outlineLevel="1">
       <c r="A132" s="31" t="s">
         <v>158</v>
       </c>
@@ -28415,7 +28467,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="133" spans="1:2" ht="34" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:2" ht="34" hidden="1" outlineLevel="1">
       <c r="A133" s="31" t="s">
         <v>160</v>
       </c>
@@ -28423,7 +28475,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="134" spans="1:2" ht="34" outlineLevel="1" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:2" ht="34" hidden="1" outlineLevel="1">
       <c r="A134" s="31" t="s">
         <v>162</v>
       </c>
@@ -28431,6 +28483,7 @@
         <v>163</v>
       </c>
     </row>
+    <row r="135" spans="1:2" collapsed="1"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -28443,7 +28496,7 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="8.9140625" customWidth="1"/>
     <col min="2" max="2" width="51.9140625" customWidth="1"/>
@@ -28452,7 +28505,7 @@
     <col min="5" max="5" width="65.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5">
       <c r="A1" s="62" t="s">
         <v>336</v>
       </c>
@@ -28469,7 +28522,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="51" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" ht="51">
       <c r="A2" s="61">
         <v>1</v>
       </c>
@@ -28486,7 +28539,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="85" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" ht="85">
       <c r="A3" s="61">
         <v>2</v>
       </c>
@@ -28503,7 +28556,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="68" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" ht="68">
       <c r="A4" s="61">
         <v>3</v>
       </c>
@@ -28520,7 +28573,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="51" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" ht="51">
       <c r="A5" s="61">
         <v>4</v>
       </c>
@@ -28537,7 +28590,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="85" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" ht="85">
       <c r="A6" s="61">
         <v>5</v>
       </c>
@@ -28554,7 +28607,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="68" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" ht="68">
       <c r="A7" s="61">
         <v>6</v>
       </c>
@@ -28571,7 +28624,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="51" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" ht="51">
       <c r="A8" s="61">
         <v>7</v>
       </c>
@@ -28588,7 +28641,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="85" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5" ht="85">
       <c r="A9" s="61">
         <v>8</v>
       </c>
@@ -28605,7 +28658,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5" ht="32" customHeight="1">
       <c r="A10" s="61">
         <v>9</v>
       </c>
@@ -28622,7 +28675,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:5" ht="51" customHeight="1">
       <c r="A11" s="61">
         <v>10</v>
       </c>
@@ -28635,7 +28688,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="51" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:5" ht="51">
       <c r="A12" s="61">
         <v>11</v>
       </c>
@@ -28652,7 +28705,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="34" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:5" ht="34">
       <c r="A13" s="61">
         <v>12</v>
       </c>
@@ -28667,7 +28720,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="34" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:5" ht="34">
       <c r="A14" s="61">
         <v>13</v>
       </c>
@@ -28682,7 +28735,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="35.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:5" ht="35.5" customHeight="1">
       <c r="A15" s="61">
         <v>14</v>
       </c>
@@ -28695,7 +28748,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="34" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:5" ht="34">
       <c r="A16" s="61">
         <v>15</v>
       </c>
@@ -28710,13 +28763,13 @@
         <v>479</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5">
       <c r="A17" s="20"/>
       <c r="B17" s="83"/>
       <c r="C17" s="80"/>
       <c r="E17" s="80"/>
     </row>
-    <row r="18" spans="1:5" ht="20.5" x14ac:dyDescent="0.55000000000000004">
+    <row r="18" spans="1:5" ht="20.5">
       <c r="A18" s="82" t="s">
         <v>491</v>
       </c>
@@ -28724,7 +28777,7 @@
       <c r="C18" s="69"/>
       <c r="E18" s="69"/>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:5">
       <c r="A19" s="60" t="s">
         <v>508</v>
       </c>
@@ -28741,7 +28794,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="85" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:5" ht="85">
       <c r="A20" s="84">
         <v>1</v>
       </c>
@@ -28758,7 +28811,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="68" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:5" ht="68">
       <c r="A21" s="84">
         <v>2</v>
       </c>
@@ -28775,7 +28828,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="102" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:5" ht="102">
       <c r="A22" s="84">
         <v>3</v>
       </c>
@@ -28792,7 +28845,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="68" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:5" ht="68">
       <c r="A23" s="84">
         <v>4</v>
       </c>
@@ -28822,11 +28875,16 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03EAFDCE-DB4E-46B3-9A49-EC7FC892A3F4}">
+  <sheetPr>
+    <tabColor theme="9" tint="0.79998168889431442"/>
+  </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -28836,7 +28894,7 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="25.9140625" style="32" customWidth="1"/>
     <col min="2" max="2" width="21.58203125" style="32" bestFit="1" customWidth="1"/>
@@ -28844,7 +28902,7 @@
     <col min="4" max="4" width="49.08203125" style="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4">
       <c r="A1" s="38" t="s">
         <v>166</v>
       </c>
@@ -28858,7 +28916,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="85" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4" ht="85">
       <c r="A2" s="33" t="s">
         <v>17</v>
       </c>
@@ -28872,7 +28930,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="34" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" ht="34">
       <c r="A3" s="34" t="s">
         <v>173</v>
       </c>
@@ -28886,7 +28944,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4">
       <c r="A4" s="33" t="s">
         <v>171</v>
       </c>
@@ -28900,7 +28958,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="34" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4" ht="34">
       <c r="A5" s="34" t="s">
         <v>172</v>
       </c>
@@ -28914,7 +28972,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4">
       <c r="A6" s="70" t="s">
         <v>174</v>
       </c>
@@ -28928,7 +28986,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4">
       <c r="A7" s="70" t="s">
         <v>174</v>
       </c>
@@ -28938,7 +28996,7 @@
       <c r="C7" s="87"/>
       <c r="D7" s="89"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4">
       <c r="A8" s="33" t="s">
         <v>175</v>
       </c>
@@ -28952,7 +29010,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4">
       <c r="A9" s="33" t="s">
         <v>176</v>
       </c>
@@ -28966,7 +29024,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="34" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4">
       <c r="A10" s="33" t="s">
         <v>177</v>
       </c>
@@ -28977,10 +29035,10 @@
         <v>46276</v>
       </c>
       <c r="D10" s="34" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="34" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4" ht="34">
       <c r="A11" s="33" t="s">
         <v>178</v>
       </c>
@@ -28989,7 +29047,7 @@
         <v>46279.645833333336</v>
       </c>
       <c r="D11" s="34" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
   </sheetData>
@@ -29020,7 +29078,7 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="1"/>
     <col min="2" max="3" width="16.83203125" style="1" customWidth="1"/>
@@ -29033,7 +29091,7 @@
     <col min="11" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:7" ht="16.5" thickBot="1">
       <c r="A1" s="39" t="s">
         <v>17</v>
       </c>
@@ -29056,7 +29114,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:7">
       <c r="A2" s="90" t="s">
         <v>18</v>
       </c>
@@ -29073,7 +29131,7 @@
       <c r="F2" s="9"/>
       <c r="G2" s="10"/>
     </row>
-    <row r="3" spans="1:7" ht="64" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:7" ht="64">
       <c r="A3" s="91"/>
       <c r="B3" s="4" t="s">
         <v>1</v>
@@ -29090,7 +29148,7 @@
       </c>
       <c r="G3" s="11"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:7">
       <c r="A4" s="91"/>
       <c r="B4" s="4" t="s">
         <v>184</v>
@@ -29105,7 +29163,7 @@
       <c r="F4" s="3"/>
       <c r="G4" s="11"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:7">
       <c r="A5" s="91"/>
       <c r="B5" s="4" t="s">
         <v>2</v>
@@ -29120,7 +29178,7 @@
       <c r="F5" s="3"/>
       <c r="G5" s="11"/>
     </row>
-    <row r="6" spans="1:7" ht="48" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:7" ht="48">
       <c r="A6" s="91"/>
       <c r="B6" s="4" t="s">
         <v>3</v>
@@ -29139,7 +29197,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:7" ht="16.5" thickBot="1">
       <c r="A7" s="92"/>
       <c r="B7" s="13" t="s">
         <v>15</v>
@@ -29156,7 +29214,7 @@
       <c r="F7" s="14"/>
       <c r="G7" s="15"/>
     </row>
-    <row r="8" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:7" ht="16.5" thickBot="1">
       <c r="A8" s="93" t="s">
         <v>19</v>
       </c>
@@ -29177,7 +29235,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:7">
       <c r="A9" s="94"/>
       <c r="B9" s="4" t="s">
         <v>6</v>
@@ -29194,7 +29252,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:7">
       <c r="A10" s="94"/>
       <c r="B10" s="4" t="s">
         <v>4</v>
@@ -29211,7 +29269,7 @@
       <c r="F10" s="3"/>
       <c r="G10" s="11"/>
     </row>
-    <row r="11" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:7" ht="16.5" thickBot="1">
       <c r="A11" s="94"/>
       <c r="B11" s="4" t="s">
         <v>7</v>
@@ -29226,7 +29284,7 @@
       <c r="F11" s="3"/>
       <c r="G11" s="11"/>
     </row>
-    <row r="12" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:7" ht="16.5" thickBot="1">
       <c r="A12" s="95"/>
       <c r="B12" s="16" t="s">
         <v>8</v>
@@ -29243,7 +29301,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:7">
       <c r="A13" s="96" t="s">
         <v>20</v>
       </c>
@@ -29264,7 +29322,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="64.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:7" ht="64.5" thickBot="1">
       <c r="A14" s="97"/>
       <c r="B14" s="4" t="s">
         <v>10</v>
@@ -29281,7 +29339,7 @@
       </c>
       <c r="G14" s="11"/>
     </row>
-    <row r="15" spans="1:7" ht="64" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:7" ht="64">
       <c r="A15" s="97"/>
       <c r="B15" s="4" t="s">
         <v>218</v>
@@ -29302,7 +29360,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
+    <row r="16" spans="1:7" ht="32.5" thickBot="1">
       <c r="A16" s="98"/>
       <c r="B16" s="16" t="s">
         <v>11</v>
@@ -29336,7 +29394,7 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="60.83203125" customWidth="1"/>
@@ -29344,13 +29402,13 @@
     <col min="4" max="4" width="62.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4">
       <c r="A1" s="76"/>
       <c r="B1" s="76" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4">
       <c r="A2" s="41"/>
       <c r="B2" s="40" t="s">
         <v>199</v>
@@ -29362,7 +29420,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="32" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" ht="32">
       <c r="A3" s="40" t="s">
         <v>179</v>
       </c>
@@ -29376,7 +29434,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="64" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:4" ht="64">
       <c r="A4" s="40" t="s">
         <v>180</v>
       </c>
@@ -29403,7 +29461,7 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:E75"/>
-  <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="32.58203125" style="45" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="21.1640625" style="45" customWidth="1"/>
@@ -29413,7 +29471,7 @@
     <col min="6" max="16384" width="8.6640625" style="45"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:4">
       <c r="A1" s="40" t="s">
         <v>194</v>
       </c>
@@ -29427,7 +29485,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:4">
       <c r="A2" s="36" t="s">
         <v>186</v>
       </c>
@@ -29441,7 +29499,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="64" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:4" ht="64">
       <c r="A3" s="36" t="s">
         <v>189</v>
       </c>
@@ -29455,14 +29513,14 @@
         <v>200</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:4">
       <c r="A5" s="100" t="s">
         <v>273</v>
       </c>
       <c r="B5" s="100"/>
       <c r="C5" s="100"/>
     </row>
-    <row r="6" spans="1:4" ht="32" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:4" ht="32">
       <c r="A6" s="112" t="s">
         <v>204</v>
       </c>
@@ -29473,7 +29531,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="32" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:4" ht="32">
       <c r="A7" s="113"/>
       <c r="B7" s="47" t="s">
         <v>292</v>
@@ -29482,7 +29540,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="32" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:4" ht="32">
       <c r="A8" s="113"/>
       <c r="B8" s="47" t="s">
         <v>295</v>
@@ -29491,7 +29549,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:4">
       <c r="A9" s="113"/>
       <c r="B9" s="47" t="s">
         <v>303</v>
@@ -29500,7 +29558,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:4">
       <c r="A10" s="114"/>
       <c r="B10" s="47" t="s">
         <v>297</v>
@@ -29509,7 +29567,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:4">
       <c r="A11" s="54" t="s">
         <v>293</v>
       </c>
@@ -29520,43 +29578,43 @@
         <v>207</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:4">
       <c r="C12" s="49"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:4">
       <c r="A13" s="105" t="s">
         <v>304</v>
       </c>
       <c r="B13" s="106"/>
       <c r="C13" s="107"/>
     </row>
-    <row r="14" spans="1:4" ht="52" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:4" ht="52" customHeight="1">
       <c r="A14" s="115" t="s">
         <v>230</v>
       </c>
       <c r="B14" s="116"/>
       <c r="C14" s="117"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:4">
       <c r="A19" s="49"/>
       <c r="C19" s="49"/>
       <c r="D19" s="49"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:4">
       <c r="A31" s="100" t="s">
         <v>274</v>
       </c>
       <c r="B31" s="100"/>
       <c r="C31" s="100"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:4">
       <c r="A32" s="108" t="s">
         <v>318</v>
       </c>
       <c r="B32" s="109"/>
       <c r="C32" s="110"/>
     </row>
-    <row r="33" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:5" ht="51" customHeight="1">
       <c r="A33" s="104" t="s">
         <v>231</v>
       </c>
@@ -29567,35 +29625,35 @@
         <v>305</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:5">
       <c r="A34" s="104"/>
       <c r="B34" s="50" t="s">
         <v>209</v>
       </c>
       <c r="C34" s="111"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:5">
       <c r="A35" s="104"/>
       <c r="B35" s="50" t="s">
         <v>210</v>
       </c>
       <c r="C35" s="111"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:5">
       <c r="A36" s="104"/>
       <c r="B36" s="50" t="s">
         <v>211</v>
       </c>
       <c r="C36" s="111"/>
     </row>
-    <row r="37" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:5" ht="32">
       <c r="A37" s="104"/>
       <c r="B37" s="48" t="s">
         <v>212</v>
       </c>
       <c r="C37" s="111"/>
     </row>
-    <row r="38" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:5" ht="51" customHeight="1">
       <c r="A38" s="104" t="s">
         <v>232</v>
       </c>
@@ -29606,42 +29664,42 @@
         <v>216</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:5">
       <c r="A39" s="104"/>
       <c r="B39" s="50" t="s">
         <v>214</v>
       </c>
       <c r="C39" s="111"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:5">
       <c r="A40" s="104"/>
       <c r="B40" s="50" t="s">
         <v>215</v>
       </c>
       <c r="C40" s="111"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:5">
       <c r="A42" s="105" t="s">
         <v>272</v>
       </c>
       <c r="B42" s="106"/>
       <c r="C42" s="107"/>
     </row>
-    <row r="43" spans="1:5" ht="53" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:5" ht="53" customHeight="1">
       <c r="A43" s="104" t="s">
         <v>217</v>
       </c>
       <c r="B43" s="104"/>
       <c r="C43" s="104"/>
     </row>
-    <row r="44" spans="1:5" ht="50.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:5" ht="50.5" customHeight="1">
       <c r="A44" s="104" t="s">
         <v>317</v>
       </c>
       <c r="B44" s="104"/>
       <c r="C44" s="104"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:5">
       <c r="A46" s="100" t="s">
         <v>271</v>
       </c>
@@ -29650,7 +29708,7 @@
       <c r="D46" s="100"/>
       <c r="E46" s="100"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:5">
       <c r="A47" s="44" t="s">
         <v>233</v>
       </c>
@@ -29667,7 +29725,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:5" ht="32">
       <c r="A48" s="43" t="s">
         <v>306</v>
       </c>
@@ -29684,7 +29742,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:5" ht="32">
       <c r="A49" s="43" t="s">
         <v>308</v>
       </c>
@@ -29701,7 +29759,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="48" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:5" ht="48">
       <c r="A50" s="43" t="s">
         <v>309</v>
       </c>
@@ -29718,7 +29776,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:5" ht="32">
       <c r="A51" s="43" t="s">
         <v>248</v>
       </c>
@@ -29735,7 +29793,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:5" ht="32">
       <c r="A52" s="43" t="s">
         <v>250</v>
       </c>
@@ -29752,7 +29810,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:5" ht="32">
       <c r="A53" s="43" t="s">
         <v>252</v>
       </c>
@@ -29769,7 +29827,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:5">
       <c r="A54" s="43" t="s">
         <v>310</v>
       </c>
@@ -29786,7 +29844,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:5" ht="32">
       <c r="A55" s="43" t="s">
         <v>311</v>
       </c>
@@ -29803,7 +29861,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="48" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:5" ht="48">
       <c r="A56" s="43"/>
       <c r="B56" s="43" t="s">
         <v>255</v>
@@ -29818,7 +29876,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="48" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:5" ht="48">
       <c r="A57" s="43"/>
       <c r="B57" s="43" t="s">
         <v>256</v>
@@ -29833,14 +29891,14 @@
         <v>261</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:5">
       <c r="A59" s="101" t="s">
         <v>275</v>
       </c>
       <c r="B59" s="102"/>
       <c r="C59" s="103"/>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:5">
       <c r="A60" s="53" t="s">
         <v>276</v>
       </c>
@@ -29851,7 +29909,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:5" ht="32">
       <c r="A61" s="52" t="s">
         <v>279</v>
       </c>
@@ -29862,7 +29920,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:5" ht="32">
       <c r="A62" s="52" t="s">
         <v>282</v>
       </c>
@@ -29873,7 +29931,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:5" ht="32">
       <c r="A63" s="52" t="s">
         <v>285</v>
       </c>
@@ -29884,7 +29942,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:5">
       <c r="A64" s="52" t="s">
         <v>288</v>
       </c>
@@ -29895,7 +29953,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:4">
       <c r="A66" s="100" t="s">
         <v>291</v>
       </c>
@@ -29903,7 +29961,7 @@
       <c r="C66" s="100"/>
       <c r="D66" s="100"/>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:4">
       <c r="A67" s="99" t="s">
         <v>262</v>
       </c>
@@ -29911,7 +29969,7 @@
       <c r="C67" s="99"/>
       <c r="D67" s="99"/>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:4">
       <c r="A68" s="99" t="s">
         <v>263</v>
       </c>
@@ -29919,7 +29977,7 @@
       <c r="C68" s="99"/>
       <c r="D68" s="99"/>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:4">
       <c r="A69" s="99" t="s">
         <v>264</v>
       </c>
@@ -29927,7 +29985,7 @@
       <c r="C69" s="99"/>
       <c r="D69" s="99"/>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:4">
       <c r="A70" s="99" t="s">
         <v>265</v>
       </c>
@@ -29935,7 +29993,7 @@
       <c r="C70" s="99"/>
       <c r="D70" s="99"/>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:4">
       <c r="A71" s="99" t="s">
         <v>266</v>
       </c>
@@ -29943,7 +30001,7 @@
       <c r="C71" s="99"/>
       <c r="D71" s="99"/>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:4">
       <c r="A72" s="99" t="s">
         <v>267</v>
       </c>
@@ -29951,7 +30009,7 @@
       <c r="C72" s="99"/>
       <c r="D72" s="99"/>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:4">
       <c r="A73" s="99" t="s">
         <v>268</v>
       </c>
@@ -29959,7 +30017,7 @@
       <c r="C73" s="99"/>
       <c r="D73" s="99"/>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:4">
       <c r="A74" s="99" t="s">
         <v>269</v>
       </c>
@@ -29967,7 +30025,7 @@
       <c r="C74" s="99"/>
       <c r="D74" s="99"/>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:4">
       <c r="A75" s="99" t="s">
         <v>270</v>
       </c>
@@ -30015,7 +30073,7 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -30029,7 +30087,7 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:H23"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="5.33203125" style="20" customWidth="1"/>
     <col min="2" max="2" width="56.25" customWidth="1"/>
@@ -30041,13 +30099,13 @@
     <col min="8" max="8" width="54.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8">
       <c r="A1" s="118" t="s">
         <v>335</v>
       </c>
       <c r="B1" s="119"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8">
       <c r="A2" s="60" t="s">
         <v>336</v>
       </c>
@@ -30055,7 +30113,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="34" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:8" ht="34">
       <c r="A3" s="61">
         <v>1</v>
       </c>
@@ -30063,7 +30121,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:8">
       <c r="A4" s="61">
         <v>2</v>
       </c>
@@ -30071,7 +30129,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:8">
       <c r="A5" s="61">
         <v>3</v>
       </c>
@@ -30079,7 +30137,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:8">
       <c r="A7" s="60" t="s">
         <v>336</v>
       </c>
@@ -30102,7 +30160,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:8">
       <c r="A8" s="61">
         <v>1</v>
       </c>
@@ -30119,7 +30177,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="238" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:8" ht="238">
       <c r="A9" s="61">
         <v>2</v>
       </c>
@@ -30142,7 +30200,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:8">
       <c r="A10" s="61">
         <v>3</v>
       </c>
@@ -30159,7 +30217,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="102" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:8" ht="102">
       <c r="A11" s="61">
         <v>4</v>
       </c>
@@ -30182,7 +30240,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="68" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:8" ht="68">
       <c r="A12" s="61">
         <v>5</v>
       </c>
@@ -30205,7 +30263,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="68" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:8" ht="68">
       <c r="A13" s="61">
         <v>6</v>
       </c>
@@ -30228,7 +30286,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:8">
       <c r="A14" s="61">
         <v>7</v>
       </c>
@@ -30245,7 +30303,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="136" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:8" ht="136">
       <c r="A15" s="61">
         <v>8</v>
       </c>
@@ -30268,7 +30326,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="187" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:8" ht="187">
       <c r="A16" s="61">
         <v>9</v>
       </c>
@@ -30288,7 +30346,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="51" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:6" ht="51">
       <c r="A17" s="61">
         <v>10</v>
       </c>
@@ -30308,7 +30366,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="68" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:6" ht="68">
       <c r="A18" s="61">
         <v>11</v>
       </c>
@@ -30328,7 +30386,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="68" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:6" ht="68">
       <c r="A19" s="61">
         <v>12</v>
       </c>
@@ -30348,7 +30406,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="68" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:6" ht="68">
       <c r="A20" s="61">
         <v>13</v>
       </c>
@@ -30368,7 +30426,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="85" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:6" ht="85">
       <c r="A21" s="61">
         <v>14</v>
       </c>
@@ -30388,7 +30446,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="170" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:6" ht="170">
       <c r="A22" s="61" t="s">
         <v>389</v>
       </c>
@@ -30408,7 +30466,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:6">
       <c r="A23" s="66" t="s">
         <v>395</v>
       </c>
@@ -30431,7 +30489,7 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="5.33203125" style="45" customWidth="1"/>
     <col min="2" max="2" width="49.5" style="45" customWidth="1"/>
@@ -30442,7 +30500,7 @@
     <col min="9" max="16384" width="8.6640625" style="45"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="16" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" ht="16">
       <c r="A1" s="62" t="s">
         <v>336</v>
       </c>
@@ -30468,7 +30526,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="256" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:8" ht="256">
       <c r="A2" s="68">
         <v>2</v>
       </c>
@@ -30494,7 +30552,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="208" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:8" ht="208">
       <c r="A3" s="68">
         <v>4</v>
       </c>
@@ -30520,7 +30578,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="272" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:8" ht="272">
       <c r="A4" s="68">
         <v>5</v>
       </c>
@@ -30546,7 +30604,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="192" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:8" ht="192">
       <c r="A5" s="68">
         <v>6</v>
       </c>
@@ -30572,7 +30630,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="192" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:8" ht="192">
       <c r="A6" s="68">
         <v>8</v>
       </c>
@@ -30598,7 +30656,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="224" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:8" ht="224">
       <c r="A7" s="68">
         <v>9</v>
       </c>
@@ -30624,7 +30682,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="192" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:8" ht="192">
       <c r="A8" s="68">
         <v>10</v>
       </c>
@@ -30650,7 +30708,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="332.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:8" ht="332.5" customHeight="1">
       <c r="A9" s="68">
         <v>11</v>
       </c>
@@ -30676,7 +30734,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="272" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:8" ht="272">
       <c r="A10" s="68">
         <v>12</v>
       </c>
@@ -30702,7 +30760,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="224" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:8" ht="224">
       <c r="A11" s="68">
         <v>13</v>
       </c>
@@ -30728,7 +30786,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="306.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:8" ht="306.5" customHeight="1">
       <c r="A12" s="68">
         <v>14</v>
       </c>
@@ -30754,7 +30812,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="144" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:8" ht="144">
       <c r="A13" s="68" t="s">
         <v>389</v>
       </c>
@@ -30789,12 +30847,12 @@
     <tabColor theme="0" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="101.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="68" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:1" ht="68">
       <c r="A1" s="67" t="s">
         <v>396</v>
       </c>

--- a/project_2/project2_project status(C2).xlsx
+++ b/project_2/project2_project status(C2).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pyostry\workspace\aiffel\ai-data-bootcamp\Project_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4A60463-41FF-4445-A1DB-285112FF7916}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D903AF-96E8-4FBE-81A9-43E2E347790B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{5FF54064-7DDC-427B-93D7-EF78D75E5195}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{5FF54064-7DDC-427B-93D7-EF78D75E5195}"/>
   </bookViews>
   <sheets>
     <sheet name="제작 가이드라인" sheetId="12" r:id="rId1"/>
@@ -2327,7 +2327,7 @@
     <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
     <numFmt numFmtId="177" formatCode="[$-412]yyyy&quot;년&quot;\ m&quot;월&quot;\ d&quot;일&quot;\ dddd\ h&quot;시&quot;\ mm&quot;분&quot;"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="31" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2609,7 +2609,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -2902,6 +2902,45 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -2911,7 +2950,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="122">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3027,9 +3066,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -3205,21 +3241,6 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -3239,6 +3260,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3262,6 +3286,18 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3273,6 +3309,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -27847,214 +27898,214 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:C135"/>
-  <sheetFormatPr defaultRowHeight="17" outlineLevelRow="2"/>
+  <sheetFormatPr defaultRowHeight="17" outlineLevelRow="2" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="16.83203125" style="20" customWidth="1"/>
     <col min="2" max="2" width="32.9140625" customWidth="1"/>
     <col min="3" max="3" width="30.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="36">
+    <row r="1" spans="1:1" ht="36" x14ac:dyDescent="0.45">
       <c r="A1" s="19" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="3" spans="1:1" ht="26">
+    <row r="3" spans="1:1" ht="26" x14ac:dyDescent="0.45">
       <c r="A3" s="21" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="4" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A4" s="22" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="5" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="5" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A5" s="22" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:1" hidden="1" outlineLevel="1"/>
-    <row r="7" spans="1:1" ht="26" collapsed="1">
+    <row r="6" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="7" spans="1:1" ht="26" collapsed="1" x14ac:dyDescent="0.45">
       <c r="A7" s="21" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="8" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="8" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A8" s="20" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="9" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A9" s="20" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="10" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A10" s="20" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="11" spans="1:1" hidden="1" outlineLevel="1"/>
-    <row r="12" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="11" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="12" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A12" s="22" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:1" hidden="1" outlineLevel="1"/>
-    <row r="14" spans="1:1" ht="21" hidden="1" outlineLevel="1">
+    <row r="13" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="14" spans="1:1" ht="21" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A14" s="23" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="15" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="15" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A15" s="24" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="16" spans="1:1" hidden="1" outlineLevel="1"/>
-    <row r="17" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="16" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="17" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A17" s="25" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="18" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="18" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A18" s="25" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="19" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="19" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A19" s="25" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="20" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="20" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A20" s="25" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="21" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="21" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A21" s="25" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="22" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="22" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A22" s="25" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="23" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="23" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A23" s="25" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="24" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="24" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A24" s="25" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="25" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A25" s="25" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="26" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A26" s="25" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="27" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="27" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A27" s="25" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="28" spans="1:1" hidden="1" outlineLevel="1"/>
-    <row r="29" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="28" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="29" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A29" s="22" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="30" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="30" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A30" s="20" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="31" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="31" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A31" s="20" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="32" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="32" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A32" s="20" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="33" spans="1:1" hidden="1" outlineLevel="1"/>
-    <row r="34" spans="1:1" ht="26" collapsed="1">
+    <row r="33" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="34" spans="1:1" ht="26" collapsed="1" x14ac:dyDescent="0.45">
       <c r="A34" s="21" t="s">
         <v>191</v>
       </c>
     </row>
-    <row r="35" spans="1:1" hidden="1" outlineLevel="2">
+    <row r="35" spans="1:1" hidden="1" outlineLevel="2" x14ac:dyDescent="0.45">
       <c r="A35" s="20" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="36" spans="1:1" hidden="1" outlineLevel="2">
+    <row r="36" spans="1:1" hidden="1" outlineLevel="2" x14ac:dyDescent="0.45">
       <c r="A36" s="22" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="37" spans="1:1" hidden="1" outlineLevel="2">
+    <row r="37" spans="1:1" hidden="1" outlineLevel="2" x14ac:dyDescent="0.45">
       <c r="A37" s="20" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="38" spans="1:1" hidden="1" outlineLevel="2"/>
-    <row r="39" spans="1:1" hidden="1" outlineLevel="2">
+    <row r="38" spans="1:1" hidden="1" outlineLevel="2" x14ac:dyDescent="0.45"/>
+    <row r="39" spans="1:1" hidden="1" outlineLevel="2" x14ac:dyDescent="0.45">
       <c r="A39" s="22" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="40" spans="1:1" hidden="1" outlineLevel="2"/>
-    <row r="41" spans="1:1" ht="26" collapsed="1">
+    <row r="40" spans="1:1" hidden="1" outlineLevel="2" x14ac:dyDescent="0.45"/>
+    <row r="41" spans="1:1" ht="26" collapsed="1" x14ac:dyDescent="0.45">
       <c r="A41" s="21" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="42" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="42" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A42" s="20" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="43" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="43" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A43" s="20" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="44" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="44" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A44" s="20" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="45" spans="1:1" hidden="1" outlineLevel="1"/>
-    <row r="46" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="45" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="46" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A46" s="22" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="47" spans="1:1" hidden="1" outlineLevel="1"/>
-    <row r="48" spans="1:1" ht="21" hidden="1" outlineLevel="1">
+    <row r="47" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="48" spans="1:1" ht="21" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A48" s="23" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="21" hidden="1" outlineLevel="1">
+    <row r="49" spans="1:3" ht="21" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A49" s="23" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="50" spans="1:3" hidden="1" outlineLevel="1">
+    <row r="50" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A50" s="26"/>
       <c r="B50" s="17" t="s">
         <v>77</v>
@@ -28063,7 +28114,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="51" spans="1:3" hidden="1" outlineLevel="1">
+    <row r="51" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A51" s="27" t="s">
         <v>79</v>
       </c>
@@ -28074,7 +28125,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="52" spans="1:3" hidden="1" outlineLevel="1">
+    <row r="52" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A52" s="27" t="s">
         <v>82</v>
       </c>
@@ -28085,7 +28136,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="53" spans="1:3" hidden="1" outlineLevel="1">
+    <row r="53" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A53" s="27" t="s">
         <v>85</v>
       </c>
@@ -28096,7 +28147,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="54" spans="1:3" hidden="1" outlineLevel="1">
+    <row r="54" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A54" s="27" t="s">
         <v>88</v>
       </c>
@@ -28107,7 +28158,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="55" spans="1:3" hidden="1" outlineLevel="1">
+    <row r="55" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A55" s="27" t="s">
         <v>91</v>
       </c>
@@ -28118,231 +28169,231 @@
         <v>93</v>
       </c>
     </row>
-    <row r="56" spans="1:3" hidden="1" outlineLevel="1"/>
-    <row r="57" spans="1:3" hidden="1" outlineLevel="1">
+    <row r="56" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="57" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A57" s="22" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="58" spans="1:3" hidden="1" outlineLevel="1">
+    <row r="58" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A58" s="24" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="59" spans="1:3" hidden="1" outlineLevel="1"/>
-    <row r="60" spans="1:3" hidden="1" outlineLevel="1">
+    <row r="59" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="60" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A60" s="25" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="61" spans="1:3" hidden="1" outlineLevel="1">
+    <row r="61" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A61" s="25" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="62" spans="1:3" hidden="1" outlineLevel="1">
+    <row r="62" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A62" s="25" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="63" spans="1:3" hidden="1" outlineLevel="1">
+    <row r="63" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A63" s="25" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="64" spans="1:3" hidden="1" outlineLevel="1">
+    <row r="64" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A64" s="25" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="65" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="65" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A65" s="25" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="66" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="66" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A66" s="25" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="67" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="67" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A67" s="25" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="68" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="68" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A68" s="25" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="69" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="69" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A69" s="25" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="70" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="70" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A70" s="25" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="71" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="71" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A71" s="25" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="72" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="72" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A72" s="25" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="73" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="73" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A73" s="25" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="74" spans="1:1" hidden="1" outlineLevel="1"/>
-    <row r="75" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="74" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="75" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A75" s="22" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="76" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="76" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A76" s="20" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="77" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="77" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A77" s="20" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="78" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="78" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A78" s="20" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="79" spans="1:1" hidden="1" outlineLevel="1"/>
-    <row r="80" spans="1:1" ht="21" hidden="1" outlineLevel="1">
+    <row r="79" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="80" spans="1:1" ht="21" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A80" s="23" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="81" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="81" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A81" s="22" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="82" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="82" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A82" s="22" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="83" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="83" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A83" s="22" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="84" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="84" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A84" s="20" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="85" spans="1:1" hidden="1" outlineLevel="1"/>
-    <row r="86" spans="1:1" ht="26" collapsed="1">
+    <row r="85" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="86" spans="1:1" ht="26" collapsed="1" x14ac:dyDescent="0.45">
       <c r="A86" s="21" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="87" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="87" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A87" s="20" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="88" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="88" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A88" s="20" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="89" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="89" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A89" s="20" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="90" spans="1:1" hidden="1" outlineLevel="1"/>
-    <row r="91" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="90" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="91" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A91" s="22" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="92" spans="1:1" hidden="1" outlineLevel="1"/>
-    <row r="93" spans="1:1" ht="26" collapsed="1">
+    <row r="92" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="93" spans="1:1" ht="26" collapsed="1" x14ac:dyDescent="0.45">
       <c r="A93" s="21" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="94" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="94" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A94" s="20" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="95" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="95" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A95" s="20" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="96" spans="1:1" hidden="1" outlineLevel="1">
+    <row r="96" spans="1:1" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A96" s="20" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="97" spans="1:3" hidden="1" outlineLevel="1"/>
-    <row r="98" spans="1:3" hidden="1" outlineLevel="1">
+    <row r="97" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="98" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A98" s="22" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="99" spans="1:3" hidden="1" outlineLevel="1"/>
-    <row r="100" spans="1:3" ht="26" collapsed="1">
+    <row r="99" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="100" spans="1:3" ht="26" collapsed="1" x14ac:dyDescent="0.45">
       <c r="A100" s="21" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="101" spans="1:3" hidden="1" outlineLevel="1">
+    <row r="101" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A101" s="20" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="102" spans="1:3" hidden="1" outlineLevel="1">
+    <row r="102" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A102" s="20" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="103" spans="1:3" hidden="1" outlineLevel="1"/>
-    <row r="104" spans="1:3" hidden="1" outlineLevel="1">
+    <row r="103" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="104" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A104" s="22" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="105" spans="1:3" hidden="1" outlineLevel="1"/>
-    <row r="106" spans="1:3" ht="26" collapsed="1">
+    <row r="105" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="106" spans="1:3" ht="26" collapsed="1" x14ac:dyDescent="0.45">
       <c r="A106" s="21" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="107" spans="1:3" hidden="1" outlineLevel="1"/>
-    <row r="108" spans="1:3" hidden="1" outlineLevel="1">
+    <row r="107" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="108" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A108" s="20" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="109" spans="1:3" hidden="1" outlineLevel="1"/>
-    <row r="110" spans="1:3" ht="21" hidden="1" outlineLevel="1">
+    <row r="109" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="110" spans="1:3" ht="21" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A110" s="23" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="111" spans="1:3" hidden="1" outlineLevel="1"/>
-    <row r="112" spans="1:3" hidden="1" outlineLevel="1">
+    <row r="111" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="112" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A112" s="26" t="s">
         <v>132</v>
       </c>
@@ -28353,7 +28404,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="34" hidden="1" outlineLevel="1">
+    <row r="113" spans="1:3" ht="34" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A113" s="27" t="s">
         <v>135</v>
       </c>
@@ -28364,7 +28415,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="51" hidden="1" outlineLevel="1">
+    <row r="114" spans="1:3" ht="51" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A114" s="27" t="s">
         <v>138</v>
       </c>
@@ -28375,51 +28426,51 @@
         <v>140</v>
       </c>
     </row>
-    <row r="115" spans="1:3" hidden="1" outlineLevel="1"/>
-    <row r="116" spans="1:3" hidden="1" outlineLevel="1">
+    <row r="115" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="116" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A116" s="20" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="117" spans="1:3" hidden="1" outlineLevel="1"/>
-    <row r="118" spans="1:3" ht="21" hidden="1" outlineLevel="1">
+    <row r="117" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="118" spans="1:3" ht="21" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A118" s="23" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="119" spans="1:3" hidden="1" outlineLevel="1">
+    <row r="119" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A119" s="20" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="120" spans="1:3" hidden="1" outlineLevel="1">
+    <row r="120" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A120" s="20" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="121" spans="1:3" hidden="1" outlineLevel="1">
+    <row r="121" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A121" s="20" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="122" spans="1:3" hidden="1" outlineLevel="1">
+    <row r="122" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A122" s="20" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="123" spans="1:3" hidden="1" outlineLevel="1"/>
-    <row r="124" spans="1:3" hidden="1" outlineLevel="1">
+    <row r="123" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="124" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A124" s="22" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="125" spans="1:3" hidden="1" outlineLevel="1"/>
-    <row r="126" spans="1:3" ht="21" collapsed="1">
+    <row r="125" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45"/>
+    <row r="126" spans="1:3" ht="21" collapsed="1" x14ac:dyDescent="0.45">
       <c r="A126" s="23" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="127" spans="1:3" hidden="1" outlineLevel="1">
+    <row r="127" spans="1:3" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A127" s="30" t="s">
         <v>148</v>
       </c>
@@ -28427,7 +28478,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="34" hidden="1" outlineLevel="1">
+    <row r="128" spans="1:3" ht="34" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A128" s="31" t="s">
         <v>150</v>
       </c>
@@ -28435,7 +28486,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="129" spans="1:2" ht="51" hidden="1" outlineLevel="1">
+    <row r="129" spans="1:2" ht="51" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A129" s="31" t="s">
         <v>152</v>
       </c>
@@ -28443,7 +28494,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="130" spans="1:2" ht="34" hidden="1" outlineLevel="1">
+    <row r="130" spans="1:2" ht="34" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A130" s="31" t="s">
         <v>154</v>
       </c>
@@ -28451,7 +28502,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="131" spans="1:2" ht="51" hidden="1" outlineLevel="1">
+    <row r="131" spans="1:2" ht="51" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A131" s="31" t="s">
         <v>156</v>
       </c>
@@ -28459,7 +28510,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="132" spans="1:2" ht="34" hidden="1" outlineLevel="1">
+    <row r="132" spans="1:2" ht="34" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A132" s="31" t="s">
         <v>158</v>
       </c>
@@ -28467,7 +28518,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="133" spans="1:2" ht="34" hidden="1" outlineLevel="1">
+    <row r="133" spans="1:2" ht="34" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A133" s="31" t="s">
         <v>160</v>
       </c>
@@ -28475,7 +28526,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="134" spans="1:2" ht="34" hidden="1" outlineLevel="1">
+    <row r="134" spans="1:2" ht="34" hidden="1" outlineLevel="1" x14ac:dyDescent="0.45">
       <c r="A134" s="31" t="s">
         <v>162</v>
       </c>
@@ -28483,7 +28534,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="135" spans="1:2" collapsed="1"/>
+    <row r="135" spans="1:2" collapsed="1" x14ac:dyDescent="0.45"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -28496,37 +28547,37 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:E23"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.9140625" customWidth="1"/>
     <col min="2" max="2" width="51.9140625" customWidth="1"/>
     <col min="3" max="3" width="71.08203125" customWidth="1"/>
-    <col min="4" max="4" width="65.33203125" style="80" customWidth="1"/>
+    <col min="4" max="4" width="65.33203125" style="79" customWidth="1"/>
     <col min="5" max="5" width="65.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="62" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A1" s="61" t="s">
         <v>336</v>
       </c>
-      <c r="B1" s="60" t="s">
+      <c r="B1" s="59" t="s">
         <v>421</v>
       </c>
-      <c r="C1" s="59" t="s">
+      <c r="C1" s="58" t="s">
         <v>199</v>
       </c>
-      <c r="D1" s="81" t="s">
+      <c r="D1" s="80" t="s">
         <v>200</v>
       </c>
-      <c r="E1" s="59" t="s">
+      <c r="E1" s="58" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="51">
-      <c r="A2" s="61">
+    <row r="2" spans="1:5" ht="51" x14ac:dyDescent="0.45">
+      <c r="A2" s="60">
         <v>1</v>
       </c>
-      <c r="B2" s="77" t="s">
+      <c r="B2" s="76" t="s">
         <v>425</v>
       </c>
       <c r="C2" s="18" t="s">
@@ -28539,11 +28590,11 @@
         <v>465</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="85">
-      <c r="A3" s="61">
+    <row r="3" spans="1:5" ht="85" x14ac:dyDescent="0.45">
+      <c r="A3" s="60">
         <v>2</v>
       </c>
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="76" t="s">
         <v>427</v>
       </c>
       <c r="C3" s="18" t="s">
@@ -28556,11 +28607,11 @@
         <v>466</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="68">
-      <c r="A4" s="61">
+    <row r="4" spans="1:5" ht="68" x14ac:dyDescent="0.45">
+      <c r="A4" s="60">
         <v>3</v>
       </c>
-      <c r="B4" s="77" t="s">
+      <c r="B4" s="76" t="s">
         <v>429</v>
       </c>
       <c r="C4" s="18" t="s">
@@ -28573,11 +28624,11 @@
         <v>467</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="51">
-      <c r="A5" s="61">
+    <row r="5" spans="1:5" ht="51" x14ac:dyDescent="0.45">
+      <c r="A5" s="60">
         <v>4</v>
       </c>
-      <c r="B5" s="77" t="s">
+      <c r="B5" s="76" t="s">
         <v>431</v>
       </c>
       <c r="C5" s="18" t="s">
@@ -28590,11 +28641,11 @@
         <v>468</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="85">
-      <c r="A6" s="61">
+    <row r="6" spans="1:5" ht="85" x14ac:dyDescent="0.45">
+      <c r="A6" s="60">
         <v>5</v>
       </c>
-      <c r="B6" s="77" t="s">
+      <c r="B6" s="76" t="s">
         <v>433</v>
       </c>
       <c r="C6" s="18" t="s">
@@ -28607,11 +28658,11 @@
         <v>469</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="68">
-      <c r="A7" s="61">
+    <row r="7" spans="1:5" ht="68" x14ac:dyDescent="0.45">
+      <c r="A7" s="60">
         <v>6</v>
       </c>
-      <c r="B7" s="77" t="s">
+      <c r="B7" s="76" t="s">
         <v>435</v>
       </c>
       <c r="C7" s="18" t="s">
@@ -28624,11 +28675,11 @@
         <v>470</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="51">
-      <c r="A8" s="61">
+    <row r="8" spans="1:5" ht="51" x14ac:dyDescent="0.45">
+      <c r="A8" s="60">
         <v>7</v>
       </c>
-      <c r="B8" s="77" t="s">
+      <c r="B8" s="76" t="s">
         <v>437</v>
       </c>
       <c r="C8" s="18" t="s">
@@ -28641,11 +28692,11 @@
         <v>471</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="85">
-      <c r="A9" s="61">
+    <row r="9" spans="1:5" ht="85" x14ac:dyDescent="0.45">
+      <c r="A9" s="60">
         <v>8</v>
       </c>
-      <c r="B9" s="77" t="s">
+      <c r="B9" s="76" t="s">
         <v>439</v>
       </c>
       <c r="C9" s="18" t="s">
@@ -28658,41 +28709,41 @@
         <v>472</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="32" customHeight="1">
-      <c r="A10" s="61">
+    <row r="10" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="60">
         <v>9</v>
       </c>
-      <c r="B10" s="77" t="s">
+      <c r="B10" s="76" t="s">
         <v>441</v>
       </c>
-      <c r="C10" s="120" t="s">
+      <c r="C10" s="119" t="s">
         <v>462</v>
       </c>
-      <c r="D10" s="121" t="s">
+      <c r="D10" s="120" t="s">
         <v>488</v>
       </c>
       <c r="E10" s="18" t="s">
         <v>473</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="51" customHeight="1">
-      <c r="A11" s="61">
+    <row r="11" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="60">
         <v>10</v>
       </c>
-      <c r="B11" s="77" t="s">
+      <c r="B11" s="76" t="s">
         <v>443</v>
       </c>
-      <c r="C11" s="120"/>
-      <c r="D11" s="121"/>
+      <c r="C11" s="119"/>
+      <c r="D11" s="120"/>
       <c r="E11" s="18" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="51">
-      <c r="A12" s="61">
+    <row r="12" spans="1:5" ht="51" x14ac:dyDescent="0.45">
+      <c r="A12" s="60">
         <v>11</v>
       </c>
-      <c r="B12" s="77" t="s">
+      <c r="B12" s="76" t="s">
         <v>445</v>
       </c>
       <c r="C12" s="18" t="s">
@@ -28705,14 +28756,14 @@
         <v>475</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="34">
-      <c r="A13" s="61">
+    <row r="13" spans="1:5" ht="34" x14ac:dyDescent="0.45">
+      <c r="A13" s="60">
         <v>12</v>
       </c>
-      <c r="B13" s="77" t="s">
+      <c r="B13" s="76" t="s">
         <v>447</v>
       </c>
-      <c r="C13" s="58"/>
+      <c r="C13" s="57"/>
       <c r="D13" s="18" t="s">
         <v>490</v>
       </c>
@@ -28720,14 +28771,14 @@
         <v>476</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="34">
-      <c r="A14" s="61">
+    <row r="14" spans="1:5" ht="34" x14ac:dyDescent="0.45">
+      <c r="A14" s="60">
         <v>13</v>
       </c>
-      <c r="B14" s="78" t="s">
+      <c r="B14" s="77" t="s">
         <v>320</v>
       </c>
-      <c r="C14" s="120" t="s">
+      <c r="C14" s="119" t="s">
         <v>460</v>
       </c>
       <c r="D14" s="18"/>
@@ -28735,24 +28786,24 @@
         <v>477</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="35.5" customHeight="1">
-      <c r="A15" s="61">
+    <row r="15" spans="1:5" ht="35.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="60">
         <v>14</v>
       </c>
-      <c r="B15" s="79" t="s">
+      <c r="B15" s="78" t="s">
         <v>322</v>
       </c>
-      <c r="C15" s="120"/>
+      <c r="C15" s="119"/>
       <c r="D15" s="18"/>
       <c r="E15" s="18" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="34">
-      <c r="A16" s="61">
+    <row r="16" spans="1:5" ht="34" x14ac:dyDescent="0.45">
+      <c r="A16" s="60">
         <v>15</v>
       </c>
-      <c r="B16" s="79" t="s">
+      <c r="B16" s="78" t="s">
         <v>326</v>
       </c>
       <c r="C16" s="18" t="s">
@@ -28763,102 +28814,102 @@
         <v>479</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" s="20"/>
-      <c r="B17" s="83"/>
-      <c r="C17" s="80"/>
-      <c r="E17" s="80"/>
+      <c r="B17" s="82"/>
+      <c r="C17" s="79"/>
+      <c r="E17" s="79"/>
     </row>
-    <row r="18" spans="1:5" ht="20.5">
-      <c r="A18" s="82" t="s">
+    <row r="18" spans="1:5" ht="20.5" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="81" t="s">
         <v>491</v>
       </c>
-      <c r="B18" s="69"/>
-      <c r="C18" s="69"/>
-      <c r="E18" s="69"/>
+      <c r="B18" s="68"/>
+      <c r="C18" s="68"/>
+      <c r="E18" s="68"/>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="60" t="s">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A19" s="59" t="s">
         <v>508</v>
       </c>
-      <c r="B19" s="60" t="s">
+      <c r="B19" s="59" t="s">
         <v>509</v>
       </c>
-      <c r="C19" s="60" t="s">
+      <c r="C19" s="59" t="s">
         <v>510</v>
       </c>
-      <c r="D19" s="60" t="s">
+      <c r="D19" s="59" t="s">
         <v>511</v>
       </c>
-      <c r="E19" s="60" t="s">
+      <c r="E19" s="59" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="85">
-      <c r="A20" s="84">
+    <row r="20" spans="1:5" ht="85" x14ac:dyDescent="0.45">
+      <c r="A20" s="83">
         <v>1</v>
       </c>
-      <c r="B20" s="85" t="s">
+      <c r="B20" s="84" t="s">
         <v>492</v>
       </c>
-      <c r="C20" s="85" t="s">
+      <c r="C20" s="84" t="s">
         <v>493</v>
       </c>
-      <c r="D20" s="85" t="s">
+      <c r="D20" s="84" t="s">
         <v>494</v>
       </c>
-      <c r="E20" s="84" t="s">
+      <c r="E20" s="83" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="68">
-      <c r="A21" s="84">
+    <row r="21" spans="1:5" ht="68" x14ac:dyDescent="0.45">
+      <c r="A21" s="83">
         <v>2</v>
       </c>
-      <c r="B21" s="85" t="s">
+      <c r="B21" s="84" t="s">
         <v>496</v>
       </c>
-      <c r="C21" s="85" t="s">
+      <c r="C21" s="84" t="s">
         <v>497</v>
       </c>
-      <c r="D21" s="85" t="s">
+      <c r="D21" s="84" t="s">
         <v>498</v>
       </c>
-      <c r="E21" s="84" t="s">
+      <c r="E21" s="83" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="102">
-      <c r="A22" s="84">
+    <row r="22" spans="1:5" ht="102" x14ac:dyDescent="0.45">
+      <c r="A22" s="83">
         <v>3</v>
       </c>
-      <c r="B22" s="85" t="s">
+      <c r="B22" s="84" t="s">
         <v>500</v>
       </c>
-      <c r="C22" s="85" t="s">
+      <c r="C22" s="84" t="s">
         <v>501</v>
       </c>
-      <c r="D22" s="85" t="s">
+      <c r="D22" s="84" t="s">
         <v>502</v>
       </c>
-      <c r="E22" s="84" t="s">
+      <c r="E22" s="83" t="s">
         <v>503</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="68">
-      <c r="A23" s="84">
+    <row r="23" spans="1:5" ht="68" x14ac:dyDescent="0.45">
+      <c r="A23" s="83">
         <v>4</v>
       </c>
-      <c r="B23" s="85" t="s">
+      <c r="B23" s="84" t="s">
         <v>504</v>
       </c>
-      <c r="C23" s="85" t="s">
+      <c r="C23" s="84" t="s">
         <v>505</v>
       </c>
-      <c r="D23" s="85" t="s">
+      <c r="D23" s="84" t="s">
         <v>506</v>
       </c>
-      <c r="E23" s="84" t="s">
+      <c r="E23" s="83" t="s">
         <v>507</v>
       </c>
     </row>
@@ -28879,7 +28930,7 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -28894,7 +28945,7 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="25.9140625" style="32" customWidth="1"/>
     <col min="2" max="2" width="21.58203125" style="32" bestFit="1" customWidth="1"/>
@@ -28902,7 +28953,7 @@
     <col min="4" max="4" width="49.08203125" style="32" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" s="38" t="s">
         <v>166</v>
       </c>
@@ -28916,11 +28967,11 @@
         <v>169</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="85">
+    <row r="2" spans="1:4" ht="85" x14ac:dyDescent="0.45">
       <c r="A2" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="55" t="s">
         <v>170</v>
       </c>
       <c r="C2" s="35">
@@ -28930,11 +28981,11 @@
         <v>220</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="34">
+    <row r="3" spans="1:4" ht="34" x14ac:dyDescent="0.45">
       <c r="A3" s="34" t="s">
         <v>173</v>
       </c>
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="55" t="s">
         <v>301</v>
       </c>
       <c r="C3" s="35">
@@ -28944,11 +28995,11 @@
         <v>316</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A4" s="33" t="s">
         <v>171</v>
       </c>
-      <c r="B4" s="56" t="s">
+      <c r="B4" s="55" t="s">
         <v>301</v>
       </c>
       <c r="C4" s="35">
@@ -28958,11 +29009,11 @@
         <v>316</v>
       </c>
     </row>
-    <row r="5" spans="1:4" ht="34">
+    <row r="5" spans="1:4" ht="34" x14ac:dyDescent="0.45">
       <c r="A5" s="34" t="s">
         <v>172</v>
       </c>
-      <c r="B5" s="71" t="s">
+      <c r="B5" s="70" t="s">
         <v>448</v>
       </c>
       <c r="C5" s="35">
@@ -28972,35 +29023,35 @@
         <v>316</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="70" t="s">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A6" s="69" t="s">
         <v>174</v>
       </c>
-      <c r="B6" s="72" t="s">
+      <c r="B6" s="71" t="s">
         <v>449</v>
       </c>
-      <c r="C6" s="86">
+      <c r="C6" s="85">
         <v>46275</v>
       </c>
-      <c r="D6" s="88" t="s">
+      <c r="D6" s="87" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="70" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A7" s="69" t="s">
         <v>174</v>
       </c>
-      <c r="B7" s="73" t="s">
+      <c r="B7" s="72" t="s">
         <v>450</v>
       </c>
-      <c r="C7" s="87"/>
-      <c r="D7" s="89"/>
+      <c r="C7" s="86"/>
+      <c r="D7" s="88"/>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" s="33" t="s">
         <v>175</v>
       </c>
-      <c r="B8" s="74" t="s">
+      <c r="B8" s="73" t="s">
         <v>451</v>
       </c>
       <c r="C8" s="35">
@@ -29010,11 +29061,11 @@
         <v>316</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A9" s="33" t="s">
         <v>176</v>
       </c>
-      <c r="B9" s="56" t="s">
+      <c r="B9" s="55" t="s">
         <v>513</v>
       </c>
       <c r="C9" s="35">
@@ -29024,11 +29075,11 @@
         <v>316</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A10" s="33" t="s">
         <v>177</v>
       </c>
-      <c r="B10" s="56" t="s">
+      <c r="B10" s="55" t="s">
         <v>513</v>
       </c>
       <c r="C10" s="35">
@@ -29038,12 +29089,12 @@
         <v>515</v>
       </c>
     </row>
-    <row r="11" spans="1:4" ht="34">
+    <row r="11" spans="1:4" ht="34" x14ac:dyDescent="0.45">
       <c r="A11" s="33" t="s">
         <v>178</v>
       </c>
       <c r="B11" s="33"/>
-      <c r="C11" s="55">
+      <c r="C11" s="54">
         <v>46279.645833333336</v>
       </c>
       <c r="D11" s="34" t="s">
@@ -29078,7 +29129,7 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:G16"/>
-  <sheetFormatPr defaultRowHeight="16"/>
+  <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="8.6640625" style="1"/>
     <col min="2" max="3" width="16.83203125" style="1" customWidth="1"/>
@@ -29091,31 +29142,31 @@
     <col min="11" max="16384" width="8.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="16.5" thickBot="1">
-      <c r="A1" s="39" t="s">
+    <row r="1" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A1" s="123" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="39" t="s">
+      <c r="B1" s="124" t="s">
         <v>24</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="124" t="s">
         <v>26</v>
       </c>
-      <c r="D1" s="39" t="s">
+      <c r="D1" s="124" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="39" t="s">
+      <c r="E1" s="124" t="s">
         <v>23</v>
       </c>
-      <c r="F1" s="39" t="s">
+      <c r="F1" s="124" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="39" t="s">
+      <c r="G1" s="125" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="90" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A2" s="89" t="s">
         <v>18</v>
       </c>
       <c r="B2" s="7" t="s">
@@ -29131,8 +29182,8 @@
       <c r="F2" s="9"/>
       <c r="G2" s="10"/>
     </row>
-    <row r="3" spans="1:7" ht="64">
-      <c r="A3" s="91"/>
+    <row r="3" spans="1:7" ht="64" x14ac:dyDescent="0.45">
+      <c r="A3" s="90"/>
       <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
@@ -29148,8 +29199,8 @@
       </c>
       <c r="G3" s="11"/>
     </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="91"/>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A4" s="90"/>
       <c r="B4" s="4" t="s">
         <v>184</v>
       </c>
@@ -29163,8 +29214,8 @@
       <c r="F4" s="3"/>
       <c r="G4" s="11"/>
     </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="91"/>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A5" s="90"/>
       <c r="B5" s="4" t="s">
         <v>2</v>
       </c>
@@ -29178,8 +29229,8 @@
       <c r="F5" s="3"/>
       <c r="G5" s="11"/>
     </row>
-    <row r="6" spans="1:7" ht="48">
-      <c r="A6" s="91"/>
+    <row r="6" spans="1:7" ht="48" x14ac:dyDescent="0.45">
+      <c r="A6" s="90"/>
       <c r="B6" s="4" t="s">
         <v>3</v>
       </c>
@@ -29197,8 +29248,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="16.5" thickBot="1">
-      <c r="A7" s="92"/>
+    <row r="7" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A7" s="91"/>
       <c r="B7" s="13" t="s">
         <v>15</v>
       </c>
@@ -29214,8 +29265,8 @@
       <c r="F7" s="14"/>
       <c r="G7" s="15"/>
     </row>
-    <row r="8" spans="1:7" ht="16.5" thickBot="1">
-      <c r="A8" s="93" t="s">
+    <row r="8" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A8" s="92" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="7" t="s">
@@ -29235,8 +29286,8 @@
         <v>221</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="94"/>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A9" s="93"/>
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -29252,8 +29303,8 @@
         <v>222</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="94"/>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A10" s="93"/>
       <c r="B10" s="4" t="s">
         <v>4</v>
       </c>
@@ -29269,8 +29320,8 @@
       <c r="F10" s="3"/>
       <c r="G10" s="11"/>
     </row>
-    <row r="11" spans="1:7" ht="16.5" thickBot="1">
-      <c r="A11" s="94"/>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A11" s="93"/>
       <c r="B11" s="4" t="s">
         <v>7</v>
       </c>
@@ -29284,8 +29335,8 @@
       <c r="F11" s="3"/>
       <c r="G11" s="11"/>
     </row>
-    <row r="12" spans="1:7" ht="16.5" thickBot="1">
-      <c r="A12" s="95"/>
+    <row r="12" spans="1:7" ht="16.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A12" s="94"/>
       <c r="B12" s="16" t="s">
         <v>8</v>
       </c>
@@ -29297,12 +29348,12 @@
       </c>
       <c r="E12" s="13"/>
       <c r="F12" s="14"/>
-      <c r="G12" s="10" t="s">
+      <c r="G12" s="122" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="96" t="s">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A13" s="95" t="s">
         <v>20</v>
       </c>
       <c r="B13" s="7" t="s">
@@ -29322,8 +29373,8 @@
         <v>226</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="64.5" thickBot="1">
-      <c r="A14" s="97"/>
+    <row r="14" spans="1:7" ht="64" x14ac:dyDescent="0.45">
+      <c r="A14" s="96"/>
       <c r="B14" s="4" t="s">
         <v>10</v>
       </c>
@@ -29333,14 +29384,14 @@
       <c r="D14" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="5"/>
+      <c r="E14" s="121"/>
       <c r="F14" s="2" t="s">
         <v>40</v>
       </c>
       <c r="G14" s="11"/>
     </row>
-    <row r="15" spans="1:7" ht="64">
-      <c r="A15" s="97"/>
+    <row r="15" spans="1:7" ht="64" x14ac:dyDescent="0.45">
+      <c r="A15" s="96"/>
       <c r="B15" s="4" t="s">
         <v>218</v>
       </c>
@@ -29350,7 +29401,7 @@
       <c r="D15" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="5" t="s">
         <v>223</v>
       </c>
       <c r="F15" s="6" t="s">
@@ -29360,8 +29411,8 @@
         <v>225</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="32.5" thickBot="1">
-      <c r="A16" s="98"/>
+    <row r="16" spans="1:7" ht="32.5" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A16" s="97"/>
       <c r="B16" s="16" t="s">
         <v>11</v>
       </c>
@@ -29373,7 +29424,7 @@
       </c>
       <c r="E16" s="13"/>
       <c r="F16" s="14"/>
-      <c r="G16" s="42" t="s">
+      <c r="G16" s="41" t="s">
         <v>219</v>
       </c>
     </row>
@@ -29394,7 +29445,7 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="60.83203125" customWidth="1"/>
@@ -29402,26 +29453,26 @@
     <col min="4" max="4" width="62.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="76"/>
-      <c r="B1" s="76" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A1" s="75"/>
+      <c r="B1" s="75" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2" s="41"/>
-      <c r="B2" s="40" t="s">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A2" s="40"/>
+      <c r="B2" s="39" t="s">
         <v>199</v>
       </c>
-      <c r="C2" s="40" t="s">
+      <c r="C2" s="39" t="s">
         <v>200</v>
       </c>
-      <c r="D2" s="40" t="s">
+      <c r="D2" s="39" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="32">
-      <c r="A3" s="40" t="s">
+    <row r="3" spans="1:4" ht="32" x14ac:dyDescent="0.45">
+      <c r="A3" s="39" t="s">
         <v>179</v>
       </c>
       <c r="B3" s="36" t="s">
@@ -29434,8 +29485,8 @@
         <v>203</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="64">
-      <c r="A4" s="40" t="s">
+    <row r="4" spans="1:4" ht="64" x14ac:dyDescent="0.45">
+      <c r="A4" s="39" t="s">
         <v>180</v>
       </c>
       <c r="B4" s="37" t="s">
@@ -29461,31 +29512,31 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:E75"/>
-  <sheetFormatPr defaultRowHeight="16"/>
+  <sheetFormatPr defaultRowHeight="16" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="32.58203125" style="45" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="21.1640625" style="45" customWidth="1"/>
-    <col min="3" max="3" width="57.9140625" style="45" customWidth="1"/>
-    <col min="4" max="4" width="16.08203125" style="45" customWidth="1"/>
-    <col min="5" max="5" width="17.08203125" style="45" customWidth="1"/>
-    <col min="6" max="16384" width="8.6640625" style="45"/>
+    <col min="1" max="1" width="32.58203125" style="44" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.1640625" style="44" customWidth="1"/>
+    <col min="3" max="3" width="57.9140625" style="44" customWidth="1"/>
+    <col min="4" max="4" width="16.08203125" style="44" customWidth="1"/>
+    <col min="5" max="5" width="17.08203125" style="44" customWidth="1"/>
+    <col min="6" max="16384" width="8.6640625" style="44"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="40" t="s">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A1" s="39" t="s">
         <v>194</v>
       </c>
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="39" t="s">
         <v>195</v>
       </c>
-      <c r="C1" s="40" t="s">
+      <c r="C1" s="39" t="s">
         <v>196</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="39" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A2" s="36" t="s">
         <v>186</v>
       </c>
@@ -29495,546 +29546,558 @@
       <c r="C2" s="36" t="s">
         <v>229</v>
       </c>
-      <c r="D2" s="50" t="s">
+      <c r="D2" s="49" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="64">
+    <row r="3" spans="1:4" ht="64" x14ac:dyDescent="0.45">
       <c r="A3" s="36" t="s">
         <v>189</v>
       </c>
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="45" t="s">
         <v>227</v>
       </c>
       <c r="C3" s="37" t="s">
         <v>198</v>
       </c>
-      <c r="D3" s="50" t="s">
+      <c r="D3" s="49" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="100" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A5" s="105" t="s">
         <v>273</v>
       </c>
-      <c r="B5" s="100"/>
-      <c r="C5" s="100"/>
+      <c r="B5" s="105"/>
+      <c r="C5" s="105"/>
     </row>
-    <row r="6" spans="1:4" ht="32">
-      <c r="A6" s="112" t="s">
+    <row r="6" spans="1:4" ht="32" x14ac:dyDescent="0.45">
+      <c r="A6" s="107" t="s">
         <v>204</v>
       </c>
-      <c r="B6" s="47" t="s">
+      <c r="B6" s="46" t="s">
         <v>205</v>
       </c>
-      <c r="C6" s="48" t="s">
+      <c r="C6" s="47" t="s">
         <v>294</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="32">
-      <c r="A7" s="113"/>
-      <c r="B7" s="47" t="s">
+    <row r="7" spans="1:4" ht="32" x14ac:dyDescent="0.45">
+      <c r="A7" s="108"/>
+      <c r="B7" s="46" t="s">
         <v>292</v>
       </c>
-      <c r="C7" s="48" t="s">
+      <c r="C7" s="47" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="32">
-      <c r="A8" s="113"/>
-      <c r="B8" s="47" t="s">
+    <row r="8" spans="1:4" ht="32" x14ac:dyDescent="0.45">
+      <c r="A8" s="108"/>
+      <c r="B8" s="46" t="s">
         <v>295</v>
       </c>
-      <c r="C8" s="48" t="s">
+      <c r="C8" s="47" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="113"/>
-      <c r="B9" s="47" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A9" s="108"/>
+      <c r="B9" s="46" t="s">
         <v>303</v>
       </c>
-      <c r="C9" s="57" t="s">
+      <c r="C9" s="56" t="s">
         <v>315</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="114"/>
-      <c r="B10" s="47" t="s">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A10" s="109"/>
+      <c r="B10" s="46" t="s">
         <v>297</v>
       </c>
-      <c r="C10" s="48" t="s">
+      <c r="C10" s="47" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="54" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A11" s="53" t="s">
         <v>293</v>
       </c>
-      <c r="B11" s="47" t="s">
+      <c r="B11" s="46" t="s">
         <v>206</v>
       </c>
-      <c r="C11" s="48" t="s">
+      <c r="C11" s="47" t="s">
         <v>207</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
-      <c r="C12" s="49"/>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="C12" s="48"/>
     </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="105" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A13" s="99" t="s">
         <v>304</v>
       </c>
-      <c r="B13" s="106"/>
-      <c r="C13" s="107"/>
+      <c r="B13" s="100"/>
+      <c r="C13" s="101"/>
     </row>
-    <row r="14" spans="1:4" ht="52" customHeight="1">
-      <c r="A14" s="115" t="s">
+    <row r="14" spans="1:4" ht="52" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="110" t="s">
         <v>230</v>
       </c>
-      <c r="B14" s="116"/>
-      <c r="C14" s="117"/>
+      <c r="B14" s="111"/>
+      <c r="C14" s="112"/>
     </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="49"/>
-      <c r="C19" s="49"/>
-      <c r="D19" s="49"/>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A19" s="48"/>
+      <c r="C19" s="48"/>
+      <c r="D19" s="48"/>
     </row>
-    <row r="31" spans="1:4">
-      <c r="A31" s="100" t="s">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A31" s="105" t="s">
         <v>274</v>
       </c>
-      <c r="B31" s="100"/>
-      <c r="C31" s="100"/>
+      <c r="B31" s="105"/>
+      <c r="C31" s="105"/>
     </row>
-    <row r="32" spans="1:4">
-      <c r="A32" s="108" t="s">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A32" s="102" t="s">
         <v>318</v>
       </c>
-      <c r="B32" s="109"/>
-      <c r="C32" s="110"/>
+      <c r="B32" s="103"/>
+      <c r="C32" s="104"/>
     </row>
-    <row r="33" spans="1:5" ht="51" customHeight="1">
-      <c r="A33" s="104" t="s">
+    <row r="33" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="98" t="s">
         <v>231</v>
       </c>
-      <c r="B33" s="50" t="s">
+      <c r="B33" s="49" t="s">
         <v>208</v>
       </c>
-      <c r="C33" s="111" t="s">
+      <c r="C33" s="106" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="104"/>
-      <c r="B34" s="50" t="s">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A34" s="98"/>
+      <c r="B34" s="49" t="s">
         <v>209</v>
       </c>
-      <c r="C34" s="111"/>
+      <c r="C34" s="106"/>
     </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="104"/>
-      <c r="B35" s="50" t="s">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A35" s="98"/>
+      <c r="B35" s="49" t="s">
         <v>210</v>
       </c>
-      <c r="C35" s="111"/>
+      <c r="C35" s="106"/>
     </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="104"/>
-      <c r="B36" s="50" t="s">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A36" s="98"/>
+      <c r="B36" s="49" t="s">
         <v>211</v>
       </c>
-      <c r="C36" s="111"/>
+      <c r="C36" s="106"/>
     </row>
-    <row r="37" spans="1:5" ht="32">
-      <c r="A37" s="104"/>
-      <c r="B37" s="48" t="s">
+    <row r="37" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+      <c r="A37" s="98"/>
+      <c r="B37" s="47" t="s">
         <v>212</v>
       </c>
-      <c r="C37" s="111"/>
+      <c r="C37" s="106"/>
     </row>
-    <row r="38" spans="1:5" ht="51" customHeight="1">
-      <c r="A38" s="104" t="s">
+    <row r="38" spans="1:5" ht="51" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="98" t="s">
         <v>232</v>
       </c>
-      <c r="B38" s="50" t="s">
+      <c r="B38" s="49" t="s">
         <v>213</v>
       </c>
-      <c r="C38" s="111" t="s">
+      <c r="C38" s="106" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="104"/>
-      <c r="B39" s="50" t="s">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A39" s="98"/>
+      <c r="B39" s="49" t="s">
         <v>214</v>
       </c>
-      <c r="C39" s="111"/>
+      <c r="C39" s="106"/>
     </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="104"/>
-      <c r="B40" s="50" t="s">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A40" s="98"/>
+      <c r="B40" s="49" t="s">
         <v>215</v>
       </c>
-      <c r="C40" s="111"/>
+      <c r="C40" s="106"/>
     </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="105" t="s">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A42" s="99" t="s">
         <v>272</v>
       </c>
-      <c r="B42" s="106"/>
-      <c r="C42" s="107"/>
+      <c r="B42" s="100"/>
+      <c r="C42" s="101"/>
     </row>
-    <row r="43" spans="1:5" ht="53" customHeight="1">
-      <c r="A43" s="104" t="s">
+    <row r="43" spans="1:5" ht="53" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A43" s="98" t="s">
         <v>217</v>
       </c>
-      <c r="B43" s="104"/>
-      <c r="C43" s="104"/>
+      <c r="B43" s="98"/>
+      <c r="C43" s="98"/>
     </row>
-    <row r="44" spans="1:5" ht="50.5" customHeight="1">
-      <c r="A44" s="104" t="s">
+    <row r="44" spans="1:5" ht="50.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A44" s="98" t="s">
         <v>317</v>
       </c>
-      <c r="B44" s="104"/>
-      <c r="C44" s="104"/>
+      <c r="B44" s="98"/>
+      <c r="C44" s="98"/>
     </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="100" t="s">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A46" s="105" t="s">
         <v>271</v>
       </c>
-      <c r="B46" s="100"/>
-      <c r="C46" s="100"/>
-      <c r="D46" s="100"/>
-      <c r="E46" s="100"/>
+      <c r="B46" s="105"/>
+      <c r="C46" s="105"/>
+      <c r="D46" s="105"/>
+      <c r="E46" s="105"/>
     </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="44" t="s">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A47" s="43" t="s">
         <v>233</v>
       </c>
-      <c r="B47" s="44" t="s">
+      <c r="B47" s="43" t="s">
         <v>242</v>
       </c>
-      <c r="C47" s="44" t="s">
+      <c r="C47" s="43" t="s">
         <v>243</v>
       </c>
-      <c r="D47" s="44" t="s">
+      <c r="D47" s="43" t="s">
         <v>244</v>
       </c>
-      <c r="E47" s="44" t="s">
+      <c r="E47" s="43" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="48" spans="1:5" ht="32">
-      <c r="A48" s="43" t="s">
+    <row r="48" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+      <c r="A48" s="42" t="s">
         <v>306</v>
       </c>
-      <c r="B48" s="43" t="s">
+      <c r="B48" s="42" t="s">
         <v>234</v>
       </c>
-      <c r="C48" s="43" t="s">
+      <c r="C48" s="42" t="s">
         <v>307</v>
       </c>
-      <c r="D48" s="43" t="s">
+      <c r="D48" s="42" t="s">
         <v>235</v>
       </c>
-      <c r="E48" s="43" t="s">
+      <c r="E48" s="42" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="49" spans="1:5" ht="32">
-      <c r="A49" s="43" t="s">
+    <row r="49" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+      <c r="A49" s="42" t="s">
         <v>308</v>
       </c>
-      <c r="B49" s="43" t="s">
+      <c r="B49" s="42" t="s">
         <v>237</v>
       </c>
-      <c r="C49" s="43" t="s">
+      <c r="C49" s="42" t="s">
         <v>246</v>
       </c>
-      <c r="D49" s="43" t="s">
+      <c r="D49" s="42" t="s">
         <v>235</v>
       </c>
-      <c r="E49" s="43" t="s">
+      <c r="E49" s="42" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="50" spans="1:5" ht="48">
-      <c r="A50" s="43" t="s">
+    <row r="50" spans="1:5" ht="48" x14ac:dyDescent="0.45">
+      <c r="A50" s="42" t="s">
         <v>309</v>
       </c>
-      <c r="B50" s="43" t="s">
+      <c r="B50" s="42" t="s">
         <v>237</v>
       </c>
-      <c r="C50" s="43" t="s">
+      <c r="C50" s="42" t="s">
         <v>314</v>
       </c>
-      <c r="D50" s="43" t="s">
+      <c r="D50" s="42" t="s">
         <v>238</v>
       </c>
-      <c r="E50" s="43" t="s">
+      <c r="E50" s="42" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="51" spans="1:5" ht="32">
-      <c r="A51" s="43" t="s">
+    <row r="51" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+      <c r="A51" s="42" t="s">
         <v>248</v>
       </c>
-      <c r="B51" s="43" t="s">
+      <c r="B51" s="42" t="s">
         <v>239</v>
       </c>
-      <c r="C51" s="43" t="s">
+      <c r="C51" s="42" t="s">
         <v>249</v>
       </c>
-      <c r="D51" s="43" t="s">
+      <c r="D51" s="42" t="s">
         <v>240</v>
       </c>
-      <c r="E51" s="43" t="s">
+      <c r="E51" s="42" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="52" spans="1:5" ht="32">
-      <c r="A52" s="43" t="s">
+    <row r="52" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+      <c r="A52" s="42" t="s">
         <v>250</v>
       </c>
-      <c r="B52" s="43" t="s">
+      <c r="B52" s="42" t="s">
         <v>239</v>
       </c>
-      <c r="C52" s="43" t="s">
+      <c r="C52" s="42" t="s">
         <v>251</v>
       </c>
-      <c r="D52" s="43" t="s">
+      <c r="D52" s="42" t="s">
         <v>240</v>
       </c>
-      <c r="E52" s="43" t="s">
+      <c r="E52" s="42" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="53" spans="1:5" ht="32">
-      <c r="A53" s="43" t="s">
+    <row r="53" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+      <c r="A53" s="42" t="s">
         <v>252</v>
       </c>
-      <c r="B53" s="43" t="s">
+      <c r="B53" s="42" t="s">
         <v>239</v>
       </c>
-      <c r="C53" s="43" t="s">
+      <c r="C53" s="42" t="s">
         <v>313</v>
       </c>
-      <c r="D53" s="43" t="s">
+      <c r="D53" s="42" t="s">
         <v>241</v>
       </c>
-      <c r="E53" s="43" t="s">
+      <c r="E53" s="42" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
-      <c r="A54" s="43" t="s">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A54" s="42" t="s">
         <v>310</v>
       </c>
-      <c r="B54" s="43" t="s">
+      <c r="B54" s="42" t="s">
         <v>239</v>
       </c>
-      <c r="C54" s="43" t="s">
+      <c r="C54" s="42" t="s">
         <v>312</v>
       </c>
-      <c r="D54" s="43" t="s">
+      <c r="D54" s="42" t="s">
         <v>235</v>
       </c>
-      <c r="E54" s="43" t="s">
+      <c r="E54" s="42" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="55" spans="1:5" ht="32">
-      <c r="A55" s="43" t="s">
+    <row r="55" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+      <c r="A55" s="42" t="s">
         <v>311</v>
       </c>
-      <c r="B55" s="43" t="s">
+      <c r="B55" s="42" t="s">
         <v>239</v>
       </c>
-      <c r="C55" s="43" t="s">
+      <c r="C55" s="42" t="s">
         <v>253</v>
       </c>
-      <c r="D55" s="43" t="s">
+      <c r="D55" s="42" t="s">
         <v>241</v>
       </c>
-      <c r="E55" s="43" t="s">
+      <c r="E55" s="42" t="s">
         <v>254</v>
       </c>
     </row>
-    <row r="56" spans="1:5" ht="48">
-      <c r="A56" s="43"/>
-      <c r="B56" s="43" t="s">
+    <row r="56" spans="1:5" ht="48" x14ac:dyDescent="0.45">
+      <c r="A56" s="42"/>
+      <c r="B56" s="42" t="s">
         <v>255</v>
       </c>
-      <c r="C56" s="43" t="s">
+      <c r="C56" s="42" t="s">
         <v>257</v>
       </c>
-      <c r="D56" s="43" t="s">
+      <c r="D56" s="42" t="s">
         <v>258</v>
       </c>
-      <c r="E56" s="51" t="s">
+      <c r="E56" s="50" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="57" spans="1:5" ht="48">
-      <c r="A57" s="43"/>
-      <c r="B57" s="43" t="s">
+    <row r="57" spans="1:5" ht="48" x14ac:dyDescent="0.45">
+      <c r="A57" s="42"/>
+      <c r="B57" s="42" t="s">
         <v>256</v>
       </c>
-      <c r="C57" s="43" t="s">
+      <c r="C57" s="42" t="s">
         <v>259</v>
       </c>
-      <c r="D57" s="43" t="s">
+      <c r="D57" s="42" t="s">
         <v>260</v>
       </c>
-      <c r="E57" s="51" t="s">
+      <c r="E57" s="50" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
-      <c r="A59" s="101" t="s">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A59" s="114" t="s">
         <v>275</v>
       </c>
-      <c r="B59" s="102"/>
-      <c r="C59" s="103"/>
+      <c r="B59" s="115"/>
+      <c r="C59" s="116"/>
     </row>
-    <row r="60" spans="1:5">
-      <c r="A60" s="53" t="s">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A60" s="52" t="s">
         <v>276</v>
       </c>
-      <c r="B60" s="53" t="s">
+      <c r="B60" s="52" t="s">
         <v>277</v>
       </c>
-      <c r="C60" s="53" t="s">
+      <c r="C60" s="52" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="61" spans="1:5" ht="32">
-      <c r="A61" s="52" t="s">
+    <row r="61" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+      <c r="A61" s="51" t="s">
         <v>279</v>
       </c>
-      <c r="B61" s="52" t="s">
+      <c r="B61" s="51" t="s">
         <v>280</v>
       </c>
-      <c r="C61" s="52" t="s">
+      <c r="C61" s="51" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="62" spans="1:5" ht="32">
-      <c r="A62" s="52" t="s">
+    <row r="62" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+      <c r="A62" s="51" t="s">
         <v>282</v>
       </c>
-      <c r="B62" s="52" t="s">
+      <c r="B62" s="51" t="s">
         <v>283</v>
       </c>
-      <c r="C62" s="52" t="s">
+      <c r="C62" s="51" t="s">
         <v>284</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="32">
-      <c r="A63" s="52" t="s">
+    <row r="63" spans="1:5" ht="32" x14ac:dyDescent="0.45">
+      <c r="A63" s="51" t="s">
         <v>285</v>
       </c>
-      <c r="B63" s="52" t="s">
+      <c r="B63" s="51" t="s">
         <v>286</v>
       </c>
-      <c r="C63" s="52" t="s">
+      <c r="C63" s="51" t="s">
         <v>287</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
-      <c r="A64" s="52" t="s">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A64" s="51" t="s">
         <v>288</v>
       </c>
-      <c r="B64" s="52" t="s">
+      <c r="B64" s="51" t="s">
         <v>289</v>
       </c>
-      <c r="C64" s="52" t="s">
+      <c r="C64" s="51" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="66" spans="1:4">
-      <c r="A66" s="100" t="s">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A66" s="105" t="s">
         <v>291</v>
       </c>
-      <c r="B66" s="100"/>
-      <c r="C66" s="100"/>
-      <c r="D66" s="100"/>
+      <c r="B66" s="105"/>
+      <c r="C66" s="105"/>
+      <c r="D66" s="105"/>
     </row>
-    <row r="67" spans="1:4">
-      <c r="A67" s="99" t="s">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A67" s="113" t="s">
         <v>262</v>
       </c>
-      <c r="B67" s="99"/>
-      <c r="C67" s="99"/>
-      <c r="D67" s="99"/>
+      <c r="B67" s="113"/>
+      <c r="C67" s="113"/>
+      <c r="D67" s="113"/>
     </row>
-    <row r="68" spans="1:4">
-      <c r="A68" s="99" t="s">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A68" s="113" t="s">
         <v>263</v>
       </c>
-      <c r="B68" s="99"/>
-      <c r="C68" s="99"/>
-      <c r="D68" s="99"/>
+      <c r="B68" s="113"/>
+      <c r="C68" s="113"/>
+      <c r="D68" s="113"/>
     </row>
-    <row r="69" spans="1:4">
-      <c r="A69" s="99" t="s">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A69" s="113" t="s">
         <v>264</v>
       </c>
-      <c r="B69" s="99"/>
-      <c r="C69" s="99"/>
-      <c r="D69" s="99"/>
+      <c r="B69" s="113"/>
+      <c r="C69" s="113"/>
+      <c r="D69" s="113"/>
     </row>
-    <row r="70" spans="1:4">
-      <c r="A70" s="99" t="s">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A70" s="113" t="s">
         <v>265</v>
       </c>
-      <c r="B70" s="99"/>
-      <c r="C70" s="99"/>
-      <c r="D70" s="99"/>
+      <c r="B70" s="113"/>
+      <c r="C70" s="113"/>
+      <c r="D70" s="113"/>
     </row>
-    <row r="71" spans="1:4">
-      <c r="A71" s="99" t="s">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A71" s="113" t="s">
         <v>266</v>
       </c>
-      <c r="B71" s="99"/>
-      <c r="C71" s="99"/>
-      <c r="D71" s="99"/>
+      <c r="B71" s="113"/>
+      <c r="C71" s="113"/>
+      <c r="D71" s="113"/>
     </row>
-    <row r="72" spans="1:4">
-      <c r="A72" s="99" t="s">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A72" s="113" t="s">
         <v>267</v>
       </c>
-      <c r="B72" s="99"/>
-      <c r="C72" s="99"/>
-      <c r="D72" s="99"/>
+      <c r="B72" s="113"/>
+      <c r="C72" s="113"/>
+      <c r="D72" s="113"/>
     </row>
-    <row r="73" spans="1:4">
-      <c r="A73" s="99" t="s">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A73" s="113" t="s">
         <v>268</v>
       </c>
-      <c r="B73" s="99"/>
-      <c r="C73" s="99"/>
-      <c r="D73" s="99"/>
+      <c r="B73" s="113"/>
+      <c r="C73" s="113"/>
+      <c r="D73" s="113"/>
     </row>
-    <row r="74" spans="1:4">
-      <c r="A74" s="99" t="s">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A74" s="113" t="s">
         <v>269</v>
       </c>
-      <c r="B74" s="99"/>
-      <c r="C74" s="99"/>
-      <c r="D74" s="99"/>
+      <c r="B74" s="113"/>
+      <c r="C74" s="113"/>
+      <c r="D74" s="113"/>
     </row>
-    <row r="75" spans="1:4">
-      <c r="A75" s="99" t="s">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A75" s="113" t="s">
         <v>270</v>
       </c>
-      <c r="B75" s="99"/>
-      <c r="C75" s="99"/>
-      <c r="D75" s="99"/>
+      <c r="B75" s="113"/>
+      <c r="C75" s="113"/>
+      <c r="D75" s="113"/>
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="A73:D73"/>
+    <mergeCell ref="A74:D74"/>
+    <mergeCell ref="A75:D75"/>
+    <mergeCell ref="A46:E46"/>
+    <mergeCell ref="A66:D66"/>
+    <mergeCell ref="A59:C59"/>
+    <mergeCell ref="A67:D67"/>
+    <mergeCell ref="A68:D68"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="A70:D70"/>
+    <mergeCell ref="A71:D71"/>
+    <mergeCell ref="A72:D72"/>
     <mergeCell ref="A44:C44"/>
     <mergeCell ref="A42:C42"/>
     <mergeCell ref="A32:C32"/>
@@ -30048,18 +30111,6 @@
     <mergeCell ref="A14:C14"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A43:C43"/>
-    <mergeCell ref="A73:D73"/>
-    <mergeCell ref="A74:D74"/>
-    <mergeCell ref="A75:D75"/>
-    <mergeCell ref="A46:E46"/>
-    <mergeCell ref="A66:D66"/>
-    <mergeCell ref="A59:C59"/>
-    <mergeCell ref="A67:D67"/>
-    <mergeCell ref="A68:D68"/>
-    <mergeCell ref="A69:D69"/>
-    <mergeCell ref="A70:D70"/>
-    <mergeCell ref="A71:D71"/>
-    <mergeCell ref="A72:D72"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -30073,7 +30124,7 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -30087,7 +30138,7 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:H23"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="5.33203125" style="20" customWidth="1"/>
     <col min="2" max="2" width="56.25" customWidth="1"/>
@@ -30099,278 +30150,280 @@
     <col min="8" max="8" width="54.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
-      <c r="A1" s="118" t="s">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A1" s="117" t="s">
         <v>335</v>
       </c>
-      <c r="B1" s="119"/>
+      <c r="B1" s="118"/>
     </row>
-    <row r="2" spans="1:8">
-      <c r="A2" s="60" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A2" s="59" t="s">
         <v>336</v>
       </c>
       <c r="B2" s="38" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="34">
-      <c r="A3" s="61">
+    <row r="3" spans="1:8" ht="34" x14ac:dyDescent="0.45">
+      <c r="A3" s="60">
         <v>1</v>
       </c>
       <c r="B3" s="18" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="61">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A4" s="60">
         <v>2</v>
       </c>
-      <c r="B4" s="58" t="s">
+      <c r="B4" s="57" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="61">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A5" s="60">
         <v>3</v>
       </c>
-      <c r="B5" s="58" t="s">
+      <c r="B5" s="57" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="60" t="s">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A7" s="59" t="s">
         <v>336</v>
       </c>
-      <c r="B7" s="59" t="s">
+      <c r="B7" s="58" t="s">
         <v>334</v>
       </c>
-      <c r="C7" s="59" t="s">
+      <c r="C7" s="58" t="s">
         <v>333</v>
       </c>
-      <c r="D7" s="59" t="s">
+      <c r="D7" s="58" t="s">
         <v>341</v>
       </c>
-      <c r="E7" s="59" t="s">
+      <c r="E7" s="58" t="s">
         <v>369</v>
       </c>
-      <c r="F7" s="59" t="s">
+      <c r="F7" s="58" t="s">
         <v>370</v>
       </c>
-      <c r="H7" s="59" t="s">
+      <c r="H7" s="58" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="61">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A8" s="60">
         <v>1</v>
       </c>
-      <c r="B8" s="58" t="s">
+      <c r="B8" s="57" t="s">
         <v>320</v>
       </c>
-      <c r="C8" s="63" t="s">
+      <c r="C8" s="62" t="s">
         <v>340</v>
       </c>
-      <c r="D8" s="65"/>
-      <c r="E8" s="65"/>
-      <c r="F8" s="65"/>
+      <c r="D8" s="64"/>
+      <c r="E8" s="64"/>
+      <c r="F8" s="64"/>
       <c r="H8" s="18" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="238">
-      <c r="A9" s="61">
+    <row r="9" spans="1:8" ht="238" x14ac:dyDescent="0.45">
+      <c r="A9" s="60">
         <v>2</v>
       </c>
-      <c r="B9" s="58" t="s">
+      <c r="B9" s="57" t="s">
         <v>321</v>
       </c>
-      <c r="C9" s="58" t="s">
+      <c r="C9" s="57" t="s">
         <v>342</v>
       </c>
       <c r="D9" s="18" t="s">
         <v>365</v>
       </c>
-      <c r="E9" s="58" t="s">
+      <c r="E9" s="57" t="s">
         <v>372</v>
       </c>
       <c r="F9" s="18" t="s">
         <v>374</v>
       </c>
-      <c r="H9" s="58" t="s">
+      <c r="H9" s="57" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="61">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A10" s="60">
         <v>3</v>
       </c>
-      <c r="B10" s="58" t="s">
+      <c r="B10" s="57" t="s">
         <v>322</v>
       </c>
-      <c r="C10" s="63" t="s">
+      <c r="C10" s="62" t="s">
         <v>340</v>
       </c>
-      <c r="D10" s="65"/>
-      <c r="E10" s="65"/>
-      <c r="F10" s="65"/>
-      <c r="H10" s="58" t="s">
+      <c r="D10" s="64"/>
+      <c r="E10" s="64"/>
+      <c r="F10" s="64"/>
+      <c r="H10" s="57" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="102">
-      <c r="A11" s="61">
+    <row r="11" spans="1:8" ht="102" x14ac:dyDescent="0.45">
+      <c r="A11" s="60">
         <v>4</v>
       </c>
-      <c r="B11" s="58" t="s">
+      <c r="B11" s="57" t="s">
         <v>323</v>
       </c>
-      <c r="C11" s="58" t="s">
+      <c r="C11" s="57" t="s">
         <v>343</v>
       </c>
       <c r="D11" s="18" t="s">
         <v>366</v>
       </c>
-      <c r="E11" s="58" t="s">
+      <c r="E11" s="57" t="s">
         <v>372</v>
       </c>
       <c r="F11" s="18" t="s">
         <v>373</v>
       </c>
-      <c r="H11" s="58" t="s">
+      <c r="H11" s="57" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="68">
-      <c r="A12" s="61">
+    <row r="12" spans="1:8" ht="68" x14ac:dyDescent="0.45">
+      <c r="A12" s="60">
         <v>5</v>
       </c>
-      <c r="B12" s="58" t="s">
+      <c r="B12" s="57" t="s">
         <v>324</v>
       </c>
-      <c r="C12" s="58" t="s">
+      <c r="C12" s="57" t="s">
         <v>344</v>
       </c>
       <c r="D12" s="18" t="s">
         <v>367</v>
       </c>
-      <c r="E12" s="58" t="s">
+      <c r="E12" s="57" t="s">
         <v>371</v>
       </c>
       <c r="F12" s="18" t="s">
         <v>384</v>
       </c>
-      <c r="H12" s="58" t="s">
+      <c r="H12" s="57" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="68">
-      <c r="A13" s="61">
+    <row r="13" spans="1:8" ht="68" x14ac:dyDescent="0.45">
+      <c r="A13" s="60">
         <v>6</v>
       </c>
-      <c r="B13" s="58" t="s">
+      <c r="B13" s="57" t="s">
         <v>325</v>
       </c>
-      <c r="C13" s="58" t="s">
+      <c r="C13" s="57" t="s">
         <v>345</v>
       </c>
       <c r="D13" s="18" t="s">
         <v>348</v>
       </c>
-      <c r="E13" s="58" t="s">
+      <c r="E13" s="57" t="s">
         <v>371</v>
       </c>
       <c r="F13" s="18" t="s">
         <v>375</v>
       </c>
-      <c r="H13" s="58" t="s">
+      <c r="H13" s="57" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
-      <c r="A14" s="61">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A14" s="60">
         <v>7</v>
       </c>
-      <c r="B14" s="58" t="s">
+      <c r="B14" s="57" t="s">
         <v>326</v>
       </c>
-      <c r="C14" s="63" t="s">
+      <c r="C14" s="62" t="s">
         <v>340</v>
       </c>
-      <c r="D14" s="65"/>
-      <c r="E14" s="65"/>
-      <c r="F14" s="65"/>
-      <c r="H14" s="58" t="s">
+      <c r="D14" s="64"/>
+      <c r="E14" s="64"/>
+      <c r="F14" s="64"/>
+      <c r="H14" s="57" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="136">
-      <c r="A15" s="61">
+    <row r="15" spans="1:8" ht="136" x14ac:dyDescent="0.45">
+      <c r="A15" s="60">
         <v>8</v>
       </c>
-      <c r="B15" s="58" t="s">
+      <c r="B15" s="57" t="s">
         <v>327</v>
       </c>
-      <c r="C15" s="58" t="s">
+      <c r="C15" s="57" t="s">
         <v>346</v>
       </c>
       <c r="D15" s="18" t="s">
         <v>349</v>
       </c>
-      <c r="E15" s="58" t="s">
+      <c r="E15" s="57" t="s">
         <v>388</v>
       </c>
       <c r="F15" s="18" t="s">
         <v>387</v>
       </c>
-      <c r="H15" s="58" t="s">
+      <c r="H15" s="57" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="187">
-      <c r="A16" s="61">
+    <row r="16" spans="1:8" ht="187" x14ac:dyDescent="0.45">
+      <c r="A16" s="60">
         <v>9</v>
       </c>
-      <c r="B16" s="58" t="s">
+      <c r="B16" s="57" t="s">
         <v>328</v>
       </c>
-      <c r="C16" s="58" t="s">
+      <c r="C16" s="57" t="s">
         <v>346</v>
       </c>
       <c r="D16" s="18" t="s">
         <v>350</v>
       </c>
-      <c r="E16" s="58" t="s">
+      <c r="E16" s="57" t="s">
         <v>378</v>
       </c>
       <c r="F16" s="18" t="s">
         <v>386</v>
       </c>
+      <c r="H16" s="57"/>
     </row>
-    <row r="17" spans="1:6" ht="51">
-      <c r="A17" s="61">
+    <row r="17" spans="1:8" ht="51" x14ac:dyDescent="0.45">
+      <c r="A17" s="60">
         <v>10</v>
       </c>
-      <c r="B17" s="58" t="s">
+      <c r="B17" s="57" t="s">
         <v>329</v>
       </c>
-      <c r="C17" s="58" t="s">
+      <c r="C17" s="57" t="s">
         <v>346</v>
       </c>
       <c r="D17" s="18" t="s">
         <v>351</v>
       </c>
-      <c r="E17" s="58" t="s">
+      <c r="E17" s="57" t="s">
         <v>371</v>
       </c>
       <c r="F17" s="18" t="s">
         <v>376</v>
       </c>
+      <c r="H17" s="57"/>
     </row>
-    <row r="18" spans="1:6" ht="68">
-      <c r="A18" s="61">
+    <row r="18" spans="1:8" ht="68" x14ac:dyDescent="0.45">
+      <c r="A18" s="60">
         <v>11</v>
       </c>
-      <c r="B18" s="58" t="s">
+      <c r="B18" s="57" t="s">
         <v>330</v>
       </c>
       <c r="C18" s="18" t="s">
@@ -30379,81 +30432,85 @@
       <c r="D18" s="18" t="s">
         <v>352</v>
       </c>
-      <c r="E18" s="58" t="s">
+      <c r="E18" s="57" t="s">
         <v>378</v>
       </c>
       <c r="F18" s="18" t="s">
         <v>379</v>
       </c>
+      <c r="H18" s="57"/>
     </row>
-    <row r="19" spans="1:6" ht="68">
-      <c r="A19" s="61">
+    <row r="19" spans="1:8" ht="68" x14ac:dyDescent="0.45">
+      <c r="A19" s="60">
         <v>12</v>
       </c>
-      <c r="B19" s="58" t="s">
+      <c r="B19" s="57" t="s">
         <v>377</v>
       </c>
-      <c r="C19" s="58" t="s">
+      <c r="C19" s="57" t="s">
         <v>347</v>
       </c>
-      <c r="D19" s="58" t="s">
+      <c r="D19" s="57" t="s">
         <v>380</v>
       </c>
-      <c r="E19" s="58" t="s">
+      <c r="E19" s="57" t="s">
         <v>381</v>
       </c>
       <c r="F19" s="18" t="s">
         <v>385</v>
       </c>
+      <c r="H19" s="57"/>
     </row>
-    <row r="20" spans="1:6" ht="68">
-      <c r="A20" s="61">
+    <row r="20" spans="1:8" ht="68" x14ac:dyDescent="0.45">
+      <c r="A20" s="60">
         <v>13</v>
       </c>
-      <c r="B20" s="58" t="s">
+      <c r="B20" s="57" t="s">
         <v>332</v>
       </c>
-      <c r="C20" s="58" t="s">
+      <c r="C20" s="57" t="s">
         <v>345</v>
       </c>
-      <c r="D20" s="58" t="s">
+      <c r="D20" s="57" t="s">
         <v>353</v>
       </c>
-      <c r="E20" s="58" t="s">
+      <c r="E20" s="57" t="s">
         <v>371</v>
       </c>
       <c r="F20" s="18" t="s">
         <v>382</v>
       </c>
+      <c r="H20" s="57"/>
     </row>
-    <row r="21" spans="1:6" ht="85">
-      <c r="A21" s="61">
+    <row r="21" spans="1:8" ht="85" x14ac:dyDescent="0.45">
+      <c r="A21" s="60">
         <v>14</v>
       </c>
-      <c r="B21" s="58" t="s">
+      <c r="B21" s="57" t="s">
         <v>331</v>
       </c>
-      <c r="C21" s="58" t="s">
+      <c r="C21" s="57" t="s">
         <v>347</v>
       </c>
       <c r="D21" s="18" t="s">
         <v>354</v>
       </c>
-      <c r="E21" s="58" t="s">
+      <c r="E21" s="57" t="s">
         <v>378</v>
       </c>
-      <c r="F21" s="64" t="s">
+      <c r="F21" s="63" t="s">
         <v>383</v>
       </c>
+      <c r="H21" s="57"/>
     </row>
-    <row r="22" spans="1:6" ht="170">
-      <c r="A22" s="61" t="s">
+    <row r="22" spans="1:8" ht="170" x14ac:dyDescent="0.45">
+      <c r="A22" s="60" t="s">
         <v>389</v>
       </c>
       <c r="B22" s="18" t="s">
         <v>393</v>
       </c>
-      <c r="C22" s="58" t="s">
+      <c r="C22" s="57" t="s">
         <v>390</v>
       </c>
       <c r="D22" s="18" t="s">
@@ -30465,9 +30522,10 @@
       <c r="F22" s="18" t="s">
         <v>394</v>
       </c>
+      <c r="H22" s="57"/>
     </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="66" t="s">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A23" s="65" t="s">
         <v>395</v>
       </c>
     </row>
@@ -30489,348 +30547,348 @@
     <tabColor theme="9" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="5.33203125" style="45" customWidth="1"/>
-    <col min="2" max="2" width="49.5" style="45" customWidth="1"/>
-    <col min="3" max="3" width="13.4140625" style="45" customWidth="1"/>
-    <col min="4" max="6" width="77" style="45" customWidth="1"/>
-    <col min="7" max="7" width="55" style="69" customWidth="1"/>
-    <col min="8" max="8" width="39.9140625" style="45" customWidth="1"/>
-    <col min="9" max="16384" width="8.6640625" style="45"/>
+    <col min="1" max="1" width="5.33203125" style="44" customWidth="1"/>
+    <col min="2" max="2" width="49.5" style="44" customWidth="1"/>
+    <col min="3" max="3" width="13.4140625" style="44" customWidth="1"/>
+    <col min="4" max="6" width="77" style="44" customWidth="1"/>
+    <col min="7" max="7" width="55" style="68" customWidth="1"/>
+    <col min="8" max="8" width="39.9140625" style="44" customWidth="1"/>
+    <col min="9" max="16384" width="8.6640625" style="44"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="16">
-      <c r="A1" s="62" t="s">
+    <row r="1" spans="1:8" ht="16" x14ac:dyDescent="0.45">
+      <c r="A1" s="61" t="s">
         <v>336</v>
       </c>
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="39" t="s">
         <v>334</v>
       </c>
-      <c r="C1" s="40" t="s">
+      <c r="C1" s="39" t="s">
         <v>195</v>
       </c>
-      <c r="D1" s="75" t="s">
+      <c r="D1" s="74" t="s">
         <v>199</v>
       </c>
-      <c r="E1" s="75" t="s">
+      <c r="E1" s="74" t="s">
         <v>398</v>
       </c>
-      <c r="F1" s="75" t="s">
+      <c r="F1" s="74" t="s">
         <v>399</v>
       </c>
-      <c r="G1" s="40" t="s">
+      <c r="G1" s="39" t="s">
         <v>422</v>
       </c>
-      <c r="H1" s="40" t="s">
+      <c r="H1" s="39" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="256">
-      <c r="A2" s="68">
+    <row r="2" spans="1:8" ht="256" x14ac:dyDescent="0.45">
+      <c r="A2" s="67">
         <v>2</v>
       </c>
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="49" t="s">
         <v>321</v>
       </c>
-      <c r="C2" s="50" t="s">
+      <c r="C2" s="49" t="s">
         <v>372</v>
       </c>
-      <c r="D2" s="48" t="s">
+      <c r="D2" s="47" t="s">
         <v>374</v>
       </c>
-      <c r="E2" s="48" t="s">
+      <c r="E2" s="47" t="s">
         <v>397</v>
       </c>
-      <c r="F2" s="48" t="s">
+      <c r="F2" s="47" t="s">
         <v>409</v>
       </c>
-      <c r="G2" s="43" t="s">
+      <c r="G2" s="42" t="s">
         <v>424</v>
       </c>
-      <c r="H2" s="43" t="s">
+      <c r="H2" s="42" t="s">
         <v>425</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="208">
-      <c r="A3" s="68">
+    <row r="3" spans="1:8" ht="208" x14ac:dyDescent="0.45">
+      <c r="A3" s="67">
         <v>4</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="49" t="s">
         <v>323</v>
       </c>
-      <c r="C3" s="50" t="s">
+      <c r="C3" s="49" t="s">
         <v>372</v>
       </c>
-      <c r="D3" s="48" t="s">
+      <c r="D3" s="47" t="s">
         <v>373</v>
       </c>
-      <c r="E3" s="48" t="s">
+      <c r="E3" s="47" t="s">
         <v>400</v>
       </c>
-      <c r="F3" s="48" t="s">
+      <c r="F3" s="47" t="s">
         <v>410</v>
       </c>
-      <c r="G3" s="43" t="s">
+      <c r="G3" s="42" t="s">
         <v>426</v>
       </c>
-      <c r="H3" s="43" t="s">
+      <c r="H3" s="42" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="272">
-      <c r="A4" s="68">
+    <row r="4" spans="1:8" ht="272" x14ac:dyDescent="0.45">
+      <c r="A4" s="67">
         <v>5</v>
       </c>
-      <c r="B4" s="50" t="s">
+      <c r="B4" s="49" t="s">
         <v>324</v>
       </c>
-      <c r="C4" s="50" t="s">
+      <c r="C4" s="49" t="s">
         <v>371</v>
       </c>
-      <c r="D4" s="48" t="s">
+      <c r="D4" s="47" t="s">
         <v>384</v>
       </c>
-      <c r="E4" s="48" t="s">
+      <c r="E4" s="47" t="s">
         <v>401</v>
       </c>
-      <c r="F4" s="48" t="s">
+      <c r="F4" s="47" t="s">
         <v>411</v>
       </c>
-      <c r="G4" s="43" t="s">
+      <c r="G4" s="42" t="s">
         <v>428</v>
       </c>
-      <c r="H4" s="43" t="s">
+      <c r="H4" s="42" t="s">
         <v>429</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="192">
-      <c r="A5" s="68">
+    <row r="5" spans="1:8" ht="192" x14ac:dyDescent="0.45">
+      <c r="A5" s="67">
         <v>6</v>
       </c>
-      <c r="B5" s="50" t="s">
+      <c r="B5" s="49" t="s">
         <v>325</v>
       </c>
-      <c r="C5" s="50" t="s">
+      <c r="C5" s="49" t="s">
         <v>371</v>
       </c>
-      <c r="D5" s="48" t="s">
+      <c r="D5" s="47" t="s">
         <v>375</v>
       </c>
-      <c r="E5" s="48" t="s">
+      <c r="E5" s="47" t="s">
         <v>420</v>
       </c>
-      <c r="F5" s="48" t="s">
+      <c r="F5" s="47" t="s">
         <v>412</v>
       </c>
-      <c r="G5" s="43" t="s">
+      <c r="G5" s="42" t="s">
         <v>430</v>
       </c>
-      <c r="H5" s="43" t="s">
+      <c r="H5" s="42" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="192">
-      <c r="A6" s="68">
+    <row r="6" spans="1:8" ht="192" x14ac:dyDescent="0.45">
+      <c r="A6" s="67">
         <v>8</v>
       </c>
-      <c r="B6" s="50" t="s">
+      <c r="B6" s="49" t="s">
         <v>327</v>
       </c>
-      <c r="C6" s="50" t="s">
+      <c r="C6" s="49" t="s">
         <v>388</v>
       </c>
-      <c r="D6" s="48" t="s">
+      <c r="D6" s="47" t="s">
         <v>387</v>
       </c>
-      <c r="E6" s="48" t="s">
+      <c r="E6" s="47" t="s">
         <v>402</v>
       </c>
-      <c r="F6" s="48" t="s">
+      <c r="F6" s="47" t="s">
         <v>413</v>
       </c>
-      <c r="G6" s="43" t="s">
+      <c r="G6" s="42" t="s">
         <v>432</v>
       </c>
-      <c r="H6" s="43" t="s">
+      <c r="H6" s="42" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="224">
-      <c r="A7" s="68">
+    <row r="7" spans="1:8" ht="224" x14ac:dyDescent="0.45">
+      <c r="A7" s="67">
         <v>9</v>
       </c>
-      <c r="B7" s="50" t="s">
+      <c r="B7" s="49" t="s">
         <v>328</v>
       </c>
-      <c r="C7" s="50" t="s">
+      <c r="C7" s="49" t="s">
         <v>378</v>
       </c>
-      <c r="D7" s="48" t="s">
+      <c r="D7" s="47" t="s">
         <v>386</v>
       </c>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="47" t="s">
         <v>403</v>
       </c>
-      <c r="F7" s="48" t="s">
+      <c r="F7" s="47" t="s">
         <v>414</v>
       </c>
-      <c r="G7" s="43" t="s">
+      <c r="G7" s="42" t="s">
         <v>434</v>
       </c>
-      <c r="H7" s="43" t="s">
+      <c r="H7" s="42" t="s">
         <v>435</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="192">
-      <c r="A8" s="68">
+    <row r="8" spans="1:8" ht="192" x14ac:dyDescent="0.45">
+      <c r="A8" s="67">
         <v>10</v>
       </c>
-      <c r="B8" s="50" t="s">
+      <c r="B8" s="49" t="s">
         <v>329</v>
       </c>
-      <c r="C8" s="50" t="s">
+      <c r="C8" s="49" t="s">
         <v>371</v>
       </c>
-      <c r="D8" s="48" t="s">
+      <c r="D8" s="47" t="s">
         <v>376</v>
       </c>
-      <c r="E8" s="48" t="s">
+      <c r="E8" s="47" t="s">
         <v>404</v>
       </c>
-      <c r="F8" s="48" t="s">
+      <c r="F8" s="47" t="s">
         <v>415</v>
       </c>
-      <c r="G8" s="43" t="s">
+      <c r="G8" s="42" t="s">
         <v>436</v>
       </c>
-      <c r="H8" s="43" t="s">
+      <c r="H8" s="42" t="s">
         <v>437</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="332.5" customHeight="1">
-      <c r="A9" s="68">
+    <row r="9" spans="1:8" ht="332.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="67">
         <v>11</v>
       </c>
-      <c r="B9" s="50" t="s">
+      <c r="B9" s="49" t="s">
         <v>330</v>
       </c>
-      <c r="C9" s="50" t="s">
+      <c r="C9" s="49" t="s">
         <v>378</v>
       </c>
-      <c r="D9" s="48" t="s">
+      <c r="D9" s="47" t="s">
         <v>379</v>
       </c>
-      <c r="E9" s="48" t="s">
+      <c r="E9" s="47" t="s">
         <v>405</v>
       </c>
-      <c r="F9" s="48" t="s">
+      <c r="F9" s="47" t="s">
         <v>416</v>
       </c>
-      <c r="G9" s="43" t="s">
+      <c r="G9" s="42" t="s">
         <v>438</v>
       </c>
-      <c r="H9" s="43" t="s">
+      <c r="H9" s="42" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="272">
-      <c r="A10" s="68">
+    <row r="10" spans="1:8" ht="272" x14ac:dyDescent="0.45">
+      <c r="A10" s="67">
         <v>12</v>
       </c>
-      <c r="B10" s="50" t="s">
+      <c r="B10" s="49" t="s">
         <v>377</v>
       </c>
-      <c r="C10" s="50" t="s">
+      <c r="C10" s="49" t="s">
         <v>381</v>
       </c>
-      <c r="D10" s="48" t="s">
+      <c r="D10" s="47" t="s">
         <v>385</v>
       </c>
-      <c r="E10" s="48" t="s">
+      <c r="E10" s="47" t="s">
         <v>406</v>
       </c>
-      <c r="F10" s="48" t="s">
+      <c r="F10" s="47" t="s">
         <v>417</v>
       </c>
-      <c r="G10" s="43" t="s">
+      <c r="G10" s="42" t="s">
         <v>440</v>
       </c>
-      <c r="H10" s="43" t="s">
+      <c r="H10" s="42" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="11" spans="1:8" ht="224">
-      <c r="A11" s="68">
+    <row r="11" spans="1:8" ht="224" x14ac:dyDescent="0.45">
+      <c r="A11" s="67">
         <v>13</v>
       </c>
-      <c r="B11" s="50" t="s">
+      <c r="B11" s="49" t="s">
         <v>332</v>
       </c>
-      <c r="C11" s="50" t="s">
+      <c r="C11" s="49" t="s">
         <v>371</v>
       </c>
-      <c r="D11" s="48" t="s">
+      <c r="D11" s="47" t="s">
         <v>382</v>
       </c>
-      <c r="E11" s="48" t="s">
+      <c r="E11" s="47" t="s">
         <v>407</v>
       </c>
-      <c r="F11" s="48" t="s">
+      <c r="F11" s="47" t="s">
         <v>418</v>
       </c>
-      <c r="G11" s="43" t="s">
+      <c r="G11" s="42" t="s">
         <v>442</v>
       </c>
-      <c r="H11" s="43" t="s">
+      <c r="H11" s="42" t="s">
         <v>443</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="306.5" customHeight="1">
-      <c r="A12" s="68">
+    <row r="12" spans="1:8" ht="306.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="67">
         <v>14</v>
       </c>
-      <c r="B12" s="50" t="s">
+      <c r="B12" s="49" t="s">
         <v>331</v>
       </c>
-      <c r="C12" s="50" t="s">
+      <c r="C12" s="49" t="s">
         <v>378</v>
       </c>
       <c r="D12" s="37" t="s">
         <v>383</v>
       </c>
-      <c r="E12" s="48" t="s">
+      <c r="E12" s="47" t="s">
         <v>408</v>
       </c>
-      <c r="F12" s="48" t="s">
+      <c r="F12" s="47" t="s">
         <v>419</v>
       </c>
-      <c r="G12" s="43" t="s">
+      <c r="G12" s="42" t="s">
         <v>444</v>
       </c>
-      <c r="H12" s="43" t="s">
+      <c r="H12" s="42" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="144">
-      <c r="A13" s="68" t="s">
+    <row r="13" spans="1:8" ht="144" x14ac:dyDescent="0.45">
+      <c r="A13" s="67" t="s">
         <v>389</v>
       </c>
-      <c r="B13" s="48" t="s">
+      <c r="B13" s="47" t="s">
         <v>393</v>
       </c>
-      <c r="C13" s="48" t="s">
+      <c r="C13" s="47" t="s">
         <v>392</v>
       </c>
-      <c r="D13" s="48" t="s">
+      <c r="D13" s="47" t="s">
         <v>394</v>
       </c>
-      <c r="E13" s="50"/>
-      <c r="F13" s="50"/>
-      <c r="G13" s="43" t="s">
+      <c r="E13" s="49"/>
+      <c r="F13" s="49"/>
+      <c r="G13" s="42" t="s">
         <v>446</v>
       </c>
-      <c r="H13" s="43" t="s">
+      <c r="H13" s="42" t="s">
         <v>447</v>
       </c>
     </row>
@@ -30847,13 +30905,13 @@
     <tabColor theme="0" tint="-0.499984740745262"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="101.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="68">
-      <c r="A1" s="67" t="s">
+    <row r="1" spans="1:1" ht="68" x14ac:dyDescent="0.45">
+      <c r="A1" s="66" t="s">
         <v>396</v>
       </c>
     </row>
